--- a/jogos_2026-08-07.xlsx
+++ b/jogos_2026-08-07.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU138"/>
+  <dimension ref="A1:AU141"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G14">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O15">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P15">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>2026-08-07 12:30:00</t>
+          <t>2026-08-07 12:00:00</t>
         </is>
       </c>
     </row>
@@ -2870,12 +2870,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>2026-08-07 12:45:00</t>
+          <t>2026-08-07 12:30:00</t>
         </is>
       </c>
     </row>
@@ -3033,12 +3033,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G17">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>2026-08-07 13:00:00</t>
+          <t>2026-08-07 12:45:00</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G18">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G19">
@@ -3527,22 +3527,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="O20">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P20">
-        <v>6.17</v>
+        <v>0</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -3690,22 +3690,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>6.17</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -3853,22 +3853,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G22">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G23">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G24">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G25">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G26">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>2026-08-07 13:30:00</t>
+          <t>2026-08-07 13:00:00</t>
         </is>
       </c>
     </row>
@@ -4663,12 +4663,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G27">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>2026-08-07 13:30:00</t>
+          <t>2026-08-07 13:00:00</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G28">
@@ -4977,7 +4977,7 @@
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>2026-08-07 14:00:00</t>
+          <t>2026-08-07 13:30:00</t>
         </is>
       </c>
     </row>
@@ -4989,12 +4989,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G29">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>2026-08-07 14:00:00</t>
+          <t>2026-08-07 13:30:00</t>
         </is>
       </c>
     </row>
@@ -5157,22 +5157,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G30">
@@ -5320,7 +5320,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G31">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G32">
@@ -5646,22 +5646,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G33">
@@ -5809,7 +5809,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G34">
@@ -5972,7 +5972,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G35">
@@ -6135,22 +6135,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G36">
@@ -6293,27 +6293,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G37">
@@ -6444,7 +6444,7 @@
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>2026-08-07 14:30:00</t>
+          <t>2026-08-07 14:00:00</t>
         </is>
       </c>
     </row>
@@ -6456,27 +6456,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G38">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>2026-08-07 14:30:00</t>
+          <t>2026-08-07 14:00:00</t>
         </is>
       </c>
     </row>
@@ -6624,7 +6624,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G39">
@@ -6787,22 +6787,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G40">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G41">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G42">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>BSK Banja Luka</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G43">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>2026-08-07 15:00:00</t>
+          <t>2026-08-07 14:30:00</t>
         </is>
       </c>
     </row>
@@ -7434,12 +7434,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G44">
@@ -7585,7 +7585,7 @@
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>2026-08-07 15:00:00</t>
+          <t>2026-08-07 14:30:00</t>
         </is>
       </c>
     </row>
@@ -7602,7 +7602,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>BSK Banja Luka</t>
         </is>
       </c>
       <c r="G45">
@@ -7765,7 +7765,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G46">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G47">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G48">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G49">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G50">
@@ -8575,12 +8575,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G51">
@@ -8726,7 +8726,7 @@
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>2026-08-07 15:15:00</t>
+          <t>2026-08-07 15:00:00</t>
         </is>
       </c>
     </row>
@@ -8738,12 +8738,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G52">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>2026-08-07 15:15:00</t>
+          <t>2026-08-07 15:00:00</t>
         </is>
       </c>
     </row>
@@ -8901,12 +8901,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G53">
@@ -9052,7 +9052,7 @@
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>2026-08-07 15:30:00</t>
+          <t>2026-08-07 15:00:00</t>
         </is>
       </c>
     </row>
@@ -9064,12 +9064,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G54">
@@ -9215,7 +9215,7 @@
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>2026-08-07 15:30:00</t>
+          <t>2026-08-07 15:15:00</t>
         </is>
       </c>
     </row>
@@ -9227,12 +9227,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Wacker Innsbruck</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G55">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>2026-08-07 15:30:00</t>
+          <t>2026-08-07 15:15:00</t>
         </is>
       </c>
     </row>
@@ -9395,7 +9395,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G56">
@@ -9558,7 +9558,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G57">
@@ -9721,7 +9721,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Wacker Innsbruck</t>
         </is>
       </c>
       <c r="G58">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G59">
@@ -10042,12 +10042,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G60">
@@ -10193,7 +10193,7 @@
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>2026-08-07 15:45:00</t>
+          <t>2026-08-07 15:30:00</t>
         </is>
       </c>
     </row>
@@ -10205,27 +10205,27 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G61">
@@ -10356,7 +10356,7 @@
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>2026-08-07 15:45:00</t>
+          <t>2026-08-07 15:30:00</t>
         </is>
       </c>
     </row>
@@ -10368,27 +10368,27 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G62">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>2026-08-07 15:45:00</t>
+          <t>2026-08-07 15:30:00</t>
         </is>
       </c>
     </row>
@@ -10536,22 +10536,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G63">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G64">
@@ -10862,22 +10862,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G65">
@@ -11025,22 +11025,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>La Roche VF</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G66">
@@ -11188,22 +11188,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G67">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G68">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>La Roche VF</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G69">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G70">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G71">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="G72">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G73">
@@ -12329,22 +12329,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G74">
@@ -12492,22 +12492,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G75">
@@ -12655,22 +12655,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G76">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G77">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G78">
@@ -13144,22 +13144,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,13 +13186,13 @@
         </is>
       </c>
       <c r="N79">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O79">
-        <v>5.82</v>
+        <v>0</v>
       </c>
       <c r="P79">
-        <v>9.550000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q79">
         <v>0</v>
@@ -13302,12 +13302,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G80">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="AU80" t="inlineStr">
         <is>
-          <t>2026-08-07 16:00:00</t>
+          <t>2026-08-07 15:45:00</t>
         </is>
       </c>
     </row>
@@ -13465,27 +13465,27 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G81">
@@ -13616,7 +13616,7 @@
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>2026-08-07 16:00:00</t>
+          <t>2026-08-07 15:45:00</t>
         </is>
       </c>
     </row>
@@ -13628,12 +13628,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,13 +13675,13 @@
         </is>
       </c>
       <c r="N82">
-        <v>3.35</v>
+        <v>1.3</v>
       </c>
       <c r="O82">
-        <v>3.64</v>
+        <v>5.82</v>
       </c>
       <c r="P82">
-        <v>2.19</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="Q82">
         <v>0</v>
@@ -13714,10 +13714,10 @@
         <v>0</v>
       </c>
       <c r="AA82">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB82">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC82">
         <v>0</v>
@@ -13779,7 +13779,7 @@
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>2026-08-07 16:15:00</t>
+          <t>2026-08-07 15:45:00</t>
         </is>
       </c>
     </row>
@@ -13791,12 +13791,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G83">
@@ -13942,7 +13942,7 @@
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>2026-08-07 18:15:00</t>
+          <t>2026-08-07 16:00:00</t>
         </is>
       </c>
     </row>
@@ -13954,27 +13954,27 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G84">
@@ -14105,7 +14105,7 @@
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>2026-08-07 19:00:00</t>
+          <t>2026-08-07 16:00:00</t>
         </is>
       </c>
     </row>
@@ -14117,27 +14117,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,13 +14164,13 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.8</v>
+        <v>3.35</v>
       </c>
       <c r="O85">
-        <v>3.32</v>
+        <v>3.64</v>
       </c>
       <c r="P85">
-        <v>4.64</v>
+        <v>2.19</v>
       </c>
       <c r="Q85">
         <v>0</v>
@@ -14203,10 +14203,10 @@
         <v>0</v>
       </c>
       <c r="AA85">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AB85">
-        <v>1.61</v>
+        <v>1.95</v>
       </c>
       <c r="AC85">
         <v>0</v>
@@ -14268,7 +14268,7 @@
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>2026-08-07 19:30:00</t>
+          <t>2026-08-07 16:15:00</t>
         </is>
       </c>
     </row>
@@ -14280,12 +14280,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G86">
@@ -14431,7 +14431,7 @@
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>2026-08-07 20:00:00</t>
+          <t>2026-08-07 18:15:00</t>
         </is>
       </c>
     </row>
@@ -14443,12 +14443,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G87">
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>2026-08-07 20:00:00</t>
+          <t>2026-08-07 19:00:00</t>
         </is>
       </c>
     </row>
@@ -14606,12 +14606,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,13 +14653,13 @@
         </is>
       </c>
       <c r="N88">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O88">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P88">
-        <v>0</v>
+        <v>4.64</v>
       </c>
       <c r="Q88">
         <v>0</v>
@@ -14692,10 +14692,10 @@
         <v>0</v>
       </c>
       <c r="AA88">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB88">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC88">
         <v>0</v>
@@ -14757,7 +14757,7 @@
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>2026-08-07 20:30:00</t>
+          <t>2026-08-07 19:30:00</t>
         </is>
       </c>
     </row>
@@ -14769,12 +14769,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,13 +14816,13 @@
         </is>
       </c>
       <c r="N89">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="O89">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="P89">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q89">
         <v>0</v>
@@ -14855,10 +14855,10 @@
         <v>0</v>
       </c>
       <c r="AA89">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB89">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC89">
         <v>0</v>
@@ -14920,7 +14920,7 @@
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>2026-08-07 20:30:00</t>
+          <t>2026-08-07 20:00:00</t>
         </is>
       </c>
     </row>
@@ -14932,27 +14932,27 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G90">
@@ -15083,7 +15083,7 @@
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>2026-08-07 21:00:00</t>
+          <t>2026-08-07 20:00:00</t>
         </is>
       </c>
     </row>
@@ -15095,27 +15095,27 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G91">
@@ -15246,7 +15246,7 @@
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>2026-08-07 21:00:00</t>
+          <t>2026-08-07 20:30:00</t>
         </is>
       </c>
     </row>
@@ -15258,27 +15258,27 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,13 +15305,13 @@
         </is>
       </c>
       <c r="N92">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O92">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P92">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q92">
         <v>0</v>
@@ -15344,10 +15344,10 @@
         <v>0</v>
       </c>
       <c r="AA92">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB92">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC92">
         <v>0</v>
@@ -15409,7 +15409,7 @@
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>2026-08-07 21:00:00</t>
+          <t>2026-08-07 20:30:00</t>
         </is>
       </c>
     </row>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G93">
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G94">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G95">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G96">
@@ -16078,7 +16078,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G97">
@@ -16241,7 +16241,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>FC Tekstilshchik Ivanovo</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G98">
@@ -16404,22 +16404,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G99">
@@ -16567,22 +16567,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G100">
@@ -16730,22 +16730,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>FC Tekstilshchik Ivanovo</t>
         </is>
       </c>
       <c r="G101">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G102">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G103">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G104">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G105">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G106">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G107">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G108">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G109">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G110">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G112">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G113">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G114">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G115">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G116">
@@ -19338,22 +19338,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G117">
@@ -19501,22 +19501,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G118">
@@ -19664,22 +19664,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G119">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G120">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G121">
@@ -20153,7 +20153,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>ETO</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G122">
@@ -20316,22 +20316,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G123">
@@ -20479,7 +20479,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>ETO</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G124">
@@ -20642,22 +20642,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G125">
@@ -20805,22 +20805,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G126">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G127">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G128">
@@ -21294,7 +21294,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G129">
@@ -21457,7 +21457,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G130">
@@ -21620,7 +21620,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G132">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G133">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G134">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G135">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G136">
@@ -22593,27 +22593,27 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G137">
@@ -22744,7 +22744,7 @@
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>2026-08-07 21:30:00</t>
+          <t>2026-08-07 21:00:00</t>
         </is>
       </c>
     </row>
@@ -22756,156 +22756,645 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Serbia Prva Liga</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Teleoptik</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Jedinstvo Ub</t>
+        </is>
+      </c>
+      <c r="G138">
+        <v>0</v>
+      </c>
+      <c r="H138">
+        <v>0</v>
+      </c>
+      <c r="I138">
+        <v>0</v>
+      </c>
+      <c r="J138">
+        <v>0</v>
+      </c>
+      <c r="K138">
+        <v>0</v>
+      </c>
+      <c r="L138">
+        <v>0</v>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N138">
+        <v>0</v>
+      </c>
+      <c r="O138">
+        <v>0</v>
+      </c>
+      <c r="P138">
+        <v>0</v>
+      </c>
+      <c r="Q138">
+        <v>0</v>
+      </c>
+      <c r="R138">
+        <v>0</v>
+      </c>
+      <c r="S138">
+        <v>0</v>
+      </c>
+      <c r="T138">
+        <v>0</v>
+      </c>
+      <c r="U138">
+        <v>0</v>
+      </c>
+      <c r="V138">
+        <v>0</v>
+      </c>
+      <c r="W138">
+        <v>0</v>
+      </c>
+      <c r="X138">
+        <v>0</v>
+      </c>
+      <c r="Y138">
+        <v>0</v>
+      </c>
+      <c r="Z138">
+        <v>0</v>
+      </c>
+      <c r="AA138">
+        <v>0</v>
+      </c>
+      <c r="AB138">
+        <v>0</v>
+      </c>
+      <c r="AC138">
+        <v>0</v>
+      </c>
+      <c r="AD138">
+        <v>0</v>
+      </c>
+      <c r="AE138">
+        <v>0</v>
+      </c>
+      <c r="AF138">
+        <v>0</v>
+      </c>
+      <c r="AG138">
+        <v>0</v>
+      </c>
+      <c r="AH138" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI138" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ138">
+        <v>0</v>
+      </c>
+      <c r="AK138">
+        <v>0</v>
+      </c>
+      <c r="AL138">
+        <v>0</v>
+      </c>
+      <c r="AM138">
+        <v>-1</v>
+      </c>
+      <c r="AN138">
+        <v>-1</v>
+      </c>
+      <c r="AO138">
+        <v>-1</v>
+      </c>
+      <c r="AP138">
+        <v>-1</v>
+      </c>
+      <c r="AQ138">
+        <v>0</v>
+      </c>
+      <c r="AR138">
+        <v>0</v>
+      </c>
+      <c r="AS138">
+        <v>0</v>
+      </c>
+      <c r="AT138">
+        <v>0</v>
+      </c>
+      <c r="AU138" t="inlineStr">
+        <is>
+          <t>2026-08-07 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Serbia Prva Liga</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>OFK Vršac</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Naftagas</t>
+        </is>
+      </c>
+      <c r="G139">
+        <v>0</v>
+      </c>
+      <c r="H139">
+        <v>0</v>
+      </c>
+      <c r="I139">
+        <v>0</v>
+      </c>
+      <c r="J139">
+        <v>0</v>
+      </c>
+      <c r="K139">
+        <v>0</v>
+      </c>
+      <c r="L139">
+        <v>0</v>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N139">
+        <v>0</v>
+      </c>
+      <c r="O139">
+        <v>0</v>
+      </c>
+      <c r="P139">
+        <v>0</v>
+      </c>
+      <c r="Q139">
+        <v>0</v>
+      </c>
+      <c r="R139">
+        <v>0</v>
+      </c>
+      <c r="S139">
+        <v>0</v>
+      </c>
+      <c r="T139">
+        <v>0</v>
+      </c>
+      <c r="U139">
+        <v>0</v>
+      </c>
+      <c r="V139">
+        <v>0</v>
+      </c>
+      <c r="W139">
+        <v>0</v>
+      </c>
+      <c r="X139">
+        <v>0</v>
+      </c>
+      <c r="Y139">
+        <v>0</v>
+      </c>
+      <c r="Z139">
+        <v>0</v>
+      </c>
+      <c r="AA139">
+        <v>0</v>
+      </c>
+      <c r="AB139">
+        <v>0</v>
+      </c>
+      <c r="AC139">
+        <v>0</v>
+      </c>
+      <c r="AD139">
+        <v>0</v>
+      </c>
+      <c r="AE139">
+        <v>0</v>
+      </c>
+      <c r="AF139">
+        <v>0</v>
+      </c>
+      <c r="AG139">
+        <v>0</v>
+      </c>
+      <c r="AH139" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI139" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ139">
+        <v>0</v>
+      </c>
+      <c r="AK139">
+        <v>0</v>
+      </c>
+      <c r="AL139">
+        <v>0</v>
+      </c>
+      <c r="AM139">
+        <v>-1</v>
+      </c>
+      <c r="AN139">
+        <v>-1</v>
+      </c>
+      <c r="AO139">
+        <v>-1</v>
+      </c>
+      <c r="AP139">
+        <v>-1</v>
+      </c>
+      <c r="AQ139">
+        <v>0</v>
+      </c>
+      <c r="AR139">
+        <v>0</v>
+      </c>
+      <c r="AS139">
+        <v>0</v>
+      </c>
+      <c r="AT139">
+        <v>0</v>
+      </c>
+      <c r="AU139" t="inlineStr">
+        <is>
+          <t>2026-08-07 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr">
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Chile Primera B</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Deportes Santa Cruz</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Puerto Montt</t>
+        </is>
+      </c>
+      <c r="G140">
+        <v>0</v>
+      </c>
+      <c r="H140">
+        <v>0</v>
+      </c>
+      <c r="I140">
+        <v>0</v>
+      </c>
+      <c r="J140">
+        <v>0</v>
+      </c>
+      <c r="K140">
+        <v>0</v>
+      </c>
+      <c r="L140">
+        <v>0</v>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N140">
+        <v>0</v>
+      </c>
+      <c r="O140">
+        <v>0</v>
+      </c>
+      <c r="P140">
+        <v>0</v>
+      </c>
+      <c r="Q140">
+        <v>0</v>
+      </c>
+      <c r="R140">
+        <v>0</v>
+      </c>
+      <c r="S140">
+        <v>0</v>
+      </c>
+      <c r="T140">
+        <v>0</v>
+      </c>
+      <c r="U140">
+        <v>0</v>
+      </c>
+      <c r="V140">
+        <v>0</v>
+      </c>
+      <c r="W140">
+        <v>0</v>
+      </c>
+      <c r="X140">
+        <v>0</v>
+      </c>
+      <c r="Y140">
+        <v>0</v>
+      </c>
+      <c r="Z140">
+        <v>0</v>
+      </c>
+      <c r="AA140">
+        <v>0</v>
+      </c>
+      <c r="AB140">
+        <v>0</v>
+      </c>
+      <c r="AC140">
+        <v>0</v>
+      </c>
+      <c r="AD140">
+        <v>0</v>
+      </c>
+      <c r="AE140">
+        <v>0</v>
+      </c>
+      <c r="AF140">
+        <v>0</v>
+      </c>
+      <c r="AG140">
+        <v>0</v>
+      </c>
+      <c r="AH140" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI140" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ140">
+        <v>0</v>
+      </c>
+      <c r="AK140">
+        <v>0</v>
+      </c>
+      <c r="AL140">
+        <v>0</v>
+      </c>
+      <c r="AM140">
+        <v>-1</v>
+      </c>
+      <c r="AN140">
+        <v>-1</v>
+      </c>
+      <c r="AO140">
+        <v>-1</v>
+      </c>
+      <c r="AP140">
+        <v>-1</v>
+      </c>
+      <c r="AQ140">
+        <v>0</v>
+      </c>
+      <c r="AR140">
+        <v>0</v>
+      </c>
+      <c r="AS140">
+        <v>0</v>
+      </c>
+      <c r="AT140">
+        <v>0</v>
+      </c>
+      <c r="AU140" t="inlineStr">
+        <is>
+          <t>2026-08-07 21:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
         <is>
           <t>Chile Primera División</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr">
+      <c r="D141" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr">
+      <c r="E141" t="inlineStr">
         <is>
           <t>Universidad Católica</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr">
+      <c r="F141" t="inlineStr">
         <is>
           <t>Cobresal</t>
         </is>
       </c>
-      <c r="G138">
-        <v>0</v>
-      </c>
-      <c r="H138">
-        <v>0</v>
-      </c>
-      <c r="I138">
-        <v>0</v>
-      </c>
-      <c r="J138">
-        <v>0</v>
-      </c>
-      <c r="K138">
-        <v>0</v>
-      </c>
-      <c r="L138">
-        <v>0</v>
-      </c>
-      <c r="M138" t="inlineStr">
+      <c r="G141">
+        <v>0</v>
+      </c>
+      <c r="H141">
+        <v>0</v>
+      </c>
+      <c r="I141">
+        <v>0</v>
+      </c>
+      <c r="J141">
+        <v>0</v>
+      </c>
+      <c r="K141">
+        <v>0</v>
+      </c>
+      <c r="L141">
+        <v>0</v>
+      </c>
+      <c r="M141" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N138">
-        <v>0</v>
-      </c>
-      <c r="O138">
-        <v>0</v>
-      </c>
-      <c r="P138">
-        <v>0</v>
-      </c>
-      <c r="Q138">
-        <v>0</v>
-      </c>
-      <c r="R138">
-        <v>0</v>
-      </c>
-      <c r="S138">
-        <v>0</v>
-      </c>
-      <c r="T138">
-        <v>0</v>
-      </c>
-      <c r="U138">
-        <v>0</v>
-      </c>
-      <c r="V138">
-        <v>0</v>
-      </c>
-      <c r="W138">
-        <v>0</v>
-      </c>
-      <c r="X138">
-        <v>0</v>
-      </c>
-      <c r="Y138">
-        <v>0</v>
-      </c>
-      <c r="Z138">
-        <v>0</v>
-      </c>
-      <c r="AA138">
-        <v>0</v>
-      </c>
-      <c r="AB138">
-        <v>0</v>
-      </c>
-      <c r="AC138">
-        <v>0</v>
-      </c>
-      <c r="AD138">
-        <v>0</v>
-      </c>
-      <c r="AE138">
-        <v>0</v>
-      </c>
-      <c r="AF138">
-        <v>0</v>
-      </c>
-      <c r="AG138">
-        <v>0</v>
-      </c>
-      <c r="AH138" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI138" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ138">
-        <v>0</v>
-      </c>
-      <c r="AK138">
-        <v>0</v>
-      </c>
-      <c r="AL138">
-        <v>0</v>
-      </c>
-      <c r="AM138">
-        <v>-1</v>
-      </c>
-      <c r="AN138">
-        <v>-1</v>
-      </c>
-      <c r="AO138">
-        <v>-1</v>
-      </c>
-      <c r="AP138">
-        <v>-1</v>
-      </c>
-      <c r="AQ138">
-        <v>0</v>
-      </c>
-      <c r="AR138">
-        <v>0</v>
-      </c>
-      <c r="AS138">
-        <v>0</v>
-      </c>
-      <c r="AT138">
-        <v>0</v>
-      </c>
-      <c r="AU138" t="inlineStr">
+      <c r="N141">
+        <v>0</v>
+      </c>
+      <c r="O141">
+        <v>0</v>
+      </c>
+      <c r="P141">
+        <v>0</v>
+      </c>
+      <c r="Q141">
+        <v>0</v>
+      </c>
+      <c r="R141">
+        <v>0</v>
+      </c>
+      <c r="S141">
+        <v>0</v>
+      </c>
+      <c r="T141">
+        <v>0</v>
+      </c>
+      <c r="U141">
+        <v>0</v>
+      </c>
+      <c r="V141">
+        <v>0</v>
+      </c>
+      <c r="W141">
+        <v>0</v>
+      </c>
+      <c r="X141">
+        <v>0</v>
+      </c>
+      <c r="Y141">
+        <v>0</v>
+      </c>
+      <c r="Z141">
+        <v>0</v>
+      </c>
+      <c r="AA141">
+        <v>0</v>
+      </c>
+      <c r="AB141">
+        <v>0</v>
+      </c>
+      <c r="AC141">
+        <v>0</v>
+      </c>
+      <c r="AD141">
+        <v>0</v>
+      </c>
+      <c r="AE141">
+        <v>0</v>
+      </c>
+      <c r="AF141">
+        <v>0</v>
+      </c>
+      <c r="AG141">
+        <v>0</v>
+      </c>
+      <c r="AH141" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI141" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ141">
+        <v>0</v>
+      </c>
+      <c r="AK141">
+        <v>0</v>
+      </c>
+      <c r="AL141">
+        <v>0</v>
+      </c>
+      <c r="AM141">
+        <v>-1</v>
+      </c>
+      <c r="AN141">
+        <v>-1</v>
+      </c>
+      <c r="AO141">
+        <v>-1</v>
+      </c>
+      <c r="AP141">
+        <v>-1</v>
+      </c>
+      <c r="AQ141">
+        <v>0</v>
+      </c>
+      <c r="AR141">
+        <v>0</v>
+      </c>
+      <c r="AS141">
+        <v>0</v>
+      </c>
+      <c r="AT141">
+        <v>0</v>
+      </c>
+      <c r="AU141" t="inlineStr">
         <is>
           <t>2026-08-07 21:30:00</t>
         </is>

--- a/jogos_2026-08-07.xlsx
+++ b/jogos_2026-08-07.xlsx
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G3">
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G4">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G5">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G6">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G7">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G24">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G25">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G26">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G27">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G51">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G52">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G53">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G64">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G65">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G66">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G67">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G70">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G71">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G72">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G73">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="G74">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G76">
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G98">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G99">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G117">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G118">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G135">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G136">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G137">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="G138">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G139">

--- a/jogos_2026-08-07.xlsx
+++ b/jogos_2026-08-07.xlsx
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G7">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G8">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G24">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G25">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G26">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G27">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G116">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G117">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G118">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G119">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G134">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G135">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G136">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="G137">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G138">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G139">

--- a/jogos_2026-08-07.xlsx
+++ b/jogos_2026-08-07.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -1815,10 +1815,10 @@
         <v>0</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC9">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="O21">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P21">
-        <v>6.17</v>
+        <v>0</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>6.17</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G25">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G26">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G27">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G49">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G50">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G51">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G52">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G53">

--- a/jogos_2026-08-07.xlsx
+++ b/jogos_2026-08-07.xlsx
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G4">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G6">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G24">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G25">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G26">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G27">
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O54">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P54">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G65">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G66">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G67">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G73">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G74">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G75">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="G76">

--- a/jogos_2026-08-07.xlsx
+++ b/jogos_2026-08-07.xlsx
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G5">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G6">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G8">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G65">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G66">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G67">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G102">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G103">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G104">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G105">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G106">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G107">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G108">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G109">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G110">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G112">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G113">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G114">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G115">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G118">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G119">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G127">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="G128">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G129">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G130">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G131">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="G136">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G137">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G138">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G139">

--- a/jogos_2026-08-07.xlsx
+++ b/jogos_2026-08-07.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU141"/>
+  <dimension ref="A1:AU138"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3527,22 +3527,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G20">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>6.17</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -3853,22 +3853,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="O22">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P22">
-        <v>6.17</v>
+        <v>0</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G23">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G24">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G25">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G26">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G27">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>2026-08-07 13:00:00</t>
+          <t>2026-08-07 13:30:00</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G28">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G29">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>2026-08-07 13:30:00</t>
+          <t>2026-08-07 14:00:00</t>
         </is>
       </c>
     </row>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G30">
@@ -5320,22 +5320,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G31">
@@ -5483,22 +5483,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G32">
@@ -5646,22 +5646,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G33">
@@ -5809,7 +5809,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G34">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G35">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G36">
@@ -6298,22 +6298,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G37">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G38">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>2026-08-07 14:00:00</t>
+          <t>2026-08-07 14:30:00</t>
         </is>
       </c>
     </row>
@@ -6624,22 +6624,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G39">
@@ -6787,22 +6787,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G40">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G41">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G43">
@@ -7434,12 +7434,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>BSK Banja Luka</t>
         </is>
       </c>
       <c r="G44">
@@ -7585,7 +7585,7 @@
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>2026-08-07 14:30:00</t>
+          <t>2026-08-07 15:00:00</t>
         </is>
       </c>
     </row>
@@ -7602,7 +7602,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>BSK Banja Luka</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G45">
@@ -7765,7 +7765,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G46">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G47">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G48">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G49">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G50">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G51">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G52">
@@ -8901,12 +8901,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,13 +8948,13 @@
         </is>
       </c>
       <c r="N53">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O53">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P53">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q53">
         <v>0</v>
@@ -9052,7 +9052,7 @@
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>2026-08-07 15:00:00</t>
+          <t>2026-08-07 15:15:00</t>
         </is>
       </c>
     </row>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O54">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P54">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -9227,12 +9227,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G55">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>2026-08-07 15:15:00</t>
+          <t>2026-08-07 15:30:00</t>
         </is>
       </c>
     </row>
@@ -9395,7 +9395,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G56">
@@ -9558,7 +9558,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Wacker Innsbruck</t>
         </is>
       </c>
       <c r="G57">
@@ -9721,7 +9721,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Wacker Innsbruck</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G58">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G59">
@@ -10047,7 +10047,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G60">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G61">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,13 +10415,13 @@
         </is>
       </c>
       <c r="N62">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O62">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="P62">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -10519,7 +10519,7 @@
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>2026-08-07 15:30:00</t>
+          <t>2026-08-07 15:45:00</t>
         </is>
       </c>
     </row>
@@ -10536,22 +10536,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G63">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G64">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G65">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G66">
@@ -11188,22 +11188,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G67">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>La Roche VF</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G68">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>La Roche VF</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O69">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P69">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q69">
         <v>0</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G70">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="N71">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O71">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P71">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="Q71">
         <v>0</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,13 +12045,13 @@
         </is>
       </c>
       <c r="N72">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O72">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P72">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q72">
         <v>0</v>
@@ -12084,10 +12084,10 @@
         <v>0</v>
       </c>
       <c r="AA72">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB72">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC72">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G73">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O74">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P74">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Q74">
         <v>0</v>
@@ -12410,10 +12410,10 @@
         <v>0</v>
       </c>
       <c r="AA74">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB74">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC74">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="G75">
@@ -12655,22 +12655,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G76">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G77">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G78">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G79">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G80">
@@ -13470,22 +13470,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,13 +13512,13 @@
         </is>
       </c>
       <c r="N81">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O81">
-        <v>0</v>
+        <v>5.82</v>
       </c>
       <c r="P81">
-        <v>0</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -13628,27 +13628,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,13 +13675,13 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O82">
-        <v>5.82</v>
+        <v>0</v>
       </c>
       <c r="P82">
-        <v>9.550000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q82">
         <v>0</v>
@@ -13779,7 +13779,7 @@
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>2026-08-07 15:45:00</t>
+          <t>2026-08-07 16:00:00</t>
         </is>
       </c>
     </row>
@@ -13796,22 +13796,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G83">
@@ -13954,12 +13954,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,13 +14001,13 @@
         </is>
       </c>
       <c r="N84">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O84">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="P84">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q84">
         <v>0</v>
@@ -14040,10 +14040,10 @@
         <v>0</v>
       </c>
       <c r="AA84">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB84">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC84">
         <v>0</v>
@@ -14105,7 +14105,7 @@
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>2026-08-07 16:00:00</t>
+          <t>2026-08-07 16:15:00</t>
         </is>
       </c>
     </row>
@@ -14117,27 +14117,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,13 +14164,13 @@
         </is>
       </c>
       <c r="N85">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O85">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="P85">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q85">
         <v>0</v>
@@ -14203,10 +14203,10 @@
         <v>0</v>
       </c>
       <c r="AA85">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB85">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC85">
         <v>0</v>
@@ -14268,7 +14268,7 @@
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>2026-08-07 16:15:00</t>
+          <t>2026-08-07 18:15:00</t>
         </is>
       </c>
     </row>
@@ -14280,12 +14280,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G86">
@@ -14431,7 +14431,7 @@
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>2026-08-07 18:15:00</t>
+          <t>2026-08-07 19:00:00</t>
         </is>
       </c>
     </row>
@@ -14443,12 +14443,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="N87">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O87">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P87">
-        <v>0</v>
+        <v>4.64</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -14529,10 +14529,10 @@
         <v>0</v>
       </c>
       <c r="AA87">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB87">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC87">
         <v>0</v>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>2026-08-07 19:00:00</t>
+          <t>2026-08-07 19:30:00</t>
         </is>
       </c>
     </row>
@@ -14606,12 +14606,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,13 +14653,13 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O88">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P88">
-        <v>4.64</v>
+        <v>0</v>
       </c>
       <c r="Q88">
         <v>0</v>
@@ -14692,10 +14692,10 @@
         <v>0</v>
       </c>
       <c r="AA88">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB88">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC88">
         <v>0</v>
@@ -14757,7 +14757,7 @@
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>2026-08-07 19:30:00</t>
+          <t>2026-08-07 20:00:00</t>
         </is>
       </c>
     </row>
@@ -14774,7 +14774,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G89">
@@ -14932,12 +14932,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G90">
@@ -15083,7 +15083,7 @@
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>2026-08-07 20:00:00</t>
+          <t>2026-08-07 20:30:00</t>
         </is>
       </c>
     </row>
@@ -15100,7 +15100,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,13 +15142,13 @@
         </is>
       </c>
       <c r="N91">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O91">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P91">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q91">
         <v>0</v>
@@ -15181,10 +15181,10 @@
         <v>0</v>
       </c>
       <c r="AA91">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB91">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC91">
         <v>0</v>
@@ -15258,27 +15258,27 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,13 +15305,13 @@
         </is>
       </c>
       <c r="N92">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="O92">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="P92">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q92">
         <v>0</v>
@@ -15344,10 +15344,10 @@
         <v>0</v>
       </c>
       <c r="AA92">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB92">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC92">
         <v>0</v>
@@ -15409,7 +15409,7 @@
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>2026-08-07 20:30:00</t>
+          <t>2026-08-07 21:00:00</t>
         </is>
       </c>
     </row>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G93">
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G94">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G95">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G96">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G97">
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G98">
@@ -16404,7 +16404,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G99">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>FC Tekstilshchik Ivanovo</t>
         </is>
       </c>
       <c r="G100">
@@ -16730,22 +16730,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>FC Tekstilshchik Ivanovo</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G101">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G102">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G103">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G104">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G105">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G106">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G107">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G108">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G109">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G110">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G112">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G113">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G114">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G116">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G117">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G118">
@@ -19664,22 +19664,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G119">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G120">
@@ -19990,7 +19990,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>ETO</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G121">
@@ -20153,22 +20153,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G122">
@@ -20316,22 +20316,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G123">
@@ -20479,7 +20479,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>ETO</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G124">
@@ -20642,22 +20642,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="G125">
@@ -20805,22 +20805,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G126">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G127">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G128">
@@ -21294,7 +21294,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G129">
@@ -21457,7 +21457,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G130">
@@ -21620,7 +21620,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G132">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="G133">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G134">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G135">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G136">
@@ -22593,27 +22593,27 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G137">
@@ -22744,7 +22744,7 @@
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>2026-08-07 21:00:00</t>
+          <t>2026-08-07 21:30:00</t>
         </is>
       </c>
     </row>
@@ -22756,27 +22756,27 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="G138">
@@ -22906,495 +22906,6 @@
         <v>0</v>
       </c>
       <c r="AU138" t="inlineStr">
-        <is>
-          <t>2026-08-07 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>Bor</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>Napredak</t>
-        </is>
-      </c>
-      <c r="G139">
-        <v>0</v>
-      </c>
-      <c r="H139">
-        <v>0</v>
-      </c>
-      <c r="I139">
-        <v>0</v>
-      </c>
-      <c r="J139">
-        <v>0</v>
-      </c>
-      <c r="K139">
-        <v>0</v>
-      </c>
-      <c r="L139">
-        <v>0</v>
-      </c>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N139">
-        <v>0</v>
-      </c>
-      <c r="O139">
-        <v>0</v>
-      </c>
-      <c r="P139">
-        <v>0</v>
-      </c>
-      <c r="Q139">
-        <v>0</v>
-      </c>
-      <c r="R139">
-        <v>0</v>
-      </c>
-      <c r="S139">
-        <v>0</v>
-      </c>
-      <c r="T139">
-        <v>0</v>
-      </c>
-      <c r="U139">
-        <v>0</v>
-      </c>
-      <c r="V139">
-        <v>0</v>
-      </c>
-      <c r="W139">
-        <v>0</v>
-      </c>
-      <c r="X139">
-        <v>0</v>
-      </c>
-      <c r="Y139">
-        <v>0</v>
-      </c>
-      <c r="Z139">
-        <v>0</v>
-      </c>
-      <c r="AA139">
-        <v>0</v>
-      </c>
-      <c r="AB139">
-        <v>0</v>
-      </c>
-      <c r="AC139">
-        <v>0</v>
-      </c>
-      <c r="AD139">
-        <v>0</v>
-      </c>
-      <c r="AE139">
-        <v>0</v>
-      </c>
-      <c r="AF139">
-        <v>0</v>
-      </c>
-      <c r="AG139">
-        <v>0</v>
-      </c>
-      <c r="AH139" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI139" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ139">
-        <v>0</v>
-      </c>
-      <c r="AK139">
-        <v>0</v>
-      </c>
-      <c r="AL139">
-        <v>0</v>
-      </c>
-      <c r="AM139">
-        <v>-1</v>
-      </c>
-      <c r="AN139">
-        <v>-1</v>
-      </c>
-      <c r="AO139">
-        <v>-1</v>
-      </c>
-      <c r="AP139">
-        <v>-1</v>
-      </c>
-      <c r="AQ139">
-        <v>0</v>
-      </c>
-      <c r="AR139">
-        <v>0</v>
-      </c>
-      <c r="AS139">
-        <v>0</v>
-      </c>
-      <c r="AT139">
-        <v>0</v>
-      </c>
-      <c r="AU139" t="inlineStr">
-        <is>
-          <t>2026-08-07 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Chile Primera B</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>Deportes Santa Cruz</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>Puerto Montt</t>
-        </is>
-      </c>
-      <c r="G140">
-        <v>0</v>
-      </c>
-      <c r="H140">
-        <v>0</v>
-      </c>
-      <c r="I140">
-        <v>0</v>
-      </c>
-      <c r="J140">
-        <v>0</v>
-      </c>
-      <c r="K140">
-        <v>0</v>
-      </c>
-      <c r="L140">
-        <v>0</v>
-      </c>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N140">
-        <v>0</v>
-      </c>
-      <c r="O140">
-        <v>0</v>
-      </c>
-      <c r="P140">
-        <v>0</v>
-      </c>
-      <c r="Q140">
-        <v>0</v>
-      </c>
-      <c r="R140">
-        <v>0</v>
-      </c>
-      <c r="S140">
-        <v>0</v>
-      </c>
-      <c r="T140">
-        <v>0</v>
-      </c>
-      <c r="U140">
-        <v>0</v>
-      </c>
-      <c r="V140">
-        <v>0</v>
-      </c>
-      <c r="W140">
-        <v>0</v>
-      </c>
-      <c r="X140">
-        <v>0</v>
-      </c>
-      <c r="Y140">
-        <v>0</v>
-      </c>
-      <c r="Z140">
-        <v>0</v>
-      </c>
-      <c r="AA140">
-        <v>0</v>
-      </c>
-      <c r="AB140">
-        <v>0</v>
-      </c>
-      <c r="AC140">
-        <v>0</v>
-      </c>
-      <c r="AD140">
-        <v>0</v>
-      </c>
-      <c r="AE140">
-        <v>0</v>
-      </c>
-      <c r="AF140">
-        <v>0</v>
-      </c>
-      <c r="AG140">
-        <v>0</v>
-      </c>
-      <c r="AH140" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI140" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ140">
-        <v>0</v>
-      </c>
-      <c r="AK140">
-        <v>0</v>
-      </c>
-      <c r="AL140">
-        <v>0</v>
-      </c>
-      <c r="AM140">
-        <v>-1</v>
-      </c>
-      <c r="AN140">
-        <v>-1</v>
-      </c>
-      <c r="AO140">
-        <v>-1</v>
-      </c>
-      <c r="AP140">
-        <v>-1</v>
-      </c>
-      <c r="AQ140">
-        <v>0</v>
-      </c>
-      <c r="AR140">
-        <v>0</v>
-      </c>
-      <c r="AS140">
-        <v>0</v>
-      </c>
-      <c r="AT140">
-        <v>0</v>
-      </c>
-      <c r="AU140" t="inlineStr">
-        <is>
-          <t>2026-08-07 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Chile Primera División</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>Universidad Católica</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>Cobresal</t>
-        </is>
-      </c>
-      <c r="G141">
-        <v>0</v>
-      </c>
-      <c r="H141">
-        <v>0</v>
-      </c>
-      <c r="I141">
-        <v>0</v>
-      </c>
-      <c r="J141">
-        <v>0</v>
-      </c>
-      <c r="K141">
-        <v>0</v>
-      </c>
-      <c r="L141">
-        <v>0</v>
-      </c>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N141">
-        <v>0</v>
-      </c>
-      <c r="O141">
-        <v>0</v>
-      </c>
-      <c r="P141">
-        <v>0</v>
-      </c>
-      <c r="Q141">
-        <v>0</v>
-      </c>
-      <c r="R141">
-        <v>0</v>
-      </c>
-      <c r="S141">
-        <v>0</v>
-      </c>
-      <c r="T141">
-        <v>0</v>
-      </c>
-      <c r="U141">
-        <v>0</v>
-      </c>
-      <c r="V141">
-        <v>0</v>
-      </c>
-      <c r="W141">
-        <v>0</v>
-      </c>
-      <c r="X141">
-        <v>0</v>
-      </c>
-      <c r="Y141">
-        <v>0</v>
-      </c>
-      <c r="Z141">
-        <v>0</v>
-      </c>
-      <c r="AA141">
-        <v>0</v>
-      </c>
-      <c r="AB141">
-        <v>0</v>
-      </c>
-      <c r="AC141">
-        <v>0</v>
-      </c>
-      <c r="AD141">
-        <v>0</v>
-      </c>
-      <c r="AE141">
-        <v>0</v>
-      </c>
-      <c r="AF141">
-        <v>0</v>
-      </c>
-      <c r="AG141">
-        <v>0</v>
-      </c>
-      <c r="AH141" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI141" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ141">
-        <v>0</v>
-      </c>
-      <c r="AK141">
-        <v>0</v>
-      </c>
-      <c r="AL141">
-        <v>0</v>
-      </c>
-      <c r="AM141">
-        <v>-1</v>
-      </c>
-      <c r="AN141">
-        <v>-1</v>
-      </c>
-      <c r="AO141">
-        <v>-1</v>
-      </c>
-      <c r="AP141">
-        <v>-1</v>
-      </c>
-      <c r="AQ141">
-        <v>0</v>
-      </c>
-      <c r="AR141">
-        <v>0</v>
-      </c>
-      <c r="AS141">
-        <v>0</v>
-      </c>
-      <c r="AT141">
-        <v>0</v>
-      </c>
-      <c r="AU141" t="inlineStr">
         <is>
           <t>2026-08-07 21:30:00</t>
         </is>

--- a/jogos_2026-08-07.xlsx
+++ b/jogos_2026-08-07.xlsx
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>5.53</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>4.51</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q37">
         <v>0</v>
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O63">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P63">
-        <v>0</v>
+        <v>6.84</v>
       </c>
       <c r="Q63">
         <v>0</v>
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O64">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P64">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -13675,13 +13675,13 @@
         </is>
       </c>
       <c r="N82">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O82">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P82">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="Q82">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G104">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G105">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G106">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G107">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G108">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G109">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G110">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G112">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G113">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G114">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G115">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G116">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G117">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G118">

--- a/jogos_2026-08-07.xlsx
+++ b/jogos_2026-08-07.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU138"/>
+  <dimension ref="A1:AU134"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G49">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G50">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G51">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G52">
@@ -16404,22 +16404,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G99">
@@ -16567,22 +16567,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>FC Tekstilshchik Ivanovo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G100">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G101">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G102">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G103">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G104">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G105">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G106">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G107">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G108">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G109">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G110">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G112">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G113">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G114">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G115">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G116">
@@ -19338,22 +19338,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G117">
@@ -19501,22 +19501,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G118">
@@ -19664,7 +19664,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>ETO</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G119">
@@ -19827,22 +19827,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G120">
@@ -19990,22 +19990,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>ETO</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G121">
@@ -20153,22 +20153,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G122">
@@ -20316,22 +20316,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G123">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G124">
@@ -20642,7 +20642,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G125">
@@ -20805,7 +20805,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G126">
@@ -20968,7 +20968,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G127">
@@ -21131,7 +21131,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G128">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="G129">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G130">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G132">
@@ -21941,27 +21941,27 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G133">
@@ -22092,7 +22092,7 @@
       </c>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>2026-08-07 21:00:00</t>
+          <t>2026-08-07 21:30:00</t>
         </is>
       </c>
     </row>
@@ -22104,27 +22104,27 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="G134">
@@ -22254,658 +22254,6 @@
         <v>0</v>
       </c>
       <c r="AU134" t="inlineStr">
-        <is>
-          <t>2026-08-07 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>Grafičar</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>Semendrija 1924</t>
-        </is>
-      </c>
-      <c r="G135">
-        <v>0</v>
-      </c>
-      <c r="H135">
-        <v>0</v>
-      </c>
-      <c r="I135">
-        <v>0</v>
-      </c>
-      <c r="J135">
-        <v>0</v>
-      </c>
-      <c r="K135">
-        <v>0</v>
-      </c>
-      <c r="L135">
-        <v>0</v>
-      </c>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N135">
-        <v>0</v>
-      </c>
-      <c r="O135">
-        <v>0</v>
-      </c>
-      <c r="P135">
-        <v>0</v>
-      </c>
-      <c r="Q135">
-        <v>0</v>
-      </c>
-      <c r="R135">
-        <v>0</v>
-      </c>
-      <c r="S135">
-        <v>0</v>
-      </c>
-      <c r="T135">
-        <v>0</v>
-      </c>
-      <c r="U135">
-        <v>0</v>
-      </c>
-      <c r="V135">
-        <v>0</v>
-      </c>
-      <c r="W135">
-        <v>0</v>
-      </c>
-      <c r="X135">
-        <v>0</v>
-      </c>
-      <c r="Y135">
-        <v>0</v>
-      </c>
-      <c r="Z135">
-        <v>0</v>
-      </c>
-      <c r="AA135">
-        <v>0</v>
-      </c>
-      <c r="AB135">
-        <v>0</v>
-      </c>
-      <c r="AC135">
-        <v>0</v>
-      </c>
-      <c r="AD135">
-        <v>0</v>
-      </c>
-      <c r="AE135">
-        <v>0</v>
-      </c>
-      <c r="AF135">
-        <v>0</v>
-      </c>
-      <c r="AG135">
-        <v>0</v>
-      </c>
-      <c r="AH135" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI135" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ135">
-        <v>0</v>
-      </c>
-      <c r="AK135">
-        <v>0</v>
-      </c>
-      <c r="AL135">
-        <v>0</v>
-      </c>
-      <c r="AM135">
-        <v>-1</v>
-      </c>
-      <c r="AN135">
-        <v>-1</v>
-      </c>
-      <c r="AO135">
-        <v>-1</v>
-      </c>
-      <c r="AP135">
-        <v>-1</v>
-      </c>
-      <c r="AQ135">
-        <v>0</v>
-      </c>
-      <c r="AR135">
-        <v>0</v>
-      </c>
-      <c r="AS135">
-        <v>0</v>
-      </c>
-      <c r="AT135">
-        <v>0</v>
-      </c>
-      <c r="AU135" t="inlineStr">
-        <is>
-          <t>2026-08-07 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>Bor</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>Napredak</t>
-        </is>
-      </c>
-      <c r="G136">
-        <v>0</v>
-      </c>
-      <c r="H136">
-        <v>0</v>
-      </c>
-      <c r="I136">
-        <v>0</v>
-      </c>
-      <c r="J136">
-        <v>0</v>
-      </c>
-      <c r="K136">
-        <v>0</v>
-      </c>
-      <c r="L136">
-        <v>0</v>
-      </c>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N136">
-        <v>0</v>
-      </c>
-      <c r="O136">
-        <v>0</v>
-      </c>
-      <c r="P136">
-        <v>0</v>
-      </c>
-      <c r="Q136">
-        <v>0</v>
-      </c>
-      <c r="R136">
-        <v>0</v>
-      </c>
-      <c r="S136">
-        <v>0</v>
-      </c>
-      <c r="T136">
-        <v>0</v>
-      </c>
-      <c r="U136">
-        <v>0</v>
-      </c>
-      <c r="V136">
-        <v>0</v>
-      </c>
-      <c r="W136">
-        <v>0</v>
-      </c>
-      <c r="X136">
-        <v>0</v>
-      </c>
-      <c r="Y136">
-        <v>0</v>
-      </c>
-      <c r="Z136">
-        <v>0</v>
-      </c>
-      <c r="AA136">
-        <v>0</v>
-      </c>
-      <c r="AB136">
-        <v>0</v>
-      </c>
-      <c r="AC136">
-        <v>0</v>
-      </c>
-      <c r="AD136">
-        <v>0</v>
-      </c>
-      <c r="AE136">
-        <v>0</v>
-      </c>
-      <c r="AF136">
-        <v>0</v>
-      </c>
-      <c r="AG136">
-        <v>0</v>
-      </c>
-      <c r="AH136" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI136" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ136">
-        <v>0</v>
-      </c>
-      <c r="AK136">
-        <v>0</v>
-      </c>
-      <c r="AL136">
-        <v>0</v>
-      </c>
-      <c r="AM136">
-        <v>-1</v>
-      </c>
-      <c r="AN136">
-        <v>-1</v>
-      </c>
-      <c r="AO136">
-        <v>-1</v>
-      </c>
-      <c r="AP136">
-        <v>-1</v>
-      </c>
-      <c r="AQ136">
-        <v>0</v>
-      </c>
-      <c r="AR136">
-        <v>0</v>
-      </c>
-      <c r="AS136">
-        <v>0</v>
-      </c>
-      <c r="AT136">
-        <v>0</v>
-      </c>
-      <c r="AU136" t="inlineStr">
-        <is>
-          <t>2026-08-07 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Chile Primera B</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>Deportes Santa Cruz</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>Puerto Montt</t>
-        </is>
-      </c>
-      <c r="G137">
-        <v>0</v>
-      </c>
-      <c r="H137">
-        <v>0</v>
-      </c>
-      <c r="I137">
-        <v>0</v>
-      </c>
-      <c r="J137">
-        <v>0</v>
-      </c>
-      <c r="K137">
-        <v>0</v>
-      </c>
-      <c r="L137">
-        <v>0</v>
-      </c>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N137">
-        <v>0</v>
-      </c>
-      <c r="O137">
-        <v>0</v>
-      </c>
-      <c r="P137">
-        <v>0</v>
-      </c>
-      <c r="Q137">
-        <v>0</v>
-      </c>
-      <c r="R137">
-        <v>0</v>
-      </c>
-      <c r="S137">
-        <v>0</v>
-      </c>
-      <c r="T137">
-        <v>0</v>
-      </c>
-      <c r="U137">
-        <v>0</v>
-      </c>
-      <c r="V137">
-        <v>0</v>
-      </c>
-      <c r="W137">
-        <v>0</v>
-      </c>
-      <c r="X137">
-        <v>0</v>
-      </c>
-      <c r="Y137">
-        <v>0</v>
-      </c>
-      <c r="Z137">
-        <v>0</v>
-      </c>
-      <c r="AA137">
-        <v>0</v>
-      </c>
-      <c r="AB137">
-        <v>0</v>
-      </c>
-      <c r="AC137">
-        <v>0</v>
-      </c>
-      <c r="AD137">
-        <v>0</v>
-      </c>
-      <c r="AE137">
-        <v>0</v>
-      </c>
-      <c r="AF137">
-        <v>0</v>
-      </c>
-      <c r="AG137">
-        <v>0</v>
-      </c>
-      <c r="AH137" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI137" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ137">
-        <v>0</v>
-      </c>
-      <c r="AK137">
-        <v>0</v>
-      </c>
-      <c r="AL137">
-        <v>0</v>
-      </c>
-      <c r="AM137">
-        <v>-1</v>
-      </c>
-      <c r="AN137">
-        <v>-1</v>
-      </c>
-      <c r="AO137">
-        <v>-1</v>
-      </c>
-      <c r="AP137">
-        <v>-1</v>
-      </c>
-      <c r="AQ137">
-        <v>0</v>
-      </c>
-      <c r="AR137">
-        <v>0</v>
-      </c>
-      <c r="AS137">
-        <v>0</v>
-      </c>
-      <c r="AT137">
-        <v>0</v>
-      </c>
-      <c r="AU137" t="inlineStr">
-        <is>
-          <t>2026-08-07 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Chile Primera División</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>Universidad Católica</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>Cobresal</t>
-        </is>
-      </c>
-      <c r="G138">
-        <v>0</v>
-      </c>
-      <c r="H138">
-        <v>0</v>
-      </c>
-      <c r="I138">
-        <v>0</v>
-      </c>
-      <c r="J138">
-        <v>0</v>
-      </c>
-      <c r="K138">
-        <v>0</v>
-      </c>
-      <c r="L138">
-        <v>0</v>
-      </c>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N138">
-        <v>0</v>
-      </c>
-      <c r="O138">
-        <v>0</v>
-      </c>
-      <c r="P138">
-        <v>0</v>
-      </c>
-      <c r="Q138">
-        <v>0</v>
-      </c>
-      <c r="R138">
-        <v>0</v>
-      </c>
-      <c r="S138">
-        <v>0</v>
-      </c>
-      <c r="T138">
-        <v>0</v>
-      </c>
-      <c r="U138">
-        <v>0</v>
-      </c>
-      <c r="V138">
-        <v>0</v>
-      </c>
-      <c r="W138">
-        <v>0</v>
-      </c>
-      <c r="X138">
-        <v>0</v>
-      </c>
-      <c r="Y138">
-        <v>0</v>
-      </c>
-      <c r="Z138">
-        <v>0</v>
-      </c>
-      <c r="AA138">
-        <v>0</v>
-      </c>
-      <c r="AB138">
-        <v>0</v>
-      </c>
-      <c r="AC138">
-        <v>0</v>
-      </c>
-      <c r="AD138">
-        <v>0</v>
-      </c>
-      <c r="AE138">
-        <v>0</v>
-      </c>
-      <c r="AF138">
-        <v>0</v>
-      </c>
-      <c r="AG138">
-        <v>0</v>
-      </c>
-      <c r="AH138" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI138" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ138">
-        <v>0</v>
-      </c>
-      <c r="AK138">
-        <v>0</v>
-      </c>
-      <c r="AL138">
-        <v>0</v>
-      </c>
-      <c r="AM138">
-        <v>-1</v>
-      </c>
-      <c r="AN138">
-        <v>-1</v>
-      </c>
-      <c r="AO138">
-        <v>-1</v>
-      </c>
-      <c r="AP138">
-        <v>-1</v>
-      </c>
-      <c r="AQ138">
-        <v>0</v>
-      </c>
-      <c r="AR138">
-        <v>0</v>
-      </c>
-      <c r="AS138">
-        <v>0</v>
-      </c>
-      <c r="AT138">
-        <v>0</v>
-      </c>
-      <c r="AU138" t="inlineStr">
         <is>
           <t>2026-08-07 21:30:00</t>
         </is>

--- a/jogos_2026-08-07.xlsx
+++ b/jogos_2026-08-07.xlsx
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,13 +8948,13 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O53">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P53">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q53">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O54">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P54">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G108">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G109">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G110">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G112">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G113">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G114">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G115">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G116">

--- a/jogos_2026-08-07.xlsx
+++ b/jogos_2026-08-07.xlsx
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G95">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G96">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G97">
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G98">

--- a/jogos_2026-08-07.xlsx
+++ b/jogos_2026-08-07.xlsx
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>5.53</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -8948,13 +8948,13 @@
         </is>
       </c>
       <c r="N53">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O53">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P53">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="Q53">
         <v>0</v>
@@ -8993,10 +8993,10 @@
         <v>0</v>
       </c>
       <c r="AC53">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD53">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE53">
         <v>0</v>

--- a/jogos_2026-08-07.xlsx
+++ b/jogos_2026-08-07.xlsx
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G132">

--- a/jogos_2026-08-07.xlsx
+++ b/jogos_2026-08-07.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU134"/>
+  <dimension ref="A1:AU128"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10862,22 +10862,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G65">
@@ -11025,22 +11025,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>La Roche VF</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G66">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="N67">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O67">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P67">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>La Roche VF</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G68">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>3.25</v>
+        <v>2.04</v>
       </c>
       <c r="O69">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P69">
-        <v>2.22</v>
+        <v>3.65</v>
       </c>
       <c r="Q69">
         <v>0</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O70">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P70">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q70">
         <v>0</v>
@@ -11758,10 +11758,10 @@
         <v>0</v>
       </c>
       <c r="AA70">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB70">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC70">
         <v>0</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O71">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P71">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="Q71">
         <v>0</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,13 +12045,13 @@
         </is>
       </c>
       <c r="N72">
-        <v>2.6</v>
+        <v>2.07</v>
       </c>
       <c r="O72">
         <v>3.2</v>
       </c>
       <c r="P72">
-        <v>2.5</v>
+        <v>3.44</v>
       </c>
       <c r="Q72">
         <v>0</v>
@@ -12084,10 +12084,10 @@
         <v>0</v>
       </c>
       <c r="AA72">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="AB72">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AC72">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="G73">
@@ -12329,22 +12329,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O74">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P74">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="Q74">
         <v>0</v>
@@ -12410,10 +12410,10 @@
         <v>0</v>
       </c>
       <c r="AA74">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB74">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC74">
         <v>0</v>
@@ -12492,22 +12492,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G75">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G76">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G77">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G78">
@@ -13144,22 +13144,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,13 +13186,13 @@
         </is>
       </c>
       <c r="N79">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O79">
-        <v>0</v>
+        <v>5.82</v>
       </c>
       <c r="P79">
-        <v>0</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="Q79">
         <v>0</v>
@@ -13302,12 +13302,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,13 +13349,13 @@
         </is>
       </c>
       <c r="N80">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O80">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P80">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="Q80">
         <v>0</v>
@@ -13453,7 +13453,7 @@
       </c>
       <c r="AU80" t="inlineStr">
         <is>
-          <t>2026-08-07 15:45:00</t>
+          <t>2026-08-07 16:00:00</t>
         </is>
       </c>
     </row>
@@ -13465,12 +13465,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,13 +13512,13 @@
         </is>
       </c>
       <c r="N81">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O81">
-        <v>5.82</v>
+        <v>0</v>
       </c>
       <c r="P81">
-        <v>9.550000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -13616,7 +13616,7 @@
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>2026-08-07 15:45:00</t>
+          <t>2026-08-07 16:00:00</t>
         </is>
       </c>
     </row>
@@ -13628,27 +13628,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,13 +13675,13 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.66</v>
+        <v>3.35</v>
       </c>
       <c r="O82">
-        <v>4</v>
+        <v>3.64</v>
       </c>
       <c r="P82">
-        <v>4.65</v>
+        <v>2.19</v>
       </c>
       <c r="Q82">
         <v>0</v>
@@ -13714,10 +13714,10 @@
         <v>0</v>
       </c>
       <c r="AA82">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB82">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC82">
         <v>0</v>
@@ -13779,7 +13779,7 @@
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>2026-08-07 16:00:00</t>
+          <t>2026-08-07 16:15:00</t>
         </is>
       </c>
     </row>
@@ -13791,27 +13791,27 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G83">
@@ -13942,7 +13942,7 @@
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>2026-08-07 16:00:00</t>
+          <t>2026-08-07 18:15:00</t>
         </is>
       </c>
     </row>
@@ -13954,27 +13954,27 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,13 +14001,13 @@
         </is>
       </c>
       <c r="N84">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O84">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="P84">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q84">
         <v>0</v>
@@ -14040,10 +14040,10 @@
         <v>0</v>
       </c>
       <c r="AA84">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB84">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC84">
         <v>0</v>
@@ -14105,7 +14105,7 @@
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>2026-08-07 16:15:00</t>
+          <t>2026-08-07 19:00:00</t>
         </is>
       </c>
     </row>
@@ -14117,12 +14117,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,13 +14164,13 @@
         </is>
       </c>
       <c r="N85">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O85">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P85">
-        <v>0</v>
+        <v>4.64</v>
       </c>
       <c r="Q85">
         <v>0</v>
@@ -14203,10 +14203,10 @@
         <v>0</v>
       </c>
       <c r="AA85">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB85">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC85">
         <v>0</v>
@@ -14268,7 +14268,7 @@
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>2026-08-07 18:15:00</t>
+          <t>2026-08-07 19:30:00</t>
         </is>
       </c>
     </row>
@@ -14280,12 +14280,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G86">
@@ -14431,7 +14431,7 @@
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>2026-08-07 19:00:00</t>
+          <t>2026-08-07 20:00:00</t>
         </is>
       </c>
     </row>
@@ -14443,12 +14443,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="N87">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O87">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P87">
-        <v>4.64</v>
+        <v>0</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -14529,10 +14529,10 @@
         <v>0</v>
       </c>
       <c r="AA87">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB87">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC87">
         <v>0</v>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>2026-08-07 19:30:00</t>
+          <t>2026-08-07 20:00:00</t>
         </is>
       </c>
     </row>
@@ -14606,12 +14606,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G88">
@@ -14757,7 +14757,7 @@
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>2026-08-07 20:00:00</t>
+          <t>2026-08-07 20:30:00</t>
         </is>
       </c>
     </row>
@@ -14769,12 +14769,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,13 +14816,13 @@
         </is>
       </c>
       <c r="N89">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O89">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P89">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q89">
         <v>0</v>
@@ -14855,10 +14855,10 @@
         <v>0</v>
       </c>
       <c r="AA89">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB89">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC89">
         <v>0</v>
@@ -14920,7 +14920,7 @@
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>2026-08-07 20:00:00</t>
+          <t>2026-08-07 20:30:00</t>
         </is>
       </c>
     </row>
@@ -14932,27 +14932,27 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G90">
@@ -15083,7 +15083,7 @@
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>2026-08-07 20:30:00</t>
+          <t>2026-08-07 21:00:00</t>
         </is>
       </c>
     </row>
@@ -15095,27 +15095,27 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,13 +15142,13 @@
         </is>
       </c>
       <c r="N91">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="O91">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="P91">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q91">
         <v>0</v>
@@ -15181,10 +15181,10 @@
         <v>0</v>
       </c>
       <c r="AA91">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB91">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC91">
         <v>0</v>
@@ -15246,7 +15246,7 @@
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>2026-08-07 20:30:00</t>
+          <t>2026-08-07 21:00:00</t>
         </is>
       </c>
     </row>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G92">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G93">
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G94">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G95">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G96">
@@ -16078,22 +16078,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G97">
@@ -16241,22 +16241,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G98">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G99">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G100">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G101">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G102">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G103">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G104">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G105">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G106">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G107">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G108">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G109">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G110">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G112">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G113">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G114">
@@ -19012,22 +19012,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>ETO</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G115">
@@ -19175,7 +19175,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G116">
@@ -19338,22 +19338,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G117">
@@ -19501,7 +19501,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G118">
@@ -19664,7 +19664,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>ETO</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G119">
@@ -19827,22 +19827,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G120">
@@ -19990,22 +19990,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G121">
@@ -20153,7 +20153,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G122">
@@ -20316,7 +20316,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="G123">
@@ -20479,7 +20479,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G124">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G125">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G126">
@@ -20963,27 +20963,27 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G127">
@@ -21114,7 +21114,7 @@
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>2026-08-07 21:00:00</t>
+          <t>2026-08-07 21:30:00</t>
         </is>
       </c>
     </row>
@@ -21126,27 +21126,27 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="G128">
@@ -21276,984 +21276,6 @@
         <v>0</v>
       </c>
       <c r="AU128" t="inlineStr">
-        <is>
-          <t>2026-08-07 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>OFK Vršac</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>Naftagas</t>
-        </is>
-      </c>
-      <c r="G129">
-        <v>0</v>
-      </c>
-      <c r="H129">
-        <v>0</v>
-      </c>
-      <c r="I129">
-        <v>0</v>
-      </c>
-      <c r="J129">
-        <v>0</v>
-      </c>
-      <c r="K129">
-        <v>0</v>
-      </c>
-      <c r="L129">
-        <v>0</v>
-      </c>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N129">
-        <v>0</v>
-      </c>
-      <c r="O129">
-        <v>0</v>
-      </c>
-      <c r="P129">
-        <v>0</v>
-      </c>
-      <c r="Q129">
-        <v>0</v>
-      </c>
-      <c r="R129">
-        <v>0</v>
-      </c>
-      <c r="S129">
-        <v>0</v>
-      </c>
-      <c r="T129">
-        <v>0</v>
-      </c>
-      <c r="U129">
-        <v>0</v>
-      </c>
-      <c r="V129">
-        <v>0</v>
-      </c>
-      <c r="W129">
-        <v>0</v>
-      </c>
-      <c r="X129">
-        <v>0</v>
-      </c>
-      <c r="Y129">
-        <v>0</v>
-      </c>
-      <c r="Z129">
-        <v>0</v>
-      </c>
-      <c r="AA129">
-        <v>0</v>
-      </c>
-      <c r="AB129">
-        <v>0</v>
-      </c>
-      <c r="AC129">
-        <v>0</v>
-      </c>
-      <c r="AD129">
-        <v>0</v>
-      </c>
-      <c r="AE129">
-        <v>0</v>
-      </c>
-      <c r="AF129">
-        <v>0</v>
-      </c>
-      <c r="AG129">
-        <v>0</v>
-      </c>
-      <c r="AH129" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI129" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ129">
-        <v>0</v>
-      </c>
-      <c r="AK129">
-        <v>0</v>
-      </c>
-      <c r="AL129">
-        <v>0</v>
-      </c>
-      <c r="AM129">
-        <v>-1</v>
-      </c>
-      <c r="AN129">
-        <v>-1</v>
-      </c>
-      <c r="AO129">
-        <v>-1</v>
-      </c>
-      <c r="AP129">
-        <v>-1</v>
-      </c>
-      <c r="AQ129">
-        <v>0</v>
-      </c>
-      <c r="AR129">
-        <v>0</v>
-      </c>
-      <c r="AS129">
-        <v>0</v>
-      </c>
-      <c r="AT129">
-        <v>0</v>
-      </c>
-      <c r="AU129" t="inlineStr">
-        <is>
-          <t>2026-08-07 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>Teleoptik</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>Jedinstvo Ub</t>
-        </is>
-      </c>
-      <c r="G130">
-        <v>0</v>
-      </c>
-      <c r="H130">
-        <v>0</v>
-      </c>
-      <c r="I130">
-        <v>0</v>
-      </c>
-      <c r="J130">
-        <v>0</v>
-      </c>
-      <c r="K130">
-        <v>0</v>
-      </c>
-      <c r="L130">
-        <v>0</v>
-      </c>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N130">
-        <v>0</v>
-      </c>
-      <c r="O130">
-        <v>0</v>
-      </c>
-      <c r="P130">
-        <v>0</v>
-      </c>
-      <c r="Q130">
-        <v>0</v>
-      </c>
-      <c r="R130">
-        <v>0</v>
-      </c>
-      <c r="S130">
-        <v>0</v>
-      </c>
-      <c r="T130">
-        <v>0</v>
-      </c>
-      <c r="U130">
-        <v>0</v>
-      </c>
-      <c r="V130">
-        <v>0</v>
-      </c>
-      <c r="W130">
-        <v>0</v>
-      </c>
-      <c r="X130">
-        <v>0</v>
-      </c>
-      <c r="Y130">
-        <v>0</v>
-      </c>
-      <c r="Z130">
-        <v>0</v>
-      </c>
-      <c r="AA130">
-        <v>0</v>
-      </c>
-      <c r="AB130">
-        <v>0</v>
-      </c>
-      <c r="AC130">
-        <v>0</v>
-      </c>
-      <c r="AD130">
-        <v>0</v>
-      </c>
-      <c r="AE130">
-        <v>0</v>
-      </c>
-      <c r="AF130">
-        <v>0</v>
-      </c>
-      <c r="AG130">
-        <v>0</v>
-      </c>
-      <c r="AH130" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI130" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ130">
-        <v>0</v>
-      </c>
-      <c r="AK130">
-        <v>0</v>
-      </c>
-      <c r="AL130">
-        <v>0</v>
-      </c>
-      <c r="AM130">
-        <v>-1</v>
-      </c>
-      <c r="AN130">
-        <v>-1</v>
-      </c>
-      <c r="AO130">
-        <v>-1</v>
-      </c>
-      <c r="AP130">
-        <v>-1</v>
-      </c>
-      <c r="AQ130">
-        <v>0</v>
-      </c>
-      <c r="AR130">
-        <v>0</v>
-      </c>
-      <c r="AS130">
-        <v>0</v>
-      </c>
-      <c r="AT130">
-        <v>0</v>
-      </c>
-      <c r="AU130" t="inlineStr">
-        <is>
-          <t>2026-08-07 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>Bor</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>Napredak</t>
-        </is>
-      </c>
-      <c r="G131">
-        <v>0</v>
-      </c>
-      <c r="H131">
-        <v>0</v>
-      </c>
-      <c r="I131">
-        <v>0</v>
-      </c>
-      <c r="J131">
-        <v>0</v>
-      </c>
-      <c r="K131">
-        <v>0</v>
-      </c>
-      <c r="L131">
-        <v>0</v>
-      </c>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N131">
-        <v>0</v>
-      </c>
-      <c r="O131">
-        <v>0</v>
-      </c>
-      <c r="P131">
-        <v>0</v>
-      </c>
-      <c r="Q131">
-        <v>0</v>
-      </c>
-      <c r="R131">
-        <v>0</v>
-      </c>
-      <c r="S131">
-        <v>0</v>
-      </c>
-      <c r="T131">
-        <v>0</v>
-      </c>
-      <c r="U131">
-        <v>0</v>
-      </c>
-      <c r="V131">
-        <v>0</v>
-      </c>
-      <c r="W131">
-        <v>0</v>
-      </c>
-      <c r="X131">
-        <v>0</v>
-      </c>
-      <c r="Y131">
-        <v>0</v>
-      </c>
-      <c r="Z131">
-        <v>0</v>
-      </c>
-      <c r="AA131">
-        <v>0</v>
-      </c>
-      <c r="AB131">
-        <v>0</v>
-      </c>
-      <c r="AC131">
-        <v>0</v>
-      </c>
-      <c r="AD131">
-        <v>0</v>
-      </c>
-      <c r="AE131">
-        <v>0</v>
-      </c>
-      <c r="AF131">
-        <v>0</v>
-      </c>
-      <c r="AG131">
-        <v>0</v>
-      </c>
-      <c r="AH131" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI131" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ131">
-        <v>0</v>
-      </c>
-      <c r="AK131">
-        <v>0</v>
-      </c>
-      <c r="AL131">
-        <v>0</v>
-      </c>
-      <c r="AM131">
-        <v>-1</v>
-      </c>
-      <c r="AN131">
-        <v>-1</v>
-      </c>
-      <c r="AO131">
-        <v>-1</v>
-      </c>
-      <c r="AP131">
-        <v>-1</v>
-      </c>
-      <c r="AQ131">
-        <v>0</v>
-      </c>
-      <c r="AR131">
-        <v>0</v>
-      </c>
-      <c r="AS131">
-        <v>0</v>
-      </c>
-      <c r="AT131">
-        <v>0</v>
-      </c>
-      <c r="AU131" t="inlineStr">
-        <is>
-          <t>2026-08-07 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>Grafičar</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>Semendrija 1924</t>
-        </is>
-      </c>
-      <c r="G132">
-        <v>0</v>
-      </c>
-      <c r="H132">
-        <v>0</v>
-      </c>
-      <c r="I132">
-        <v>0</v>
-      </c>
-      <c r="J132">
-        <v>0</v>
-      </c>
-      <c r="K132">
-        <v>0</v>
-      </c>
-      <c r="L132">
-        <v>0</v>
-      </c>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N132">
-        <v>0</v>
-      </c>
-      <c r="O132">
-        <v>0</v>
-      </c>
-      <c r="P132">
-        <v>0</v>
-      </c>
-      <c r="Q132">
-        <v>0</v>
-      </c>
-      <c r="R132">
-        <v>0</v>
-      </c>
-      <c r="S132">
-        <v>0</v>
-      </c>
-      <c r="T132">
-        <v>0</v>
-      </c>
-      <c r="U132">
-        <v>0</v>
-      </c>
-      <c r="V132">
-        <v>0</v>
-      </c>
-      <c r="W132">
-        <v>0</v>
-      </c>
-      <c r="X132">
-        <v>0</v>
-      </c>
-      <c r="Y132">
-        <v>0</v>
-      </c>
-      <c r="Z132">
-        <v>0</v>
-      </c>
-      <c r="AA132">
-        <v>0</v>
-      </c>
-      <c r="AB132">
-        <v>0</v>
-      </c>
-      <c r="AC132">
-        <v>0</v>
-      </c>
-      <c r="AD132">
-        <v>0</v>
-      </c>
-      <c r="AE132">
-        <v>0</v>
-      </c>
-      <c r="AF132">
-        <v>0</v>
-      </c>
-      <c r="AG132">
-        <v>0</v>
-      </c>
-      <c r="AH132" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI132" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ132">
-        <v>0</v>
-      </c>
-      <c r="AK132">
-        <v>0</v>
-      </c>
-      <c r="AL132">
-        <v>0</v>
-      </c>
-      <c r="AM132">
-        <v>-1</v>
-      </c>
-      <c r="AN132">
-        <v>-1</v>
-      </c>
-      <c r="AO132">
-        <v>-1</v>
-      </c>
-      <c r="AP132">
-        <v>-1</v>
-      </c>
-      <c r="AQ132">
-        <v>0</v>
-      </c>
-      <c r="AR132">
-        <v>0</v>
-      </c>
-      <c r="AS132">
-        <v>0</v>
-      </c>
-      <c r="AT132">
-        <v>0</v>
-      </c>
-      <c r="AU132" t="inlineStr">
-        <is>
-          <t>2026-08-07 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Chile Primera B</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>Deportes Santa Cruz</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>Puerto Montt</t>
-        </is>
-      </c>
-      <c r="G133">
-        <v>0</v>
-      </c>
-      <c r="H133">
-        <v>0</v>
-      </c>
-      <c r="I133">
-        <v>0</v>
-      </c>
-      <c r="J133">
-        <v>0</v>
-      </c>
-      <c r="K133">
-        <v>0</v>
-      </c>
-      <c r="L133">
-        <v>0</v>
-      </c>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N133">
-        <v>0</v>
-      </c>
-      <c r="O133">
-        <v>0</v>
-      </c>
-      <c r="P133">
-        <v>0</v>
-      </c>
-      <c r="Q133">
-        <v>0</v>
-      </c>
-      <c r="R133">
-        <v>0</v>
-      </c>
-      <c r="S133">
-        <v>0</v>
-      </c>
-      <c r="T133">
-        <v>0</v>
-      </c>
-      <c r="U133">
-        <v>0</v>
-      </c>
-      <c r="V133">
-        <v>0</v>
-      </c>
-      <c r="W133">
-        <v>0</v>
-      </c>
-      <c r="X133">
-        <v>0</v>
-      </c>
-      <c r="Y133">
-        <v>0</v>
-      </c>
-      <c r="Z133">
-        <v>0</v>
-      </c>
-      <c r="AA133">
-        <v>0</v>
-      </c>
-      <c r="AB133">
-        <v>0</v>
-      </c>
-      <c r="AC133">
-        <v>0</v>
-      </c>
-      <c r="AD133">
-        <v>0</v>
-      </c>
-      <c r="AE133">
-        <v>0</v>
-      </c>
-      <c r="AF133">
-        <v>0</v>
-      </c>
-      <c r="AG133">
-        <v>0</v>
-      </c>
-      <c r="AH133" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI133" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ133">
-        <v>0</v>
-      </c>
-      <c r="AK133">
-        <v>0</v>
-      </c>
-      <c r="AL133">
-        <v>0</v>
-      </c>
-      <c r="AM133">
-        <v>-1</v>
-      </c>
-      <c r="AN133">
-        <v>-1</v>
-      </c>
-      <c r="AO133">
-        <v>-1</v>
-      </c>
-      <c r="AP133">
-        <v>-1</v>
-      </c>
-      <c r="AQ133">
-        <v>0</v>
-      </c>
-      <c r="AR133">
-        <v>0</v>
-      </c>
-      <c r="AS133">
-        <v>0</v>
-      </c>
-      <c r="AT133">
-        <v>0</v>
-      </c>
-      <c r="AU133" t="inlineStr">
-        <is>
-          <t>2026-08-07 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Chile Primera División</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>Universidad Católica</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>Cobresal</t>
-        </is>
-      </c>
-      <c r="G134">
-        <v>0</v>
-      </c>
-      <c r="H134">
-        <v>0</v>
-      </c>
-      <c r="I134">
-        <v>0</v>
-      </c>
-      <c r="J134">
-        <v>0</v>
-      </c>
-      <c r="K134">
-        <v>0</v>
-      </c>
-      <c r="L134">
-        <v>0</v>
-      </c>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N134">
-        <v>0</v>
-      </c>
-      <c r="O134">
-        <v>0</v>
-      </c>
-      <c r="P134">
-        <v>0</v>
-      </c>
-      <c r="Q134">
-        <v>0</v>
-      </c>
-      <c r="R134">
-        <v>0</v>
-      </c>
-      <c r="S134">
-        <v>0</v>
-      </c>
-      <c r="T134">
-        <v>0</v>
-      </c>
-      <c r="U134">
-        <v>0</v>
-      </c>
-      <c r="V134">
-        <v>0</v>
-      </c>
-      <c r="W134">
-        <v>0</v>
-      </c>
-      <c r="X134">
-        <v>0</v>
-      </c>
-      <c r="Y134">
-        <v>0</v>
-      </c>
-      <c r="Z134">
-        <v>0</v>
-      </c>
-      <c r="AA134">
-        <v>0</v>
-      </c>
-      <c r="AB134">
-        <v>0</v>
-      </c>
-      <c r="AC134">
-        <v>0</v>
-      </c>
-      <c r="AD134">
-        <v>0</v>
-      </c>
-      <c r="AE134">
-        <v>0</v>
-      </c>
-      <c r="AF134">
-        <v>0</v>
-      </c>
-      <c r="AG134">
-        <v>0</v>
-      </c>
-      <c r="AH134" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI134" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ134">
-        <v>0</v>
-      </c>
-      <c r="AK134">
-        <v>0</v>
-      </c>
-      <c r="AL134">
-        <v>0</v>
-      </c>
-      <c r="AM134">
-        <v>-1</v>
-      </c>
-      <c r="AN134">
-        <v>-1</v>
-      </c>
-      <c r="AO134">
-        <v>-1</v>
-      </c>
-      <c r="AP134">
-        <v>-1</v>
-      </c>
-      <c r="AQ134">
-        <v>0</v>
-      </c>
-      <c r="AR134">
-        <v>0</v>
-      </c>
-      <c r="AS134">
-        <v>0</v>
-      </c>
-      <c r="AT134">
-        <v>0</v>
-      </c>
-      <c r="AU134" t="inlineStr">
         <is>
           <t>2026-08-07 21:30:00</t>
         </is>

--- a/jogos_2026-08-07.xlsx
+++ b/jogos_2026-08-07.xlsx
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="N87">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O87">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P87">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q87">
         <v>0</v>

--- a/jogos_2026-08-07.xlsx
+++ b/jogos_2026-08-07.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU128"/>
+  <dimension ref="A1:AU122"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G90">
@@ -15100,22 +15100,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G91">
@@ -15263,22 +15263,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G92">
@@ -15426,22 +15426,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G93">
@@ -15589,22 +15589,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G94">
@@ -15752,22 +15752,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G95">
@@ -15915,22 +15915,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G96">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G97">
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G98">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G99">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G100">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G101">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G102">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G103">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G104">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G105">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G106">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G107">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G108">
@@ -18034,22 +18034,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>ETO</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G109">
@@ -18197,7 +18197,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G110">
@@ -18360,7 +18360,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G111">
@@ -18523,22 +18523,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G112">
@@ -18686,22 +18686,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G113">
@@ -18849,22 +18849,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G114">
@@ -19012,7 +19012,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>ETO</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G115">
@@ -19175,22 +19175,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G116">
@@ -19338,22 +19338,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="G117">
@@ -19501,7 +19501,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G118">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G119">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G120">
@@ -19985,27 +19985,27 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G121">
@@ -20136,7 +20136,7 @@
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>2026-08-07 21:00:00</t>
+          <t>2026-08-07 21:30:00</t>
         </is>
       </c>
     </row>
@@ -20148,27 +20148,27 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="G122">
@@ -20298,984 +20298,6 @@
         <v>0</v>
       </c>
       <c r="AU122" t="inlineStr">
-        <is>
-          <t>2026-08-07 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>OFK Vršac</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>Naftagas</t>
-        </is>
-      </c>
-      <c r="G123">
-        <v>0</v>
-      </c>
-      <c r="H123">
-        <v>0</v>
-      </c>
-      <c r="I123">
-        <v>0</v>
-      </c>
-      <c r="J123">
-        <v>0</v>
-      </c>
-      <c r="K123">
-        <v>0</v>
-      </c>
-      <c r="L123">
-        <v>0</v>
-      </c>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N123">
-        <v>0</v>
-      </c>
-      <c r="O123">
-        <v>0</v>
-      </c>
-      <c r="P123">
-        <v>0</v>
-      </c>
-      <c r="Q123">
-        <v>0</v>
-      </c>
-      <c r="R123">
-        <v>0</v>
-      </c>
-      <c r="S123">
-        <v>0</v>
-      </c>
-      <c r="T123">
-        <v>0</v>
-      </c>
-      <c r="U123">
-        <v>0</v>
-      </c>
-      <c r="V123">
-        <v>0</v>
-      </c>
-      <c r="W123">
-        <v>0</v>
-      </c>
-      <c r="X123">
-        <v>0</v>
-      </c>
-      <c r="Y123">
-        <v>0</v>
-      </c>
-      <c r="Z123">
-        <v>0</v>
-      </c>
-      <c r="AA123">
-        <v>0</v>
-      </c>
-      <c r="AB123">
-        <v>0</v>
-      </c>
-      <c r="AC123">
-        <v>0</v>
-      </c>
-      <c r="AD123">
-        <v>0</v>
-      </c>
-      <c r="AE123">
-        <v>0</v>
-      </c>
-      <c r="AF123">
-        <v>0</v>
-      </c>
-      <c r="AG123">
-        <v>0</v>
-      </c>
-      <c r="AH123" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI123" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ123">
-        <v>0</v>
-      </c>
-      <c r="AK123">
-        <v>0</v>
-      </c>
-      <c r="AL123">
-        <v>0</v>
-      </c>
-      <c r="AM123">
-        <v>-1</v>
-      </c>
-      <c r="AN123">
-        <v>-1</v>
-      </c>
-      <c r="AO123">
-        <v>-1</v>
-      </c>
-      <c r="AP123">
-        <v>-1</v>
-      </c>
-      <c r="AQ123">
-        <v>0</v>
-      </c>
-      <c r="AR123">
-        <v>0</v>
-      </c>
-      <c r="AS123">
-        <v>0</v>
-      </c>
-      <c r="AT123">
-        <v>0</v>
-      </c>
-      <c r="AU123" t="inlineStr">
-        <is>
-          <t>2026-08-07 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>Teleoptik</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>Jedinstvo Ub</t>
-        </is>
-      </c>
-      <c r="G124">
-        <v>0</v>
-      </c>
-      <c r="H124">
-        <v>0</v>
-      </c>
-      <c r="I124">
-        <v>0</v>
-      </c>
-      <c r="J124">
-        <v>0</v>
-      </c>
-      <c r="K124">
-        <v>0</v>
-      </c>
-      <c r="L124">
-        <v>0</v>
-      </c>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N124">
-        <v>0</v>
-      </c>
-      <c r="O124">
-        <v>0</v>
-      </c>
-      <c r="P124">
-        <v>0</v>
-      </c>
-      <c r="Q124">
-        <v>0</v>
-      </c>
-      <c r="R124">
-        <v>0</v>
-      </c>
-      <c r="S124">
-        <v>0</v>
-      </c>
-      <c r="T124">
-        <v>0</v>
-      </c>
-      <c r="U124">
-        <v>0</v>
-      </c>
-      <c r="V124">
-        <v>0</v>
-      </c>
-      <c r="W124">
-        <v>0</v>
-      </c>
-      <c r="X124">
-        <v>0</v>
-      </c>
-      <c r="Y124">
-        <v>0</v>
-      </c>
-      <c r="Z124">
-        <v>0</v>
-      </c>
-      <c r="AA124">
-        <v>0</v>
-      </c>
-      <c r="AB124">
-        <v>0</v>
-      </c>
-      <c r="AC124">
-        <v>0</v>
-      </c>
-      <c r="AD124">
-        <v>0</v>
-      </c>
-      <c r="AE124">
-        <v>0</v>
-      </c>
-      <c r="AF124">
-        <v>0</v>
-      </c>
-      <c r="AG124">
-        <v>0</v>
-      </c>
-      <c r="AH124" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI124" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ124">
-        <v>0</v>
-      </c>
-      <c r="AK124">
-        <v>0</v>
-      </c>
-      <c r="AL124">
-        <v>0</v>
-      </c>
-      <c r="AM124">
-        <v>-1</v>
-      </c>
-      <c r="AN124">
-        <v>-1</v>
-      </c>
-      <c r="AO124">
-        <v>-1</v>
-      </c>
-      <c r="AP124">
-        <v>-1</v>
-      </c>
-      <c r="AQ124">
-        <v>0</v>
-      </c>
-      <c r="AR124">
-        <v>0</v>
-      </c>
-      <c r="AS124">
-        <v>0</v>
-      </c>
-      <c r="AT124">
-        <v>0</v>
-      </c>
-      <c r="AU124" t="inlineStr">
-        <is>
-          <t>2026-08-07 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>Bor</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>Napredak</t>
-        </is>
-      </c>
-      <c r="G125">
-        <v>0</v>
-      </c>
-      <c r="H125">
-        <v>0</v>
-      </c>
-      <c r="I125">
-        <v>0</v>
-      </c>
-      <c r="J125">
-        <v>0</v>
-      </c>
-      <c r="K125">
-        <v>0</v>
-      </c>
-      <c r="L125">
-        <v>0</v>
-      </c>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N125">
-        <v>0</v>
-      </c>
-      <c r="O125">
-        <v>0</v>
-      </c>
-      <c r="P125">
-        <v>0</v>
-      </c>
-      <c r="Q125">
-        <v>0</v>
-      </c>
-      <c r="R125">
-        <v>0</v>
-      </c>
-      <c r="S125">
-        <v>0</v>
-      </c>
-      <c r="T125">
-        <v>0</v>
-      </c>
-      <c r="U125">
-        <v>0</v>
-      </c>
-      <c r="V125">
-        <v>0</v>
-      </c>
-      <c r="W125">
-        <v>0</v>
-      </c>
-      <c r="X125">
-        <v>0</v>
-      </c>
-      <c r="Y125">
-        <v>0</v>
-      </c>
-      <c r="Z125">
-        <v>0</v>
-      </c>
-      <c r="AA125">
-        <v>0</v>
-      </c>
-      <c r="AB125">
-        <v>0</v>
-      </c>
-      <c r="AC125">
-        <v>0</v>
-      </c>
-      <c r="AD125">
-        <v>0</v>
-      </c>
-      <c r="AE125">
-        <v>0</v>
-      </c>
-      <c r="AF125">
-        <v>0</v>
-      </c>
-      <c r="AG125">
-        <v>0</v>
-      </c>
-      <c r="AH125" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI125" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ125">
-        <v>0</v>
-      </c>
-      <c r="AK125">
-        <v>0</v>
-      </c>
-      <c r="AL125">
-        <v>0</v>
-      </c>
-      <c r="AM125">
-        <v>-1</v>
-      </c>
-      <c r="AN125">
-        <v>-1</v>
-      </c>
-      <c r="AO125">
-        <v>-1</v>
-      </c>
-      <c r="AP125">
-        <v>-1</v>
-      </c>
-      <c r="AQ125">
-        <v>0</v>
-      </c>
-      <c r="AR125">
-        <v>0</v>
-      </c>
-      <c r="AS125">
-        <v>0</v>
-      </c>
-      <c r="AT125">
-        <v>0</v>
-      </c>
-      <c r="AU125" t="inlineStr">
-        <is>
-          <t>2026-08-07 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>Grafičar</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>Semendrija 1924</t>
-        </is>
-      </c>
-      <c r="G126">
-        <v>0</v>
-      </c>
-      <c r="H126">
-        <v>0</v>
-      </c>
-      <c r="I126">
-        <v>0</v>
-      </c>
-      <c r="J126">
-        <v>0</v>
-      </c>
-      <c r="K126">
-        <v>0</v>
-      </c>
-      <c r="L126">
-        <v>0</v>
-      </c>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N126">
-        <v>0</v>
-      </c>
-      <c r="O126">
-        <v>0</v>
-      </c>
-      <c r="P126">
-        <v>0</v>
-      </c>
-      <c r="Q126">
-        <v>0</v>
-      </c>
-      <c r="R126">
-        <v>0</v>
-      </c>
-      <c r="S126">
-        <v>0</v>
-      </c>
-      <c r="T126">
-        <v>0</v>
-      </c>
-      <c r="U126">
-        <v>0</v>
-      </c>
-      <c r="V126">
-        <v>0</v>
-      </c>
-      <c r="W126">
-        <v>0</v>
-      </c>
-      <c r="X126">
-        <v>0</v>
-      </c>
-      <c r="Y126">
-        <v>0</v>
-      </c>
-      <c r="Z126">
-        <v>0</v>
-      </c>
-      <c r="AA126">
-        <v>0</v>
-      </c>
-      <c r="AB126">
-        <v>0</v>
-      </c>
-      <c r="AC126">
-        <v>0</v>
-      </c>
-      <c r="AD126">
-        <v>0</v>
-      </c>
-      <c r="AE126">
-        <v>0</v>
-      </c>
-      <c r="AF126">
-        <v>0</v>
-      </c>
-      <c r="AG126">
-        <v>0</v>
-      </c>
-      <c r="AH126" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI126" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ126">
-        <v>0</v>
-      </c>
-      <c r="AK126">
-        <v>0</v>
-      </c>
-      <c r="AL126">
-        <v>0</v>
-      </c>
-      <c r="AM126">
-        <v>-1</v>
-      </c>
-      <c r="AN126">
-        <v>-1</v>
-      </c>
-      <c r="AO126">
-        <v>-1</v>
-      </c>
-      <c r="AP126">
-        <v>-1</v>
-      </c>
-      <c r="AQ126">
-        <v>0</v>
-      </c>
-      <c r="AR126">
-        <v>0</v>
-      </c>
-      <c r="AS126">
-        <v>0</v>
-      </c>
-      <c r="AT126">
-        <v>0</v>
-      </c>
-      <c r="AU126" t="inlineStr">
-        <is>
-          <t>2026-08-07 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Chile Primera B</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>Deportes Santa Cruz</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>Puerto Montt</t>
-        </is>
-      </c>
-      <c r="G127">
-        <v>0</v>
-      </c>
-      <c r="H127">
-        <v>0</v>
-      </c>
-      <c r="I127">
-        <v>0</v>
-      </c>
-      <c r="J127">
-        <v>0</v>
-      </c>
-      <c r="K127">
-        <v>0</v>
-      </c>
-      <c r="L127">
-        <v>0</v>
-      </c>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N127">
-        <v>0</v>
-      </c>
-      <c r="O127">
-        <v>0</v>
-      </c>
-      <c r="P127">
-        <v>0</v>
-      </c>
-      <c r="Q127">
-        <v>0</v>
-      </c>
-      <c r="R127">
-        <v>0</v>
-      </c>
-      <c r="S127">
-        <v>0</v>
-      </c>
-      <c r="T127">
-        <v>0</v>
-      </c>
-      <c r="U127">
-        <v>0</v>
-      </c>
-      <c r="V127">
-        <v>0</v>
-      </c>
-      <c r="W127">
-        <v>0</v>
-      </c>
-      <c r="X127">
-        <v>0</v>
-      </c>
-      <c r="Y127">
-        <v>0</v>
-      </c>
-      <c r="Z127">
-        <v>0</v>
-      </c>
-      <c r="AA127">
-        <v>0</v>
-      </c>
-      <c r="AB127">
-        <v>0</v>
-      </c>
-      <c r="AC127">
-        <v>0</v>
-      </c>
-      <c r="AD127">
-        <v>0</v>
-      </c>
-      <c r="AE127">
-        <v>0</v>
-      </c>
-      <c r="AF127">
-        <v>0</v>
-      </c>
-      <c r="AG127">
-        <v>0</v>
-      </c>
-      <c r="AH127" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI127" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ127">
-        <v>0</v>
-      </c>
-      <c r="AK127">
-        <v>0</v>
-      </c>
-      <c r="AL127">
-        <v>0</v>
-      </c>
-      <c r="AM127">
-        <v>-1</v>
-      </c>
-      <c r="AN127">
-        <v>-1</v>
-      </c>
-      <c r="AO127">
-        <v>-1</v>
-      </c>
-      <c r="AP127">
-        <v>-1</v>
-      </c>
-      <c r="AQ127">
-        <v>0</v>
-      </c>
-      <c r="AR127">
-        <v>0</v>
-      </c>
-      <c r="AS127">
-        <v>0</v>
-      </c>
-      <c r="AT127">
-        <v>0</v>
-      </c>
-      <c r="AU127" t="inlineStr">
-        <is>
-          <t>2026-08-07 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Chile Primera División</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>Universidad Católica</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>Cobresal</t>
-        </is>
-      </c>
-      <c r="G128">
-        <v>0</v>
-      </c>
-      <c r="H128">
-        <v>0</v>
-      </c>
-      <c r="I128">
-        <v>0</v>
-      </c>
-      <c r="J128">
-        <v>0</v>
-      </c>
-      <c r="K128">
-        <v>0</v>
-      </c>
-      <c r="L128">
-        <v>0</v>
-      </c>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N128">
-        <v>0</v>
-      </c>
-      <c r="O128">
-        <v>0</v>
-      </c>
-      <c r="P128">
-        <v>0</v>
-      </c>
-      <c r="Q128">
-        <v>0</v>
-      </c>
-      <c r="R128">
-        <v>0</v>
-      </c>
-      <c r="S128">
-        <v>0</v>
-      </c>
-      <c r="T128">
-        <v>0</v>
-      </c>
-      <c r="U128">
-        <v>0</v>
-      </c>
-      <c r="V128">
-        <v>0</v>
-      </c>
-      <c r="W128">
-        <v>0</v>
-      </c>
-      <c r="X128">
-        <v>0</v>
-      </c>
-      <c r="Y128">
-        <v>0</v>
-      </c>
-      <c r="Z128">
-        <v>0</v>
-      </c>
-      <c r="AA128">
-        <v>0</v>
-      </c>
-      <c r="AB128">
-        <v>0</v>
-      </c>
-      <c r="AC128">
-        <v>0</v>
-      </c>
-      <c r="AD128">
-        <v>0</v>
-      </c>
-      <c r="AE128">
-        <v>0</v>
-      </c>
-      <c r="AF128">
-        <v>0</v>
-      </c>
-      <c r="AG128">
-        <v>0</v>
-      </c>
-      <c r="AH128" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI128" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ128">
-        <v>0</v>
-      </c>
-      <c r="AK128">
-        <v>0</v>
-      </c>
-      <c r="AL128">
-        <v>0</v>
-      </c>
-      <c r="AM128">
-        <v>-1</v>
-      </c>
-      <c r="AN128">
-        <v>-1</v>
-      </c>
-      <c r="AO128">
-        <v>-1</v>
-      </c>
-      <c r="AP128">
-        <v>-1</v>
-      </c>
-      <c r="AQ128">
-        <v>0</v>
-      </c>
-      <c r="AR128">
-        <v>0</v>
-      </c>
-      <c r="AS128">
-        <v>0</v>
-      </c>
-      <c r="AT128">
-        <v>0</v>
-      </c>
-      <c r="AU128" t="inlineStr">
         <is>
           <t>2026-08-07 21:30:00</t>
         </is>

--- a/jogos_2026-08-07.xlsx
+++ b/jogos_2026-08-07.xlsx
@@ -644,55 +644,55 @@
         <v>1.99</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -807,55 +807,55 @@
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>5.48</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1785,34 +1785,34 @@
         <v>3.04</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA9">
         <v>2</v>
@@ -1821,19 +1821,19 @@
         <v>1.76</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1948,55 +1948,55 @@
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2926,55 +2926,55 @@
         <v>2.75</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -5371,55 +5371,55 @@
         <v>4.51</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5697,55 +5697,55 @@
         <v>3.2</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -6542,10 +6542,10 @@
         <v>0</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC38">
         <v>0</v>
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O55">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P55">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q55">
         <v>0</v>

--- a/jogos_2026-08-07.xlsx
+++ b/jogos_2026-08-07.xlsx
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G25">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G26">

--- a/jogos_2026-08-07.xlsx
+++ b/jogos_2026-08-07.xlsx
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G94">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G95">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G96">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G97">
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G98">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G99">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G100">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G101">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G102">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G103">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G104">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G105">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G106">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G107">

--- a/jogos_2026-08-07.xlsx
+++ b/jogos_2026-08-07.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU122"/>
+  <dimension ref="A1:AU121"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3252,55 +3252,55 @@
         <v>4.19</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -6135,22 +6135,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK36">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6293,12 +6293,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.82</v>
+        <v>1.88</v>
       </c>
       <c r="O37">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="P37">
-        <v>2.3</v>
+        <v>3.99</v>
       </c>
       <c r="Q37">
         <v>0</v>
@@ -6379,10 +6379,10 @@
         <v>0</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC37">
         <v>0</v>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>2026-08-07 14:00:00</t>
+          <t>2026-08-07 14:30:00</t>
         </is>
       </c>
     </row>
@@ -6461,22 +6461,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O38">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="P38">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -6542,10 +6542,10 @@
         <v>0</v>
       </c>
       <c r="AA38">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB38">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC38">
         <v>0</v>
@@ -6624,22 +6624,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G39">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>5.53</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="O41">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="P41">
-        <v>5.53</v>
+        <v>0</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -7113,7 +7113,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y42">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK42">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7271,12 +7271,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>BSK Banja Luka</t>
         </is>
       </c>
       <c r="G43">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>2026-08-07 14:30:00</t>
+          <t>2026-08-07 15:00:00</t>
         </is>
       </c>
     </row>
@@ -7439,7 +7439,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>BSK Banja Luka</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G44">
@@ -7602,7 +7602,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S45">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T45">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="U45">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V45">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W45">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X45">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y45">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z45">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA45">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB45">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC45">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD45">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE45">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF45">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG45">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK45">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7765,7 +7765,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G46">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O47">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P47">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q47">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R47">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="S47">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T47">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="U47">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="V47">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W47">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X47">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y47">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z47">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AA47">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB47">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC47">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD47">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE47">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF47">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG47">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK47">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O48">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q48">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R48">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S48">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T48">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U48">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V48">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W48">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X48">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y48">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z48">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA48">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB48">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC48">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD48">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE48">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF48">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG48">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK48">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T49">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U49">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="V49">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W49">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X49">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z49">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC49">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD49">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE49">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF49">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG49">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AK49">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q50">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S50">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T50">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U50">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V50">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W50">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X50">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y50">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z50">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA50">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB50">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AC50">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD50">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE50">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF50">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG50">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK50">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O51">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P51">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="Q51">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R51">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="S51">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T51">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="U51">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="V51">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W51">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X51">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z51">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AA51">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AB51">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC51">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD51">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE51">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF51">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG51">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK51">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8738,12 +8738,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O52">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P52">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="Q52">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="S52">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T52">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U52">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V52">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="W52">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X52">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y52">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z52">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA52">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AB52">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AC52">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD52">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE52">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF52">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG52">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK52">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>2026-08-07 15:00:00</t>
+          <t>2026-08-07 15:15:00</t>
         </is>
       </c>
     </row>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.3</v>
+        <v>2.35</v>
       </c>
       <c r="O53">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="P53">
-        <v>8.1</v>
+        <v>2.5</v>
       </c>
       <c r="Q53">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="R53">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S53">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T53">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U53">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="V53">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W53">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X53">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y53">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z53">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA53">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB53">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AC53">
-        <v>1.78</v>
+        <v>2.08</v>
       </c>
       <c r="AD53">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="AE53">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF53">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG53">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK53">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9064,12 +9064,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.35</v>
+        <v>2.12</v>
       </c>
       <c r="O54">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="P54">
+        <v>3.05</v>
+      </c>
+      <c r="Q54">
+        <v>2.63</v>
+      </c>
+      <c r="R54">
+        <v>2.25</v>
+      </c>
+      <c r="S54">
+        <v>1.31</v>
+      </c>
+      <c r="T54">
+        <v>3.02</v>
+      </c>
+      <c r="U54">
         <v>2.5</v>
       </c>
-      <c r="Q54">
-        <v>0</v>
-      </c>
-      <c r="R54">
-        <v>0</v>
-      </c>
-      <c r="S54">
-        <v>0</v>
-      </c>
-      <c r="T54">
-        <v>0</v>
-      </c>
-      <c r="U54">
-        <v>0</v>
-      </c>
       <c r="V54">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W54">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X54">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y54">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z54">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AA54">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB54">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AC54">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD54">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE54">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF54">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG54">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK54">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9215,7 +9215,7 @@
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>2026-08-07 15:15:00</t>
+          <t>2026-08-07 15:30:00</t>
         </is>
       </c>
     </row>
@@ -9232,7 +9232,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O55">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P55">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -9395,7 +9395,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Wacker Innsbruck</t>
         </is>
       </c>
       <c r="G56">
@@ -9558,7 +9558,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Wacker Innsbruck</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G57">
@@ -9721,7 +9721,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="O58">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="P58">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q58">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R58">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S58">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T58">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U58">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V58">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W58">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X58">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y58">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z58">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA58">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AB58">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC58">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD58">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE58">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF58">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG58">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK58">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9884,7 +9884,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G59">
@@ -10047,7 +10047,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G60">
@@ -10205,12 +10205,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="N61">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O61">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="P61">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="Q61">
         <v>0</v>
@@ -10356,7 +10356,7 @@
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>2026-08-07 15:30:00</t>
+          <t>2026-08-07 15:45:00</t>
         </is>
       </c>
     </row>
@@ -10373,22 +10373,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,13 +10415,13 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="O62">
-        <v>4.65</v>
+        <v>4.3</v>
       </c>
       <c r="P62">
-        <v>4.9</v>
+        <v>6.84</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.44</v>
+        <v>2.01</v>
       </c>
       <c r="O63">
-        <v>4.3</v>
+        <v>3.55</v>
       </c>
       <c r="P63">
-        <v>6.84</v>
+        <v>3.41</v>
       </c>
       <c r="Q63">
         <v>0</v>
@@ -10699,22 +10699,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O64">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P64">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>La Roche VF</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G65">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>La Roche VF</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O66">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P66">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="N67">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O67">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P67">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,13 +11393,13 @@
         </is>
       </c>
       <c r="N68">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O68">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P68">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="Q68">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.04</v>
+        <v>2.6</v>
       </c>
       <c r="O69">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P69">
-        <v>3.65</v>
+        <v>2.5</v>
       </c>
       <c r="Q69">
         <v>0</v>
@@ -11595,10 +11595,10 @@
         <v>0</v>
       </c>
       <c r="AA69">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB69">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC69">
         <v>0</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O70">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P70">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q70">
         <v>0</v>
@@ -11758,10 +11758,10 @@
         <v>0</v>
       </c>
       <c r="AA70">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB70">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC70">
         <v>0</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="N71">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O71">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P71">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Q71">
         <v>0</v>
@@ -11921,10 +11921,10 @@
         <v>0</v>
       </c>
       <c r="AA71">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB71">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC71">
         <v>0</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,13 +12045,13 @@
         </is>
       </c>
       <c r="N72">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O72">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P72">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="Q72">
         <v>0</v>
@@ -12084,10 +12084,10 @@
         <v>0</v>
       </c>
       <c r="AA72">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB72">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC72">
         <v>0</v>
@@ -12166,22 +12166,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,13 +12208,13 @@
         </is>
       </c>
       <c r="N73">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O73">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P73">
-        <v>0</v>
+        <v>6.56</v>
       </c>
       <c r="Q73">
         <v>0</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O74">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P74">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q74">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,13 +12534,13 @@
         </is>
       </c>
       <c r="N75">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O75">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P75">
-        <v>0</v>
+        <v>6.17</v>
       </c>
       <c r="Q75">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,13 +12697,13 @@
         </is>
       </c>
       <c r="N76">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O76">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P76">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,13 +12860,13 @@
         </is>
       </c>
       <c r="N77">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O77">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P77">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q77">
         <v>0</v>
@@ -12981,22 +12981,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,13 +13023,13 @@
         </is>
       </c>
       <c r="N78">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O78">
-        <v>0</v>
+        <v>5.82</v>
       </c>
       <c r="P78">
-        <v>0</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="Q78">
         <v>0</v>
@@ -13062,10 +13062,10 @@
         <v>0</v>
       </c>
       <c r="AA78">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB78">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC78">
         <v>0</v>
@@ -13139,27 +13139,27 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,13 +13186,13 @@
         </is>
       </c>
       <c r="N79">
-        <v>1.3</v>
+        <v>1.66</v>
       </c>
       <c r="O79">
-        <v>5.82</v>
+        <v>4</v>
       </c>
       <c r="P79">
-        <v>9.550000000000001</v>
+        <v>4.65</v>
       </c>
       <c r="Q79">
         <v>0</v>
@@ -13290,7 +13290,7 @@
       </c>
       <c r="AU79" t="inlineStr">
         <is>
-          <t>2026-08-07 15:45:00</t>
+          <t>2026-08-07 16:00:00</t>
         </is>
       </c>
     </row>
@@ -13307,22 +13307,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,13 +13349,13 @@
         </is>
       </c>
       <c r="N80">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O80">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P80">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="Q80">
         <v>0</v>
@@ -13465,12 +13465,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O81">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="P81">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q81">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R81">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S81">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T81">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U81">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V81">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W81">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X81">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y81">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z81">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA81">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB81">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC81">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD81">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE81">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF81">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG81">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AK81">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13616,7 +13616,7 @@
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>2026-08-07 16:00:00</t>
+          <t>2026-08-07 16:15:00</t>
         </is>
       </c>
     </row>
@@ -13628,27 +13628,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,13 +13675,13 @@
         </is>
       </c>
       <c r="N82">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O82">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="P82">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q82">
         <v>0</v>
@@ -13714,10 +13714,10 @@
         <v>0</v>
       </c>
       <c r="AA82">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB82">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC82">
         <v>0</v>
@@ -13779,7 +13779,7 @@
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>2026-08-07 16:15:00</t>
+          <t>2026-08-07 18:15:00</t>
         </is>
       </c>
     </row>
@@ -13791,12 +13791,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G83">
@@ -13942,7 +13942,7 @@
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>2026-08-07 18:15:00</t>
+          <t>2026-08-07 19:00:00</t>
         </is>
       </c>
     </row>
@@ -13954,12 +13954,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O84">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P84">
-        <v>0</v>
+        <v>4.64</v>
       </c>
       <c r="Q84">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="R84">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S84">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T84">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U84">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="V84">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W84">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X84">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y84">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z84">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA84">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB84">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC84">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AD84">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE84">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF84">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG84">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK84">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14105,7 +14105,7 @@
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>2026-08-07 19:00:00</t>
+          <t>2026-08-07 19:30:00</t>
         </is>
       </c>
     </row>
@@ -14117,12 +14117,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,13 +14164,13 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O85">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P85">
-        <v>4.64</v>
+        <v>0</v>
       </c>
       <c r="Q85">
         <v>0</v>
@@ -14203,10 +14203,10 @@
         <v>0</v>
       </c>
       <c r="AA85">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB85">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC85">
         <v>0</v>
@@ -14268,7 +14268,7 @@
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>2026-08-07 19:30:00</t>
+          <t>2026-08-07 20:00:00</t>
         </is>
       </c>
     </row>
@@ -14285,7 +14285,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,13 +14327,13 @@
         </is>
       </c>
       <c r="N86">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O86">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P86">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q86">
         <v>0</v>
@@ -14443,12 +14443,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="N87">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="O87">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P87">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>2026-08-07 20:00:00</t>
+          <t>2026-08-07 20:30:00</t>
         </is>
       </c>
     </row>
@@ -14611,7 +14611,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,64 +14653,64 @@
         </is>
       </c>
       <c r="N88">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O88">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P88">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q88">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="R88">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S88">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T88">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U88">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="V88">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W88">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X88">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y88">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z88">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA88">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB88">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC88">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD88">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE88">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF88">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG88">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK88">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14769,27 +14769,27 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,13 +14816,13 @@
         </is>
       </c>
       <c r="N89">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="O89">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="P89">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q89">
         <v>0</v>
@@ -14855,10 +14855,10 @@
         <v>0</v>
       </c>
       <c r="AA89">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB89">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC89">
         <v>0</v>
@@ -14920,7 +14920,7 @@
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>2026-08-07 20:30:00</t>
+          <t>2026-08-07 21:00:00</t>
         </is>
       </c>
     </row>
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G90">
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G91">
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G92">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G93">
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G94">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G95">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G96">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G97">
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G98">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G99">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G100">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G101">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G102">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G103">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G104">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G105">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G106">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G107">
@@ -17871,22 +17871,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>ETO</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G108">
@@ -18034,22 +18034,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>ETO</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G109">
@@ -18197,7 +18197,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G110">
@@ -18360,22 +18360,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G111">
@@ -18523,7 +18523,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G112">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G113">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G114">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G115">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="G116">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G117">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G118">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G119">
@@ -19822,27 +19822,27 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G120">
@@ -19973,7 +19973,7 @@
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>2026-08-07 21:00:00</t>
+          <t>2026-08-07 21:30:00</t>
         </is>
       </c>
     </row>
@@ -19990,7 +19990,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="G121">
@@ -20135,169 +20135,6 @@
         <v>0</v>
       </c>
       <c r="AU121" t="inlineStr">
-        <is>
-          <t>2026-08-07 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Chile Primera División</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>Universidad Católica</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>Cobresal</t>
-        </is>
-      </c>
-      <c r="G122">
-        <v>0</v>
-      </c>
-      <c r="H122">
-        <v>0</v>
-      </c>
-      <c r="I122">
-        <v>0</v>
-      </c>
-      <c r="J122">
-        <v>0</v>
-      </c>
-      <c r="K122">
-        <v>0</v>
-      </c>
-      <c r="L122">
-        <v>0</v>
-      </c>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N122">
-        <v>0</v>
-      </c>
-      <c r="O122">
-        <v>0</v>
-      </c>
-      <c r="P122">
-        <v>0</v>
-      </c>
-      <c r="Q122">
-        <v>0</v>
-      </c>
-      <c r="R122">
-        <v>0</v>
-      </c>
-      <c r="S122">
-        <v>0</v>
-      </c>
-      <c r="T122">
-        <v>0</v>
-      </c>
-      <c r="U122">
-        <v>0</v>
-      </c>
-      <c r="V122">
-        <v>0</v>
-      </c>
-      <c r="W122">
-        <v>0</v>
-      </c>
-      <c r="X122">
-        <v>0</v>
-      </c>
-      <c r="Y122">
-        <v>0</v>
-      </c>
-      <c r="Z122">
-        <v>0</v>
-      </c>
-      <c r="AA122">
-        <v>0</v>
-      </c>
-      <c r="AB122">
-        <v>0</v>
-      </c>
-      <c r="AC122">
-        <v>0</v>
-      </c>
-      <c r="AD122">
-        <v>0</v>
-      </c>
-      <c r="AE122">
-        <v>0</v>
-      </c>
-      <c r="AF122">
-        <v>0</v>
-      </c>
-      <c r="AG122">
-        <v>0</v>
-      </c>
-      <c r="AH122" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI122" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ122">
-        <v>0</v>
-      </c>
-      <c r="AK122">
-        <v>0</v>
-      </c>
-      <c r="AL122">
-        <v>0</v>
-      </c>
-      <c r="AM122">
-        <v>-1</v>
-      </c>
-      <c r="AN122">
-        <v>-1</v>
-      </c>
-      <c r="AO122">
-        <v>-1</v>
-      </c>
-      <c r="AP122">
-        <v>-1</v>
-      </c>
-      <c r="AQ122">
-        <v>0</v>
-      </c>
-      <c r="AR122">
-        <v>0</v>
-      </c>
-      <c r="AS122">
-        <v>0</v>
-      </c>
-      <c r="AT122">
-        <v>0</v>
-      </c>
-      <c r="AU122" t="inlineStr">
         <is>
           <t>2026-08-07 21:30:00</t>
         </is>

--- a/jogos_2026-08-07.xlsx
+++ b/jogos_2026-08-07.xlsx
@@ -3578,10 +3578,10 @@
         <v>2.34</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S20">
         <v>0</v>
@@ -3590,43 +3590,43 @@
         <v>0</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X20">
         <v>0</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -6349,34 +6349,34 @@
         <v>3.99</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA37">
         <v>1.95</v>
@@ -6385,19 +6385,19 @@
         <v>1.73</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>5.53</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK39">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="O40">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="P40">
-        <v>5.53</v>
+        <v>0</v>
       </c>
       <c r="Q40">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="R40">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S40">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T40">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U40">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="V40">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="W40">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X40">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y40">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z40">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA40">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AB40">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AC40">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD40">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE40">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AF40">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG40">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK40">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.27</v>
+        <v>1.44</v>
       </c>
       <c r="O47">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="P47">
-        <v>2.7</v>
+        <v>5.45</v>
       </c>
       <c r="Q47">
-        <v>2.63</v>
+        <v>1.83</v>
       </c>
       <c r="R47">
-        <v>2.53</v>
+        <v>2.76</v>
       </c>
       <c r="S47">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="T47">
-        <v>3.68</v>
+        <v>3.86</v>
       </c>
       <c r="U47">
-        <v>2.16</v>
+        <v>2.11</v>
       </c>
       <c r="V47">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="W47">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X47">
         <v>1.02</v>
       </c>
       <c r="Y47">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Z47">
-        <v>5.35</v>
+        <v>5.45</v>
       </c>
       <c r="AA47">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AB47">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AC47">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AD47">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AE47">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AF47">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AG47">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AK47">
-        <v>1.6</v>
+        <v>2.64</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,80 +8296,80 @@
         </is>
       </c>
       <c r="N49">
-        <v>4.46</v>
+        <v>2.27</v>
       </c>
       <c r="O49">
-        <v>4.05</v>
+        <v>3.8</v>
       </c>
       <c r="P49">
-        <v>1.66</v>
+        <v>2.7</v>
       </c>
       <c r="Q49">
-        <v>4.5</v>
+        <v>2.63</v>
       </c>
       <c r="R49">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="S49">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T49">
-        <v>3.8</v>
+        <v>3.68</v>
       </c>
       <c r="U49">
-        <v>2.27</v>
+        <v>2.16</v>
       </c>
       <c r="V49">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="W49">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X49">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y49">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="Z49">
-        <v>4.6</v>
+        <v>5.35</v>
       </c>
       <c r="AA49">
-        <v>1.65</v>
+        <v>1.42</v>
       </c>
       <c r="AB49">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AC49">
-        <v>2.35</v>
+        <v>2.19</v>
       </c>
       <c r="AD49">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AE49">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AF49">
+        <v>1.44</v>
+      </c>
+      <c r="AG49">
+        <v>2.63</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ49">
+        <v>1.25</v>
+      </c>
+      <c r="AK49">
         <v>1.6</v>
-      </c>
-      <c r="AG49">
-        <v>2.32</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ49">
-        <v>2.05</v>
-      </c>
-      <c r="AK49">
-        <v>1.2</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,34 +8459,34 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.32</v>
+        <v>4.46</v>
       </c>
       <c r="O50">
-        <v>3.6</v>
+        <v>4.05</v>
       </c>
       <c r="P50">
-        <v>2.7</v>
+        <v>1.66</v>
       </c>
       <c r="Q50">
-        <v>2.82</v>
+        <v>4.5</v>
       </c>
       <c r="R50">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="S50">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T50">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="U50">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="V50">
         <v>1.57</v>
       </c>
       <c r="W50">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X50">
         <v>1.03</v>
@@ -8495,44 +8495,44 @@
         <v>1.17</v>
       </c>
       <c r="Z50">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AA50">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AB50">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="AC50">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AD50">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AE50">
+        <v>1.22</v>
+      </c>
+      <c r="AF50">
+        <v>1.6</v>
+      </c>
+      <c r="AG50">
+        <v>2.32</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ50">
+        <v>2.05</v>
+      </c>
+      <c r="AK50">
         <v>1.2</v>
-      </c>
-      <c r="AF50">
-        <v>1.45</v>
-      </c>
-      <c r="AG50">
-        <v>2.5</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ50">
-        <v>1.3</v>
-      </c>
-      <c r="AK50">
-        <v>1.53</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.44</v>
+        <v>2.32</v>
       </c>
       <c r="O51">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="P51">
-        <v>5.45</v>
+        <v>2.7</v>
       </c>
       <c r="Q51">
-        <v>1.83</v>
+        <v>2.82</v>
       </c>
       <c r="R51">
-        <v>2.76</v>
+        <v>2.25</v>
       </c>
       <c r="S51">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="T51">
-        <v>3.86</v>
+        <v>3.6</v>
       </c>
       <c r="U51">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="V51">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="W51">
         <v>1.15</v>
       </c>
       <c r="X51">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y51">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="Z51">
-        <v>5.45</v>
+        <v>4.8</v>
       </c>
       <c r="AA51">
-        <v>1.39</v>
+        <v>1.56</v>
       </c>
       <c r="AB51">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
       <c r="AC51">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AD51">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AE51">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AF51">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="AG51">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AK51">
-        <v>2.64</v>
+        <v>1.53</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -10261,55 +10261,55 @@
         <v>4.9</v>
       </c>
       <c r="Q61">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R61">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S61">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T61">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U61">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V61">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W61">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X61">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y61">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z61">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AA61">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB61">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AC61">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AD61">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE61">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF61">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG61">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK61">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10424,55 +10424,55 @@
         <v>6.84</v>
       </c>
       <c r="Q62">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R62">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S62">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T62">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U62">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V62">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W62">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y62">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z62">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="AA62">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB62">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC62">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD62">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE62">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF62">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG62">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK62">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10587,55 +10587,55 @@
         <v>3.41</v>
       </c>
       <c r="Q63">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R63">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S63">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T63">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U63">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V63">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W63">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X63">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y63">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z63">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA63">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB63">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC63">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AD63">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE63">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF63">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG63">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK63">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,19 +12208,19 @@
         </is>
       </c>
       <c r="N73">
-        <v>1.43</v>
+        <v>1.98</v>
       </c>
       <c r="O73">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="P73">
-        <v>6.56</v>
+        <v>3.3</v>
       </c>
       <c r="Q73">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="R73">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S73">
         <v>0</v>
@@ -12229,10 +12229,10 @@
         <v>0</v>
       </c>
       <c r="U73">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V73">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W73">
         <v>0</v>
@@ -12241,31 +12241,31 @@
         <v>0</v>
       </c>
       <c r="Y73">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z73">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA73">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB73">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC73">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD73">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE73">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF73">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG73">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK73">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12380,10 +12380,10 @@
         <v>3.25</v>
       </c>
       <c r="Q74">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R74">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S74">
         <v>0</v>
@@ -12392,10 +12392,10 @@
         <v>0</v>
       </c>
       <c r="U74">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V74">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W74">
         <v>0</v>
@@ -12404,31 +12404,31 @@
         <v>0</v>
       </c>
       <c r="Y74">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z74">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA74">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB74">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC74">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD74">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE74">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF74">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG74">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK74">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,25 +12534,25 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.41</v>
+        <v>2.3</v>
       </c>
       <c r="O75">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="P75">
-        <v>6.17</v>
+        <v>2.94</v>
       </c>
       <c r="Q75">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R75">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S75">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T75">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U75">
         <v>0</v>
@@ -12567,31 +12567,31 @@
         <v>0</v>
       </c>
       <c r="Y75">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z75">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA75">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB75">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC75">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD75">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE75">
         <v>0</v>
       </c>
       <c r="AF75">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG75">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK75">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,19 +12697,19 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.3</v>
+        <v>1.41</v>
       </c>
       <c r="O76">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="P76">
-        <v>2.94</v>
+        <v>6.17</v>
       </c>
       <c r="Q76">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="R76">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S76">
         <v>0</v>
@@ -12718,10 +12718,10 @@
         <v>0</v>
       </c>
       <c r="U76">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="V76">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W76">
         <v>0</v>
@@ -12730,31 +12730,31 @@
         <v>0</v>
       </c>
       <c r="Y76">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z76">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA76">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB76">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AC76">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AD76">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE76">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF76">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG76">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK76">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,13 +12860,13 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.98</v>
+        <v>1.43</v>
       </c>
       <c r="O77">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="P77">
-        <v>3.3</v>
+        <v>6.56</v>
       </c>
       <c r="Q77">
         <v>0</v>
@@ -13195,55 +13195,55 @@
         <v>4.65</v>
       </c>
       <c r="Q79">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="R79">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S79">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T79">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U79">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V79">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W79">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X79">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y79">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z79">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA79">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB79">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC79">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD79">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE79">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF79">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG79">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK79">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -14336,55 +14336,55 @@
         <v>4.1</v>
       </c>
       <c r="Q86">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R86">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S86">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T86">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U86">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V86">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W86">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X86">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y86">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z86">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA86">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB86">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC86">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD86">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE86">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF86">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG86">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK86">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O90">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P90">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q90">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R90">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S90">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="T90">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U90">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="V90">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W90">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X90">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y90">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z90">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA90">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AB90">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AC90">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD90">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE90">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF90">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG90">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK90">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,13 +15142,13 @@
         </is>
       </c>
       <c r="N91">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O91">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P91">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q91">
         <v>0</v>
@@ -15181,10 +15181,10 @@
         <v>0</v>
       </c>
       <c r="AA91">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB91">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC91">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,64 +15305,64 @@
         </is>
       </c>
       <c r="N92">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O92">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P92">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Q92">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R92">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S92">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="T92">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U92">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="V92">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W92">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X92">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y92">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z92">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AA92">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AB92">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC92">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="AD92">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE92">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF92">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AG92">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK92">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O93">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P93">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="Q93">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="R93">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="S93">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="T93">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U93">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="V93">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W93">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X93">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Y93">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z93">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AA93">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AB93">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC93">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AD93">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE93">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF93">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AG93">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK93">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,13 +15631,13 @@
         </is>
       </c>
       <c r="N94">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O94">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P94">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q94">
         <v>0</v>
@@ -15670,10 +15670,10 @@
         <v>0</v>
       </c>
       <c r="AA94">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB94">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC94">
         <v>0</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,13 +15794,13 @@
         </is>
       </c>
       <c r="N95">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O95">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P95">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="Q95">
         <v>0</v>
@@ -15833,10 +15833,10 @@
         <v>0</v>
       </c>
       <c r="AA95">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB95">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC95">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,13 +15957,13 @@
         </is>
       </c>
       <c r="N96">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="O96">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="P96">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="Q96">
         <v>0</v>
@@ -15996,10 +15996,10 @@
         <v>0</v>
       </c>
       <c r="AA96">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB96">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC96">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,13 +16120,13 @@
         </is>
       </c>
       <c r="N97">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O97">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P97">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="Q97">
         <v>0</v>
@@ -16159,10 +16159,10 @@
         <v>0</v>
       </c>
       <c r="AA97">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB97">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC97">
         <v>0</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,13 +16283,13 @@
         </is>
       </c>
       <c r="N98">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O98">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P98">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Q98">
         <v>0</v>
@@ -16322,10 +16322,10 @@
         <v>0</v>
       </c>
       <c r="AA98">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB98">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC98">
         <v>0</v>
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,13 +16446,13 @@
         </is>
       </c>
       <c r="N99">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O99">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="P99">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q99">
         <v>0</v>
@@ -16485,10 +16485,10 @@
         <v>0</v>
       </c>
       <c r="AA99">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB99">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC99">
         <v>0</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,13 +16609,13 @@
         </is>
       </c>
       <c r="N100">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O100">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P100">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q100">
         <v>0</v>
@@ -16648,10 +16648,10 @@
         <v>0</v>
       </c>
       <c r="AA100">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB100">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC100">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G101">
@@ -16781,55 +16781,55 @@
         <v>0</v>
       </c>
       <c r="Q101">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R101">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="S101">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T101">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U101">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="V101">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W101">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X101">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y101">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z101">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AA101">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AB101">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC101">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AD101">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE101">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF101">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AG101">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK101">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,13 +16935,13 @@
         </is>
       </c>
       <c r="N102">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O102">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P102">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -16974,10 +16974,10 @@
         <v>0</v>
       </c>
       <c r="AA102">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB102">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC102">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G103">
@@ -17137,10 +17137,10 @@
         <v>0</v>
       </c>
       <c r="AA103">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB103">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC103">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O104">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P104">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q104">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R104">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S104">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="T104">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U104">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="V104">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W104">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X104">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y104">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z104">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA104">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB104">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC104">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AD104">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE104">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF104">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG104">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK104">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O105">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P105">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Q105">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="R105">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S105">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="T105">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U105">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V105">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W105">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X105">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Y105">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z105">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA105">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB105">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC105">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AD105">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE105">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF105">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG105">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK105">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G106">
@@ -17626,10 +17626,10 @@
         <v>0</v>
       </c>
       <c r="AA106">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB106">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC106">
         <v>0</v>
@@ -17750,64 +17750,64 @@
         </is>
       </c>
       <c r="N107">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O107">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P107">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q107">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="R107">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S107">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T107">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U107">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="V107">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W107">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X107">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y107">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z107">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AA107">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB107">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC107">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AD107">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE107">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF107">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG107">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK107">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -18085,55 +18085,55 @@
         <v>0</v>
       </c>
       <c r="Q109">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R109">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S109">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T109">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="U109">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="V109">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W109">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X109">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y109">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z109">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA109">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB109">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC109">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD109">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE109">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF109">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG109">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK109">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O110">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P110">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="Q110">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R110">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S110">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T110">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U110">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V110">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W110">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X110">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y110">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z110">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA110">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB110">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC110">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AD110">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE110">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF110">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG110">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK110">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O111">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P111">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q111">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R111">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S111">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T111">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="U111">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V111">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W111">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X111">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y111">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z111">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA111">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB111">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC111">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD111">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE111">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF111">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG111">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK111">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -20032,64 +20032,64 @@
         </is>
       </c>
       <c r="N121">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O121">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="P121">
-        <v>0</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="Q121">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="R121">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="S121">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T121">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U121">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V121">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W121">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X121">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y121">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z121">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA121">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB121">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AC121">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD121">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE121">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF121">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG121">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK121">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AL121">
         <v>0</v>

--- a/jogos_2026-08-07.xlsx
+++ b/jogos_2026-08-07.xlsx
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,28 +10415,28 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.44</v>
+        <v>2.01</v>
       </c>
       <c r="O62">
-        <v>4.3</v>
+        <v>3.55</v>
       </c>
       <c r="P62">
-        <v>6.84</v>
+        <v>3.41</v>
       </c>
       <c r="Q62">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="R62">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="S62">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T62">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="U62">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="V62">
         <v>1.48</v>
@@ -10445,34 +10445,34 @@
         <v>1.08</v>
       </c>
       <c r="X62">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y62">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z62">
-        <v>4.06</v>
+        <v>4.33</v>
       </c>
       <c r="AA62">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AB62">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="AC62">
-        <v>2.88</v>
+        <v>2.57</v>
       </c>
       <c r="AD62">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE62">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF62">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="AG62">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AK62">
-        <v>2.76</v>
+        <v>1.67</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,28 +10578,28 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.01</v>
+        <v>1.44</v>
       </c>
       <c r="O63">
-        <v>3.55</v>
+        <v>4.3</v>
       </c>
       <c r="P63">
-        <v>3.41</v>
+        <v>6.84</v>
       </c>
       <c r="Q63">
-        <v>2.38</v>
+        <v>1.83</v>
       </c>
       <c r="R63">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="S63">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T63">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U63">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="V63">
         <v>1.48</v>
@@ -10608,34 +10608,34 @@
         <v>1.08</v>
       </c>
       <c r="X63">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y63">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z63">
-        <v>4.33</v>
+        <v>4.06</v>
       </c>
       <c r="AA63">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AB63">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="AC63">
-        <v>2.57</v>
+        <v>2.88</v>
       </c>
       <c r="AD63">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AE63">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF63">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AG63">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AK63">
-        <v>1.67</v>
+        <v>2.76</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G90">
@@ -14982,61 +14982,61 @@
         <v>1.95</v>
       </c>
       <c r="O90">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="P90">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="Q90">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R90">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="S90">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="T90">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U90">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="V90">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W90">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X90">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Y90">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z90">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA90">
-        <v>2.52</v>
+        <v>3.1</v>
       </c>
       <c r="AB90">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AC90">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AD90">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AE90">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF90">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG90">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK90">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>1.95</v>
+        <v>1.5</v>
       </c>
       <c r="O91">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="P91">
-        <v>4.2</v>
+        <v>7.5</v>
       </c>
       <c r="Q91">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R91">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S91">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="T91">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U91">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="V91">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W91">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X91">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y91">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z91">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AA91">
-        <v>3.1</v>
+        <v>2.48</v>
       </c>
       <c r="AB91">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="AC91">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="AD91">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE91">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF91">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AG91">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK91">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,58 +15305,58 @@
         </is>
       </c>
       <c r="N92">
-        <v>1.5</v>
+        <v>1.91</v>
       </c>
       <c r="O92">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="P92">
-        <v>7.5</v>
+        <v>5.3</v>
       </c>
       <c r="Q92">
-        <v>2</v>
+        <v>2.71</v>
       </c>
       <c r="R92">
-        <v>2.1</v>
+        <v>1.69</v>
       </c>
       <c r="S92">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="T92">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="U92">
-        <v>3.46</v>
+        <v>4.45</v>
       </c>
       <c r="V92">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="W92">
+        <v>1.03</v>
+      </c>
+      <c r="X92">
+        <v>1.15</v>
+      </c>
+      <c r="Y92">
+        <v>1.7</v>
+      </c>
+      <c r="Z92">
+        <v>2.03</v>
+      </c>
+      <c r="AA92">
+        <v>3.14</v>
+      </c>
+      <c r="AB92">
+        <v>1.27</v>
+      </c>
+      <c r="AC92">
+        <v>6.75</v>
+      </c>
+      <c r="AD92">
+        <v>1.1</v>
+      </c>
+      <c r="AE92">
         <v>1.02</v>
-      </c>
-      <c r="X92">
-        <v>1.1</v>
-      </c>
-      <c r="Y92">
-        <v>1.44</v>
-      </c>
-      <c r="Z92">
-        <v>2.49</v>
-      </c>
-      <c r="AA92">
-        <v>2.48</v>
-      </c>
-      <c r="AB92">
-        <v>1.51</v>
-      </c>
-      <c r="AC92">
-        <v>4.76</v>
-      </c>
-      <c r="AD92">
-        <v>1.17</v>
-      </c>
-      <c r="AE92">
-        <v>1.05</v>
       </c>
       <c r="AF92">
         <v>2.6</v>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="AK92">
-        <v>2.45</v>
+        <v>1.75</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="O93">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="P93">
-        <v>5.3</v>
+        <v>3.9</v>
       </c>
       <c r="Q93">
-        <v>2.71</v>
+        <v>2.63</v>
       </c>
       <c r="R93">
-        <v>1.69</v>
+        <v>1.95</v>
       </c>
       <c r="S93">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="T93">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="U93">
-        <v>4.45</v>
+        <v>3.7</v>
       </c>
       <c r="V93">
+        <v>1.2</v>
+      </c>
+      <c r="W93">
+        <v>1.02</v>
+      </c>
+      <c r="X93">
+        <v>1.11</v>
+      </c>
+      <c r="Y93">
+        <v>1.5</v>
+      </c>
+      <c r="Z93">
+        <v>2.45</v>
+      </c>
+      <c r="AA93">
+        <v>2.52</v>
+      </c>
+      <c r="AB93">
+        <v>1.41</v>
+      </c>
+      <c r="AC93">
+        <v>5</v>
+      </c>
+      <c r="AD93">
         <v>1.14</v>
       </c>
-      <c r="W93">
-        <v>1.03</v>
-      </c>
-      <c r="X93">
-        <v>1.15</v>
-      </c>
-      <c r="Y93">
-        <v>1.7</v>
-      </c>
-      <c r="Z93">
-        <v>2.03</v>
-      </c>
-      <c r="AA93">
-        <v>3.14</v>
-      </c>
-      <c r="AB93">
-        <v>1.27</v>
-      </c>
-      <c r="AC93">
-        <v>6.75</v>
-      </c>
-      <c r="AD93">
-        <v>1.1</v>
-      </c>
       <c r="AE93">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF93">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="AG93">
-        <v>1.44</v>
+        <v>1.59</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.09</v>
+        <v>1.28</v>
       </c>
       <c r="AK93">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -18398,7 +18398,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N111">

--- a/jogos_2026-08-07.xlsx
+++ b/jogos_2026-08-07.xlsx
@@ -807,22 +807,22 @@
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>2.23</v>
+        <v>2.31</v>
       </c>
       <c r="R3">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="S3">
         <v>1.38</v>
       </c>
       <c r="T3">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="U3">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="V3">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="W3">
         <v>1.03</v>
@@ -834,28 +834,28 @@
         <v>1.29</v>
       </c>
       <c r="Z3">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="AA3">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AB3">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AC3">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="AD3">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE3">
         <v>1.05</v>
       </c>
       <c r="AF3">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AG3">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AK3">
         <v>1.92</v>
@@ -961,28 +961,28 @@
         </is>
       </c>
       <c r="N4">
-        <v>3.79</v>
+        <v>3.96</v>
       </c>
       <c r="O4">
-        <v>3.65</v>
+        <v>3.72</v>
       </c>
       <c r="P4">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="Q4">
-        <v>4.62</v>
+        <v>4</v>
       </c>
       <c r="R4">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="S4">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="T4">
-        <v>3.2</v>
+        <v>3.02</v>
       </c>
       <c r="U4">
-        <v>2.53</v>
+        <v>2.63</v>
       </c>
       <c r="V4">
         <v>1.43</v>
@@ -991,25 +991,25 @@
         <v>1.07</v>
       </c>
       <c r="X4">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y4">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z4">
-        <v>3.58</v>
+        <v>3.87</v>
       </c>
       <c r="AA4">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AB4">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AC4">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="AD4">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE4">
         <v>1.12</v>
@@ -1018,7 +1018,7 @@
         <v>1.68</v>
       </c>
       <c r="AG4">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
+        <v>1.19</v>
+      </c>
+      <c r="AK4">
         <v>1.22</v>
-      </c>
-      <c r="AK4">
-        <v>1.15</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,31 +1124,31 @@
         </is>
       </c>
       <c r="N5">
-        <v>3.04</v>
+        <v>2.95</v>
       </c>
       <c r="O5">
-        <v>3.32</v>
+        <v>3.26</v>
       </c>
       <c r="P5">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="Q5">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="R5">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S5">
         <v>1.33</v>
       </c>
       <c r="T5">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="U5">
-        <v>2.48</v>
+        <v>2.59</v>
       </c>
       <c r="V5">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W5">
         <v>1.06</v>
@@ -1163,22 +1163,22 @@
         <v>3.55</v>
       </c>
       <c r="AA5">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AB5">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AC5">
-        <v>3.02</v>
+        <v>2.83</v>
       </c>
       <c r="AD5">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AE5">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF5">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AG5">
         <v>2.15</v>
@@ -1197,7 +1197,7 @@
         <v>1.23</v>
       </c>
       <c r="AK5">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,16 +1287,16 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="O6">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="P6">
-        <v>5.48</v>
+        <v>5</v>
       </c>
       <c r="Q6">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="R6">
         <v>2.3</v>
@@ -1308,7 +1308,7 @@
         <v>3.08</v>
       </c>
       <c r="U6">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="V6">
         <v>1.42</v>
@@ -1323,16 +1323,16 @@
         <v>1.25</v>
       </c>
       <c r="Z6">
-        <v>3.82</v>
+        <v>3.85</v>
       </c>
       <c r="AA6">
-        <v>1.86</v>
+        <v>1.76</v>
       </c>
       <c r="AB6">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="AC6">
-        <v>2.83</v>
+        <v>2.6</v>
       </c>
       <c r="AD6">
         <v>1.33</v>
@@ -1341,7 +1341,7 @@
         <v>1.13</v>
       </c>
       <c r="AF6">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AG6">
         <v>1.87</v>
@@ -1360,7 +1360,7 @@
         <v>1.22</v>
       </c>
       <c r="AK6">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,55 +1450,55 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.79</v>
+        <v>3.6</v>
       </c>
       <c r="O7">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
       <c r="P7">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="Q7">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="R7">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="S7">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T7">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="U7">
-        <v>2.55</v>
+        <v>2.88</v>
       </c>
       <c r="V7">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W7">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X7">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z7">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="AA7">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AB7">
         <v>1.8</v>
       </c>
       <c r="AC7">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AD7">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE7">
         <v>1.07</v>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK7">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1622,46 +1622,46 @@
         <v>9.050000000000001</v>
       </c>
       <c r="Q8">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="R8">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="S8">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="T8">
-        <v>3.46</v>
+        <v>3.54</v>
       </c>
       <c r="U8">
         <v>2.25</v>
       </c>
       <c r="V8">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="W8">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X8">
         <v>1.03</v>
       </c>
       <c r="Y8">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z8">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AA8">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AB8">
         <v>2.2</v>
       </c>
       <c r="AC8">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AD8">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AE8">
         <v>1.18</v>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AK8">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O64">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P64">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -10780,10 +10780,10 @@
         <v>0</v>
       </c>
       <c r="AA64">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB64">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC64">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>La Roche VF</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="G65">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O66">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P66">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>La Roche VF</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G67">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,13 +11393,13 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.04</v>
+        <v>3.25</v>
       </c>
       <c r="O68">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P68">
-        <v>3.65</v>
+        <v>2.22</v>
       </c>
       <c r="Q68">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O69">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P69">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q69">
         <v>0</v>
@@ -11595,10 +11595,10 @@
         <v>0</v>
       </c>
       <c r="AA69">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB69">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC69">
         <v>0</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O70">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P70">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="Q70">
         <v>0</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.07</v>
+        <v>2.6</v>
       </c>
       <c r="O71">
         <v>3.2</v>
       </c>
       <c r="P71">
-        <v>3.44</v>
+        <v>2.5</v>
       </c>
       <c r="Q71">
         <v>0</v>
@@ -11921,10 +11921,10 @@
         <v>0</v>
       </c>
       <c r="AA71">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="AB71">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AC71">
         <v>0</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G72">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,65 +12371,65 @@
         </is>
       </c>
       <c r="N74">
+        <v>1.41</v>
+      </c>
+      <c r="O74">
+        <v>4.5</v>
+      </c>
+      <c r="P74">
+        <v>6.17</v>
+      </c>
+      <c r="Q74">
+        <v>1.74</v>
+      </c>
+      <c r="R74">
+        <v>2.7</v>
+      </c>
+      <c r="S74">
+        <v>0</v>
+      </c>
+      <c r="T74">
+        <v>0</v>
+      </c>
+      <c r="U74">
+        <v>1.98</v>
+      </c>
+      <c r="V74">
+        <v>1.64</v>
+      </c>
+      <c r="W74">
+        <v>0</v>
+      </c>
+      <c r="X74">
+        <v>0</v>
+      </c>
+      <c r="Y74">
+        <v>1.12</v>
+      </c>
+      <c r="Z74">
+        <v>4.8</v>
+      </c>
+      <c r="AA74">
+        <v>1.43</v>
+      </c>
+      <c r="AB74">
+        <v>2.48</v>
+      </c>
+      <c r="AC74">
+        <v>2.07</v>
+      </c>
+      <c r="AD74">
+        <v>1.61</v>
+      </c>
+      <c r="AE74">
+        <v>1.24</v>
+      </c>
+      <c r="AF74">
+        <v>1.64</v>
+      </c>
+      <c r="AG74">
         <v>2.04</v>
       </c>
-      <c r="O74">
-        <v>3.4</v>
-      </c>
-      <c r="P74">
-        <v>3.25</v>
-      </c>
-      <c r="Q74">
-        <v>2.5</v>
-      </c>
-      <c r="R74">
-        <v>2.28</v>
-      </c>
-      <c r="S74">
-        <v>0</v>
-      </c>
-      <c r="T74">
-        <v>0</v>
-      </c>
-      <c r="U74">
-        <v>2.32</v>
-      </c>
-      <c r="V74">
-        <v>1.46</v>
-      </c>
-      <c r="W74">
-        <v>0</v>
-      </c>
-      <c r="X74">
-        <v>0</v>
-      </c>
-      <c r="Y74">
-        <v>1.2</v>
-      </c>
-      <c r="Z74">
-        <v>3.75</v>
-      </c>
-      <c r="AA74">
-        <v>1.66</v>
-      </c>
-      <c r="AB74">
-        <v>2</v>
-      </c>
-      <c r="AC74">
-        <v>2.6</v>
-      </c>
-      <c r="AD74">
-        <v>1.38</v>
-      </c>
-      <c r="AE74">
-        <v>1.14</v>
-      </c>
-      <c r="AF74">
-        <v>1.56</v>
-      </c>
-      <c r="AG74">
-        <v>2.18</v>
-      </c>
       <c r="AH74" t="inlineStr">
         <is>
           <t>[]</t>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AK74">
-        <v>1.58</v>
+        <v>2.63</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,19 +12697,19 @@
         </is>
       </c>
       <c r="N76">
-        <v>1.41</v>
+        <v>2.04</v>
       </c>
       <c r="O76">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="P76">
-        <v>6.17</v>
+        <v>3.25</v>
       </c>
       <c r="Q76">
-        <v>1.74</v>
+        <v>2.5</v>
       </c>
       <c r="R76">
-        <v>2.7</v>
+        <v>2.28</v>
       </c>
       <c r="S76">
         <v>0</v>
@@ -12718,10 +12718,10 @@
         <v>0</v>
       </c>
       <c r="U76">
-        <v>1.98</v>
+        <v>2.32</v>
       </c>
       <c r="V76">
-        <v>1.64</v>
+        <v>1.46</v>
       </c>
       <c r="W76">
         <v>0</v>
@@ -12730,31 +12730,31 @@
         <v>0</v>
       </c>
       <c r="Y76">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="Z76">
-        <v>4.8</v>
+        <v>3.75</v>
       </c>
       <c r="AA76">
-        <v>1.43</v>
+        <v>1.66</v>
       </c>
       <c r="AB76">
-        <v>2.48</v>
+        <v>2</v>
       </c>
       <c r="AC76">
-        <v>2.07</v>
+        <v>2.6</v>
       </c>
       <c r="AD76">
-        <v>1.61</v>
+        <v>1.38</v>
       </c>
       <c r="AE76">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="AF76">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="AG76">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="AK76">
-        <v>2.63</v>
+        <v>1.58</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,13 +15631,13 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O94">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P94">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Q94">
         <v>0</v>
@@ -15670,10 +15670,10 @@
         <v>0</v>
       </c>
       <c r="AA94">
-        <v>3.1</v>
+        <v>2.87</v>
       </c>
       <c r="AB94">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AC94">
         <v>0</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,13 +15794,13 @@
         </is>
       </c>
       <c r="N95">
-        <v>1.6</v>
+        <v>2.02</v>
       </c>
       <c r="O95">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="P95">
-        <v>5.75</v>
+        <v>4.61</v>
       </c>
       <c r="Q95">
         <v>0</v>
@@ -15833,10 +15833,10 @@
         <v>0</v>
       </c>
       <c r="AA95">
-        <v>2.6</v>
+        <v>2.87</v>
       </c>
       <c r="AB95">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AC95">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,13 +15957,13 @@
         </is>
       </c>
       <c r="N96">
-        <v>2.51</v>
+        <v>2.1</v>
       </c>
       <c r="O96">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="P96">
-        <v>3.21</v>
+        <v>3.6</v>
       </c>
       <c r="Q96">
         <v>0</v>
@@ -15996,10 +15996,10 @@
         <v>0</v>
       </c>
       <c r="AA96">
-        <v>2.87</v>
+        <v>3.1</v>
       </c>
       <c r="AB96">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AC96">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,13 +16120,13 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.02</v>
+        <v>1.6</v>
       </c>
       <c r="O97">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="P97">
-        <v>4.61</v>
+        <v>5.75</v>
       </c>
       <c r="Q97">
         <v>0</v>
@@ -16159,10 +16159,10 @@
         <v>0</v>
       </c>
       <c r="AA97">
-        <v>2.87</v>
+        <v>2.6</v>
       </c>
       <c r="AB97">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AC97">
         <v>0</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,13 +16283,13 @@
         </is>
       </c>
       <c r="N98">
-        <v>1.6</v>
+        <v>2.51</v>
       </c>
       <c r="O98">
-        <v>3.3</v>
+        <v>2.81</v>
       </c>
       <c r="P98">
-        <v>5.5</v>
+        <v>3.21</v>
       </c>
       <c r="Q98">
         <v>0</v>
@@ -16322,10 +16322,10 @@
         <v>0</v>
       </c>
       <c r="AA98">
-        <v>2.35</v>
+        <v>2.87</v>
       </c>
       <c r="AB98">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AC98">
         <v>0</v>
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,13 +16446,13 @@
         </is>
       </c>
       <c r="N99">
-        <v>2.02</v>
+        <v>1.6</v>
       </c>
       <c r="O99">
-        <v>3.11</v>
+        <v>3.3</v>
       </c>
       <c r="P99">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="Q99">
         <v>0</v>
@@ -16485,10 +16485,10 @@
         <v>0</v>
       </c>
       <c r="AA99">
-        <v>3.1</v>
+        <v>2.35</v>
       </c>
       <c r="AB99">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AC99">
         <v>0</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,13 +16609,13 @@
         </is>
       </c>
       <c r="N100">
-        <v>2.9</v>
+        <v>2.02</v>
       </c>
       <c r="O100">
-        <v>2.5</v>
+        <v>3.11</v>
       </c>
       <c r="P100">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="Q100">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O101">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P101">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q101">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R101">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="S101">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="T101">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U101">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="V101">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="W101">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X101">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y101">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z101">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AA101">
-        <v>2.81</v>
+        <v>3.1</v>
       </c>
       <c r="AB101">
         <v>1.36</v>
       </c>
       <c r="AC101">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AD101">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AE101">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF101">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AG101">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AK101">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O102">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P102">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="Q102">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R102">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="S102">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T102">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U102">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="V102">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W102">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X102">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y102">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z102">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AA102">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="AB102">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AC102">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AD102">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE102">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF102">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AG102">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK102">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,13 +17098,13 @@
         </is>
       </c>
       <c r="N103">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O103">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P103">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Q103">
         <v>0</v>
@@ -17137,10 +17137,10 @@
         <v>0</v>
       </c>
       <c r="AA103">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="AB103">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AC103">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O104">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="P104">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="Q104">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R104">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S104">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="T104">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="U104">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="V104">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="W104">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X104">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y104">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z104">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA104">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="AB104">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AC104">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AD104">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AE104">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF104">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG104">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK104">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G105">
@@ -17427,61 +17427,61 @@
         <v>1.95</v>
       </c>
       <c r="O105">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="P105">
-        <v>4.15</v>
+        <v>4.4</v>
       </c>
       <c r="Q105">
-        <v>2.87</v>
+        <v>2.5</v>
       </c>
       <c r="R105">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="S105">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="T105">
+        <v>2.13</v>
+      </c>
+      <c r="U105">
+        <v>3.95</v>
+      </c>
+      <c r="V105">
+        <v>1.17</v>
+      </c>
+      <c r="W105">
+        <v>1.01</v>
+      </c>
+      <c r="X105">
+        <v>1.07</v>
+      </c>
+      <c r="Y105">
+        <v>1.58</v>
+      </c>
+      <c r="Z105">
         <v>2.25</v>
       </c>
-      <c r="U105">
-        <v>3.75</v>
-      </c>
-      <c r="V105">
-        <v>1.22</v>
-      </c>
-      <c r="W105">
-        <v>1.02</v>
-      </c>
-      <c r="X105">
-        <v>1.15</v>
-      </c>
-      <c r="Y105">
-        <v>1.65</v>
-      </c>
-      <c r="Z105">
-        <v>2.15</v>
-      </c>
       <c r="AA105">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AB105">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AC105">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="AD105">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AE105">
         <v>1.03</v>
       </c>
       <c r="AF105">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AG105">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="AK105">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,80 +17587,80 @@
         </is>
       </c>
       <c r="N106">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O106">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P106">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Q106">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="R106">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S106">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="T106">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U106">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V106">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W106">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X106">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Y106">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z106">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA106">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="AB106">
+        <v>1.33</v>
+      </c>
+      <c r="AC106">
+        <v>6</v>
+      </c>
+      <c r="AD106">
+        <v>1.11</v>
+      </c>
+      <c r="AE106">
+        <v>1.03</v>
+      </c>
+      <c r="AF106">
+        <v>2.4</v>
+      </c>
+      <c r="AG106">
+        <v>1.54</v>
+      </c>
+      <c r="AH106" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI106" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ106">
         <v>1.4</v>
       </c>
-      <c r="AC106">
-        <v>0</v>
-      </c>
-      <c r="AD106">
-        <v>0</v>
-      </c>
-      <c r="AE106">
-        <v>0</v>
-      </c>
-      <c r="AF106">
-        <v>0</v>
-      </c>
-      <c r="AG106">
-        <v>0</v>
-      </c>
-      <c r="AH106" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI106" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ106">
-        <v>0</v>
-      </c>
       <c r="AK106">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL106">
         <v>0</v>

--- a/jogos_2026-08-07.xlsx
+++ b/jogos_2026-08-07.xlsx
@@ -635,49 +635,49 @@
         </is>
       </c>
       <c r="N2">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="O2">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="P2">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="Q2">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="R2">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="S2">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T2">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="U2">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="V2">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W2">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X2">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y2">
         <v>1.3</v>
       </c>
       <c r="Z2">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="AA2">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AB2">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AC2">
         <v>3.6</v>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.82</v>
+        <v>1.24</v>
       </c>
       <c r="AK2">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -1776,28 +1776,28 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="O9">
-        <v>3.36</v>
+        <v>3.35</v>
       </c>
       <c r="P9">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="Q9">
         <v>2.9</v>
       </c>
       <c r="R9">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="S9">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T9">
-        <v>2.69</v>
+        <v>2.89</v>
       </c>
       <c r="U9">
-        <v>2.94</v>
+        <v>2.73</v>
       </c>
       <c r="V9">
         <v>1.38</v>
@@ -1806,7 +1806,7 @@
         <v>1.03</v>
       </c>
       <c r="X9">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y9">
         <v>1.3</v>
@@ -1815,25 +1815,25 @@
         <v>3.25</v>
       </c>
       <c r="AA9">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AB9">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AC9">
-        <v>3.55</v>
+        <v>3.38</v>
       </c>
       <c r="AD9">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE9">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF9">
         <v>1.73</v>
       </c>
       <c r="AG9">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AK9">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O55">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P55">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -9313,10 +9313,10 @@
         <v>0</v>
       </c>
       <c r="AA55">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB55">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC55">
         <v>0</v>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O56">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>4.86</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,28 +10415,28 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.01</v>
+        <v>1.44</v>
       </c>
       <c r="O62">
-        <v>3.55</v>
+        <v>4.3</v>
       </c>
       <c r="P62">
-        <v>3.41</v>
+        <v>6.84</v>
       </c>
       <c r="Q62">
-        <v>2.38</v>
+        <v>1.83</v>
       </c>
       <c r="R62">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="S62">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T62">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U62">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="V62">
         <v>1.48</v>
@@ -10445,34 +10445,34 @@
         <v>1.08</v>
       </c>
       <c r="X62">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y62">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z62">
-        <v>4.33</v>
+        <v>4.06</v>
       </c>
       <c r="AA62">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AB62">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="AC62">
-        <v>2.57</v>
+        <v>2.88</v>
       </c>
       <c r="AD62">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AE62">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF62">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AG62">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AK62">
-        <v>1.67</v>
+        <v>2.76</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,28 +10578,28 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.44</v>
+        <v>2.01</v>
       </c>
       <c r="O63">
-        <v>4.3</v>
+        <v>3.55</v>
       </c>
       <c r="P63">
-        <v>6.84</v>
+        <v>3.41</v>
       </c>
       <c r="Q63">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="R63">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="S63">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T63">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="U63">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="V63">
         <v>1.48</v>
@@ -10608,34 +10608,34 @@
         <v>1.08</v>
       </c>
       <c r="X63">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y63">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z63">
-        <v>4.06</v>
+        <v>4.33</v>
       </c>
       <c r="AA63">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AB63">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="AC63">
-        <v>2.88</v>
+        <v>2.57</v>
       </c>
       <c r="AD63">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE63">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF63">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="AG63">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AK63">
-        <v>2.76</v>
+        <v>1.67</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -14164,13 +14164,13 @@
         </is>
       </c>
       <c r="N85">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O85">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P85">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="Q85">
         <v>0</v>

--- a/jogos_2026-08-07.xlsx
+++ b/jogos_2026-08-07.xlsx
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q3">
-        <v>2.31</v>
+        <v>3.5</v>
       </c>
       <c r="R3">
         <v>2.15</v>
       </c>
       <c r="S3">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T3">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="U3">
-        <v>2.8</v>
+        <v>2.59</v>
       </c>
       <c r="V3">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W3">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y3">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z3">
-        <v>3.08</v>
+        <v>3.6</v>
       </c>
       <c r="AA3">
-        <v>1.96</v>
+        <v>1.8</v>
       </c>
       <c r="AB3">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="AC3">
-        <v>3.34</v>
+        <v>2.83</v>
       </c>
       <c r="AD3">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AE3">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AF3">
-        <v>1.83</v>
+        <v>1.63</v>
       </c>
       <c r="AG3">
-        <v>1.81</v>
+        <v>2.15</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="AK3">
-        <v>1.92</v>
+        <v>1.33</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="O4">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Q4">
-        <v>4</v>
+        <v>2.31</v>
       </c>
       <c r="R4">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="S4">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="T4">
-        <v>3.02</v>
+        <v>2.7</v>
       </c>
       <c r="U4">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="V4">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="W4">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X4">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="Z4">
-        <v>3.87</v>
+        <v>3.08</v>
       </c>
       <c r="AA4">
+        <v>1.96</v>
+      </c>
+      <c r="AB4">
         <v>1.75</v>
       </c>
-      <c r="AB4">
-        <v>1.93</v>
-      </c>
       <c r="AC4">
-        <v>2.75</v>
+        <v>3.34</v>
       </c>
       <c r="AD4">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="AE4">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="AF4">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="AG4">
-        <v>2.04</v>
+        <v>1.81</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AK4">
-        <v>1.22</v>
+        <v>1.92</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.95</v>
+        <v>3.96</v>
       </c>
       <c r="O5">
-        <v>3.26</v>
+        <v>3.72</v>
       </c>
       <c r="P5">
-        <v>2.2</v>
+        <v>1.77</v>
       </c>
       <c r="Q5">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="R5">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="S5">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T5">
-        <v>2.82</v>
+        <v>3.02</v>
       </c>
       <c r="U5">
-        <v>2.59</v>
+        <v>2.64</v>
       </c>
       <c r="V5">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W5">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X5">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y5">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="Z5">
-        <v>3.55</v>
+        <v>3.83</v>
       </c>
       <c r="AA5">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AB5">
         <v>1.93</v>
       </c>
       <c r="AC5">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="AD5">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AE5">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF5">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="AG5">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AK5">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,16 +1287,16 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="O6">
-        <v>3.8</v>
+        <v>4.05</v>
       </c>
       <c r="P6">
         <v>5</v>
       </c>
       <c r="Q6">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="R6">
         <v>2.3</v>
@@ -1456,7 +1456,7 @@
         <v>3.45</v>
       </c>
       <c r="P7">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="Q7">
         <v>4.25</v>
@@ -1486,19 +1486,19 @@
         <v>1.3</v>
       </c>
       <c r="Z7">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AA7">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="AB7">
         <v>1.8</v>
       </c>
       <c r="AC7">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="AD7">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AE7">
         <v>1.07</v>
@@ -1628,10 +1628,10 @@
         <v>2.64</v>
       </c>
       <c r="S8">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T8">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="U8">
         <v>2.25</v>
@@ -1948,25 +1948,25 @@
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="R10">
         <v>2.75</v>
       </c>
       <c r="S10">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="T10">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="U10">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V10">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="W10">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X10">
         <v>1.01</v>
@@ -1975,25 +1975,25 @@
         <v>1.1</v>
       </c>
       <c r="Z10">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AA10">
         <v>1.31</v>
       </c>
       <c r="AB10">
-        <v>2.92</v>
+        <v>3.19</v>
       </c>
       <c r="AC10">
         <v>1.96</v>
       </c>
       <c r="AD10">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AE10">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AF10">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AG10">
         <v>2.3</v>
@@ -3584,10 +3584,10 @@
         <v>2.38</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U20">
         <v>2.3</v>
@@ -3599,7 +3599,7 @@
         <v>1.12</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
         <v>1.16</v>
@@ -4749,10 +4749,10 @@
         <v>0</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC27">
         <v>0</v>
@@ -5045,55 +5045,55 @@
         <v>0</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5860,10 +5860,10 @@
         <v>0</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S34">
         <v>0</v>
@@ -5872,10 +5872,10 @@
         <v>0</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W34">
         <v>0</v>
@@ -5884,31 +5884,31 @@
         <v>0</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -9283,34 +9283,34 @@
         <v>2.69</v>
       </c>
       <c r="Q55">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="R55">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S55">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T55">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U55">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="V55">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W55">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X55">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y55">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z55">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA55">
         <v>2.05</v>
@@ -9319,19 +9319,19 @@
         <v>1.68</v>
       </c>
       <c r="AC55">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="AD55">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE55">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF55">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG55">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK55">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9446,55 +9446,55 @@
         <v>4.86</v>
       </c>
       <c r="Q56">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="R56">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S56">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T56">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="U56">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V56">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W56">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X56">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y56">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z56">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA56">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB56">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AC56">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD56">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE56">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF56">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG56">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK56">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -12223,10 +12223,10 @@
         <v>2.38</v>
       </c>
       <c r="S73">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T73">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U73">
         <v>2.2</v>
@@ -12235,10 +12235,10 @@
         <v>1.5</v>
       </c>
       <c r="W73">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X73">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y73">
         <v>1.16</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.41</v>
+        <v>2.3</v>
       </c>
       <c r="O74">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="P74">
-        <v>6.17</v>
+        <v>2.94</v>
       </c>
       <c r="Q74">
-        <v>1.74</v>
+        <v>2.8</v>
       </c>
       <c r="R74">
+        <v>2.15</v>
+      </c>
+      <c r="S74">
+        <v>1.35</v>
+      </c>
+      <c r="T74">
         <v>2.7</v>
       </c>
-      <c r="S74">
-        <v>0</v>
-      </c>
-      <c r="T74">
-        <v>0</v>
-      </c>
       <c r="U74">
-        <v>1.98</v>
+        <v>2.85</v>
       </c>
       <c r="V74">
-        <v>1.64</v>
+        <v>1.39</v>
       </c>
       <c r="W74">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y74">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="Z74">
-        <v>4.8</v>
+        <v>3.05</v>
       </c>
       <c r="AA74">
-        <v>1.43</v>
+        <v>1.92</v>
       </c>
       <c r="AB74">
-        <v>2.48</v>
+        <v>1.72</v>
       </c>
       <c r="AC74">
-        <v>2.07</v>
+        <v>3.3</v>
       </c>
       <c r="AD74">
-        <v>1.61</v>
+        <v>1.25</v>
       </c>
       <c r="AE74">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="AF74">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="AG74">
-        <v>2.04</v>
+        <v>1.93</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AK74">
-        <v>2.63</v>
+        <v>1.48</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
-        <v>2.3</v>
+        <v>2.04</v>
       </c>
       <c r="O75">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P75">
-        <v>2.94</v>
+        <v>3.25</v>
       </c>
       <c r="Q75">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="R75">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="S75">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T75">
-        <v>2.7</v>
+        <v>2.91</v>
       </c>
       <c r="U75">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V75">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W75">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X75">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y75">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="Z75">
-        <v>3.05</v>
+        <v>3.75</v>
       </c>
       <c r="AA75">
-        <v>1.92</v>
+        <v>1.66</v>
       </c>
       <c r="AB75">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="AC75">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="AD75">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AE75">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF75">
-        <v>1.72</v>
+        <v>1.56</v>
       </c>
       <c r="AG75">
-        <v>1.93</v>
+        <v>2.18</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK75">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,65 +12697,65 @@
         </is>
       </c>
       <c r="N76">
+        <v>1.41</v>
+      </c>
+      <c r="O76">
+        <v>4.5</v>
+      </c>
+      <c r="P76">
+        <v>6.17</v>
+      </c>
+      <c r="Q76">
+        <v>1.74</v>
+      </c>
+      <c r="R76">
+        <v>2.7</v>
+      </c>
+      <c r="S76">
+        <v>1.19</v>
+      </c>
+      <c r="T76">
+        <v>3.8</v>
+      </c>
+      <c r="U76">
+        <v>1.98</v>
+      </c>
+      <c r="V76">
+        <v>1.64</v>
+      </c>
+      <c r="W76">
+        <v>1.14</v>
+      </c>
+      <c r="X76">
+        <v>1.02</v>
+      </c>
+      <c r="Y76">
+        <v>1.12</v>
+      </c>
+      <c r="Z76">
+        <v>4.8</v>
+      </c>
+      <c r="AA76">
+        <v>1.43</v>
+      </c>
+      <c r="AB76">
+        <v>2.48</v>
+      </c>
+      <c r="AC76">
+        <v>2.07</v>
+      </c>
+      <c r="AD76">
+        <v>1.61</v>
+      </c>
+      <c r="AE76">
+        <v>1.24</v>
+      </c>
+      <c r="AF76">
+        <v>1.64</v>
+      </c>
+      <c r="AG76">
         <v>2.04</v>
       </c>
-      <c r="O76">
-        <v>3.4</v>
-      </c>
-      <c r="P76">
-        <v>3.25</v>
-      </c>
-      <c r="Q76">
-        <v>2.5</v>
-      </c>
-      <c r="R76">
-        <v>2.28</v>
-      </c>
-      <c r="S76">
-        <v>0</v>
-      </c>
-      <c r="T76">
-        <v>0</v>
-      </c>
-      <c r="U76">
-        <v>2.32</v>
-      </c>
-      <c r="V76">
-        <v>1.46</v>
-      </c>
-      <c r="W76">
-        <v>0</v>
-      </c>
-      <c r="X76">
-        <v>0</v>
-      </c>
-      <c r="Y76">
-        <v>1.2</v>
-      </c>
-      <c r="Z76">
-        <v>3.75</v>
-      </c>
-      <c r="AA76">
-        <v>1.66</v>
-      </c>
-      <c r="AB76">
-        <v>2</v>
-      </c>
-      <c r="AC76">
-        <v>2.6</v>
-      </c>
-      <c r="AD76">
-        <v>1.38</v>
-      </c>
-      <c r="AE76">
-        <v>1.14</v>
-      </c>
-      <c r="AF76">
-        <v>1.56</v>
-      </c>
-      <c r="AG76">
-        <v>2.18</v>
-      </c>
       <c r="AH76" t="inlineStr">
         <is>
           <t>[]</t>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AK76">
-        <v>1.58</v>
+        <v>2.63</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -14203,10 +14203,10 @@
         <v>0</v>
       </c>
       <c r="AA85">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB85">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC85">
         <v>0</v>
@@ -14825,55 +14825,55 @@
         <v>0</v>
       </c>
       <c r="Q89">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R89">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S89">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T89">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U89">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="V89">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W89">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X89">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y89">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z89">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA89">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AB89">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC89">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD89">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE89">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF89">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG89">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK89">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,58 +15142,58 @@
         </is>
       </c>
       <c r="N91">
-        <v>1.5</v>
+        <v>1.91</v>
       </c>
       <c r="O91">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="P91">
-        <v>7.5</v>
+        <v>5.3</v>
       </c>
       <c r="Q91">
-        <v>2</v>
+        <v>2.71</v>
       </c>
       <c r="R91">
-        <v>2.1</v>
+        <v>1.69</v>
       </c>
       <c r="S91">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="T91">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="U91">
-        <v>3.46</v>
+        <v>4.45</v>
       </c>
       <c r="V91">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="W91">
+        <v>1.03</v>
+      </c>
+      <c r="X91">
+        <v>1.15</v>
+      </c>
+      <c r="Y91">
+        <v>1.7</v>
+      </c>
+      <c r="Z91">
+        <v>2.03</v>
+      </c>
+      <c r="AA91">
+        <v>3.14</v>
+      </c>
+      <c r="AB91">
+        <v>1.27</v>
+      </c>
+      <c r="AC91">
+        <v>6.75</v>
+      </c>
+      <c r="AD91">
+        <v>1.1</v>
+      </c>
+      <c r="AE91">
         <v>1.02</v>
-      </c>
-      <c r="X91">
-        <v>1.1</v>
-      </c>
-      <c r="Y91">
-        <v>1.44</v>
-      </c>
-      <c r="Z91">
-        <v>2.49</v>
-      </c>
-      <c r="AA91">
-        <v>2.48</v>
-      </c>
-      <c r="AB91">
-        <v>1.51</v>
-      </c>
-      <c r="AC91">
-        <v>4.76</v>
-      </c>
-      <c r="AD91">
-        <v>1.17</v>
-      </c>
-      <c r="AE91">
-        <v>1.05</v>
       </c>
       <c r="AF91">
         <v>2.6</v>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="AK91">
-        <v>2.45</v>
+        <v>1.75</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,64 +15305,64 @@
         </is>
       </c>
       <c r="N92">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="O92">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="P92">
-        <v>5.3</v>
+        <v>3.9</v>
       </c>
       <c r="Q92">
-        <v>2.71</v>
+        <v>2.63</v>
       </c>
       <c r="R92">
-        <v>1.69</v>
+        <v>1.95</v>
       </c>
       <c r="S92">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="T92">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="U92">
-        <v>4.45</v>
+        <v>3.7</v>
       </c>
       <c r="V92">
+        <v>1.2</v>
+      </c>
+      <c r="W92">
+        <v>1.02</v>
+      </c>
+      <c r="X92">
+        <v>1.11</v>
+      </c>
+      <c r="Y92">
+        <v>1.5</v>
+      </c>
+      <c r="Z92">
+        <v>2.45</v>
+      </c>
+      <c r="AA92">
+        <v>2.52</v>
+      </c>
+      <c r="AB92">
+        <v>1.41</v>
+      </c>
+      <c r="AC92">
+        <v>5</v>
+      </c>
+      <c r="AD92">
         <v>1.14</v>
       </c>
-      <c r="W92">
-        <v>1.03</v>
-      </c>
-      <c r="X92">
-        <v>1.15</v>
-      </c>
-      <c r="Y92">
-        <v>1.7</v>
-      </c>
-      <c r="Z92">
-        <v>2.03</v>
-      </c>
-      <c r="AA92">
-        <v>3.14</v>
-      </c>
-      <c r="AB92">
-        <v>1.27</v>
-      </c>
-      <c r="AC92">
-        <v>6.75</v>
-      </c>
-      <c r="AD92">
-        <v>1.1</v>
-      </c>
       <c r="AE92">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF92">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="AG92">
-        <v>1.44</v>
+        <v>1.59</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.09</v>
+        <v>1.28</v>
       </c>
       <c r="AK92">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="O93">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="P93">
-        <v>3.9</v>
+        <v>4.61</v>
       </c>
       <c r="Q93">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R93">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="S93">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="T93">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U93">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="V93">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W93">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X93">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Y93">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z93">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA93">
-        <v>2.52</v>
+        <v>2.87</v>
       </c>
       <c r="AB93">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AC93">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AD93">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AE93">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF93">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG93">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK93">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,80 +15794,80 @@
         </is>
       </c>
       <c r="N95">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="O95">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="P95">
-        <v>4.61</v>
+        <v>4.15</v>
       </c>
       <c r="Q95">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="R95">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S95">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="T95">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U95">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V95">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W95">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X95">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Y95">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z95">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA95">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="AB95">
+        <v>1.33</v>
+      </c>
+      <c r="AC95">
+        <v>6</v>
+      </c>
+      <c r="AD95">
+        <v>1.11</v>
+      </c>
+      <c r="AE95">
+        <v>1.03</v>
+      </c>
+      <c r="AF95">
+        <v>2.4</v>
+      </c>
+      <c r="AG95">
+        <v>1.54</v>
+      </c>
+      <c r="AH95" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI95" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ95">
         <v>1.4</v>
       </c>
-      <c r="AC95">
-        <v>0</v>
-      </c>
-      <c r="AD95">
-        <v>0</v>
-      </c>
-      <c r="AE95">
-        <v>0</v>
-      </c>
-      <c r="AF95">
-        <v>0</v>
-      </c>
-      <c r="AG95">
-        <v>0</v>
-      </c>
-      <c r="AH95" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI95" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ95">
-        <v>0</v>
-      </c>
       <c r="AK95">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="O96">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="P96">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="Q96">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R96">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S96">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="T96">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U96">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="V96">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W96">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X96">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y96">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z96">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA96">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AB96">
         <v>1.36</v>
       </c>
       <c r="AC96">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AD96">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE96">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF96">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG96">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK96">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="O97">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="P97">
-        <v>5.75</v>
+        <v>7.5</v>
       </c>
       <c r="Q97">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R97">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S97">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="T97">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U97">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="V97">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W97">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X97">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y97">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z97">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AA97">
+        <v>2.48</v>
+      </c>
+      <c r="AB97">
+        <v>1.51</v>
+      </c>
+      <c r="AC97">
+        <v>4.76</v>
+      </c>
+      <c r="AD97">
+        <v>1.17</v>
+      </c>
+      <c r="AE97">
+        <v>1.05</v>
+      </c>
+      <c r="AF97">
         <v>2.6</v>
       </c>
-      <c r="AB97">
-        <v>1.47</v>
-      </c>
-      <c r="AC97">
-        <v>0</v>
-      </c>
-      <c r="AD97">
-        <v>0</v>
-      </c>
-      <c r="AE97">
-        <v>0</v>
-      </c>
-      <c r="AF97">
-        <v>0</v>
-      </c>
       <c r="AG97">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK97">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,13 +16283,13 @@
         </is>
       </c>
       <c r="N98">
-        <v>2.51</v>
+        <v>2.1</v>
       </c>
       <c r="O98">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="P98">
-        <v>3.21</v>
+        <v>3.6</v>
       </c>
       <c r="Q98">
         <v>0</v>
@@ -16322,10 +16322,10 @@
         <v>0</v>
       </c>
       <c r="AA98">
-        <v>2.87</v>
+        <v>3.1</v>
       </c>
       <c r="AB98">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AC98">
         <v>0</v>
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G99">
@@ -16449,10 +16449,10 @@
         <v>1.6</v>
       </c>
       <c r="O99">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P99">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="Q99">
         <v>0</v>
@@ -16485,10 +16485,10 @@
         <v>0</v>
       </c>
       <c r="AA99">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="AB99">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AC99">
         <v>0</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,13 +16609,13 @@
         </is>
       </c>
       <c r="N100">
-        <v>2.02</v>
+        <v>2.51</v>
       </c>
       <c r="O100">
-        <v>3.11</v>
+        <v>2.81</v>
       </c>
       <c r="P100">
-        <v>4</v>
+        <v>3.21</v>
       </c>
       <c r="Q100">
         <v>0</v>
@@ -16648,10 +16648,10 @@
         <v>0</v>
       </c>
       <c r="AA100">
-        <v>3.1</v>
+        <v>2.87</v>
       </c>
       <c r="AB100">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AC100">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,13 +16772,13 @@
         </is>
       </c>
       <c r="N101">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="O101">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="P101">
-        <v>2.8</v>
+        <v>5.5</v>
       </c>
       <c r="Q101">
         <v>0</v>
@@ -16811,10 +16811,10 @@
         <v>0</v>
       </c>
       <c r="AA101">
-        <v>3.1</v>
+        <v>2.35</v>
       </c>
       <c r="AB101">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AC101">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O102">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="P102">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q102">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R102">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="S102">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="T102">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U102">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="V102">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="W102">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X102">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y102">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z102">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AA102">
-        <v>2.81</v>
+        <v>3.1</v>
       </c>
       <c r="AB102">
         <v>1.36</v>
       </c>
       <c r="AC102">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AD102">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AE102">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF102">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AG102">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AK102">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,13 +17098,13 @@
         </is>
       </c>
       <c r="N103">
-        <v>1.73</v>
+        <v>2.9</v>
       </c>
       <c r="O103">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="P103">
-        <v>4.8</v>
+        <v>2.8</v>
       </c>
       <c r="Q103">
         <v>0</v>
@@ -17137,10 +17137,10 @@
         <v>0</v>
       </c>
       <c r="AA103">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="AB103">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AC103">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G104">
@@ -17270,55 +17270,55 @@
         <v>0</v>
       </c>
       <c r="Q104">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R104">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="S104">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T104">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U104">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="V104">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W104">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X104">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y104">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z104">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AA104">
-        <v>2.4</v>
+        <v>2.81</v>
       </c>
       <c r="AB104">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AC104">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AD104">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE104">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF104">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AG104">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK104">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="O105">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="P105">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="Q105">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R105">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S105">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="T105">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="U105">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="V105">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="W105">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X105">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y105">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z105">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA105">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="AB105">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AC105">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AD105">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AE105">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF105">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG105">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK105">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O106">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P106">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="Q106">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="R106">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="S106">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="T106">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U106">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="V106">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W106">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X106">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Y106">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z106">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA106">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="AB106">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="AC106">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AD106">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AE106">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF106">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AG106">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AK106">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G112">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G113">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G114">

--- a/jogos_2026-08-07.xlsx
+++ b/jogos_2026-08-07.xlsx
@@ -2926,25 +2926,25 @@
         <v>2.75</v>
       </c>
       <c r="Q16">
-        <v>3.25</v>
+        <v>3.53</v>
       </c>
       <c r="R16">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="S16">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="T16">
         <v>2.32</v>
       </c>
       <c r="U16">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="V16">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="W16">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X16">
         <v>1.1</v>
@@ -2953,7 +2953,7 @@
         <v>1.4</v>
       </c>
       <c r="Z16">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="AA16">
         <v>2.38</v>
@@ -2971,7 +2971,7 @@
         <v>1.02</v>
       </c>
       <c r="AF16">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AG16">
         <v>1.8</v>
@@ -2990,7 +2990,7 @@
         <v>1.4</v>
       </c>
       <c r="AK16">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G22">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G23">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G24">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G25">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G26">
@@ -5205,16 +5205,16 @@
         <v>3.2</v>
       </c>
       <c r="P30">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q30">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="R30">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="S30">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T30">
         <v>2.95</v>
@@ -5229,34 +5229,34 @@
         <v>1.06</v>
       </c>
       <c r="X30">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y30">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="Z30">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="AA30">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="AB30">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="AC30">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="AD30">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AE30">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF30">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG30">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -7161,58 +7161,58 @@
         <v>4.3</v>
       </c>
       <c r="P42">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="Q42">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="R42">
-        <v>2.19</v>
+        <v>2.37</v>
       </c>
       <c r="S42">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="T42">
-        <v>2.73</v>
+        <v>2.85</v>
       </c>
       <c r="U42">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="V42">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W42">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X42">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y42">
         <v>1.3</v>
       </c>
       <c r="Z42">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AA42">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AB42">
         <v>1.8</v>
       </c>
       <c r="AC42">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="AD42">
         <v>1.25</v>
       </c>
       <c r="AE42">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF42">
         <v>2.2</v>
       </c>
       <c r="AG42">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK42">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -10415,13 +10415,13 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="O62">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="P62">
-        <v>6.84</v>
+        <v>6.85</v>
       </c>
       <c r="Q62">
         <v>1.83</v>
@@ -10448,7 +10448,7 @@
         <v>1</v>
       </c>
       <c r="Y62">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z62">
         <v>4.06</v>
@@ -10457,7 +10457,7 @@
         <v>1.72</v>
       </c>
       <c r="AB62">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AC62">
         <v>2.88</v>
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.01</v>
+        <v>1.96</v>
       </c>
       <c r="O63">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="P63">
-        <v>3.41</v>
+        <v>3.25</v>
       </c>
       <c r="Q63">
         <v>2.38</v>
@@ -10596,13 +10596,13 @@
         <v>1.35</v>
       </c>
       <c r="T63">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="U63">
         <v>2.55</v>
       </c>
       <c r="V63">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="W63">
         <v>1.08</v>
@@ -10620,7 +10620,7 @@
         <v>1.68</v>
       </c>
       <c r="AB63">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AC63">
         <v>2.57</v>
@@ -10629,13 +10629,13 @@
         <v>1.4</v>
       </c>
       <c r="AE63">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF63">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG63">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10651,7 +10651,7 @@
         <v>1.33</v>
       </c>
       <c r="AK63">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="O73">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P73">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="Q73">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="R73">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="S73">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="T73">
-        <v>3.02</v>
+        <v>2.91</v>
       </c>
       <c r="U73">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="V73">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="W73">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X73">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y73">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z73">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="AA73">
+        <v>1.66</v>
+      </c>
+      <c r="AB73">
+        <v>2</v>
+      </c>
+      <c r="AC73">
+        <v>2.6</v>
+      </c>
+      <c r="AD73">
+        <v>1.38</v>
+      </c>
+      <c r="AE73">
+        <v>1.14</v>
+      </c>
+      <c r="AF73">
         <v>1.56</v>
       </c>
-      <c r="AB73">
-        <v>2.17</v>
-      </c>
-      <c r="AC73">
-        <v>2.38</v>
-      </c>
-      <c r="AD73">
-        <v>1.46</v>
-      </c>
-      <c r="AE73">
-        <v>1.17</v>
-      </c>
-      <c r="AF73">
-        <v>1.52</v>
-      </c>
       <c r="AG73">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AK73">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
-        <v>2.3</v>
+        <v>1.41</v>
       </c>
       <c r="O74">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="P74">
-        <v>2.94</v>
+        <v>6.17</v>
       </c>
       <c r="Q74">
-        <v>2.8</v>
+        <v>1.74</v>
       </c>
       <c r="R74">
-        <v>2.15</v>
+        <v>2.7</v>
       </c>
       <c r="S74">
-        <v>1.35</v>
+        <v>1.19</v>
       </c>
       <c r="T74">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="U74">
-        <v>2.85</v>
+        <v>1.98</v>
       </c>
       <c r="V74">
-        <v>1.39</v>
+        <v>1.64</v>
       </c>
       <c r="W74">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="X74">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y74">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="Z74">
-        <v>3.05</v>
+        <v>4.8</v>
       </c>
       <c r="AA74">
-        <v>1.92</v>
+        <v>1.43</v>
       </c>
       <c r="AB74">
-        <v>1.72</v>
+        <v>2.48</v>
       </c>
       <c r="AC74">
-        <v>3.3</v>
+        <v>2.07</v>
       </c>
       <c r="AD74">
-        <v>1.25</v>
+        <v>1.61</v>
       </c>
       <c r="AE74">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="AF74">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="AG74">
-        <v>1.93</v>
+        <v>2.04</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AK74">
-        <v>1.48</v>
+        <v>2.63</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,65 +12534,65 @@
         </is>
       </c>
       <c r="N75">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="O75">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P75">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q75">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="R75">
+        <v>2.38</v>
+      </c>
+      <c r="S75">
+        <v>1.31</v>
+      </c>
+      <c r="T75">
+        <v>3.02</v>
+      </c>
+      <c r="U75">
+        <v>2.2</v>
+      </c>
+      <c r="V75">
+        <v>1.5</v>
+      </c>
+      <c r="W75">
+        <v>1.07</v>
+      </c>
+      <c r="X75">
+        <v>1.04</v>
+      </c>
+      <c r="Y75">
+        <v>1.16</v>
+      </c>
+      <c r="Z75">
+        <v>4.1</v>
+      </c>
+      <c r="AA75">
+        <v>1.56</v>
+      </c>
+      <c r="AB75">
+        <v>2.17</v>
+      </c>
+      <c r="AC75">
+        <v>2.38</v>
+      </c>
+      <c r="AD75">
+        <v>1.46</v>
+      </c>
+      <c r="AE75">
+        <v>1.17</v>
+      </c>
+      <c r="AF75">
+        <v>1.52</v>
+      </c>
+      <c r="AG75">
         <v>2.28</v>
       </c>
-      <c r="S75">
-        <v>1.33</v>
-      </c>
-      <c r="T75">
-        <v>2.91</v>
-      </c>
-      <c r="U75">
-        <v>2.32</v>
-      </c>
-      <c r="V75">
-        <v>1.46</v>
-      </c>
-      <c r="W75">
-        <v>1.04</v>
-      </c>
-      <c r="X75">
-        <v>1.05</v>
-      </c>
-      <c r="Y75">
-        <v>1.2</v>
-      </c>
-      <c r="Z75">
-        <v>3.75</v>
-      </c>
-      <c r="AA75">
-        <v>1.66</v>
-      </c>
-      <c r="AB75">
-        <v>2</v>
-      </c>
-      <c r="AC75">
-        <v>2.6</v>
-      </c>
-      <c r="AD75">
-        <v>1.38</v>
-      </c>
-      <c r="AE75">
-        <v>1.14</v>
-      </c>
-      <c r="AF75">
-        <v>1.56</v>
-      </c>
-      <c r="AG75">
-        <v>2.18</v>
-      </c>
       <c r="AH75" t="inlineStr">
         <is>
           <t>[]</t>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AK75">
-        <v>1.58</v>
+        <v>1.73</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
-        <v>1.41</v>
+        <v>2.3</v>
       </c>
       <c r="O76">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="P76">
-        <v>6.17</v>
+        <v>2.94</v>
       </c>
       <c r="Q76">
-        <v>1.74</v>
+        <v>2.8</v>
       </c>
       <c r="R76">
+        <v>2.15</v>
+      </c>
+      <c r="S76">
+        <v>1.35</v>
+      </c>
+      <c r="T76">
         <v>2.7</v>
       </c>
-      <c r="S76">
-        <v>1.19</v>
-      </c>
-      <c r="T76">
-        <v>3.8</v>
-      </c>
       <c r="U76">
-        <v>1.98</v>
+        <v>2.85</v>
       </c>
       <c r="V76">
-        <v>1.64</v>
+        <v>1.39</v>
       </c>
       <c r="W76">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="X76">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y76">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="Z76">
-        <v>4.8</v>
+        <v>3.05</v>
       </c>
       <c r="AA76">
-        <v>1.43</v>
+        <v>1.92</v>
       </c>
       <c r="AB76">
-        <v>2.48</v>
+        <v>1.72</v>
       </c>
       <c r="AC76">
-        <v>2.07</v>
+        <v>3.3</v>
       </c>
       <c r="AD76">
-        <v>1.61</v>
+        <v>1.25</v>
       </c>
       <c r="AE76">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="AF76">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="AG76">
-        <v>2.04</v>
+        <v>1.93</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AK76">
-        <v>2.63</v>
+        <v>1.48</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -13186,10 +13186,10 @@
         </is>
       </c>
       <c r="N79">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="O79">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="P79">
         <v>4.65</v>
@@ -13219,22 +13219,22 @@
         <v>1.04</v>
       </c>
       <c r="Y79">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="Z79">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AA79">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AB79">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC79">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="AD79">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AE79">
         <v>1.17</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="O91">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="P91">
-        <v>5.3</v>
+        <v>3.9</v>
       </c>
       <c r="Q91">
-        <v>2.71</v>
+        <v>2.63</v>
       </c>
       <c r="R91">
-        <v>1.69</v>
+        <v>1.95</v>
       </c>
       <c r="S91">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="T91">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="U91">
-        <v>4.45</v>
+        <v>3.7</v>
       </c>
       <c r="V91">
+        <v>1.2</v>
+      </c>
+      <c r="W91">
+        <v>1.02</v>
+      </c>
+      <c r="X91">
+        <v>1.11</v>
+      </c>
+      <c r="Y91">
+        <v>1.5</v>
+      </c>
+      <c r="Z91">
+        <v>2.45</v>
+      </c>
+      <c r="AA91">
+        <v>2.52</v>
+      </c>
+      <c r="AB91">
+        <v>1.41</v>
+      </c>
+      <c r="AC91">
+        <v>5</v>
+      </c>
+      <c r="AD91">
         <v>1.14</v>
       </c>
-      <c r="W91">
-        <v>1.03</v>
-      </c>
-      <c r="X91">
-        <v>1.15</v>
-      </c>
-      <c r="Y91">
-        <v>1.7</v>
-      </c>
-      <c r="Z91">
-        <v>2.03</v>
-      </c>
-      <c r="AA91">
-        <v>3.14</v>
-      </c>
-      <c r="AB91">
-        <v>1.27</v>
-      </c>
-      <c r="AC91">
-        <v>6.75</v>
-      </c>
-      <c r="AD91">
-        <v>1.1</v>
-      </c>
       <c r="AE91">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF91">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="AG91">
-        <v>1.44</v>
+        <v>1.59</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.09</v>
+        <v>1.28</v>
       </c>
       <c r="AK91">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,64 +15305,64 @@
         </is>
       </c>
       <c r="N92">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="O92">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="P92">
-        <v>3.9</v>
+        <v>4.61</v>
       </c>
       <c r="Q92">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R92">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="S92">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="T92">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U92">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="V92">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W92">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X92">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Y92">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z92">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA92">
-        <v>2.52</v>
+        <v>2.87</v>
       </c>
       <c r="AB92">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AC92">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AD92">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AE92">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF92">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG92">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK92">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,13 +15468,13 @@
         </is>
       </c>
       <c r="N93">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O93">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P93">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="Q93">
         <v>0</v>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,80 +15631,80 @@
         </is>
       </c>
       <c r="N94">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O94">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P94">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Q94">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="R94">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S94">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="T94">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U94">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V94">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W94">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X94">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Y94">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z94">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA94">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="AB94">
+        <v>1.33</v>
+      </c>
+      <c r="AC94">
+        <v>6</v>
+      </c>
+      <c r="AD94">
+        <v>1.11</v>
+      </c>
+      <c r="AE94">
+        <v>1.03</v>
+      </c>
+      <c r="AF94">
+        <v>2.4</v>
+      </c>
+      <c r="AG94">
+        <v>1.54</v>
+      </c>
+      <c r="AH94" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI94" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ94">
         <v>1.4</v>
       </c>
-      <c r="AC94">
-        <v>0</v>
-      </c>
-      <c r="AD94">
-        <v>0</v>
-      </c>
-      <c r="AE94">
-        <v>0</v>
-      </c>
-      <c r="AF94">
-        <v>0</v>
-      </c>
-      <c r="AG94">
-        <v>0</v>
-      </c>
-      <c r="AH94" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI94" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ94">
-        <v>0</v>
-      </c>
       <c r="AK94">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,64 +15794,64 @@
         </is>
       </c>
       <c r="N95">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="O95">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="P95">
-        <v>4.15</v>
+        <v>5.3</v>
       </c>
       <c r="Q95">
-        <v>2.87</v>
+        <v>2.71</v>
       </c>
       <c r="R95">
-        <v>1.85</v>
+        <v>1.69</v>
       </c>
       <c r="S95">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="T95">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="U95">
-        <v>3.75</v>
+        <v>4.45</v>
       </c>
       <c r="V95">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="W95">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X95">
         <v>1.15</v>
       </c>
       <c r="Y95">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="Z95">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="AA95">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="AB95">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AC95">
-        <v>6</v>
+        <v>6.75</v>
       </c>
       <c r="AD95">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AE95">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF95">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AG95">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.4</v>
+        <v>1.09</v>
       </c>
       <c r="AK95">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AL95">
         <v>0</v>

--- a/jogos_2026-08-07.xlsx
+++ b/jogos_2026-08-07.xlsx
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,80 +12371,80 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.41</v>
+        <v>1.98</v>
       </c>
       <c r="O74">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="P74">
-        <v>6.17</v>
+        <v>3.3</v>
       </c>
       <c r="Q74">
-        <v>1.74</v>
+        <v>2.33</v>
       </c>
       <c r="R74">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="S74">
+        <v>1.31</v>
+      </c>
+      <c r="T74">
+        <v>3.02</v>
+      </c>
+      <c r="U74">
+        <v>2.2</v>
+      </c>
+      <c r="V74">
+        <v>1.5</v>
+      </c>
+      <c r="W74">
+        <v>1.07</v>
+      </c>
+      <c r="X74">
+        <v>1.04</v>
+      </c>
+      <c r="Y74">
+        <v>1.16</v>
+      </c>
+      <c r="Z74">
+        <v>4.1</v>
+      </c>
+      <c r="AA74">
+        <v>1.56</v>
+      </c>
+      <c r="AB74">
+        <v>2.17</v>
+      </c>
+      <c r="AC74">
+        <v>2.38</v>
+      </c>
+      <c r="AD74">
+        <v>1.46</v>
+      </c>
+      <c r="AE74">
+        <v>1.17</v>
+      </c>
+      <c r="AF74">
+        <v>1.52</v>
+      </c>
+      <c r="AG74">
+        <v>2.28</v>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ74">
         <v>1.19</v>
       </c>
-      <c r="T74">
-        <v>3.8</v>
-      </c>
-      <c r="U74">
-        <v>1.98</v>
-      </c>
-      <c r="V74">
-        <v>1.64</v>
-      </c>
-      <c r="W74">
-        <v>1.14</v>
-      </c>
-      <c r="X74">
-        <v>1.02</v>
-      </c>
-      <c r="Y74">
-        <v>1.12</v>
-      </c>
-      <c r="Z74">
-        <v>4.8</v>
-      </c>
-      <c r="AA74">
-        <v>1.43</v>
-      </c>
-      <c r="AB74">
-        <v>2.48</v>
-      </c>
-      <c r="AC74">
-        <v>2.07</v>
-      </c>
-      <c r="AD74">
-        <v>1.61</v>
-      </c>
-      <c r="AE74">
-        <v>1.24</v>
-      </c>
-      <c r="AF74">
-        <v>1.64</v>
-      </c>
-      <c r="AG74">
-        <v>2.04</v>
-      </c>
-      <c r="AH74" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI74" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ74">
-        <v>1.11</v>
-      </c>
       <c r="AK74">
-        <v>2.63</v>
+        <v>1.73</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.98</v>
+        <v>2.3</v>
       </c>
       <c r="O75">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="P75">
+        <v>2.94</v>
+      </c>
+      <c r="Q75">
+        <v>2.8</v>
+      </c>
+      <c r="R75">
+        <v>2.15</v>
+      </c>
+      <c r="S75">
+        <v>1.35</v>
+      </c>
+      <c r="T75">
+        <v>2.7</v>
+      </c>
+      <c r="U75">
+        <v>2.85</v>
+      </c>
+      <c r="V75">
+        <v>1.39</v>
+      </c>
+      <c r="W75">
+        <v>1.04</v>
+      </c>
+      <c r="X75">
+        <v>1</v>
+      </c>
+      <c r="Y75">
+        <v>1.29</v>
+      </c>
+      <c r="Z75">
+        <v>3.05</v>
+      </c>
+      <c r="AA75">
+        <v>1.92</v>
+      </c>
+      <c r="AB75">
+        <v>1.72</v>
+      </c>
+      <c r="AC75">
         <v>3.3</v>
       </c>
-      <c r="Q75">
-        <v>2.33</v>
-      </c>
-      <c r="R75">
-        <v>2.38</v>
-      </c>
-      <c r="S75">
-        <v>1.31</v>
-      </c>
-      <c r="T75">
-        <v>3.02</v>
-      </c>
-      <c r="U75">
-        <v>2.2</v>
-      </c>
-      <c r="V75">
-        <v>1.5</v>
-      </c>
-      <c r="W75">
-        <v>1.07</v>
-      </c>
-      <c r="X75">
-        <v>1.04</v>
-      </c>
-      <c r="Y75">
-        <v>1.16</v>
-      </c>
-      <c r="Z75">
-        <v>4.1</v>
-      </c>
-      <c r="AA75">
-        <v>1.56</v>
-      </c>
-      <c r="AB75">
-        <v>2.17</v>
-      </c>
-      <c r="AC75">
-        <v>2.38</v>
-      </c>
       <c r="AD75">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="AE75">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AF75">
-        <v>1.52</v>
+        <v>1.72</v>
       </c>
       <c r="AG75">
-        <v>2.28</v>
+        <v>1.93</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK75">
-        <v>1.73</v>
+        <v>1.48</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.3</v>
+        <v>1.41</v>
       </c>
       <c r="O76">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="P76">
-        <v>2.94</v>
+        <v>6.17</v>
       </c>
       <c r="Q76">
-        <v>2.8</v>
+        <v>1.74</v>
       </c>
       <c r="R76">
-        <v>2.15</v>
+        <v>2.7</v>
       </c>
       <c r="S76">
-        <v>1.35</v>
+        <v>1.19</v>
       </c>
       <c r="T76">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="U76">
-        <v>2.85</v>
+        <v>1.98</v>
       </c>
       <c r="V76">
-        <v>1.39</v>
+        <v>1.64</v>
       </c>
       <c r="W76">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="X76">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y76">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="Z76">
-        <v>3.05</v>
+        <v>4.8</v>
       </c>
       <c r="AA76">
-        <v>1.92</v>
+        <v>1.43</v>
       </c>
       <c r="AB76">
-        <v>1.72</v>
+        <v>2.48</v>
       </c>
       <c r="AC76">
-        <v>3.3</v>
+        <v>2.07</v>
       </c>
       <c r="AD76">
-        <v>1.25</v>
+        <v>1.61</v>
       </c>
       <c r="AE76">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="AF76">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="AG76">
-        <v>1.93</v>
+        <v>2.04</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AK76">
-        <v>1.48</v>
+        <v>2.63</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -14342,10 +14342,10 @@
         <v>2.38</v>
       </c>
       <c r="S86">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T86">
-        <v>3.8</v>
+        <v>2.75</v>
       </c>
       <c r="U86">
         <v>2.25</v>
@@ -14357,7 +14357,7 @@
         <v>1.14</v>
       </c>
       <c r="X86">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y86">
         <v>1.13</v>
@@ -14369,13 +14369,13 @@
         <v>1.47</v>
       </c>
       <c r="AB86">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AC86">
-        <v>2.17</v>
+        <v>2.4</v>
       </c>
       <c r="AD86">
-        <v>1.56</v>
+        <v>1.43</v>
       </c>
       <c r="AE86">
         <v>1.18</v>
@@ -14397,7 +14397,7 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AK86">
         <v>2.03</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,64 +15794,64 @@
         </is>
       </c>
       <c r="N95">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O95">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P95">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="Q95">
-        <v>2.71</v>
+        <v>2.9</v>
       </c>
       <c r="R95">
-        <v>1.69</v>
+        <v>1.86</v>
       </c>
       <c r="S95">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="T95">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="U95">
-        <v>4.45</v>
+        <v>3.98</v>
       </c>
       <c r="V95">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="W95">
         <v>1.03</v>
       </c>
       <c r="X95">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="Y95">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="Z95">
-        <v>2.03</v>
+        <v>2.23</v>
       </c>
       <c r="AA95">
-        <v>3.14</v>
+        <v>2.81</v>
       </c>
       <c r="AB95">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AC95">
-        <v>6.75</v>
+        <v>5.75</v>
       </c>
       <c r="AD95">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AE95">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF95">
-        <v>2.6</v>
+        <v>2.32</v>
       </c>
       <c r="AG95">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.09</v>
+        <v>1.4</v>
       </c>
       <c r="AK95">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>1.95</v>
+        <v>1.5</v>
       </c>
       <c r="O96">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="P96">
-        <v>4.4</v>
+        <v>7.5</v>
       </c>
       <c r="Q96">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="R96">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="S96">
-        <v>1.63</v>
+        <v>1.51</v>
       </c>
       <c r="T96">
-        <v>2.13</v>
+        <v>2.31</v>
       </c>
       <c r="U96">
-        <v>3.95</v>
+        <v>3.46</v>
       </c>
       <c r="V96">
+        <v>1.24</v>
+      </c>
+      <c r="W96">
+        <v>1.02</v>
+      </c>
+      <c r="X96">
+        <v>1.1</v>
+      </c>
+      <c r="Y96">
+        <v>1.44</v>
+      </c>
+      <c r="Z96">
+        <v>2.49</v>
+      </c>
+      <c r="AA96">
+        <v>2.48</v>
+      </c>
+      <c r="AB96">
+        <v>1.51</v>
+      </c>
+      <c r="AC96">
+        <v>4.76</v>
+      </c>
+      <c r="AD96">
         <v>1.17</v>
       </c>
-      <c r="W96">
-        <v>1.01</v>
-      </c>
-      <c r="X96">
-        <v>1.07</v>
-      </c>
-      <c r="Y96">
-        <v>1.58</v>
-      </c>
-      <c r="Z96">
-        <v>2.25</v>
-      </c>
-      <c r="AA96">
-        <v>2.9</v>
-      </c>
-      <c r="AB96">
-        <v>1.36</v>
-      </c>
-      <c r="AC96">
-        <v>5.75</v>
-      </c>
-      <c r="AD96">
-        <v>1.07</v>
-      </c>
       <c r="AE96">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF96">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="AG96">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK96">
-        <v>1.74</v>
+        <v>2.45</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>1.5</v>
+        <v>1.95</v>
       </c>
       <c r="O97">
-        <v>3.5</v>
+        <v>2.88</v>
       </c>
       <c r="P97">
-        <v>7.5</v>
+        <v>4.4</v>
       </c>
       <c r="Q97">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="R97">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="S97">
-        <v>1.51</v>
+        <v>1.63</v>
       </c>
       <c r="T97">
-        <v>2.31</v>
+        <v>2.13</v>
       </c>
       <c r="U97">
-        <v>3.46</v>
+        <v>3.95</v>
       </c>
       <c r="V97">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="W97">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X97">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Y97">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="Z97">
-        <v>2.49</v>
+        <v>2.25</v>
       </c>
       <c r="AA97">
-        <v>2.48</v>
+        <v>2.9</v>
       </c>
       <c r="AB97">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="AC97">
-        <v>4.76</v>
+        <v>5.75</v>
       </c>
       <c r="AD97">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="AE97">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF97">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="AG97">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK97">
-        <v>2.45</v>
+        <v>1.74</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,64 +16283,64 @@
         </is>
       </c>
       <c r="N98">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="O98">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="P98">
-        <v>3.6</v>
+        <v>5.3</v>
       </c>
       <c r="Q98">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="R98">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="S98">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="T98">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U98">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="V98">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W98">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X98">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Y98">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z98">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AA98">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="AB98">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AC98">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AD98">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE98">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF98">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AG98">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK98">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,13 +16446,13 @@
         </is>
       </c>
       <c r="N99">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="O99">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="P99">
-        <v>5.75</v>
+        <v>3.6</v>
       </c>
       <c r="Q99">
         <v>0</v>
@@ -16485,10 +16485,10 @@
         <v>0</v>
       </c>
       <c r="AA99">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="AB99">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AC99">
         <v>0</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,13 +16609,13 @@
         </is>
       </c>
       <c r="N100">
-        <v>2.51</v>
+        <v>1.6</v>
       </c>
       <c r="O100">
-        <v>2.81</v>
+        <v>3.2</v>
       </c>
       <c r="P100">
-        <v>3.21</v>
+        <v>5.75</v>
       </c>
       <c r="Q100">
         <v>0</v>
@@ -16648,10 +16648,10 @@
         <v>0</v>
       </c>
       <c r="AA100">
-        <v>2.87</v>
+        <v>2.6</v>
       </c>
       <c r="AB100">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AC100">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,13 +16772,13 @@
         </is>
       </c>
       <c r="N101">
-        <v>1.6</v>
+        <v>2.51</v>
       </c>
       <c r="O101">
-        <v>3.3</v>
+        <v>2.81</v>
       </c>
       <c r="P101">
-        <v>5.5</v>
+        <v>3.21</v>
       </c>
       <c r="Q101">
         <v>0</v>
@@ -16811,10 +16811,10 @@
         <v>0</v>
       </c>
       <c r="AA101">
-        <v>2.35</v>
+        <v>2.87</v>
       </c>
       <c r="AB101">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AC101">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,13 +16935,13 @@
         </is>
       </c>
       <c r="N102">
-        <v>2.02</v>
+        <v>1.6</v>
       </c>
       <c r="O102">
-        <v>3.11</v>
+        <v>3.3</v>
       </c>
       <c r="P102">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -16974,10 +16974,10 @@
         <v>0</v>
       </c>
       <c r="AA102">
-        <v>3.1</v>
+        <v>2.35</v>
       </c>
       <c r="AB102">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AC102">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,13 +17098,13 @@
         </is>
       </c>
       <c r="N103">
-        <v>2.9</v>
+        <v>2.02</v>
       </c>
       <c r="O103">
-        <v>2.5</v>
+        <v>3.11</v>
       </c>
       <c r="P103">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="Q103">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O104">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P104">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q104">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R104">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="S104">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="T104">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U104">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="V104">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="W104">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X104">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y104">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z104">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AA104">
-        <v>2.81</v>
+        <v>3.1</v>
       </c>
       <c r="AB104">
         <v>1.36</v>
       </c>
       <c r="AC104">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AD104">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AE104">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF104">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AG104">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AK104">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL104">
         <v>0</v>

--- a/jogos_2026-08-07.xlsx
+++ b/jogos_2026-08-07.xlsx
@@ -635,58 +635,58 @@
         </is>
       </c>
       <c r="N2">
-        <v>3.82</v>
+        <v>3.84</v>
       </c>
       <c r="O2">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P2">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="Q2">
-        <v>3.98</v>
+        <v>4.4</v>
       </c>
       <c r="R2">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="S2">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T2">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="U2">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="V2">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W2">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X2">
         <v>1.06</v>
       </c>
       <c r="Y2">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z2">
         <v>3.1</v>
       </c>
       <c r="AA2">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="AB2">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AC2">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AD2">
         <v>1.25</v>
       </c>
       <c r="AE2">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF2">
         <v>1.8</v>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.24</v>
+        <v>1.8</v>
       </c>
       <c r="AK2">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -1779,10 +1779,10 @@
         <v>2.36</v>
       </c>
       <c r="O9">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="P9">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="Q9">
         <v>2.9</v>
@@ -1809,28 +1809,28 @@
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z9">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="AA9">
         <v>2.02</v>
       </c>
       <c r="AB9">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC9">
-        <v>3.38</v>
+        <v>3.6</v>
       </c>
       <c r="AD9">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE9">
         <v>1.1</v>
       </c>
       <c r="AF9">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AG9">
         <v>1.98</v>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AK9">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -3243,19 +3243,19 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="O18">
         <v>3.7</v>
       </c>
       <c r="P18">
-        <v>4.19</v>
+        <v>4.05</v>
       </c>
       <c r="Q18">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="R18">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="S18">
         <v>1.29</v>
@@ -3270,50 +3270,50 @@
         <v>1.47</v>
       </c>
       <c r="W18">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X18">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y18">
+        <v>1.22</v>
+      </c>
+      <c r="Z18">
+        <v>3.8</v>
+      </c>
+      <c r="AA18">
+        <v>1.69</v>
+      </c>
+      <c r="AB18">
+        <v>2</v>
+      </c>
+      <c r="AC18">
+        <v>2.62</v>
+      </c>
+      <c r="AD18">
+        <v>1.42</v>
+      </c>
+      <c r="AE18">
+        <v>1.14</v>
+      </c>
+      <c r="AF18">
+        <v>1.65</v>
+      </c>
+      <c r="AG18">
+        <v>2.08</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18">
         <v>1.2</v>
-      </c>
-      <c r="Z18">
-        <v>4</v>
-      </c>
-      <c r="AA18">
-        <v>1.67</v>
-      </c>
-      <c r="AB18">
-        <v>2.04</v>
-      </c>
-      <c r="AC18">
-        <v>2.75</v>
-      </c>
-      <c r="AD18">
-        <v>1.4</v>
-      </c>
-      <c r="AE18">
-        <v>1.15</v>
-      </c>
-      <c r="AF18">
-        <v>1.62</v>
-      </c>
-      <c r="AG18">
-        <v>2.15</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18">
-        <v>1.25</v>
       </c>
       <c r="AK18">
         <v>1.95</v>
@@ -5205,7 +5205,7 @@
         <v>3.2</v>
       </c>
       <c r="P30">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="Q30">
         <v>3.04</v>
@@ -5241,7 +5241,7 @@
         <v>1.79</v>
       </c>
       <c r="AB30">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="AC30">
         <v>2.83</v>
@@ -5253,7 +5253,7 @@
         <v>1.11</v>
       </c>
       <c r="AF30">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG30">
         <v>2.1</v>
@@ -5272,7 +5272,7 @@
         <v>1.28</v>
       </c>
       <c r="AK30">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="O32">
-        <v>3.46</v>
+        <v>3.4</v>
       </c>
       <c r="P32">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="Q32">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="R32">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="S32">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T32">
         <v>3.2</v>
       </c>
       <c r="U32">
-        <v>2.44</v>
+        <v>2.28</v>
       </c>
       <c r="V32">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="W32">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X32">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y32">
         <v>1.22</v>
       </c>
       <c r="Z32">
-        <v>3.84</v>
+        <v>4.2</v>
       </c>
       <c r="AA32">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AB32">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AC32">
         <v>2.62</v>
       </c>
       <c r="AD32">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="AE32">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AF32">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AG32">
-        <v>2.23</v>
+        <v>2.35</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>1.22</v>
       </c>
       <c r="AK32">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5851,19 +5851,19 @@
         </is>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="Q34">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="R34">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S34">
         <v>0</v>
@@ -5872,10 +5872,10 @@
         <v>0</v>
       </c>
       <c r="U34">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V34">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W34">
         <v>0</v>
@@ -5884,31 +5884,31 @@
         <v>0</v>
       </c>
       <c r="Y34">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z34">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AA34">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AB34">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AC34">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AD34">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AE34">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AF34">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AG34">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK34">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6177,37 +6177,37 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="O36">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P36">
+        <v>2.2</v>
+      </c>
+      <c r="Q36">
+        <v>3.3</v>
+      </c>
+      <c r="R36">
+        <v>2.4</v>
+      </c>
+      <c r="S36">
+        <v>1.29</v>
+      </c>
+      <c r="T36">
+        <v>3.28</v>
+      </c>
+      <c r="U36">
         <v>2.3</v>
       </c>
-      <c r="Q36">
-        <v>3.2</v>
-      </c>
-      <c r="R36">
-        <v>2.3</v>
-      </c>
-      <c r="S36">
-        <v>1.28</v>
-      </c>
-      <c r="T36">
-        <v>3.3</v>
-      </c>
-      <c r="U36">
-        <v>2.36</v>
-      </c>
       <c r="V36">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W36">
         <v>1.1</v>
       </c>
       <c r="X36">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y36">
         <v>1.18</v>
@@ -6216,13 +6216,13 @@
         <v>4.4</v>
       </c>
       <c r="AA36">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AB36">
         <v>2.25</v>
       </c>
       <c r="AC36">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AD36">
         <v>1.44</v>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK36">
         <v>1.4</v>
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="O37">
-        <v>3.52</v>
+        <v>3.3</v>
       </c>
       <c r="P37">
-        <v>3.99</v>
+        <v>3.2</v>
       </c>
       <c r="Q37">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="R37">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="S37">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T37">
-        <v>2.53</v>
+        <v>2.65</v>
       </c>
       <c r="U37">
-        <v>2.82</v>
+        <v>3.04</v>
       </c>
       <c r="V37">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W37">
+        <v>1.04</v>
+      </c>
+      <c r="X37">
         <v>1.05</v>
       </c>
-      <c r="X37">
-        <v>1.06</v>
-      </c>
       <c r="Y37">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Z37">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="AA37">
-        <v>1.95</v>
+        <v>2.14</v>
       </c>
       <c r="AB37">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AC37">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AD37">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE37">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF37">
         <v>1.85</v>
       </c>
       <c r="AG37">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AK37">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6666,19 +6666,19 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="O39">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="P39">
-        <v>5.53</v>
+        <v>5.7</v>
       </c>
       <c r="Q39">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="R39">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="S39">
         <v>1.2</v>
@@ -6687,43 +6687,43 @@
         <v>4</v>
       </c>
       <c r="U39">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V39">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="W39">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="X39">
         <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Z39">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="AA39">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AB39">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="AC39">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AD39">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AE39">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AF39">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AG39">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -7164,55 +7164,55 @@
         <v>9</v>
       </c>
       <c r="Q42">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="R42">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="S42">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T42">
-        <v>2.85</v>
+        <v>2.73</v>
       </c>
       <c r="U42">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="V42">
         <v>1.4</v>
       </c>
       <c r="W42">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X42">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y42">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z42">
         <v>3.2</v>
       </c>
       <c r="AA42">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AB42">
         <v>1.8</v>
       </c>
       <c r="AC42">
-        <v>3.34</v>
+        <v>3.39</v>
       </c>
       <c r="AD42">
         <v>1.25</v>
       </c>
       <c r="AE42">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF42">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AG42">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.19</v>
+        <v>1.06</v>
       </c>
       <c r="AK42">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S44">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T44">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U44">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V44">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W44">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X44">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y44">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z44">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA44">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB44">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC44">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD44">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE44">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF44">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG44">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK44">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.33</v>
+        <v>2.44</v>
       </c>
       <c r="O45">
-        <v>3.77</v>
+        <v>3.6</v>
       </c>
       <c r="P45">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="Q45">
-        <v>2.95</v>
+        <v>3.06</v>
       </c>
       <c r="R45">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="S45">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T45">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="U45">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="V45">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="W45">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X45">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y45">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z45">
-        <v>4.8</v>
+        <v>4.35</v>
       </c>
       <c r="AA45">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AB45">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="AC45">
         <v>2.42</v>
       </c>
       <c r="AD45">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AE45">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AF45">
         <v>1.5</v>
       </c>
       <c r="AG45">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK45">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7973,25 +7973,25 @@
         <v>1.44</v>
       </c>
       <c r="O47">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="P47">
-        <v>5.45</v>
+        <v>5.25</v>
       </c>
       <c r="Q47">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="R47">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="S47">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="T47">
-        <v>3.86</v>
+        <v>3.88</v>
       </c>
       <c r="U47">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="V47">
         <v>1.7</v>
@@ -8003,22 +8003,22 @@
         <v>1.02</v>
       </c>
       <c r="Y47">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="Z47">
-        <v>5.45</v>
+        <v>5.5</v>
       </c>
       <c r="AA47">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AB47">
-        <v>2.35</v>
+        <v>2.59</v>
       </c>
       <c r="AC47">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AD47">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AE47">
         <v>1.25</v>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AK47">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="O48">
-        <v>3.52</v>
+        <v>3.55</v>
       </c>
       <c r="P48">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="Q48">
         <v>3.1</v>
@@ -8151,13 +8151,13 @@
         <v>1.29</v>
       </c>
       <c r="T48">
-        <v>3.6</v>
+        <v>3.22</v>
       </c>
       <c r="U48">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="V48">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="W48">
         <v>1.1</v>
@@ -8169,28 +8169,28 @@
         <v>1.15</v>
       </c>
       <c r="Z48">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA48">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AB48">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AC48">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="AD48">
         <v>1.44</v>
       </c>
       <c r="AE48">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AF48">
         <v>1.5</v>
       </c>
       <c r="AG48">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.29</v>
+        <v>1.62</v>
       </c>
       <c r="AK48">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="O49">
         <v>3.8</v>
       </c>
       <c r="P49">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="Q49">
         <v>2.63</v>
@@ -8311,43 +8311,43 @@
         <v>2.53</v>
       </c>
       <c r="S49">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="T49">
-        <v>3.68</v>
+        <v>4</v>
       </c>
       <c r="U49">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V49">
         <v>1.64</v>
       </c>
       <c r="W49">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="X49">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y49">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="Z49">
         <v>5.35</v>
       </c>
       <c r="AA49">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AB49">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="AC49">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AD49">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AE49">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AF49">
         <v>1.44</v>
@@ -8459,31 +8459,31 @@
         </is>
       </c>
       <c r="N50">
-        <v>4.46</v>
+        <v>4</v>
       </c>
       <c r="O50">
-        <v>4.05</v>
+        <v>3.75</v>
       </c>
       <c r="P50">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="Q50">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="R50">
         <v>2.5</v>
       </c>
       <c r="S50">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="T50">
-        <v>3.8</v>
+        <v>3.44</v>
       </c>
       <c r="U50">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="V50">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="W50">
         <v>1.11</v>
@@ -8492,31 +8492,31 @@
         <v>1.03</v>
       </c>
       <c r="Y50">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="Z50">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AA50">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AB50">
+        <v>2.4</v>
+      </c>
+      <c r="AC50">
         <v>2.3</v>
       </c>
-      <c r="AC50">
-        <v>2.35</v>
-      </c>
       <c r="AD50">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AE50">
         <v>1.22</v>
       </c>
       <c r="AF50">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AG50">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>2.05</v>
+        <v>1.25</v>
       </c>
       <c r="AK50">
         <v>1.2</v>
@@ -8622,34 +8622,34 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="O51">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P51">
         <v>2.7</v>
       </c>
       <c r="Q51">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="R51">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S51">
         <v>1.25</v>
       </c>
       <c r="T51">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="U51">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="V51">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W51">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X51">
         <v>1.03</v>
@@ -8664,10 +8664,10 @@
         <v>1.56</v>
       </c>
       <c r="AB51">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="AC51">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AD51">
         <v>1.53</v>
@@ -8676,10 +8676,10 @@
         <v>1.2</v>
       </c>
       <c r="AF51">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AG51">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK51">
         <v>1.53</v>
@@ -8785,61 +8785,61 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="O52">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="P52">
-        <v>8.1</v>
+        <v>6.74</v>
       </c>
       <c r="Q52">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="R52">
-        <v>2.58</v>
+        <v>2.53</v>
       </c>
       <c r="S52">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T52">
-        <v>3.9</v>
+        <v>3.72</v>
       </c>
       <c r="U52">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V52">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="W52">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="X52">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y52">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Z52">
-        <v>6</v>
+        <v>5.55</v>
       </c>
       <c r="AA52">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="AB52">
-        <v>2.84</v>
+        <v>2.59</v>
       </c>
       <c r="AC52">
-        <v>1.78</v>
+        <v>2.08</v>
       </c>
       <c r="AD52">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="AE52">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AF52">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AG52">
         <v>2.3</v>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AK52">
-        <v>2.9</v>
+        <v>2.72</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8948,58 +8948,58 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.35</v>
+        <v>2.44</v>
       </c>
       <c r="O53">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="P53">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="Q53">
-        <v>2.97</v>
+        <v>2.8</v>
       </c>
       <c r="R53">
         <v>2.5</v>
       </c>
       <c r="S53">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="T53">
-        <v>4</v>
+        <v>3.34</v>
       </c>
       <c r="U53">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="V53">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="W53">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X53">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y53">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Z53">
-        <v>5.25</v>
+        <v>4.9</v>
       </c>
       <c r="AA53">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="AB53">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="AC53">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AD53">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AE53">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AF53">
         <v>1.4</v>
@@ -9018,7 +9018,7 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="AK53">
         <v>1.43</v>
@@ -9111,19 +9111,19 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="O54">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="P54">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="Q54">
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="R54">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="S54">
         <v>1.31</v>
@@ -9132,7 +9132,7 @@
         <v>3.02</v>
       </c>
       <c r="U54">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="V54">
         <v>1.47</v>
@@ -9147,16 +9147,16 @@
         <v>1.18</v>
       </c>
       <c r="Z54">
-        <v>3.84</v>
+        <v>3.96</v>
       </c>
       <c r="AA54">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AB54">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="AC54">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="AD54">
         <v>1.35</v>
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
+        <v>2.2</v>
+      </c>
+      <c r="O58">
+        <v>3.6</v>
+      </c>
+      <c r="P58">
+        <v>2.7</v>
+      </c>
+      <c r="Q58">
+        <v>2.62</v>
+      </c>
+      <c r="R58">
+        <v>2.21</v>
+      </c>
+      <c r="S58">
+        <v>1.3</v>
+      </c>
+      <c r="T58">
+        <v>3.22</v>
+      </c>
+      <c r="U58">
         <v>2.34</v>
       </c>
-      <c r="O58">
-        <v>3.66</v>
-      </c>
-      <c r="P58">
-        <v>2.69</v>
-      </c>
-      <c r="Q58">
-        <v>2.63</v>
-      </c>
-      <c r="R58">
-        <v>2.25</v>
-      </c>
-      <c r="S58">
-        <v>1.27</v>
-      </c>
-      <c r="T58">
-        <v>3.28</v>
-      </c>
-      <c r="U58">
-        <v>2.36</v>
-      </c>
       <c r="V58">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="W58">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="X58">
         <v>1.01</v>
       </c>
       <c r="Y58">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z58">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="AA58">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AB58">
         <v>2.25</v>
       </c>
       <c r="AC58">
-        <v>2.15</v>
+        <v>2.55</v>
       </c>
       <c r="AD58">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="AE58">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF58">
         <v>1.5</v>
       </c>
       <c r="AG58">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="AK58">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="N60">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O60">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="P60">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q60">
         <v>0</v>
@@ -10128,10 +10128,10 @@
         <v>0</v>
       </c>
       <c r="AA60">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB60">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC60">
         <v>0</v>
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="O64">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P64">
-        <v>3.44</v>
+        <v>3.34</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -11393,13 +11393,13 @@
         </is>
       </c>
       <c r="N68">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="O68">
         <v>3</v>
       </c>
       <c r="P68">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="Q68">
         <v>0</v>
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="O70">
         <v>3.1</v>
       </c>
       <c r="P70">
-        <v>3.65</v>
+        <v>3.59</v>
       </c>
       <c r="Q70">
         <v>0</v>
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="O71">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="P71">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="Q71">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="O73">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P73">
-        <v>3.25</v>
+        <v>2.94</v>
       </c>
       <c r="Q73">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="R73">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="S73">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T73">
-        <v>2.91</v>
+        <v>2.7</v>
       </c>
       <c r="U73">
-        <v>2.32</v>
+        <v>2.85</v>
       </c>
       <c r="V73">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="W73">
         <v>1.04</v>
       </c>
       <c r="X73">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y73">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="Z73">
-        <v>3.75</v>
+        <v>3.05</v>
       </c>
       <c r="AA73">
-        <v>1.66</v>
+        <v>1.92</v>
       </c>
       <c r="AB73">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AC73">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="AD73">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AE73">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF73">
-        <v>1.56</v>
+        <v>1.72</v>
       </c>
       <c r="AG73">
-        <v>2.18</v>
+        <v>1.93</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK73">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
-        <v>2.3</v>
+        <v>2.04</v>
       </c>
       <c r="O75">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P75">
-        <v>2.94</v>
+        <v>3.25</v>
       </c>
       <c r="Q75">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="R75">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="S75">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T75">
-        <v>2.7</v>
+        <v>2.91</v>
       </c>
       <c r="U75">
-        <v>2.85</v>
+        <v>2.32</v>
       </c>
       <c r="V75">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="W75">
         <v>1.04</v>
       </c>
       <c r="X75">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y75">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="Z75">
-        <v>3.05</v>
+        <v>3.75</v>
       </c>
       <c r="AA75">
-        <v>1.92</v>
+        <v>1.66</v>
       </c>
       <c r="AB75">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="AC75">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="AD75">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AE75">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF75">
-        <v>1.72</v>
+        <v>1.56</v>
       </c>
       <c r="AG75">
-        <v>1.93</v>
+        <v>2.18</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK75">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -13023,13 +13023,13 @@
         </is>
       </c>
       <c r="N78">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="O78">
-        <v>5.82</v>
+        <v>6</v>
       </c>
       <c r="P78">
-        <v>9.550000000000001</v>
+        <v>10</v>
       </c>
       <c r="Q78">
         <v>0</v>
@@ -13512,61 +13512,61 @@
         </is>
       </c>
       <c r="N81">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="O81">
-        <v>3.64</v>
+        <v>3.4</v>
       </c>
       <c r="P81">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="Q81">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="R81">
         <v>2.25</v>
       </c>
       <c r="S81">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="T81">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="U81">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="V81">
         <v>1.39</v>
       </c>
       <c r="W81">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X81">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y81">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Z81">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AA81">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AB81">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC81">
-        <v>3.25</v>
+        <v>3.13</v>
       </c>
       <c r="AD81">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AE81">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF81">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG81">
         <v>2</v>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="AK81">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>1.5</v>
+        <v>1.95</v>
       </c>
       <c r="O96">
-        <v>3.5</v>
+        <v>2.88</v>
       </c>
       <c r="P96">
-        <v>7.5</v>
+        <v>4.4</v>
       </c>
       <c r="Q96">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="R96">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="S96">
-        <v>1.51</v>
+        <v>1.63</v>
       </c>
       <c r="T96">
-        <v>2.31</v>
+        <v>2.13</v>
       </c>
       <c r="U96">
-        <v>3.46</v>
+        <v>3.95</v>
       </c>
       <c r="V96">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="W96">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X96">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Y96">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="Z96">
-        <v>2.49</v>
+        <v>2.25</v>
       </c>
       <c r="AA96">
-        <v>2.48</v>
+        <v>2.9</v>
       </c>
       <c r="AB96">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="AC96">
-        <v>4.76</v>
+        <v>5.75</v>
       </c>
       <c r="AD96">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="AE96">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF96">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="AG96">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK96">
-        <v>2.45</v>
+        <v>1.74</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="O97">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="P97">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="Q97">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="R97">
-        <v>1.91</v>
+        <v>1.69</v>
       </c>
       <c r="S97">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="T97">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="U97">
-        <v>3.95</v>
+        <v>4.45</v>
       </c>
       <c r="V97">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="W97">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X97">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="Y97">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="Z97">
-        <v>2.25</v>
+        <v>2.03</v>
       </c>
       <c r="AA97">
-        <v>2.9</v>
+        <v>3.14</v>
       </c>
       <c r="AB97">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AC97">
-        <v>5.75</v>
+        <v>6.75</v>
       </c>
       <c r="AD97">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AE97">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF97">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="AG97">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AK97">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,58 +16283,58 @@
         </is>
       </c>
       <c r="N98">
-        <v>1.91</v>
+        <v>1.5</v>
       </c>
       <c r="O98">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="P98">
-        <v>5.3</v>
+        <v>7.5</v>
       </c>
       <c r="Q98">
-        <v>2.71</v>
+        <v>2</v>
       </c>
       <c r="R98">
-        <v>1.69</v>
+        <v>2.1</v>
       </c>
       <c r="S98">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="T98">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="U98">
-        <v>4.45</v>
+        <v>3.46</v>
       </c>
       <c r="V98">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="W98">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X98">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Y98">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="Z98">
-        <v>2.03</v>
+        <v>2.49</v>
       </c>
       <c r="AA98">
-        <v>3.14</v>
+        <v>2.48</v>
       </c>
       <c r="AB98">
-        <v>1.27</v>
+        <v>1.51</v>
       </c>
       <c r="AC98">
-        <v>6.75</v>
+        <v>4.76</v>
       </c>
       <c r="AD98">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AE98">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF98">
         <v>2.6</v>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AK98">
-        <v>1.75</v>
+        <v>2.45</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -18411,10 +18411,10 @@
         <v>2.25</v>
       </c>
       <c r="Q111">
-        <v>3.4</v>
+        <v>3.67</v>
       </c>
       <c r="R111">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="S111">
         <v>1.33</v>
@@ -18432,25 +18432,25 @@
         <v>1.08</v>
       </c>
       <c r="X111">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y111">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="Z111">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AA111">
         <v>1.8</v>
       </c>
       <c r="AB111">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="AC111">
-        <v>2.9</v>
+        <v>2.59</v>
       </c>
       <c r="AD111">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AE111">
         <v>1.13</v>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK111">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL111">
         <v>0</v>

--- a/jogos_2026-08-07.xlsx
+++ b/jogos_2026-08-07.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU121"/>
+  <dimension ref="A1:AU95"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="O3">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P3">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q3">
         <v>3.5</v>
       </c>
       <c r="R3">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S3">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T3">
-        <v>2.82</v>
+        <v>2.91</v>
       </c>
       <c r="U3">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="V3">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W3">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X3">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y3">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z3">
-        <v>3.6</v>
+        <v>3.96</v>
       </c>
       <c r="AA3">
         <v>1.8</v>
       </c>
       <c r="AB3">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="AC3">
-        <v>2.83</v>
+        <v>2.91</v>
       </c>
       <c r="AD3">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE3">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF3">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AG3">
         <v>2.15</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK3">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -970,22 +970,22 @@
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>2.31</v>
+        <v>2.42</v>
       </c>
       <c r="R4">
         <v>2.15</v>
       </c>
       <c r="S4">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="T4">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="U4">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="V4">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="W4">
         <v>1.03</v>
@@ -997,29 +997,29 @@
         <v>1.29</v>
       </c>
       <c r="Z4">
-        <v>3.08</v>
+        <v>3.01</v>
       </c>
       <c r="AA4">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="AB4">
+        <v>1.68</v>
+      </c>
+      <c r="AC4">
+        <v>3.58</v>
+      </c>
+      <c r="AD4">
+        <v>1.21</v>
+      </c>
+      <c r="AE4">
+        <v>1.03</v>
+      </c>
+      <c r="AF4">
+        <v>1.91</v>
+      </c>
+      <c r="AG4">
         <v>1.75</v>
       </c>
-      <c r="AC4">
-        <v>3.34</v>
-      </c>
-      <c r="AD4">
-        <v>1.24</v>
-      </c>
-      <c r="AE4">
-        <v>1.05</v>
-      </c>
-      <c r="AF4">
-        <v>1.83</v>
-      </c>
-      <c r="AG4">
-        <v>1.81</v>
-      </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="AK4">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,19 +1124,19 @@
         </is>
       </c>
       <c r="N5">
-        <v>3.96</v>
+        <v>3.7</v>
       </c>
       <c r="O5">
-        <v>3.72</v>
+        <v>3.5</v>
       </c>
       <c r="P5">
         <v>1.77</v>
       </c>
       <c r="Q5">
-        <v>4</v>
+        <v>4.49</v>
       </c>
       <c r="R5">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="S5">
         <v>1.31</v>
@@ -1145,10 +1145,10 @@
         <v>3.02</v>
       </c>
       <c r="U5">
-        <v>2.64</v>
+        <v>2.47</v>
       </c>
       <c r="V5">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="W5">
         <v>1.07</v>
@@ -1157,7 +1157,7 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z5">
         <v>3.83</v>
@@ -1166,19 +1166,19 @@
         <v>1.7</v>
       </c>
       <c r="AB5">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="AC5">
         <v>2.75</v>
       </c>
       <c r="AD5">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AE5">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF5">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AG5">
         <v>2.04</v>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AK5">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1293,7 +1293,7 @@
         <v>4.05</v>
       </c>
       <c r="P6">
-        <v>5</v>
+        <v>5.53</v>
       </c>
       <c r="Q6">
         <v>2</v>
@@ -1302,49 +1302,49 @@
         <v>2.3</v>
       </c>
       <c r="S6">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T6">
-        <v>3.08</v>
+        <v>2.87</v>
       </c>
       <c r="U6">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="V6">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="W6">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X6">
         <v>1.04</v>
       </c>
       <c r="Y6">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="Z6">
-        <v>3.85</v>
+        <v>3.82</v>
       </c>
       <c r="AA6">
         <v>1.76</v>
       </c>
       <c r="AB6">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="AC6">
-        <v>2.6</v>
+        <v>2.93</v>
       </c>
       <c r="AD6">
         <v>1.33</v>
       </c>
       <c r="AE6">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF6">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AG6">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1450,25 +1450,25 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="O7">
         <v>3.45</v>
       </c>
       <c r="P7">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="Q7">
         <v>4.25</v>
       </c>
       <c r="R7">
-        <v>2.21</v>
+        <v>2.06</v>
       </c>
       <c r="S7">
         <v>1.38</v>
       </c>
       <c r="T7">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="U7">
         <v>2.88</v>
@@ -1483,19 +1483,19 @@
         <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z7">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AA7">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="AB7">
         <v>1.8</v>
       </c>
       <c r="AC7">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="AD7">
         <v>1.27</v>
@@ -1622,46 +1622,46 @@
         <v>9.050000000000001</v>
       </c>
       <c r="Q8">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="R8">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="S8">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T8">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="U8">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="V8">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="W8">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X8">
         <v>1.03</v>
       </c>
       <c r="Y8">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z8">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AA8">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AB8">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="AC8">
-        <v>2.55</v>
+        <v>2.68</v>
       </c>
       <c r="AD8">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AE8">
         <v>1.18</v>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AK8">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1960,22 +1960,22 @@
         <v>4.33</v>
       </c>
       <c r="U10">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="V10">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="W10">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X10">
         <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Z10">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AA10">
         <v>1.31</v>
@@ -1984,13 +1984,13 @@
         <v>3.19</v>
       </c>
       <c r="AC10">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="AD10">
         <v>1.83</v>
       </c>
       <c r="AE10">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AF10">
         <v>1.54</v>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,80 +2917,80 @@
         </is>
       </c>
       <c r="N16">
+        <v>2.4</v>
+      </c>
+      <c r="O16">
+        <v>3.55</v>
+      </c>
+      <c r="P16">
         <v>2.55</v>
       </c>
-      <c r="O16">
-        <v>3.1</v>
-      </c>
-      <c r="P16">
-        <v>2.75</v>
-      </c>
       <c r="Q16">
-        <v>3.53</v>
+        <v>2.9</v>
       </c>
       <c r="R16">
-        <v>2.01</v>
+        <v>2.3</v>
       </c>
       <c r="S16">
-        <v>1.45</v>
+        <v>1.28</v>
       </c>
       <c r="T16">
-        <v>2.32</v>
+        <v>3.18</v>
       </c>
       <c r="U16">
-        <v>3.2</v>
+        <v>2.38</v>
       </c>
       <c r="V16">
+        <v>1.48</v>
+      </c>
+      <c r="W16">
+        <v>1.11</v>
+      </c>
+      <c r="X16">
+        <v>1.04</v>
+      </c>
+      <c r="Y16">
+        <v>1.2</v>
+      </c>
+      <c r="Z16">
+        <v>4.2</v>
+      </c>
+      <c r="AA16">
+        <v>1.67</v>
+      </c>
+      <c r="AB16">
+        <v>2.1</v>
+      </c>
+      <c r="AC16">
+        <v>2.63</v>
+      </c>
+      <c r="AD16">
+        <v>1.4</v>
+      </c>
+      <c r="AE16">
+        <v>1.12</v>
+      </c>
+      <c r="AF16">
+        <v>1.57</v>
+      </c>
+      <c r="AG16">
+        <v>2.3</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16">
         <v>1.29</v>
       </c>
-      <c r="W16">
-        <v>1.03</v>
-      </c>
-      <c r="X16">
-        <v>1.1</v>
-      </c>
-      <c r="Y16">
-        <v>1.4</v>
-      </c>
-      <c r="Z16">
-        <v>2.63</v>
-      </c>
-      <c r="AA16">
-        <v>2.38</v>
-      </c>
-      <c r="AB16">
-        <v>1.53</v>
-      </c>
-      <c r="AC16">
-        <v>4.6</v>
-      </c>
-      <c r="AD16">
-        <v>1.18</v>
-      </c>
-      <c r="AE16">
-        <v>1.02</v>
-      </c>
-      <c r="AF16">
-        <v>1.9</v>
-      </c>
-      <c r="AG16">
-        <v>1.8</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16">
-        <v>1.4</v>
-      </c>
       <c r="AK16">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3569,16 +3569,16 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="O20">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P20">
-        <v>2.34</v>
+        <v>2.23</v>
       </c>
       <c r="Q20">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="R20">
         <v>2.38</v>
@@ -3596,7 +3596,7 @@
         <v>1.52</v>
       </c>
       <c r="W20">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X20">
         <v>1.01</v>
@@ -3611,22 +3611,22 @@
         <v>1.58</v>
       </c>
       <c r="AB20">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="AC20">
-        <v>2.48</v>
+        <v>2.43</v>
       </c>
       <c r="AD20">
         <v>1.44</v>
       </c>
       <c r="AE20">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AF20">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AG20">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AK20">
         <v>1.38</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="O27">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="P27">
-        <v>5.53</v>
+        <v>5.65</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="O31">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="P31">
-        <v>4.51</v>
+        <v>6.7</v>
       </c>
       <c r="Q31">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="R31">
         <v>2.3</v>
       </c>
       <c r="S31">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="T31">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="U31">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="V31">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W31">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X31">
         <v>1</v>
       </c>
       <c r="Y31">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z31">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="AA31">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AB31">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="AC31">
-        <v>2.91</v>
+        <v>3.11</v>
       </c>
       <c r="AD31">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AE31">
         <v>1.11</v>
       </c>
       <c r="AF31">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AG31">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.19</v>
+        <v>1.1</v>
       </c>
       <c r="AK31">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5688,10 +5688,10 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="O33">
-        <v>3.74</v>
+        <v>3.62</v>
       </c>
       <c r="P33">
         <v>3.2</v>
@@ -5700,49 +5700,49 @@
         <v>2.5</v>
       </c>
       <c r="R33">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S33">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T33">
-        <v>2.87</v>
+        <v>3.3</v>
       </c>
       <c r="U33">
-        <v>2.56</v>
+        <v>2.37</v>
       </c>
       <c r="V33">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W33">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X33">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y33">
         <v>1.2</v>
       </c>
       <c r="Z33">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AA33">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AB33">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="AC33">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="AD33">
         <v>1.44</v>
       </c>
       <c r="AE33">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AF33">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AG33">
         <v>2.2</v>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK33">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5860,10 +5860,10 @@
         <v>3.89</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S34">
         <v>0</v>
@@ -5872,10 +5872,10 @@
         <v>0</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W34">
         <v>0</v>
@@ -5884,31 +5884,31 @@
         <v>0</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O39">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="P39">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="Q39">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="R39">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S39">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T39">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U39">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V39">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="W39">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X39">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y39">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z39">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AA39">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB39">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AC39">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AD39">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AE39">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF39">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AG39">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK39">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G40">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK41">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7439,7 +7439,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="O44">
-        <v>3.55</v>
+        <v>3.13</v>
       </c>
       <c r="P44">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="Q44">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R44">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S44">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T44">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="U44">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V44">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W44">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X44">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y44">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z44">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA44">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="AB44">
-        <v>2.1</v>
+        <v>1.66</v>
       </c>
       <c r="AC44">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD44">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE44">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF44">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG44">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK44">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -9274,65 +9274,65 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="O55">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="P55">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="Q55">
-        <v>3.11</v>
+        <v>2.9</v>
       </c>
       <c r="R55">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="S55">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="T55">
-        <v>2.53</v>
+        <v>2.7</v>
       </c>
       <c r="U55">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="V55">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="W55">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X55">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y55">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="Z55">
-        <v>2.92</v>
+        <v>3.4</v>
       </c>
       <c r="AA55">
+        <v>2.1</v>
+      </c>
+      <c r="AB55">
+        <v>1.7</v>
+      </c>
+      <c r="AC55">
+        <v>3.3</v>
+      </c>
+      <c r="AD55">
+        <v>1.3</v>
+      </c>
+      <c r="AE55">
+        <v>1.11</v>
+      </c>
+      <c r="AF55">
+        <v>1.69</v>
+      </c>
+      <c r="AG55">
         <v>2.05</v>
       </c>
-      <c r="AB55">
-        <v>1.68</v>
-      </c>
-      <c r="AC55">
-        <v>3.67</v>
-      </c>
-      <c r="AD55">
-        <v>1.26</v>
-      </c>
-      <c r="AE55">
-        <v>1.05</v>
-      </c>
-      <c r="AF55">
-        <v>1.79</v>
-      </c>
-      <c r="AG55">
-        <v>1.9</v>
-      </c>
       <c r="AH55" t="inlineStr">
         <is>
           <t>[]</t>
@@ -9344,7 +9344,7 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK55">
         <v>1.5</v>
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="O56">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="P56">
-        <v>4.86</v>
+        <v>4.65</v>
       </c>
       <c r="Q56">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="R56">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="S56">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T56">
-        <v>3.16</v>
+        <v>3.5</v>
       </c>
       <c r="U56">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="V56">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="W56">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X56">
         <v>1.01</v>
       </c>
       <c r="Y56">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z56">
-        <v>4.3</v>
+        <v>4.53</v>
       </c>
       <c r="AA56">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AB56">
-        <v>2.27</v>
+        <v>2.32</v>
       </c>
       <c r="AC56">
-        <v>2.33</v>
+        <v>2.47</v>
       </c>
       <c r="AD56">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="AE56">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AF56">
         <v>1.62</v>
       </c>
       <c r="AG56">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK56">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -10042,12 +10042,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.9</v>
+        <v>1.47</v>
       </c>
       <c r="O60">
-        <v>3.13</v>
+        <v>4.05</v>
       </c>
       <c r="P60">
-        <v>2.45</v>
+        <v>4.89</v>
       </c>
       <c r="Q60">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R60">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S60">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T60">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U60">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="V60">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W60">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X60">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y60">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z60">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA60">
-        <v>2.05</v>
+        <v>1.46</v>
       </c>
       <c r="AB60">
-        <v>1.66</v>
+        <v>2.38</v>
       </c>
       <c r="AC60">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD60">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE60">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF60">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG60">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK60">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10193,7 +10193,7 @@
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>2026-08-07 15:30:00</t>
+          <t>2026-08-07 15:45:00</t>
         </is>
       </c>
     </row>
@@ -10210,22 +10210,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="O61">
-        <v>4.65</v>
+        <v>4.5</v>
       </c>
       <c r="P61">
-        <v>4.9</v>
+        <v>6.85</v>
       </c>
       <c r="Q61">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="R61">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S61">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="T61">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="U61">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="V61">
-        <v>1.61</v>
+        <v>1.48</v>
       </c>
       <c r="W61">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X61">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y61">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z61">
-        <v>4.85</v>
+        <v>4.06</v>
       </c>
       <c r="AA61">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
       <c r="AB61">
-        <v>2.41</v>
+        <v>2.15</v>
       </c>
       <c r="AC61">
-        <v>2.31</v>
+        <v>2.88</v>
       </c>
       <c r="AD61">
-        <v>1.57</v>
+        <v>1.39</v>
       </c>
       <c r="AE61">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AF61">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AG61">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>1.18</v>
       </c>
       <c r="AK61">
-        <v>2.63</v>
+        <v>2.76</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,31 +10415,31 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.37</v>
+        <v>1.95</v>
       </c>
       <c r="O62">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="P62">
-        <v>6.85</v>
+        <v>3.2</v>
       </c>
       <c r="Q62">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="R62">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="S62">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T62">
-        <v>3.2</v>
+        <v>2.89</v>
       </c>
       <c r="U62">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="V62">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="W62">
         <v>1.08</v>
@@ -10448,31 +10448,31 @@
         <v>1</v>
       </c>
       <c r="Y62">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z62">
-        <v>4.06</v>
+        <v>4</v>
       </c>
       <c r="AA62">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AB62">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC62">
-        <v>2.88</v>
+        <v>2.68</v>
       </c>
       <c r="AD62">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AE62">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF62">
-        <v>1.83</v>
+        <v>1.61</v>
       </c>
       <c r="AG62">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AK62">
-        <v>2.76</v>
+        <v>1.67</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10536,22 +10536,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.96</v>
+        <v>2.09</v>
       </c>
       <c r="O63">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="P63">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="Q63">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="R63">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S63">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T63">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="U63">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="V63">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W63">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X63">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y63">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z63">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AA63">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="AB63">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AC63">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AD63">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE63">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF63">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG63">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK63">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="O64">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P64">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -10780,10 +10780,10 @@
         <v>0</v>
       </c>
       <c r="AA64">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB64">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC64">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G65">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>La Roche VF</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G66">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>La Roche VF</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="N67">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O67">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P67">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,13 +11393,13 @@
         </is>
       </c>
       <c r="N68">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O68">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P68">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Q68">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O69">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P69">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="Q69">
         <v>0</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.08</v>
+        <v>2.65</v>
       </c>
       <c r="O70">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="P70">
-        <v>3.59</v>
+        <v>2.48</v>
       </c>
       <c r="Q70">
         <v>0</v>
@@ -11758,10 +11758,10 @@
         <v>0</v>
       </c>
       <c r="AA70">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB70">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC70">
         <v>0</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O71">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="P71">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q71">
         <v>0</v>
@@ -11921,10 +11921,10 @@
         <v>0</v>
       </c>
       <c r="AA71">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB71">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC71">
         <v>0</v>
@@ -12003,22 +12003,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,64 +12045,64 @@
         </is>
       </c>
       <c r="N72">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O72">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P72">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="Q72">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R72">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S72">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T72">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="U72">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="V72">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W72">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X72">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y72">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z72">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA72">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB72">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC72">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD72">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE72">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF72">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG72">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK72">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="O73">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="P73">
-        <v>2.94</v>
+        <v>3.29</v>
       </c>
       <c r="Q73">
+        <v>2.33</v>
+      </c>
+      <c r="R73">
+        <v>2.25</v>
+      </c>
+      <c r="S73">
+        <v>1.31</v>
+      </c>
+      <c r="T73">
+        <v>3.02</v>
+      </c>
+      <c r="U73">
+        <v>2.2</v>
+      </c>
+      <c r="V73">
+        <v>1.5</v>
+      </c>
+      <c r="W73">
+        <v>1.07</v>
+      </c>
+      <c r="X73">
+        <v>1.04</v>
+      </c>
+      <c r="Y73">
+        <v>1.22</v>
+      </c>
+      <c r="Z73">
+        <v>3.9</v>
+      </c>
+      <c r="AA73">
+        <v>1.56</v>
+      </c>
+      <c r="AB73">
+        <v>2</v>
+      </c>
+      <c r="AC73">
         <v>2.8</v>
       </c>
-      <c r="R73">
-        <v>2.15</v>
-      </c>
-      <c r="S73">
-        <v>1.35</v>
-      </c>
-      <c r="T73">
-        <v>2.7</v>
-      </c>
-      <c r="U73">
-        <v>2.85</v>
-      </c>
-      <c r="V73">
-        <v>1.39</v>
-      </c>
-      <c r="W73">
-        <v>1.04</v>
-      </c>
-      <c r="X73">
-        <v>1</v>
-      </c>
-      <c r="Y73">
-        <v>1.29</v>
-      </c>
-      <c r="Z73">
-        <v>3.05</v>
-      </c>
-      <c r="AA73">
-        <v>1.92</v>
-      </c>
-      <c r="AB73">
-        <v>1.72</v>
-      </c>
-      <c r="AC73">
-        <v>3.3</v>
-      </c>
       <c r="AD73">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AE73">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF73">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="AG73">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK73">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="O74">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P74">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="Q74">
-        <v>2.33</v>
+        <v>2.65</v>
       </c>
       <c r="R74">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="S74">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T74">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="U74">
-        <v>2.2</v>
+        <v>2.56</v>
       </c>
       <c r="V74">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="W74">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X74">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y74">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z74">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="AA74">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="AB74">
-        <v>2.17</v>
+        <v>1.96</v>
       </c>
       <c r="AC74">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="AD74">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="AE74">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF74">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AG74">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK74">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
-        <v>2.04</v>
+        <v>1.3</v>
       </c>
       <c r="O75">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="P75">
-        <v>3.25</v>
+        <v>7.5</v>
       </c>
       <c r="Q75">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R75">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S75">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T75">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="U75">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="V75">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W75">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X75">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y75">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z75">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA75">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB75">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC75">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD75">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE75">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF75">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AG75">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK75">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12712,10 +12712,10 @@
         <v>2.7</v>
       </c>
       <c r="S76">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="T76">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="U76">
         <v>1.98</v>
@@ -12724,37 +12724,37 @@
         <v>1.64</v>
       </c>
       <c r="W76">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X76">
         <v>1.02</v>
       </c>
       <c r="Y76">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="Z76">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AA76">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AB76">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="AC76">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="AD76">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AE76">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AF76">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AG76">
-        <v>2.04</v>
+        <v>1.91</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AK76">
-        <v>2.63</v>
+        <v>3.4</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12818,22 +12818,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,13 +12860,13 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="O77">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="P77">
-        <v>6.56</v>
+        <v>10</v>
       </c>
       <c r="Q77">
         <v>0</v>
@@ -12899,10 +12899,10 @@
         <v>0</v>
       </c>
       <c r="AA77">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB77">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC77">
         <v>0</v>
@@ -12976,27 +12976,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="O78">
-        <v>6</v>
+        <v>3.92</v>
       </c>
       <c r="P78">
-        <v>10</v>
+        <v>4.5</v>
       </c>
       <c r="Q78">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="R78">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S78">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T78">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U78">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V78">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W78">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X78">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y78">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z78">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA78">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AB78">
-        <v>2.7</v>
+        <v>2.13</v>
       </c>
       <c r="AC78">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AD78">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE78">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF78">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG78">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK78">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13127,7 +13127,7 @@
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>2026-08-07 15:45:00</t>
+          <t>2026-08-07 16:00:00</t>
         </is>
       </c>
     </row>
@@ -13144,22 +13144,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="O79">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P79">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="Q79">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="R79">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S79">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T79">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="U79">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V79">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W79">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X79">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y79">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z79">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA79">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB79">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC79">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="AD79">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AE79">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF79">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG79">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK79">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13302,12 +13302,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O80">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P80">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q80">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R80">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S80">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T80">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U80">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="V80">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W80">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X80">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y80">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z80">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA80">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB80">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC80">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD80">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE80">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF80">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG80">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK80">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13453,7 +13453,7 @@
       </c>
       <c r="AU80" t="inlineStr">
         <is>
-          <t>2026-08-07 16:00:00</t>
+          <t>2026-08-07 16:15:00</t>
         </is>
       </c>
     </row>
@@ -13465,27 +13465,27 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O81">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P81">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q81">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R81">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S81">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T81">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U81">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="V81">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W81">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X81">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y81">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z81">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA81">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB81">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC81">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="AD81">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE81">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF81">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG81">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK81">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13616,7 +13616,7 @@
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>2026-08-07 16:15:00</t>
+          <t>2026-08-07 18:15:00</t>
         </is>
       </c>
     </row>
@@ -13628,12 +13628,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G82">
@@ -13779,7 +13779,7 @@
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>2026-08-07 18:15:00</t>
+          <t>2026-08-07 19:00:00</t>
         </is>
       </c>
     </row>
@@ -13791,12 +13791,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O83">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P83">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q83">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R83">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S83">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T83">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U83">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="V83">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W83">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X83">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y83">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z83">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA83">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB83">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC83">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="AD83">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE83">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF83">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG83">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK83">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13942,7 +13942,7 @@
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>2026-08-07 19:00:00</t>
+          <t>2026-08-07 19:30:00</t>
         </is>
       </c>
     </row>
@@ -13954,12 +13954,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,80 +14001,80 @@
         </is>
       </c>
       <c r="N84">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="O84">
-        <v>3.32</v>
+        <v>3</v>
       </c>
       <c r="P84">
-        <v>4.64</v>
+        <v>4</v>
       </c>
       <c r="Q84">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="R84">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="S84">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="T84">
-        <v>2.75</v>
+        <v>2.32</v>
       </c>
       <c r="U84">
-        <v>3.16</v>
+        <v>3.05</v>
       </c>
       <c r="V84">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="W84">
         <v>1.02</v>
       </c>
       <c r="X84">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Y84">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="Z84">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="AA84">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="AB84">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="AC84">
-        <v>3.98</v>
+        <v>4.8</v>
       </c>
       <c r="AD84">
+        <v>1.15</v>
+      </c>
+      <c r="AE84">
+        <v>1.04</v>
+      </c>
+      <c r="AF84">
+        <v>2.2</v>
+      </c>
+      <c r="AG84">
+        <v>1.6</v>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI84" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ84">
         <v>1.2</v>
       </c>
-      <c r="AE84">
-        <v>1.06</v>
-      </c>
-      <c r="AF84">
-        <v>1.98</v>
-      </c>
-      <c r="AG84">
-        <v>1.72</v>
-      </c>
-      <c r="AH84" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI84" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ84">
-        <v>1.33</v>
-      </c>
       <c r="AK84">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14105,7 +14105,7 @@
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>2026-08-07 19:30:00</t>
+          <t>2026-08-07 20:00:00</t>
         </is>
       </c>
     </row>
@@ -14369,10 +14369,10 @@
         <v>1.47</v>
       </c>
       <c r="AB86">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AC86">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="AD86">
         <v>1.43</v>
@@ -14668,49 +14668,49 @@
         <v>2.4</v>
       </c>
       <c r="S88">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T88">
-        <v>2.9</v>
+        <v>3.13</v>
       </c>
       <c r="U88">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="V88">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="W88">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X88">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y88">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z88">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="AA88">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AB88">
-        <v>1.73</v>
+        <v>1.98</v>
       </c>
       <c r="AC88">
-        <v>3</v>
+        <v>3.06</v>
       </c>
       <c r="AD88">
         <v>1.33</v>
       </c>
       <c r="AE88">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF88">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AG88">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="AK88">
-        <v>3.12</v>
+        <v>2.9</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14825,55 +14825,55 @@
         <v>0</v>
       </c>
       <c r="Q89">
-        <v>4.33</v>
+        <v>4.62</v>
       </c>
       <c r="R89">
-        <v>2.31</v>
+        <v>2.24</v>
       </c>
       <c r="S89">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T89">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="U89">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="V89">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W89">
         <v>1.1</v>
       </c>
       <c r="X89">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y89">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z89">
-        <v>4.8</v>
+        <v>4.85</v>
       </c>
       <c r="AA89">
+        <v>1.7</v>
+      </c>
+      <c r="AB89">
+        <v>2.1</v>
+      </c>
+      <c r="AC89">
+        <v>2.27</v>
+      </c>
+      <c r="AD89">
+        <v>1.42</v>
+      </c>
+      <c r="AE89">
+        <v>1.18</v>
+      </c>
+      <c r="AF89">
         <v>1.49</v>
       </c>
-      <c r="AB89">
-        <v>2.3</v>
-      </c>
-      <c r="AC89">
-        <v>2.33</v>
-      </c>
-      <c r="AD89">
-        <v>1.53</v>
-      </c>
-      <c r="AE89">
-        <v>1.17</v>
-      </c>
-      <c r="AF89">
-        <v>1.52</v>
-      </c>
       <c r="AG89">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK89">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>ETO</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,13 +14979,13 @@
         </is>
       </c>
       <c r="N90">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O90">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P90">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Q90">
         <v>0</v>
@@ -15018,10 +15018,10 @@
         <v>0</v>
       </c>
       <c r="AA90">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AB90">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC90">
         <v>0</v>
@@ -15100,7 +15100,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,80 +15142,80 @@
         </is>
       </c>
       <c r="N91">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O91">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P91">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="Q91">
-        <v>2.63</v>
+        <v>3.22</v>
       </c>
       <c r="R91">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="S91">
-        <v>1.54</v>
+        <v>1.37</v>
       </c>
       <c r="T91">
-        <v>2.31</v>
+        <v>2.75</v>
       </c>
       <c r="U91">
-        <v>3.7</v>
+        <v>2.75</v>
       </c>
       <c r="V91">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="W91">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X91">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="Y91">
+        <v>1.29</v>
+      </c>
+      <c r="Z91">
+        <v>3.35</v>
+      </c>
+      <c r="AA91">
+        <v>1.9</v>
+      </c>
+      <c r="AB91">
+        <v>1.83</v>
+      </c>
+      <c r="AC91">
+        <v>3.4</v>
+      </c>
+      <c r="AD91">
+        <v>1.29</v>
+      </c>
+      <c r="AE91">
+        <v>1.1</v>
+      </c>
+      <c r="AF91">
+        <v>1.7</v>
+      </c>
+      <c r="AG91">
+        <v>2</v>
+      </c>
+      <c r="AH91" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI91" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ91">
+        <v>1.33</v>
+      </c>
+      <c r="AK91">
         <v>1.5</v>
-      </c>
-      <c r="Z91">
-        <v>2.45</v>
-      </c>
-      <c r="AA91">
-        <v>2.52</v>
-      </c>
-      <c r="AB91">
-        <v>1.41</v>
-      </c>
-      <c r="AC91">
-        <v>5</v>
-      </c>
-      <c r="AD91">
-        <v>1.14</v>
-      </c>
-      <c r="AE91">
-        <v>1.01</v>
-      </c>
-      <c r="AF91">
-        <v>2.15</v>
-      </c>
-      <c r="AG91">
-        <v>1.59</v>
-      </c>
-      <c r="AH91" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI91" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ91">
-        <v>1.28</v>
-      </c>
-      <c r="AK91">
-        <v>1.73</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15263,7 +15263,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G92">
@@ -15308,61 +15308,61 @@
         <v>2.02</v>
       </c>
       <c r="O92">
+        <v>3.24</v>
+      </c>
+      <c r="P92">
+        <v>3.35</v>
+      </c>
+      <c r="Q92">
         <v>2.5</v>
       </c>
-      <c r="P92">
-        <v>4.61</v>
-      </c>
-      <c r="Q92">
-        <v>0</v>
-      </c>
       <c r="R92">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S92">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T92">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U92">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V92">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W92">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X92">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y92">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z92">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA92">
-        <v>2.87</v>
+        <v>2.02</v>
       </c>
       <c r="AB92">
-        <v>1.4</v>
+        <v>1.69</v>
       </c>
       <c r="AC92">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AD92">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE92">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF92">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG92">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK92">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15426,22 +15426,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G93">
@@ -15464,68 +15464,68 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N93">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O93">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P93">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q93">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R93">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S93">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T93">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="U93">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V93">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W93">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X93">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y93">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z93">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA93">
-        <v>2.87</v>
+        <v>1.8</v>
       </c>
       <c r="AB93">
-        <v>1.4</v>
+        <v>2.06</v>
       </c>
       <c r="AC93">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD93">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE93">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF93">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG93">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK93">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15584,12 +15584,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,64 +15631,64 @@
         </is>
       </c>
       <c r="N94">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O94">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P94">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="Q94">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="R94">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="S94">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="T94">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U94">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="V94">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W94">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X94">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Y94">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z94">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA94">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB94">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC94">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AD94">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AE94">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF94">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AG94">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AK94">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15735,7 +15735,7 @@
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>2026-08-07 21:00:00</t>
+          <t>2026-08-07 21:30:00</t>
         </is>
       </c>
     </row>
@@ -15747,12 +15747,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,64 +15794,64 @@
         </is>
       </c>
       <c r="N95">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="O95">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P95">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Q95">
-        <v>2.9</v>
+        <v>1.62</v>
       </c>
       <c r="R95">
-        <v>1.86</v>
+        <v>2.8</v>
       </c>
       <c r="S95">
-        <v>1.57</v>
+        <v>1.22</v>
       </c>
       <c r="T95">
-        <v>2.25</v>
+        <v>4</v>
       </c>
       <c r="U95">
-        <v>3.98</v>
+        <v>2.1</v>
       </c>
       <c r="V95">
+        <v>1.67</v>
+      </c>
+      <c r="W95">
         <v>1.17</v>
       </c>
-      <c r="W95">
-        <v>1.03</v>
-      </c>
       <c r="X95">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="Y95">
-        <v>1.63</v>
+        <v>1.14</v>
       </c>
       <c r="Z95">
-        <v>2.23</v>
+        <v>4.7</v>
       </c>
       <c r="AA95">
-        <v>2.81</v>
+        <v>1.44</v>
       </c>
       <c r="AB95">
-        <v>1.36</v>
+        <v>2.7</v>
       </c>
       <c r="AC95">
-        <v>5.75</v>
+        <v>2.1</v>
       </c>
       <c r="AD95">
-        <v>1.07</v>
+        <v>1.65</v>
       </c>
       <c r="AE95">
-        <v>1.03</v>
+        <v>1.24</v>
       </c>
       <c r="AF95">
-        <v>2.32</v>
+        <v>1.7</v>
       </c>
       <c r="AG95">
-        <v>1.51</v>
+        <v>2</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.4</v>
+        <v>1.06</v>
       </c>
       <c r="AK95">
-        <v>1.65</v>
+        <v>3.1</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15897,4244 +15897,6 @@
         <v>0</v>
       </c>
       <c r="AU95" t="inlineStr">
-        <is>
-          <t>2026-08-07 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Argentina Prim B Nacional</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>Midland</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Deportivo Maipú</t>
-        </is>
-      </c>
-      <c r="G96">
-        <v>0</v>
-      </c>
-      <c r="H96">
-        <v>0</v>
-      </c>
-      <c r="I96">
-        <v>0</v>
-      </c>
-      <c r="J96">
-        <v>0</v>
-      </c>
-      <c r="K96">
-        <v>0</v>
-      </c>
-      <c r="L96">
-        <v>0</v>
-      </c>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N96">
-        <v>1.95</v>
-      </c>
-      <c r="O96">
-        <v>2.88</v>
-      </c>
-      <c r="P96">
-        <v>4.4</v>
-      </c>
-      <c r="Q96">
-        <v>2.5</v>
-      </c>
-      <c r="R96">
-        <v>1.91</v>
-      </c>
-      <c r="S96">
-        <v>1.63</v>
-      </c>
-      <c r="T96">
-        <v>2.13</v>
-      </c>
-      <c r="U96">
-        <v>3.95</v>
-      </c>
-      <c r="V96">
-        <v>1.17</v>
-      </c>
-      <c r="W96">
-        <v>1.01</v>
-      </c>
-      <c r="X96">
-        <v>1.07</v>
-      </c>
-      <c r="Y96">
-        <v>1.58</v>
-      </c>
-      <c r="Z96">
-        <v>2.25</v>
-      </c>
-      <c r="AA96">
-        <v>2.9</v>
-      </c>
-      <c r="AB96">
-        <v>1.36</v>
-      </c>
-      <c r="AC96">
-        <v>5.75</v>
-      </c>
-      <c r="AD96">
-        <v>1.07</v>
-      </c>
-      <c r="AE96">
-        <v>1.03</v>
-      </c>
-      <c r="AF96">
-        <v>2.3</v>
-      </c>
-      <c r="AG96">
-        <v>1.57</v>
-      </c>
-      <c r="AH96" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI96" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ96">
-        <v>1.2</v>
-      </c>
-      <c r="AK96">
-        <v>1.74</v>
-      </c>
-      <c r="AL96">
-        <v>0</v>
-      </c>
-      <c r="AM96">
-        <v>-1</v>
-      </c>
-      <c r="AN96">
-        <v>-1</v>
-      </c>
-      <c r="AO96">
-        <v>-1</v>
-      </c>
-      <c r="AP96">
-        <v>-1</v>
-      </c>
-      <c r="AQ96">
-        <v>0</v>
-      </c>
-      <c r="AR96">
-        <v>0</v>
-      </c>
-      <c r="AS96">
-        <v>0</v>
-      </c>
-      <c r="AT96">
-        <v>0</v>
-      </c>
-      <c r="AU96" t="inlineStr">
-        <is>
-          <t>2026-08-07 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Argentina Prim B Nacional</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>Almirante Brown</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Ciudad de Bolívar</t>
-        </is>
-      </c>
-      <c r="G97">
-        <v>0</v>
-      </c>
-      <c r="H97">
-        <v>0</v>
-      </c>
-      <c r="I97">
-        <v>0</v>
-      </c>
-      <c r="J97">
-        <v>0</v>
-      </c>
-      <c r="K97">
-        <v>0</v>
-      </c>
-      <c r="L97">
-        <v>0</v>
-      </c>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N97">
-        <v>1.91</v>
-      </c>
-      <c r="O97">
-        <v>2.7</v>
-      </c>
-      <c r="P97">
-        <v>5.3</v>
-      </c>
-      <c r="Q97">
-        <v>2.71</v>
-      </c>
-      <c r="R97">
-        <v>1.69</v>
-      </c>
-      <c r="S97">
-        <v>1.62</v>
-      </c>
-      <c r="T97">
-        <v>2.2</v>
-      </c>
-      <c r="U97">
-        <v>4.45</v>
-      </c>
-      <c r="V97">
-        <v>1.14</v>
-      </c>
-      <c r="W97">
-        <v>1.03</v>
-      </c>
-      <c r="X97">
-        <v>1.15</v>
-      </c>
-      <c r="Y97">
-        <v>1.7</v>
-      </c>
-      <c r="Z97">
-        <v>2.03</v>
-      </c>
-      <c r="AA97">
-        <v>3.14</v>
-      </c>
-      <c r="AB97">
-        <v>1.27</v>
-      </c>
-      <c r="AC97">
-        <v>6.75</v>
-      </c>
-      <c r="AD97">
-        <v>1.1</v>
-      </c>
-      <c r="AE97">
-        <v>1.02</v>
-      </c>
-      <c r="AF97">
-        <v>2.6</v>
-      </c>
-      <c r="AG97">
-        <v>1.44</v>
-      </c>
-      <c r="AH97" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI97" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ97">
-        <v>1.09</v>
-      </c>
-      <c r="AK97">
-        <v>1.75</v>
-      </c>
-      <c r="AL97">
-        <v>0</v>
-      </c>
-      <c r="AM97">
-        <v>-1</v>
-      </c>
-      <c r="AN97">
-        <v>-1</v>
-      </c>
-      <c r="AO97">
-        <v>-1</v>
-      </c>
-      <c r="AP97">
-        <v>-1</v>
-      </c>
-      <c r="AQ97">
-        <v>0</v>
-      </c>
-      <c r="AR97">
-        <v>0</v>
-      </c>
-      <c r="AS97">
-        <v>0</v>
-      </c>
-      <c r="AT97">
-        <v>0</v>
-      </c>
-      <c r="AU97" t="inlineStr">
-        <is>
-          <t>2026-08-07 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Argentina Prim B Nacional</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>Deportivo Morón</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Acassuso</t>
-        </is>
-      </c>
-      <c r="G98">
-        <v>0</v>
-      </c>
-      <c r="H98">
-        <v>0</v>
-      </c>
-      <c r="I98">
-        <v>0</v>
-      </c>
-      <c r="J98">
-        <v>0</v>
-      </c>
-      <c r="K98">
-        <v>0</v>
-      </c>
-      <c r="L98">
-        <v>0</v>
-      </c>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N98">
-        <v>1.5</v>
-      </c>
-      <c r="O98">
-        <v>3.5</v>
-      </c>
-      <c r="P98">
-        <v>7.5</v>
-      </c>
-      <c r="Q98">
-        <v>2</v>
-      </c>
-      <c r="R98">
-        <v>2.1</v>
-      </c>
-      <c r="S98">
-        <v>1.51</v>
-      </c>
-      <c r="T98">
-        <v>2.31</v>
-      </c>
-      <c r="U98">
-        <v>3.46</v>
-      </c>
-      <c r="V98">
-        <v>1.24</v>
-      </c>
-      <c r="W98">
-        <v>1.02</v>
-      </c>
-      <c r="X98">
-        <v>1.1</v>
-      </c>
-      <c r="Y98">
-        <v>1.44</v>
-      </c>
-      <c r="Z98">
-        <v>2.49</v>
-      </c>
-      <c r="AA98">
-        <v>2.48</v>
-      </c>
-      <c r="AB98">
-        <v>1.51</v>
-      </c>
-      <c r="AC98">
-        <v>4.76</v>
-      </c>
-      <c r="AD98">
-        <v>1.17</v>
-      </c>
-      <c r="AE98">
-        <v>1.05</v>
-      </c>
-      <c r="AF98">
-        <v>2.6</v>
-      </c>
-      <c r="AG98">
-        <v>1.44</v>
-      </c>
-      <c r="AH98" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI98" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ98">
-        <v>1.25</v>
-      </c>
-      <c r="AK98">
-        <v>2.45</v>
-      </c>
-      <c r="AL98">
-        <v>0</v>
-      </c>
-      <c r="AM98">
-        <v>-1</v>
-      </c>
-      <c r="AN98">
-        <v>-1</v>
-      </c>
-      <c r="AO98">
-        <v>-1</v>
-      </c>
-      <c r="AP98">
-        <v>-1</v>
-      </c>
-      <c r="AQ98">
-        <v>0</v>
-      </c>
-      <c r="AR98">
-        <v>0</v>
-      </c>
-      <c r="AS98">
-        <v>0</v>
-      </c>
-      <c r="AT98">
-        <v>0</v>
-      </c>
-      <c r="AU98" t="inlineStr">
-        <is>
-          <t>2026-08-07 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Argentina Prim B Nacional</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>Gimnasia y Tiro</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>Nueva Chicago</t>
-        </is>
-      </c>
-      <c r="G99">
-        <v>0</v>
-      </c>
-      <c r="H99">
-        <v>0</v>
-      </c>
-      <c r="I99">
-        <v>0</v>
-      </c>
-      <c r="J99">
-        <v>0</v>
-      </c>
-      <c r="K99">
-        <v>0</v>
-      </c>
-      <c r="L99">
-        <v>0</v>
-      </c>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N99">
-        <v>2.1</v>
-      </c>
-      <c r="O99">
-        <v>2.75</v>
-      </c>
-      <c r="P99">
-        <v>3.6</v>
-      </c>
-      <c r="Q99">
-        <v>0</v>
-      </c>
-      <c r="R99">
-        <v>0</v>
-      </c>
-      <c r="S99">
-        <v>0</v>
-      </c>
-      <c r="T99">
-        <v>0</v>
-      </c>
-      <c r="U99">
-        <v>0</v>
-      </c>
-      <c r="V99">
-        <v>0</v>
-      </c>
-      <c r="W99">
-        <v>0</v>
-      </c>
-      <c r="X99">
-        <v>0</v>
-      </c>
-      <c r="Y99">
-        <v>0</v>
-      </c>
-      <c r="Z99">
-        <v>0</v>
-      </c>
-      <c r="AA99">
-        <v>3.1</v>
-      </c>
-      <c r="AB99">
-        <v>1.36</v>
-      </c>
-      <c r="AC99">
-        <v>0</v>
-      </c>
-      <c r="AD99">
-        <v>0</v>
-      </c>
-      <c r="AE99">
-        <v>0</v>
-      </c>
-      <c r="AF99">
-        <v>0</v>
-      </c>
-      <c r="AG99">
-        <v>0</v>
-      </c>
-      <c r="AH99" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI99" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ99">
-        <v>0</v>
-      </c>
-      <c r="AK99">
-        <v>0</v>
-      </c>
-      <c r="AL99">
-        <v>0</v>
-      </c>
-      <c r="AM99">
-        <v>-1</v>
-      </c>
-      <c r="AN99">
-        <v>-1</v>
-      </c>
-      <c r="AO99">
-        <v>-1</v>
-      </c>
-      <c r="AP99">
-        <v>-1</v>
-      </c>
-      <c r="AQ99">
-        <v>0</v>
-      </c>
-      <c r="AR99">
-        <v>0</v>
-      </c>
-      <c r="AS99">
-        <v>0</v>
-      </c>
-      <c r="AT99">
-        <v>0</v>
-      </c>
-      <c r="AU99" t="inlineStr">
-        <is>
-          <t>2026-08-07 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Argentina Prim B Nacional</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>Quilmes</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>Almagro</t>
-        </is>
-      </c>
-      <c r="G100">
-        <v>0</v>
-      </c>
-      <c r="H100">
-        <v>0</v>
-      </c>
-      <c r="I100">
-        <v>0</v>
-      </c>
-      <c r="J100">
-        <v>0</v>
-      </c>
-      <c r="K100">
-        <v>0</v>
-      </c>
-      <c r="L100">
-        <v>0</v>
-      </c>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N100">
-        <v>1.6</v>
-      </c>
-      <c r="O100">
-        <v>3.2</v>
-      </c>
-      <c r="P100">
-        <v>5.75</v>
-      </c>
-      <c r="Q100">
-        <v>0</v>
-      </c>
-      <c r="R100">
-        <v>0</v>
-      </c>
-      <c r="S100">
-        <v>0</v>
-      </c>
-      <c r="T100">
-        <v>0</v>
-      </c>
-      <c r="U100">
-        <v>0</v>
-      </c>
-      <c r="V100">
-        <v>0</v>
-      </c>
-      <c r="W100">
-        <v>0</v>
-      </c>
-      <c r="X100">
-        <v>0</v>
-      </c>
-      <c r="Y100">
-        <v>0</v>
-      </c>
-      <c r="Z100">
-        <v>0</v>
-      </c>
-      <c r="AA100">
-        <v>2.6</v>
-      </c>
-      <c r="AB100">
-        <v>1.47</v>
-      </c>
-      <c r="AC100">
-        <v>0</v>
-      </c>
-      <c r="AD100">
-        <v>0</v>
-      </c>
-      <c r="AE100">
-        <v>0</v>
-      </c>
-      <c r="AF100">
-        <v>0</v>
-      </c>
-      <c r="AG100">
-        <v>0</v>
-      </c>
-      <c r="AH100" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI100" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ100">
-        <v>0</v>
-      </c>
-      <c r="AK100">
-        <v>0</v>
-      </c>
-      <c r="AL100">
-        <v>0</v>
-      </c>
-      <c r="AM100">
-        <v>-1</v>
-      </c>
-      <c r="AN100">
-        <v>-1</v>
-      </c>
-      <c r="AO100">
-        <v>-1</v>
-      </c>
-      <c r="AP100">
-        <v>-1</v>
-      </c>
-      <c r="AQ100">
-        <v>0</v>
-      </c>
-      <c r="AR100">
-        <v>0</v>
-      </c>
-      <c r="AS100">
-        <v>0</v>
-      </c>
-      <c r="AT100">
-        <v>0</v>
-      </c>
-      <c r="AU100" t="inlineStr">
-        <is>
-          <t>2026-08-07 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Argentina Prim B Nacional</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>Club Atlético Mitre</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>Defensores de Belgrano</t>
-        </is>
-      </c>
-      <c r="G101">
-        <v>0</v>
-      </c>
-      <c r="H101">
-        <v>0</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>0</v>
-      </c>
-      <c r="K101">
-        <v>0</v>
-      </c>
-      <c r="L101">
-        <v>0</v>
-      </c>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N101">
-        <v>2.51</v>
-      </c>
-      <c r="O101">
-        <v>2.81</v>
-      </c>
-      <c r="P101">
-        <v>3.21</v>
-      </c>
-      <c r="Q101">
-        <v>0</v>
-      </c>
-      <c r="R101">
-        <v>0</v>
-      </c>
-      <c r="S101">
-        <v>0</v>
-      </c>
-      <c r="T101">
-        <v>0</v>
-      </c>
-      <c r="U101">
-        <v>0</v>
-      </c>
-      <c r="V101">
-        <v>0</v>
-      </c>
-      <c r="W101">
-        <v>0</v>
-      </c>
-      <c r="X101">
-        <v>0</v>
-      </c>
-      <c r="Y101">
-        <v>0</v>
-      </c>
-      <c r="Z101">
-        <v>0</v>
-      </c>
-      <c r="AA101">
-        <v>2.87</v>
-      </c>
-      <c r="AB101">
-        <v>1.4</v>
-      </c>
-      <c r="AC101">
-        <v>0</v>
-      </c>
-      <c r="AD101">
-        <v>0</v>
-      </c>
-      <c r="AE101">
-        <v>0</v>
-      </c>
-      <c r="AF101">
-        <v>0</v>
-      </c>
-      <c r="AG101">
-        <v>0</v>
-      </c>
-      <c r="AH101" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI101" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ101">
-        <v>0</v>
-      </c>
-      <c r="AK101">
-        <v>0</v>
-      </c>
-      <c r="AL101">
-        <v>0</v>
-      </c>
-      <c r="AM101">
-        <v>-1</v>
-      </c>
-      <c r="AN101">
-        <v>-1</v>
-      </c>
-      <c r="AO101">
-        <v>-1</v>
-      </c>
-      <c r="AP101">
-        <v>-1</v>
-      </c>
-      <c r="AQ101">
-        <v>0</v>
-      </c>
-      <c r="AR101">
-        <v>0</v>
-      </c>
-      <c r="AS101">
-        <v>0</v>
-      </c>
-      <c r="AT101">
-        <v>0</v>
-      </c>
-      <c r="AU101" t="inlineStr">
-        <is>
-          <t>2026-08-07 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Argentina Prim B Nacional</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>Godoy Cruz</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>Chaco For Ever</t>
-        </is>
-      </c>
-      <c r="G102">
-        <v>0</v>
-      </c>
-      <c r="H102">
-        <v>0</v>
-      </c>
-      <c r="I102">
-        <v>0</v>
-      </c>
-      <c r="J102">
-        <v>0</v>
-      </c>
-      <c r="K102">
-        <v>0</v>
-      </c>
-      <c r="L102">
-        <v>0</v>
-      </c>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N102">
-        <v>1.6</v>
-      </c>
-      <c r="O102">
-        <v>3.3</v>
-      </c>
-      <c r="P102">
-        <v>5.5</v>
-      </c>
-      <c r="Q102">
-        <v>0</v>
-      </c>
-      <c r="R102">
-        <v>0</v>
-      </c>
-      <c r="S102">
-        <v>0</v>
-      </c>
-      <c r="T102">
-        <v>0</v>
-      </c>
-      <c r="U102">
-        <v>0</v>
-      </c>
-      <c r="V102">
-        <v>0</v>
-      </c>
-      <c r="W102">
-        <v>0</v>
-      </c>
-      <c r="X102">
-        <v>0</v>
-      </c>
-      <c r="Y102">
-        <v>0</v>
-      </c>
-      <c r="Z102">
-        <v>0</v>
-      </c>
-      <c r="AA102">
-        <v>2.35</v>
-      </c>
-      <c r="AB102">
-        <v>1.57</v>
-      </c>
-      <c r="AC102">
-        <v>0</v>
-      </c>
-      <c r="AD102">
-        <v>0</v>
-      </c>
-      <c r="AE102">
-        <v>0</v>
-      </c>
-      <c r="AF102">
-        <v>0</v>
-      </c>
-      <c r="AG102">
-        <v>0</v>
-      </c>
-      <c r="AH102" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI102" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ102">
-        <v>0</v>
-      </c>
-      <c r="AK102">
-        <v>0</v>
-      </c>
-      <c r="AL102">
-        <v>0</v>
-      </c>
-      <c r="AM102">
-        <v>-1</v>
-      </c>
-      <c r="AN102">
-        <v>-1</v>
-      </c>
-      <c r="AO102">
-        <v>-1</v>
-      </c>
-      <c r="AP102">
-        <v>-1</v>
-      </c>
-      <c r="AQ102">
-        <v>0</v>
-      </c>
-      <c r="AR102">
-        <v>0</v>
-      </c>
-      <c r="AS102">
-        <v>0</v>
-      </c>
-      <c r="AT102">
-        <v>0</v>
-      </c>
-      <c r="AU102" t="inlineStr">
-        <is>
-          <t>2026-08-07 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Argentina Prim B Nacional</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>Atlanta</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>Temperley</t>
-        </is>
-      </c>
-      <c r="G103">
-        <v>0</v>
-      </c>
-      <c r="H103">
-        <v>0</v>
-      </c>
-      <c r="I103">
-        <v>0</v>
-      </c>
-      <c r="J103">
-        <v>0</v>
-      </c>
-      <c r="K103">
-        <v>0</v>
-      </c>
-      <c r="L103">
-        <v>0</v>
-      </c>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N103">
-        <v>2.02</v>
-      </c>
-      <c r="O103">
-        <v>3.11</v>
-      </c>
-      <c r="P103">
-        <v>4</v>
-      </c>
-      <c r="Q103">
-        <v>0</v>
-      </c>
-      <c r="R103">
-        <v>0</v>
-      </c>
-      <c r="S103">
-        <v>0</v>
-      </c>
-      <c r="T103">
-        <v>0</v>
-      </c>
-      <c r="U103">
-        <v>0</v>
-      </c>
-      <c r="V103">
-        <v>0</v>
-      </c>
-      <c r="W103">
-        <v>0</v>
-      </c>
-      <c r="X103">
-        <v>0</v>
-      </c>
-      <c r="Y103">
-        <v>0</v>
-      </c>
-      <c r="Z103">
-        <v>0</v>
-      </c>
-      <c r="AA103">
-        <v>3.1</v>
-      </c>
-      <c r="AB103">
-        <v>1.36</v>
-      </c>
-      <c r="AC103">
-        <v>0</v>
-      </c>
-      <c r="AD103">
-        <v>0</v>
-      </c>
-      <c r="AE103">
-        <v>0</v>
-      </c>
-      <c r="AF103">
-        <v>0</v>
-      </c>
-      <c r="AG103">
-        <v>0</v>
-      </c>
-      <c r="AH103" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI103" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ103">
-        <v>0</v>
-      </c>
-      <c r="AK103">
-        <v>0</v>
-      </c>
-      <c r="AL103">
-        <v>0</v>
-      </c>
-      <c r="AM103">
-        <v>-1</v>
-      </c>
-      <c r="AN103">
-        <v>-1</v>
-      </c>
-      <c r="AO103">
-        <v>-1</v>
-      </c>
-      <c r="AP103">
-        <v>-1</v>
-      </c>
-      <c r="AQ103">
-        <v>0</v>
-      </c>
-      <c r="AR103">
-        <v>0</v>
-      </c>
-      <c r="AS103">
-        <v>0</v>
-      </c>
-      <c r="AT103">
-        <v>0</v>
-      </c>
-      <c r="AU103" t="inlineStr">
-        <is>
-          <t>2026-08-07 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Argentina Prim B Nacional</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>Los Andes</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>Ferro Carril Oeste</t>
-        </is>
-      </c>
-      <c r="G104">
-        <v>0</v>
-      </c>
-      <c r="H104">
-        <v>0</v>
-      </c>
-      <c r="I104">
-        <v>0</v>
-      </c>
-      <c r="J104">
-        <v>0</v>
-      </c>
-      <c r="K104">
-        <v>0</v>
-      </c>
-      <c r="L104">
-        <v>0</v>
-      </c>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N104">
-        <v>2.9</v>
-      </c>
-      <c r="O104">
-        <v>2.5</v>
-      </c>
-      <c r="P104">
-        <v>2.8</v>
-      </c>
-      <c r="Q104">
-        <v>0</v>
-      </c>
-      <c r="R104">
-        <v>0</v>
-      </c>
-      <c r="S104">
-        <v>0</v>
-      </c>
-      <c r="T104">
-        <v>0</v>
-      </c>
-      <c r="U104">
-        <v>0</v>
-      </c>
-      <c r="V104">
-        <v>0</v>
-      </c>
-      <c r="W104">
-        <v>0</v>
-      </c>
-      <c r="X104">
-        <v>0</v>
-      </c>
-      <c r="Y104">
-        <v>0</v>
-      </c>
-      <c r="Z104">
-        <v>0</v>
-      </c>
-      <c r="AA104">
-        <v>3.1</v>
-      </c>
-      <c r="AB104">
-        <v>1.36</v>
-      </c>
-      <c r="AC104">
-        <v>0</v>
-      </c>
-      <c r="AD104">
-        <v>0</v>
-      </c>
-      <c r="AE104">
-        <v>0</v>
-      </c>
-      <c r="AF104">
-        <v>0</v>
-      </c>
-      <c r="AG104">
-        <v>0</v>
-      </c>
-      <c r="AH104" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI104" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ104">
-        <v>0</v>
-      </c>
-      <c r="AK104">
-        <v>0</v>
-      </c>
-      <c r="AL104">
-        <v>0</v>
-      </c>
-      <c r="AM104">
-        <v>-1</v>
-      </c>
-      <c r="AN104">
-        <v>-1</v>
-      </c>
-      <c r="AO104">
-        <v>-1</v>
-      </c>
-      <c r="AP104">
-        <v>-1</v>
-      </c>
-      <c r="AQ104">
-        <v>0</v>
-      </c>
-      <c r="AR104">
-        <v>0</v>
-      </c>
-      <c r="AS104">
-        <v>0</v>
-      </c>
-      <c r="AT104">
-        <v>0</v>
-      </c>
-      <c r="AU104" t="inlineStr">
-        <is>
-          <t>2026-08-07 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Argentina Prim B Nacional</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>Gimnasia Jujuy</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>Tristán Suárez</t>
-        </is>
-      </c>
-      <c r="G105">
-        <v>0</v>
-      </c>
-      <c r="H105">
-        <v>0</v>
-      </c>
-      <c r="I105">
-        <v>0</v>
-      </c>
-      <c r="J105">
-        <v>0</v>
-      </c>
-      <c r="K105">
-        <v>0</v>
-      </c>
-      <c r="L105">
-        <v>0</v>
-      </c>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N105">
-        <v>1.73</v>
-      </c>
-      <c r="O105">
-        <v>3</v>
-      </c>
-      <c r="P105">
-        <v>4.8</v>
-      </c>
-      <c r="Q105">
-        <v>0</v>
-      </c>
-      <c r="R105">
-        <v>0</v>
-      </c>
-      <c r="S105">
-        <v>0</v>
-      </c>
-      <c r="T105">
-        <v>0</v>
-      </c>
-      <c r="U105">
-        <v>0</v>
-      </c>
-      <c r="V105">
-        <v>0</v>
-      </c>
-      <c r="W105">
-        <v>0</v>
-      </c>
-      <c r="X105">
-        <v>0</v>
-      </c>
-      <c r="Y105">
-        <v>0</v>
-      </c>
-      <c r="Z105">
-        <v>0</v>
-      </c>
-      <c r="AA105">
-        <v>2.7</v>
-      </c>
-      <c r="AB105">
-        <v>1.44</v>
-      </c>
-      <c r="AC105">
-        <v>0</v>
-      </c>
-      <c r="AD105">
-        <v>0</v>
-      </c>
-      <c r="AE105">
-        <v>0</v>
-      </c>
-      <c r="AF105">
-        <v>0</v>
-      </c>
-      <c r="AG105">
-        <v>0</v>
-      </c>
-      <c r="AH105" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI105" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ105">
-        <v>0</v>
-      </c>
-      <c r="AK105">
-        <v>0</v>
-      </c>
-      <c r="AL105">
-        <v>0</v>
-      </c>
-      <c r="AM105">
-        <v>-1</v>
-      </c>
-      <c r="AN105">
-        <v>-1</v>
-      </c>
-      <c r="AO105">
-        <v>-1</v>
-      </c>
-      <c r="AP105">
-        <v>-1</v>
-      </c>
-      <c r="AQ105">
-        <v>0</v>
-      </c>
-      <c r="AR105">
-        <v>0</v>
-      </c>
-      <c r="AS105">
-        <v>0</v>
-      </c>
-      <c r="AT105">
-        <v>0</v>
-      </c>
-      <c r="AU105" t="inlineStr">
-        <is>
-          <t>2026-08-07 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Argentina Prim B Nacional</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>Colón</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>San Telmo</t>
-        </is>
-      </c>
-      <c r="G106">
-        <v>0</v>
-      </c>
-      <c r="H106">
-        <v>0</v>
-      </c>
-      <c r="I106">
-        <v>0</v>
-      </c>
-      <c r="J106">
-        <v>0</v>
-      </c>
-      <c r="K106">
-        <v>0</v>
-      </c>
-      <c r="L106">
-        <v>0</v>
-      </c>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N106">
-        <v>0</v>
-      </c>
-      <c r="O106">
-        <v>0</v>
-      </c>
-      <c r="P106">
-        <v>0</v>
-      </c>
-      <c r="Q106">
-        <v>0</v>
-      </c>
-      <c r="R106">
-        <v>0</v>
-      </c>
-      <c r="S106">
-        <v>0</v>
-      </c>
-      <c r="T106">
-        <v>0</v>
-      </c>
-      <c r="U106">
-        <v>0</v>
-      </c>
-      <c r="V106">
-        <v>0</v>
-      </c>
-      <c r="W106">
-        <v>0</v>
-      </c>
-      <c r="X106">
-        <v>0</v>
-      </c>
-      <c r="Y106">
-        <v>0</v>
-      </c>
-      <c r="Z106">
-        <v>0</v>
-      </c>
-      <c r="AA106">
-        <v>2.4</v>
-      </c>
-      <c r="AB106">
-        <v>1.53</v>
-      </c>
-      <c r="AC106">
-        <v>0</v>
-      </c>
-      <c r="AD106">
-        <v>0</v>
-      </c>
-      <c r="AE106">
-        <v>0</v>
-      </c>
-      <c r="AF106">
-        <v>0</v>
-      </c>
-      <c r="AG106">
-        <v>0</v>
-      </c>
-      <c r="AH106" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI106" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ106">
-        <v>0</v>
-      </c>
-      <c r="AK106">
-        <v>0</v>
-      </c>
-      <c r="AL106">
-        <v>0</v>
-      </c>
-      <c r="AM106">
-        <v>-1</v>
-      </c>
-      <c r="AN106">
-        <v>-1</v>
-      </c>
-      <c r="AO106">
-        <v>-1</v>
-      </c>
-      <c r="AP106">
-        <v>-1</v>
-      </c>
-      <c r="AQ106">
-        <v>0</v>
-      </c>
-      <c r="AR106">
-        <v>0</v>
-      </c>
-      <c r="AS106">
-        <v>0</v>
-      </c>
-      <c r="AT106">
-        <v>0</v>
-      </c>
-      <c r="AU106" t="inlineStr">
-        <is>
-          <t>2026-08-07 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Argentina Prim B Nacional</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>Estudiantes Caseros</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>Deportivo Madryn</t>
-        </is>
-      </c>
-      <c r="G107">
-        <v>0</v>
-      </c>
-      <c r="H107">
-        <v>0</v>
-      </c>
-      <c r="I107">
-        <v>0</v>
-      </c>
-      <c r="J107">
-        <v>0</v>
-      </c>
-      <c r="K107">
-        <v>0</v>
-      </c>
-      <c r="L107">
-        <v>0</v>
-      </c>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N107">
-        <v>2</v>
-      </c>
-      <c r="O107">
-        <v>2.8</v>
-      </c>
-      <c r="P107">
-        <v>3.9</v>
-      </c>
-      <c r="Q107">
-        <v>2.71</v>
-      </c>
-      <c r="R107">
-        <v>1.89</v>
-      </c>
-      <c r="S107">
-        <v>1.57</v>
-      </c>
-      <c r="T107">
-        <v>2.25</v>
-      </c>
-      <c r="U107">
-        <v>3.84</v>
-      </c>
-      <c r="V107">
-        <v>1.18</v>
-      </c>
-      <c r="W107">
-        <v>1.03</v>
-      </c>
-      <c r="X107">
-        <v>1.09</v>
-      </c>
-      <c r="Y107">
-        <v>1.6</v>
-      </c>
-      <c r="Z107">
-        <v>2.19</v>
-      </c>
-      <c r="AA107">
-        <v>2.7</v>
-      </c>
-      <c r="AB107">
-        <v>1.36</v>
-      </c>
-      <c r="AC107">
-        <v>5.4</v>
-      </c>
-      <c r="AD107">
-        <v>1.09</v>
-      </c>
-      <c r="AE107">
-        <v>1.03</v>
-      </c>
-      <c r="AF107">
-        <v>2.3</v>
-      </c>
-      <c r="AG107">
-        <v>1.57</v>
-      </c>
-      <c r="AH107" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI107" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ107">
-        <v>1.4</v>
-      </c>
-      <c r="AK107">
-        <v>1.7</v>
-      </c>
-      <c r="AL107">
-        <v>0</v>
-      </c>
-      <c r="AM107">
-        <v>-1</v>
-      </c>
-      <c r="AN107">
-        <v>-1</v>
-      </c>
-      <c r="AO107">
-        <v>-1</v>
-      </c>
-      <c r="AP107">
-        <v>-1</v>
-      </c>
-      <c r="AQ107">
-        <v>0</v>
-      </c>
-      <c r="AR107">
-        <v>0</v>
-      </c>
-      <c r="AS107">
-        <v>0</v>
-      </c>
-      <c r="AT107">
-        <v>0</v>
-      </c>
-      <c r="AU107" t="inlineStr">
-        <is>
-          <t>2026-08-07 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Hungary NB I</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>ETO</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>Ferencváros</t>
-        </is>
-      </c>
-      <c r="G108">
-        <v>0</v>
-      </c>
-      <c r="H108">
-        <v>0</v>
-      </c>
-      <c r="I108">
-        <v>0</v>
-      </c>
-      <c r="J108">
-        <v>0</v>
-      </c>
-      <c r="K108">
-        <v>0</v>
-      </c>
-      <c r="L108">
-        <v>0</v>
-      </c>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N108">
-        <v>0</v>
-      </c>
-      <c r="O108">
-        <v>0</v>
-      </c>
-      <c r="P108">
-        <v>0</v>
-      </c>
-      <c r="Q108">
-        <v>0</v>
-      </c>
-      <c r="R108">
-        <v>0</v>
-      </c>
-      <c r="S108">
-        <v>0</v>
-      </c>
-      <c r="T108">
-        <v>0</v>
-      </c>
-      <c r="U108">
-        <v>0</v>
-      </c>
-      <c r="V108">
-        <v>0</v>
-      </c>
-      <c r="W108">
-        <v>0</v>
-      </c>
-      <c r="X108">
-        <v>0</v>
-      </c>
-      <c r="Y108">
-        <v>0</v>
-      </c>
-      <c r="Z108">
-        <v>0</v>
-      </c>
-      <c r="AA108">
-        <v>0</v>
-      </c>
-      <c r="AB108">
-        <v>0</v>
-      </c>
-      <c r="AC108">
-        <v>0</v>
-      </c>
-      <c r="AD108">
-        <v>0</v>
-      </c>
-      <c r="AE108">
-        <v>0</v>
-      </c>
-      <c r="AF108">
-        <v>0</v>
-      </c>
-      <c r="AG108">
-        <v>0</v>
-      </c>
-      <c r="AH108" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI108" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ108">
-        <v>0</v>
-      </c>
-      <c r="AK108">
-        <v>0</v>
-      </c>
-      <c r="AL108">
-        <v>0</v>
-      </c>
-      <c r="AM108">
-        <v>-1</v>
-      </c>
-      <c r="AN108">
-        <v>-1</v>
-      </c>
-      <c r="AO108">
-        <v>-1</v>
-      </c>
-      <c r="AP108">
-        <v>-1</v>
-      </c>
-      <c r="AQ108">
-        <v>0</v>
-      </c>
-      <c r="AR108">
-        <v>0</v>
-      </c>
-      <c r="AS108">
-        <v>0</v>
-      </c>
-      <c r="AT108">
-        <v>0</v>
-      </c>
-      <c r="AU108" t="inlineStr">
-        <is>
-          <t>2026-08-07 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Ecuador Primera Categoría Serie A</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>LDU Quito</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>CSD Independiente del Valle</t>
-        </is>
-      </c>
-      <c r="G109">
-        <v>0</v>
-      </c>
-      <c r="H109">
-        <v>0</v>
-      </c>
-      <c r="I109">
-        <v>0</v>
-      </c>
-      <c r="J109">
-        <v>0</v>
-      </c>
-      <c r="K109">
-        <v>0</v>
-      </c>
-      <c r="L109">
-        <v>0</v>
-      </c>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N109">
-        <v>0</v>
-      </c>
-      <c r="O109">
-        <v>0</v>
-      </c>
-      <c r="P109">
-        <v>0</v>
-      </c>
-      <c r="Q109">
-        <v>2.88</v>
-      </c>
-      <c r="R109">
-        <v>2.15</v>
-      </c>
-      <c r="S109">
-        <v>1.36</v>
-      </c>
-      <c r="T109">
-        <v>2.78</v>
-      </c>
-      <c r="U109">
-        <v>2.74</v>
-      </c>
-      <c r="V109">
-        <v>1.37</v>
-      </c>
-      <c r="W109">
-        <v>1.07</v>
-      </c>
-      <c r="X109">
-        <v>1.05</v>
-      </c>
-      <c r="Y109">
-        <v>1.25</v>
-      </c>
-      <c r="Z109">
-        <v>3.4</v>
-      </c>
-      <c r="AA109">
-        <v>1.85</v>
-      </c>
-      <c r="AB109">
-        <v>1.8</v>
-      </c>
-      <c r="AC109">
-        <v>3.1</v>
-      </c>
-      <c r="AD109">
-        <v>1.3</v>
-      </c>
-      <c r="AE109">
-        <v>1.1</v>
-      </c>
-      <c r="AF109">
-        <v>1.7</v>
-      </c>
-      <c r="AG109">
-        <v>2</v>
-      </c>
-      <c r="AH109" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI109" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ109">
-        <v>1.29</v>
-      </c>
-      <c r="AK109">
-        <v>1.53</v>
-      </c>
-      <c r="AL109">
-        <v>0</v>
-      </c>
-      <c r="AM109">
-        <v>-1</v>
-      </c>
-      <c r="AN109">
-        <v>-1</v>
-      </c>
-      <c r="AO109">
-        <v>-1</v>
-      </c>
-      <c r="AP109">
-        <v>-1</v>
-      </c>
-      <c r="AQ109">
-        <v>0</v>
-      </c>
-      <c r="AR109">
-        <v>0</v>
-      </c>
-      <c r="AS109">
-        <v>0</v>
-      </c>
-      <c r="AT109">
-        <v>0</v>
-      </c>
-      <c r="AU109" t="inlineStr">
-        <is>
-          <t>2026-08-07 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>Gotham FC</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>San Diego Wave</t>
-        </is>
-      </c>
-      <c r="G110">
-        <v>0</v>
-      </c>
-      <c r="H110">
-        <v>0</v>
-      </c>
-      <c r="I110">
-        <v>0</v>
-      </c>
-      <c r="J110">
-        <v>0</v>
-      </c>
-      <c r="K110">
-        <v>0</v>
-      </c>
-      <c r="L110">
-        <v>0</v>
-      </c>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N110">
-        <v>2.02</v>
-      </c>
-      <c r="O110">
-        <v>3.24</v>
-      </c>
-      <c r="P110">
-        <v>3.35</v>
-      </c>
-      <c r="Q110">
-        <v>2.5</v>
-      </c>
-      <c r="R110">
-        <v>2.1</v>
-      </c>
-      <c r="S110">
-        <v>1.4</v>
-      </c>
-      <c r="T110">
-        <v>2.75</v>
-      </c>
-      <c r="U110">
-        <v>2.88</v>
-      </c>
-      <c r="V110">
-        <v>1.33</v>
-      </c>
-      <c r="W110">
-        <v>1.04</v>
-      </c>
-      <c r="X110">
-        <v>1.05</v>
-      </c>
-      <c r="Y110">
-        <v>1.33</v>
-      </c>
-      <c r="Z110">
-        <v>2.9</v>
-      </c>
-      <c r="AA110">
-        <v>2.02</v>
-      </c>
-      <c r="AB110">
-        <v>1.68</v>
-      </c>
-      <c r="AC110">
-        <v>3.75</v>
-      </c>
-      <c r="AD110">
-        <v>1.22</v>
-      </c>
-      <c r="AE110">
-        <v>1.06</v>
-      </c>
-      <c r="AF110">
-        <v>1.8</v>
-      </c>
-      <c r="AG110">
-        <v>1.85</v>
-      </c>
-      <c r="AH110" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI110" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ110">
-        <v>1.33</v>
-      </c>
-      <c r="AK110">
-        <v>1.67</v>
-      </c>
-      <c r="AL110">
-        <v>0</v>
-      </c>
-      <c r="AM110">
-        <v>-1</v>
-      </c>
-      <c r="AN110">
-        <v>-1</v>
-      </c>
-      <c r="AO110">
-        <v>-1</v>
-      </c>
-      <c r="AP110">
-        <v>-1</v>
-      </c>
-      <c r="AQ110">
-        <v>0</v>
-      </c>
-      <c r="AR110">
-        <v>0</v>
-      </c>
-      <c r="AS110">
-        <v>0</v>
-      </c>
-      <c r="AT110">
-        <v>0</v>
-      </c>
-      <c r="AU110" t="inlineStr">
-        <is>
-          <t>2026-08-07 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Croatia Prva HNL</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>Rijeka</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>Dinamo Zagreb</t>
-        </is>
-      </c>
-      <c r="G111">
-        <v>0</v>
-      </c>
-      <c r="H111">
-        <v>0</v>
-      </c>
-      <c r="I111">
-        <v>0</v>
-      </c>
-      <c r="J111">
-        <v>0</v>
-      </c>
-      <c r="K111">
-        <v>0</v>
-      </c>
-      <c r="L111">
-        <v>0</v>
-      </c>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>suspended</t>
-        </is>
-      </c>
-      <c r="N111">
-        <v>2.95</v>
-      </c>
-      <c r="O111">
-        <v>3.2</v>
-      </c>
-      <c r="P111">
-        <v>2.25</v>
-      </c>
-      <c r="Q111">
-        <v>3.67</v>
-      </c>
-      <c r="R111">
-        <v>2.28</v>
-      </c>
-      <c r="S111">
-        <v>1.33</v>
-      </c>
-      <c r="T111">
-        <v>2.98</v>
-      </c>
-      <c r="U111">
-        <v>2.44</v>
-      </c>
-      <c r="V111">
-        <v>1.48</v>
-      </c>
-      <c r="W111">
-        <v>1.08</v>
-      </c>
-      <c r="X111">
-        <v>1.01</v>
-      </c>
-      <c r="Y111">
-        <v>1.19</v>
-      </c>
-      <c r="Z111">
-        <v>3.8</v>
-      </c>
-      <c r="AA111">
-        <v>1.8</v>
-      </c>
-      <c r="AB111">
-        <v>2.06</v>
-      </c>
-      <c r="AC111">
-        <v>2.59</v>
-      </c>
-      <c r="AD111">
-        <v>1.39</v>
-      </c>
-      <c r="AE111">
-        <v>1.13</v>
-      </c>
-      <c r="AF111">
-        <v>1.62</v>
-      </c>
-      <c r="AG111">
-        <v>2.2</v>
-      </c>
-      <c r="AH111" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI111" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ111">
-        <v>1.29</v>
-      </c>
-      <c r="AK111">
-        <v>1.36</v>
-      </c>
-      <c r="AL111">
-        <v>0</v>
-      </c>
-      <c r="AM111">
-        <v>-1</v>
-      </c>
-      <c r="AN111">
-        <v>-1</v>
-      </c>
-      <c r="AO111">
-        <v>-1</v>
-      </c>
-      <c r="AP111">
-        <v>-1</v>
-      </c>
-      <c r="AQ111">
-        <v>0</v>
-      </c>
-      <c r="AR111">
-        <v>0</v>
-      </c>
-      <c r="AS111">
-        <v>0</v>
-      </c>
-      <c r="AT111">
-        <v>0</v>
-      </c>
-      <c r="AU111" t="inlineStr">
-        <is>
-          <t>2026-08-07 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>Borac Čačak</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>Voždovac</t>
-        </is>
-      </c>
-      <c r="G112">
-        <v>0</v>
-      </c>
-      <c r="H112">
-        <v>0</v>
-      </c>
-      <c r="I112">
-        <v>0</v>
-      </c>
-      <c r="J112">
-        <v>0</v>
-      </c>
-      <c r="K112">
-        <v>0</v>
-      </c>
-      <c r="L112">
-        <v>0</v>
-      </c>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N112">
-        <v>0</v>
-      </c>
-      <c r="O112">
-        <v>0</v>
-      </c>
-      <c r="P112">
-        <v>0</v>
-      </c>
-      <c r="Q112">
-        <v>0</v>
-      </c>
-      <c r="R112">
-        <v>0</v>
-      </c>
-      <c r="S112">
-        <v>0</v>
-      </c>
-      <c r="T112">
-        <v>0</v>
-      </c>
-      <c r="U112">
-        <v>0</v>
-      </c>
-      <c r="V112">
-        <v>0</v>
-      </c>
-      <c r="W112">
-        <v>0</v>
-      </c>
-      <c r="X112">
-        <v>0</v>
-      </c>
-      <c r="Y112">
-        <v>0</v>
-      </c>
-      <c r="Z112">
-        <v>0</v>
-      </c>
-      <c r="AA112">
-        <v>0</v>
-      </c>
-      <c r="AB112">
-        <v>0</v>
-      </c>
-      <c r="AC112">
-        <v>0</v>
-      </c>
-      <c r="AD112">
-        <v>0</v>
-      </c>
-      <c r="AE112">
-        <v>0</v>
-      </c>
-      <c r="AF112">
-        <v>0</v>
-      </c>
-      <c r="AG112">
-        <v>0</v>
-      </c>
-      <c r="AH112" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI112" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ112">
-        <v>0</v>
-      </c>
-      <c r="AK112">
-        <v>0</v>
-      </c>
-      <c r="AL112">
-        <v>0</v>
-      </c>
-      <c r="AM112">
-        <v>-1</v>
-      </c>
-      <c r="AN112">
-        <v>-1</v>
-      </c>
-      <c r="AO112">
-        <v>-1</v>
-      </c>
-      <c r="AP112">
-        <v>-1</v>
-      </c>
-      <c r="AQ112">
-        <v>0</v>
-      </c>
-      <c r="AR112">
-        <v>0</v>
-      </c>
-      <c r="AS112">
-        <v>0</v>
-      </c>
-      <c r="AT112">
-        <v>0</v>
-      </c>
-      <c r="AU112" t="inlineStr">
-        <is>
-          <t>2026-08-07 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>Bačka Topola</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>Javor Ivanjica</t>
-        </is>
-      </c>
-      <c r="G113">
-        <v>0</v>
-      </c>
-      <c r="H113">
-        <v>0</v>
-      </c>
-      <c r="I113">
-        <v>0</v>
-      </c>
-      <c r="J113">
-        <v>0</v>
-      </c>
-      <c r="K113">
-        <v>0</v>
-      </c>
-      <c r="L113">
-        <v>0</v>
-      </c>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N113">
-        <v>0</v>
-      </c>
-      <c r="O113">
-        <v>0</v>
-      </c>
-      <c r="P113">
-        <v>0</v>
-      </c>
-      <c r="Q113">
-        <v>0</v>
-      </c>
-      <c r="R113">
-        <v>0</v>
-      </c>
-      <c r="S113">
-        <v>0</v>
-      </c>
-      <c r="T113">
-        <v>0</v>
-      </c>
-      <c r="U113">
-        <v>0</v>
-      </c>
-      <c r="V113">
-        <v>0</v>
-      </c>
-      <c r="W113">
-        <v>0</v>
-      </c>
-      <c r="X113">
-        <v>0</v>
-      </c>
-      <c r="Y113">
-        <v>0</v>
-      </c>
-      <c r="Z113">
-        <v>0</v>
-      </c>
-      <c r="AA113">
-        <v>0</v>
-      </c>
-      <c r="AB113">
-        <v>0</v>
-      </c>
-      <c r="AC113">
-        <v>0</v>
-      </c>
-      <c r="AD113">
-        <v>0</v>
-      </c>
-      <c r="AE113">
-        <v>0</v>
-      </c>
-      <c r="AF113">
-        <v>0</v>
-      </c>
-      <c r="AG113">
-        <v>0</v>
-      </c>
-      <c r="AH113" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI113" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ113">
-        <v>0</v>
-      </c>
-      <c r="AK113">
-        <v>0</v>
-      </c>
-      <c r="AL113">
-        <v>0</v>
-      </c>
-      <c r="AM113">
-        <v>-1</v>
-      </c>
-      <c r="AN113">
-        <v>-1</v>
-      </c>
-      <c r="AO113">
-        <v>-1</v>
-      </c>
-      <c r="AP113">
-        <v>-1</v>
-      </c>
-      <c r="AQ113">
-        <v>0</v>
-      </c>
-      <c r="AR113">
-        <v>0</v>
-      </c>
-      <c r="AS113">
-        <v>0</v>
-      </c>
-      <c r="AT113">
-        <v>0</v>
-      </c>
-      <c r="AU113" t="inlineStr">
-        <is>
-          <t>2026-08-07 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>Dubočica</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>Loznica</t>
-        </is>
-      </c>
-      <c r="G114">
-        <v>0</v>
-      </c>
-      <c r="H114">
-        <v>0</v>
-      </c>
-      <c r="I114">
-        <v>0</v>
-      </c>
-      <c r="J114">
-        <v>0</v>
-      </c>
-      <c r="K114">
-        <v>0</v>
-      </c>
-      <c r="L114">
-        <v>0</v>
-      </c>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N114">
-        <v>0</v>
-      </c>
-      <c r="O114">
-        <v>0</v>
-      </c>
-      <c r="P114">
-        <v>0</v>
-      </c>
-      <c r="Q114">
-        <v>0</v>
-      </c>
-      <c r="R114">
-        <v>0</v>
-      </c>
-      <c r="S114">
-        <v>0</v>
-      </c>
-      <c r="T114">
-        <v>0</v>
-      </c>
-      <c r="U114">
-        <v>0</v>
-      </c>
-      <c r="V114">
-        <v>0</v>
-      </c>
-      <c r="W114">
-        <v>0</v>
-      </c>
-      <c r="X114">
-        <v>0</v>
-      </c>
-      <c r="Y114">
-        <v>0</v>
-      </c>
-      <c r="Z114">
-        <v>0</v>
-      </c>
-      <c r="AA114">
-        <v>0</v>
-      </c>
-      <c r="AB114">
-        <v>0</v>
-      </c>
-      <c r="AC114">
-        <v>0</v>
-      </c>
-      <c r="AD114">
-        <v>0</v>
-      </c>
-      <c r="AE114">
-        <v>0</v>
-      </c>
-      <c r="AF114">
-        <v>0</v>
-      </c>
-      <c r="AG114">
-        <v>0</v>
-      </c>
-      <c r="AH114" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI114" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ114">
-        <v>0</v>
-      </c>
-      <c r="AK114">
-        <v>0</v>
-      </c>
-      <c r="AL114">
-        <v>0</v>
-      </c>
-      <c r="AM114">
-        <v>-1</v>
-      </c>
-      <c r="AN114">
-        <v>-1</v>
-      </c>
-      <c r="AO114">
-        <v>-1</v>
-      </c>
-      <c r="AP114">
-        <v>-1</v>
-      </c>
-      <c r="AQ114">
-        <v>0</v>
-      </c>
-      <c r="AR114">
-        <v>0</v>
-      </c>
-      <c r="AS114">
-        <v>0</v>
-      </c>
-      <c r="AT114">
-        <v>0</v>
-      </c>
-      <c r="AU114" t="inlineStr">
-        <is>
-          <t>2026-08-07 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>Metalac GM</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>Spartak Subotica</t>
-        </is>
-      </c>
-      <c r="G115">
-        <v>0</v>
-      </c>
-      <c r="H115">
-        <v>0</v>
-      </c>
-      <c r="I115">
-        <v>0</v>
-      </c>
-      <c r="J115">
-        <v>0</v>
-      </c>
-      <c r="K115">
-        <v>0</v>
-      </c>
-      <c r="L115">
-        <v>0</v>
-      </c>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N115">
-        <v>0</v>
-      </c>
-      <c r="O115">
-        <v>0</v>
-      </c>
-      <c r="P115">
-        <v>0</v>
-      </c>
-      <c r="Q115">
-        <v>0</v>
-      </c>
-      <c r="R115">
-        <v>0</v>
-      </c>
-      <c r="S115">
-        <v>0</v>
-      </c>
-      <c r="T115">
-        <v>0</v>
-      </c>
-      <c r="U115">
-        <v>0</v>
-      </c>
-      <c r="V115">
-        <v>0</v>
-      </c>
-      <c r="W115">
-        <v>0</v>
-      </c>
-      <c r="X115">
-        <v>0</v>
-      </c>
-      <c r="Y115">
-        <v>0</v>
-      </c>
-      <c r="Z115">
-        <v>0</v>
-      </c>
-      <c r="AA115">
-        <v>0</v>
-      </c>
-      <c r="AB115">
-        <v>0</v>
-      </c>
-      <c r="AC115">
-        <v>0</v>
-      </c>
-      <c r="AD115">
-        <v>0</v>
-      </c>
-      <c r="AE115">
-        <v>0</v>
-      </c>
-      <c r="AF115">
-        <v>0</v>
-      </c>
-      <c r="AG115">
-        <v>0</v>
-      </c>
-      <c r="AH115" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI115" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ115">
-        <v>0</v>
-      </c>
-      <c r="AK115">
-        <v>0</v>
-      </c>
-      <c r="AL115">
-        <v>0</v>
-      </c>
-      <c r="AM115">
-        <v>-1</v>
-      </c>
-      <c r="AN115">
-        <v>-1</v>
-      </c>
-      <c r="AO115">
-        <v>-1</v>
-      </c>
-      <c r="AP115">
-        <v>-1</v>
-      </c>
-      <c r="AQ115">
-        <v>0</v>
-      </c>
-      <c r="AR115">
-        <v>0</v>
-      </c>
-      <c r="AS115">
-        <v>0</v>
-      </c>
-      <c r="AT115">
-        <v>0</v>
-      </c>
-      <c r="AU115" t="inlineStr">
-        <is>
-          <t>2026-08-07 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>OFK Vršac</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>Naftagas</t>
-        </is>
-      </c>
-      <c r="G116">
-        <v>0</v>
-      </c>
-      <c r="H116">
-        <v>0</v>
-      </c>
-      <c r="I116">
-        <v>0</v>
-      </c>
-      <c r="J116">
-        <v>0</v>
-      </c>
-      <c r="K116">
-        <v>0</v>
-      </c>
-      <c r="L116">
-        <v>0</v>
-      </c>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N116">
-        <v>0</v>
-      </c>
-      <c r="O116">
-        <v>0</v>
-      </c>
-      <c r="P116">
-        <v>0</v>
-      </c>
-      <c r="Q116">
-        <v>0</v>
-      </c>
-      <c r="R116">
-        <v>0</v>
-      </c>
-      <c r="S116">
-        <v>0</v>
-      </c>
-      <c r="T116">
-        <v>0</v>
-      </c>
-      <c r="U116">
-        <v>0</v>
-      </c>
-      <c r="V116">
-        <v>0</v>
-      </c>
-      <c r="W116">
-        <v>0</v>
-      </c>
-      <c r="X116">
-        <v>0</v>
-      </c>
-      <c r="Y116">
-        <v>0</v>
-      </c>
-      <c r="Z116">
-        <v>0</v>
-      </c>
-      <c r="AA116">
-        <v>0</v>
-      </c>
-      <c r="AB116">
-        <v>0</v>
-      </c>
-      <c r="AC116">
-        <v>0</v>
-      </c>
-      <c r="AD116">
-        <v>0</v>
-      </c>
-      <c r="AE116">
-        <v>0</v>
-      </c>
-      <c r="AF116">
-        <v>0</v>
-      </c>
-      <c r="AG116">
-        <v>0</v>
-      </c>
-      <c r="AH116" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI116" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ116">
-        <v>0</v>
-      </c>
-      <c r="AK116">
-        <v>0</v>
-      </c>
-      <c r="AL116">
-        <v>0</v>
-      </c>
-      <c r="AM116">
-        <v>-1</v>
-      </c>
-      <c r="AN116">
-        <v>-1</v>
-      </c>
-      <c r="AO116">
-        <v>-1</v>
-      </c>
-      <c r="AP116">
-        <v>-1</v>
-      </c>
-      <c r="AQ116">
-        <v>0</v>
-      </c>
-      <c r="AR116">
-        <v>0</v>
-      </c>
-      <c r="AS116">
-        <v>0</v>
-      </c>
-      <c r="AT116">
-        <v>0</v>
-      </c>
-      <c r="AU116" t="inlineStr">
-        <is>
-          <t>2026-08-07 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>Teleoptik</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>Jedinstvo Ub</t>
-        </is>
-      </c>
-      <c r="G117">
-        <v>0</v>
-      </c>
-      <c r="H117">
-        <v>0</v>
-      </c>
-      <c r="I117">
-        <v>0</v>
-      </c>
-      <c r="J117">
-        <v>0</v>
-      </c>
-      <c r="K117">
-        <v>0</v>
-      </c>
-      <c r="L117">
-        <v>0</v>
-      </c>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N117">
-        <v>0</v>
-      </c>
-      <c r="O117">
-        <v>0</v>
-      </c>
-      <c r="P117">
-        <v>0</v>
-      </c>
-      <c r="Q117">
-        <v>0</v>
-      </c>
-      <c r="R117">
-        <v>0</v>
-      </c>
-      <c r="S117">
-        <v>0</v>
-      </c>
-      <c r="T117">
-        <v>0</v>
-      </c>
-      <c r="U117">
-        <v>0</v>
-      </c>
-      <c r="V117">
-        <v>0</v>
-      </c>
-      <c r="W117">
-        <v>0</v>
-      </c>
-      <c r="X117">
-        <v>0</v>
-      </c>
-      <c r="Y117">
-        <v>0</v>
-      </c>
-      <c r="Z117">
-        <v>0</v>
-      </c>
-      <c r="AA117">
-        <v>0</v>
-      </c>
-      <c r="AB117">
-        <v>0</v>
-      </c>
-      <c r="AC117">
-        <v>0</v>
-      </c>
-      <c r="AD117">
-        <v>0</v>
-      </c>
-      <c r="AE117">
-        <v>0</v>
-      </c>
-      <c r="AF117">
-        <v>0</v>
-      </c>
-      <c r="AG117">
-        <v>0</v>
-      </c>
-      <c r="AH117" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI117" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ117">
-        <v>0</v>
-      </c>
-      <c r="AK117">
-        <v>0</v>
-      </c>
-      <c r="AL117">
-        <v>0</v>
-      </c>
-      <c r="AM117">
-        <v>-1</v>
-      </c>
-      <c r="AN117">
-        <v>-1</v>
-      </c>
-      <c r="AO117">
-        <v>-1</v>
-      </c>
-      <c r="AP117">
-        <v>-1</v>
-      </c>
-      <c r="AQ117">
-        <v>0</v>
-      </c>
-      <c r="AR117">
-        <v>0</v>
-      </c>
-      <c r="AS117">
-        <v>0</v>
-      </c>
-      <c r="AT117">
-        <v>0</v>
-      </c>
-      <c r="AU117" t="inlineStr">
-        <is>
-          <t>2026-08-07 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>Bor</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>Napredak</t>
-        </is>
-      </c>
-      <c r="G118">
-        <v>0</v>
-      </c>
-      <c r="H118">
-        <v>0</v>
-      </c>
-      <c r="I118">
-        <v>0</v>
-      </c>
-      <c r="J118">
-        <v>0</v>
-      </c>
-      <c r="K118">
-        <v>0</v>
-      </c>
-      <c r="L118">
-        <v>0</v>
-      </c>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N118">
-        <v>0</v>
-      </c>
-      <c r="O118">
-        <v>0</v>
-      </c>
-      <c r="P118">
-        <v>0</v>
-      </c>
-      <c r="Q118">
-        <v>0</v>
-      </c>
-      <c r="R118">
-        <v>0</v>
-      </c>
-      <c r="S118">
-        <v>0</v>
-      </c>
-      <c r="T118">
-        <v>0</v>
-      </c>
-      <c r="U118">
-        <v>0</v>
-      </c>
-      <c r="V118">
-        <v>0</v>
-      </c>
-      <c r="W118">
-        <v>0</v>
-      </c>
-      <c r="X118">
-        <v>0</v>
-      </c>
-      <c r="Y118">
-        <v>0</v>
-      </c>
-      <c r="Z118">
-        <v>0</v>
-      </c>
-      <c r="AA118">
-        <v>0</v>
-      </c>
-      <c r="AB118">
-        <v>0</v>
-      </c>
-      <c r="AC118">
-        <v>0</v>
-      </c>
-      <c r="AD118">
-        <v>0</v>
-      </c>
-      <c r="AE118">
-        <v>0</v>
-      </c>
-      <c r="AF118">
-        <v>0</v>
-      </c>
-      <c r="AG118">
-        <v>0</v>
-      </c>
-      <c r="AH118" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI118" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ118">
-        <v>0</v>
-      </c>
-      <c r="AK118">
-        <v>0</v>
-      </c>
-      <c r="AL118">
-        <v>0</v>
-      </c>
-      <c r="AM118">
-        <v>-1</v>
-      </c>
-      <c r="AN118">
-        <v>-1</v>
-      </c>
-      <c r="AO118">
-        <v>-1</v>
-      </c>
-      <c r="AP118">
-        <v>-1</v>
-      </c>
-      <c r="AQ118">
-        <v>0</v>
-      </c>
-      <c r="AR118">
-        <v>0</v>
-      </c>
-      <c r="AS118">
-        <v>0</v>
-      </c>
-      <c r="AT118">
-        <v>0</v>
-      </c>
-      <c r="AU118" t="inlineStr">
-        <is>
-          <t>2026-08-07 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>Grafičar</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>Semendrija 1924</t>
-        </is>
-      </c>
-      <c r="G119">
-        <v>0</v>
-      </c>
-      <c r="H119">
-        <v>0</v>
-      </c>
-      <c r="I119">
-        <v>0</v>
-      </c>
-      <c r="J119">
-        <v>0</v>
-      </c>
-      <c r="K119">
-        <v>0</v>
-      </c>
-      <c r="L119">
-        <v>0</v>
-      </c>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N119">
-        <v>0</v>
-      </c>
-      <c r="O119">
-        <v>0</v>
-      </c>
-      <c r="P119">
-        <v>0</v>
-      </c>
-      <c r="Q119">
-        <v>0</v>
-      </c>
-      <c r="R119">
-        <v>0</v>
-      </c>
-      <c r="S119">
-        <v>0</v>
-      </c>
-      <c r="T119">
-        <v>0</v>
-      </c>
-      <c r="U119">
-        <v>0</v>
-      </c>
-      <c r="V119">
-        <v>0</v>
-      </c>
-      <c r="W119">
-        <v>0</v>
-      </c>
-      <c r="X119">
-        <v>0</v>
-      </c>
-      <c r="Y119">
-        <v>0</v>
-      </c>
-      <c r="Z119">
-        <v>0</v>
-      </c>
-      <c r="AA119">
-        <v>0</v>
-      </c>
-      <c r="AB119">
-        <v>0</v>
-      </c>
-      <c r="AC119">
-        <v>0</v>
-      </c>
-      <c r="AD119">
-        <v>0</v>
-      </c>
-      <c r="AE119">
-        <v>0</v>
-      </c>
-      <c r="AF119">
-        <v>0</v>
-      </c>
-      <c r="AG119">
-        <v>0</v>
-      </c>
-      <c r="AH119" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI119" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ119">
-        <v>0</v>
-      </c>
-      <c r="AK119">
-        <v>0</v>
-      </c>
-      <c r="AL119">
-        <v>0</v>
-      </c>
-      <c r="AM119">
-        <v>-1</v>
-      </c>
-      <c r="AN119">
-        <v>-1</v>
-      </c>
-      <c r="AO119">
-        <v>-1</v>
-      </c>
-      <c r="AP119">
-        <v>-1</v>
-      </c>
-      <c r="AQ119">
-        <v>0</v>
-      </c>
-      <c r="AR119">
-        <v>0</v>
-      </c>
-      <c r="AS119">
-        <v>0</v>
-      </c>
-      <c r="AT119">
-        <v>0</v>
-      </c>
-      <c r="AU119" t="inlineStr">
-        <is>
-          <t>2026-08-07 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Chile Primera B</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>Deportes Santa Cruz</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>Puerto Montt</t>
-        </is>
-      </c>
-      <c r="G120">
-        <v>0</v>
-      </c>
-      <c r="H120">
-        <v>0</v>
-      </c>
-      <c r="I120">
-        <v>0</v>
-      </c>
-      <c r="J120">
-        <v>0</v>
-      </c>
-      <c r="K120">
-        <v>0</v>
-      </c>
-      <c r="L120">
-        <v>0</v>
-      </c>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N120">
-        <v>0</v>
-      </c>
-      <c r="O120">
-        <v>0</v>
-      </c>
-      <c r="P120">
-        <v>0</v>
-      </c>
-      <c r="Q120">
-        <v>0</v>
-      </c>
-      <c r="R120">
-        <v>0</v>
-      </c>
-      <c r="S120">
-        <v>0</v>
-      </c>
-      <c r="T120">
-        <v>0</v>
-      </c>
-      <c r="U120">
-        <v>0</v>
-      </c>
-      <c r="V120">
-        <v>0</v>
-      </c>
-      <c r="W120">
-        <v>0</v>
-      </c>
-      <c r="X120">
-        <v>0</v>
-      </c>
-      <c r="Y120">
-        <v>0</v>
-      </c>
-      <c r="Z120">
-        <v>0</v>
-      </c>
-      <c r="AA120">
-        <v>0</v>
-      </c>
-      <c r="AB120">
-        <v>0</v>
-      </c>
-      <c r="AC120">
-        <v>0</v>
-      </c>
-      <c r="AD120">
-        <v>0</v>
-      </c>
-      <c r="AE120">
-        <v>0</v>
-      </c>
-      <c r="AF120">
-        <v>0</v>
-      </c>
-      <c r="AG120">
-        <v>0</v>
-      </c>
-      <c r="AH120" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI120" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ120">
-        <v>0</v>
-      </c>
-      <c r="AK120">
-        <v>0</v>
-      </c>
-      <c r="AL120">
-        <v>0</v>
-      </c>
-      <c r="AM120">
-        <v>-1</v>
-      </c>
-      <c r="AN120">
-        <v>-1</v>
-      </c>
-      <c r="AO120">
-        <v>-1</v>
-      </c>
-      <c r="AP120">
-        <v>-1</v>
-      </c>
-      <c r="AQ120">
-        <v>0</v>
-      </c>
-      <c r="AR120">
-        <v>0</v>
-      </c>
-      <c r="AS120">
-        <v>0</v>
-      </c>
-      <c r="AT120">
-        <v>0</v>
-      </c>
-      <c r="AU120" t="inlineStr">
-        <is>
-          <t>2026-08-07 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Chile Primera División</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>Universidad Católica</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>Cobresal</t>
-        </is>
-      </c>
-      <c r="G121">
-        <v>0</v>
-      </c>
-      <c r="H121">
-        <v>0</v>
-      </c>
-      <c r="I121">
-        <v>0</v>
-      </c>
-      <c r="J121">
-        <v>0</v>
-      </c>
-      <c r="K121">
-        <v>0</v>
-      </c>
-      <c r="L121">
-        <v>0</v>
-      </c>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N121">
-        <v>1.25</v>
-      </c>
-      <c r="O121">
-        <v>5.25</v>
-      </c>
-      <c r="P121">
-        <v>8.949999999999999</v>
-      </c>
-      <c r="Q121">
-        <v>1.69</v>
-      </c>
-      <c r="R121">
-        <v>2.66</v>
-      </c>
-      <c r="S121">
-        <v>1.2</v>
-      </c>
-      <c r="T121">
-        <v>4</v>
-      </c>
-      <c r="U121">
-        <v>2.14</v>
-      </c>
-      <c r="V121">
-        <v>1.67</v>
-      </c>
-      <c r="W121">
-        <v>1.17</v>
-      </c>
-      <c r="X121">
-        <v>1.03</v>
-      </c>
-      <c r="Y121">
-        <v>1.14</v>
-      </c>
-      <c r="Z121">
-        <v>5.5</v>
-      </c>
-      <c r="AA121">
-        <v>1.47</v>
-      </c>
-      <c r="AB121">
-        <v>2.56</v>
-      </c>
-      <c r="AC121">
-        <v>2.2</v>
-      </c>
-      <c r="AD121">
-        <v>1.6</v>
-      </c>
-      <c r="AE121">
-        <v>1.23</v>
-      </c>
-      <c r="AF121">
-        <v>1.75</v>
-      </c>
-      <c r="AG121">
-        <v>1.97</v>
-      </c>
-      <c r="AH121" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI121" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ121">
-        <v>1.1</v>
-      </c>
-      <c r="AK121">
-        <v>3.6</v>
-      </c>
-      <c r="AL121">
-        <v>0</v>
-      </c>
-      <c r="AM121">
-        <v>-1</v>
-      </c>
-      <c r="AN121">
-        <v>-1</v>
-      </c>
-      <c r="AO121">
-        <v>-1</v>
-      </c>
-      <c r="AP121">
-        <v>-1</v>
-      </c>
-      <c r="AQ121">
-        <v>0</v>
-      </c>
-      <c r="AR121">
-        <v>0</v>
-      </c>
-      <c r="AS121">
-        <v>0</v>
-      </c>
-      <c r="AT121">
-        <v>0</v>
-      </c>
-      <c r="AU121" t="inlineStr">
         <is>
           <t>2026-08-07 21:30:00</t>
         </is>

--- a/jogos_2026-08-07.xlsx
+++ b/jogos_2026-08-07.xlsx
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,64 +12045,64 @@
         </is>
       </c>
       <c r="N72">
-        <v>2.3</v>
+        <v>2.07</v>
       </c>
       <c r="O72">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P72">
-        <v>2.93</v>
+        <v>3.24</v>
       </c>
       <c r="Q72">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="R72">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S72">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="T72">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="U72">
-        <v>2.74</v>
+        <v>2.56</v>
       </c>
       <c r="V72">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="W72">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X72">
         <v>1.05</v>
       </c>
       <c r="Y72">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="Z72">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="AA72">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AB72">
-        <v>1.8</v>
+        <v>1.96</v>
       </c>
       <c r="AC72">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="AD72">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AE72">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF72">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AG72">
-        <v>2.05</v>
+        <v>2.18</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AK72">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="O73">
-        <v>3.45</v>
+        <v>4.6</v>
       </c>
       <c r="P73">
-        <v>3.29</v>
+        <v>7.5</v>
       </c>
       <c r="Q73">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="R73">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S73">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T73">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="U73">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V73">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W73">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X73">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y73">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z73">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA73">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AB73">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC73">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD73">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE73">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF73">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG73">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK73">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
-        <v>2.07</v>
+        <v>2.3</v>
       </c>
       <c r="O74">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P74">
-        <v>3.24</v>
+        <v>2.93</v>
       </c>
       <c r="Q74">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="R74">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S74">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="T74">
-        <v>3.1</v>
+        <v>2.74</v>
       </c>
       <c r="U74">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="V74">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="W74">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X74">
         <v>1.05</v>
       </c>
       <c r="Y74">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="Z74">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="AA74">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AB74">
-        <v>1.96</v>
+        <v>1.8</v>
       </c>
       <c r="AC74">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="AD74">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AE74">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF74">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AG74">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AK74">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="O75">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="P75">
-        <v>7.5</v>
+        <v>6.17</v>
       </c>
       <c r="Q75">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="R75">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S75">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T75">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U75">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="V75">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W75">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X75">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y75">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z75">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA75">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB75">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC75">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD75">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE75">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF75">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG75">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK75">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
-        <v>1.41</v>
+        <v>2</v>
       </c>
       <c r="O76">
-        <v>4.5</v>
+        <v>3.45</v>
       </c>
       <c r="P76">
-        <v>6.17</v>
+        <v>3.29</v>
       </c>
       <c r="Q76">
-        <v>1.74</v>
+        <v>2.33</v>
       </c>
       <c r="R76">
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="S76">
-        <v>1.21</v>
+        <v>1.31</v>
       </c>
       <c r="T76">
-        <v>3.58</v>
+        <v>3.02</v>
       </c>
       <c r="U76">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="V76">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="W76">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="X76">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y76">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="Z76">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="AA76">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AB76">
-        <v>2.55</v>
+        <v>2</v>
       </c>
       <c r="AC76">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="AD76">
-        <v>1.59</v>
+        <v>1.4</v>
       </c>
       <c r="AE76">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AF76">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AG76">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AK76">
-        <v>3.4</v>
+        <v>1.7</v>
       </c>
       <c r="AL76">
         <v>0</v>

--- a/jogos_2026-08-07.xlsx
+++ b/jogos_2026-08-07.xlsx
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,64 +12045,64 @@
         </is>
       </c>
       <c r="N72">
-        <v>2.07</v>
+        <v>1.3</v>
       </c>
       <c r="O72">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="P72">
-        <v>3.24</v>
+        <v>7.5</v>
       </c>
       <c r="Q72">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="R72">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S72">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T72">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U72">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="V72">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W72">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X72">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y72">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z72">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA72">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB72">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AC72">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD72">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE72">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF72">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG72">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK72">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
+        <v>2.3</v>
+      </c>
+      <c r="O73">
+        <v>3.25</v>
+      </c>
+      <c r="P73">
+        <v>2.93</v>
+      </c>
+      <c r="Q73">
+        <v>2.8</v>
+      </c>
+      <c r="R73">
+        <v>2.15</v>
+      </c>
+      <c r="S73">
+        <v>1.37</v>
+      </c>
+      <c r="T73">
+        <v>2.74</v>
+      </c>
+      <c r="U73">
+        <v>2.74</v>
+      </c>
+      <c r="V73">
+        <v>1.37</v>
+      </c>
+      <c r="W73">
+        <v>1.04</v>
+      </c>
+      <c r="X73">
+        <v>1.05</v>
+      </c>
+      <c r="Y73">
+        <v>1.29</v>
+      </c>
+      <c r="Z73">
+        <v>3.3</v>
+      </c>
+      <c r="AA73">
+        <v>1.91</v>
+      </c>
+      <c r="AB73">
+        <v>1.8</v>
+      </c>
+      <c r="AC73">
+        <v>3.3</v>
+      </c>
+      <c r="AD73">
         <v>1.3</v>
       </c>
-      <c r="O73">
-        <v>4.6</v>
-      </c>
-      <c r="P73">
-        <v>7.5</v>
-      </c>
-      <c r="Q73">
-        <v>0</v>
-      </c>
-      <c r="R73">
-        <v>0</v>
-      </c>
-      <c r="S73">
-        <v>0</v>
-      </c>
-      <c r="T73">
-        <v>0</v>
-      </c>
-      <c r="U73">
-        <v>0</v>
-      </c>
-      <c r="V73">
-        <v>0</v>
-      </c>
-      <c r="W73">
-        <v>0</v>
-      </c>
-      <c r="X73">
-        <v>0</v>
-      </c>
-      <c r="Y73">
-        <v>0</v>
-      </c>
-      <c r="Z73">
-        <v>0</v>
-      </c>
-      <c r="AA73">
-        <v>0</v>
-      </c>
-      <c r="AB73">
-        <v>0</v>
-      </c>
-      <c r="AC73">
-        <v>0</v>
-      </c>
-      <c r="AD73">
-        <v>0</v>
-      </c>
       <c r="AE73">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF73">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG73">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK73">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,65 +12371,65 @@
         </is>
       </c>
       <c r="N74">
-        <v>2.3</v>
+        <v>1.41</v>
       </c>
       <c r="O74">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="P74">
-        <v>2.93</v>
+        <v>6.17</v>
       </c>
       <c r="Q74">
-        <v>2.8</v>
+        <v>1.74</v>
       </c>
       <c r="R74">
-        <v>2.15</v>
+        <v>2.7</v>
       </c>
       <c r="S74">
-        <v>1.37</v>
+        <v>1.21</v>
       </c>
       <c r="T74">
-        <v>2.74</v>
+        <v>3.58</v>
       </c>
       <c r="U74">
-        <v>2.74</v>
+        <v>1.98</v>
       </c>
       <c r="V74">
-        <v>1.37</v>
+        <v>1.64</v>
       </c>
       <c r="W74">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="X74">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y74">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="Z74">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="AA74">
+        <v>1.44</v>
+      </c>
+      <c r="AB74">
+        <v>2.55</v>
+      </c>
+      <c r="AC74">
+        <v>2.25</v>
+      </c>
+      <c r="AD74">
+        <v>1.59</v>
+      </c>
+      <c r="AE74">
+        <v>1.22</v>
+      </c>
+      <c r="AF74">
+        <v>1.75</v>
+      </c>
+      <c r="AG74">
         <v>1.91</v>
       </c>
-      <c r="AB74">
-        <v>1.8</v>
-      </c>
-      <c r="AC74">
-        <v>3.3</v>
-      </c>
-      <c r="AD74">
-        <v>1.3</v>
-      </c>
-      <c r="AE74">
-        <v>1.1</v>
-      </c>
-      <c r="AF74">
-        <v>1.7</v>
-      </c>
-      <c r="AG74">
-        <v>2.05</v>
-      </c>
       <c r="AH74" t="inlineStr">
         <is>
           <t>[]</t>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AK74">
-        <v>1.57</v>
+        <v>3.4</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,80 +12534,80 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.41</v>
+        <v>2.07</v>
       </c>
       <c r="O75">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="P75">
-        <v>6.17</v>
+        <v>3.24</v>
       </c>
       <c r="Q75">
-        <v>1.74</v>
+        <v>2.65</v>
       </c>
       <c r="R75">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="S75">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="T75">
-        <v>3.58</v>
+        <v>3.1</v>
       </c>
       <c r="U75">
-        <v>1.98</v>
+        <v>2.56</v>
       </c>
       <c r="V75">
-        <v>1.64</v>
+        <v>1.42</v>
       </c>
       <c r="W75">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="X75">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y75">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="Z75">
-        <v>5</v>
+        <v>3.75</v>
       </c>
       <c r="AA75">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="AB75">
-        <v>2.55</v>
+        <v>1.96</v>
       </c>
       <c r="AC75">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="AD75">
-        <v>1.59</v>
+        <v>1.38</v>
       </c>
       <c r="AE75">
+        <v>1.14</v>
+      </c>
+      <c r="AF75">
+        <v>1.62</v>
+      </c>
+      <c r="AG75">
+        <v>2.18</v>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ75">
         <v>1.22</v>
       </c>
-      <c r="AF75">
-        <v>1.75</v>
-      </c>
-      <c r="AG75">
-        <v>1.91</v>
-      </c>
-      <c r="AH75" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI75" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ75">
-        <v>1.15</v>
-      </c>
       <c r="AK75">
-        <v>3.4</v>
+        <v>1.62</v>
       </c>
       <c r="AL75">
         <v>0</v>

--- a/jogos_2026-08-07.xlsx
+++ b/jogos_2026-08-07.xlsx
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>3.84</v>
+        <v>3.5</v>
       </c>
       <c r="O2">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P2">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="Q2">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="R2">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S2">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T2">
-        <v>2.69</v>
+        <v>2.82</v>
       </c>
       <c r="U2">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="V2">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W2">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X2">
         <v>1.06</v>
       </c>
       <c r="Y2">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z2">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="AA2">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AB2">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AC2">
-        <v>3.7</v>
+        <v>3.44</v>
       </c>
       <c r="AD2">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE2">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF2">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG2">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="AK2">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -1776,16 +1776,16 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="O9">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P9">
-        <v>2.95</v>
+        <v>2.98</v>
       </c>
       <c r="Q9">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="R9">
         <v>2.03</v>
@@ -1803,19 +1803,19 @@
         <v>1.38</v>
       </c>
       <c r="W9">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X9">
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z9">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="AA9">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AB9">
         <v>1.8</v>
@@ -1827,13 +1827,13 @@
         <v>1.24</v>
       </c>
       <c r="AE9">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AF9">
         <v>1.74</v>
       </c>
       <c r="AG9">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AK9">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2926,10 +2926,10 @@
         <v>2.55</v>
       </c>
       <c r="Q16">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="R16">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="S16">
         <v>1.28</v>
@@ -2938,28 +2938,28 @@
         <v>3.18</v>
       </c>
       <c r="U16">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="V16">
         <v>1.48</v>
       </c>
       <c r="W16">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X16">
         <v>1.04</v>
       </c>
       <c r="Y16">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z16">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AA16">
         <v>1.67</v>
       </c>
       <c r="AB16">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="AC16">
         <v>2.63</v>
@@ -2968,7 +2968,7 @@
         <v>1.4</v>
       </c>
       <c r="AE16">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AF16">
         <v>1.57</v>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="AK16">
         <v>1.5</v>
@@ -3243,77 +3243,77 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="O18">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="P18">
-        <v>4.05</v>
+        <v>4.02</v>
       </c>
       <c r="Q18">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="R18">
         <v>2.3</v>
       </c>
       <c r="S18">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T18">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="U18">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="V18">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W18">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X18">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z18">
-        <v>3.8</v>
+        <v>3.88</v>
       </c>
       <c r="AA18">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AB18">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AC18">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="AD18">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AE18">
+        <v>1.12</v>
+      </c>
+      <c r="AF18">
+        <v>1.67</v>
+      </c>
+      <c r="AG18">
+        <v>2.05</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18">
         <v>1.14</v>
-      </c>
-      <c r="AF18">
-        <v>1.65</v>
-      </c>
-      <c r="AG18">
-        <v>2.08</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18">
-        <v>1.2</v>
       </c>
       <c r="AK18">
         <v>1.95</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="O27">
         <v>4.7</v>
       </c>
       <c r="P27">
-        <v>5.65</v>
+        <v>6.03</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -5045,55 +5045,55 @@
         <v>0</v>
       </c>
       <c r="Q29">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R29">
-        <v>2.05</v>
+        <v>1.88</v>
       </c>
       <c r="S29">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="T29">
-        <v>2.47</v>
+        <v>2.36</v>
       </c>
       <c r="U29">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="V29">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W29">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X29">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y29">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="Z29">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="AA29">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="AB29">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AC29">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="AD29">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AE29">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF29">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="AG29">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AK29">
         <v>1.47</v>
@@ -5205,22 +5205,22 @@
         <v>3.2</v>
       </c>
       <c r="P30">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="Q30">
         <v>3.04</v>
       </c>
       <c r="R30">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="S30">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T30">
         <v>2.95</v>
       </c>
       <c r="U30">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="V30">
         <v>1.42</v>
@@ -5232,19 +5232,19 @@
         <v>1.05</v>
       </c>
       <c r="Y30">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="Z30">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AA30">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AB30">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="AC30">
-        <v>2.83</v>
+        <v>2.95</v>
       </c>
       <c r="AD30">
         <v>1.3</v>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK30">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="O32">
-        <v>3.4</v>
+        <v>3.46</v>
       </c>
       <c r="P32">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="Q32">
-        <v>3.36</v>
+        <v>3.72</v>
       </c>
       <c r="R32">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="S32">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T32">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U32">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="V32">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="W32">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X32">
         <v>1.04</v>
       </c>
       <c r="Y32">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z32">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AA32">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AB32">
         <v>2.2</v>
       </c>
       <c r="AC32">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AD32">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AE32">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AF32">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AG32">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.22</v>
+        <v>1.66</v>
       </c>
       <c r="AK32">
         <v>1.33</v>
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="O36">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="P36">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q36">
         <v>3.3</v>
@@ -6192,49 +6192,49 @@
         <v>2.4</v>
       </c>
       <c r="S36">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="T36">
-        <v>3.28</v>
+        <v>3.45</v>
       </c>
       <c r="U36">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="V36">
         <v>1.53</v>
       </c>
       <c r="W36">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X36">
         <v>1.03</v>
       </c>
       <c r="Y36">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z36">
-        <v>4.4</v>
+        <v>4.25</v>
       </c>
       <c r="AA36">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AB36">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AC36">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="AD36">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AE36">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AF36">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AG36">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AK36">
         <v>1.4</v>
@@ -6340,49 +6340,49 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="O37">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P37">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="Q37">
         <v>2.8</v>
       </c>
       <c r="R37">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="S37">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="T37">
         <v>2.65</v>
       </c>
       <c r="U37">
-        <v>3.04</v>
+        <v>2.9</v>
       </c>
       <c r="V37">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W37">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X37">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y37">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="Z37">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="AA37">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="AB37">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AC37">
         <v>3.95</v>
@@ -6391,7 +6391,7 @@
         <v>1.25</v>
       </c>
       <c r="AE37">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF37">
         <v>1.85</v>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK37">
         <v>1.68</v>
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK39">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O41">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="P41">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="Q41">
-        <v>1.84</v>
+        <v>3.72</v>
       </c>
       <c r="R41">
-        <v>2.7</v>
+        <v>2.36</v>
       </c>
       <c r="S41">
         <v>1.2</v>
       </c>
       <c r="T41">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="U41">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="V41">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="W41">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="X41">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y41">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Z41">
-        <v>5.75</v>
+        <v>5.55</v>
       </c>
       <c r="AA41">
         <v>1.4</v>
       </c>
       <c r="AB41">
-        <v>2.74</v>
+        <v>2.56</v>
       </c>
       <c r="AC41">
-        <v>1.99</v>
+        <v>2.09</v>
       </c>
       <c r="AD41">
-        <v>1.76</v>
+        <v>1.66</v>
       </c>
       <c r="AE41">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AF41">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="AG41">
-        <v>2.36</v>
+        <v>2.64</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK41">
-        <v>2.63</v>
+        <v>1.29</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7155,80 +7155,80 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="O42">
-        <v>4.3</v>
+        <v>4.75</v>
       </c>
       <c r="P42">
         <v>9</v>
       </c>
       <c r="Q42">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="R42">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="S42">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T42">
-        <v>2.73</v>
+        <v>3.13</v>
       </c>
       <c r="U42">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="V42">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W42">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="X42">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="Z42">
+        <v>3.58</v>
+      </c>
+      <c r="AA42">
+        <v>1.73</v>
+      </c>
+      <c r="AB42">
+        <v>2</v>
+      </c>
+      <c r="AC42">
+        <v>2.83</v>
+      </c>
+      <c r="AD42">
+        <v>1.33</v>
+      </c>
+      <c r="AE42">
+        <v>1.1</v>
+      </c>
+      <c r="AF42">
+        <v>2.15</v>
+      </c>
+      <c r="AG42">
+        <v>1.6</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ42">
+        <v>1.18</v>
+      </c>
+      <c r="AK42">
         <v>3.2</v>
-      </c>
-      <c r="AA42">
-        <v>1.95</v>
-      </c>
-      <c r="AB42">
-        <v>1.8</v>
-      </c>
-      <c r="AC42">
-        <v>3.39</v>
-      </c>
-      <c r="AD42">
-        <v>1.25</v>
-      </c>
-      <c r="AE42">
-        <v>1.06</v>
-      </c>
-      <c r="AF42">
-        <v>2.25</v>
-      </c>
-      <c r="AG42">
-        <v>1.54</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ42">
-        <v>1.06</v>
-      </c>
-      <c r="AK42">
-        <v>3.08</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="O45">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P45">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="Q45">
         <v>3.06</v>
       </c>
       <c r="R45">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="S45">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T45">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="U45">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="V45">
         <v>1.57</v>
       </c>
       <c r="W45">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X45">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y45">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z45">
-        <v>4.35</v>
+        <v>4.6</v>
       </c>
       <c r="AA45">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AB45">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="AC45">
-        <v>2.42</v>
+        <v>2.51</v>
       </c>
       <c r="AD45">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="AE45">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF45">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AG45">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK45">
         <v>1.53</v>
@@ -7973,61 +7973,61 @@
         <v>1.44</v>
       </c>
       <c r="O47">
-        <v>4.4</v>
+        <v>4.85</v>
       </c>
       <c r="P47">
-        <v>5.25</v>
+        <v>5.78</v>
       </c>
       <c r="Q47">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="R47">
-        <v>2.77</v>
+        <v>2.42</v>
       </c>
       <c r="S47">
         <v>1.22</v>
       </c>
       <c r="T47">
-        <v>3.88</v>
+        <v>4</v>
       </c>
       <c r="U47">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="V47">
         <v>1.7</v>
       </c>
       <c r="W47">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X47">
         <v>1.02</v>
       </c>
       <c r="Y47">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="Z47">
-        <v>5.5</v>
+        <v>5.55</v>
       </c>
       <c r="AA47">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AB47">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="AC47">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="AD47">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AE47">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AF47">
         <v>1.57</v>
       </c>
       <c r="AG47">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AK47">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,25 +8133,25 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="O48">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P48">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="Q48">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="R48">
-        <v>2.23</v>
+        <v>2.43</v>
       </c>
       <c r="S48">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T48">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="U48">
         <v>2.37</v>
@@ -8166,31 +8166,31 @@
         <v>1.03</v>
       </c>
       <c r="Y48">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z48">
-        <v>4.2</v>
+        <v>4.64</v>
       </c>
       <c r="AA48">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AB48">
         <v>2.28</v>
       </c>
       <c r="AC48">
-        <v>2.41</v>
+        <v>2.55</v>
       </c>
       <c r="AD48">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="AE48">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF48">
         <v>1.5</v>
       </c>
       <c r="AG48">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AK48">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8296,7 +8296,7 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="O49">
         <v>3.8</v>
@@ -8305,10 +8305,10 @@
         <v>2.65</v>
       </c>
       <c r="Q49">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="R49">
-        <v>2.53</v>
+        <v>2.4</v>
       </c>
       <c r="S49">
         <v>1.2</v>
@@ -8317,19 +8317,19 @@
         <v>4</v>
       </c>
       <c r="U49">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="V49">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W49">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X49">
         <v>1.03</v>
       </c>
       <c r="Y49">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="Z49">
         <v>5.35</v>
@@ -8341,35 +8341,35 @@
         <v>2.56</v>
       </c>
       <c r="AC49">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AD49">
+        <v>1.65</v>
+      </c>
+      <c r="AE49">
+        <v>1.26</v>
+      </c>
+      <c r="AF49">
+        <v>1.43</v>
+      </c>
+      <c r="AG49">
+        <v>2.68</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ49">
+        <v>1.22</v>
+      </c>
+      <c r="AK49">
         <v>1.62</v>
-      </c>
-      <c r="AE49">
-        <v>1.25</v>
-      </c>
-      <c r="AF49">
-        <v>1.44</v>
-      </c>
-      <c r="AG49">
-        <v>2.63</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ49">
-        <v>1.25</v>
-      </c>
-      <c r="AK49">
-        <v>1.6</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8459,10 +8459,10 @@
         </is>
       </c>
       <c r="N50">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="O50">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="P50">
         <v>1.65</v>
@@ -8471,31 +8471,31 @@
         <v>4.2</v>
       </c>
       <c r="R50">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="S50">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T50">
-        <v>3.44</v>
+        <v>3.6</v>
       </c>
       <c r="U50">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="V50">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="W50">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X50">
         <v>1.03</v>
       </c>
       <c r="Y50">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="Z50">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AA50">
         <v>1.53</v>
@@ -8507,13 +8507,13 @@
         <v>2.3</v>
       </c>
       <c r="AD50">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AE50">
         <v>1.22</v>
       </c>
       <c r="AF50">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AG50">
         <v>2.25</v>
@@ -8532,7 +8532,7 @@
         <v>1.25</v>
       </c>
       <c r="AK50">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8625,28 +8625,28 @@
         <v>2.25</v>
       </c>
       <c r="O51">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P51">
         <v>2.7</v>
       </c>
       <c r="Q51">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="R51">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S51">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T51">
         <v>3.8</v>
       </c>
       <c r="U51">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="V51">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W51">
         <v>1.11</v>
@@ -8655,19 +8655,19 @@
         <v>1.03</v>
       </c>
       <c r="Y51">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="Z51">
-        <v>4.8</v>
+        <v>4.86</v>
       </c>
       <c r="AA51">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AB51">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AC51">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="AD51">
         <v>1.53</v>
@@ -8788,28 +8788,28 @@
         <v>1.37</v>
       </c>
       <c r="O52">
-        <v>4.75</v>
+        <v>4.85</v>
       </c>
       <c r="P52">
-        <v>6.74</v>
+        <v>6.05</v>
       </c>
       <c r="Q52">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="R52">
-        <v>2.53</v>
+        <v>2.63</v>
       </c>
       <c r="S52">
         <v>1.2</v>
       </c>
       <c r="T52">
-        <v>3.72</v>
+        <v>4</v>
       </c>
       <c r="U52">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="V52">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="W52">
         <v>1.13</v>
@@ -8836,10 +8836,10 @@
         <v>1.67</v>
       </c>
       <c r="AE52">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AF52">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AG52">
         <v>2.3</v>
@@ -8858,7 +8858,7 @@
         <v>1.1</v>
       </c>
       <c r="AK52">
-        <v>2.72</v>
+        <v>2.63</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8948,13 +8948,13 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="O53">
         <v>3.48</v>
       </c>
       <c r="P53">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="Q53">
         <v>2.8</v>
@@ -8963,7 +8963,7 @@
         <v>2.5</v>
       </c>
       <c r="S53">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="T53">
         <v>3.34</v>
@@ -8978,19 +8978,19 @@
         <v>1.13</v>
       </c>
       <c r="X53">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y53">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z53">
-        <v>4.9</v>
+        <v>5.37</v>
       </c>
       <c r="AA53">
         <v>1.49</v>
       </c>
       <c r="AB53">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="AC53">
         <v>2.14</v>
@@ -8999,13 +8999,13 @@
         <v>1.63</v>
       </c>
       <c r="AE53">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AF53">
         <v>1.4</v>
       </c>
       <c r="AG53">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.44</v>
+        <v>1.2</v>
       </c>
       <c r="AK53">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9111,31 +9111,31 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="O54">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="P54">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="Q54">
-        <v>2.66</v>
+        <v>2.43</v>
       </c>
       <c r="R54">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="S54">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="T54">
-        <v>3.02</v>
+        <v>2.96</v>
       </c>
       <c r="U54">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="V54">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W54">
         <v>1.09</v>
@@ -9144,31 +9144,31 @@
         <v>1.04</v>
       </c>
       <c r="Y54">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z54">
-        <v>3.96</v>
+        <v>3.95</v>
       </c>
       <c r="AA54">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AB54">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="AC54">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="AD54">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE54">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF54">
         <v>1.62</v>
       </c>
       <c r="AG54">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK54">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9274,7 +9274,7 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="O55">
         <v>3.2</v>
@@ -9283,28 +9283,28 @@
         <v>2.7</v>
       </c>
       <c r="Q55">
-        <v>2.9</v>
+        <v>3.02</v>
       </c>
       <c r="R55">
-        <v>2.2</v>
+        <v>2.03</v>
       </c>
       <c r="S55">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T55">
         <v>2.7</v>
       </c>
       <c r="U55">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
       <c r="V55">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W55">
         <v>1.04</v>
       </c>
       <c r="X55">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y55">
         <v>1.29</v>
@@ -9313,22 +9313,22 @@
         <v>3.4</v>
       </c>
       <c r="AA55">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AB55">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AC55">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="AD55">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE55">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF55">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AG55">
         <v>2.05</v>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AK55">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9446,49 +9446,49 @@
         <v>4.65</v>
       </c>
       <c r="Q56">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="R56">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="S56">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T56">
         <v>3.5</v>
       </c>
       <c r="U56">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="V56">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W56">
         <v>1.14</v>
       </c>
       <c r="X56">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y56">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Z56">
-        <v>4.53</v>
+        <v>4.33</v>
       </c>
       <c r="AA56">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AB56">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="AC56">
         <v>2.47</v>
       </c>
       <c r="AD56">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="AE56">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AF56">
         <v>1.62</v>
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O57">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P57">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q57">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="R57">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S57">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T57">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U57">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V57">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W57">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X57">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y57">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z57">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA57">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB57">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC57">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD57">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE57">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF57">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG57">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK57">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="O58">
-        <v>3.6</v>
+        <v>3.52</v>
       </c>
       <c r="P58">
-        <v>2.7</v>
+        <v>2.91</v>
       </c>
       <c r="Q58">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="R58">
-        <v>2.21</v>
+        <v>2.4</v>
       </c>
       <c r="S58">
         <v>1.3</v>
       </c>
       <c r="T58">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="U58">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="V58">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="W58">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X58">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y58">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z58">
         <v>4.33</v>
       </c>
       <c r="AA58">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AB58">
         <v>2.25</v>
       </c>
       <c r="AC58">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="AD58">
         <v>1.51</v>
       </c>
       <c r="AE58">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AF58">
         <v>1.5</v>
       </c>
       <c r="AG58">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="AK58">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -10095,28 +10095,28 @@
         <v>4.05</v>
       </c>
       <c r="P60">
-        <v>4.89</v>
+        <v>4.5</v>
       </c>
       <c r="Q60">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="R60">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="S60">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T60">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="U60">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="V60">
         <v>1.61</v>
       </c>
       <c r="W60">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X60">
         <v>1.02</v>
@@ -10128,16 +10128,16 @@
         <v>4.8</v>
       </c>
       <c r="AA60">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AB60">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="AC60">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="AD60">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AE60">
         <v>1.19</v>
@@ -10146,7 +10146,7 @@
         <v>1.62</v>
       </c>
       <c r="AG60">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10162,7 +10162,7 @@
         <v>1.12</v>
       </c>
       <c r="AK60">
-        <v>2.33</v>
+        <v>2.63</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>2.09</v>
       </c>
       <c r="O63">
-        <v>3</v>
+        <v>3.29</v>
       </c>
       <c r="P63">
-        <v>3.34</v>
+        <v>3.26</v>
       </c>
       <c r="Q63">
         <v>0</v>
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="N67">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O67">
-        <v>3</v>
+        <v>3.07</v>
       </c>
       <c r="P67">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="Q67">
         <v>0</v>
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="O69">
         <v>3.1</v>
       </c>
       <c r="P69">
-        <v>3.59</v>
+        <v>3.6</v>
       </c>
       <c r="Q69">
         <v>0</v>
@@ -11719,7 +11719,7 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.65</v>
+        <v>2.57</v>
       </c>
       <c r="O70">
         <v>3.14</v>
@@ -12045,13 +12045,13 @@
         </is>
       </c>
       <c r="N72">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="O72">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="P72">
-        <v>7.5</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="Q72">
         <v>0</v>
@@ -12084,10 +12084,10 @@
         <v>0</v>
       </c>
       <c r="AA72">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB72">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC72">
         <v>0</v>
@@ -12211,52 +12211,52 @@
         <v>2.3</v>
       </c>
       <c r="O73">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P73">
         <v>2.93</v>
       </c>
       <c r="Q73">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="R73">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="S73">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="T73">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="U73">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="V73">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W73">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X73">
         <v>1.05</v>
       </c>
       <c r="Y73">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z73">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="AA73">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AB73">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AC73">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AD73">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE73">
         <v>1.1</v>
@@ -12265,7 +12265,7 @@
         <v>1.7</v>
       </c>
       <c r="AG73">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK73">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12380,55 +12380,55 @@
         <v>6.17</v>
       </c>
       <c r="Q74">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="R74">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="S74">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T74">
         <v>3.58</v>
       </c>
       <c r="U74">
-        <v>1.98</v>
+        <v>2.18</v>
       </c>
       <c r="V74">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="W74">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X74">
         <v>1.02</v>
       </c>
       <c r="Y74">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="Z74">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="AA74">
         <v>1.44</v>
       </c>
       <c r="AB74">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="AC74">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AD74">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AE74">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF74">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AG74">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AK74">
-        <v>3.4</v>
+        <v>2.63</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12534,7 +12534,7 @@
         </is>
       </c>
       <c r="N75">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="O75">
         <v>3.4</v>
@@ -12543,49 +12543,49 @@
         <v>3.24</v>
       </c>
       <c r="Q75">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="R75">
         <v>2.2</v>
       </c>
       <c r="S75">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T75">
         <v>3.1</v>
       </c>
       <c r="U75">
-        <v>2.56</v>
+        <v>2.32</v>
       </c>
       <c r="V75">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W75">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X75">
         <v>1.05</v>
       </c>
       <c r="Y75">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z75">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AA75">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AB75">
-        <v>1.96</v>
+        <v>2.01</v>
       </c>
       <c r="AC75">
-        <v>2.6</v>
+        <v>2.96</v>
       </c>
       <c r="AD75">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AE75">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF75">
         <v>1.62</v>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK75">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12703,13 +12703,13 @@
         <v>3.45</v>
       </c>
       <c r="P76">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="Q76">
         <v>2.33</v>
       </c>
       <c r="R76">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="S76">
         <v>1.31</v>
@@ -12718,43 +12718,43 @@
         <v>3.02</v>
       </c>
       <c r="U76">
-        <v>2.2</v>
+        <v>2.59</v>
       </c>
       <c r="V76">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W76">
         <v>1.07</v>
       </c>
       <c r="X76">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y76">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z76">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AA76">
         <v>1.56</v>
       </c>
       <c r="AB76">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AC76">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AD76">
         <v>1.4</v>
       </c>
       <c r="AE76">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF76">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="AG76">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK76">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12863,10 +12863,10 @@
         <v>1.25</v>
       </c>
       <c r="O77">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="P77">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q77">
         <v>0</v>
@@ -13349,31 +13349,31 @@
         </is>
       </c>
       <c r="N80">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="O80">
-        <v>3.4</v>
+        <v>2.95</v>
       </c>
       <c r="P80">
         <v>2.2</v>
       </c>
       <c r="Q80">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="R80">
-        <v>1.94</v>
+        <v>2.25</v>
       </c>
       <c r="S80">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="T80">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="U80">
         <v>2.79</v>
       </c>
       <c r="V80">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="W80">
         <v>1.06</v>
@@ -13388,25 +13388,25 @@
         <v>3.4</v>
       </c>
       <c r="AA80">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AB80">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AC80">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AD80">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE80">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AF80">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AG80">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13422,7 +13422,7 @@
         <v>1.35</v>
       </c>
       <c r="AK80">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13838,19 +13838,19 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="O83">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P83">
-        <v>4.1</v>
+        <v>4.73</v>
       </c>
       <c r="Q83">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="R83">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="S83">
         <v>1.42</v>
@@ -13871,25 +13871,25 @@
         <v>1.02</v>
       </c>
       <c r="Y83">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="Z83">
         <v>3.1</v>
       </c>
       <c r="AA83">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB83">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AC83">
-        <v>3.63</v>
+        <v>3.75</v>
       </c>
       <c r="AD83">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE83">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF83">
         <v>1.85</v>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK83">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14662,10 +14662,10 @@
         <v>9</v>
       </c>
       <c r="Q88">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="R88">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S88">
         <v>1.33</v>
@@ -14674,10 +14674,10 @@
         <v>3.13</v>
       </c>
       <c r="U88">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="V88">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="W88">
         <v>1.1</v>
@@ -14686,19 +14686,19 @@
         <v>1.02</v>
       </c>
       <c r="Y88">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z88">
-        <v>3.95</v>
+        <v>3.72</v>
       </c>
       <c r="AA88">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AB88">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="AC88">
-        <v>3.06</v>
+        <v>2.95</v>
       </c>
       <c r="AD88">
         <v>1.33</v>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="AK88">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14825,34 +14825,34 @@
         <v>0</v>
       </c>
       <c r="Q89">
-        <v>4.62</v>
+        <v>4.67</v>
       </c>
       <c r="R89">
         <v>2.24</v>
       </c>
       <c r="S89">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T89">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="U89">
-        <v>2.24</v>
+        <v>2.29</v>
       </c>
       <c r="V89">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="W89">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X89">
         <v>1.04</v>
       </c>
       <c r="Y89">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z89">
-        <v>4.85</v>
+        <v>4</v>
       </c>
       <c r="AA89">
         <v>1.7</v>
@@ -14861,19 +14861,19 @@
         <v>2.1</v>
       </c>
       <c r="AC89">
-        <v>2.27</v>
+        <v>2.75</v>
       </c>
       <c r="AD89">
         <v>1.42</v>
       </c>
       <c r="AE89">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AF89">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="AG89">
-        <v>2.42</v>
+        <v>2.1</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
+        <v>1.19</v>
+      </c>
+      <c r="AK89">
         <v>1.2</v>
-      </c>
-      <c r="AK89">
-        <v>1.16</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -15480,43 +15480,43 @@
         <v>3.67</v>
       </c>
       <c r="R93">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="S93">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T93">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="U93">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="V93">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W93">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X93">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y93">
         <v>1.19</v>
       </c>
       <c r="Z93">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AA93">
         <v>1.8</v>
       </c>
       <c r="AB93">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AC93">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="AD93">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AE93">
         <v>1.13</v>
@@ -15538,7 +15538,7 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AK93">
         <v>1.36</v>

--- a/jogos_2026-08-07.xlsx
+++ b/jogos_2026-08-07.xlsx
@@ -804,31 +804,31 @@
         <v>3.4</v>
       </c>
       <c r="P3">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q3">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R3">
         <v>2.2</v>
       </c>
       <c r="S3">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T3">
-        <v>2.91</v>
+        <v>3.1</v>
       </c>
       <c r="U3">
         <v>2.62</v>
       </c>
       <c r="V3">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W3">
         <v>1.07</v>
       </c>
       <c r="X3">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y3">
         <v>1.23</v>
@@ -837,22 +837,22 @@
         <v>3.96</v>
       </c>
       <c r="AA3">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB3">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AC3">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="AD3">
         <v>1.36</v>
       </c>
       <c r="AE3">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF3">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG3">
         <v>2.15</v>
@@ -871,7 +871,7 @@
         <v>1.24</v>
       </c>
       <c r="AK3">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -973,37 +973,37 @@
         <v>2.42</v>
       </c>
       <c r="R4">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S4">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T4">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="U4">
         <v>3</v>
       </c>
       <c r="V4">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W4">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X4">
         <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="Z4">
-        <v>3.01</v>
+        <v>2.92</v>
       </c>
       <c r="AA4">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="AB4">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AC4">
         <v>3.58</v>
@@ -1012,13 +1012,13 @@
         <v>1.21</v>
       </c>
       <c r="AE4">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF4">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AG4">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AK4">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1130,58 +1130,58 @@
         <v>3.5</v>
       </c>
       <c r="P5">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="Q5">
-        <v>4.49</v>
+        <v>4.2</v>
       </c>
       <c r="R5">
         <v>2.25</v>
       </c>
       <c r="S5">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T5">
-        <v>3.02</v>
+        <v>3.2</v>
       </c>
       <c r="U5">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="V5">
         <v>1.43</v>
       </c>
       <c r="W5">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X5">
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z5">
         <v>3.83</v>
       </c>
       <c r="AA5">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AB5">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AC5">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AD5">
         <v>1.34</v>
       </c>
       <c r="AE5">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF5">
         <v>1.7</v>
       </c>
       <c r="AG5">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.29</v>
+        <v>1.9</v>
       </c>
       <c r="AK5">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,19 +1287,19 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="O6">
-        <v>4.05</v>
+        <v>3.95</v>
       </c>
       <c r="P6">
-        <v>5.53</v>
+        <v>5</v>
       </c>
       <c r="Q6">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R6">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="S6">
         <v>1.35</v>
@@ -1311,13 +1311,13 @@
         <v>2.46</v>
       </c>
       <c r="V6">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W6">
         <v>1.07</v>
       </c>
       <c r="X6">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y6">
         <v>1.19</v>
@@ -1326,19 +1326,19 @@
         <v>3.82</v>
       </c>
       <c r="AA6">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AB6">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AC6">
         <v>2.93</v>
       </c>
       <c r="AD6">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE6">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF6">
         <v>1.79</v>
@@ -1450,46 +1450,46 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="O7">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P7">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="Q7">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="R7">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="S7">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T7">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="U7">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="V7">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W7">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X7">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y7">
         <v>1.27</v>
       </c>
       <c r="Z7">
-        <v>3.4</v>
+        <v>3.14</v>
       </c>
       <c r="AA7">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AB7">
         <v>1.8</v>
@@ -1498,10 +1498,10 @@
         <v>3.36</v>
       </c>
       <c r="AD7">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AE7">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF7">
         <v>1.75</v>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.19</v>
+        <v>1.88</v>
       </c>
       <c r="AK7">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1622,55 +1622,55 @@
         <v>9.050000000000001</v>
       </c>
       <c r="Q8">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="R8">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="S8">
         <v>1.25</v>
       </c>
       <c r="T8">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U8">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="V8">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W8">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X8">
         <v>1.03</v>
       </c>
       <c r="Y8">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z8">
         <v>4.4</v>
       </c>
       <c r="AA8">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AB8">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AC8">
         <v>2.68</v>
       </c>
       <c r="AD8">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AE8">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF8">
         <v>1.91</v>
       </c>
       <c r="AG8">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>1.08</v>
       </c>
       <c r="AK8">
-        <v>3.5</v>
+        <v>3.01</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1948,22 +1948,22 @@
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="R10">
-        <v>2.75</v>
+        <v>2.58</v>
       </c>
       <c r="S10">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="T10">
         <v>4.33</v>
       </c>
       <c r="U10">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="V10">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="W10">
         <v>1.18</v>
@@ -1972,28 +1972,28 @@
         <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Z10">
-        <v>7</v>
+        <v>6.45</v>
       </c>
       <c r="AA10">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AB10">
-        <v>3.19</v>
+        <v>2.95</v>
       </c>
       <c r="AC10">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="AD10">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AE10">
         <v>1.33</v>
       </c>
       <c r="AF10">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AG10">
         <v>2.3</v>
@@ -3569,25 +3569,25 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="O20">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P20">
         <v>2.23</v>
       </c>
       <c r="Q20">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="R20">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S20">
         <v>1.27</v>
       </c>
       <c r="T20">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="U20">
         <v>2.3</v>
@@ -3605,19 +3605,19 @@
         <v>1.16</v>
       </c>
       <c r="Z20">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="AA20">
         <v>1.58</v>
       </c>
       <c r="AB20">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="AC20">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="AD20">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AE20">
         <v>1.14</v>
@@ -3626,7 +3626,7 @@
         <v>1.51</v>
       </c>
       <c r="AG20">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>1.21</v>
       </c>
       <c r="AK20">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -5371,52 +5371,52 @@
         <v>6.7</v>
       </c>
       <c r="Q31">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="R31">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="S31">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T31">
         <v>3</v>
       </c>
       <c r="U31">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="V31">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W31">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X31">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y31">
         <v>1.25</v>
       </c>
       <c r="Z31">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="AA31">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AB31">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AC31">
-        <v>3.11</v>
+        <v>2.88</v>
       </c>
       <c r="AD31">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AE31">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AF31">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AG31">
         <v>1.75</v>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AK31">
         <v>2.7</v>
@@ -5691,25 +5691,25 @@
         <v>2</v>
       </c>
       <c r="O33">
-        <v>3.62</v>
+        <v>3.64</v>
       </c>
       <c r="P33">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q33">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="R33">
         <v>2.25</v>
       </c>
       <c r="S33">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T33">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U33">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="V33">
         <v>1.48</v>
@@ -5721,31 +5721,31 @@
         <v>1.04</v>
       </c>
       <c r="Y33">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z33">
-        <v>4.1</v>
+        <v>3.98</v>
       </c>
       <c r="AA33">
         <v>1.7</v>
       </c>
       <c r="AB33">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AC33">
         <v>2.75</v>
       </c>
       <c r="AD33">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AE33">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF33">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AG33">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>1.22</v>
       </c>
       <c r="AK33">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -6512,10 +6512,10 @@
         <v>2.79</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S38">
         <v>0</v>
@@ -6524,10 +6524,10 @@
         <v>0</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W38">
         <v>0</v>
@@ -6536,31 +6536,31 @@
         <v>0</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -7155,19 +7155,19 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="O42">
-        <v>4.75</v>
+        <v>4.7</v>
       </c>
       <c r="P42">
         <v>9</v>
       </c>
       <c r="Q42">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="R42">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="S42">
         <v>1.36</v>
@@ -7182,10 +7182,10 @@
         <v>1.43</v>
       </c>
       <c r="W42">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X42">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y42">
         <v>1.21</v>
@@ -7194,10 +7194,10 @@
         <v>3.58</v>
       </c>
       <c r="AA42">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AB42">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC42">
         <v>2.83</v>
@@ -7206,7 +7206,7 @@
         <v>1.33</v>
       </c>
       <c r="AE42">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF42">
         <v>2.15</v>
@@ -7225,7 +7225,7 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="AK42">
         <v>3.2</v>
@@ -10261,31 +10261,31 @@
         <v>6.85</v>
       </c>
       <c r="Q61">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="R61">
         <v>2.4</v>
       </c>
       <c r="S61">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="T61">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="U61">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="V61">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W61">
         <v>1.08</v>
       </c>
       <c r="X61">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y61">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z61">
         <v>4.06</v>
@@ -10294,22 +10294,22 @@
         <v>1.72</v>
       </c>
       <c r="AB61">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AC61">
         <v>2.88</v>
       </c>
       <c r="AD61">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="AE61">
         <v>1.12</v>
       </c>
       <c r="AF61">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG61">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>1.18</v>
       </c>
       <c r="AK61">
-        <v>2.76</v>
+        <v>2.73</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="O62">
+        <v>3.25</v>
+      </c>
+      <c r="P62">
         <v>3.3</v>
-      </c>
-      <c r="P62">
-        <v>3.2</v>
       </c>
       <c r="Q62">
         <v>2.38</v>
       </c>
       <c r="R62">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="S62">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="T62">
-        <v>2.89</v>
+        <v>3.22</v>
       </c>
       <c r="U62">
-        <v>2.55</v>
+        <v>2.43</v>
       </c>
       <c r="V62">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W62">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X62">
         <v>1</v>
       </c>
       <c r="Y62">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z62">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AA62">
         <v>1.68</v>
       </c>
       <c r="AB62">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="AC62">
-        <v>2.68</v>
+        <v>2.95</v>
       </c>
       <c r="AD62">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AE62">
         <v>1.14</v>
       </c>
       <c r="AF62">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AG62">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK62">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -13023,58 +13023,58 @@
         </is>
       </c>
       <c r="N78">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="O78">
-        <v>3.92</v>
+        <v>3.8</v>
       </c>
       <c r="P78">
-        <v>4.5</v>
+        <v>4.65</v>
       </c>
       <c r="Q78">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="R78">
         <v>2.3</v>
       </c>
       <c r="S78">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T78">
         <v>3.15</v>
       </c>
       <c r="U78">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="V78">
         <v>1.46</v>
       </c>
       <c r="W78">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X78">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y78">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z78">
-        <v>4.15</v>
+        <v>3.8</v>
       </c>
       <c r="AA78">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AB78">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="AC78">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="AD78">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AE78">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AF78">
         <v>1.7</v>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AK78">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -14007,58 +14007,58 @@
         <v>3</v>
       </c>
       <c r="P84">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="Q84">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="R84">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="S84">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="T84">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="U84">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="V84">
         <v>1.22</v>
       </c>
       <c r="W84">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X84">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="Y84">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="Z84">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="AA84">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="AB84">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="AC84">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="AD84">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AE84">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF84">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AG84">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,7 +14071,7 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AK84">
         <v>1.79</v>
@@ -14339,19 +14339,19 @@
         <v>2</v>
       </c>
       <c r="R86">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="S86">
         <v>1.25</v>
       </c>
       <c r="T86">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="U86">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="V86">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W86">
         <v>1.14</v>
@@ -14360,25 +14360,25 @@
         <v>1.03</v>
       </c>
       <c r="Y86">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z86">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="AA86">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AB86">
-        <v>2.31</v>
+        <v>1.98</v>
       </c>
       <c r="AC86">
-        <v>2.44</v>
+        <v>2.01</v>
       </c>
       <c r="AD86">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AE86">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF86">
         <v>1.57</v>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AK86">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14825,7 +14825,7 @@
         <v>0</v>
       </c>
       <c r="Q89">
-        <v>4.67</v>
+        <v>3.95</v>
       </c>
       <c r="R89">
         <v>2.24</v>
@@ -15154,19 +15154,19 @@
         <v>3.22</v>
       </c>
       <c r="R91">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="S91">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="T91">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="U91">
-        <v>2.75</v>
+        <v>2.82</v>
       </c>
       <c r="V91">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="W91">
         <v>1.08</v>
@@ -15175,16 +15175,16 @@
         <v>1.05</v>
       </c>
       <c r="Y91">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z91">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="AA91">
-        <v>1.9</v>
+        <v>2.01</v>
       </c>
       <c r="AB91">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AC91">
         <v>3.4</v>
@@ -15212,7 +15212,7 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AK91">
         <v>1.5</v>
@@ -15314,10 +15314,10 @@
         <v>3.35</v>
       </c>
       <c r="Q92">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="R92">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="S92">
         <v>1.4</v>
@@ -15341,13 +15341,13 @@
         <v>1.31</v>
       </c>
       <c r="Z92">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="AA92">
         <v>2.02</v>
       </c>
       <c r="AB92">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AC92">
         <v>3.75</v>
@@ -15362,7 +15362,7 @@
         <v>1.8</v>
       </c>
       <c r="AG92">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AK92">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15794,22 +15794,22 @@
         </is>
       </c>
       <c r="N95">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="O95">
-        <v>5</v>
+        <v>5.45</v>
       </c>
       <c r="P95">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="Q95">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="R95">
-        <v>2.8</v>
+        <v>2.59</v>
       </c>
       <c r="S95">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T95">
         <v>4</v>
@@ -15827,31 +15827,31 @@
         <v>1.02</v>
       </c>
       <c r="Y95">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Z95">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="AA95">
         <v>1.44</v>
       </c>
       <c r="AB95">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AC95">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AD95">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AE95">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AF95">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG95">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,7 +15864,7 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AK95">
         <v>3.1</v>

--- a/jogos_2026-08-07.xlsx
+++ b/jogos_2026-08-07.xlsx
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="O75">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P75">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="Q75">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="R75">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="S75">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T75">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="U75">
-        <v>2.32</v>
+        <v>2.59</v>
       </c>
       <c r="V75">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W75">
+        <v>1.07</v>
+      </c>
+      <c r="X75">
+        <v>1.03</v>
+      </c>
+      <c r="Y75">
+        <v>1.16</v>
+      </c>
+      <c r="Z75">
+        <v>4.1</v>
+      </c>
+      <c r="AA75">
+        <v>1.56</v>
+      </c>
+      <c r="AB75">
+        <v>2.17</v>
+      </c>
+      <c r="AC75">
+        <v>2.7</v>
+      </c>
+      <c r="AD75">
+        <v>1.4</v>
+      </c>
+      <c r="AE75">
         <v>1.11</v>
       </c>
-      <c r="X75">
-        <v>1.05</v>
-      </c>
-      <c r="Y75">
-        <v>1.25</v>
-      </c>
-      <c r="Z75">
-        <v>3.8</v>
-      </c>
-      <c r="AA75">
-        <v>1.78</v>
-      </c>
-      <c r="AB75">
-        <v>2.01</v>
-      </c>
-      <c r="AC75">
-        <v>2.96</v>
-      </c>
-      <c r="AD75">
-        <v>1.37</v>
-      </c>
-      <c r="AE75">
-        <v>1.13</v>
-      </c>
       <c r="AF75">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AG75">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK75">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="O76">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P76">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="Q76">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="R76">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="S76">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="T76">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="U76">
-        <v>2.59</v>
+        <v>2.32</v>
       </c>
       <c r="V76">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W76">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X76">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y76">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="Z76">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="AA76">
-        <v>1.56</v>
+        <v>1.78</v>
       </c>
       <c r="AB76">
-        <v>2.17</v>
+        <v>2.01</v>
       </c>
       <c r="AC76">
-        <v>2.7</v>
+        <v>2.96</v>
       </c>
       <c r="AD76">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AE76">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF76">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AG76">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK76">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AL76">
         <v>0</v>

--- a/jogos_2026-08-07.xlsx
+++ b/jogos_2026-08-07.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="O2">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P2">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="Q2">
         <v>4</v>
@@ -650,65 +650,65 @@
         <v>2.15</v>
       </c>
       <c r="S2">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T2">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="U2">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="V2">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W2">
         <v>1.05</v>
       </c>
       <c r="X2">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y2">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z2">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="AA2">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AB2">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AC2">
-        <v>3.44</v>
+        <v>3.7</v>
       </c>
       <c r="AD2">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE2">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF2">
+        <v>1.84</v>
+      </c>
+      <c r="AG2">
+        <v>1.91</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ2">
         <v>1.83</v>
       </c>
-      <c r="AG2">
-        <v>1.85</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ2">
-        <v>1.3</v>
-      </c>
       <c r="AK2">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,10 +798,10 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="O3">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P3">
         <v>2.15</v>
@@ -810,7 +810,7 @@
         <v>3.4</v>
       </c>
       <c r="R3">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S3">
         <v>1.3</v>
@@ -819,7 +819,7 @@
         <v>3.1</v>
       </c>
       <c r="U3">
-        <v>2.62</v>
+        <v>2.47</v>
       </c>
       <c r="V3">
         <v>1.44</v>
@@ -828,34 +828,34 @@
         <v>1.07</v>
       </c>
       <c r="X3">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y3">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z3">
-        <v>3.96</v>
+        <v>4.2</v>
       </c>
       <c r="AA3">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB3">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AC3">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AD3">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE3">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF3">
         <v>1.6</v>
       </c>
       <c r="AG3">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>1.24</v>
       </c>
       <c r="AK3">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G4">
@@ -961,80 +961,80 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q4">
-        <v>2.42</v>
+        <v>3.69</v>
       </c>
       <c r="R4">
+        <v>2.23</v>
+      </c>
+      <c r="S4">
+        <v>1.31</v>
+      </c>
+      <c r="T4">
+        <v>2.86</v>
+      </c>
+      <c r="U4">
+        <v>2.64</v>
+      </c>
+      <c r="V4">
+        <v>1.43</v>
+      </c>
+      <c r="W4">
+        <v>1.07</v>
+      </c>
+      <c r="X4">
+        <v>1</v>
+      </c>
+      <c r="Y4">
+        <v>1.24</v>
+      </c>
+      <c r="Z4">
+        <v>3.83</v>
+      </c>
+      <c r="AA4">
+        <v>1.74</v>
+      </c>
+      <c r="AB4">
+        <v>1.98</v>
+      </c>
+      <c r="AC4">
+        <v>2.78</v>
+      </c>
+      <c r="AD4">
+        <v>1.34</v>
+      </c>
+      <c r="AE4">
+        <v>1.14</v>
+      </c>
+      <c r="AF4">
+        <v>1.7</v>
+      </c>
+      <c r="AG4">
         <v>2.1</v>
       </c>
-      <c r="S4">
-        <v>1.4</v>
-      </c>
-      <c r="T4">
-        <v>2.62</v>
-      </c>
-      <c r="U4">
-        <v>3</v>
-      </c>
-      <c r="V4">
-        <v>1.32</v>
-      </c>
-      <c r="W4">
-        <v>1.06</v>
-      </c>
-      <c r="X4">
-        <v>1.01</v>
-      </c>
-      <c r="Y4">
-        <v>1.31</v>
-      </c>
-      <c r="Z4">
-        <v>2.92</v>
-      </c>
-      <c r="AA4">
-        <v>2.04</v>
-      </c>
-      <c r="AB4">
-        <v>1.73</v>
-      </c>
-      <c r="AC4">
-        <v>3.58</v>
-      </c>
-      <c r="AD4">
-        <v>1.21</v>
-      </c>
-      <c r="AE4">
-        <v>1.04</v>
-      </c>
-      <c r="AF4">
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ4">
         <v>1.9</v>
       </c>
-      <c r="AG4">
-        <v>1.79</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ4">
-        <v>1.21</v>
-      </c>
       <c r="AK4">
-        <v>1.95</v>
+        <v>1.2</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>3.7</v>
+        <v>1.53</v>
       </c>
       <c r="O5">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="P5">
-        <v>1.75</v>
+        <v>5</v>
       </c>
       <c r="Q5">
-        <v>4.2</v>
+        <v>2</v>
       </c>
       <c r="R5">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="S5">
         <v>1.3</v>
       </c>
       <c r="T5">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="U5">
-        <v>2.45</v>
+        <v>2.56</v>
       </c>
       <c r="V5">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W5">
         <v>1.11</v>
       </c>
       <c r="X5">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z5">
-        <v>3.83</v>
+        <v>3.82</v>
       </c>
       <c r="AA5">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AB5">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AC5">
-        <v>2.78</v>
+        <v>2.93</v>
       </c>
       <c r="AD5">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AE5">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF5">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AG5">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.9</v>
+        <v>1.18</v>
       </c>
       <c r="AK5">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="O6">
-        <v>3.95</v>
+        <v>5.25</v>
       </c>
       <c r="P6">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q6">
-        <v>2.02</v>
+        <v>1.7</v>
       </c>
       <c r="R6">
-        <v>2.28</v>
+        <v>2.6</v>
       </c>
       <c r="S6">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="T6">
-        <v>2.87</v>
+        <v>3.25</v>
       </c>
       <c r="U6">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="V6">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W6">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X6">
         <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z6">
-        <v>3.82</v>
+        <v>4.4</v>
       </c>
       <c r="AA6">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AB6">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AC6">
-        <v>2.93</v>
+        <v>2.63</v>
       </c>
       <c r="AD6">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE6">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF6">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="AG6">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AK6">
-        <v>2.38</v>
+        <v>3.01</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,16 +1450,16 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.55</v>
+        <v>3.02</v>
       </c>
       <c r="O7">
-        <v>3.3</v>
+        <v>3.07</v>
       </c>
       <c r="P7">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="Q7">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="R7">
         <v>2.2</v>
@@ -1468,46 +1468,46 @@
         <v>1.36</v>
       </c>
       <c r="T7">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="U7">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="V7">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W7">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X7">
         <v>1.05</v>
       </c>
       <c r="Y7">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Z7">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AA7">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="AB7">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AC7">
-        <v>3.36</v>
+        <v>3.32</v>
       </c>
       <c r="AD7">
         <v>1.3</v>
       </c>
       <c r="AE7">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF7">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AG7">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.88</v>
+        <v>1.3</v>
       </c>
       <c r="AK7">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
+        <v>1.75</v>
+      </c>
+      <c r="O8">
+        <v>3.23</v>
+      </c>
+      <c r="P8">
+        <v>3.75</v>
+      </c>
+      <c r="Q8">
+        <v>2.23</v>
+      </c>
+      <c r="R8">
+        <v>2.1</v>
+      </c>
+      <c r="S8">
+        <v>1.41</v>
+      </c>
+      <c r="T8">
+        <v>2.75</v>
+      </c>
+      <c r="U8">
+        <v>2.78</v>
+      </c>
+      <c r="V8">
+        <v>1.33</v>
+      </c>
+      <c r="W8">
+        <v>1.03</v>
+      </c>
+      <c r="X8">
+        <v>1.06</v>
+      </c>
+      <c r="Y8">
+        <v>1.37</v>
+      </c>
+      <c r="Z8">
+        <v>3.1</v>
+      </c>
+      <c r="AA8">
+        <v>2.04</v>
+      </c>
+      <c r="AB8">
+        <v>1.73</v>
+      </c>
+      <c r="AC8">
+        <v>3.8</v>
+      </c>
+      <c r="AD8">
         <v>1.25</v>
       </c>
-      <c r="O8">
-        <v>5.3</v>
-      </c>
-      <c r="P8">
-        <v>9.050000000000001</v>
-      </c>
-      <c r="Q8">
-        <v>1.7</v>
-      </c>
-      <c r="R8">
-        <v>2.6</v>
-      </c>
-      <c r="S8">
-        <v>1.25</v>
-      </c>
-      <c r="T8">
-        <v>3.3</v>
-      </c>
-      <c r="U8">
-        <v>2.3</v>
-      </c>
-      <c r="V8">
-        <v>1.5</v>
-      </c>
-      <c r="W8">
-        <v>1.13</v>
-      </c>
-      <c r="X8">
-        <v>1.03</v>
-      </c>
-      <c r="Y8">
-        <v>1.18</v>
-      </c>
-      <c r="Z8">
-        <v>4.4</v>
-      </c>
-      <c r="AA8">
-        <v>1.62</v>
-      </c>
-      <c r="AB8">
-        <v>2.25</v>
-      </c>
-      <c r="AC8">
-        <v>2.68</v>
-      </c>
-      <c r="AD8">
-        <v>1.39</v>
-      </c>
       <c r="AE8">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AF8">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AG8">
-        <v>1.64</v>
+        <v>1.79</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AK8">
-        <v>3.01</v>
+        <v>1.92</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="O9">
         <v>3.3</v>
       </c>
       <c r="P9">
-        <v>2.98</v>
+        <v>2.87</v>
       </c>
       <c r="Q9">
-        <v>2.83</v>
+        <v>2.99</v>
       </c>
       <c r="R9">
         <v>2.03</v>
       </c>
       <c r="S9">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="T9">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="U9">
-        <v>2.73</v>
+        <v>2.97</v>
       </c>
       <c r="V9">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W9">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X9">
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z9">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AA9">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AB9">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AC9">
         <v>3.6</v>
       </c>
       <c r="AD9">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AE9">
         <v>1.04</v>
       </c>
       <c r="AF9">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AG9">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>1.33</v>
       </c>
       <c r="AK9">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1948,22 +1948,22 @@
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="R10">
-        <v>2.58</v>
+        <v>2.85</v>
       </c>
       <c r="S10">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="T10">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="U10">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="V10">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="W10">
         <v>1.18</v>
@@ -1972,31 +1972,31 @@
         <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z10">
-        <v>6.45</v>
+        <v>6.25</v>
       </c>
       <c r="AA10">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AB10">
         <v>2.95</v>
       </c>
       <c r="AC10">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AD10">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AE10">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AF10">
         <v>1.53</v>
       </c>
       <c r="AG10">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2763,55 +2763,55 @@
         <v>4.73</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,25 +2917,25 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="O16">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P16">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="Q16">
-        <v>2.89</v>
+        <v>3.14</v>
       </c>
       <c r="R16">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="S16">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T16">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="U16">
         <v>2.5</v>
@@ -2944,7 +2944,7 @@
         <v>1.48</v>
       </c>
       <c r="W16">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X16">
         <v>1.04</v>
@@ -2956,13 +2956,13 @@
         <v>4</v>
       </c>
       <c r="AA16">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AB16">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="AC16">
-        <v>2.63</v>
+        <v>2.68</v>
       </c>
       <c r="AD16">
         <v>1.4</v>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="AK16">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,43 +3243,43 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="O18">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="P18">
-        <v>4.02</v>
+        <v>4.3</v>
       </c>
       <c r="Q18">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="R18">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="S18">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="T18">
         <v>3.15</v>
       </c>
       <c r="U18">
-        <v>2.38</v>
+        <v>2.67</v>
       </c>
       <c r="V18">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W18">
         <v>1.11</v>
       </c>
       <c r="X18">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y18">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z18">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="AA18">
         <v>1.67</v>
@@ -3288,10 +3288,10 @@
         <v>2.07</v>
       </c>
       <c r="AC18">
-        <v>2.59</v>
+        <v>2.8</v>
       </c>
       <c r="AD18">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AE18">
         <v>1.12</v>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AK18">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3569,19 +3569,19 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="O20">
         <v>3.4</v>
       </c>
       <c r="P20">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="Q20">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="R20">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="S20">
         <v>1.27</v>
@@ -3590,10 +3590,10 @@
         <v>3.5</v>
       </c>
       <c r="U20">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="V20">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W20">
         <v>1.1</v>
@@ -3608,10 +3608,10 @@
         <v>4.15</v>
       </c>
       <c r="AA20">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AB20">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AC20">
         <v>2.46</v>
@@ -3623,10 +3623,10 @@
         <v>1.14</v>
       </c>
       <c r="AF20">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AG20">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3904,55 +3904,55 @@
         <v>0</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4067,55 +4067,55 @@
         <v>0</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4230,55 +4230,55 @@
         <v>0</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4393,55 +4393,55 @@
         <v>0</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4556,55 +4556,55 @@
         <v>0</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="O27">
-        <v>4.7</v>
+        <v>4.33</v>
       </c>
       <c r="P27">
-        <v>6.03</v>
+        <v>5.25</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -4882,55 +4882,55 @@
         <v>3.56</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q29">
         <v>3.3</v>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="AK29">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,16 +5199,16 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="O30">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P30">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="Q30">
-        <v>3.04</v>
+        <v>3.02</v>
       </c>
       <c r="R30">
         <v>2.15</v>
@@ -5217,43 +5217,43 @@
         <v>1.33</v>
       </c>
       <c r="T30">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="U30">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="V30">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W30">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X30">
         <v>1.05</v>
       </c>
       <c r="Y30">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Z30">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AA30">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="AB30">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="AC30">
-        <v>2.95</v>
+        <v>3.13</v>
       </c>
       <c r="AD30">
         <v>1.3</v>
       </c>
       <c r="AE30">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF30">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG30">
         <v>2.1</v>
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK30">
         <v>1.47</v>
@@ -5368,28 +5368,28 @@
         <v>4</v>
       </c>
       <c r="P31">
-        <v>6.7</v>
+        <v>6.25</v>
       </c>
       <c r="Q31">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="R31">
         <v>2.23</v>
       </c>
       <c r="S31">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T31">
         <v>3</v>
       </c>
       <c r="U31">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="V31">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="W31">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X31">
         <v>1.05</v>
@@ -5398,19 +5398,19 @@
         <v>1.25</v>
       </c>
       <c r="Z31">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="AA31">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AB31">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AC31">
         <v>2.88</v>
       </c>
       <c r="AD31">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AE31">
         <v>1.16</v>
@@ -5525,25 +5525,25 @@
         </is>
       </c>
       <c r="N32">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O32">
-        <v>3.46</v>
+        <v>3.45</v>
       </c>
       <c r="P32">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="Q32">
-        <v>3.72</v>
+        <v>3.22</v>
       </c>
       <c r="R32">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="S32">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T32">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="U32">
         <v>2.38</v>
@@ -5555,34 +5555,34 @@
         <v>1.13</v>
       </c>
       <c r="X32">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z32">
         <v>4</v>
       </c>
       <c r="AA32">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AB32">
-        <v>2.2</v>
+        <v>1.84</v>
       </c>
       <c r="AC32">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="AD32">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AE32">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF32">
         <v>1.57</v>
       </c>
       <c r="AG32">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AK32">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,16 +5688,16 @@
         </is>
       </c>
       <c r="N33">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="O33">
-        <v>3.64</v>
+        <v>3.5</v>
       </c>
       <c r="P33">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="Q33">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="R33">
         <v>2.25</v>
@@ -5730,7 +5730,7 @@
         <v>1.7</v>
       </c>
       <c r="AB33">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="AC33">
         <v>2.75</v>
@@ -5761,7 +5761,7 @@
         <v>1.22</v>
       </c>
       <c r="AK33">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -6177,25 +6177,25 @@
         </is>
       </c>
       <c r="N36">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="O36">
-        <v>3.62</v>
+        <v>3.61</v>
       </c>
       <c r="P36">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="Q36">
         <v>3.3</v>
       </c>
       <c r="R36">
-        <v>2.4</v>
+        <v>2.22</v>
       </c>
       <c r="S36">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="T36">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="U36">
         <v>2.34</v>
@@ -6204,37 +6204,37 @@
         <v>1.53</v>
       </c>
       <c r="W36">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X36">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y36">
         <v>1.15</v>
       </c>
       <c r="Z36">
-        <v>4.25</v>
+        <v>4.6</v>
       </c>
       <c r="AA36">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="AB36">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="AC36">
         <v>2.39</v>
       </c>
       <c r="AD36">
+        <v>1.44</v>
+      </c>
+      <c r="AE36">
+        <v>1.19</v>
+      </c>
+      <c r="AF36">
         <v>1.53</v>
       </c>
-      <c r="AE36">
-        <v>1.21</v>
-      </c>
-      <c r="AF36">
-        <v>1.51</v>
-      </c>
       <c r="AG36">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AK36">
         <v>1.4</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.12</v>
+        <v>2.03</v>
       </c>
       <c r="O37">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="P37">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="Q37">
         <v>2.8</v>
@@ -6355,40 +6355,40 @@
         <v>2.05</v>
       </c>
       <c r="S37">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T37">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="U37">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="V37">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W37">
         <v>1.07</v>
       </c>
       <c r="X37">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y37">
         <v>1.32</v>
       </c>
       <c r="Z37">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="AA37">
         <v>2.06</v>
       </c>
       <c r="AB37">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AC37">
         <v>3.95</v>
       </c>
       <c r="AD37">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE37">
         <v>1.07</v>
@@ -6397,7 +6397,7 @@
         <v>1.85</v>
       </c>
       <c r="AG37">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AK37">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6666,61 +6666,61 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="O39">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="P39">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="Q39">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R39">
-        <v>2.41</v>
+        <v>2.25</v>
       </c>
       <c r="S39">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T39">
         <v>3.5</v>
       </c>
       <c r="U39">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="V39">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="W39">
+        <v>1.15</v>
+      </c>
+      <c r="X39">
+        <v>1.03</v>
+      </c>
+      <c r="Y39">
         <v>1.12</v>
       </c>
-      <c r="X39">
-        <v>1.01</v>
-      </c>
-      <c r="Y39">
-        <v>1.15</v>
-      </c>
       <c r="Z39">
-        <v>4.94</v>
+        <v>4.65</v>
       </c>
       <c r="AA39">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AB39">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AC39">
-        <v>2.29</v>
+        <v>2.34</v>
       </c>
       <c r="AD39">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AE39">
         <v>1.22</v>
       </c>
       <c r="AF39">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AG39">
         <v>2.45</v>
@@ -6739,7 +6739,7 @@
         <v>1.18</v>
       </c>
       <c r="AK39">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,19 +6829,19 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.4</v>
+        <v>3.3</v>
       </c>
       <c r="O40">
-        <v>4.75</v>
+        <v>3.75</v>
       </c>
       <c r="P40">
-        <v>5.7</v>
+        <v>1.91</v>
       </c>
       <c r="Q40">
-        <v>1.83</v>
+        <v>3.3</v>
       </c>
       <c r="R40">
-        <v>2.7</v>
+        <v>2.32</v>
       </c>
       <c r="S40">
         <v>1.2</v>
@@ -6850,43 +6850,43 @@
         <v>4</v>
       </c>
       <c r="U40">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="V40">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="W40">
         <v>1.17</v>
       </c>
       <c r="X40">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y40">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Z40">
-        <v>5.65</v>
+        <v>5.4</v>
       </c>
       <c r="AA40">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="AB40">
-        <v>2.74</v>
+        <v>2.52</v>
       </c>
       <c r="AC40">
-        <v>1.99</v>
+        <v>2.15</v>
       </c>
       <c r="AD40">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AE40">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AF40">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AG40">
-        <v>2.4</v>
+        <v>2.66</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AK40">
-        <v>2.53</v>
+        <v>1.2</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="Q41">
-        <v>3.72</v>
+        <v>1.83</v>
       </c>
       <c r="R41">
-        <v>2.36</v>
+        <v>2.7</v>
       </c>
       <c r="S41">
         <v>1.2</v>
       </c>
       <c r="T41">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="U41">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="V41">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="W41">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X41">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y41">
         <v>1.08</v>
       </c>
       <c r="Z41">
-        <v>5.55</v>
+        <v>5.65</v>
       </c>
       <c r="AA41">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AB41">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="AC41">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
       <c r="AD41">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AE41">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AF41">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AG41">
-        <v>2.64</v>
+        <v>2.4</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="AK41">
-        <v>1.29</v>
+        <v>2.53</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7108,12 +7108,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>BSK Banja Luka</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="O42">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="P42">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q42">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="R42">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S42">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T42">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="U42">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V42">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W42">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y42">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z42">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA42">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB42">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC42">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AD42">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE42">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF42">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG42">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK42">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7259,7 +7259,7 @@
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>2026-08-07 14:30:00</t>
+          <t>2026-08-07 15:00:00</t>
         </is>
       </c>
     </row>
@@ -7276,7 +7276,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>BSK Banja Luka</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X43">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y43">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z43">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC43">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AD43">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG43">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK43">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7439,7 +7439,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="O44">
-        <v>3.13</v>
+        <v>3.6</v>
       </c>
       <c r="P44">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S44">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T44">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="U44">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V44">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W44">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X44">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y44">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z44">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA44">
-        <v>2.05</v>
+        <v>1.61</v>
       </c>
       <c r="AB44">
-        <v>1.66</v>
+        <v>2.3</v>
       </c>
       <c r="AC44">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD44">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE44">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF44">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG44">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK44">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7602,7 +7602,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O45">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P45">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q45">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="R45">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S45">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="T45">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U45">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="V45">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="W45">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X45">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y45">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z45">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AA45">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB45">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AC45">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AD45">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AE45">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF45">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AG45">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK45">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7765,7 +7765,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O46">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P46">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="Q46">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R46">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S46">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T46">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U46">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V46">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W46">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X46">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y46">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z46">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AA46">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB46">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AC46">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD46">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE46">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF46">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG46">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK46">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,80 +7970,80 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.44</v>
+        <v>2.63</v>
       </c>
       <c r="O47">
-        <v>4.85</v>
+        <v>3.35</v>
       </c>
       <c r="P47">
-        <v>5.78</v>
+        <v>2.25</v>
       </c>
       <c r="Q47">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="R47">
-        <v>2.42</v>
+        <v>2.24</v>
       </c>
       <c r="S47">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="T47">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="U47">
-        <v>2.08</v>
+        <v>2.37</v>
       </c>
       <c r="V47">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="W47">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="X47">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y47">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="Z47">
-        <v>5.55</v>
+        <v>4.25</v>
       </c>
       <c r="AA47">
+        <v>1.62</v>
+      </c>
+      <c r="AB47">
+        <v>2.2</v>
+      </c>
+      <c r="AC47">
+        <v>2.5</v>
+      </c>
+      <c r="AD47">
+        <v>1.52</v>
+      </c>
+      <c r="AE47">
+        <v>1.16</v>
+      </c>
+      <c r="AF47">
         <v>1.48</v>
       </c>
-      <c r="AB47">
-        <v>2.62</v>
-      </c>
-      <c r="AC47">
-        <v>2.09</v>
-      </c>
-      <c r="AD47">
-        <v>1.71</v>
-      </c>
-      <c r="AE47">
-        <v>1.28</v>
-      </c>
-      <c r="AF47">
+      <c r="AG47">
+        <v>2.38</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ47">
         <v>1.57</v>
       </c>
-      <c r="AG47">
-        <v>2.2</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ47">
-        <v>1.11</v>
-      </c>
       <c r="AK47">
-        <v>2.56</v>
+        <v>1.36</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,65 +8133,65 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="O48">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="P48">
+        <v>2.5</v>
+      </c>
+      <c r="Q48">
+        <v>2.56</v>
+      </c>
+      <c r="R48">
+        <v>2.4</v>
+      </c>
+      <c r="S48">
+        <v>1.22</v>
+      </c>
+      <c r="T48">
+        <v>3.8</v>
+      </c>
+      <c r="U48">
+        <v>2.18</v>
+      </c>
+      <c r="V48">
+        <v>1.65</v>
+      </c>
+      <c r="W48">
+        <v>1.14</v>
+      </c>
+      <c r="X48">
+        <v>1.02</v>
+      </c>
+      <c r="Y48">
+        <v>1.09</v>
+      </c>
+      <c r="Z48">
+        <v>5.35</v>
+      </c>
+      <c r="AA48">
+        <v>1.5</v>
+      </c>
+      <c r="AB48">
+        <v>2.49</v>
+      </c>
+      <c r="AC48">
         <v>2.2</v>
       </c>
-      <c r="Q48">
-        <v>3.2</v>
-      </c>
-      <c r="R48">
-        <v>2.43</v>
-      </c>
-      <c r="S48">
-        <v>1.28</v>
-      </c>
-      <c r="T48">
-        <v>3.25</v>
-      </c>
-      <c r="U48">
-        <v>2.37</v>
-      </c>
-      <c r="V48">
-        <v>1.55</v>
-      </c>
-      <c r="W48">
-        <v>1.1</v>
-      </c>
-      <c r="X48">
-        <v>1.03</v>
-      </c>
-      <c r="Y48">
-        <v>1.18</v>
-      </c>
-      <c r="Z48">
-        <v>4.64</v>
-      </c>
-      <c r="AA48">
-        <v>1.61</v>
-      </c>
-      <c r="AB48">
-        <v>2.28</v>
-      </c>
-      <c r="AC48">
+      <c r="AD48">
+        <v>1.62</v>
+      </c>
+      <c r="AE48">
+        <v>1.25</v>
+      </c>
+      <c r="AF48">
+        <v>1.44</v>
+      </c>
+      <c r="AG48">
         <v>2.55</v>
       </c>
-      <c r="AD48">
-        <v>1.52</v>
-      </c>
-      <c r="AE48">
-        <v>1.16</v>
-      </c>
-      <c r="AF48">
-        <v>1.5</v>
-      </c>
-      <c r="AG48">
-        <v>2.42</v>
-      </c>
       <c r="AH48" t="inlineStr">
         <is>
           <t>[]</t>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.6</v>
+        <v>1.22</v>
       </c>
       <c r="AK48">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,31 +8296,31 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.27</v>
+        <v>4.46</v>
       </c>
       <c r="O49">
-        <v>3.8</v>
+        <v>4.05</v>
       </c>
       <c r="P49">
-        <v>2.65</v>
+        <v>1.65</v>
       </c>
       <c r="Q49">
-        <v>2.7</v>
+        <v>4.73</v>
       </c>
       <c r="R49">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="S49">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="T49">
-        <v>4</v>
+        <v>3.44</v>
       </c>
       <c r="U49">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="V49">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="W49">
         <v>1.15</v>
@@ -8329,31 +8329,31 @@
         <v>1.03</v>
       </c>
       <c r="Y49">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="Z49">
-        <v>5.35</v>
+        <v>5</v>
       </c>
       <c r="AA49">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AB49">
-        <v>2.56</v>
+        <v>2.35</v>
       </c>
       <c r="AC49">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AD49">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AE49">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AF49">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="AG49">
-        <v>2.68</v>
+        <v>2.35</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK49">
-        <v>1.62</v>
+        <v>1.2</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>4.33</v>
+        <v>2.25</v>
       </c>
       <c r="O50">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="P50">
-        <v>1.65</v>
+        <v>2.74</v>
       </c>
       <c r="Q50">
-        <v>4.2</v>
+        <v>2.61</v>
       </c>
       <c r="R50">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="S50">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T50">
-        <v>3.6</v>
+        <v>3.36</v>
       </c>
       <c r="U50">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="V50">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="W50">
         <v>1.15</v>
       </c>
       <c r="X50">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="Z50">
-        <v>5</v>
+        <v>4.81</v>
       </c>
       <c r="AA50">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AB50">
+        <v>2.36</v>
+      </c>
+      <c r="AC50">
         <v>2.4</v>
-      </c>
-      <c r="AC50">
-        <v>2.3</v>
       </c>
       <c r="AD50">
         <v>1.53</v>
       </c>
       <c r="AE50">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF50">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="AG50">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK50">
-        <v>1.16</v>
+        <v>1.5</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8575,12 +8575,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,19 +8622,19 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.25</v>
+        <v>1.37</v>
       </c>
       <c r="O51">
-        <v>3.5</v>
+        <v>4.75</v>
       </c>
       <c r="P51">
-        <v>2.7</v>
+        <v>5.6</v>
       </c>
       <c r="Q51">
-        <v>2.75</v>
+        <v>1.81</v>
       </c>
       <c r="R51">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="S51">
         <v>1.22</v>
@@ -8643,59 +8643,59 @@
         <v>3.8</v>
       </c>
       <c r="U51">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="V51">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="W51">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X51">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y51">
+        <v>1.13</v>
+      </c>
+      <c r="Z51">
+        <v>5.5</v>
+      </c>
+      <c r="AA51">
+        <v>1.4</v>
+      </c>
+      <c r="AB51">
+        <v>2.63</v>
+      </c>
+      <c r="AC51">
+        <v>2.09</v>
+      </c>
+      <c r="AD51">
+        <v>1.67</v>
+      </c>
+      <c r="AE51">
+        <v>1.24</v>
+      </c>
+      <c r="AF51">
+        <v>1.59</v>
+      </c>
+      <c r="AG51">
+        <v>2.3</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ51">
         <v>1.12</v>
       </c>
-      <c r="Z51">
-        <v>4.86</v>
-      </c>
-      <c r="AA51">
-        <v>1.57</v>
-      </c>
-      <c r="AB51">
-        <v>2.38</v>
-      </c>
-      <c r="AC51">
-        <v>2.42</v>
-      </c>
-      <c r="AD51">
-        <v>1.53</v>
-      </c>
-      <c r="AE51">
-        <v>1.2</v>
-      </c>
-      <c r="AF51">
-        <v>1.44</v>
-      </c>
-      <c r="AG51">
-        <v>2.55</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ51">
-        <v>1.25</v>
-      </c>
       <c r="AK51">
-        <v>1.53</v>
+        <v>2.72</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>2026-08-07 15:00:00</t>
+          <t>2026-08-07 15:15:00</t>
         </is>
       </c>
     </row>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,22 +8785,22 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.37</v>
+        <v>2.44</v>
       </c>
       <c r="O52">
-        <v>4.85</v>
+        <v>3.5</v>
       </c>
       <c r="P52">
-        <v>6.05</v>
+        <v>2.42</v>
       </c>
       <c r="Q52">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="R52">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="S52">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T52">
         <v>4</v>
@@ -8809,40 +8809,40 @@
         <v>2.1</v>
       </c>
       <c r="V52">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="W52">
         <v>1.13</v>
       </c>
       <c r="X52">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y52">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Z52">
-        <v>5.55</v>
+        <v>5</v>
       </c>
       <c r="AA52">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="AB52">
-        <v>2.59</v>
+        <v>2.45</v>
       </c>
       <c r="AC52">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AD52">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AE52">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AF52">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="AG52">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.1</v>
+        <v>1.43</v>
       </c>
       <c r="AK52">
-        <v>2.63</v>
+        <v>1.42</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8906,7 +8906,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,65 +8948,65 @@
         </is>
       </c>
       <c r="N53">
+        <v>1.28</v>
+      </c>
+      <c r="O53">
+        <v>4.6</v>
+      </c>
+      <c r="P53">
+        <v>9</v>
+      </c>
+      <c r="Q53">
+        <v>1.75</v>
+      </c>
+      <c r="R53">
+        <v>2.45</v>
+      </c>
+      <c r="S53">
+        <v>1.34</v>
+      </c>
+      <c r="T53">
+        <v>3</v>
+      </c>
+      <c r="U53">
         <v>2.5</v>
       </c>
-      <c r="O53">
-        <v>3.48</v>
-      </c>
-      <c r="P53">
-        <v>2.45</v>
-      </c>
-      <c r="Q53">
-        <v>2.8</v>
-      </c>
-      <c r="R53">
-        <v>2.5</v>
-      </c>
-      <c r="S53">
-        <v>1.22</v>
-      </c>
-      <c r="T53">
-        <v>3.34</v>
-      </c>
-      <c r="U53">
-        <v>2.1</v>
-      </c>
       <c r="V53">
+        <v>1.44</v>
+      </c>
+      <c r="W53">
+        <v>1.1</v>
+      </c>
+      <c r="X53">
+        <v>1</v>
+      </c>
+      <c r="Y53">
+        <v>1.26</v>
+      </c>
+      <c r="Z53">
+        <v>3.9</v>
+      </c>
+      <c r="AA53">
+        <v>1.78</v>
+      </c>
+      <c r="AB53">
+        <v>2</v>
+      </c>
+      <c r="AC53">
+        <v>3</v>
+      </c>
+      <c r="AD53">
+        <v>1.38</v>
+      </c>
+      <c r="AE53">
+        <v>1.13</v>
+      </c>
+      <c r="AF53">
+        <v>2.15</v>
+      </c>
+      <c r="AG53">
         <v>1.62</v>
       </c>
-      <c r="W53">
-        <v>1.13</v>
-      </c>
-      <c r="X53">
-        <v>1.02</v>
-      </c>
-      <c r="Y53">
-        <v>1.11</v>
-      </c>
-      <c r="Z53">
-        <v>5.37</v>
-      </c>
-      <c r="AA53">
-        <v>1.49</v>
-      </c>
-      <c r="AB53">
-        <v>2.5</v>
-      </c>
-      <c r="AC53">
-        <v>2.14</v>
-      </c>
-      <c r="AD53">
-        <v>1.63</v>
-      </c>
-      <c r="AE53">
-        <v>1.23</v>
-      </c>
-      <c r="AF53">
-        <v>1.4</v>
-      </c>
-      <c r="AG53">
-        <v>2.7</v>
-      </c>
       <c r="AH53" t="inlineStr">
         <is>
           <t>[]</t>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="AK53">
-        <v>1.42</v>
+        <v>3.2</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9114,52 +9114,52 @@
         <v>2.06</v>
       </c>
       <c r="O54">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="P54">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q54">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="R54">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="S54">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="T54">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="U54">
         <v>2.6</v>
       </c>
       <c r="V54">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W54">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X54">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y54">
         <v>1.19</v>
       </c>
       <c r="Z54">
-        <v>3.95</v>
+        <v>3.82</v>
       </c>
       <c r="AA54">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AB54">
-        <v>2.03</v>
+        <v>1.99</v>
       </c>
       <c r="AC54">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="AD54">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AE54">
         <v>1.15</v>
@@ -9168,7 +9168,7 @@
         <v>1.62</v>
       </c>
       <c r="AG54">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK54">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9283,19 +9283,19 @@
         <v>2.7</v>
       </c>
       <c r="Q55">
-        <v>3.02</v>
+        <v>2.94</v>
       </c>
       <c r="R55">
         <v>2.03</v>
       </c>
       <c r="S55">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="T55">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="U55">
-        <v>2.89</v>
+        <v>2.75</v>
       </c>
       <c r="V55">
         <v>1.36</v>
@@ -9304,34 +9304,34 @@
         <v>1.04</v>
       </c>
       <c r="X55">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y55">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="Z55">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AA55">
         <v>2</v>
       </c>
       <c r="AB55">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AC55">
         <v>3.14</v>
       </c>
       <c r="AD55">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AE55">
         <v>1.08</v>
       </c>
       <c r="AF55">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AG55">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AK55">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9443,13 +9443,13 @@
         <v>4.2</v>
       </c>
       <c r="P56">
-        <v>4.65</v>
+        <v>4.5</v>
       </c>
       <c r="Q56">
         <v>2.07</v>
       </c>
       <c r="R56">
-        <v>2.38</v>
+        <v>2.53</v>
       </c>
       <c r="S56">
         <v>1.27</v>
@@ -9458,7 +9458,7 @@
         <v>3.5</v>
       </c>
       <c r="U56">
-        <v>2.29</v>
+        <v>2.36</v>
       </c>
       <c r="V56">
         <v>1.56</v>
@@ -9467,22 +9467,22 @@
         <v>1.14</v>
       </c>
       <c r="X56">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y56">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z56">
-        <v>4.33</v>
+        <v>4.53</v>
       </c>
       <c r="AA56">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AB56">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="AC56">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="AD56">
         <v>1.47</v>
@@ -9494,7 +9494,7 @@
         <v>1.62</v>
       </c>
       <c r="AG56">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AK56">
         <v>2.25</v>
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="O57">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P57">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="Q57">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="R57">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="S57">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T57">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U57">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="V57">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W57">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X57">
         <v>1.01</v>
       </c>
       <c r="Y57">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Z57">
         <v>3.34</v>
       </c>
       <c r="AA57">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AB57">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AC57">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="AD57">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE57">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF57">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="AG57">
-        <v>2.01</v>
+        <v>1.94</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="AK57">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="O58">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="P58">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="Q58">
         <v>2.63</v>
@@ -9778,10 +9778,10 @@
         <v>2.4</v>
       </c>
       <c r="S58">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T58">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="U58">
         <v>2.25</v>
@@ -9790,7 +9790,7 @@
         <v>1.57</v>
       </c>
       <c r="W58">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X58">
         <v>1.03</v>
@@ -9799,28 +9799,28 @@
         <v>1.2</v>
       </c>
       <c r="Z58">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="AA58">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AB58">
         <v>2.25</v>
       </c>
       <c r="AC58">
-        <v>2.54</v>
+        <v>2.43</v>
       </c>
       <c r="AD58">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="AE58">
         <v>1.15</v>
       </c>
       <c r="AF58">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AG58">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="O59">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P59">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Q59">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R59">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S59">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T59">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U59">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V59">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W59">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X59">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y59">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z59">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA59">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB59">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC59">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD59">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE59">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF59">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG59">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK59">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10089,28 +10089,28 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="O60">
-        <v>4.05</v>
+        <v>4.65</v>
       </c>
       <c r="P60">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="Q60">
         <v>1.95</v>
       </c>
       <c r="R60">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="S60">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T60">
         <v>3.75</v>
       </c>
       <c r="U60">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="V60">
         <v>1.61</v>
@@ -10125,28 +10125,28 @@
         <v>1.15</v>
       </c>
       <c r="Z60">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AA60">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AB60">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="AC60">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="AD60">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AE60">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AF60">
         <v>1.62</v>
       </c>
       <c r="AG60">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,7 +10159,7 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AK60">
         <v>2.63</v>
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="O61">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="P61">
-        <v>6.85</v>
+        <v>6</v>
       </c>
       <c r="Q61">
         <v>1.83</v>
@@ -10267,28 +10267,28 @@
         <v>2.4</v>
       </c>
       <c r="S61">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T61">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U61">
         <v>2.5</v>
       </c>
       <c r="V61">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W61">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X61">
         <v>1.04</v>
       </c>
       <c r="Y61">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="Z61">
-        <v>4.06</v>
+        <v>4.1</v>
       </c>
       <c r="AA61">
         <v>1.72</v>
@@ -10297,19 +10297,19 @@
         <v>2.07</v>
       </c>
       <c r="AC61">
-        <v>2.88</v>
+        <v>2.61</v>
       </c>
       <c r="AD61">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AE61">
         <v>1.12</v>
       </c>
       <c r="AF61">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AG61">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AK61">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10415,52 +10415,52 @@
         </is>
       </c>
       <c r="N62">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="O62">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P62">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="Q62">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="R62">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="S62">
         <v>1.32</v>
       </c>
       <c r="T62">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="U62">
         <v>2.43</v>
       </c>
       <c r="V62">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W62">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X62">
         <v>1</v>
       </c>
       <c r="Y62">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z62">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AA62">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="AB62">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="AC62">
-        <v>2.95</v>
+        <v>2.68</v>
       </c>
       <c r="AD62">
         <v>1.37</v>
@@ -10469,10 +10469,10 @@
         <v>1.14</v>
       </c>
       <c r="AF62">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AG62">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,7 +10485,7 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AK62">
         <v>1.73</v>
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="O63">
-        <v>3.29</v>
+        <v>3.25</v>
       </c>
       <c r="P63">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="Q63">
         <v>0</v>
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="N67">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O67">
-        <v>3.07</v>
+        <v>2.98</v>
       </c>
       <c r="P67">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q67">
         <v>0</v>
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="O69">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="P69">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Q69">
         <v>0</v>
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="O70">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="P70">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q70">
         <v>0</v>
@@ -12048,10 +12048,10 @@
         <v>1.32</v>
       </c>
       <c r="O72">
-        <v>4.2</v>
+        <v>4.75</v>
       </c>
       <c r="P72">
-        <v>9.550000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q72">
         <v>0</v>
@@ -12084,10 +12084,10 @@
         <v>0</v>
       </c>
       <c r="AA72">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AB72">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC72">
         <v>0</v>
@@ -12208,16 +12208,16 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="O73">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P73">
-        <v>2.93</v>
+        <v>2.85</v>
       </c>
       <c r="Q73">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="R73">
         <v>2.21</v>
@@ -12244,25 +12244,25 @@
         <v>1.3</v>
       </c>
       <c r="Z73">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="AA73">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AB73">
-        <v>1.72</v>
+        <v>1.86</v>
       </c>
       <c r="AC73">
         <v>3.35</v>
       </c>
       <c r="AD73">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AE73">
         <v>1.1</v>
       </c>
       <c r="AF73">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AG73">
         <v>2</v>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AK73">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12374,19 +12374,19 @@
         <v>1.41</v>
       </c>
       <c r="O74">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="P74">
-        <v>6.17</v>
+        <v>7.5</v>
       </c>
       <c r="Q74">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="R74">
-        <v>2.85</v>
+        <v>2.63</v>
       </c>
       <c r="S74">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T74">
         <v>3.58</v>
@@ -12398,7 +12398,7 @@
         <v>1.6</v>
       </c>
       <c r="W74">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X74">
         <v>1.02</v>
@@ -12416,19 +12416,19 @@
         <v>2.48</v>
       </c>
       <c r="AC74">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AD74">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AE74">
         <v>1.25</v>
       </c>
       <c r="AF74">
-        <v>1.64</v>
+        <v>1.81</v>
       </c>
       <c r="AG74">
-        <v>2.04</v>
+        <v>1.88</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="AK74">
-        <v>2.63</v>
+        <v>3.24</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12534,19 +12534,19 @@
         </is>
       </c>
       <c r="N75">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="O75">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P75">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="Q75">
-        <v>2.33</v>
+        <v>2.47</v>
       </c>
       <c r="R75">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S75">
         <v>1.31</v>
@@ -12555,10 +12555,10 @@
         <v>3.02</v>
       </c>
       <c r="U75">
-        <v>2.59</v>
+        <v>2.2</v>
       </c>
       <c r="V75">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W75">
         <v>1.07</v>
@@ -12567,25 +12567,25 @@
         <v>1.03</v>
       </c>
       <c r="Y75">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z75">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="AA75">
         <v>1.56</v>
       </c>
       <c r="AB75">
-        <v>2.17</v>
+        <v>2.03</v>
       </c>
       <c r="AC75">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AD75">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE75">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF75">
         <v>1.52</v>
@@ -12700,25 +12700,25 @@
         <v>2.04</v>
       </c>
       <c r="O76">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P76">
-        <v>3.24</v>
+        <v>3.05</v>
       </c>
       <c r="Q76">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="R76">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S76">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T76">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="U76">
-        <v>2.32</v>
+        <v>2.56</v>
       </c>
       <c r="V76">
         <v>1.44</v>
@@ -12727,13 +12727,13 @@
         <v>1.11</v>
       </c>
       <c r="X76">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y76">
         <v>1.25</v>
       </c>
       <c r="Z76">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AA76">
         <v>1.78</v>
@@ -12754,7 +12754,7 @@
         <v>1.62</v>
       </c>
       <c r="AG76">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12863,10 +12863,10 @@
         <v>1.25</v>
       </c>
       <c r="O77">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="P77">
-        <v>8.199999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="Q77">
         <v>0</v>
@@ -13023,13 +13023,13 @@
         </is>
       </c>
       <c r="N78">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="O78">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P78">
-        <v>4.65</v>
+        <v>4.33</v>
       </c>
       <c r="Q78">
         <v>2.1</v>
@@ -13056,16 +13056,16 @@
         <v>1.04</v>
       </c>
       <c r="Y78">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="Z78">
-        <v>3.8</v>
+        <v>4.09</v>
       </c>
       <c r="AA78">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB78">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="AC78">
         <v>2.8</v>
@@ -13093,7 +13093,7 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AK78">
         <v>2.15</v>
@@ -13349,34 +13349,34 @@
         </is>
       </c>
       <c r="N80">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="O80">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="P80">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q80">
-        <v>3.7</v>
+        <v>3.56</v>
       </c>
       <c r="R80">
         <v>2.25</v>
       </c>
       <c r="S80">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T80">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="U80">
-        <v>2.79</v>
+        <v>2.73</v>
       </c>
       <c r="V80">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W80">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X80">
         <v>1.05</v>
@@ -13385,44 +13385,44 @@
         <v>1.27</v>
       </c>
       <c r="Z80">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AA80">
         <v>1.93</v>
       </c>
       <c r="AB80">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AC80">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AD80">
+        <v>1.35</v>
+      </c>
+      <c r="AE80">
+        <v>1.08</v>
+      </c>
+      <c r="AF80">
+        <v>1.66</v>
+      </c>
+      <c r="AG80">
+        <v>2</v>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ80">
         <v>1.33</v>
       </c>
-      <c r="AE80">
-        <v>1.09</v>
-      </c>
-      <c r="AF80">
-        <v>1.71</v>
-      </c>
-      <c r="AG80">
-        <v>1.98</v>
-      </c>
-      <c r="AH80" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI80" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ80">
-        <v>1.35</v>
-      </c>
       <c r="AK80">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13838,28 +13838,28 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="O83">
         <v>3.3</v>
       </c>
       <c r="P83">
-        <v>4.73</v>
+        <v>4.1</v>
       </c>
       <c r="Q83">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="R83">
         <v>2.1</v>
       </c>
       <c r="S83">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T83">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="U83">
-        <v>3.07</v>
+        <v>2.9</v>
       </c>
       <c r="V83">
         <v>1.35</v>
@@ -13868,19 +13868,19 @@
         <v>1.05</v>
       </c>
       <c r="X83">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y83">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="Z83">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AA83">
         <v>2.1</v>
       </c>
       <c r="AB83">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC83">
         <v>3.75</v>
@@ -13892,10 +13892,10 @@
         <v>1.08</v>
       </c>
       <c r="AF83">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AG83">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK83">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14037,28 +14037,28 @@
         <v>1.47</v>
       </c>
       <c r="Z84">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="AA84">
         <v>2.42</v>
       </c>
       <c r="AB84">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="AC84">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="AD84">
         <v>1.2</v>
       </c>
       <c r="AE84">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AF84">
         <v>2.17</v>
       </c>
       <c r="AG84">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14336,7 +14336,7 @@
         <v>4.1</v>
       </c>
       <c r="Q86">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="R86">
         <v>2.2</v>
@@ -14345,10 +14345,10 @@
         <v>1.25</v>
       </c>
       <c r="T86">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U86">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="V86">
         <v>1.57</v>
@@ -14357,34 +14357,34 @@
         <v>1.14</v>
       </c>
       <c r="X86">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y86">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z86">
-        <v>3.3</v>
+        <v>4.45</v>
       </c>
       <c r="AA86">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AB86">
-        <v>1.98</v>
+        <v>2.38</v>
       </c>
       <c r="AC86">
         <v>2.01</v>
       </c>
       <c r="AD86">
-        <v>1.42</v>
+        <v>1.56</v>
       </c>
       <c r="AE86">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF86">
         <v>1.57</v>
       </c>
       <c r="AG86">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AK86">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14656,34 +14656,34 @@
         <v>1.34</v>
       </c>
       <c r="O88">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="P88">
-        <v>9</v>
+        <v>6.4</v>
       </c>
       <c r="Q88">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R88">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="S88">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T88">
-        <v>3.13</v>
+        <v>3.15</v>
       </c>
       <c r="U88">
-        <v>2.72</v>
+        <v>2.55</v>
       </c>
       <c r="V88">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="W88">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X88">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y88">
         <v>1.26</v>
@@ -14695,22 +14695,22 @@
         <v>1.83</v>
       </c>
       <c r="AB88">
-        <v>1.89</v>
+        <v>1.99</v>
       </c>
       <c r="AC88">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="AD88">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AE88">
         <v>1.08</v>
       </c>
       <c r="AF88">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG88">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14825,13 +14825,13 @@
         <v>0</v>
       </c>
       <c r="Q89">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="R89">
         <v>2.24</v>
       </c>
       <c r="S89">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="T89">
         <v>3.25</v>
@@ -14840,7 +14840,7 @@
         <v>2.29</v>
       </c>
       <c r="V89">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W89">
         <v>1.09</v>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.19</v>
+        <v>1.98</v>
       </c>
       <c r="AK89">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14979,13 +14979,13 @@
         </is>
       </c>
       <c r="N90">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O90">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P90">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q90">
         <v>0</v>
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O91">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P91">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q91">
         <v>3.22</v>
       </c>
       <c r="R91">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="S91">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T91">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="U91">
         <v>2.82</v>
       </c>
       <c r="V91">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W91">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X91">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y91">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z91">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AA91">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AB91">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AC91">
-        <v>3.4</v>
+        <v>3.41</v>
       </c>
       <c r="AD91">
         <v>1.29</v>
       </c>
       <c r="AE91">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF91">
         <v>1.7</v>
       </c>
       <c r="AG91">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AK91">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15314,7 +15314,7 @@
         <v>3.35</v>
       </c>
       <c r="Q92">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="R92">
         <v>2.03</v>
@@ -15323,34 +15323,34 @@
         <v>1.4</v>
       </c>
       <c r="T92">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="U92">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="V92">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W92">
         <v>1.04</v>
       </c>
       <c r="X92">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y92">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="Z92">
-        <v>2.9</v>
+        <v>2.97</v>
       </c>
       <c r="AA92">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="AB92">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AC92">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AD92">
         <v>1.22</v>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AK92">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15480,10 +15480,10 @@
         <v>3.67</v>
       </c>
       <c r="R93">
-        <v>2.27</v>
+        <v>2.12</v>
       </c>
       <c r="S93">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T93">
         <v>3.2</v>
@@ -15495,28 +15495,28 @@
         <v>1.44</v>
       </c>
       <c r="W93">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X93">
         <v>1</v>
       </c>
       <c r="Y93">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="Z93">
-        <v>3.75</v>
+        <v>3.84</v>
       </c>
       <c r="AA93">
         <v>1.8</v>
       </c>
       <c r="AB93">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AC93">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="AD93">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE93">
         <v>1.13</v>
@@ -15538,7 +15538,7 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK93">
         <v>1.36</v>
@@ -15794,13 +15794,13 @@
         </is>
       </c>
       <c r="N95">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="O95">
-        <v>5.45</v>
+        <v>4.95</v>
       </c>
       <c r="P95">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="Q95">
         <v>1.65</v>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AK95">
-        <v>3.1</v>
+        <v>3.38</v>
       </c>
       <c r="AL95">
         <v>0</v>

--- a/jogos_2026-08-07.xlsx
+++ b/jogos_2026-08-07.xlsx
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,65 +1287,65 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.25</v>
+        <v>3.02</v>
       </c>
       <c r="O6">
-        <v>5.25</v>
+        <v>3.07</v>
       </c>
       <c r="P6">
-        <v>8</v>
+        <v>1.91</v>
       </c>
       <c r="Q6">
-        <v>1.7</v>
+        <v>4.33</v>
       </c>
       <c r="R6">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="S6">
+        <v>1.36</v>
+      </c>
+      <c r="T6">
+        <v>2.88</v>
+      </c>
+      <c r="U6">
+        <v>2.88</v>
+      </c>
+      <c r="V6">
+        <v>1.4</v>
+      </c>
+      <c r="W6">
+        <v>1.07</v>
+      </c>
+      <c r="X6">
+        <v>1.05</v>
+      </c>
+      <c r="Y6">
         <v>1.26</v>
       </c>
-      <c r="T6">
-        <v>3.25</v>
-      </c>
-      <c r="U6">
-        <v>2.49</v>
-      </c>
-      <c r="V6">
-        <v>1.5</v>
-      </c>
-      <c r="W6">
-        <v>1.13</v>
-      </c>
-      <c r="X6">
-        <v>1.02</v>
-      </c>
-      <c r="Y6">
-        <v>1.2</v>
-      </c>
       <c r="Z6">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="AA6">
-        <v>1.67</v>
+        <v>1.96</v>
       </c>
       <c r="AB6">
-        <v>2.2</v>
+        <v>1.81</v>
       </c>
       <c r="AC6">
-        <v>2.63</v>
+        <v>3.32</v>
       </c>
       <c r="AD6">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AE6">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AF6">
+        <v>1.76</v>
+      </c>
+      <c r="AG6">
         <v>1.91</v>
       </c>
-      <c r="AG6">
-        <v>1.65</v>
-      </c>
       <c r="AH6" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.09</v>
+        <v>1.3</v>
       </c>
       <c r="AK6">
-        <v>3.01</v>
+        <v>1.19</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.02</v>
+        <v>1.25</v>
       </c>
       <c r="O7">
-        <v>3.07</v>
+        <v>5.25</v>
       </c>
       <c r="P7">
+        <v>8</v>
+      </c>
+      <c r="Q7">
+        <v>1.7</v>
+      </c>
+      <c r="R7">
+        <v>2.6</v>
+      </c>
+      <c r="S7">
+        <v>1.26</v>
+      </c>
+      <c r="T7">
+        <v>3.25</v>
+      </c>
+      <c r="U7">
+        <v>2.49</v>
+      </c>
+      <c r="V7">
+        <v>1.5</v>
+      </c>
+      <c r="W7">
+        <v>1.13</v>
+      </c>
+      <c r="X7">
+        <v>1.02</v>
+      </c>
+      <c r="Y7">
+        <v>1.2</v>
+      </c>
+      <c r="Z7">
+        <v>4.4</v>
+      </c>
+      <c r="AA7">
+        <v>1.67</v>
+      </c>
+      <c r="AB7">
+        <v>2.2</v>
+      </c>
+      <c r="AC7">
+        <v>2.63</v>
+      </c>
+      <c r="AD7">
+        <v>1.4</v>
+      </c>
+      <c r="AE7">
+        <v>1.14</v>
+      </c>
+      <c r="AF7">
         <v>1.91</v>
       </c>
-      <c r="Q7">
-        <v>4.33</v>
-      </c>
-      <c r="R7">
-        <v>2.2</v>
-      </c>
-      <c r="S7">
-        <v>1.36</v>
-      </c>
-      <c r="T7">
-        <v>2.88</v>
-      </c>
-      <c r="U7">
-        <v>2.88</v>
-      </c>
-      <c r="V7">
-        <v>1.4</v>
-      </c>
-      <c r="W7">
-        <v>1.07</v>
-      </c>
-      <c r="X7">
-        <v>1.05</v>
-      </c>
-      <c r="Y7">
-        <v>1.26</v>
-      </c>
-      <c r="Z7">
-        <v>3.2</v>
-      </c>
-      <c r="AA7">
-        <v>1.96</v>
-      </c>
-      <c r="AB7">
-        <v>1.81</v>
-      </c>
-      <c r="AC7">
-        <v>3.32</v>
-      </c>
-      <c r="AD7">
-        <v>1.3</v>
-      </c>
-      <c r="AE7">
-        <v>1.07</v>
-      </c>
-      <c r="AF7">
-        <v>1.76</v>
-      </c>
       <c r="AG7">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.3</v>
+        <v>1.09</v>
       </c>
       <c r="AK7">
-        <v>1.19</v>
+        <v>3.01</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -2141,10 +2141,10 @@
         <v>0</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC11">
         <v>0</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -2304,10 +2304,10 @@
         <v>0</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC12">
         <v>0</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>6.19</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -2467,10 +2467,10 @@
         <v>0</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC13">
         <v>0</v>
@@ -3569,7 +3569,7 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="O20">
         <v>3.4</v>
@@ -3587,16 +3587,16 @@
         <v>1.27</v>
       </c>
       <c r="T20">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="U20">
         <v>2.33</v>
       </c>
       <c r="V20">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W20">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X20">
         <v>1.01</v>
@@ -3611,10 +3611,10 @@
         <v>1.61</v>
       </c>
       <c r="AB20">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AC20">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="AD20">
         <v>1.46</v>
@@ -3626,7 +3626,7 @@
         <v>1.5</v>
       </c>
       <c r="AG20">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G22">
@@ -3904,16 +3904,16 @@
         <v>0</v>
       </c>
       <c r="Q22">
-        <v>2.1</v>
+        <v>4.4</v>
       </c>
       <c r="R22">
         <v>2.3</v>
       </c>
       <c r="S22">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T22">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="U22">
         <v>2.6</v>
@@ -3922,7 +3922,7 @@
         <v>1.4</v>
       </c>
       <c r="W22">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X22">
         <v>1.04</v>
@@ -3934,10 +3934,10 @@
         <v>3.75</v>
       </c>
       <c r="AA22">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB22">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC22">
         <v>2.9</v>
@@ -3952,7 +3952,7 @@
         <v>1.75</v>
       </c>
       <c r="AG22">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK22">
-        <v>2.3</v>
+        <v>1.18</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G23">
@@ -4067,55 +4067,55 @@
         <v>0</v>
       </c>
       <c r="Q23">
-        <v>4.4</v>
+        <v>2</v>
       </c>
       <c r="R23">
         <v>2.3</v>
       </c>
       <c r="S23">
+        <v>1.35</v>
+      </c>
+      <c r="T23">
+        <v>2.79</v>
+      </c>
+      <c r="U23">
+        <v>2.63</v>
+      </c>
+      <c r="V23">
+        <v>1.39</v>
+      </c>
+      <c r="W23">
+        <v>1.04</v>
+      </c>
+      <c r="X23">
+        <v>1.05</v>
+      </c>
+      <c r="Y23">
+        <v>1.25</v>
+      </c>
+      <c r="Z23">
+        <v>3.6</v>
+      </c>
+      <c r="AA23">
+        <v>1.8</v>
+      </c>
+      <c r="AB23">
+        <v>1.91</v>
+      </c>
+      <c r="AC23">
+        <v>3</v>
+      </c>
+      <c r="AD23">
         <v>1.33</v>
-      </c>
-      <c r="T23">
-        <v>2.88</v>
-      </c>
-      <c r="U23">
-        <v>2.6</v>
-      </c>
-      <c r="V23">
-        <v>1.4</v>
-      </c>
-      <c r="W23">
-        <v>1.05</v>
-      </c>
-      <c r="X23">
-        <v>1.04</v>
-      </c>
-      <c r="Y23">
-        <v>1.22</v>
-      </c>
-      <c r="Z23">
-        <v>3.75</v>
-      </c>
-      <c r="AA23">
-        <v>1.75</v>
-      </c>
-      <c r="AB23">
-        <v>1.95</v>
-      </c>
-      <c r="AC23">
-        <v>2.9</v>
-      </c>
-      <c r="AD23">
-        <v>1.36</v>
       </c>
       <c r="AE23">
         <v>1.13</v>
       </c>
       <c r="AF23">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AG23">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>1.25</v>
       </c>
       <c r="AK23">
-        <v>1.18</v>
+        <v>2.38</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G24">
@@ -4230,55 +4230,55 @@
         <v>0</v>
       </c>
       <c r="Q24">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="R24">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S24">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="T24">
-        <v>2.79</v>
+        <v>3.12</v>
       </c>
       <c r="U24">
-        <v>2.63</v>
+        <v>2.41</v>
       </c>
       <c r="V24">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="W24">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X24">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y24">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z24">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="AA24">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AB24">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AC24">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AD24">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AE24">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF24">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AG24">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>1.25</v>
       </c>
       <c r="AK24">
-        <v>2.38</v>
+        <v>1.85</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G25">
@@ -4393,55 +4393,55 @@
         <v>0</v>
       </c>
       <c r="Q25">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="R25">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="S25">
         <v>1.28</v>
       </c>
       <c r="T25">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="U25">
-        <v>2.41</v>
+        <v>2.25</v>
       </c>
       <c r="V25">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="W25">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X25">
         <v>1.03</v>
       </c>
       <c r="Y25">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z25">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AA25">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AB25">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AC25">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AD25">
         <v>1.44</v>
       </c>
       <c r="AE25">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF25">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG25">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK25">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G26">
@@ -4559,52 +4559,52 @@
         <v>2.1</v>
       </c>
       <c r="R26">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="S26">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T26">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="U26">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="V26">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="W26">
+        <v>1.1</v>
+      </c>
+      <c r="X26">
+        <v>1.04</v>
+      </c>
+      <c r="Y26">
+        <v>1.22</v>
+      </c>
+      <c r="Z26">
+        <v>3.75</v>
+      </c>
+      <c r="AA26">
+        <v>1.8</v>
+      </c>
+      <c r="AB26">
+        <v>2</v>
+      </c>
+      <c r="AC26">
+        <v>2.9</v>
+      </c>
+      <c r="AD26">
+        <v>1.36</v>
+      </c>
+      <c r="AE26">
         <v>1.13</v>
       </c>
-      <c r="X26">
-        <v>1.03</v>
-      </c>
-      <c r="Y26">
-        <v>1.18</v>
-      </c>
-      <c r="Z26">
-        <v>4.5</v>
-      </c>
-      <c r="AA26">
-        <v>1.57</v>
-      </c>
-      <c r="AB26">
-        <v>2.25</v>
-      </c>
-      <c r="AC26">
-        <v>2.5</v>
-      </c>
-      <c r="AD26">
-        <v>1.44</v>
-      </c>
-      <c r="AE26">
-        <v>1.18</v>
-      </c>
       <c r="AF26">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AG26">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -5365,13 +5365,13 @@
         <v>1.43</v>
       </c>
       <c r="O31">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P31">
-        <v>6.25</v>
+        <v>6.85</v>
       </c>
       <c r="Q31">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="R31">
         <v>2.23</v>
@@ -5386,37 +5386,37 @@
         <v>2.62</v>
       </c>
       <c r="V31">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W31">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X31">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y31">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z31">
         <v>3.75</v>
       </c>
       <c r="AA31">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AB31">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AC31">
-        <v>2.88</v>
+        <v>2.55</v>
       </c>
       <c r="AD31">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE31">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AF31">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AG31">
         <v>1.75</v>
@@ -5688,10 +5688,10 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="O33">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P33">
         <v>3.2</v>
@@ -5712,7 +5712,7 @@
         <v>2.5</v>
       </c>
       <c r="V33">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W33">
         <v>1.08</v>
@@ -5724,7 +5724,7 @@
         <v>1.22</v>
       </c>
       <c r="Z33">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="AA33">
         <v>1.7</v>
@@ -5736,7 +5736,7 @@
         <v>2.75</v>
       </c>
       <c r="AD33">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AE33">
         <v>1.15</v>
@@ -5745,7 +5745,7 @@
         <v>1.62</v>
       </c>
       <c r="AG33">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5860,25 +5860,25 @@
         <v>3.89</v>
       </c>
       <c r="Q34">
-        <v>2.23</v>
+        <v>2.32</v>
       </c>
       <c r="R34">
         <v>2.38</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U34">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="V34">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X34">
         <v>0</v>
@@ -5890,19 +5890,19 @@
         <v>4.1</v>
       </c>
       <c r="AA34">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AB34">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AC34">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="AD34">
         <v>1.45</v>
       </c>
       <c r="AE34">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AF34">
         <v>1.54</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK34">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6512,46 +6512,46 @@
         <v>2.79</v>
       </c>
       <c r="Q38">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="R38">
         <v>2.25</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U38">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="V38">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z38">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="AA38">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AB38">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AC38">
         <v>2.75</v>
       </c>
       <c r="AD38">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE38">
         <v>1.12</v>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK38">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="O61">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="P61">
-        <v>6</v>
+        <v>7.09</v>
       </c>
       <c r="Q61">
         <v>1.83</v>
@@ -10276,34 +10276,34 @@
         <v>2.5</v>
       </c>
       <c r="V61">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W61">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X61">
         <v>1.04</v>
       </c>
       <c r="Y61">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="Z61">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="AA61">
         <v>1.72</v>
       </c>
       <c r="AB61">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AC61">
-        <v>2.61</v>
+        <v>2.8</v>
       </c>
       <c r="AD61">
         <v>1.4</v>
       </c>
       <c r="AE61">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AF61">
         <v>1.92</v>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="AK61">
-        <v>2.88</v>
+        <v>2.59</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10418,13 +10418,13 @@
         <v>1.98</v>
       </c>
       <c r="O62">
+        <v>3.4</v>
+      </c>
+      <c r="P62">
         <v>3.3</v>
       </c>
-      <c r="P62">
-        <v>3</v>
-      </c>
       <c r="Q62">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="R62">
         <v>2.33</v>
@@ -10445,7 +10445,7 @@
         <v>1.1</v>
       </c>
       <c r="X62">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y62">
         <v>1.25</v>
@@ -10457,7 +10457,7 @@
         <v>1.77</v>
       </c>
       <c r="AB62">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AC62">
         <v>2.68</v>
@@ -10466,13 +10466,13 @@
         <v>1.37</v>
       </c>
       <c r="AE62">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF62">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AG62">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AK62">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,64 +12045,64 @@
         </is>
       </c>
       <c r="N72">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="O72">
-        <v>4.75</v>
+        <v>5.35</v>
       </c>
       <c r="P72">
-        <v>8.199999999999999</v>
+        <v>6.17</v>
       </c>
       <c r="Q72">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="R72">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S72">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T72">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U72">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V72">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W72">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X72">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y72">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z72">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AA72">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AB72">
+        <v>2.48</v>
+      </c>
+      <c r="AC72">
         <v>2.25</v>
       </c>
-      <c r="AC72">
-        <v>0</v>
-      </c>
       <c r="AD72">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE72">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF72">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG72">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK72">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.19</v>
+        <v>1.95</v>
       </c>
       <c r="O73">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P73">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="Q73">
+        <v>2.46</v>
+      </c>
+      <c r="R73">
+        <v>2.38</v>
+      </c>
+      <c r="S73">
+        <v>1.31</v>
+      </c>
+      <c r="T73">
+        <v>3.3</v>
+      </c>
+      <c r="U73">
+        <v>2.4</v>
+      </c>
+      <c r="V73">
+        <v>1.5</v>
+      </c>
+      <c r="W73">
+        <v>1.07</v>
+      </c>
+      <c r="X73">
+        <v>1.03</v>
+      </c>
+      <c r="Y73">
+        <v>1.22</v>
+      </c>
+      <c r="Z73">
+        <v>3.85</v>
+      </c>
+      <c r="AA73">
+        <v>1.7</v>
+      </c>
+      <c r="AB73">
+        <v>2.03</v>
+      </c>
+      <c r="AC73">
         <v>2.8</v>
       </c>
-      <c r="R73">
-        <v>2.21</v>
-      </c>
-      <c r="S73">
-        <v>1.35</v>
-      </c>
-      <c r="T73">
-        <v>2.7</v>
-      </c>
-      <c r="U73">
-        <v>2.7</v>
-      </c>
-      <c r="V73">
-        <v>1.4</v>
-      </c>
-      <c r="W73">
-        <v>1.08</v>
-      </c>
-      <c r="X73">
-        <v>1.05</v>
-      </c>
-      <c r="Y73">
-        <v>1.3</v>
-      </c>
-      <c r="Z73">
-        <v>3.45</v>
-      </c>
-      <c r="AA73">
-        <v>1.93</v>
-      </c>
-      <c r="AB73">
-        <v>1.86</v>
-      </c>
-      <c r="AC73">
-        <v>3.35</v>
-      </c>
       <c r="AD73">
-        <v>1.31</v>
+        <v>1.46</v>
       </c>
       <c r="AE73">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AF73">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="AG73">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AK73">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,65 +12371,65 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.41</v>
+        <v>2.07</v>
       </c>
       <c r="O74">
-        <v>5.2</v>
+        <v>3.4</v>
       </c>
       <c r="P74">
-        <v>7.5</v>
+        <v>3.24</v>
       </c>
       <c r="Q74">
-        <v>1.69</v>
+        <v>2.52</v>
       </c>
       <c r="R74">
-        <v>2.63</v>
+        <v>2.12</v>
       </c>
       <c r="S74">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="T74">
-        <v>3.58</v>
+        <v>3.18</v>
       </c>
       <c r="U74">
+        <v>2.56</v>
+      </c>
+      <c r="V74">
+        <v>1.46</v>
+      </c>
+      <c r="W74">
+        <v>1.05</v>
+      </c>
+      <c r="X74">
+        <v>1.04</v>
+      </c>
+      <c r="Y74">
+        <v>1.25</v>
+      </c>
+      <c r="Z74">
+        <v>3.74</v>
+      </c>
+      <c r="AA74">
+        <v>1.78</v>
+      </c>
+      <c r="AB74">
+        <v>2.01</v>
+      </c>
+      <c r="AC74">
+        <v>2.83</v>
+      </c>
+      <c r="AD74">
+        <v>1.33</v>
+      </c>
+      <c r="AE74">
+        <v>1.13</v>
+      </c>
+      <c r="AF74">
+        <v>1.56</v>
+      </c>
+      <c r="AG74">
         <v>2.18</v>
       </c>
-      <c r="V74">
-        <v>1.6</v>
-      </c>
-      <c r="W74">
-        <v>1.17</v>
-      </c>
-      <c r="X74">
-        <v>1.02</v>
-      </c>
-      <c r="Y74">
-        <v>1.12</v>
-      </c>
-      <c r="Z74">
-        <v>4.95</v>
-      </c>
-      <c r="AA74">
-        <v>1.44</v>
-      </c>
-      <c r="AB74">
-        <v>2.48</v>
-      </c>
-      <c r="AC74">
-        <v>2.25</v>
-      </c>
-      <c r="AD74">
-        <v>1.62</v>
-      </c>
-      <c r="AE74">
-        <v>1.25</v>
-      </c>
-      <c r="AF74">
-        <v>1.81</v>
-      </c>
-      <c r="AG74">
-        <v>1.88</v>
-      </c>
       <c r="AH74" t="inlineStr">
         <is>
           <t>[]</t>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="AK74">
-        <v>3.24</v>
+        <v>1.61</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.93</v>
+        <v>1.43</v>
       </c>
       <c r="O75">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="P75">
-        <v>3.1</v>
+        <v>6.5</v>
       </c>
       <c r="Q75">
-        <v>2.47</v>
+        <v>1.97</v>
       </c>
       <c r="R75">
+        <v>2.18</v>
+      </c>
+      <c r="S75">
+        <v>1.29</v>
+      </c>
+      <c r="T75">
+        <v>3.3</v>
+      </c>
+      <c r="U75">
         <v>2.3</v>
       </c>
-      <c r="S75">
-        <v>1.31</v>
-      </c>
-      <c r="T75">
-        <v>3.02</v>
-      </c>
-      <c r="U75">
-        <v>2.2</v>
-      </c>
       <c r="V75">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W75">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X75">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y75">
+        <v>1.22</v>
+      </c>
+      <c r="Z75">
+        <v>3.55</v>
+      </c>
+      <c r="AA75">
+        <v>1.71</v>
+      </c>
+      <c r="AB75">
+        <v>1.94</v>
+      </c>
+      <c r="AC75">
+        <v>2.75</v>
+      </c>
+      <c r="AD75">
+        <v>1.35</v>
+      </c>
+      <c r="AE75">
         <v>1.18</v>
       </c>
-      <c r="Z75">
-        <v>3.85</v>
-      </c>
-      <c r="AA75">
-        <v>1.56</v>
-      </c>
-      <c r="AB75">
-        <v>2.03</v>
-      </c>
-      <c r="AC75">
-        <v>2.8</v>
-      </c>
-      <c r="AD75">
-        <v>1.36</v>
-      </c>
-      <c r="AE75">
-        <v>1.15</v>
-      </c>
       <c r="AF75">
-        <v>1.52</v>
+        <v>1.85</v>
       </c>
       <c r="AG75">
-        <v>2.28</v>
+        <v>1.85</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK75">
-        <v>1.73</v>
+        <v>2.73</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,80 +12697,80 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="O76">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="P76">
-        <v>3.05</v>
+        <v>2.75</v>
       </c>
       <c r="Q76">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="R76">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="S76">
+        <v>1.35</v>
+      </c>
+      <c r="T76">
+        <v>2.9</v>
+      </c>
+      <c r="U76">
+        <v>2.7</v>
+      </c>
+      <c r="V76">
+        <v>1.4</v>
+      </c>
+      <c r="W76">
+        <v>1.08</v>
+      </c>
+      <c r="X76">
+        <v>1.05</v>
+      </c>
+      <c r="Y76">
         <v>1.3</v>
       </c>
-      <c r="T76">
-        <v>3.08</v>
-      </c>
-      <c r="U76">
-        <v>2.56</v>
-      </c>
-      <c r="V76">
-        <v>1.44</v>
-      </c>
-      <c r="W76">
-        <v>1.11</v>
-      </c>
-      <c r="X76">
-        <v>1.04</v>
-      </c>
-      <c r="Y76">
+      <c r="Z76">
+        <v>3.45</v>
+      </c>
+      <c r="AA76">
+        <v>1.95</v>
+      </c>
+      <c r="AB76">
+        <v>1.82</v>
+      </c>
+      <c r="AC76">
+        <v>3.35</v>
+      </c>
+      <c r="AD76">
+        <v>1.31</v>
+      </c>
+      <c r="AE76">
+        <v>1.1</v>
+      </c>
+      <c r="AF76">
+        <v>1.7</v>
+      </c>
+      <c r="AG76">
+        <v>2</v>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ76">
         <v>1.25</v>
       </c>
-      <c r="Z76">
-        <v>3.75</v>
-      </c>
-      <c r="AA76">
-        <v>1.78</v>
-      </c>
-      <c r="AB76">
-        <v>2.01</v>
-      </c>
-      <c r="AC76">
-        <v>2.96</v>
-      </c>
-      <c r="AD76">
-        <v>1.37</v>
-      </c>
-      <c r="AE76">
-        <v>1.13</v>
-      </c>
-      <c r="AF76">
-        <v>1.62</v>
-      </c>
-      <c r="AG76">
-        <v>2.15</v>
-      </c>
-      <c r="AH76" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI76" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ76">
-        <v>1.29</v>
-      </c>
       <c r="AK76">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -13023,19 +13023,19 @@
         </is>
       </c>
       <c r="N78">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="O78">
-        <v>3.7</v>
+        <v>3.92</v>
       </c>
       <c r="P78">
-        <v>4.33</v>
+        <v>4.69</v>
       </c>
       <c r="Q78">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="R78">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="S78">
         <v>1.31</v>
@@ -13050,7 +13050,7 @@
         <v>1.46</v>
       </c>
       <c r="W78">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X78">
         <v>1.04</v>
@@ -13062,19 +13062,19 @@
         <v>4.09</v>
       </c>
       <c r="AA78">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AB78">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AC78">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="AD78">
         <v>1.4</v>
       </c>
       <c r="AE78">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AF78">
         <v>1.7</v>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK78">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -14004,7 +14004,7 @@
         <v>1.85</v>
       </c>
       <c r="O84">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P84">
         <v>4.2</v>
@@ -14022,28 +14022,28 @@
         <v>2.5</v>
       </c>
       <c r="U84">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="V84">
         <v>1.22</v>
       </c>
       <c r="W84">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X84">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="Y84">
         <v>1.47</v>
       </c>
       <c r="Z84">
-        <v>2.56</v>
+        <v>2.49</v>
       </c>
       <c r="AA84">
-        <v>2.42</v>
+        <v>2.16</v>
       </c>
       <c r="AB84">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AC84">
         <v>4.8</v>
@@ -14052,13 +14052,13 @@
         <v>1.2</v>
       </c>
       <c r="AE84">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AF84">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AG84">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14164,13 +14164,13 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="O85">
-        <v>3.68</v>
+        <v>3.8</v>
       </c>
       <c r="P85">
-        <v>4.73</v>
+        <v>4.8</v>
       </c>
       <c r="Q85">
         <v>0</v>
@@ -14327,13 +14327,13 @@
         </is>
       </c>
       <c r="N86">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="O86">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="P86">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="Q86">
         <v>2.05</v>
@@ -14348,10 +14348,10 @@
         <v>3.6</v>
       </c>
       <c r="U86">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="V86">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W86">
         <v>1.14</v>
@@ -14363,28 +14363,28 @@
         <v>1.14</v>
       </c>
       <c r="Z86">
-        <v>4.45</v>
+        <v>4.7</v>
       </c>
       <c r="AA86">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="AB86">
         <v>2.38</v>
       </c>
       <c r="AC86">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="AD86">
         <v>1.56</v>
       </c>
       <c r="AE86">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF86">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AG86">
-        <v>2.35</v>
+        <v>2.27</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="AK86">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -15142,19 +15142,19 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="O91">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="P91">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="Q91">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="R91">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="S91">
         <v>1.37</v>
@@ -15163,40 +15163,40 @@
         <v>2.75</v>
       </c>
       <c r="U91">
-        <v>2.82</v>
+        <v>2.93</v>
       </c>
       <c r="V91">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W91">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X91">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y91">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z91">
-        <v>3.1</v>
+        <v>3.38</v>
       </c>
       <c r="AA91">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB91">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AC91">
-        <v>3.41</v>
+        <v>3.2</v>
       </c>
       <c r="AD91">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE91">
         <v>1.06</v>
       </c>
       <c r="AF91">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AG91">
         <v>1.98</v>
@@ -15212,7 +15212,7 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AK91">
         <v>1.48</v>
@@ -15317,19 +15317,19 @@
         <v>2.5</v>
       </c>
       <c r="R92">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="S92">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="T92">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="U92">
-        <v>2.92</v>
+        <v>2.79</v>
       </c>
       <c r="V92">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W92">
         <v>1.04</v>
@@ -15338,31 +15338,31 @@
         <v>1.06</v>
       </c>
       <c r="Y92">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="Z92">
-        <v>2.97</v>
+        <v>3.4</v>
       </c>
       <c r="AA92">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="AB92">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AC92">
-        <v>3.8</v>
+        <v>2.95</v>
       </c>
       <c r="AD92">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AE92">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF92">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG92">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AK92">
-        <v>1.63</v>
+        <v>1.74</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15797,16 +15797,16 @@
         <v>1.28</v>
       </c>
       <c r="O95">
-        <v>4.95</v>
+        <v>5.5</v>
       </c>
       <c r="P95">
-        <v>8.5</v>
+        <v>8.25</v>
       </c>
       <c r="Q95">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="R95">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="S95">
         <v>1.2</v>
@@ -15815,10 +15815,10 @@
         <v>4</v>
       </c>
       <c r="U95">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="V95">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="W95">
         <v>1.17</v>
@@ -15827,10 +15827,10 @@
         <v>1.02</v>
       </c>
       <c r="Y95">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Z95">
-        <v>5.5</v>
+        <v>5.58</v>
       </c>
       <c r="AA95">
         <v>1.44</v>
@@ -15842,7 +15842,7 @@
         <v>2.15</v>
       </c>
       <c r="AD95">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AE95">
         <v>1.28</v>
@@ -15851,7 +15851,7 @@
         <v>1.75</v>
       </c>
       <c r="AG95">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AK95">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="AL95">
         <v>0</v>

--- a/jogos_2026-08-07.xlsx
+++ b/jogos_2026-08-07.xlsx
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="O5">
-        <v>3.9</v>
+        <v>5.25</v>
       </c>
       <c r="P5">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q5">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="R5">
-        <v>2.28</v>
+        <v>2.6</v>
       </c>
       <c r="S5">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="T5">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="U5">
-        <v>2.56</v>
+        <v>2.49</v>
       </c>
       <c r="V5">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W5">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X5">
         <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z5">
-        <v>3.82</v>
+        <v>4.4</v>
       </c>
       <c r="AA5">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AB5">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="AC5">
-        <v>2.93</v>
+        <v>2.63</v>
       </c>
       <c r="AD5">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE5">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF5">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AG5">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="AK5">
-        <v>2.4</v>
+        <v>3.01</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>3.02</v>
+        <v>1.75</v>
       </c>
       <c r="O6">
-        <v>3.07</v>
+        <v>3.23</v>
       </c>
       <c r="P6">
-        <v>1.91</v>
+        <v>3.75</v>
       </c>
       <c r="Q6">
-        <v>4.33</v>
+        <v>2.23</v>
       </c>
       <c r="R6">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S6">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="T6">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="U6">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="V6">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="W6">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X6">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y6">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="Z6">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AA6">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="AB6">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AC6">
-        <v>3.32</v>
+        <v>3.8</v>
       </c>
       <c r="AD6">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE6">
         <v>1.07</v>
       </c>
       <c r="AF6">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="AG6">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AK6">
-        <v>1.19</v>
+        <v>1.92</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,65 +1450,65 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.25</v>
+        <v>3.02</v>
       </c>
       <c r="O7">
-        <v>5.25</v>
+        <v>3.07</v>
       </c>
       <c r="P7">
-        <v>8</v>
+        <v>1.91</v>
       </c>
       <c r="Q7">
-        <v>1.7</v>
+        <v>4.33</v>
       </c>
       <c r="R7">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="S7">
+        <v>1.36</v>
+      </c>
+      <c r="T7">
+        <v>2.88</v>
+      </c>
+      <c r="U7">
+        <v>2.88</v>
+      </c>
+      <c r="V7">
+        <v>1.4</v>
+      </c>
+      <c r="W7">
+        <v>1.07</v>
+      </c>
+      <c r="X7">
+        <v>1.05</v>
+      </c>
+      <c r="Y7">
         <v>1.26</v>
       </c>
-      <c r="T7">
-        <v>3.25</v>
-      </c>
-      <c r="U7">
-        <v>2.49</v>
-      </c>
-      <c r="V7">
-        <v>1.5</v>
-      </c>
-      <c r="W7">
-        <v>1.13</v>
-      </c>
-      <c r="X7">
-        <v>1.02</v>
-      </c>
-      <c r="Y7">
-        <v>1.2</v>
-      </c>
       <c r="Z7">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="AA7">
-        <v>1.67</v>
+        <v>1.96</v>
       </c>
       <c r="AB7">
-        <v>2.2</v>
+        <v>1.81</v>
       </c>
       <c r="AC7">
-        <v>2.63</v>
+        <v>3.32</v>
       </c>
       <c r="AD7">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AE7">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AF7">
+        <v>1.76</v>
+      </c>
+      <c r="AG7">
         <v>1.91</v>
       </c>
-      <c r="AG7">
-        <v>1.65</v>
-      </c>
       <c r="AH7" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.09</v>
+        <v>1.3</v>
       </c>
       <c r="AK7">
-        <v>3.01</v>
+        <v>1.19</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="O8">
-        <v>3.23</v>
+        <v>3.9</v>
       </c>
       <c r="P8">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="Q8">
-        <v>2.23</v>
+        <v>2</v>
       </c>
       <c r="R8">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="S8">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="T8">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="U8">
-        <v>2.78</v>
+        <v>2.56</v>
       </c>
       <c r="V8">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="W8">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="X8">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y8">
-        <v>1.37</v>
+        <v>1.19</v>
       </c>
       <c r="Z8">
-        <v>3.1</v>
+        <v>3.82</v>
       </c>
       <c r="AA8">
-        <v>2.04</v>
+        <v>1.76</v>
       </c>
       <c r="AB8">
-        <v>1.73</v>
+        <v>2.02</v>
       </c>
       <c r="AC8">
-        <v>3.8</v>
+        <v>2.93</v>
       </c>
       <c r="AD8">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AE8">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF8">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AG8">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AK8">
-        <v>1.92</v>
+        <v>2.4</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.37</v>
+        <v>2.44</v>
       </c>
       <c r="O51">
-        <v>4.75</v>
+        <v>3.5</v>
       </c>
       <c r="P51">
-        <v>5.6</v>
+        <v>2.42</v>
       </c>
       <c r="Q51">
-        <v>1.81</v>
+        <v>2.8</v>
       </c>
       <c r="R51">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="S51">
         <v>1.22</v>
       </c>
       <c r="T51">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U51">
         <v>2.1</v>
       </c>
       <c r="V51">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="W51">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X51">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y51">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z51">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AA51">
+        <v>1.5</v>
+      </c>
+      <c r="AB51">
+        <v>2.45</v>
+      </c>
+      <c r="AC51">
+        <v>2.14</v>
+      </c>
+      <c r="AD51">
+        <v>1.62</v>
+      </c>
+      <c r="AE51">
+        <v>1.23</v>
+      </c>
+      <c r="AF51">
         <v>1.4</v>
       </c>
-      <c r="AB51">
-        <v>2.63</v>
-      </c>
-      <c r="AC51">
-        <v>2.09</v>
-      </c>
-      <c r="AD51">
-        <v>1.67</v>
-      </c>
-      <c r="AE51">
-        <v>1.24</v>
-      </c>
-      <c r="AF51">
-        <v>1.59</v>
-      </c>
       <c r="AG51">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.12</v>
+        <v>1.43</v>
       </c>
       <c r="AK51">
-        <v>2.72</v>
+        <v>1.42</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.44</v>
+        <v>1.37</v>
       </c>
       <c r="O52">
-        <v>3.5</v>
+        <v>4.75</v>
       </c>
       <c r="P52">
-        <v>2.42</v>
+        <v>5.6</v>
       </c>
       <c r="Q52">
-        <v>2.8</v>
+        <v>1.81</v>
       </c>
       <c r="R52">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="S52">
         <v>1.22</v>
       </c>
       <c r="T52">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U52">
         <v>2.1</v>
       </c>
       <c r="V52">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="W52">
+        <v>1.17</v>
+      </c>
+      <c r="X52">
+        <v>1.02</v>
+      </c>
+      <c r="Y52">
         <v>1.13</v>
       </c>
-      <c r="X52">
-        <v>1.03</v>
-      </c>
-      <c r="Y52">
-        <v>1.14</v>
-      </c>
       <c r="Z52">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AA52">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AB52">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="AC52">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="AD52">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AE52">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AF52">
-        <v>1.4</v>
+        <v>1.59</v>
       </c>
       <c r="AG52">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.43</v>
+        <v>1.12</v>
       </c>
       <c r="AK52">
-        <v>1.42</v>
+        <v>2.72</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="O73">
         <v>3.4</v>
       </c>
       <c r="P73">
-        <v>3.1</v>
+        <v>3.24</v>
       </c>
       <c r="Q73">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="R73">
-        <v>2.38</v>
+        <v>2.12</v>
       </c>
       <c r="S73">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="T73">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="U73">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="V73">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="W73">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X73">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y73">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z73">
-        <v>3.85</v>
+        <v>3.74</v>
       </c>
       <c r="AA73">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AB73">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="AC73">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="AD73">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AE73">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF73">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AG73">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK73">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
-        <v>2.07</v>
+        <v>1.43</v>
       </c>
       <c r="O74">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="P74">
-        <v>3.24</v>
+        <v>6.5</v>
       </c>
       <c r="Q74">
-        <v>2.52</v>
+        <v>1.97</v>
       </c>
       <c r="R74">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="S74">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T74">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="U74">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="V74">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="W74">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X74">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y74">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z74">
-        <v>3.74</v>
+        <v>3.55</v>
       </c>
       <c r="AA74">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="AB74">
-        <v>2.01</v>
+        <v>1.94</v>
       </c>
       <c r="AC74">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="AD74">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AE74">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AF74">
-        <v>1.56</v>
+        <v>1.85</v>
       </c>
       <c r="AG74">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AK74">
-        <v>1.61</v>
+        <v>2.73</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.43</v>
+        <v>2.3</v>
       </c>
       <c r="O75">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="P75">
-        <v>6.5</v>
+        <v>2.75</v>
       </c>
       <c r="Q75">
-        <v>1.97</v>
+        <v>2.8</v>
       </c>
       <c r="R75">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="S75">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="T75">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="U75">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="V75">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="W75">
         <v>1.08</v>
       </c>
       <c r="X75">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y75">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z75">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="AA75">
-        <v>1.71</v>
+        <v>1.95</v>
       </c>
       <c r="AB75">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="AC75">
-        <v>2.75</v>
+        <v>3.35</v>
       </c>
       <c r="AD75">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AE75">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AF75">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AG75">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK75">
-        <v>2.73</v>
+        <v>1.53</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="O76">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P76">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="Q76">
+        <v>2.46</v>
+      </c>
+      <c r="R76">
+        <v>2.38</v>
+      </c>
+      <c r="S76">
+        <v>1.31</v>
+      </c>
+      <c r="T76">
+        <v>3.3</v>
+      </c>
+      <c r="U76">
+        <v>2.4</v>
+      </c>
+      <c r="V76">
+        <v>1.5</v>
+      </c>
+      <c r="W76">
+        <v>1.07</v>
+      </c>
+      <c r="X76">
+        <v>1.03</v>
+      </c>
+      <c r="Y76">
+        <v>1.22</v>
+      </c>
+      <c r="Z76">
+        <v>3.85</v>
+      </c>
+      <c r="AA76">
+        <v>1.7</v>
+      </c>
+      <c r="AB76">
+        <v>2.03</v>
+      </c>
+      <c r="AC76">
         <v>2.8</v>
       </c>
-      <c r="R76">
-        <v>2.21</v>
-      </c>
-      <c r="S76">
-        <v>1.35</v>
-      </c>
-      <c r="T76">
-        <v>2.9</v>
-      </c>
-      <c r="U76">
-        <v>2.7</v>
-      </c>
-      <c r="V76">
-        <v>1.4</v>
-      </c>
-      <c r="W76">
-        <v>1.08</v>
-      </c>
-      <c r="X76">
-        <v>1.05</v>
-      </c>
-      <c r="Y76">
-        <v>1.3</v>
-      </c>
-      <c r="Z76">
-        <v>3.45</v>
-      </c>
-      <c r="AA76">
-        <v>1.95</v>
-      </c>
-      <c r="AB76">
-        <v>1.82</v>
-      </c>
-      <c r="AC76">
-        <v>3.35</v>
-      </c>
       <c r="AD76">
-        <v>1.31</v>
+        <v>1.46</v>
       </c>
       <c r="AE76">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AF76">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AG76">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK76">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AL76">
         <v>0</v>

--- a/jogos_2026-08-07.xlsx
+++ b/jogos_2026-08-07.xlsx
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,61 +1450,61 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.02</v>
+        <v>1.53</v>
       </c>
       <c r="O7">
-        <v>3.07</v>
+        <v>3.9</v>
       </c>
       <c r="P7">
-        <v>1.91</v>
+        <v>5</v>
       </c>
       <c r="Q7">
-        <v>4.33</v>
+        <v>2</v>
       </c>
       <c r="R7">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="S7">
+        <v>1.3</v>
+      </c>
+      <c r="T7">
+        <v>3.1</v>
+      </c>
+      <c r="U7">
+        <v>2.56</v>
+      </c>
+      <c r="V7">
+        <v>1.44</v>
+      </c>
+      <c r="W7">
+        <v>1.11</v>
+      </c>
+      <c r="X7">
+        <v>1.02</v>
+      </c>
+      <c r="Y7">
+        <v>1.19</v>
+      </c>
+      <c r="Z7">
+        <v>3.82</v>
+      </c>
+      <c r="AA7">
+        <v>1.76</v>
+      </c>
+      <c r="AB7">
+        <v>2.02</v>
+      </c>
+      <c r="AC7">
+        <v>2.93</v>
+      </c>
+      <c r="AD7">
         <v>1.36</v>
       </c>
-      <c r="T7">
-        <v>2.88</v>
-      </c>
-      <c r="U7">
-        <v>2.88</v>
-      </c>
-      <c r="V7">
-        <v>1.4</v>
-      </c>
-      <c r="W7">
-        <v>1.07</v>
-      </c>
-      <c r="X7">
-        <v>1.05</v>
-      </c>
-      <c r="Y7">
-        <v>1.26</v>
-      </c>
-      <c r="Z7">
-        <v>3.2</v>
-      </c>
-      <c r="AA7">
-        <v>1.96</v>
-      </c>
-      <c r="AB7">
-        <v>1.81</v>
-      </c>
-      <c r="AC7">
-        <v>3.32</v>
-      </c>
-      <c r="AD7">
-        <v>1.3</v>
-      </c>
       <c r="AE7">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF7">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AG7">
         <v>1.91</v>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AK7">
-        <v>1.19</v>
+        <v>2.4</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,61 +1613,61 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.53</v>
+        <v>3.02</v>
       </c>
       <c r="O8">
-        <v>3.9</v>
+        <v>3.07</v>
       </c>
       <c r="P8">
-        <v>5</v>
+        <v>1.91</v>
       </c>
       <c r="Q8">
-        <v>2</v>
+        <v>4.33</v>
       </c>
       <c r="R8">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="S8">
+        <v>1.36</v>
+      </c>
+      <c r="T8">
+        <v>2.88</v>
+      </c>
+      <c r="U8">
+        <v>2.88</v>
+      </c>
+      <c r="V8">
+        <v>1.4</v>
+      </c>
+      <c r="W8">
+        <v>1.07</v>
+      </c>
+      <c r="X8">
+        <v>1.05</v>
+      </c>
+      <c r="Y8">
+        <v>1.26</v>
+      </c>
+      <c r="Z8">
+        <v>3.2</v>
+      </c>
+      <c r="AA8">
+        <v>1.96</v>
+      </c>
+      <c r="AB8">
+        <v>1.81</v>
+      </c>
+      <c r="AC8">
+        <v>3.32</v>
+      </c>
+      <c r="AD8">
         <v>1.3</v>
       </c>
-      <c r="T8">
-        <v>3.1</v>
-      </c>
-      <c r="U8">
-        <v>2.56</v>
-      </c>
-      <c r="V8">
-        <v>1.44</v>
-      </c>
-      <c r="W8">
-        <v>1.11</v>
-      </c>
-      <c r="X8">
-        <v>1.02</v>
-      </c>
-      <c r="Y8">
-        <v>1.19</v>
-      </c>
-      <c r="Z8">
-        <v>3.82</v>
-      </c>
-      <c r="AA8">
+      <c r="AE8">
+        <v>1.07</v>
+      </c>
+      <c r="AF8">
         <v>1.76</v>
-      </c>
-      <c r="AB8">
-        <v>2.02</v>
-      </c>
-      <c r="AC8">
-        <v>2.93</v>
-      </c>
-      <c r="AD8">
-        <v>1.36</v>
-      </c>
-      <c r="AE8">
-        <v>1.13</v>
-      </c>
-      <c r="AF8">
-        <v>1.8</v>
       </c>
       <c r="AG8">
         <v>1.91</v>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AK8">
-        <v>2.4</v>
+        <v>1.19</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.43</v>
+        <v>2.3</v>
       </c>
       <c r="O74">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="P74">
-        <v>6.5</v>
+        <v>2.75</v>
       </c>
       <c r="Q74">
-        <v>1.97</v>
+        <v>2.8</v>
       </c>
       <c r="R74">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="S74">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="T74">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="U74">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="V74">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="W74">
         <v>1.08</v>
       </c>
       <c r="X74">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y74">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z74">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="AA74">
-        <v>1.71</v>
+        <v>1.95</v>
       </c>
       <c r="AB74">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="AC74">
-        <v>2.75</v>
+        <v>3.35</v>
       </c>
       <c r="AD74">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AE74">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AF74">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AG74">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK74">
-        <v>2.73</v>
+        <v>1.53</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="O75">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P75">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="Q75">
+        <v>2.46</v>
+      </c>
+      <c r="R75">
+        <v>2.38</v>
+      </c>
+      <c r="S75">
+        <v>1.31</v>
+      </c>
+      <c r="T75">
+        <v>3.3</v>
+      </c>
+      <c r="U75">
+        <v>2.4</v>
+      </c>
+      <c r="V75">
+        <v>1.5</v>
+      </c>
+      <c r="W75">
+        <v>1.07</v>
+      </c>
+      <c r="X75">
+        <v>1.03</v>
+      </c>
+      <c r="Y75">
+        <v>1.22</v>
+      </c>
+      <c r="Z75">
+        <v>3.85</v>
+      </c>
+      <c r="AA75">
+        <v>1.7</v>
+      </c>
+      <c r="AB75">
+        <v>2.03</v>
+      </c>
+      <c r="AC75">
         <v>2.8</v>
       </c>
-      <c r="R75">
-        <v>2.21</v>
-      </c>
-      <c r="S75">
-        <v>1.35</v>
-      </c>
-      <c r="T75">
-        <v>2.9</v>
-      </c>
-      <c r="U75">
-        <v>2.7</v>
-      </c>
-      <c r="V75">
-        <v>1.4</v>
-      </c>
-      <c r="W75">
-        <v>1.08</v>
-      </c>
-      <c r="X75">
-        <v>1.05</v>
-      </c>
-      <c r="Y75">
-        <v>1.3</v>
-      </c>
-      <c r="Z75">
-        <v>3.45</v>
-      </c>
-      <c r="AA75">
-        <v>1.95</v>
-      </c>
-      <c r="AB75">
-        <v>1.82</v>
-      </c>
-      <c r="AC75">
-        <v>3.35</v>
-      </c>
       <c r="AD75">
-        <v>1.31</v>
+        <v>1.46</v>
       </c>
       <c r="AE75">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AF75">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AG75">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK75">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
-        <v>1.95</v>
+        <v>1.43</v>
       </c>
       <c r="O76">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="P76">
-        <v>3.1</v>
+        <v>6.5</v>
       </c>
       <c r="Q76">
-        <v>2.46</v>
+        <v>1.97</v>
       </c>
       <c r="R76">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="S76">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="T76">
         <v>3.3</v>
       </c>
       <c r="U76">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="V76">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W76">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X76">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y76">
         <v>1.22</v>
       </c>
       <c r="Z76">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="AA76">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AB76">
-        <v>2.03</v>
+        <v>1.94</v>
       </c>
       <c r="AC76">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AD76">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="AE76">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF76">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AG76">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK76">
-        <v>1.73</v>
+        <v>2.73</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -14022,7 +14022,7 @@
         <v>2.5</v>
       </c>
       <c r="U84">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="V84">
         <v>1.22</v>
@@ -14031,16 +14031,16 @@
         <v>1.02</v>
       </c>
       <c r="X84">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="Y84">
         <v>1.47</v>
       </c>
       <c r="Z84">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="AA84">
-        <v>2.16</v>
+        <v>2.56</v>
       </c>
       <c r="AB84">
         <v>1.44</v>
@@ -14049,10 +14049,10 @@
         <v>4.8</v>
       </c>
       <c r="AD84">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AE84">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF84">
         <v>2.2</v>

--- a/jogos_2026-08-07.xlsx
+++ b/jogos_2026-08-07.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>3.7</v>
+        <v>3.78</v>
       </c>
       <c r="O2">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="P2">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="Q2">
         <v>4</v>
@@ -653,7 +653,7 @@
         <v>1.42</v>
       </c>
       <c r="T2">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="U2">
         <v>2.94</v>
@@ -671,7 +671,7 @@
         <v>1.33</v>
       </c>
       <c r="Z2">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="AA2">
         <v>2.08</v>
@@ -680,19 +680,19 @@
         <v>1.76</v>
       </c>
       <c r="AC2">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AD2">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE2">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF2">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AG2">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="O3">
         <v>3.3</v>
       </c>
       <c r="P3">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="Q3">
         <v>3.4</v>
@@ -834,28 +834,28 @@
         <v>1.22</v>
       </c>
       <c r="Z3">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="AA3">
         <v>1.8</v>
       </c>
       <c r="AB3">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AC3">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="AD3">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AE3">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF3">
         <v>1.6</v>
       </c>
       <c r="AG3">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -964,28 +964,28 @@
         <v>3.7</v>
       </c>
       <c r="O4">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P4">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="Q4">
-        <v>3.69</v>
+        <v>4.5</v>
       </c>
       <c r="R4">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="S4">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T4">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="U4">
-        <v>2.64</v>
+        <v>2.61</v>
       </c>
       <c r="V4">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W4">
         <v>1.07</v>
@@ -997,25 +997,25 @@
         <v>1.24</v>
       </c>
       <c r="Z4">
-        <v>3.83</v>
+        <v>3.98</v>
       </c>
       <c r="AA4">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="AB4">
         <v>1.98</v>
       </c>
       <c r="AC4">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="AD4">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AE4">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF4">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AG4">
         <v>2.1</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
+        <v>3.75</v>
+      </c>
+      <c r="O5">
+        <v>3.6</v>
+      </c>
+      <c r="P5">
+        <v>1.84</v>
+      </c>
+      <c r="Q5">
+        <v>4.33</v>
+      </c>
+      <c r="R5">
+        <v>2.27</v>
+      </c>
+      <c r="S5">
+        <v>1.35</v>
+      </c>
+      <c r="T5">
+        <v>2.9</v>
+      </c>
+      <c r="U5">
+        <v>2.88</v>
+      </c>
+      <c r="V5">
+        <v>1.4</v>
+      </c>
+      <c r="W5">
+        <v>1.07</v>
+      </c>
+      <c r="X5">
+        <v>1.05</v>
+      </c>
+      <c r="Y5">
         <v>1.25</v>
       </c>
-      <c r="O5">
-        <v>5.25</v>
-      </c>
-      <c r="P5">
-        <v>8</v>
-      </c>
-      <c r="Q5">
-        <v>1.7</v>
-      </c>
-      <c r="R5">
-        <v>2.6</v>
-      </c>
-      <c r="S5">
-        <v>1.26</v>
-      </c>
-      <c r="T5">
-        <v>3.25</v>
-      </c>
-      <c r="U5">
-        <v>2.49</v>
-      </c>
-      <c r="V5">
-        <v>1.5</v>
-      </c>
-      <c r="W5">
-        <v>1.13</v>
-      </c>
-      <c r="X5">
-        <v>1.02</v>
-      </c>
-      <c r="Y5">
-        <v>1.2</v>
-      </c>
       <c r="Z5">
-        <v>4.4</v>
+        <v>3.28</v>
       </c>
       <c r="AA5">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AB5">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AC5">
-        <v>2.63</v>
+        <v>3.19</v>
       </c>
       <c r="AD5">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AE5">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF5">
-        <v>1.91</v>
+        <v>1.68</v>
       </c>
       <c r="AG5">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.09</v>
+        <v>1.3</v>
       </c>
       <c r="AK5">
-        <v>3.01</v>
+        <v>1.19</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="O6">
-        <v>3.23</v>
+        <v>3.5</v>
       </c>
       <c r="P6">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="Q6">
         <v>2.23</v>
@@ -1308,7 +1308,7 @@
         <v>2.75</v>
       </c>
       <c r="U6">
-        <v>2.78</v>
+        <v>3.14</v>
       </c>
       <c r="V6">
         <v>1.33</v>
@@ -1317,16 +1317,16 @@
         <v>1.03</v>
       </c>
       <c r="X6">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Z6">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="AA6">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="AB6">
         <v>1.73</v>
@@ -1335,10 +1335,10 @@
         <v>3.8</v>
       </c>
       <c r="AD6">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE6">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF6">
         <v>1.9</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK6">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="O7">
-        <v>3.9</v>
+        <v>5.25</v>
       </c>
       <c r="P7">
-        <v>5</v>
+        <v>7.3</v>
       </c>
       <c r="Q7">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="R7">
-        <v>2.28</v>
+        <v>2.6</v>
       </c>
       <c r="S7">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="T7">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="U7">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="V7">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W7">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X7">
         <v>1.02</v>
       </c>
       <c r="Y7">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z7">
-        <v>3.82</v>
+        <v>4.4</v>
       </c>
       <c r="AA7">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="AB7">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="AC7">
-        <v>2.93</v>
+        <v>2.59</v>
       </c>
       <c r="AD7">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AE7">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF7">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AG7">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="AK7">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.02</v>
+        <v>1.5</v>
       </c>
       <c r="O8">
-        <v>3.07</v>
+        <v>3.9</v>
       </c>
       <c r="P8">
-        <v>1.91</v>
+        <v>5</v>
       </c>
       <c r="Q8">
-        <v>4.33</v>
+        <v>2</v>
       </c>
       <c r="R8">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="S8">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T8">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="U8">
-        <v>2.88</v>
+        <v>2.53</v>
       </c>
       <c r="V8">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W8">
         <v>1.07</v>
       </c>
       <c r="X8">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y8">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="Z8">
-        <v>3.2</v>
+        <v>3.84</v>
       </c>
       <c r="AA8">
-        <v>1.96</v>
+        <v>1.76</v>
       </c>
       <c r="AB8">
-        <v>1.81</v>
+        <v>1.97</v>
       </c>
       <c r="AC8">
-        <v>3.32</v>
+        <v>2.95</v>
       </c>
       <c r="AD8">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AE8">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF8">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AG8">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AK8">
-        <v>1.19</v>
+        <v>2.26</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1779,43 +1779,43 @@
         <v>2.4</v>
       </c>
       <c r="O9">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P9">
         <v>2.87</v>
       </c>
       <c r="Q9">
-        <v>2.99</v>
+        <v>3.02</v>
       </c>
       <c r="R9">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="S9">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T9">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="U9">
-        <v>2.97</v>
+        <v>2.98</v>
       </c>
       <c r="V9">
         <v>1.37</v>
       </c>
       <c r="W9">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X9">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y9">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z9">
         <v>3.4</v>
       </c>
       <c r="AA9">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="AB9">
         <v>1.74</v>
@@ -1827,7 +1827,7 @@
         <v>1.29</v>
       </c>
       <c r="AE9">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF9">
         <v>1.75</v>
@@ -1948,10 +1948,10 @@
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R10">
-        <v>2.85</v>
+        <v>2.71</v>
       </c>
       <c r="S10">
         <v>1.2</v>
@@ -1963,7 +1963,7 @@
         <v>1.99</v>
       </c>
       <c r="V10">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="W10">
         <v>1.18</v>
@@ -1972,31 +1972,31 @@
         <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z10">
-        <v>6.25</v>
+        <v>6.65</v>
       </c>
       <c r="AA10">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AB10">
         <v>2.95</v>
       </c>
       <c r="AC10">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="AD10">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AE10">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AF10">
         <v>1.53</v>
       </c>
       <c r="AG10">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2757,13 +2757,13 @@
         <v>1.65</v>
       </c>
       <c r="O15">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="P15">
-        <v>4.73</v>
+        <v>4.47</v>
       </c>
       <c r="Q15">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="R15">
         <v>2.3</v>
@@ -2772,13 +2772,13 @@
         <v>1.31</v>
       </c>
       <c r="T15">
-        <v>2.97</v>
+        <v>3.15</v>
       </c>
       <c r="U15">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="V15">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W15">
         <v>1.07</v>
@@ -2793,16 +2793,16 @@
         <v>3.9</v>
       </c>
       <c r="AA15">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AB15">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AC15">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AD15">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE15">
         <v>1.14</v>
@@ -2827,7 +2827,7 @@
         <v>1.25</v>
       </c>
       <c r="AK15">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2929,7 +2929,7 @@
         <v>3.14</v>
       </c>
       <c r="R16">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="S16">
         <v>1.3</v>
@@ -2944,7 +2944,7 @@
         <v>1.48</v>
       </c>
       <c r="W16">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X16">
         <v>1.04</v>
@@ -2968,7 +2968,7 @@
         <v>1.4</v>
       </c>
       <c r="AE16">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AF16">
         <v>1.57</v>
@@ -3080,34 +3080,34 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="O17">
         <v>3.25</v>
       </c>
       <c r="P17">
-        <v>3.1</v>
+        <v>3.76</v>
       </c>
       <c r="Q17">
-        <v>2.63</v>
+        <v>2.49</v>
       </c>
       <c r="R17">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="S17">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="T17">
-        <v>2.67</v>
+        <v>2.53</v>
       </c>
       <c r="U17">
-        <v>2.79</v>
+        <v>2.88</v>
       </c>
       <c r="V17">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W17">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X17">
         <v>1.06</v>
@@ -3116,13 +3116,13 @@
         <v>1.3</v>
       </c>
       <c r="Z17">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AA17">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="AB17">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC17">
         <v>3.5</v>
@@ -3134,7 +3134,7 @@
         <v>1.08</v>
       </c>
       <c r="AF17">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG17">
         <v>1.95</v>
@@ -3153,7 +3153,7 @@
         <v>1.33</v>
       </c>
       <c r="AK17">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="O18">
         <v>3.8</v>
@@ -3252,13 +3252,13 @@
         <v>4.3</v>
       </c>
       <c r="Q18">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="R18">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="S18">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T18">
         <v>3.15</v>
@@ -3294,13 +3294,13 @@
         <v>1.36</v>
       </c>
       <c r="AE18">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF18">
         <v>1.67</v>
       </c>
       <c r="AG18">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AK18">
         <v>2.05</v>
@@ -3895,25 +3895,25 @@
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Q22">
-        <v>4.4</v>
+        <v>5.35</v>
       </c>
       <c r="R22">
         <v>2.3</v>
       </c>
       <c r="S22">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T22">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="U22">
         <v>2.6</v>
@@ -3922,25 +3922,25 @@
         <v>1.4</v>
       </c>
       <c r="W22">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X22">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y22">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z22">
-        <v>3.75</v>
+        <v>3.58</v>
       </c>
       <c r="AA22">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AB22">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC22">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AD22">
         <v>1.36</v>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK22">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,34 +4058,34 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="Q23">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="R23">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S23">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T23">
-        <v>2.79</v>
+        <v>3</v>
       </c>
       <c r="U23">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="V23">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W23">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X23">
         <v>1.05</v>
@@ -4094,22 +4094,22 @@
         <v>1.25</v>
       </c>
       <c r="Z23">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AA23">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AB23">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AC23">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AD23">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AE23">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AF23">
         <v>1.85</v>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK23">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,31 +4221,31 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="Q24">
+        <v>2</v>
+      </c>
+      <c r="R24">
         <v>2.4</v>
       </c>
-      <c r="R24">
+      <c r="S24">
+        <v>1.29</v>
+      </c>
+      <c r="T24">
+        <v>3.08</v>
+      </c>
+      <c r="U24">
         <v>2.38</v>
       </c>
-      <c r="S24">
-        <v>1.28</v>
-      </c>
-      <c r="T24">
-        <v>3.12</v>
-      </c>
-      <c r="U24">
-        <v>2.41</v>
-      </c>
       <c r="V24">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="W24">
         <v>1.07</v>
@@ -4257,28 +4257,28 @@
         <v>1.2</v>
       </c>
       <c r="Z24">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="AA24">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AB24">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AC24">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AD24">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AE24">
         <v>1.17</v>
       </c>
       <c r="AF24">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AG24">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="AK24">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,80 +4384,80 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q25">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="R25">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="S25">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T25">
-        <v>3.14</v>
+        <v>2.83</v>
       </c>
       <c r="U25">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="V25">
-        <v>1.57</v>
+        <v>1.41</v>
       </c>
       <c r="W25">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X25">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y25">
+        <v>1.25</v>
+      </c>
+      <c r="Z25">
+        <v>3.5</v>
+      </c>
+      <c r="AA25">
+        <v>1.85</v>
+      </c>
+      <c r="AB25">
+        <v>1.95</v>
+      </c>
+      <c r="AC25">
+        <v>3.1</v>
+      </c>
+      <c r="AD25">
+        <v>1.3</v>
+      </c>
+      <c r="AE25">
+        <v>1.11</v>
+      </c>
+      <c r="AF25">
+        <v>1.85</v>
+      </c>
+      <c r="AG25">
+        <v>1.85</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ25">
         <v>1.18</v>
       </c>
-      <c r="Z25">
-        <v>4.5</v>
-      </c>
-      <c r="AA25">
-        <v>1.57</v>
-      </c>
-      <c r="AB25">
-        <v>2.25</v>
-      </c>
-      <c r="AC25">
-        <v>2.5</v>
-      </c>
-      <c r="AD25">
-        <v>1.44</v>
-      </c>
-      <c r="AE25">
-        <v>1.18</v>
-      </c>
-      <c r="AF25">
-        <v>1.62</v>
-      </c>
-      <c r="AG25">
-        <v>2.15</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ25">
-        <v>1.22</v>
-      </c>
       <c r="AK25">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G26">
@@ -4556,10 +4556,10 @@
         <v>0</v>
       </c>
       <c r="Q26">
-        <v>2.1</v>
+        <v>2.41</v>
       </c>
       <c r="R26">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="S26">
         <v>1.3</v>
@@ -4568,43 +4568,43 @@
         <v>3.2</v>
       </c>
       <c r="U26">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="V26">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W26">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X26">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y26">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z26">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="AA26">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AB26">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC26">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="AD26">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AE26">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF26">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AG26">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         <v>1.22</v>
       </c>
       <c r="AK26">
-        <v>2.3</v>
+        <v>1.78</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="O27">
         <v>4.33</v>
@@ -4882,10 +4882,10 @@
         <v>3.56</v>
       </c>
       <c r="Q28">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="R28">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="S28">
         <v>1.25</v>
@@ -4915,22 +4915,22 @@
         <v>1.53</v>
       </c>
       <c r="AB28">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AC28">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="AD28">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AE28">
         <v>1.22</v>
       </c>
       <c r="AF28">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AG28">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="O29">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="P29">
-        <v>2.9</v>
+        <v>2.69</v>
       </c>
       <c r="Q29">
         <v>3.3</v>
@@ -5069,16 +5069,16 @@
         <v>1.04</v>
       </c>
       <c r="Y29">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="Z29">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="AA29">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="AB29">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AC29">
         <v>4.15</v>
@@ -5090,10 +5090,10 @@
         <v>1.01</v>
       </c>
       <c r="AF29">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AG29">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="O30">
         <v>3.3</v>
       </c>
       <c r="P30">
-        <v>2.52</v>
+        <v>2.65</v>
       </c>
       <c r="Q30">
         <v>3.02</v>
@@ -5217,13 +5217,13 @@
         <v>1.33</v>
       </c>
       <c r="T30">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="U30">
         <v>2.62</v>
       </c>
       <c r="V30">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W30">
         <v>1.07</v>
@@ -5232,25 +5232,25 @@
         <v>1.05</v>
       </c>
       <c r="Y30">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z30">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="AA30">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AB30">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="AC30">
-        <v>3.13</v>
+        <v>2.78</v>
       </c>
       <c r="AD30">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE30">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF30">
         <v>1.62</v>
@@ -5525,25 +5525,25 @@
         </is>
       </c>
       <c r="N32">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O32">
-        <v>3.45</v>
+        <v>3.46</v>
       </c>
       <c r="P32">
-        <v>2.07</v>
+        <v>2.19</v>
       </c>
       <c r="Q32">
-        <v>3.22</v>
+        <v>3.13</v>
       </c>
       <c r="R32">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="S32">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T32">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U32">
         <v>2.38</v>
@@ -5555,7 +5555,7 @@
         <v>1.13</v>
       </c>
       <c r="X32">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y32">
         <v>1.2</v>
@@ -5567,10 +5567,10 @@
         <v>1.61</v>
       </c>
       <c r="AB32">
-        <v>1.84</v>
+        <v>2.11</v>
       </c>
       <c r="AC32">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="AD32">
         <v>1.33</v>
@@ -5579,7 +5579,7 @@
         <v>1.14</v>
       </c>
       <c r="AF32">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AG32">
         <v>2.25</v>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AK32">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.92</v>
+        <v>2.68</v>
       </c>
       <c r="O36">
-        <v>3.61</v>
+        <v>3.4</v>
       </c>
       <c r="P36">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="Q36">
         <v>3.3</v>
@@ -6195,7 +6195,7 @@
         <v>1.27</v>
       </c>
       <c r="T36">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="U36">
         <v>2.34</v>
@@ -6204,10 +6204,10 @@
         <v>1.53</v>
       </c>
       <c r="W36">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X36">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y36">
         <v>1.15</v>
@@ -6216,7 +6216,7 @@
         <v>4.6</v>
       </c>
       <c r="AA36">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AB36">
         <v>2.26</v>
@@ -6231,7 +6231,7 @@
         <v>1.19</v>
       </c>
       <c r="AF36">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AG36">
         <v>2.39</v>
@@ -6343,10 +6343,10 @@
         <v>2.03</v>
       </c>
       <c r="O37">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P37">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="Q37">
         <v>2.8</v>
@@ -6355,7 +6355,7 @@
         <v>2.05</v>
       </c>
       <c r="S37">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T37">
         <v>2.6</v>
@@ -6397,7 +6397,7 @@
         <v>1.85</v>
       </c>
       <c r="AG37">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="O39">
         <v>3.5</v>
       </c>
       <c r="P39">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="Q39">
         <v>2.32</v>
@@ -6699,31 +6699,31 @@
         <v>1.03</v>
       </c>
       <c r="Y39">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="Z39">
-        <v>4.65</v>
+        <v>4.8</v>
       </c>
       <c r="AA39">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AB39">
         <v>2.3</v>
       </c>
       <c r="AC39">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="AD39">
         <v>1.53</v>
       </c>
       <c r="AE39">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AF39">
         <v>1.5</v>
       </c>
       <c r="AG39">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6829,25 +6829,25 @@
         </is>
       </c>
       <c r="N40">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="O40">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P40">
         <v>1.91</v>
       </c>
       <c r="Q40">
-        <v>3.3</v>
+        <v>3.84</v>
       </c>
       <c r="R40">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="S40">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T40">
-        <v>4</v>
+        <v>3.58</v>
       </c>
       <c r="U40">
         <v>2.15</v>
@@ -6880,7 +6880,7 @@
         <v>1.64</v>
       </c>
       <c r="AE40">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF40">
         <v>1.41</v>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AK40">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="O41">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="P41">
-        <v>5.7</v>
+        <v>5.68</v>
       </c>
       <c r="Q41">
         <v>1.83</v>
@@ -7007,7 +7007,7 @@
         <v>2.7</v>
       </c>
       <c r="S41">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="T41">
         <v>4</v>
@@ -7019,7 +7019,7 @@
         <v>1.71</v>
       </c>
       <c r="W41">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X41">
         <v>1.01</v>
@@ -7031,16 +7031,16 @@
         <v>5.65</v>
       </c>
       <c r="AA41">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AB41">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AC41">
         <v>1.95</v>
       </c>
       <c r="AD41">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AE41">
         <v>1.3</v>
@@ -7062,7 +7062,7 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AK41">
         <v>2.53</v>
@@ -7164,55 +7164,55 @@
         <v>6</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y42">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK42">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,7 +7318,7 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="O43">
         <v>3.12</v>
@@ -7363,13 +7363,13 @@
         <v>1.7</v>
       </c>
       <c r="AC43">
-        <v>3.65</v>
+        <v>3.48</v>
       </c>
       <c r="AD43">
         <v>1.22</v>
       </c>
       <c r="AE43">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF43">
         <v>1.81</v>
@@ -7481,49 +7481,49 @@
         </is>
       </c>
       <c r="N44">
+        <v>2.3</v>
+      </c>
+      <c r="O44">
+        <v>3.7</v>
+      </c>
+      <c r="P44">
+        <v>2.61</v>
+      </c>
+      <c r="Q44">
+        <v>3.01</v>
+      </c>
+      <c r="R44">
         <v>2.45</v>
       </c>
-      <c r="O44">
-        <v>3.6</v>
-      </c>
-      <c r="P44">
-        <v>2.5</v>
-      </c>
-      <c r="Q44">
-        <v>3.03</v>
-      </c>
-      <c r="R44">
-        <v>2.43</v>
-      </c>
       <c r="S44">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T44">
         <v>3.45</v>
       </c>
       <c r="U44">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="V44">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="W44">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X44">
         <v>1.04</v>
       </c>
       <c r="Y44">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z44">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="AA44">
         <v>1.61</v>
       </c>
       <c r="AB44">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AC44">
         <v>2.55</v>
@@ -7535,10 +7535,10 @@
         <v>1.2</v>
       </c>
       <c r="AF44">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AG44">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7807,22 +7807,22 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="O46">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="P46">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Q46">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="R46">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="S46">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="T46">
         <v>4</v>
@@ -7834,7 +7834,7 @@
         <v>1.7</v>
       </c>
       <c r="W46">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X46">
         <v>1.02</v>
@@ -7846,7 +7846,7 @@
         <v>5.55</v>
       </c>
       <c r="AA46">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AB46">
         <v>2.62</v>
@@ -7864,7 +7864,7 @@
         <v>1.57</v>
       </c>
       <c r="AG46">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
         <v>1.14</v>
       </c>
       <c r="AK46">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.63</v>
+        <v>2.78</v>
       </c>
       <c r="O47">
         <v>3.35</v>
       </c>
       <c r="P47">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="Q47">
         <v>3</v>
@@ -7991,13 +7991,13 @@
         <v>3.25</v>
       </c>
       <c r="U47">
-        <v>2.37</v>
+        <v>2.32</v>
       </c>
       <c r="V47">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="W47">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X47">
         <v>1.03</v>
@@ -8006,7 +8006,7 @@
         <v>1.15</v>
       </c>
       <c r="Z47">
-        <v>4.25</v>
+        <v>4.6</v>
       </c>
       <c r="AA47">
         <v>1.62</v>
@@ -8024,7 +8024,7 @@
         <v>1.16</v>
       </c>
       <c r="AF47">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AG47">
         <v>2.38</v>
@@ -8040,7 +8040,7 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AK47">
         <v>1.36</v>
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="O48">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="P48">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="Q48">
         <v>2.56</v>
@@ -8151,7 +8151,7 @@
         <v>1.22</v>
       </c>
       <c r="T48">
-        <v>3.8</v>
+        <v>3.68</v>
       </c>
       <c r="U48">
         <v>2.18</v>
@@ -8160,10 +8160,10 @@
         <v>1.65</v>
       </c>
       <c r="W48">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X48">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y48">
         <v>1.09</v>
@@ -8181,16 +8181,16 @@
         <v>2.2</v>
       </c>
       <c r="AD48">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AE48">
         <v>1.25</v>
       </c>
       <c r="AF48">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AG48">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8206,7 +8206,7 @@
         <v>1.22</v>
       </c>
       <c r="AK48">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8296,7 +8296,7 @@
         </is>
       </c>
       <c r="N49">
-        <v>4.46</v>
+        <v>4.37</v>
       </c>
       <c r="O49">
         <v>4.05</v>
@@ -8338,10 +8338,10 @@
         <v>1.52</v>
       </c>
       <c r="AB49">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AC49">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="AD49">
         <v>1.55</v>
@@ -8350,7 +8350,7 @@
         <v>1.22</v>
       </c>
       <c r="AF49">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AG49">
         <v>2.35</v>
@@ -8465,7 +8465,7 @@
         <v>3.5</v>
       </c>
       <c r="P50">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="Q50">
         <v>2.61</v>
@@ -8474,13 +8474,13 @@
         <v>2.45</v>
       </c>
       <c r="S50">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T50">
         <v>3.36</v>
       </c>
       <c r="U50">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="V50">
         <v>1.57</v>
@@ -8498,7 +8498,7 @@
         <v>4.81</v>
       </c>
       <c r="AA50">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AB50">
         <v>2.36</v>
@@ -8510,7 +8510,7 @@
         <v>1.53</v>
       </c>
       <c r="AE50">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AF50">
         <v>1.43</v>
@@ -8622,7 +8622,7 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="O51">
         <v>3.5</v>
@@ -8637,7 +8637,7 @@
         <v>2.5</v>
       </c>
       <c r="S51">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="T51">
         <v>4</v>
@@ -8655,7 +8655,7 @@
         <v>1.03</v>
       </c>
       <c r="Y51">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z51">
         <v>5</v>
@@ -8679,7 +8679,7 @@
         <v>1.4</v>
       </c>
       <c r="AG51">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.43</v>
+        <v>1.2</v>
       </c>
       <c r="AK51">
         <v>1.42</v>
@@ -8785,7 +8785,7 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="O52">
         <v>4.75</v>
@@ -8806,10 +8806,10 @@
         <v>3.8</v>
       </c>
       <c r="U52">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="V52">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="W52">
         <v>1.17</v>
@@ -8827,10 +8827,10 @@
         <v>1.4</v>
       </c>
       <c r="AB52">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="AC52">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="AD52">
         <v>1.67</v>
@@ -8855,7 +8855,7 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AK52">
         <v>2.72</v>
@@ -8951,7 +8951,7 @@
         <v>1.28</v>
       </c>
       <c r="O53">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="P53">
         <v>9</v>
@@ -8966,22 +8966,22 @@
         <v>1.34</v>
       </c>
       <c r="T53">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="U53">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="V53">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W53">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X53">
         <v>1</v>
       </c>
       <c r="Y53">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="Z53">
         <v>3.9</v>
@@ -9002,10 +9002,10 @@
         <v>1.13</v>
       </c>
       <c r="AF53">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="AG53">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>1.06</v>
       </c>
       <c r="AK53">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9114,16 +9114,16 @@
         <v>2.06</v>
       </c>
       <c r="O54">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="P54">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="Q54">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="R54">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="S54">
         <v>1.31</v>
@@ -9138,7 +9138,7 @@
         <v>1.44</v>
       </c>
       <c r="W54">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X54">
         <v>1.03</v>
@@ -9156,13 +9156,13 @@
         <v>1.99</v>
       </c>
       <c r="AC54">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="AD54">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE54">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF54">
         <v>1.62</v>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK54">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9280,10 +9280,10 @@
         <v>3.2</v>
       </c>
       <c r="P55">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="Q55">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="R55">
         <v>2.03</v>
@@ -9298,7 +9298,7 @@
         <v>2.75</v>
       </c>
       <c r="V55">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W55">
         <v>1.04</v>
@@ -9310,7 +9310,7 @@
         <v>1.26</v>
       </c>
       <c r="Z55">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AA55">
         <v>2</v>
@@ -9319,10 +9319,10 @@
         <v>1.79</v>
       </c>
       <c r="AC55">
-        <v>3.14</v>
+        <v>3.35</v>
       </c>
       <c r="AD55">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AE55">
         <v>1.08</v>
@@ -9331,7 +9331,7 @@
         <v>1.71</v>
       </c>
       <c r="AG55">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,7 +9344,7 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="AK55">
         <v>1.57</v>
@@ -9437,16 +9437,16 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="O56">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="P56">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Q56">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="R56">
         <v>2.53</v>
@@ -9455,7 +9455,7 @@
         <v>1.27</v>
       </c>
       <c r="T56">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="U56">
         <v>2.36</v>
@@ -9464,10 +9464,10 @@
         <v>1.56</v>
       </c>
       <c r="W56">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X56">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y56">
         <v>1.18</v>
@@ -9479,16 +9479,16 @@
         <v>1.58</v>
       </c>
       <c r="AB56">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AC56">
         <v>2.45</v>
       </c>
       <c r="AD56">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AE56">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AF56">
         <v>1.62</v>
@@ -9507,7 +9507,7 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AK56">
         <v>2.25</v>
@@ -9600,25 +9600,25 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="O57">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="P57">
-        <v>3.9</v>
+        <v>4.54</v>
       </c>
       <c r="Q57">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="R57">
         <v>2.28</v>
       </c>
       <c r="S57">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T57">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U57">
         <v>2.88</v>
@@ -9627,7 +9627,7 @@
         <v>1.4</v>
       </c>
       <c r="W57">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X57">
         <v>1.01</v>
@@ -9645,19 +9645,19 @@
         <v>1.91</v>
       </c>
       <c r="AC57">
-        <v>3</v>
+        <v>3.17</v>
       </c>
       <c r="AD57">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE57">
         <v>1.11</v>
       </c>
       <c r="AF57">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AG57">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="AK57">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="O58">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P58">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="Q58">
         <v>2.63</v>
@@ -9784,7 +9784,7 @@
         <v>3.22</v>
       </c>
       <c r="U58">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="V58">
         <v>1.57</v>
@@ -9805,22 +9805,22 @@
         <v>1.67</v>
       </c>
       <c r="AB58">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AC58">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="AD58">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AE58">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AF58">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AG58">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9926,43 +9926,43 @@
         </is>
       </c>
       <c r="N59">
-        <v>6.75</v>
+        <v>6</v>
       </c>
       <c r="O59">
         <v>4.2</v>
       </c>
       <c r="P59">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="Q59">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="R59">
+        <v>2.33</v>
+      </c>
+      <c r="S59">
+        <v>1.3</v>
+      </c>
+      <c r="T59">
+        <v>3.08</v>
+      </c>
+      <c r="U59">
         <v>2.45</v>
-      </c>
-      <c r="S59">
-        <v>1.28</v>
-      </c>
-      <c r="T59">
-        <v>3.18</v>
-      </c>
-      <c r="U59">
-        <v>2.41</v>
       </c>
       <c r="V59">
         <v>1.47</v>
       </c>
       <c r="W59">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X59">
         <v>1.04</v>
       </c>
       <c r="Y59">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z59">
-        <v>4.2</v>
+        <v>3.86</v>
       </c>
       <c r="AA59">
         <v>1.67</v>
@@ -9971,19 +9971,19 @@
         <v>2.1</v>
       </c>
       <c r="AC59">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AD59">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE59">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AF59">
         <v>1.83</v>
       </c>
       <c r="AG59">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AK59">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="O60">
         <v>4.65</v>
       </c>
       <c r="P60">
-        <v>4.7</v>
+        <v>4.89</v>
       </c>
       <c r="Q60">
         <v>1.95</v>
@@ -10146,7 +10146,7 @@
         <v>1.62</v>
       </c>
       <c r="AG60">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,7 +10159,7 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AK60">
         <v>2.63</v>
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="O63">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P63">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="Q63">
         <v>0</v>
@@ -11233,10 +11233,10 @@
         <v>3.2</v>
       </c>
       <c r="O67">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="P67">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="Q67">
         <v>0</v>
@@ -11559,7 +11559,7 @@
         <v>2.05</v>
       </c>
       <c r="O69">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="P69">
         <v>3.5</v>
@@ -11719,10 +11719,10 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="O70">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P70">
         <v>2.5</v>
@@ -12045,52 +12045,52 @@
         </is>
       </c>
       <c r="N72">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O72">
-        <v>5.35</v>
+        <v>5.1</v>
       </c>
       <c r="P72">
-        <v>6.17</v>
+        <v>7.9</v>
       </c>
       <c r="Q72">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R72">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="S72">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T72">
         <v>3.5</v>
       </c>
       <c r="U72">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V72">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="W72">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X72">
         <v>1.03</v>
       </c>
       <c r="Y72">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Z72">
-        <v>4.9</v>
+        <v>4.75</v>
       </c>
       <c r="AA72">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AB72">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="AC72">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="AD72">
         <v>1.62</v>
@@ -12099,10 +12099,10 @@
         <v>1.25</v>
       </c>
       <c r="AF72">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AG72">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AK72">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12217,10 +12217,10 @@
         <v>3.24</v>
       </c>
       <c r="Q73">
-        <v>2.52</v>
+        <v>2.65</v>
       </c>
       <c r="R73">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="S73">
         <v>1.33</v>
@@ -12244,7 +12244,7 @@
         <v>1.25</v>
       </c>
       <c r="Z73">
-        <v>3.74</v>
+        <v>3.83</v>
       </c>
       <c r="AA73">
         <v>1.78</v>
@@ -12262,10 +12262,10 @@
         <v>1.13</v>
       </c>
       <c r="AF73">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="AG73">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O74">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P74">
-        <v>2.75</v>
+        <v>2.83</v>
       </c>
       <c r="Q74">
         <v>2.8</v>
@@ -12386,10 +12386,10 @@
         <v>2.21</v>
       </c>
       <c r="S74">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T74">
-        <v>2.9</v>
+        <v>2.99</v>
       </c>
       <c r="U74">
         <v>2.7</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.95</v>
+        <v>1.42</v>
       </c>
       <c r="O75">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="P75">
-        <v>3.1</v>
+        <v>6.7</v>
       </c>
       <c r="Q75">
-        <v>2.46</v>
+        <v>1.97</v>
       </c>
       <c r="R75">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="S75">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="T75">
         <v>3.3</v>
       </c>
       <c r="U75">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="V75">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W75">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X75">
         <v>1.03</v>
       </c>
       <c r="Y75">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z75">
-        <v>3.85</v>
+        <v>4.33</v>
       </c>
       <c r="AA75">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AB75">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="AC75">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="AD75">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="AE75">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF75">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="AG75">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK75">
-        <v>1.73</v>
+        <v>2.85</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
-        <v>1.43</v>
+        <v>1.95</v>
       </c>
       <c r="O76">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="P76">
-        <v>6.5</v>
+        <v>3.1</v>
       </c>
       <c r="Q76">
-        <v>1.97</v>
+        <v>2.33</v>
       </c>
       <c r="R76">
-        <v>2.18</v>
+        <v>2.34</v>
       </c>
       <c r="S76">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="T76">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U76">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="V76">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="W76">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X76">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y76">
         <v>1.22</v>
       </c>
       <c r="Z76">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="AA76">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AB76">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AC76">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AD76">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="AE76">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AF76">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AG76">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK76">
-        <v>2.73</v>
+        <v>1.73</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12863,7 +12863,7 @@
         <v>1.25</v>
       </c>
       <c r="O77">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="P77">
         <v>9.5</v>
@@ -13352,7 +13352,7 @@
         <v>3</v>
       </c>
       <c r="O80">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="P80">
         <v>2.3</v>
@@ -13364,13 +13364,13 @@
         <v>2.25</v>
       </c>
       <c r="S80">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="T80">
-        <v>2.9</v>
+        <v>2.59</v>
       </c>
       <c r="U80">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="V80">
         <v>1.4</v>
@@ -13379,7 +13379,7 @@
         <v>1.07</v>
       </c>
       <c r="X80">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y80">
         <v>1.27</v>
@@ -13388,22 +13388,22 @@
         <v>3.5</v>
       </c>
       <c r="AA80">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AB80">
-        <v>1.88</v>
+        <v>1.74</v>
       </c>
       <c r="AC80">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="AD80">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AE80">
         <v>1.08</v>
       </c>
       <c r="AF80">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AG80">
         <v>2</v>
@@ -13419,7 +13419,7 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AK80">
         <v>1.33</v>
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O81">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P81">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q81">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="R81">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="S81">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T81">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U81">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="V81">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="W81">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X81">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y81">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z81">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="AA81">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AB81">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AC81">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD81">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE81">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AF81">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AG81">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK81">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13838,13 +13838,13 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="O83">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P83">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="Q83">
         <v>2.6</v>
@@ -13880,7 +13880,7 @@
         <v>2.1</v>
       </c>
       <c r="AB83">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC83">
         <v>3.75</v>
@@ -13892,7 +13892,7 @@
         <v>1.08</v>
       </c>
       <c r="AF83">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AG83">
         <v>1.83</v>
@@ -13911,7 +13911,7 @@
         <v>1.22</v>
       </c>
       <c r="AK83">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14001,7 +14001,7 @@
         </is>
       </c>
       <c r="N84">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="O84">
         <v>3.1</v>
@@ -14049,7 +14049,7 @@
         <v>4.8</v>
       </c>
       <c r="AD84">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AE84">
         <v>1.04</v>
@@ -14327,13 +14327,13 @@
         </is>
       </c>
       <c r="N86">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="O86">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="P86">
-        <v>3.85</v>
+        <v>3.74</v>
       </c>
       <c r="Q86">
         <v>2.05</v>
@@ -14345,7 +14345,7 @@
         <v>1.25</v>
       </c>
       <c r="T86">
-        <v>3.6</v>
+        <v>2.75</v>
       </c>
       <c r="U86">
         <v>2.15</v>
@@ -14360,13 +14360,13 @@
         <v>1.02</v>
       </c>
       <c r="Y86">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z86">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AA86">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AB86">
         <v>2.38</v>
@@ -14375,16 +14375,16 @@
         <v>1.98</v>
       </c>
       <c r="AD86">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="AE86">
         <v>1.14</v>
       </c>
       <c r="AF86">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AG86">
-        <v>2.27</v>
+        <v>2.38</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="AK86">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14490,64 +14490,64 @@
         </is>
       </c>
       <c r="N87">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O87">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P87">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q87">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="R87">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S87">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T87">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="U87">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="V87">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="W87">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X87">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y87">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z87">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AA87">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AB87">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AC87">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD87">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AE87">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF87">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG87">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK87">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14653,16 +14653,16 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="O88">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="P88">
-        <v>6.4</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="Q88">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R88">
         <v>2.28</v>
@@ -14671,25 +14671,25 @@
         <v>1.36</v>
       </c>
       <c r="T88">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="U88">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="V88">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="W88">
         <v>1.05</v>
       </c>
       <c r="X88">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y88">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z88">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="AA88">
         <v>1.83</v>
@@ -14701,7 +14701,7 @@
         <v>2.88</v>
       </c>
       <c r="AD88">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AE88">
         <v>1.08</v>
@@ -14710,7 +14710,7 @@
         <v>2.15</v>
       </c>
       <c r="AG88">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14825,31 +14825,31 @@
         <v>0</v>
       </c>
       <c r="Q89">
-        <v>4.5</v>
+        <v>4.57</v>
       </c>
       <c r="R89">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="S89">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="T89">
-        <v>3.25</v>
+        <v>3.32</v>
       </c>
       <c r="U89">
         <v>2.29</v>
       </c>
       <c r="V89">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W89">
         <v>1.09</v>
       </c>
       <c r="X89">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y89">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Z89">
         <v>4</v>
@@ -14864,7 +14864,7 @@
         <v>2.75</v>
       </c>
       <c r="AD89">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="AE89">
         <v>1.16</v>
@@ -14886,7 +14886,7 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AK89">
         <v>1.15</v>
@@ -14982,10 +14982,10 @@
         <v>2.66</v>
       </c>
       <c r="O90">
-        <v>3.72</v>
+        <v>3.6</v>
       </c>
       <c r="P90">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="Q90">
         <v>0</v>
@@ -15332,7 +15332,7 @@
         <v>1.35</v>
       </c>
       <c r="W92">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X92">
         <v>1.06</v>
@@ -15341,28 +15341,28 @@
         <v>1.24</v>
       </c>
       <c r="Z92">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="AA92">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="AB92">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AC92">
-        <v>2.95</v>
+        <v>3.28</v>
       </c>
       <c r="AD92">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE92">
         <v>1.08</v>
       </c>
       <c r="AF92">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG92">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AK92">
-        <v>1.74</v>
+        <v>1.59</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15468,25 +15468,25 @@
         </is>
       </c>
       <c r="N93">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="O93">
         <v>3.2</v>
       </c>
       <c r="P93">
+        <v>2.3</v>
+      </c>
+      <c r="Q93">
+        <v>3.25</v>
+      </c>
+      <c r="R93">
         <v>2.25</v>
       </c>
-      <c r="Q93">
-        <v>3.67</v>
-      </c>
-      <c r="R93">
-        <v>2.12</v>
-      </c>
       <c r="S93">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T93">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="U93">
         <v>2.5</v>
@@ -15498,31 +15498,31 @@
         <v>1.08</v>
       </c>
       <c r="X93">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y93">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z93">
         <v>3.84</v>
       </c>
       <c r="AA93">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AB93">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AC93">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AD93">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AE93">
         <v>1.13</v>
       </c>
       <c r="AF93">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG93">
         <v>2.2</v>
@@ -15538,7 +15538,7 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AK93">
         <v>1.36</v>

--- a/jogos_2026-08-07.xlsx
+++ b/jogos_2026-08-07.xlsx
@@ -756,22 +756,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Urawa Reds</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
+        <v>2.4</v>
+      </c>
+      <c r="O3">
+        <v>3.25</v>
+      </c>
+      <c r="P3">
+        <v>2.87</v>
+      </c>
+      <c r="Q3">
+        <v>3.02</v>
+      </c>
+      <c r="R3">
+        <v>2.02</v>
+      </c>
+      <c r="S3">
+        <v>1.39</v>
+      </c>
+      <c r="T3">
         <v>2.9</v>
       </c>
-      <c r="O3">
-        <v>3.3</v>
-      </c>
-      <c r="P3">
-        <v>2.16</v>
-      </c>
-      <c r="Q3">
-        <v>3.4</v>
-      </c>
-      <c r="R3">
-        <v>2.25</v>
-      </c>
-      <c r="S3">
-        <v>1.3</v>
-      </c>
-      <c r="T3">
-        <v>3.1</v>
-      </c>
       <c r="U3">
-        <v>2.47</v>
+        <v>2.98</v>
       </c>
       <c r="V3">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="W3">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X3">
         <v>1.04</v>
       </c>
       <c r="Y3">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z3">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="AA3">
-        <v>1.8</v>
+        <v>2.04</v>
       </c>
       <c r="AB3">
-        <v>1.86</v>
+        <v>1.74</v>
       </c>
       <c r="AC3">
-        <v>2.85</v>
+        <v>3.6</v>
       </c>
       <c r="AD3">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="AE3">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF3">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AG3">
-        <v>2.15</v>
+        <v>1.94</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AK3">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -914,7 +914,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G4">
@@ -961,28 +961,28 @@
         </is>
       </c>
       <c r="N4">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="O4">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P4">
-        <v>1.78</v>
+        <v>2.2</v>
       </c>
       <c r="Q4">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="R4">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="S4">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T4">
-        <v>2.87</v>
+        <v>3.1</v>
       </c>
       <c r="U4">
-        <v>2.61</v>
+        <v>2.47</v>
       </c>
       <c r="V4">
         <v>1.44</v>
@@ -991,50 +991,50 @@
         <v>1.07</v>
       </c>
       <c r="X4">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y4">
+        <v>1.2</v>
+      </c>
+      <c r="Z4">
+        <v>3.72</v>
+      </c>
+      <c r="AA4">
+        <v>1.8</v>
+      </c>
+      <c r="AB4">
+        <v>2</v>
+      </c>
+      <c r="AC4">
+        <v>2.85</v>
+      </c>
+      <c r="AD4">
+        <v>1.41</v>
+      </c>
+      <c r="AE4">
+        <v>1.11</v>
+      </c>
+      <c r="AF4">
+        <v>1.6</v>
+      </c>
+      <c r="AG4">
+        <v>2.15</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ4">
         <v>1.24</v>
       </c>
-      <c r="Z4">
-        <v>3.98</v>
-      </c>
-      <c r="AA4">
-        <v>1.71</v>
-      </c>
-      <c r="AB4">
-        <v>1.98</v>
-      </c>
-      <c r="AC4">
-        <v>2.7</v>
-      </c>
-      <c r="AD4">
-        <v>1.36</v>
-      </c>
-      <c r="AE4">
-        <v>1.15</v>
-      </c>
-      <c r="AF4">
-        <v>1.65</v>
-      </c>
-      <c r="AG4">
-        <v>2.1</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ4">
-        <v>1.9</v>
-      </c>
       <c r="AK4">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2026-08-07 07:30:00</t>
+          <t>2026-08-07 08:00:00</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>3.75</v>
+        <v>3.22</v>
       </c>
       <c r="O5">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="P5">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="Q5">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="R5">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="S5">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="T5">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="U5">
-        <v>2.88</v>
+        <v>2.61</v>
       </c>
       <c r="V5">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W5">
         <v>1.07</v>
       </c>
       <c r="X5">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y5">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z5">
-        <v>3.28</v>
+        <v>3.95</v>
       </c>
       <c r="AA5">
-        <v>1.86</v>
+        <v>1.72</v>
       </c>
       <c r="AB5">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AC5">
-        <v>3.19</v>
+        <v>2.7</v>
       </c>
       <c r="AD5">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AE5">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AF5">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AG5">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="AK5">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2026-08-07 07:30:00</t>
+          <t>2026-08-07 08:00:00</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.7</v>
+        <v>3.02</v>
       </c>
       <c r="O6">
-        <v>3.5</v>
+        <v>3.07</v>
       </c>
       <c r="P6">
-        <v>4.3</v>
+        <v>1.85</v>
       </c>
       <c r="Q6">
-        <v>2.23</v>
+        <v>4.33</v>
       </c>
       <c r="R6">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S6">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T6">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="U6">
-        <v>3.14</v>
+        <v>2.88</v>
       </c>
       <c r="V6">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="W6">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X6">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y6">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="Z6">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="AA6">
-        <v>2.03</v>
+        <v>1.87</v>
       </c>
       <c r="AB6">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AC6">
-        <v>3.8</v>
+        <v>3.24</v>
       </c>
       <c r="AD6">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AE6">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF6">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="AG6">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK6">
-        <v>1.91</v>
+        <v>1.19</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2026-08-07 07:30:00</t>
+          <t>2026-08-07 08:00:00</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,31 +1450,31 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="O7">
-        <v>5.25</v>
+        <v>3.95</v>
       </c>
       <c r="P7">
-        <v>7.3</v>
+        <v>5.26</v>
       </c>
       <c r="Q7">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="R7">
-        <v>2.6</v>
+        <v>2.28</v>
       </c>
       <c r="S7">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="T7">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="U7">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="V7">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W7">
         <v>1.07</v>
@@ -1483,31 +1483,31 @@
         <v>1.02</v>
       </c>
       <c r="Y7">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z7">
-        <v>4.4</v>
+        <v>3.87</v>
       </c>
       <c r="AA7">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AB7">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="AC7">
-        <v>2.59</v>
+        <v>2.95</v>
       </c>
       <c r="AD7">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AE7">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF7">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AG7">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="AK7">
-        <v>2.75</v>
+        <v>2.26</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2026-08-07 07:30:00</t>
+          <t>2026-08-07 08:00:00</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,31 +1613,31 @@
         </is>
       </c>
       <c r="N8">
+        <v>1.19</v>
+      </c>
+      <c r="O8">
+        <v>5.25</v>
+      </c>
+      <c r="P8">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="Q8">
+        <v>1.75</v>
+      </c>
+      <c r="R8">
+        <v>2.6</v>
+      </c>
+      <c r="S8">
+        <v>1.26</v>
+      </c>
+      <c r="T8">
+        <v>3.32</v>
+      </c>
+      <c r="U8">
+        <v>2.52</v>
+      </c>
+      <c r="V8">
         <v>1.5</v>
-      </c>
-      <c r="O8">
-        <v>3.9</v>
-      </c>
-      <c r="P8">
-        <v>5</v>
-      </c>
-      <c r="Q8">
-        <v>2</v>
-      </c>
-      <c r="R8">
-        <v>2.28</v>
-      </c>
-      <c r="S8">
-        <v>1.35</v>
-      </c>
-      <c r="T8">
-        <v>3.1</v>
-      </c>
-      <c r="U8">
-        <v>2.53</v>
-      </c>
-      <c r="V8">
-        <v>1.44</v>
       </c>
       <c r="W8">
         <v>1.07</v>
@@ -1646,31 +1646,31 @@
         <v>1.02</v>
       </c>
       <c r="Y8">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z8">
-        <v>3.84</v>
+        <v>4.4</v>
       </c>
       <c r="AA8">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="AB8">
-        <v>1.97</v>
+        <v>2.2</v>
       </c>
       <c r="AC8">
-        <v>2.95</v>
+        <v>2.59</v>
       </c>
       <c r="AD8">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AE8">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF8">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AG8">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="AK8">
-        <v>2.26</v>
+        <v>3.38</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2026-08-07 07:30:00</t>
+          <t>2026-08-07 08:00:00</t>
         </is>
       </c>
     </row>
@@ -1729,27 +1729,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Urawa Reds</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.4</v>
+        <v>1.73</v>
       </c>
       <c r="O9">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="P9">
-        <v>2.87</v>
+        <v>4.28</v>
       </c>
       <c r="Q9">
-        <v>3.02</v>
+        <v>2.23</v>
       </c>
       <c r="R9">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="S9">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="T9">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="U9">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="V9">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="W9">
         <v>1.03</v>
       </c>
       <c r="X9">
+        <v>1.06</v>
+      </c>
+      <c r="Y9">
+        <v>1.36</v>
+      </c>
+      <c r="Z9">
+        <v>3.1</v>
+      </c>
+      <c r="AA9">
+        <v>2.03</v>
+      </c>
+      <c r="AB9">
+        <v>1.73</v>
+      </c>
+      <c r="AC9">
+        <v>3.8</v>
+      </c>
+      <c r="AD9">
+        <v>1.26</v>
+      </c>
+      <c r="AE9">
         <v>1.04</v>
       </c>
-      <c r="Y9">
-        <v>1.3</v>
-      </c>
-      <c r="Z9">
-        <v>3.4</v>
-      </c>
-      <c r="AA9">
-        <v>2.04</v>
-      </c>
-      <c r="AB9">
-        <v>1.74</v>
-      </c>
-      <c r="AC9">
-        <v>3.6</v>
-      </c>
-      <c r="AD9">
-        <v>1.29</v>
-      </c>
-      <c r="AE9">
-        <v>1.06</v>
-      </c>
       <c r="AF9">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AG9">
-        <v>1.94</v>
+        <v>1.79</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="AK9">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2026-08-07 07:30:00</t>
+          <t>2026-08-07 08:00:00</t>
         </is>
       </c>
     </row>
@@ -2111,55 +2111,55 @@
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA11">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AB11">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="O12">
-        <v>3.32</v>
+        <v>3.1</v>
       </c>
       <c r="P12">
-        <v>3.17</v>
+        <v>3.1</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AA12">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB12">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="O13">
-        <v>3.99</v>
+        <v>3.4</v>
       </c>
       <c r="P13">
-        <v>6.19</v>
+        <v>4.57</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AA13">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AB13">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2929,7 +2929,7 @@
         <v>3.14</v>
       </c>
       <c r="R16">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="S16">
         <v>1.3</v>
@@ -2938,13 +2938,13 @@
         <v>3.3</v>
       </c>
       <c r="U16">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="V16">
         <v>1.48</v>
       </c>
       <c r="W16">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X16">
         <v>1.04</v>
@@ -2956,19 +2956,19 @@
         <v>4</v>
       </c>
       <c r="AA16">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AB16">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AC16">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="AD16">
         <v>1.4</v>
       </c>
       <c r="AE16">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF16">
         <v>1.57</v>
@@ -3264,7 +3264,7 @@
         <v>3.15</v>
       </c>
       <c r="U18">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="V18">
         <v>1.5</v>
@@ -3273,13 +3273,13 @@
         <v>1.11</v>
       </c>
       <c r="X18">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z18">
-        <v>3.9</v>
+        <v>4.15</v>
       </c>
       <c r="AA18">
         <v>1.67</v>
@@ -3288,19 +3288,19 @@
         <v>2.07</v>
       </c>
       <c r="AC18">
-        <v>2.8</v>
+        <v>2.59</v>
       </c>
       <c r="AD18">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AE18">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF18">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG18">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK18">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3569,49 +3569,49 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="O20">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="P20">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="Q20">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="R20">
-        <v>2.27</v>
+        <v>2.38</v>
       </c>
       <c r="S20">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="T20">
         <v>3.25</v>
       </c>
       <c r="U20">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="V20">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="W20">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X20">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y20">
         <v>1.16</v>
       </c>
       <c r="Z20">
-        <v>4.15</v>
+        <v>3.92</v>
       </c>
       <c r="AA20">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AB20">
-        <v>2.17</v>
+        <v>2.09</v>
       </c>
       <c r="AC20">
         <v>2.48</v>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AK20">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="O25">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P25">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q25">
-        <v>2.03</v>
+        <v>2.41</v>
       </c>
       <c r="R25">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="S25">
         <v>1.3</v>
       </c>
       <c r="T25">
-        <v>2.83</v>
+        <v>3.2</v>
       </c>
       <c r="U25">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="V25">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="W25">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X25">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y25">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="Z25">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AA25">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AB25">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AC25">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="AD25">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AE25">
         <v>1.11</v>
       </c>
       <c r="AF25">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AG25">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK25">
-        <v>2.38</v>
+        <v>1.78</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q26">
-        <v>2.41</v>
+        <v>2.03</v>
       </c>
       <c r="R26">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="S26">
         <v>1.3</v>
       </c>
       <c r="T26">
-        <v>3.2</v>
+        <v>2.83</v>
       </c>
       <c r="U26">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="V26">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="W26">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X26">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y26">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="Z26">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AA26">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AB26">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AC26">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="AD26">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AE26">
         <v>1.11</v>
       </c>
       <c r="AF26">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AG26">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK26">
-        <v>1.78</v>
+        <v>2.38</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -5045,7 +5045,7 @@
         <v>2.69</v>
       </c>
       <c r="Q29">
-        <v>3.3</v>
+        <v>3.02</v>
       </c>
       <c r="R29">
         <v>1.88</v>
@@ -5109,7 +5109,7 @@
         <v>1.41</v>
       </c>
       <c r="AK29">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,16 +5199,16 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="O30">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P30">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="Q30">
-        <v>3.02</v>
+        <v>3.12</v>
       </c>
       <c r="R30">
         <v>2.15</v>
@@ -5217,13 +5217,13 @@
         <v>1.33</v>
       </c>
       <c r="T30">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="U30">
         <v>2.62</v>
       </c>
       <c r="V30">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W30">
         <v>1.07</v>
@@ -5238,13 +5238,13 @@
         <v>3.7</v>
       </c>
       <c r="AA30">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AB30">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC30">
-        <v>2.78</v>
+        <v>3.25</v>
       </c>
       <c r="AD30">
         <v>1.33</v>
@@ -5253,7 +5253,7 @@
         <v>1.1</v>
       </c>
       <c r="AF30">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG30">
         <v>2.1</v>
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK30">
         <v>1.47</v>
@@ -5365,10 +5365,10 @@
         <v>1.43</v>
       </c>
       <c r="O31">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P31">
-        <v>6.85</v>
+        <v>6</v>
       </c>
       <c r="Q31">
         <v>1.91</v>
@@ -5395,7 +5395,7 @@
         <v>1</v>
       </c>
       <c r="Y31">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="Z31">
         <v>3.75</v>
@@ -5404,19 +5404,19 @@
         <v>1.87</v>
       </c>
       <c r="AB31">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AC31">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="AD31">
         <v>1.32</v>
       </c>
       <c r="AE31">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF31">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AG31">
         <v>1.75</v>
@@ -5435,7 +5435,7 @@
         <v>1.08</v>
       </c>
       <c r="AK31">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5688,10 +5688,10 @@
         </is>
       </c>
       <c r="N33">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="O33">
-        <v>3.55</v>
+        <v>3.64</v>
       </c>
       <c r="P33">
         <v>3.2</v>
@@ -5724,25 +5724,25 @@
         <v>1.22</v>
       </c>
       <c r="Z33">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AA33">
         <v>1.7</v>
       </c>
       <c r="AB33">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC33">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AD33">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AE33">
         <v>1.15</v>
       </c>
       <c r="AF33">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG33">
         <v>2.2</v>
@@ -5872,13 +5872,13 @@
         <v>3.5</v>
       </c>
       <c r="U34">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="V34">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W34">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X34">
         <v>0</v>
@@ -5902,7 +5902,7 @@
         <v>1.45</v>
       </c>
       <c r="AE34">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AF34">
         <v>1.54</v>
@@ -5924,7 +5924,7 @@
         <v>1.2</v>
       </c>
       <c r="AK34">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6503,58 +6503,58 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="O38">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="P38">
-        <v>2.79</v>
+        <v>2.43</v>
       </c>
       <c r="Q38">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="R38">
         <v>2.25</v>
       </c>
       <c r="S38">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T38">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="U38">
         <v>2.5</v>
       </c>
       <c r="V38">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="W38">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X38">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y38">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z38">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="AA38">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AB38">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="AC38">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="AD38">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE38">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF38">
         <v>1.58</v>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK38">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -7327,7 +7327,7 @@
         <v>2.45</v>
       </c>
       <c r="Q43">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="R43">
         <v>2.1</v>
@@ -7363,19 +7363,19 @@
         <v>1.7</v>
       </c>
       <c r="AC43">
-        <v>3.48</v>
+        <v>3.6</v>
       </c>
       <c r="AD43">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE43">
         <v>1.04</v>
       </c>
       <c r="AF43">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AG43">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AK43">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -9111,16 +9111,16 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="O54">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="P54">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="Q54">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="R54">
         <v>2.3</v>
@@ -9135,13 +9135,13 @@
         <v>2.6</v>
       </c>
       <c r="V54">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W54">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X54">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y54">
         <v>1.19</v>
@@ -9153,7 +9153,7 @@
         <v>1.73</v>
       </c>
       <c r="AB54">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="AC54">
         <v>2.88</v>
@@ -9162,10 +9162,10 @@
         <v>1.36</v>
       </c>
       <c r="AE54">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF54">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AG54">
         <v>2.15</v>
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="O57">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="P57">
-        <v>4.54</v>
+        <v>3.9</v>
       </c>
       <c r="Q57">
         <v>2.3</v>
@@ -9615,13 +9615,13 @@
         <v>2.28</v>
       </c>
       <c r="S57">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="T57">
         <v>2.88</v>
       </c>
       <c r="U57">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="V57">
         <v>1.4</v>
@@ -9630,28 +9630,28 @@
         <v>1.06</v>
       </c>
       <c r="X57">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y57">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="Z57">
         <v>3.34</v>
       </c>
       <c r="AA57">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AB57">
         <v>1.91</v>
       </c>
       <c r="AC57">
-        <v>3.17</v>
+        <v>2.97</v>
       </c>
       <c r="AD57">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE57">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF57">
         <v>1.83</v>
@@ -9673,7 +9673,7 @@
         <v>1.24</v>
       </c>
       <c r="AK57">
-        <v>1.91</v>
+        <v>2.01</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -10255,10 +10255,10 @@
         <v>1.4</v>
       </c>
       <c r="O61">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="P61">
-        <v>7.09</v>
+        <v>6.85</v>
       </c>
       <c r="Q61">
         <v>1.83</v>
@@ -10267,13 +10267,13 @@
         <v>2.4</v>
       </c>
       <c r="S61">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T61">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U61">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="V61">
         <v>1.44</v>
@@ -10285,13 +10285,13 @@
         <v>1.04</v>
       </c>
       <c r="Y61">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="Z61">
-        <v>3.6</v>
+        <v>3.82</v>
       </c>
       <c r="AA61">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AB61">
         <v>2.1</v>
@@ -10306,7 +10306,7 @@
         <v>1.15</v>
       </c>
       <c r="AF61">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AG61">
         <v>1.81</v>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="AK61">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10418,13 +10418,13 @@
         <v>1.98</v>
       </c>
       <c r="O62">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P62">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="Q62">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="R62">
         <v>2.33</v>
@@ -10469,7 +10469,7 @@
         <v>1.12</v>
       </c>
       <c r="AF62">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AG62">
         <v>2.15</v>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK62">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="O74">
+        <v>3.4</v>
+      </c>
+      <c r="P74">
+        <v>3.1</v>
+      </c>
+      <c r="Q74">
+        <v>2.33</v>
+      </c>
+      <c r="R74">
+        <v>2.34</v>
+      </c>
+      <c r="S74">
+        <v>1.31</v>
+      </c>
+      <c r="T74">
         <v>3.2</v>
       </c>
-      <c r="P74">
-        <v>2.83</v>
-      </c>
-      <c r="Q74">
+      <c r="U74">
+        <v>2.4</v>
+      </c>
+      <c r="V74">
+        <v>1.5</v>
+      </c>
+      <c r="W74">
+        <v>1.07</v>
+      </c>
+      <c r="X74">
+        <v>1.04</v>
+      </c>
+      <c r="Y74">
+        <v>1.22</v>
+      </c>
+      <c r="Z74">
+        <v>3.85</v>
+      </c>
+      <c r="AA74">
+        <v>1.75</v>
+      </c>
+      <c r="AB74">
+        <v>2.05</v>
+      </c>
+      <c r="AC74">
         <v>2.8</v>
       </c>
-      <c r="R74">
-        <v>2.21</v>
-      </c>
-      <c r="S74">
-        <v>1.36</v>
-      </c>
-      <c r="T74">
-        <v>2.99</v>
-      </c>
-      <c r="U74">
-        <v>2.7</v>
-      </c>
-      <c r="V74">
-        <v>1.4</v>
-      </c>
-      <c r="W74">
-        <v>1.08</v>
-      </c>
-      <c r="X74">
-        <v>1.05</v>
-      </c>
-      <c r="Y74">
-        <v>1.3</v>
-      </c>
-      <c r="Z74">
-        <v>3.45</v>
-      </c>
-      <c r="AA74">
-        <v>1.95</v>
-      </c>
-      <c r="AB74">
-        <v>1.82</v>
-      </c>
-      <c r="AC74">
-        <v>3.35</v>
-      </c>
       <c r="AD74">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AE74">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AF74">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AG74">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK74">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
+        <v>2.25</v>
+      </c>
+      <c r="O76">
+        <v>3.2</v>
+      </c>
+      <c r="P76">
+        <v>2.83</v>
+      </c>
+      <c r="Q76">
+        <v>2.8</v>
+      </c>
+      <c r="R76">
+        <v>2.21</v>
+      </c>
+      <c r="S76">
+        <v>1.36</v>
+      </c>
+      <c r="T76">
+        <v>2.99</v>
+      </c>
+      <c r="U76">
+        <v>2.7</v>
+      </c>
+      <c r="V76">
+        <v>1.4</v>
+      </c>
+      <c r="W76">
+        <v>1.08</v>
+      </c>
+      <c r="X76">
+        <v>1.05</v>
+      </c>
+      <c r="Y76">
+        <v>1.3</v>
+      </c>
+      <c r="Z76">
+        <v>3.45</v>
+      </c>
+      <c r="AA76">
         <v>1.95</v>
       </c>
-      <c r="O76">
-        <v>3.4</v>
-      </c>
-      <c r="P76">
-        <v>3.1</v>
-      </c>
-      <c r="Q76">
-        <v>2.33</v>
-      </c>
-      <c r="R76">
-        <v>2.34</v>
-      </c>
-      <c r="S76">
+      <c r="AB76">
+        <v>1.82</v>
+      </c>
+      <c r="AC76">
+        <v>3.35</v>
+      </c>
+      <c r="AD76">
         <v>1.31</v>
       </c>
-      <c r="T76">
-        <v>3.2</v>
-      </c>
-      <c r="U76">
-        <v>2.4</v>
-      </c>
-      <c r="V76">
-        <v>1.5</v>
-      </c>
-      <c r="W76">
-        <v>1.07</v>
-      </c>
-      <c r="X76">
-        <v>1.04</v>
-      </c>
-      <c r="Y76">
-        <v>1.22</v>
-      </c>
-      <c r="Z76">
-        <v>3.85</v>
-      </c>
-      <c r="AA76">
-        <v>1.75</v>
-      </c>
-      <c r="AB76">
-        <v>2.05</v>
-      </c>
-      <c r="AC76">
-        <v>2.8</v>
-      </c>
-      <c r="AD76">
-        <v>1.41</v>
-      </c>
       <c r="AE76">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AF76">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AG76">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK76">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -13023,19 +13023,19 @@
         </is>
       </c>
       <c r="N78">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="O78">
         <v>3.92</v>
       </c>
       <c r="P78">
-        <v>4.69</v>
+        <v>4.2</v>
       </c>
       <c r="Q78">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R78">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="S78">
         <v>1.31</v>
@@ -13056,16 +13056,16 @@
         <v>1.04</v>
       </c>
       <c r="Y78">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z78">
-        <v>4.09</v>
+        <v>4</v>
       </c>
       <c r="AA78">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AB78">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AC78">
         <v>2.83</v>
@@ -13080,7 +13080,7 @@
         <v>1.7</v>
       </c>
       <c r="AG78">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK78">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -14001,10 +14001,10 @@
         </is>
       </c>
       <c r="N84">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="O84">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="P84">
         <v>4.2</v>
@@ -14022,22 +14022,22 @@
         <v>2.5</v>
       </c>
       <c r="U84">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="V84">
         <v>1.22</v>
       </c>
       <c r="W84">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="X84">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="Y84">
         <v>1.47</v>
       </c>
       <c r="Z84">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="AA84">
         <v>2.56</v>
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="O85">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P85">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="Q85">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R85">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S85">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T85">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="U85">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V85">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W85">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y85">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z85">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA85">
         <v>1.75</v>
       </c>
       <c r="AB85">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="AC85">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD85">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE85">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF85">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG85">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK85">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14982,7 +14982,7 @@
         <v>2.66</v>
       </c>
       <c r="O90">
-        <v>3.6</v>
+        <v>3.72</v>
       </c>
       <c r="P90">
         <v>2.3</v>
@@ -15142,31 +15142,31 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="O91">
         <v>3.15</v>
       </c>
       <c r="P91">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q91">
         <v>3.24</v>
       </c>
       <c r="R91">
-        <v>1.97</v>
+        <v>2.15</v>
       </c>
       <c r="S91">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T91">
-        <v>2.75</v>
+        <v>2.92</v>
       </c>
       <c r="U91">
-        <v>2.93</v>
+        <v>2.82</v>
       </c>
       <c r="V91">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W91">
         <v>1.08</v>
@@ -15178,13 +15178,13 @@
         <v>1.27</v>
       </c>
       <c r="Z91">
-        <v>3.38</v>
+        <v>3.18</v>
       </c>
       <c r="AA91">
         <v>2</v>
       </c>
       <c r="AB91">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AC91">
         <v>3.2</v>
@@ -15193,13 +15193,13 @@
         <v>1.3</v>
       </c>
       <c r="AE91">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF91">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AG91">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15483,10 +15483,10 @@
         <v>2.25</v>
       </c>
       <c r="S93">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T93">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="U93">
         <v>2.5</v>
@@ -15495,28 +15495,28 @@
         <v>1.44</v>
       </c>
       <c r="W93">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X93">
         <v>1.05</v>
       </c>
       <c r="Y93">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z93">
         <v>3.84</v>
       </c>
       <c r="AA93">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AB93">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AC93">
         <v>3</v>
       </c>
       <c r="AD93">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AE93">
         <v>1.13</v>
@@ -15538,7 +15538,7 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AK93">
         <v>1.36</v>
@@ -15794,10 +15794,10 @@
         </is>
       </c>
       <c r="N95">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="O95">
-        <v>5.5</v>
+        <v>5.45</v>
       </c>
       <c r="P95">
         <v>8.25</v>
@@ -15809,28 +15809,28 @@
         <v>2.75</v>
       </c>
       <c r="S95">
+        <v>1.22</v>
+      </c>
+      <c r="T95">
+        <v>4.15</v>
+      </c>
+      <c r="U95">
+        <v>2.09</v>
+      </c>
+      <c r="V95">
+        <v>1.68</v>
+      </c>
+      <c r="W95">
         <v>1.2</v>
-      </c>
-      <c r="T95">
-        <v>4</v>
-      </c>
-      <c r="U95">
-        <v>2.05</v>
-      </c>
-      <c r="V95">
-        <v>1.63</v>
-      </c>
-      <c r="W95">
-        <v>1.17</v>
       </c>
       <c r="X95">
         <v>1.02</v>
       </c>
       <c r="Y95">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Z95">
-        <v>5.58</v>
+        <v>5.7</v>
       </c>
       <c r="AA95">
         <v>1.44</v>
@@ -15845,13 +15845,13 @@
         <v>1.65</v>
       </c>
       <c r="AE95">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AF95">
         <v>1.75</v>
       </c>
       <c r="AG95">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>

--- a/jogos_2026-08-07.xlsx
+++ b/jogos_2026-08-07.xlsx
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.49</v>
+        <v>1.73</v>
       </c>
       <c r="O7">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="P7">
-        <v>5.26</v>
+        <v>4.28</v>
       </c>
       <c r="Q7">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="R7">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="S7">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="T7">
+        <v>2.75</v>
+      </c>
+      <c r="U7">
+        <v>2.96</v>
+      </c>
+      <c r="V7">
+        <v>1.34</v>
+      </c>
+      <c r="W7">
+        <v>1.03</v>
+      </c>
+      <c r="X7">
+        <v>1.06</v>
+      </c>
+      <c r="Y7">
+        <v>1.36</v>
+      </c>
+      <c r="Z7">
         <v>3.1</v>
       </c>
-      <c r="U7">
-        <v>2.53</v>
-      </c>
-      <c r="V7">
-        <v>1.44</v>
-      </c>
-      <c r="W7">
-        <v>1.07</v>
-      </c>
-      <c r="X7">
-        <v>1.02</v>
-      </c>
-      <c r="Y7">
-        <v>1.19</v>
-      </c>
-      <c r="Z7">
-        <v>3.87</v>
-      </c>
       <c r="AA7">
-        <v>1.76</v>
+        <v>2.03</v>
       </c>
       <c r="AB7">
-        <v>2.02</v>
+        <v>1.73</v>
       </c>
       <c r="AC7">
-        <v>2.95</v>
+        <v>3.8</v>
       </c>
       <c r="AD7">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AE7">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="AF7">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AG7">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AK7">
-        <v>2.26</v>
+        <v>1.91</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,31 +1613,31 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.19</v>
+        <v>1.49</v>
       </c>
       <c r="O8">
-        <v>5.25</v>
+        <v>3.95</v>
       </c>
       <c r="P8">
-        <v>9.699999999999999</v>
+        <v>5.26</v>
       </c>
       <c r="Q8">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="R8">
-        <v>2.6</v>
+        <v>2.28</v>
       </c>
       <c r="S8">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="T8">
-        <v>3.32</v>
+        <v>3.1</v>
       </c>
       <c r="U8">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="V8">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W8">
         <v>1.07</v>
@@ -1646,31 +1646,31 @@
         <v>1.02</v>
       </c>
       <c r="Y8">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z8">
-        <v>4.4</v>
+        <v>3.87</v>
       </c>
       <c r="AA8">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="AB8">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="AC8">
-        <v>2.59</v>
+        <v>2.95</v>
       </c>
       <c r="AD8">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AE8">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF8">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AG8">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="AK8">
-        <v>3.38</v>
+        <v>2.26</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.73</v>
+        <v>1.19</v>
       </c>
       <c r="O9">
-        <v>3.5</v>
+        <v>5.25</v>
       </c>
       <c r="P9">
-        <v>4.28</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Q9">
-        <v>2.23</v>
+        <v>1.75</v>
       </c>
       <c r="R9">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="S9">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="T9">
-        <v>2.75</v>
+        <v>3.32</v>
       </c>
       <c r="U9">
-        <v>2.96</v>
+        <v>2.52</v>
       </c>
       <c r="V9">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="W9">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X9">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y9">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="Z9">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="AA9">
-        <v>2.03</v>
+        <v>1.65</v>
       </c>
       <c r="AB9">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="AC9">
-        <v>3.8</v>
+        <v>2.59</v>
       </c>
       <c r="AD9">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="AE9">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AF9">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AG9">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.21</v>
+        <v>1.09</v>
       </c>
       <c r="AK9">
-        <v>1.91</v>
+        <v>3.38</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.95</v>
+        <v>1.42</v>
       </c>
       <c r="O74">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="P74">
-        <v>3.1</v>
+        <v>6.7</v>
       </c>
       <c r="Q74">
-        <v>2.33</v>
+        <v>1.97</v>
       </c>
       <c r="R74">
-        <v>2.34</v>
+        <v>2.18</v>
       </c>
       <c r="S74">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="T74">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U74">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="V74">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W74">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X74">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y74">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z74">
-        <v>3.85</v>
+        <v>4.33</v>
       </c>
       <c r="AA74">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AB74">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AC74">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="AD74">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="AE74">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF74">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="AG74">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK74">
-        <v>1.73</v>
+        <v>2.85</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.42</v>
+        <v>1.95</v>
       </c>
       <c r="O75">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="P75">
-        <v>6.7</v>
+        <v>3.1</v>
       </c>
       <c r="Q75">
-        <v>1.97</v>
+        <v>2.33</v>
       </c>
       <c r="R75">
-        <v>2.18</v>
+        <v>2.34</v>
       </c>
       <c r="S75">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="T75">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U75">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="V75">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="W75">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X75">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y75">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z75">
-        <v>4.33</v>
+        <v>3.85</v>
       </c>
       <c r="AA75">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AB75">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AC75">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AD75">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="AE75">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AF75">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AG75">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK75">
-        <v>2.85</v>
+        <v>1.73</v>
       </c>
       <c r="AL75">
         <v>0</v>

--- a/jogos_2026-08-07.xlsx
+++ b/jogos_2026-08-07.xlsx
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,80 +4221,80 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="O24">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="P24">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="Q24">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="R24">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S24">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T24">
-        <v>3.08</v>
+        <v>2.83</v>
       </c>
       <c r="U24">
+        <v>2.6</v>
+      </c>
+      <c r="V24">
+        <v>1.41</v>
+      </c>
+      <c r="W24">
+        <v>1.1</v>
+      </c>
+      <c r="X24">
+        <v>1.04</v>
+      </c>
+      <c r="Y24">
+        <v>1.25</v>
+      </c>
+      <c r="Z24">
+        <v>3.5</v>
+      </c>
+      <c r="AA24">
+        <v>1.85</v>
+      </c>
+      <c r="AB24">
+        <v>1.95</v>
+      </c>
+      <c r="AC24">
+        <v>3.1</v>
+      </c>
+      <c r="AD24">
+        <v>1.3</v>
+      </c>
+      <c r="AE24">
+        <v>1.11</v>
+      </c>
+      <c r="AF24">
+        <v>1.85</v>
+      </c>
+      <c r="AG24">
+        <v>1.85</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ24">
+        <v>1.18</v>
+      </c>
+      <c r="AK24">
         <v>2.38</v>
-      </c>
-      <c r="V24">
-        <v>1.55</v>
-      </c>
-      <c r="W24">
-        <v>1.07</v>
-      </c>
-      <c r="X24">
-        <v>1.03</v>
-      </c>
-      <c r="Y24">
-        <v>1.2</v>
-      </c>
-      <c r="Z24">
-        <v>4.15</v>
-      </c>
-      <c r="AA24">
-        <v>1.63</v>
-      </c>
-      <c r="AB24">
-        <v>2.12</v>
-      </c>
-      <c r="AC24">
-        <v>2.63</v>
-      </c>
-      <c r="AD24">
-        <v>1.45</v>
-      </c>
-      <c r="AE24">
-        <v>1.17</v>
-      </c>
-      <c r="AF24">
-        <v>1.67</v>
-      </c>
-      <c r="AG24">
-        <v>2.1</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ24">
-        <v>1.09</v>
-      </c>
-      <c r="AK24">
-        <v>2.25</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
+        <v>1.57</v>
+      </c>
+      <c r="O26">
+        <v>4</v>
+      </c>
+      <c r="P26">
+        <v>4.7</v>
+      </c>
+      <c r="Q26">
+        <v>2</v>
+      </c>
+      <c r="R26">
+        <v>2.4</v>
+      </c>
+      <c r="S26">
+        <v>1.29</v>
+      </c>
+      <c r="T26">
+        <v>3.08</v>
+      </c>
+      <c r="U26">
+        <v>2.38</v>
+      </c>
+      <c r="V26">
         <v>1.55</v>
       </c>
-      <c r="O26">
-        <v>3.7</v>
-      </c>
-      <c r="P26">
-        <v>5</v>
-      </c>
-      <c r="Q26">
-        <v>2.03</v>
-      </c>
-      <c r="R26">
-        <v>2.3</v>
-      </c>
-      <c r="S26">
-        <v>1.3</v>
-      </c>
-      <c r="T26">
-        <v>2.83</v>
-      </c>
-      <c r="U26">
-        <v>2.6</v>
-      </c>
-      <c r="V26">
-        <v>1.41</v>
-      </c>
       <c r="W26">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X26">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y26">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z26">
-        <v>3.5</v>
+        <v>4.15</v>
       </c>
       <c r="AA26">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="AB26">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
       <c r="AC26">
-        <v>3.1</v>
+        <v>2.63</v>
       </c>
       <c r="AD26">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AE26">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF26">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AG26">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="AK26">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
+        <v>2.25</v>
+      </c>
+      <c r="O75">
+        <v>3.2</v>
+      </c>
+      <c r="P75">
+        <v>2.83</v>
+      </c>
+      <c r="Q75">
+        <v>2.8</v>
+      </c>
+      <c r="R75">
+        <v>2.21</v>
+      </c>
+      <c r="S75">
+        <v>1.36</v>
+      </c>
+      <c r="T75">
+        <v>2.99</v>
+      </c>
+      <c r="U75">
+        <v>2.7</v>
+      </c>
+      <c r="V75">
+        <v>1.4</v>
+      </c>
+      <c r="W75">
+        <v>1.08</v>
+      </c>
+      <c r="X75">
+        <v>1.05</v>
+      </c>
+      <c r="Y75">
+        <v>1.3</v>
+      </c>
+      <c r="Z75">
+        <v>3.45</v>
+      </c>
+      <c r="AA75">
         <v>1.95</v>
       </c>
-      <c r="O75">
-        <v>3.4</v>
-      </c>
-      <c r="P75">
-        <v>3.1</v>
-      </c>
-      <c r="Q75">
-        <v>2.33</v>
-      </c>
-      <c r="R75">
-        <v>2.34</v>
-      </c>
-      <c r="S75">
+      <c r="AB75">
+        <v>1.82</v>
+      </c>
+      <c r="AC75">
+        <v>3.35</v>
+      </c>
+      <c r="AD75">
         <v>1.31</v>
       </c>
-      <c r="T75">
-        <v>3.2</v>
-      </c>
-      <c r="U75">
-        <v>2.4</v>
-      </c>
-      <c r="V75">
-        <v>1.5</v>
-      </c>
-      <c r="W75">
-        <v>1.07</v>
-      </c>
-      <c r="X75">
-        <v>1.04</v>
-      </c>
-      <c r="Y75">
-        <v>1.22</v>
-      </c>
-      <c r="Z75">
-        <v>3.85</v>
-      </c>
-      <c r="AA75">
-        <v>1.75</v>
-      </c>
-      <c r="AB75">
-        <v>2.05</v>
-      </c>
-      <c r="AC75">
-        <v>2.8</v>
-      </c>
-      <c r="AD75">
-        <v>1.41</v>
-      </c>
       <c r="AE75">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AF75">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AG75">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK75">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="O76">
+        <v>3.4</v>
+      </c>
+      <c r="P76">
+        <v>3.1</v>
+      </c>
+      <c r="Q76">
+        <v>2.33</v>
+      </c>
+      <c r="R76">
+        <v>2.34</v>
+      </c>
+      <c r="S76">
+        <v>1.31</v>
+      </c>
+      <c r="T76">
         <v>3.2</v>
       </c>
-      <c r="P76">
-        <v>2.83</v>
-      </c>
-      <c r="Q76">
+      <c r="U76">
+        <v>2.4</v>
+      </c>
+      <c r="V76">
+        <v>1.5</v>
+      </c>
+      <c r="W76">
+        <v>1.07</v>
+      </c>
+      <c r="X76">
+        <v>1.04</v>
+      </c>
+      <c r="Y76">
+        <v>1.22</v>
+      </c>
+      <c r="Z76">
+        <v>3.85</v>
+      </c>
+      <c r="AA76">
+        <v>1.75</v>
+      </c>
+      <c r="AB76">
+        <v>2.05</v>
+      </c>
+      <c r="AC76">
         <v>2.8</v>
       </c>
-      <c r="R76">
-        <v>2.21</v>
-      </c>
-      <c r="S76">
-        <v>1.36</v>
-      </c>
-      <c r="T76">
-        <v>2.99</v>
-      </c>
-      <c r="U76">
-        <v>2.7</v>
-      </c>
-      <c r="V76">
-        <v>1.4</v>
-      </c>
-      <c r="W76">
-        <v>1.08</v>
-      </c>
-      <c r="X76">
-        <v>1.05</v>
-      </c>
-      <c r="Y76">
-        <v>1.3</v>
-      </c>
-      <c r="Z76">
-        <v>3.45</v>
-      </c>
-      <c r="AA76">
-        <v>1.95</v>
-      </c>
-      <c r="AB76">
-        <v>1.82</v>
-      </c>
-      <c r="AC76">
-        <v>3.35</v>
-      </c>
       <c r="AD76">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AE76">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AF76">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AG76">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK76">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AL76">
         <v>0</v>

--- a/jogos_2026-08-07.xlsx
+++ b/jogos_2026-08-07.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>3.78</v>
+        <v>3.66</v>
       </c>
       <c r="O2">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P2">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="Q2">
         <v>4</v>
@@ -650,10 +650,10 @@
         <v>2.15</v>
       </c>
       <c r="S2">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="T2">
-        <v>2.65</v>
+        <v>2.53</v>
       </c>
       <c r="U2">
         <v>2.94</v>
@@ -671,7 +671,7 @@
         <v>1.33</v>
       </c>
       <c r="Z2">
-        <v>2.94</v>
+        <v>3.24</v>
       </c>
       <c r="AA2">
         <v>2.08</v>
@@ -680,19 +680,19 @@
         <v>1.76</v>
       </c>
       <c r="AC2">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AD2">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE2">
         <v>1.08</v>
       </c>
       <c r="AF2">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AG2">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AK2">
         <v>1.25</v>
@@ -798,37 +798,37 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="O3">
         <v>3.25</v>
       </c>
       <c r="P3">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="Q3">
         <v>3.02</v>
       </c>
       <c r="R3">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="S3">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T3">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="U3">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="V3">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W3">
         <v>1.03</v>
       </c>
       <c r="X3">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y3">
         <v>1.3</v>
@@ -837,10 +837,10 @@
         <v>3.4</v>
       </c>
       <c r="AA3">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AB3">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AC3">
         <v>3.6</v>
@@ -849,13 +849,13 @@
         <v>1.29</v>
       </c>
       <c r="AE3">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF3">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AG3">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AK3">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,10 +961,10 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="O4">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="P4">
         <v>2.2</v>
@@ -988,16 +988,16 @@
         <v>1.44</v>
       </c>
       <c r="W4">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X4">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y4">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z4">
-        <v>3.72</v>
+        <v>4.2</v>
       </c>
       <c r="AA4">
         <v>1.8</v>
@@ -1006,19 +1006,19 @@
         <v>2</v>
       </c>
       <c r="AC4">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="AD4">
         <v>1.41</v>
       </c>
       <c r="AE4">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF4">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG4">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1124,28 +1124,28 @@
         </is>
       </c>
       <c r="N5">
-        <v>3.22</v>
+        <v>3.55</v>
       </c>
       <c r="O5">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P5">
         <v>1.78</v>
       </c>
       <c r="Q5">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="R5">
         <v>2.24</v>
       </c>
       <c r="S5">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="T5">
         <v>2.87</v>
       </c>
       <c r="U5">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="V5">
         <v>1.44</v>
@@ -1160,13 +1160,13 @@
         <v>1.24</v>
       </c>
       <c r="Z5">
-        <v>3.95</v>
+        <v>3.98</v>
       </c>
       <c r="AA5">
         <v>1.72</v>
       </c>
       <c r="AB5">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AC5">
         <v>2.7</v>
@@ -1178,7 +1178,7 @@
         <v>1.15</v>
       </c>
       <c r="AF5">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AG5">
         <v>2.1</v>
@@ -1287,25 +1287,25 @@
         </is>
       </c>
       <c r="N6">
-        <v>3.02</v>
+        <v>3.8</v>
       </c>
       <c r="O6">
-        <v>3.07</v>
+        <v>3.3</v>
       </c>
       <c r="P6">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
       </c>
       <c r="R6">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="S6">
         <v>1.36</v>
       </c>
       <c r="T6">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="U6">
         <v>2.88</v>
@@ -1314,10 +1314,10 @@
         <v>1.4</v>
       </c>
       <c r="W6">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X6">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y6">
         <v>1.26</v>
@@ -1332,7 +1332,7 @@
         <v>1.83</v>
       </c>
       <c r="AC6">
-        <v>3.24</v>
+        <v>3.26</v>
       </c>
       <c r="AD6">
         <v>1.3</v>
@@ -1341,7 +1341,7 @@
         <v>1.07</v>
       </c>
       <c r="AF6">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AG6">
         <v>1.95</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.73</v>
+        <v>1.24</v>
       </c>
       <c r="O7">
-        <v>3.5</v>
+        <v>5.15</v>
       </c>
       <c r="P7">
-        <v>4.28</v>
+        <v>8.19</v>
       </c>
       <c r="Q7">
-        <v>2.23</v>
+        <v>1.75</v>
       </c>
       <c r="R7">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="S7">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="T7">
-        <v>2.75</v>
+        <v>3.35</v>
       </c>
       <c r="U7">
-        <v>2.96</v>
+        <v>2.54</v>
       </c>
       <c r="V7">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="W7">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="X7">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y7">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="Z7">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="AA7">
-        <v>2.03</v>
+        <v>1.64</v>
       </c>
       <c r="AB7">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="AC7">
-        <v>3.8</v>
+        <v>2.59</v>
       </c>
       <c r="AD7">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="AE7">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AF7">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AG7">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="AK7">
-        <v>1.91</v>
+        <v>3.4</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,80 +1613,80 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.49</v>
+        <v>1.67</v>
       </c>
       <c r="O8">
-        <v>3.95</v>
+        <v>3.55</v>
       </c>
       <c r="P8">
-        <v>5.26</v>
+        <v>4.35</v>
       </c>
       <c r="Q8">
+        <v>2.23</v>
+      </c>
+      <c r="R8">
+        <v>2.1</v>
+      </c>
+      <c r="S8">
+        <v>1.41</v>
+      </c>
+      <c r="T8">
+        <v>2.75</v>
+      </c>
+      <c r="U8">
+        <v>2.77</v>
+      </c>
+      <c r="V8">
+        <v>1.37</v>
+      </c>
+      <c r="W8">
+        <v>1.05</v>
+      </c>
+      <c r="X8">
+        <v>1.04</v>
+      </c>
+      <c r="Y8">
+        <v>1.36</v>
+      </c>
+      <c r="Z8">
+        <v>2.97</v>
+      </c>
+      <c r="AA8">
+        <v>2.03</v>
+      </c>
+      <c r="AB8">
+        <v>1.65</v>
+      </c>
+      <c r="AC8">
+        <v>3.82</v>
+      </c>
+      <c r="AD8">
+        <v>1.26</v>
+      </c>
+      <c r="AE8">
+        <v>1.04</v>
+      </c>
+      <c r="AF8">
+        <v>1.9</v>
+      </c>
+      <c r="AG8">
+        <v>1.79</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8">
+        <v>1.21</v>
+      </c>
+      <c r="AK8">
         <v>2</v>
-      </c>
-      <c r="R8">
-        <v>2.28</v>
-      </c>
-      <c r="S8">
-        <v>1.33</v>
-      </c>
-      <c r="T8">
-        <v>3.1</v>
-      </c>
-      <c r="U8">
-        <v>2.53</v>
-      </c>
-      <c r="V8">
-        <v>1.44</v>
-      </c>
-      <c r="W8">
-        <v>1.07</v>
-      </c>
-      <c r="X8">
-        <v>1.02</v>
-      </c>
-      <c r="Y8">
-        <v>1.19</v>
-      </c>
-      <c r="Z8">
-        <v>3.87</v>
-      </c>
-      <c r="AA8">
-        <v>1.76</v>
-      </c>
-      <c r="AB8">
-        <v>2.02</v>
-      </c>
-      <c r="AC8">
-        <v>2.95</v>
-      </c>
-      <c r="AD8">
-        <v>1.36</v>
-      </c>
-      <c r="AE8">
-        <v>1.13</v>
-      </c>
-      <c r="AF8">
-        <v>1.8</v>
-      </c>
-      <c r="AG8">
-        <v>2</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8">
-        <v>1.16</v>
-      </c>
-      <c r="AK8">
-        <v>2.26</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,65 +1776,65 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.19</v>
+        <v>1.41</v>
       </c>
       <c r="O9">
-        <v>5.25</v>
+        <v>3.83</v>
       </c>
       <c r="P9">
-        <v>9.699999999999999</v>
+        <v>5</v>
       </c>
       <c r="Q9">
-        <v>1.75</v>
+        <v>2.02</v>
       </c>
       <c r="R9">
-        <v>2.6</v>
+        <v>2.24</v>
       </c>
       <c r="S9">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="T9">
-        <v>3.32</v>
+        <v>3.1</v>
       </c>
       <c r="U9">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="V9">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W9">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X9">
         <v>1.02</v>
       </c>
       <c r="Y9">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z9">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="AA9">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AB9">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AC9">
-        <v>2.59</v>
+        <v>2.96</v>
       </c>
       <c r="AD9">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AE9">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF9">
+        <v>1.8</v>
+      </c>
+      <c r="AG9">
         <v>1.91</v>
       </c>
-      <c r="AG9">
-        <v>1.75</v>
-      </c>
       <c r="AH9" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AK9">
-        <v>3.38</v>
+        <v>2.31</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,31 +1939,31 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="Q10">
         <v>1.74</v>
       </c>
       <c r="R10">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="S10">
         <v>1.2</v>
       </c>
       <c r="T10">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="U10">
-        <v>1.99</v>
+        <v>1.86</v>
       </c>
       <c r="V10">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="W10">
         <v>1.18</v>
@@ -1987,7 +1987,7 @@
         <v>1.96</v>
       </c>
       <c r="AD10">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AE10">
         <v>1.3</v>
@@ -2111,10 +2111,10 @@
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>5.35</v>
+        <v>5.25</v>
       </c>
       <c r="R11">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="S11">
         <v>1.36</v>
@@ -2123,37 +2123,37 @@
         <v>2.75</v>
       </c>
       <c r="U11">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="V11">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W11">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X11">
         <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="Z11">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="AA11">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AB11">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AC11">
-        <v>3.24</v>
+        <v>3.42</v>
       </c>
       <c r="AD11">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AE11">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF11">
         <v>1.9</v>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AK11">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,34 +2265,34 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="O12">
-        <v>3.1</v>
+        <v>3.41</v>
       </c>
       <c r="P12">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="Q12">
+        <v>2.75</v>
+      </c>
+      <c r="R12">
+        <v>2.1</v>
+      </c>
+      <c r="S12">
+        <v>1.37</v>
+      </c>
+      <c r="T12">
+        <v>2.9</v>
+      </c>
+      <c r="U12">
         <v>2.67</v>
       </c>
-      <c r="R12">
-        <v>2.11</v>
-      </c>
-      <c r="S12">
-        <v>1.34</v>
-      </c>
-      <c r="T12">
-        <v>2.83</v>
-      </c>
-      <c r="U12">
-        <v>2.63</v>
-      </c>
       <c r="V12">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W12">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X12">
         <v>1.01</v>
@@ -2301,25 +2301,25 @@
         <v>1.25</v>
       </c>
       <c r="Z12">
-        <v>3.38</v>
+        <v>3.8</v>
       </c>
       <c r="AA12">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AB12">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AC12">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="AD12">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AE12">
         <v>1.08</v>
       </c>
       <c r="AF12">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AG12">
         <v>2.05</v>
@@ -2338,7 +2338,7 @@
         <v>1.24</v>
       </c>
       <c r="AK12">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,19 +2428,19 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="O13">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P13">
-        <v>4.57</v>
+        <v>4.7</v>
       </c>
       <c r="Q13">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="R13">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="S13">
         <v>1.38</v>
@@ -2449,43 +2449,43 @@
         <v>2.67</v>
       </c>
       <c r="U13">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="V13">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="W13">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X13">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y13">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Z13">
-        <v>3.18</v>
+        <v>3.08</v>
       </c>
       <c r="AA13">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="AB13">
         <v>1.76</v>
       </c>
       <c r="AC13">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="AD13">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AE13">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF13">
         <v>1.9</v>
       </c>
       <c r="AG13">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.24</v>
+        <v>1.11</v>
       </c>
       <c r="AK13">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>6.83</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>6.48</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="O15">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="P15">
-        <v>4.47</v>
+        <v>4.88</v>
       </c>
       <c r="Q15">
         <v>2.1</v>
       </c>
       <c r="R15">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="S15">
         <v>1.31</v>
       </c>
       <c r="T15">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="U15">
-        <v>2.52</v>
+        <v>2.47</v>
       </c>
       <c r="V15">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W15">
         <v>1.07</v>
       </c>
       <c r="X15">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z15">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AA15">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AB15">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="AC15">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="AD15">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE15">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF15">
         <v>1.67</v>
       </c>
       <c r="AG15">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK15">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2929,7 +2929,7 @@
         <v>3.14</v>
       </c>
       <c r="R16">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="S16">
         <v>1.3</v>
@@ -2938,7 +2938,7 @@
         <v>3.3</v>
       </c>
       <c r="U16">
-        <v>2.51</v>
+        <v>2.38</v>
       </c>
       <c r="V16">
         <v>1.48</v>
@@ -2956,10 +2956,10 @@
         <v>4</v>
       </c>
       <c r="AA16">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB16">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC16">
         <v>2.7</v>
@@ -2968,13 +2968,13 @@
         <v>1.4</v>
       </c>
       <c r="AE16">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF16">
         <v>1.57</v>
       </c>
       <c r="AG16">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="O17">
         <v>3.25</v>
       </c>
       <c r="P17">
-        <v>3.76</v>
+        <v>3.4</v>
       </c>
       <c r="Q17">
         <v>2.49</v>
@@ -3098,7 +3098,7 @@
         <v>1.42</v>
       </c>
       <c r="T17">
-        <v>2.53</v>
+        <v>2.72</v>
       </c>
       <c r="U17">
         <v>2.88</v>
@@ -3107,37 +3107,37 @@
         <v>1.36</v>
       </c>
       <c r="W17">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X17">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y17">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z17">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="AA17">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AB17">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC17">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AD17">
         <v>1.25</v>
       </c>
       <c r="AE17">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF17">
         <v>1.8</v>
       </c>
       <c r="AG17">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AK17">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,25 +3243,25 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="O18">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P18">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Q18">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="R18">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S18">
         <v>1.3</v>
       </c>
       <c r="T18">
-        <v>3.15</v>
+        <v>3.08</v>
       </c>
       <c r="U18">
         <v>2.68</v>
@@ -3273,13 +3273,13 @@
         <v>1.11</v>
       </c>
       <c r="X18">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y18">
         <v>1.2</v>
       </c>
       <c r="Z18">
-        <v>4.15</v>
+        <v>4.33</v>
       </c>
       <c r="AA18">
         <v>1.67</v>
@@ -3288,16 +3288,16 @@
         <v>2.07</v>
       </c>
       <c r="AC18">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="AD18">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE18">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF18">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG18">
         <v>2.05</v>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK18">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="O19">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="P19">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,16 +3569,16 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="O20">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
       <c r="P20">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="Q20">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="R20">
         <v>2.38</v>
@@ -3593,19 +3593,19 @@
         <v>2.41</v>
       </c>
       <c r="V20">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="W20">
         <v>1.11</v>
       </c>
       <c r="X20">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y20">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z20">
-        <v>3.92</v>
+        <v>4.33</v>
       </c>
       <c r="AA20">
         <v>1.66</v>
@@ -3614,7 +3614,7 @@
         <v>2.09</v>
       </c>
       <c r="AC20">
-        <v>2.48</v>
+        <v>2.88</v>
       </c>
       <c r="AD20">
         <v>1.46</v>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK20">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3895,25 +3895,25 @@
         </is>
       </c>
       <c r="N22">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="O22">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P22">
         <v>1.7</v>
       </c>
       <c r="Q22">
-        <v>5.35</v>
+        <v>4.12</v>
       </c>
       <c r="R22">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="S22">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T22">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="U22">
         <v>2.6</v>
@@ -3925,7 +3925,7 @@
         <v>1.08</v>
       </c>
       <c r="X22">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y22">
         <v>1.21</v>
@@ -3934,25 +3934,25 @@
         <v>3.58</v>
       </c>
       <c r="AA22">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AB22">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AC22">
         <v>3.1</v>
       </c>
       <c r="AD22">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AE22">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF22">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG22">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.21</v>
+        <v>2.05</v>
       </c>
       <c r="AK22">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,16 +4058,16 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="O23">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P23">
-        <v>4.9</v>
+        <v>4.75</v>
       </c>
       <c r="Q23">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="R23">
         <v>2.25</v>
@@ -4085,10 +4085,10 @@
         <v>1.4</v>
       </c>
       <c r="W23">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X23">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
         <v>1.25</v>
@@ -4097,16 +4097,16 @@
         <v>3.5</v>
       </c>
       <c r="AA23">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AB23">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AC23">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AD23">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE23">
         <v>1.07</v>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK23">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,37 +4221,37 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="O24">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P24">
-        <v>5</v>
+        <v>5.88</v>
       </c>
       <c r="Q24">
-        <v>2.03</v>
+        <v>2.07</v>
       </c>
       <c r="R24">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S24">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T24">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="U24">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="V24">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="W24">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X24">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y24">
         <v>1.25</v>
@@ -4260,25 +4260,25 @@
         <v>3.5</v>
       </c>
       <c r="AA24">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB24">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AC24">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AD24">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE24">
         <v>1.11</v>
       </c>
       <c r="AF24">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AG24">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK24">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,19 +4384,19 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q25">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="R25">
-        <v>2.14</v>
+        <v>2.38</v>
       </c>
       <c r="S25">
         <v>1.3</v>
@@ -4405,40 +4405,40 @@
         <v>3.2</v>
       </c>
       <c r="U25">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="V25">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W25">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X25">
         <v>1.03</v>
       </c>
       <c r="Y25">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z25">
         <v>4</v>
       </c>
       <c r="AA25">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AB25">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AC25">
         <v>2.7</v>
       </c>
       <c r="AD25">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AE25">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF25">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG25">
         <v>2.2</v>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK25">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,61 +4547,61 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="O26">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="P26">
-        <v>4.7</v>
+        <v>5.28</v>
       </c>
       <c r="Q26">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="R26">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S26">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T26">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="U26">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="V26">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W26">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X26">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z26">
-        <v>4.15</v>
+        <v>4.33</v>
       </c>
       <c r="AA26">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AB26">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="AC26">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="AD26">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AE26">
         <v>1.17</v>
       </c>
       <c r="AF26">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG26">
         <v>2.1</v>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="AK26">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4873,58 +4873,58 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="O28">
-        <v>3.92</v>
+        <v>3.85</v>
       </c>
       <c r="P28">
-        <v>3.56</v>
+        <v>3.33</v>
       </c>
       <c r="Q28">
         <v>2.38</v>
       </c>
       <c r="R28">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="S28">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T28">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="U28">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="V28">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W28">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X28">
         <v>1.03</v>
       </c>
       <c r="Y28">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z28">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="AA28">
+        <v>1.5</v>
+      </c>
+      <c r="AB28">
+        <v>2.3</v>
+      </c>
+      <c r="AC28">
+        <v>2.31</v>
+      </c>
+      <c r="AD28">
         <v>1.53</v>
       </c>
-      <c r="AB28">
-        <v>2.45</v>
-      </c>
-      <c r="AC28">
-        <v>2.33</v>
-      </c>
-      <c r="AD28">
-        <v>1.58</v>
-      </c>
       <c r="AE28">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AF28">
         <v>1.46</v>
@@ -5036,19 +5036,19 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="O29">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P29">
-        <v>2.69</v>
+        <v>2.74</v>
       </c>
       <c r="Q29">
-        <v>3.02</v>
+        <v>3.3</v>
       </c>
       <c r="R29">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="S29">
         <v>1.51</v>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AK29">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,7 +5199,7 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="O30">
         <v>3.35</v>
@@ -5223,7 +5223,7 @@
         <v>2.62</v>
       </c>
       <c r="V30">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W30">
         <v>1.07</v>
@@ -5235,28 +5235,28 @@
         <v>1.25</v>
       </c>
       <c r="Z30">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AA30">
         <v>1.77</v>
       </c>
       <c r="AB30">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AC30">
-        <v>3.25</v>
+        <v>2.78</v>
       </c>
       <c r="AD30">
         <v>1.33</v>
       </c>
       <c r="AE30">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF30">
         <v>1.67</v>
       </c>
       <c r="AG30">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>1.29</v>
       </c>
       <c r="AK30">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,22 +5362,22 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="O31">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="P31">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="Q31">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="R31">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="S31">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T31">
         <v>3</v>
@@ -5386,37 +5386,37 @@
         <v>2.62</v>
       </c>
       <c r="V31">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W31">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X31">
         <v>1</v>
       </c>
       <c r="Y31">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z31">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AA31">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AB31">
-        <v>1.97</v>
+        <v>2.01</v>
       </c>
       <c r="AC31">
         <v>2.7</v>
       </c>
       <c r="AD31">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE31">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF31">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="AG31">
         <v>1.75</v>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AK31">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5528,19 +5528,19 @@
         <v>3.05</v>
       </c>
       <c r="O32">
-        <v>3.46</v>
+        <v>3.4</v>
       </c>
       <c r="P32">
         <v>2.19</v>
       </c>
       <c r="Q32">
-        <v>3.13</v>
+        <v>3.25</v>
       </c>
       <c r="R32">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S32">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T32">
         <v>3.3</v>
@@ -5549,40 +5549,40 @@
         <v>2.38</v>
       </c>
       <c r="V32">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="W32">
         <v>1.13</v>
       </c>
       <c r="X32">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y32">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z32">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AA32">
         <v>1.61</v>
       </c>
       <c r="AB32">
-        <v>2.11</v>
+        <v>2.17</v>
       </c>
       <c r="AC32">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="AD32">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="AE32">
         <v>1.14</v>
       </c>
       <c r="AF32">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AG32">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="AK32">
         <v>1.33</v>
@@ -5691,7 +5691,7 @@
         <v>2.05</v>
       </c>
       <c r="O33">
-        <v>3.64</v>
+        <v>3.5</v>
       </c>
       <c r="P33">
         <v>3.2</v>
@@ -5709,7 +5709,7 @@
         <v>3.2</v>
       </c>
       <c r="U33">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="V33">
         <v>1.5</v>
@@ -5724,25 +5724,25 @@
         <v>1.22</v>
       </c>
       <c r="Z33">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA33">
         <v>1.7</v>
       </c>
       <c r="AB33">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC33">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="AD33">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AE33">
         <v>1.15</v>
       </c>
       <c r="AF33">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AG33">
         <v>2.2</v>
@@ -5761,7 +5761,7 @@
         <v>1.22</v>
       </c>
       <c r="AK33">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.78</v>
+        <v>2.63</v>
       </c>
       <c r="O34">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P34">
-        <v>3.89</v>
+        <v>2.3</v>
       </c>
       <c r="Q34">
-        <v>2.32</v>
+        <v>4.22</v>
       </c>
       <c r="R34">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="S34">
         <v>1.25</v>
       </c>
       <c r="T34">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U34">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="V34">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="W34">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="Z34">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="AA34">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AB34">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AC34">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AD34">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="AE34">
         <v>1.16</v>
       </c>
       <c r="AF34">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="AG34">
-        <v>2.23</v>
+        <v>2.38</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK34">
-        <v>1.91</v>
+        <v>1.37</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W35">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X35">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z35">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA35">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF35">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG35">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK35">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6177,16 +6177,16 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.68</v>
+        <v>3.16</v>
       </c>
       <c r="O36">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="P36">
         <v>2.12</v>
       </c>
       <c r="Q36">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R36">
         <v>2.22</v>
@@ -6204,31 +6204,31 @@
         <v>1.53</v>
       </c>
       <c r="W36">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X36">
         <v>1.03</v>
       </c>
       <c r="Y36">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="Z36">
         <v>4.6</v>
       </c>
       <c r="AA36">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AB36">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="AC36">
         <v>2.39</v>
       </c>
       <c r="AD36">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="AE36">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AF36">
         <v>1.51</v>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AK36">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.03</v>
+        <v>2.13</v>
       </c>
       <c r="O37">
         <v>3.2</v>
       </c>
       <c r="P37">
-        <v>3.05</v>
+        <v>3.12</v>
       </c>
       <c r="Q37">
         <v>2.8</v>
@@ -6355,19 +6355,19 @@
         <v>2.05</v>
       </c>
       <c r="S37">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T37">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="U37">
         <v>3.2</v>
       </c>
       <c r="V37">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W37">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X37">
         <v>1.07</v>
@@ -6376,28 +6376,28 @@
         <v>1.32</v>
       </c>
       <c r="Z37">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="AA37">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="AB37">
         <v>1.65</v>
       </c>
       <c r="AC37">
-        <v>3.95</v>
+        <v>3.98</v>
       </c>
       <c r="AD37">
         <v>1.22</v>
       </c>
       <c r="AE37">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF37">
         <v>1.85</v>
       </c>
       <c r="AG37">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="O38">
         <v>3.25</v>
       </c>
       <c r="P38">
-        <v>2.43</v>
+        <v>1.98</v>
       </c>
       <c r="Q38">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="R38">
         <v>2.25</v>
       </c>
       <c r="S38">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T38">
-        <v>2.88</v>
+        <v>3.03</v>
       </c>
       <c r="U38">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="V38">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W38">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X38">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y38">
         <v>1.22</v>
       </c>
       <c r="Z38">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="AA38">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AB38">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="AC38">
-        <v>2.69</v>
+        <v>2.9</v>
       </c>
       <c r="AD38">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE38">
         <v>1.14</v>
       </c>
       <c r="AF38">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AG38">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
+        <v>1.57</v>
+      </c>
+      <c r="AK38">
         <v>1.25</v>
-      </c>
-      <c r="AK38">
-        <v>1.44</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,46 +6666,46 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="O39">
         <v>3.5</v>
       </c>
       <c r="P39">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="Q39">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="R39">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="S39">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T39">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U39">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="V39">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="W39">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X39">
         <v>1.03</v>
       </c>
       <c r="Y39">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="Z39">
-        <v>4.8</v>
+        <v>4.65</v>
       </c>
       <c r="AA39">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AB39">
         <v>2.3</v>
@@ -6717,13 +6717,13 @@
         <v>1.53</v>
       </c>
       <c r="AE39">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AF39">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AG39">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AK39">
         <v>1.8</v>
@@ -6832,31 +6832,31 @@
         <v>3.2</v>
       </c>
       <c r="O40">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P40">
         <v>1.91</v>
       </c>
       <c r="Q40">
-        <v>3.84</v>
+        <v>3.93</v>
       </c>
       <c r="R40">
         <v>2.5</v>
       </c>
       <c r="S40">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T40">
-        <v>3.58</v>
+        <v>3.75</v>
       </c>
       <c r="U40">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="V40">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="W40">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X40">
         <v>1.03</v>
@@ -6865,28 +6865,28 @@
         <v>1.09</v>
       </c>
       <c r="Z40">
-        <v>5.4</v>
+        <v>5.35</v>
       </c>
       <c r="AA40">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AB40">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="AC40">
         <v>2.15</v>
       </c>
       <c r="AD40">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AE40">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AF40">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AG40">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,7 +6899,7 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AK40">
         <v>1.3</v>
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="O41">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="P41">
-        <v>5.68</v>
+        <v>5.7</v>
       </c>
       <c r="Q41">
         <v>1.83</v>
@@ -7010,7 +7010,7 @@
         <v>1.19</v>
       </c>
       <c r="T41">
-        <v>4</v>
+        <v>3.82</v>
       </c>
       <c r="U41">
         <v>2.01</v>
@@ -7019,7 +7019,7 @@
         <v>1.71</v>
       </c>
       <c r="W41">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X41">
         <v>1.01</v>
@@ -7037,13 +7037,13 @@
         <v>2.7</v>
       </c>
       <c r="AC41">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AD41">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AE41">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AF41">
         <v>1.5</v>
@@ -7062,7 +7062,7 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AK41">
         <v>2.53</v>
@@ -7155,28 +7155,28 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.57</v>
+        <v>2.05</v>
       </c>
       <c r="O42">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="P42">
-        <v>6</v>
+        <v>3.41</v>
       </c>
       <c r="Q42">
-        <v>2.28</v>
+        <v>2.86</v>
       </c>
       <c r="R42">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="S42">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="T42">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="U42">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="V42">
         <v>1.28</v>
@@ -7191,28 +7191,28 @@
         <v>1.45</v>
       </c>
       <c r="Z42">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AA42">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="AB42">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AC42">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AD42">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AE42">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF42">
-        <v>2.32</v>
+        <v>2</v>
       </c>
       <c r="AG42">
-        <v>1.55</v>
+        <v>1.72</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK42">
-        <v>2.14</v>
+        <v>1.61</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,7 +7318,7 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="O43">
         <v>3.12</v>
@@ -7327,10 +7327,10 @@
         <v>2.45</v>
       </c>
       <c r="Q43">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="R43">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="S43">
         <v>1.4</v>
@@ -7363,19 +7363,19 @@
         <v>1.7</v>
       </c>
       <c r="AC43">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="AD43">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE43">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF43">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AG43">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AK43">
         <v>1.44</v>
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="O44">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P44">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="Q44">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="R44">
         <v>2.45</v>
       </c>
       <c r="S44">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T44">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="U44">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="V44">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="W44">
         <v>1.11</v>
       </c>
       <c r="X44">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y44">
         <v>1.15</v>
       </c>
       <c r="Z44">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="AA44">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AB44">
         <v>2.36</v>
       </c>
       <c r="AC44">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="AD44">
+        <v>1.47</v>
+      </c>
+      <c r="AE44">
+        <v>1.16</v>
+      </c>
+      <c r="AF44">
         <v>1.5</v>
       </c>
-      <c r="AE44">
-        <v>1.2</v>
-      </c>
-      <c r="AF44">
-        <v>1.47</v>
-      </c>
       <c r="AG44">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S45">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="T45">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U45">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V45">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W45">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X45">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y45">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z45">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AA45">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB45">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC45">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AD45">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE45">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF45">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AG45">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK45">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7807,34 +7807,34 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="O46">
-        <v>4.3</v>
+        <v>4.85</v>
       </c>
       <c r="P46">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Q46">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="R46">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="S46">
         <v>1.19</v>
       </c>
       <c r="T46">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="U46">
         <v>2.08</v>
       </c>
       <c r="V46">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="W46">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X46">
         <v>1.02</v>
@@ -7843,10 +7843,10 @@
         <v>1.08</v>
       </c>
       <c r="Z46">
-        <v>5.55</v>
+        <v>5.3</v>
       </c>
       <c r="AA46">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AB46">
         <v>2.62</v>
@@ -7855,10 +7855,10 @@
         <v>2.1</v>
       </c>
       <c r="AD46">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AE46">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AF46">
         <v>1.57</v>
@@ -7880,7 +7880,7 @@
         <v>1.14</v>
       </c>
       <c r="AK46">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7970,16 +7970,16 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="O47">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="P47">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="Q47">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="R47">
         <v>2.24</v>
@@ -8003,10 +8003,10 @@
         <v>1.03</v>
       </c>
       <c r="Y47">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z47">
-        <v>4.6</v>
+        <v>4.25</v>
       </c>
       <c r="AA47">
         <v>1.62</v>
@@ -8018,7 +8018,7 @@
         <v>2.5</v>
       </c>
       <c r="AD47">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AE47">
         <v>1.16</v>
@@ -8027,7 +8027,7 @@
         <v>1.5</v>
       </c>
       <c r="AG47">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>1.6</v>
       </c>
       <c r="AK47">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8139,55 +8139,55 @@
         <v>3.5</v>
       </c>
       <c r="P48">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="Q48">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="R48">
         <v>2.4</v>
       </c>
       <c r="S48">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T48">
-        <v>3.68</v>
+        <v>3.75</v>
       </c>
       <c r="U48">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="V48">
         <v>1.65</v>
       </c>
       <c r="W48">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X48">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y48">
         <v>1.09</v>
       </c>
       <c r="Z48">
-        <v>5.35</v>
+        <v>5.3</v>
       </c>
       <c r="AA48">
         <v>1.5</v>
       </c>
       <c r="AB48">
-        <v>2.49</v>
+        <v>2.63</v>
       </c>
       <c r="AC48">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AD48">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AE48">
         <v>1.25</v>
       </c>
       <c r="AF48">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AG48">
         <v>2.62</v>
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AK48">
         <v>1.6</v>
@@ -8296,16 +8296,16 @@
         </is>
       </c>
       <c r="N49">
-        <v>4.37</v>
+        <v>4.33</v>
       </c>
       <c r="O49">
-        <v>4.05</v>
+        <v>3.8</v>
       </c>
       <c r="P49">
         <v>1.65</v>
       </c>
       <c r="Q49">
-        <v>4.73</v>
+        <v>4.71</v>
       </c>
       <c r="R49">
         <v>2.45</v>
@@ -8314,16 +8314,16 @@
         <v>1.24</v>
       </c>
       <c r="T49">
-        <v>3.44</v>
+        <v>3.6</v>
       </c>
       <c r="U49">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="V49">
         <v>1.62</v>
       </c>
       <c r="W49">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X49">
         <v>1.03</v>
@@ -8341,7 +8341,7 @@
         <v>2.4</v>
       </c>
       <c r="AC49">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AD49">
         <v>1.55</v>
@@ -8465,19 +8465,19 @@
         <v>3.5</v>
       </c>
       <c r="P50">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="Q50">
         <v>2.61</v>
       </c>
       <c r="R50">
-        <v>2.45</v>
+        <v>2.28</v>
       </c>
       <c r="S50">
         <v>1.25</v>
       </c>
       <c r="T50">
-        <v>3.36</v>
+        <v>3.6</v>
       </c>
       <c r="U50">
         <v>2.25</v>
@@ -8495,25 +8495,25 @@
         <v>1.12</v>
       </c>
       <c r="Z50">
-        <v>4.81</v>
+        <v>4.85</v>
       </c>
       <c r="AA50">
         <v>1.53</v>
       </c>
       <c r="AB50">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="AC50">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="AD50">
         <v>1.53</v>
       </c>
       <c r="AE50">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AF50">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AG50">
         <v>2.55</v>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK50">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,25 +8622,25 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.4</v>
+        <v>1.39</v>
       </c>
       <c r="O51">
-        <v>3.5</v>
+        <v>4.75</v>
       </c>
       <c r="P51">
-        <v>2.42</v>
+        <v>5.4</v>
       </c>
       <c r="Q51">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="R51">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="S51">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="T51">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="U51">
         <v>2.1</v>
@@ -8652,50 +8652,50 @@
         <v>1.13</v>
       </c>
       <c r="X51">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Z51">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AA51">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AB51">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="AC51">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="AD51">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AE51">
         <v>1.23</v>
       </c>
       <c r="AF51">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AG51">
+        <v>2.3</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ51">
+        <v>1.11</v>
+      </c>
+      <c r="AK51">
         <v>2.7</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ51">
-        <v>1.2</v>
-      </c>
-      <c r="AK51">
-        <v>1.42</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.4</v>
+        <v>2.44</v>
       </c>
       <c r="O52">
-        <v>4.75</v>
+        <v>3.5</v>
       </c>
       <c r="P52">
-        <v>5.6</v>
+        <v>2.42</v>
       </c>
       <c r="Q52">
-        <v>1.81</v>
+        <v>2.8</v>
       </c>
       <c r="R52">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="S52">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="T52">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U52">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="V52">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="W52">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X52">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y52">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z52">
         <v>5.5</v>
       </c>
       <c r="AA52">
+        <v>1.5</v>
+      </c>
+      <c r="AB52">
+        <v>2.45</v>
+      </c>
+      <c r="AC52">
+        <v>2.12</v>
+      </c>
+      <c r="AD52">
+        <v>1.64</v>
+      </c>
+      <c r="AE52">
+        <v>1.23</v>
+      </c>
+      <c r="AF52">
         <v>1.4</v>
       </c>
-      <c r="AB52">
-        <v>2.75</v>
-      </c>
-      <c r="AC52">
-        <v>2.08</v>
-      </c>
-      <c r="AD52">
-        <v>1.67</v>
-      </c>
-      <c r="AE52">
-        <v>1.24</v>
-      </c>
-      <c r="AF52">
-        <v>1.59</v>
-      </c>
       <c r="AG52">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AK52">
-        <v>2.72</v>
+        <v>1.42</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8948,10 +8948,10 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O53">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="P53">
         <v>9</v>
@@ -8963,43 +8963,43 @@
         <v>2.45</v>
       </c>
       <c r="S53">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T53">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="U53">
-        <v>2.68</v>
+        <v>2.56</v>
       </c>
       <c r="V53">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W53">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X53">
         <v>1</v>
       </c>
       <c r="Y53">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z53">
-        <v>3.9</v>
+        <v>3.72</v>
       </c>
       <c r="AA53">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AB53">
         <v>2</v>
       </c>
       <c r="AC53">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AD53">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE53">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF53">
         <v>2.23</v>
@@ -9021,7 +9021,7 @@
         <v>1.06</v>
       </c>
       <c r="AK53">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9111,10 +9111,10 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="O54">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P54">
         <v>3</v>
@@ -9123,25 +9123,25 @@
         <v>2.7</v>
       </c>
       <c r="R54">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S54">
         <v>1.31</v>
       </c>
       <c r="T54">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="U54">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="V54">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W54">
         <v>1.07</v>
       </c>
       <c r="X54">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y54">
         <v>1.19</v>
@@ -9150,10 +9150,10 @@
         <v>3.82</v>
       </c>
       <c r="AA54">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AB54">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="AC54">
         <v>2.88</v>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK54">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9277,19 +9277,19 @@
         <v>2.3</v>
       </c>
       <c r="O55">
-        <v>3.2</v>
+        <v>2.98</v>
       </c>
       <c r="P55">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="Q55">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="R55">
         <v>2.03</v>
       </c>
       <c r="S55">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="T55">
         <v>2.8</v>
@@ -9310,16 +9310,16 @@
         <v>1.26</v>
       </c>
       <c r="Z55">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AA55">
         <v>2</v>
       </c>
       <c r="AB55">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AC55">
-        <v>3.35</v>
+        <v>3.14</v>
       </c>
       <c r="AD55">
         <v>1.3</v>
@@ -9328,7 +9328,7 @@
         <v>1.08</v>
       </c>
       <c r="AF55">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AG55">
         <v>2.05</v>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AK55">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9437,16 +9437,16 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="O56">
         <v>3.8</v>
       </c>
       <c r="P56">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Q56">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="R56">
         <v>2.53</v>
@@ -9455,16 +9455,16 @@
         <v>1.27</v>
       </c>
       <c r="T56">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="U56">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="V56">
         <v>1.56</v>
       </c>
       <c r="W56">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X56">
         <v>1.03</v>
@@ -9473,28 +9473,28 @@
         <v>1.18</v>
       </c>
       <c r="Z56">
-        <v>4.53</v>
+        <v>4.58</v>
       </c>
       <c r="AA56">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AB56">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="AC56">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
       <c r="AD56">
         <v>1.5</v>
       </c>
       <c r="AE56">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AF56">
         <v>1.62</v>
       </c>
       <c r="AG56">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AK56">
         <v>2.25</v>
@@ -9603,10 +9603,10 @@
         <v>1.8</v>
       </c>
       <c r="O57">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="P57">
-        <v>3.9</v>
+        <v>4.15</v>
       </c>
       <c r="Q57">
         <v>2.3</v>
@@ -9615,40 +9615,40 @@
         <v>2.28</v>
       </c>
       <c r="S57">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="T57">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="U57">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="V57">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W57">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X57">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y57">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="Z57">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="AA57">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="AB57">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AC57">
-        <v>2.97</v>
+        <v>3.19</v>
       </c>
       <c r="AD57">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE57">
         <v>1.08</v>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AK57">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="O58">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P58">
-        <v>2.87</v>
+        <v>2.98</v>
       </c>
       <c r="Q58">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="R58">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S58">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T58">
-        <v>3.22</v>
+        <v>3.04</v>
       </c>
       <c r="U58">
         <v>2.28</v>
       </c>
       <c r="V58">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W58">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X58">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y58">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z58">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="AA58">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AB58">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AC58">
-        <v>2.44</v>
+        <v>2.57</v>
       </c>
       <c r="AD58">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AE58">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AF58">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AG58">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,7 +9833,7 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK58">
         <v>1.6</v>
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>6</v>
+        <v>6.85</v>
       </c>
       <c r="O59">
-        <v>4.2</v>
+        <v>4.35</v>
       </c>
       <c r="P59">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="Q59">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="R59">
-        <v>2.33</v>
+        <v>2.47</v>
       </c>
       <c r="S59">
         <v>1.3</v>
       </c>
       <c r="T59">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="U59">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="V59">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W59">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X59">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y59">
         <v>1.22</v>
       </c>
       <c r="Z59">
-        <v>3.86</v>
+        <v>3.92</v>
       </c>
       <c r="AA59">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AB59">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AC59">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AD59">
         <v>1.4</v>
       </c>
       <c r="AE59">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AF59">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG59">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -10089,16 +10089,16 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="O60">
-        <v>4.65</v>
+        <v>4.4</v>
       </c>
       <c r="P60">
-        <v>4.89</v>
+        <v>4.73</v>
       </c>
       <c r="Q60">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="R60">
         <v>2.64</v>
@@ -10116,16 +10116,16 @@
         <v>1.61</v>
       </c>
       <c r="W60">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X60">
         <v>1.02</v>
       </c>
       <c r="Y60">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="Z60">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="AA60">
         <v>1.5</v>
@@ -10143,7 +10143,7 @@
         <v>1.22</v>
       </c>
       <c r="AF60">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG60">
         <v>1.95</v>
@@ -10162,7 +10162,7 @@
         <v>1.12</v>
       </c>
       <c r="AK60">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="O63">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="P63">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="Q63">
         <v>0</v>
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O64">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P64">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -10904,13 +10904,13 @@
         </is>
       </c>
       <c r="N65">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O65">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P65">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q65">
         <v>0</v>
@@ -11236,7 +11236,7 @@
         <v>3</v>
       </c>
       <c r="P67">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="Q67">
         <v>0</v>
@@ -11559,10 +11559,10 @@
         <v>2.05</v>
       </c>
       <c r="O69">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="P69">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="Q69">
         <v>0</v>
@@ -12045,52 +12045,52 @@
         </is>
       </c>
       <c r="N72">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="O72">
-        <v>5.1</v>
+        <v>5.25</v>
       </c>
       <c r="P72">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
       <c r="Q72">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="R72">
-        <v>2.63</v>
+        <v>2.92</v>
       </c>
       <c r="S72">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T72">
-        <v>3.5</v>
+        <v>3.72</v>
       </c>
       <c r="U72">
-        <v>2.22</v>
+        <v>2.11</v>
       </c>
       <c r="V72">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="W72">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X72">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y72">
         <v>1.1</v>
       </c>
       <c r="Z72">
-        <v>4.75</v>
+        <v>5.25</v>
       </c>
       <c r="AA72">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="AB72">
         <v>2.6</v>
       </c>
       <c r="AC72">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="AD72">
         <v>1.62</v>
@@ -12099,10 +12099,10 @@
         <v>1.25</v>
       </c>
       <c r="AF72">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AG72">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AK72">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12211,10 +12211,10 @@
         <v>2.07</v>
       </c>
       <c r="O73">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P73">
-        <v>3.24</v>
+        <v>3.05</v>
       </c>
       <c r="Q73">
         <v>2.65</v>
@@ -12226,10 +12226,10 @@
         <v>1.33</v>
       </c>
       <c r="T73">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="U73">
-        <v>2.56</v>
+        <v>2.32</v>
       </c>
       <c r="V73">
         <v>1.46</v>
@@ -12238,34 +12238,34 @@
         <v>1.05</v>
       </c>
       <c r="X73">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y73">
         <v>1.25</v>
       </c>
       <c r="Z73">
-        <v>3.83</v>
+        <v>3.75</v>
       </c>
       <c r="AA73">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AB73">
         <v>2.01</v>
       </c>
       <c r="AC73">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="AD73">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE73">
         <v>1.13</v>
       </c>
       <c r="AF73">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="AG73">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12371,37 +12371,37 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="O74">
-        <v>3.9</v>
+        <v>4.55</v>
       </c>
       <c r="P74">
-        <v>6.7</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="Q74">
-        <v>1.97</v>
+        <v>1.75</v>
       </c>
       <c r="R74">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="S74">
         <v>1.25</v>
       </c>
       <c r="T74">
-        <v>3.3</v>
+        <v>2.96</v>
       </c>
       <c r="U74">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="V74">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="W74">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X74">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y74">
         <v>1.2</v>
@@ -12416,16 +12416,16 @@
         <v>2.15</v>
       </c>
       <c r="AC74">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AD74">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AE74">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF74">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AG74">
         <v>1.85</v>
@@ -12444,7 +12444,7 @@
         <v>1.2</v>
       </c>
       <c r="AK74">
-        <v>2.85</v>
+        <v>2.64</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12534,7 +12534,7 @@
         </is>
       </c>
       <c r="N75">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="O75">
         <v>3.2</v>
@@ -12549,16 +12549,16 @@
         <v>2.21</v>
       </c>
       <c r="S75">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T75">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="U75">
         <v>2.7</v>
       </c>
       <c r="V75">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W75">
         <v>1.08</v>
@@ -12573,22 +12573,22 @@
         <v>3.45</v>
       </c>
       <c r="AA75">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AB75">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AC75">
         <v>3.35</v>
       </c>
       <c r="AD75">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AE75">
         <v>1.1</v>
       </c>
       <c r="AF75">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AG75">
         <v>2</v>
@@ -12604,7 +12604,7 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK75">
         <v>1.53</v>
@@ -12697,25 +12697,25 @@
         </is>
       </c>
       <c r="N76">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="O76">
         <v>3.4</v>
       </c>
       <c r="P76">
-        <v>3.1</v>
+        <v>3.29</v>
       </c>
       <c r="Q76">
-        <v>2.33</v>
+        <v>2.49</v>
       </c>
       <c r="R76">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="S76">
         <v>1.31</v>
       </c>
       <c r="T76">
-        <v>3.2</v>
+        <v>3.02</v>
       </c>
       <c r="U76">
         <v>2.4</v>
@@ -12727,34 +12727,34 @@
         <v>1.07</v>
       </c>
       <c r="X76">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y76">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z76">
         <v>3.85</v>
       </c>
       <c r="AA76">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AB76">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AC76">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="AD76">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AE76">
         <v>1.15</v>
       </c>
       <c r="AF76">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG76">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12863,10 +12863,10 @@
         <v>1.25</v>
       </c>
       <c r="O77">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="P77">
-        <v>9.5</v>
+        <v>8.6</v>
       </c>
       <c r="Q77">
         <v>0</v>
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O79">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P79">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q79">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="R79">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S79">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T79">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U79">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="V79">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W79">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X79">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y79">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z79">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA79">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB79">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC79">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AD79">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE79">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF79">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG79">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK79">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13355,52 +13355,52 @@
         <v>3.3</v>
       </c>
       <c r="P80">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="Q80">
-        <v>3.56</v>
+        <v>3.76</v>
       </c>
       <c r="R80">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="S80">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="T80">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
       <c r="U80">
         <v>2.65</v>
       </c>
       <c r="V80">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W80">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X80">
         <v>1.06</v>
       </c>
       <c r="Y80">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Z80">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AA80">
         <v>1.94</v>
       </c>
       <c r="AB80">
-        <v>1.74</v>
+        <v>1.87</v>
       </c>
       <c r="AC80">
-        <v>2.99</v>
+        <v>3.3</v>
       </c>
       <c r="AD80">
         <v>1.33</v>
       </c>
       <c r="AE80">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF80">
         <v>1.71</v>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AK80">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13512,7 +13512,7 @@
         </is>
       </c>
       <c r="N81">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="O81">
         <v>4</v>
@@ -13521,22 +13521,22 @@
         <v>3.6</v>
       </c>
       <c r="Q81">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="R81">
-        <v>2.53</v>
+        <v>2.63</v>
       </c>
       <c r="S81">
         <v>1.18</v>
       </c>
       <c r="T81">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="U81">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="V81">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="W81">
         <v>1.22</v>
@@ -13551,10 +13551,10 @@
         <v>6.15</v>
       </c>
       <c r="AA81">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AB81">
-        <v>2.92</v>
+        <v>2.95</v>
       </c>
       <c r="AC81">
         <v>1.85</v>
@@ -13563,10 +13563,10 @@
         <v>1.85</v>
       </c>
       <c r="AE81">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AF81">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AG81">
         <v>2.9</v>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK81">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13838,13 +13838,13 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="O83">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P83">
-        <v>3.6</v>
+        <v>4.73</v>
       </c>
       <c r="Q83">
         <v>2.6</v>
@@ -13853,10 +13853,10 @@
         <v>2.1</v>
       </c>
       <c r="S83">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T83">
-        <v>2.8</v>
+        <v>2.56</v>
       </c>
       <c r="U83">
         <v>2.9</v>
@@ -13880,7 +13880,7 @@
         <v>2.1</v>
       </c>
       <c r="AB83">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC83">
         <v>3.75</v>
@@ -13895,7 +13895,7 @@
         <v>1.83</v>
       </c>
       <c r="AG83">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -14001,19 +14001,19 @@
         </is>
       </c>
       <c r="N84">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="O84">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="P84">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="Q84">
         <v>2.5</v>
       </c>
       <c r="R84">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="S84">
         <v>1.5</v>
@@ -14022,13 +14022,13 @@
         <v>2.5</v>
       </c>
       <c r="U84">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="V84">
         <v>1.22</v>
       </c>
       <c r="W84">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="X84">
         <v>1.13</v>
@@ -14037,13 +14037,13 @@
         <v>1.47</v>
       </c>
       <c r="Z84">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="AA84">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="AB84">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AC84">
         <v>4.8</v>
@@ -14164,7 +14164,7 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="O85">
         <v>3.6</v>
@@ -14173,55 +14173,55 @@
         <v>4.6</v>
       </c>
       <c r="Q85">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="R85">
         <v>2.3</v>
       </c>
       <c r="S85">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T85">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="U85">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="V85">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="W85">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X85">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y85">
         <v>1.22</v>
       </c>
       <c r="Z85">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="AA85">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB85">
         <v>1.96</v>
       </c>
       <c r="AC85">
-        <v>2.74</v>
+        <v>2.85</v>
       </c>
       <c r="AD85">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AE85">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF85">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AG85">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14237,7 +14237,7 @@
         <v>1.25</v>
       </c>
       <c r="AK85">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14345,7 +14345,7 @@
         <v>1.25</v>
       </c>
       <c r="T86">
-        <v>2.75</v>
+        <v>3.6</v>
       </c>
       <c r="U86">
         <v>2.15</v>
@@ -14357,34 +14357,34 @@
         <v>1.14</v>
       </c>
       <c r="X86">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y86">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z86">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AA86">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AB86">
         <v>2.38</v>
       </c>
       <c r="AC86">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="AD86">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="AE86">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF86">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG86">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="AK86">
-        <v>1.93</v>
+        <v>2.01</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14493,28 +14493,28 @@
         <v>1.8</v>
       </c>
       <c r="O87">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P87">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="Q87">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="R87">
-        <v>2.44</v>
+        <v>2.55</v>
       </c>
       <c r="S87">
         <v>1.18</v>
       </c>
       <c r="T87">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="U87">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="V87">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="W87">
         <v>1.22</v>
@@ -14523,28 +14523,28 @@
         <v>1.01</v>
       </c>
       <c r="Y87">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z87">
-        <v>6.4</v>
+        <v>6.35</v>
       </c>
       <c r="AA87">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AB87">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="AC87">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AD87">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AE87">
         <v>1.33</v>
       </c>
       <c r="AF87">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AG87">
         <v>3</v>
@@ -14563,7 +14563,7 @@
         <v>1.18</v>
       </c>
       <c r="AK87">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14653,19 +14653,19 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="O88">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="P88">
-        <v>8.630000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="Q88">
         <v>1.84</v>
       </c>
       <c r="R88">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="S88">
         <v>1.36</v>
@@ -14677,13 +14677,13 @@
         <v>2.5</v>
       </c>
       <c r="V88">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="W88">
         <v>1.05</v>
       </c>
       <c r="X88">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y88">
         <v>1.27</v>
@@ -14701,16 +14701,16 @@
         <v>2.88</v>
       </c>
       <c r="AD88">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE88">
         <v>1.08</v>
       </c>
       <c r="AF88">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AG88">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14837,16 +14837,16 @@
         <v>3.32</v>
       </c>
       <c r="U89">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="V89">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W89">
         <v>1.09</v>
       </c>
       <c r="X89">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y89">
         <v>1.13</v>
@@ -14870,10 +14870,10 @@
         <v>1.16</v>
       </c>
       <c r="AF89">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="AG89">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,7 +14886,7 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.97</v>
+        <v>1.19</v>
       </c>
       <c r="AK89">
         <v>1.15</v>
@@ -14982,7 +14982,7 @@
         <v>2.66</v>
       </c>
       <c r="O90">
-        <v>3.72</v>
+        <v>3.6</v>
       </c>
       <c r="P90">
         <v>2.3</v>
@@ -15142,49 +15142,49 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="O91">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P91">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q91">
         <v>3.24</v>
       </c>
       <c r="R91">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="S91">
         <v>1.36</v>
       </c>
       <c r="T91">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="U91">
-        <v>2.82</v>
+        <v>2.93</v>
       </c>
       <c r="V91">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W91">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X91">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y91">
         <v>1.27</v>
       </c>
       <c r="Z91">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="AA91">
         <v>2</v>
       </c>
       <c r="AB91">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AC91">
         <v>3.2</v>
@@ -15193,10 +15193,10 @@
         <v>1.3</v>
       </c>
       <c r="AE91">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF91">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG91">
         <v>2</v>
@@ -15212,7 +15212,7 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK91">
         <v>1.48</v>
@@ -15305,64 +15305,64 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="O92">
-        <v>3.24</v>
+        <v>3.15</v>
       </c>
       <c r="P92">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="Q92">
         <v>2.5</v>
       </c>
       <c r="R92">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S92">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="T92">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="U92">
-        <v>2.79</v>
+        <v>2.88</v>
       </c>
       <c r="V92">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W92">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X92">
         <v>1.06</v>
       </c>
       <c r="Y92">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="Z92">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="AA92">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="AB92">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="AC92">
-        <v>3.28</v>
+        <v>3.7</v>
       </c>
       <c r="AD92">
         <v>1.25</v>
       </c>
       <c r="AE92">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF92">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AG92">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK92">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15480,13 +15480,13 @@
         <v>3.25</v>
       </c>
       <c r="R93">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="S93">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T93">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="U93">
         <v>2.5</v>
@@ -15495,31 +15495,31 @@
         <v>1.44</v>
       </c>
       <c r="W93">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X93">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y93">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z93">
         <v>3.84</v>
       </c>
       <c r="AA93">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB93">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AC93">
         <v>3</v>
       </c>
       <c r="AD93">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AE93">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF93">
         <v>1.57</v>
@@ -15794,13 +15794,13 @@
         </is>
       </c>
       <c r="N95">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="O95">
-        <v>5.45</v>
+        <v>5</v>
       </c>
       <c r="P95">
-        <v>8.25</v>
+        <v>7</v>
       </c>
       <c r="Q95">
         <v>1.7</v>
@@ -15812,16 +15812,16 @@
         <v>1.22</v>
       </c>
       <c r="T95">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="U95">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="V95">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="W95">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X95">
         <v>1.02</v>
@@ -15851,7 +15851,7 @@
         <v>1.75</v>
       </c>
       <c r="AG95">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>

--- a/jogos_2026-08-07.xlsx
+++ b/jogos_2026-08-07.xlsx
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>3.8</v>
+        <v>1.67</v>
       </c>
       <c r="O6">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="P6">
-        <v>1.87</v>
+        <v>4.35</v>
       </c>
       <c r="Q6">
-        <v>4.33</v>
+        <v>2.23</v>
       </c>
       <c r="R6">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="S6">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="T6">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="U6">
-        <v>2.88</v>
+        <v>2.77</v>
       </c>
       <c r="V6">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W6">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X6">
         <v>1.04</v>
       </c>
       <c r="Y6">
+        <v>1.36</v>
+      </c>
+      <c r="Z6">
+        <v>2.97</v>
+      </c>
+      <c r="AA6">
+        <v>2.03</v>
+      </c>
+      <c r="AB6">
+        <v>1.65</v>
+      </c>
+      <c r="AC6">
+        <v>3.82</v>
+      </c>
+      <c r="AD6">
         <v>1.26</v>
       </c>
-      <c r="Z6">
-        <v>3.2</v>
-      </c>
-      <c r="AA6">
-        <v>1.87</v>
-      </c>
-      <c r="AB6">
-        <v>1.83</v>
-      </c>
-      <c r="AC6">
-        <v>3.26</v>
-      </c>
-      <c r="AD6">
-        <v>1.3</v>
-      </c>
       <c r="AE6">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF6">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AG6">
-        <v>1.95</v>
+        <v>1.79</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AK6">
-        <v>1.19</v>
+        <v>2</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.24</v>
+        <v>3.8</v>
       </c>
       <c r="O7">
-        <v>5.15</v>
+        <v>3.3</v>
       </c>
       <c r="P7">
-        <v>8.19</v>
+        <v>1.87</v>
       </c>
       <c r="Q7">
+        <v>4.33</v>
+      </c>
+      <c r="R7">
+        <v>2.12</v>
+      </c>
+      <c r="S7">
+        <v>1.36</v>
+      </c>
+      <c r="T7">
+        <v>2.9</v>
+      </c>
+      <c r="U7">
+        <v>2.88</v>
+      </c>
+      <c r="V7">
+        <v>1.4</v>
+      </c>
+      <c r="W7">
+        <v>1.08</v>
+      </c>
+      <c r="X7">
+        <v>1.04</v>
+      </c>
+      <c r="Y7">
+        <v>1.26</v>
+      </c>
+      <c r="Z7">
+        <v>3.2</v>
+      </c>
+      <c r="AA7">
+        <v>1.87</v>
+      </c>
+      <c r="AB7">
+        <v>1.83</v>
+      </c>
+      <c r="AC7">
+        <v>3.26</v>
+      </c>
+      <c r="AD7">
+        <v>1.3</v>
+      </c>
+      <c r="AE7">
+        <v>1.07</v>
+      </c>
+      <c r="AF7">
         <v>1.75</v>
       </c>
-      <c r="R7">
-        <v>2.6</v>
-      </c>
-      <c r="S7">
-        <v>1.27</v>
-      </c>
-      <c r="T7">
-        <v>3.35</v>
-      </c>
-      <c r="U7">
-        <v>2.54</v>
-      </c>
-      <c r="V7">
-        <v>1.5</v>
-      </c>
-      <c r="W7">
-        <v>1.13</v>
-      </c>
-      <c r="X7">
-        <v>1.02</v>
-      </c>
-      <c r="Y7">
-        <v>1.22</v>
-      </c>
-      <c r="Z7">
-        <v>4.4</v>
-      </c>
-      <c r="AA7">
-        <v>1.64</v>
-      </c>
-      <c r="AB7">
-        <v>2.2</v>
-      </c>
-      <c r="AC7">
-        <v>2.59</v>
-      </c>
-      <c r="AD7">
-        <v>1.39</v>
-      </c>
-      <c r="AE7">
-        <v>1.14</v>
-      </c>
-      <c r="AF7">
-        <v>1.91</v>
-      </c>
       <c r="AG7">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="AK7">
-        <v>3.4</v>
+        <v>1.19</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.67</v>
+        <v>1.24</v>
       </c>
       <c r="O8">
-        <v>3.55</v>
+        <v>5.15</v>
       </c>
       <c r="P8">
-        <v>4.35</v>
+        <v>8.19</v>
       </c>
       <c r="Q8">
-        <v>2.23</v>
+        <v>1.75</v>
       </c>
       <c r="R8">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="S8">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="T8">
-        <v>2.75</v>
+        <v>3.35</v>
       </c>
       <c r="U8">
-        <v>2.77</v>
+        <v>2.54</v>
       </c>
       <c r="V8">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="W8">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="X8">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y8">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="Z8">
-        <v>2.97</v>
+        <v>4.4</v>
       </c>
       <c r="AA8">
-        <v>2.03</v>
+        <v>1.64</v>
       </c>
       <c r="AB8">
-        <v>1.65</v>
+        <v>2.2</v>
       </c>
       <c r="AC8">
-        <v>3.82</v>
+        <v>2.59</v>
       </c>
       <c r="AD8">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="AE8">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AF8">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AG8">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="AK8">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,80 +4221,80 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="O24">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="P24">
-        <v>5.88</v>
+        <v>3.4</v>
       </c>
       <c r="Q24">
-        <v>2.07</v>
+        <v>2.4</v>
       </c>
       <c r="R24">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="S24">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T24">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U24">
-        <v>2.59</v>
+        <v>2.47</v>
       </c>
       <c r="V24">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="W24">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X24">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y24">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z24">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AA24">
+        <v>1.68</v>
+      </c>
+      <c r="AB24">
+        <v>2.02</v>
+      </c>
+      <c r="AC24">
+        <v>2.7</v>
+      </c>
+      <c r="AD24">
+        <v>1.4</v>
+      </c>
+      <c r="AE24">
+        <v>1.15</v>
+      </c>
+      <c r="AF24">
+        <v>1.62</v>
+      </c>
+      <c r="AG24">
+        <v>2.2</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ24">
+        <v>1.19</v>
+      </c>
+      <c r="AK24">
         <v>1.8</v>
-      </c>
-      <c r="AB24">
-        <v>1.93</v>
-      </c>
-      <c r="AC24">
-        <v>3.2</v>
-      </c>
-      <c r="AD24">
-        <v>1.33</v>
-      </c>
-      <c r="AE24">
-        <v>1.11</v>
-      </c>
-      <c r="AF24">
-        <v>1.87</v>
-      </c>
-      <c r="AG24">
-        <v>1.79</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ24">
-        <v>1.25</v>
-      </c>
-      <c r="AK24">
-        <v>2.3</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="O25">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="P25">
-        <v>3.4</v>
+        <v>5.88</v>
       </c>
       <c r="Q25">
-        <v>2.4</v>
+        <v>2.07</v>
       </c>
       <c r="R25">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="S25">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T25">
+        <v>3</v>
+      </c>
+      <c r="U25">
+        <v>2.59</v>
+      </c>
+      <c r="V25">
+        <v>1.39</v>
+      </c>
+      <c r="W25">
+        <v>1.04</v>
+      </c>
+      <c r="X25">
+        <v>1.02</v>
+      </c>
+      <c r="Y25">
+        <v>1.25</v>
+      </c>
+      <c r="Z25">
+        <v>3.5</v>
+      </c>
+      <c r="AA25">
+        <v>1.8</v>
+      </c>
+      <c r="AB25">
+        <v>1.93</v>
+      </c>
+      <c r="AC25">
         <v>3.2</v>
       </c>
-      <c r="U25">
-        <v>2.47</v>
-      </c>
-      <c r="V25">
-        <v>1.44</v>
-      </c>
-      <c r="W25">
-        <v>1.06</v>
-      </c>
-      <c r="X25">
-        <v>1.03</v>
-      </c>
-      <c r="Y25">
-        <v>1.2</v>
-      </c>
-      <c r="Z25">
-        <v>4</v>
-      </c>
-      <c r="AA25">
-        <v>1.68</v>
-      </c>
-      <c r="AB25">
-        <v>2.02</v>
-      </c>
-      <c r="AC25">
-        <v>2.7</v>
-      </c>
       <c r="AD25">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AE25">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AF25">
-        <v>1.62</v>
+        <v>1.87</v>
       </c>
       <c r="AG25">
-        <v>2.2</v>
+        <v>1.79</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK25">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -10273,10 +10273,10 @@
         <v>3.3</v>
       </c>
       <c r="U61">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="V61">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W61">
         <v>1.08</v>
@@ -10285,10 +10285,10 @@
         <v>1.04</v>
       </c>
       <c r="Y61">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="Z61">
-        <v>3.82</v>
+        <v>3.6</v>
       </c>
       <c r="AA61">
         <v>1.71</v>
@@ -10309,7 +10309,7 @@
         <v>1.85</v>
       </c>
       <c r="AG61">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10418,22 +10418,22 @@
         <v>1.98</v>
       </c>
       <c r="O62">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P62">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q62">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="R62">
         <v>2.33</v>
       </c>
       <c r="S62">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T62">
-        <v>3.21</v>
+        <v>3.23</v>
       </c>
       <c r="U62">
         <v>2.43</v>
@@ -10442,10 +10442,10 @@
         <v>1.45</v>
       </c>
       <c r="W62">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X62">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y62">
         <v>1.25</v>
@@ -10457,22 +10457,22 @@
         <v>1.77</v>
       </c>
       <c r="AB62">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AC62">
-        <v>2.68</v>
+        <v>2.71</v>
       </c>
       <c r="AD62">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AE62">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF62">
         <v>1.58</v>
       </c>
       <c r="AG62">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>1.24</v>
       </c>
       <c r="AK62">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.35</v>
+        <v>1.98</v>
       </c>
       <c r="O74">
-        <v>4.55</v>
+        <v>3.4</v>
       </c>
       <c r="P74">
-        <v>8.449999999999999</v>
+        <v>3.29</v>
       </c>
       <c r="Q74">
-        <v>1.75</v>
+        <v>2.49</v>
       </c>
       <c r="R74">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="S74">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="T74">
-        <v>2.96</v>
+        <v>3.02</v>
       </c>
       <c r="U74">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V74">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W74">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X74">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y74">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z74">
-        <v>4.33</v>
+        <v>3.85</v>
       </c>
       <c r="AA74">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AB74">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="AC74">
-        <v>2.63</v>
+        <v>2.81</v>
       </c>
       <c r="AD74">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AE74">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF74">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AG74">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK74">
-        <v>2.64</v>
+        <v>1.73</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
-        <v>2.18</v>
+        <v>1.35</v>
       </c>
       <c r="O75">
-        <v>3.2</v>
+        <v>4.55</v>
       </c>
       <c r="P75">
-        <v>2.83</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="Q75">
-        <v>2.8</v>
+        <v>1.75</v>
       </c>
       <c r="R75">
-        <v>2.21</v>
+        <v>2.5</v>
       </c>
       <c r="S75">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="T75">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="U75">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="V75">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="W75">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X75">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y75">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="Z75">
-        <v>3.45</v>
+        <v>4.33</v>
       </c>
       <c r="AA75">
-        <v>1.92</v>
+        <v>1.62</v>
       </c>
       <c r="AB75">
+        <v>2.15</v>
+      </c>
+      <c r="AC75">
+        <v>2.63</v>
+      </c>
+      <c r="AD75">
+        <v>1.5</v>
+      </c>
+      <c r="AE75">
+        <v>1.17</v>
+      </c>
+      <c r="AF75">
         <v>1.85</v>
       </c>
-      <c r="AC75">
-        <v>3.35</v>
-      </c>
-      <c r="AD75">
-        <v>1.32</v>
-      </c>
-      <c r="AE75">
-        <v>1.1</v>
-      </c>
-      <c r="AF75">
-        <v>1.69</v>
-      </c>
       <c r="AG75">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AK75">
-        <v>1.53</v>
+        <v>2.64</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
-        <v>1.98</v>
+        <v>2.18</v>
       </c>
       <c r="O76">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P76">
-        <v>3.29</v>
+        <v>2.83</v>
       </c>
       <c r="Q76">
-        <v>2.49</v>
+        <v>2.8</v>
       </c>
       <c r="R76">
-        <v>2.38</v>
+        <v>2.21</v>
       </c>
       <c r="S76">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="T76">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="U76">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="V76">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="W76">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X76">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y76">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="Z76">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="AA76">
-        <v>1.7</v>
+        <v>1.92</v>
       </c>
       <c r="AB76">
-        <v>2.03</v>
+        <v>1.85</v>
       </c>
       <c r="AC76">
-        <v>2.81</v>
+        <v>3.35</v>
       </c>
       <c r="AD76">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="AE76">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AF76">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="AG76">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AK76">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -13023,7 +13023,7 @@
         </is>
       </c>
       <c r="N78">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="O78">
         <v>3.92</v>
@@ -13035,13 +13035,13 @@
         <v>2.1</v>
       </c>
       <c r="R78">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="S78">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="T78">
-        <v>3.15</v>
+        <v>3.04</v>
       </c>
       <c r="U78">
         <v>2.43</v>
@@ -13056,22 +13056,22 @@
         <v>1.04</v>
       </c>
       <c r="Y78">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z78">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AA78">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AB78">
         <v>2.05</v>
       </c>
       <c r="AC78">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="AD78">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE78">
         <v>1.1</v>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AK78">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O82">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P82">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q82">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R82">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S82">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T82">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U82">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V82">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W82">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y82">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z82">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AA82">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB82">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC82">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD82">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE82">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF82">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG82">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK82">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -15631,64 +15631,64 @@
         </is>
       </c>
       <c r="N94">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O94">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P94">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q94">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R94">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S94">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T94">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U94">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V94">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W94">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X94">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y94">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z94">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA94">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AB94">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AC94">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD94">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE94">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF94">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG94">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK94">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL94">
         <v>0</v>

--- a/jogos_2026-08-07.xlsx
+++ b/jogos_2026-08-07.xlsx
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,65 +1613,65 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.24</v>
+        <v>1.41</v>
       </c>
       <c r="O8">
-        <v>5.15</v>
+        <v>3.83</v>
       </c>
       <c r="P8">
-        <v>8.19</v>
+        <v>5</v>
       </c>
       <c r="Q8">
-        <v>1.75</v>
+        <v>2.02</v>
       </c>
       <c r="R8">
-        <v>2.6</v>
+        <v>2.24</v>
       </c>
       <c r="S8">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="T8">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="U8">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="V8">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W8">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X8">
         <v>1.02</v>
       </c>
       <c r="Y8">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z8">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="AA8">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="AB8">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AC8">
-        <v>2.59</v>
+        <v>2.96</v>
       </c>
       <c r="AD8">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AE8">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF8">
+        <v>1.8</v>
+      </c>
+      <c r="AG8">
         <v>1.91</v>
       </c>
-      <c r="AG8">
-        <v>1.75</v>
-      </c>
       <c r="AH8" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AK8">
-        <v>3.4</v>
+        <v>2.31</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.41</v>
+        <v>1.24</v>
       </c>
       <c r="O9">
-        <v>3.83</v>
+        <v>5.15</v>
       </c>
       <c r="P9">
-        <v>5</v>
+        <v>8.19</v>
       </c>
       <c r="Q9">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="R9">
-        <v>2.24</v>
+        <v>2.6</v>
       </c>
       <c r="S9">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="T9">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="U9">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="V9">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W9">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X9">
         <v>1.02</v>
       </c>
       <c r="Y9">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z9">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="AA9">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="AB9">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AC9">
-        <v>2.96</v>
+        <v>2.59</v>
       </c>
       <c r="AD9">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AE9">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF9">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AG9">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AK9">
-        <v>2.31</v>
+        <v>3.4</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="O24">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="P24">
-        <v>3.4</v>
+        <v>5.88</v>
       </c>
       <c r="Q24">
-        <v>2.4</v>
+        <v>2.07</v>
       </c>
       <c r="R24">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="S24">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T24">
+        <v>3</v>
+      </c>
+      <c r="U24">
+        <v>2.59</v>
+      </c>
+      <c r="V24">
+        <v>1.39</v>
+      </c>
+      <c r="W24">
+        <v>1.04</v>
+      </c>
+      <c r="X24">
+        <v>1.02</v>
+      </c>
+      <c r="Y24">
+        <v>1.25</v>
+      </c>
+      <c r="Z24">
+        <v>3.5</v>
+      </c>
+      <c r="AA24">
+        <v>1.8</v>
+      </c>
+      <c r="AB24">
+        <v>1.93</v>
+      </c>
+      <c r="AC24">
         <v>3.2</v>
       </c>
-      <c r="U24">
-        <v>2.47</v>
-      </c>
-      <c r="V24">
-        <v>1.44</v>
-      </c>
-      <c r="W24">
-        <v>1.06</v>
-      </c>
-      <c r="X24">
-        <v>1.03</v>
-      </c>
-      <c r="Y24">
-        <v>1.2</v>
-      </c>
-      <c r="Z24">
-        <v>4</v>
-      </c>
-      <c r="AA24">
-        <v>1.68</v>
-      </c>
-      <c r="AB24">
-        <v>2.02</v>
-      </c>
-      <c r="AC24">
-        <v>2.7</v>
-      </c>
       <c r="AD24">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AE24">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AF24">
-        <v>1.62</v>
+        <v>1.87</v>
       </c>
       <c r="AG24">
-        <v>2.2</v>
+        <v>1.79</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK24">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,80 +4384,80 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="O25">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="P25">
-        <v>5.88</v>
+        <v>3.4</v>
       </c>
       <c r="Q25">
-        <v>2.07</v>
+        <v>2.4</v>
       </c>
       <c r="R25">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="S25">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T25">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U25">
-        <v>2.59</v>
+        <v>2.47</v>
       </c>
       <c r="V25">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="W25">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X25">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y25">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z25">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AA25">
+        <v>1.68</v>
+      </c>
+      <c r="AB25">
+        <v>2.02</v>
+      </c>
+      <c r="AC25">
+        <v>2.7</v>
+      </c>
+      <c r="AD25">
+        <v>1.4</v>
+      </c>
+      <c r="AE25">
+        <v>1.15</v>
+      </c>
+      <c r="AF25">
+        <v>1.62</v>
+      </c>
+      <c r="AG25">
+        <v>2.2</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ25">
+        <v>1.19</v>
+      </c>
+      <c r="AK25">
         <v>1.8</v>
-      </c>
-      <c r="AB25">
-        <v>1.93</v>
-      </c>
-      <c r="AC25">
-        <v>3.2</v>
-      </c>
-      <c r="AD25">
-        <v>1.33</v>
-      </c>
-      <c r="AE25">
-        <v>1.11</v>
-      </c>
-      <c r="AF25">
-        <v>1.87</v>
-      </c>
-      <c r="AG25">
-        <v>1.79</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ25">
-        <v>1.25</v>
-      </c>
-      <c r="AK25">
-        <v>2.3</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.35</v>
+        <v>2.18</v>
       </c>
       <c r="O75">
-        <v>4.55</v>
+        <v>3.2</v>
       </c>
       <c r="P75">
-        <v>8.449999999999999</v>
+        <v>2.83</v>
       </c>
       <c r="Q75">
-        <v>1.75</v>
+        <v>2.8</v>
       </c>
       <c r="R75">
-        <v>2.5</v>
+        <v>2.21</v>
       </c>
       <c r="S75">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="T75">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="U75">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="V75">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="W75">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X75">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y75">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="Z75">
-        <v>4.33</v>
+        <v>3.45</v>
       </c>
       <c r="AA75">
-        <v>1.62</v>
+        <v>1.92</v>
       </c>
       <c r="AB75">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AC75">
-        <v>2.63</v>
+        <v>3.35</v>
       </c>
       <c r="AD75">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="AE75">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AF75">
-        <v>1.85</v>
+        <v>1.69</v>
       </c>
       <c r="AG75">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AK75">
-        <v>2.64</v>
+        <v>1.53</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.18</v>
+        <v>1.35</v>
       </c>
       <c r="O76">
-        <v>3.2</v>
+        <v>4.55</v>
       </c>
       <c r="P76">
-        <v>2.83</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="Q76">
-        <v>2.8</v>
+        <v>1.75</v>
       </c>
       <c r="R76">
-        <v>2.21</v>
+        <v>2.5</v>
       </c>
       <c r="S76">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="T76">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="U76">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="V76">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="W76">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X76">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y76">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="Z76">
-        <v>3.45</v>
+        <v>4.33</v>
       </c>
       <c r="AA76">
-        <v>1.92</v>
+        <v>1.62</v>
       </c>
       <c r="AB76">
+        <v>2.15</v>
+      </c>
+      <c r="AC76">
+        <v>2.63</v>
+      </c>
+      <c r="AD76">
+        <v>1.5</v>
+      </c>
+      <c r="AE76">
+        <v>1.17</v>
+      </c>
+      <c r="AF76">
         <v>1.85</v>
       </c>
-      <c r="AC76">
-        <v>3.35</v>
-      </c>
-      <c r="AD76">
-        <v>1.32</v>
-      </c>
-      <c r="AE76">
-        <v>1.1</v>
-      </c>
-      <c r="AF76">
-        <v>1.69</v>
-      </c>
       <c r="AG76">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AK76">
-        <v>1.53</v>
+        <v>2.64</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -13521,55 +13521,55 @@
         <v>3.6</v>
       </c>
       <c r="Q81">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="R81">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="S81">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="T81">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="U81">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="V81">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="W81">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="X81">
         <v>1.01</v>
       </c>
       <c r="Y81">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="Z81">
-        <v>6.15</v>
+        <v>5.4</v>
       </c>
       <c r="AA81">
         <v>1.33</v>
       </c>
       <c r="AB81">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="AC81">
-        <v>1.85</v>
+        <v>2.06</v>
       </c>
       <c r="AD81">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AE81">
         <v>1.35</v>
       </c>
       <c r="AF81">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AG81">
-        <v>2.9</v>
+        <v>2.59</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13585,7 +13585,7 @@
         <v>1.17</v>
       </c>
       <c r="AK81">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -14490,7 +14490,7 @@
         </is>
       </c>
       <c r="N87">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="O87">
         <v>3.9</v>
@@ -14514,7 +14514,7 @@
         <v>1.93</v>
       </c>
       <c r="V87">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="W87">
         <v>1.22</v>
@@ -14523,19 +14523,19 @@
         <v>1.01</v>
       </c>
       <c r="Y87">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Z87">
-        <v>6.35</v>
+        <v>6.4</v>
       </c>
       <c r="AA87">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AB87">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AC87">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AD87">
         <v>1.83</v>
@@ -14560,7 +14560,7 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK87">
         <v>1.83</v>

--- a/jogos_2026-08-07.xlsx
+++ b/jogos_2026-08-07.xlsx
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.67</v>
+        <v>1.41</v>
       </c>
       <c r="O6">
-        <v>3.55</v>
+        <v>3.83</v>
       </c>
       <c r="P6">
-        <v>4.35</v>
+        <v>5</v>
       </c>
       <c r="Q6">
-        <v>2.23</v>
+        <v>2.02</v>
       </c>
       <c r="R6">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="S6">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="T6">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="U6">
-        <v>2.77</v>
+        <v>2.53</v>
       </c>
       <c r="V6">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="W6">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X6">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y6">
+        <v>1.19</v>
+      </c>
+      <c r="Z6">
+        <v>3.8</v>
+      </c>
+      <c r="AA6">
+        <v>1.72</v>
+      </c>
+      <c r="AB6">
+        <v>2</v>
+      </c>
+      <c r="AC6">
+        <v>2.96</v>
+      </c>
+      <c r="AD6">
         <v>1.36</v>
       </c>
-      <c r="Z6">
-        <v>2.97</v>
-      </c>
-      <c r="AA6">
-        <v>2.03</v>
-      </c>
-      <c r="AB6">
-        <v>1.65</v>
-      </c>
-      <c r="AC6">
-        <v>3.82</v>
-      </c>
-      <c r="AD6">
-        <v>1.26</v>
-      </c>
       <c r="AE6">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AF6">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AG6">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="AK6">
-        <v>2</v>
+        <v>2.31</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.8</v>
+        <v>1.67</v>
       </c>
       <c r="O7">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="P7">
-        <v>1.87</v>
+        <v>4.35</v>
       </c>
       <c r="Q7">
-        <v>4.33</v>
+        <v>2.23</v>
       </c>
       <c r="R7">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="S7">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="T7">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="U7">
-        <v>2.88</v>
+        <v>2.77</v>
       </c>
       <c r="V7">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W7">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X7">
         <v>1.04</v>
       </c>
       <c r="Y7">
+        <v>1.36</v>
+      </c>
+      <c r="Z7">
+        <v>2.97</v>
+      </c>
+      <c r="AA7">
+        <v>2.03</v>
+      </c>
+      <c r="AB7">
+        <v>1.65</v>
+      </c>
+      <c r="AC7">
+        <v>3.82</v>
+      </c>
+      <c r="AD7">
         <v>1.26</v>
       </c>
-      <c r="Z7">
-        <v>3.2</v>
-      </c>
-      <c r="AA7">
-        <v>1.87</v>
-      </c>
-      <c r="AB7">
-        <v>1.83</v>
-      </c>
-      <c r="AC7">
-        <v>3.26</v>
-      </c>
-      <c r="AD7">
-        <v>1.3</v>
-      </c>
       <c r="AE7">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF7">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AG7">
-        <v>1.95</v>
+        <v>1.79</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AK7">
-        <v>1.19</v>
+        <v>2</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,80 +1613,80 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.41</v>
+        <v>3.8</v>
       </c>
       <c r="O8">
-        <v>3.83</v>
+        <v>3.3</v>
       </c>
       <c r="P8">
-        <v>5</v>
+        <v>1.87</v>
       </c>
       <c r="Q8">
-        <v>2.02</v>
+        <v>4.33</v>
       </c>
       <c r="R8">
-        <v>2.24</v>
+        <v>2.12</v>
       </c>
       <c r="S8">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="T8">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="U8">
-        <v>2.53</v>
+        <v>2.88</v>
       </c>
       <c r="V8">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W8">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X8">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y8">
+        <v>1.26</v>
+      </c>
+      <c r="Z8">
+        <v>3.2</v>
+      </c>
+      <c r="AA8">
+        <v>1.87</v>
+      </c>
+      <c r="AB8">
+        <v>1.83</v>
+      </c>
+      <c r="AC8">
+        <v>3.26</v>
+      </c>
+      <c r="AD8">
+        <v>1.3</v>
+      </c>
+      <c r="AE8">
+        <v>1.07</v>
+      </c>
+      <c r="AF8">
+        <v>1.75</v>
+      </c>
+      <c r="AG8">
+        <v>1.95</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8">
+        <v>1.3</v>
+      </c>
+      <c r="AK8">
         <v>1.19</v>
-      </c>
-      <c r="Z8">
-        <v>3.8</v>
-      </c>
-      <c r="AA8">
-        <v>1.72</v>
-      </c>
-      <c r="AB8">
-        <v>2</v>
-      </c>
-      <c r="AC8">
-        <v>2.96</v>
-      </c>
-      <c r="AD8">
-        <v>1.36</v>
-      </c>
-      <c r="AE8">
-        <v>1.13</v>
-      </c>
-      <c r="AF8">
-        <v>1.8</v>
-      </c>
-      <c r="AG8">
-        <v>1.91</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8">
-        <v>1.08</v>
-      </c>
-      <c r="AK8">
-        <v>2.31</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,80 +4221,80 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="O24">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="P24">
-        <v>5.88</v>
+        <v>3.4</v>
       </c>
       <c r="Q24">
-        <v>2.07</v>
+        <v>2.4</v>
       </c>
       <c r="R24">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="S24">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T24">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U24">
-        <v>2.59</v>
+        <v>2.47</v>
       </c>
       <c r="V24">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="W24">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X24">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y24">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z24">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AA24">
+        <v>1.68</v>
+      </c>
+      <c r="AB24">
+        <v>2.02</v>
+      </c>
+      <c r="AC24">
+        <v>2.7</v>
+      </c>
+      <c r="AD24">
+        <v>1.4</v>
+      </c>
+      <c r="AE24">
+        <v>1.15</v>
+      </c>
+      <c r="AF24">
+        <v>1.62</v>
+      </c>
+      <c r="AG24">
+        <v>2.2</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ24">
+        <v>1.19</v>
+      </c>
+      <c r="AK24">
         <v>1.8</v>
-      </c>
-      <c r="AB24">
-        <v>1.93</v>
-      </c>
-      <c r="AC24">
-        <v>3.2</v>
-      </c>
-      <c r="AD24">
-        <v>1.33</v>
-      </c>
-      <c r="AE24">
-        <v>1.11</v>
-      </c>
-      <c r="AF24">
-        <v>1.87</v>
-      </c>
-      <c r="AG24">
-        <v>1.79</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ24">
-        <v>1.25</v>
-      </c>
-      <c r="AK24">
-        <v>2.3</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,16 +4384,16 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="O25">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="P25">
-        <v>3.4</v>
+        <v>5.28</v>
       </c>
       <c r="Q25">
-        <v>2.4</v>
+        <v>2.12</v>
       </c>
       <c r="R25">
         <v>2.38</v>
@@ -4402,46 +4402,46 @@
         <v>1.3</v>
       </c>
       <c r="T25">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="U25">
-        <v>2.47</v>
+        <v>2.3</v>
       </c>
       <c r="V25">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="W25">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X25">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y25">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z25">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AA25">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AB25">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="AC25">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AD25">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AE25">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF25">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG25">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK25">
-        <v>1.8</v>
+        <v>2.06</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="O26">
         <v>3.8</v>
       </c>
       <c r="P26">
-        <v>5.28</v>
+        <v>5.88</v>
       </c>
       <c r="Q26">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="R26">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="S26">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T26">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="U26">
-        <v>2.3</v>
+        <v>2.59</v>
       </c>
       <c r="V26">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="W26">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="X26">
         <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="Z26">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="AA26">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AB26">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AC26">
-        <v>2.55</v>
+        <v>3.2</v>
       </c>
       <c r="AD26">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="AE26">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AF26">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="AG26">
-        <v>2.1</v>
+        <v>1.79</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK26">
-        <v>2.06</v>
+        <v>2.3</v>
       </c>
       <c r="AL26">
         <v>0</v>

--- a/jogos_2026-08-07.xlsx
+++ b/jogos_2026-08-07.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>3.66</v>
+        <v>3.75</v>
       </c>
       <c r="O2">
-        <v>3.4</v>
+        <v>3.46</v>
       </c>
       <c r="P2">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="Q2">
         <v>4</v>
@@ -650,10 +650,10 @@
         <v>2.15</v>
       </c>
       <c r="S2">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="T2">
-        <v>2.53</v>
+        <v>2.82</v>
       </c>
       <c r="U2">
         <v>2.94</v>
@@ -671,7 +671,7 @@
         <v>1.33</v>
       </c>
       <c r="Z2">
-        <v>3.24</v>
+        <v>2.94</v>
       </c>
       <c r="AA2">
         <v>2.08</v>
@@ -680,16 +680,16 @@
         <v>1.76</v>
       </c>
       <c r="AC2">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="AD2">
         <v>1.25</v>
       </c>
       <c r="AE2">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF2">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AG2">
         <v>1.91</v>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AK2">
         <v>1.25</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.46</v>
+        <v>2.26</v>
       </c>
       <c r="O3">
         <v>3.25</v>
       </c>
       <c r="P3">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="Q3">
         <v>3.02</v>
@@ -813,19 +813,19 @@
         <v>2.01</v>
       </c>
       <c r="S3">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T3">
-        <v>2.92</v>
+        <v>2.89</v>
       </c>
       <c r="U3">
-        <v>2.94</v>
+        <v>3.06</v>
       </c>
       <c r="V3">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W3">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X3">
         <v>1</v>
@@ -837,19 +837,19 @@
         <v>3.4</v>
       </c>
       <c r="AA3">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AB3">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AC3">
         <v>3.6</v>
       </c>
       <c r="AD3">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE3">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AF3">
         <v>1.74</v>
@@ -871,7 +871,7 @@
         <v>1.34</v>
       </c>
       <c r="AK3">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.88</v>
+        <v>3.22</v>
       </c>
       <c r="O4">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P4">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="Q4">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="R4">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="S4">
         <v>1.33</v>
       </c>
       <c r="T4">
-        <v>3.1</v>
+        <v>2.87</v>
       </c>
       <c r="U4">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="V4">
         <v>1.44</v>
       </c>
       <c r="W4">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X4">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y4">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z4">
-        <v>4.2</v>
+        <v>4.01</v>
       </c>
       <c r="AA4">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AB4">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AC4">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="AD4">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AE4">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF4">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AG4">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.24</v>
+        <v>1.9</v>
       </c>
       <c r="AK4">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,28 +1124,28 @@
         </is>
       </c>
       <c r="N5">
-        <v>3.55</v>
+        <v>1.46</v>
       </c>
       <c r="O5">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="P5">
-        <v>1.78</v>
+        <v>4.4</v>
       </c>
       <c r="Q5">
-        <v>4</v>
+        <v>2.18</v>
       </c>
       <c r="R5">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="S5">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T5">
-        <v>2.87</v>
+        <v>3.1</v>
       </c>
       <c r="U5">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="V5">
         <v>1.44</v>
@@ -1154,34 +1154,34 @@
         <v>1.07</v>
       </c>
       <c r="X5">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="Z5">
-        <v>3.98</v>
+        <v>3.81</v>
       </c>
       <c r="AA5">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="AB5">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AC5">
-        <v>2.7</v>
+        <v>3.07</v>
       </c>
       <c r="AD5">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE5">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF5">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG5">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.9</v>
+        <v>1.25</v>
       </c>
       <c r="AK5">
-        <v>1.2</v>
+        <v>2.08</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.41</v>
+        <v>3.7</v>
       </c>
       <c r="O6">
-        <v>3.83</v>
+        <v>3.3</v>
       </c>
       <c r="P6">
-        <v>5</v>
+        <v>1.83</v>
       </c>
       <c r="Q6">
-        <v>2.02</v>
+        <v>4.33</v>
       </c>
       <c r="R6">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="S6">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="T6">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="U6">
-        <v>2.53</v>
+        <v>2.88</v>
       </c>
       <c r="V6">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W6">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X6">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y6">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="Z6">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="AA6">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="AB6">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AC6">
-        <v>2.96</v>
+        <v>3.29</v>
       </c>
       <c r="AD6">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE6">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AF6">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG6">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.08</v>
+        <v>1.3</v>
       </c>
       <c r="AK6">
-        <v>2.31</v>
+        <v>1.2</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.67</v>
+        <v>2.91</v>
       </c>
       <c r="O7">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="P7">
-        <v>4.35</v>
+        <v>2.2</v>
       </c>
       <c r="Q7">
-        <v>2.23</v>
+        <v>3.4</v>
       </c>
       <c r="R7">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S7">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="T7">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="U7">
-        <v>2.77</v>
+        <v>2.44</v>
       </c>
       <c r="V7">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="W7">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X7">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y7">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="Z7">
-        <v>2.97</v>
+        <v>3.45</v>
       </c>
       <c r="AA7">
-        <v>2.03</v>
+        <v>1.8</v>
       </c>
       <c r="AB7">
-        <v>1.65</v>
+        <v>1.93</v>
       </c>
       <c r="AC7">
-        <v>3.82</v>
+        <v>2.87</v>
       </c>
       <c r="AD7">
-        <v>1.26</v>
+        <v>1.42</v>
       </c>
       <c r="AE7">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AF7">
-        <v>1.9</v>
+        <v>1.57</v>
       </c>
       <c r="AG7">
-        <v>1.79</v>
+        <v>2.25</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AK7">
-        <v>2</v>
+        <v>1.32</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.8</v>
+        <v>1.26</v>
       </c>
       <c r="O8">
-        <v>3.3</v>
+        <v>5.15</v>
       </c>
       <c r="P8">
-        <v>1.87</v>
+        <v>8.19</v>
       </c>
       <c r="Q8">
-        <v>4.33</v>
+        <v>1.75</v>
       </c>
       <c r="R8">
-        <v>2.12</v>
+        <v>2.6</v>
       </c>
       <c r="S8">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="T8">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="U8">
-        <v>2.88</v>
+        <v>2.55</v>
       </c>
       <c r="V8">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="W8">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X8">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y8">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="Z8">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="AA8">
-        <v>1.87</v>
+        <v>1.57</v>
       </c>
       <c r="AB8">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="AC8">
-        <v>3.26</v>
+        <v>2.5</v>
       </c>
       <c r="AD8">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="AE8">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AF8">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AG8">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.3</v>
+        <v>1.09</v>
       </c>
       <c r="AK8">
-        <v>1.19</v>
+        <v>3.4</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.24</v>
+        <v>1.73</v>
       </c>
       <c r="O9">
-        <v>5.15</v>
+        <v>3.35</v>
       </c>
       <c r="P9">
-        <v>8.19</v>
+        <v>4.45</v>
       </c>
       <c r="Q9">
-        <v>1.75</v>
+        <v>2.44</v>
       </c>
       <c r="R9">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="S9">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="T9">
-        <v>3.35</v>
+        <v>2.75</v>
       </c>
       <c r="U9">
-        <v>2.54</v>
+        <v>3.17</v>
       </c>
       <c r="V9">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="W9">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="X9">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y9">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="Z9">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="AA9">
-        <v>1.64</v>
+        <v>2.04</v>
       </c>
       <c r="AB9">
-        <v>2.2</v>
+        <v>1.65</v>
       </c>
       <c r="AC9">
-        <v>2.59</v>
+        <v>3.86</v>
       </c>
       <c r="AD9">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="AE9">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AF9">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AG9">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AK9">
-        <v>3.4</v>
+        <v>1.9</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,31 +1939,31 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="O10">
-        <v>4.6</v>
+        <v>5.45</v>
       </c>
       <c r="P10">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="Q10">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="R10">
-        <v>2.75</v>
+        <v>3.03</v>
       </c>
       <c r="S10">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T10">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="U10">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="V10">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="W10">
         <v>1.18</v>
@@ -1975,25 +1975,25 @@
         <v>1.11</v>
       </c>
       <c r="Z10">
-        <v>6.65</v>
+        <v>6.84</v>
       </c>
       <c r="AA10">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AB10">
         <v>2.95</v>
       </c>
       <c r="AC10">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="AD10">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AE10">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AF10">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AG10">
         <v>2.3</v>
@@ -2111,55 +2111,55 @@
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>5.25</v>
+        <v>4.75</v>
       </c>
       <c r="R11">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="S11">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T11">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="U11">
-        <v>2.75</v>
+        <v>3.04</v>
       </c>
       <c r="V11">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="W11">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X11">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y11">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="Z11">
-        <v>3.25</v>
+        <v>2.87</v>
       </c>
       <c r="AA11">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB11">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AC11">
-        <v>3.42</v>
+        <v>3.72</v>
       </c>
       <c r="AD11">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AE11">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AF11">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AG11">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AK11">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2268,31 +2268,31 @@
         <v>2.25</v>
       </c>
       <c r="O12">
-        <v>3.41</v>
+        <v>3.25</v>
       </c>
       <c r="P12">
-        <v>2.97</v>
+        <v>2.87</v>
       </c>
       <c r="Q12">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="R12">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="S12">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="T12">
-        <v>2.9</v>
+        <v>2.79</v>
       </c>
       <c r="U12">
         <v>2.67</v>
       </c>
       <c r="V12">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W12">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X12">
         <v>1.01</v>
@@ -2304,16 +2304,16 @@
         <v>3.8</v>
       </c>
       <c r="AA12">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AB12">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AC12">
         <v>2.96</v>
       </c>
       <c r="AD12">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AE12">
         <v>1.08</v>
@@ -2338,7 +2338,7 @@
         <v>1.24</v>
       </c>
       <c r="AK12">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,19 +2428,19 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="O13">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P13">
-        <v>4.7</v>
+        <v>4.35</v>
       </c>
       <c r="Q13">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="R13">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="S13">
         <v>1.38</v>
@@ -2449,13 +2449,13 @@
         <v>2.67</v>
       </c>
       <c r="U13">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="V13">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="W13">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X13">
         <v>1.02</v>
@@ -2467,25 +2467,25 @@
         <v>3.08</v>
       </c>
       <c r="AA13">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="AB13">
         <v>1.76</v>
       </c>
       <c r="AC13">
-        <v>3.34</v>
+        <v>3.38</v>
       </c>
       <c r="AD13">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE13">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF13">
         <v>1.9</v>
       </c>
       <c r="AG13">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AK13">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2600,55 +2600,55 @@
         <v>1.34</v>
       </c>
       <c r="Q14">
-        <v>6.48</v>
+        <v>5</v>
       </c>
       <c r="R14">
-        <v>2.58</v>
+        <v>2.49</v>
       </c>
       <c r="S14">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T14">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="U14">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="V14">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="W14">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X14">
         <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z14">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="AA14">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AB14">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="AC14">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="AD14">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AE14">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AF14">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AG14">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>1.13</v>
       </c>
       <c r="AK14">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,25 +2754,25 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="O15">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="P15">
-        <v>4.88</v>
+        <v>4.5</v>
       </c>
       <c r="Q15">
         <v>2.1</v>
       </c>
       <c r="R15">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="S15">
         <v>1.31</v>
       </c>
       <c r="T15">
-        <v>3.12</v>
+        <v>2.97</v>
       </c>
       <c r="U15">
         <v>2.47</v>
@@ -2784,34 +2784,34 @@
         <v>1.07</v>
       </c>
       <c r="X15">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y15">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z15">
         <v>4.1</v>
       </c>
       <c r="AA15">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AB15">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AC15">
-        <v>2.76</v>
+        <v>2.88</v>
       </c>
       <c r="AD15">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE15">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF15">
         <v>1.67</v>
       </c>
       <c r="AG15">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="AK15">
-        <v>2.01</v>
+        <v>2.2</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,19 +2917,19 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.5</v>
+        <v>2.61</v>
       </c>
       <c r="O16">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P16">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Q16">
         <v>3.14</v>
       </c>
       <c r="R16">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S16">
         <v>1.3</v>
@@ -2938,13 +2938,13 @@
         <v>3.3</v>
       </c>
       <c r="U16">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="V16">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W16">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X16">
         <v>1.04</v>
@@ -2956,19 +2956,19 @@
         <v>4</v>
       </c>
       <c r="AA16">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB16">
         <v>2.15</v>
       </c>
       <c r="AC16">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="AD16">
         <v>1.4</v>
       </c>
       <c r="AE16">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AF16">
         <v>1.57</v>
@@ -3080,80 +3080,80 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="O17">
         <v>3.25</v>
       </c>
       <c r="P17">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="Q17">
-        <v>2.49</v>
+        <v>2.63</v>
       </c>
       <c r="R17">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="S17">
         <v>1.42</v>
       </c>
       <c r="T17">
-        <v>2.72</v>
+        <v>2.53</v>
       </c>
       <c r="U17">
         <v>2.88</v>
       </c>
       <c r="V17">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W17">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X17">
         <v>1.03</v>
       </c>
       <c r="Y17">
+        <v>1.3</v>
+      </c>
+      <c r="Z17">
+        <v>2.97</v>
+      </c>
+      <c r="AA17">
+        <v>2</v>
+      </c>
+      <c r="AB17">
+        <v>1.71</v>
+      </c>
+      <c r="AC17">
+        <v>3.34</v>
+      </c>
+      <c r="AD17">
+        <v>1.24</v>
+      </c>
+      <c r="AE17">
+        <v>1.05</v>
+      </c>
+      <c r="AF17">
+        <v>1.83</v>
+      </c>
+      <c r="AG17">
+        <v>1.87</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17">
         <v>1.33</v>
       </c>
-      <c r="Z17">
-        <v>3.14</v>
-      </c>
-      <c r="AA17">
-        <v>2.05</v>
-      </c>
-      <c r="AB17">
-        <v>1.75</v>
-      </c>
-      <c r="AC17">
-        <v>3.6</v>
-      </c>
-      <c r="AD17">
-        <v>1.25</v>
-      </c>
-      <c r="AE17">
-        <v>1.06</v>
-      </c>
-      <c r="AF17">
-        <v>1.8</v>
-      </c>
-      <c r="AG17">
-        <v>1.9</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17">
-        <v>1.24</v>
-      </c>
       <c r="AK17">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,16 +3243,16 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="O18">
         <v>3.75</v>
       </c>
       <c r="P18">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="Q18">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="R18">
         <v>2.25</v>
@@ -3264,7 +3264,7 @@
         <v>3.08</v>
       </c>
       <c r="U18">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="V18">
         <v>1.5</v>
@@ -3276,10 +3276,10 @@
         <v>1.04</v>
       </c>
       <c r="Y18">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z18">
-        <v>4.33</v>
+        <v>3.88</v>
       </c>
       <c r="AA18">
         <v>1.67</v>
@@ -3294,10 +3294,10 @@
         <v>1.4</v>
       </c>
       <c r="AE18">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF18">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG18">
         <v>2.05</v>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK18">
         <v>2.05</v>
@@ -3406,49 +3406,49 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="O19">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P19">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q19">
-        <v>3.83</v>
+        <v>3.82</v>
       </c>
       <c r="R19">
         <v>2</v>
       </c>
       <c r="S19">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="T19">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="U19">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="V19">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W19">
         <v>1.04</v>
       </c>
       <c r="X19">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z19">
-        <v>2.81</v>
+        <v>3.1</v>
       </c>
       <c r="AA19">
         <v>2.1</v>
       </c>
       <c r="AB19">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AC19">
         <v>3.72</v>
@@ -3457,13 +3457,13 @@
         <v>1.2</v>
       </c>
       <c r="AE19">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF19">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AG19">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>1.25</v>
       </c>
       <c r="AK19">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3575,46 +3575,46 @@
         <v>3.45</v>
       </c>
       <c r="P20">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q20">
         <v>3.24</v>
       </c>
       <c r="R20">
-        <v>2.38</v>
+        <v>2.16</v>
       </c>
       <c r="S20">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T20">
         <v>3.25</v>
       </c>
       <c r="U20">
-        <v>2.41</v>
+        <v>2.04</v>
       </c>
       <c r="V20">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="W20">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X20">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y20">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="Z20">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="AA20">
         <v>1.66</v>
       </c>
       <c r="AB20">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AC20">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AD20">
         <v>1.46</v>
@@ -3623,10 +3623,10 @@
         <v>1.14</v>
       </c>
       <c r="AF20">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AG20">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AK20">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
+        <v>1.83</v>
+      </c>
+      <c r="O22">
+        <v>3.46</v>
+      </c>
+      <c r="P22">
+        <v>3.75</v>
+      </c>
+      <c r="Q22">
+        <v>2.41</v>
+      </c>
+      <c r="R22">
+        <v>2.34</v>
+      </c>
+      <c r="S22">
+        <v>1.3</v>
+      </c>
+      <c r="T22">
+        <v>3.1</v>
+      </c>
+      <c r="U22">
+        <v>2.47</v>
+      </c>
+      <c r="V22">
+        <v>1.44</v>
+      </c>
+      <c r="W22">
+        <v>1.06</v>
+      </c>
+      <c r="X22">
+        <v>1.04</v>
+      </c>
+      <c r="Y22">
+        <v>1.2</v>
+      </c>
+      <c r="Z22">
         <v>4</v>
       </c>
-      <c r="O22">
-        <v>3.55</v>
-      </c>
-      <c r="P22">
+      <c r="AA22">
         <v>1.7</v>
       </c>
-      <c r="Q22">
-        <v>4.12</v>
-      </c>
-      <c r="R22">
-        <v>2.12</v>
-      </c>
-      <c r="S22">
-        <v>1.35</v>
-      </c>
-      <c r="T22">
-        <v>3</v>
-      </c>
-      <c r="U22">
-        <v>2.6</v>
-      </c>
-      <c r="V22">
+      <c r="AB22">
+        <v>2.05</v>
+      </c>
+      <c r="AC22">
+        <v>2.7</v>
+      </c>
+      <c r="AD22">
         <v>1.4</v>
       </c>
-      <c r="W22">
-        <v>1.08</v>
-      </c>
-      <c r="X22">
-        <v>1.02</v>
-      </c>
-      <c r="Y22">
-        <v>1.21</v>
-      </c>
-      <c r="Z22">
-        <v>3.58</v>
-      </c>
-      <c r="AA22">
-        <v>1.77</v>
-      </c>
-      <c r="AB22">
-        <v>1.92</v>
-      </c>
-      <c r="AC22">
-        <v>3.1</v>
-      </c>
-      <c r="AD22">
-        <v>1.32</v>
-      </c>
       <c r="AE22">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF22">
-        <v>1.73</v>
+        <v>1.59</v>
       </c>
       <c r="AG22">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>2.05</v>
+        <v>1.19</v>
       </c>
       <c r="AK22">
-        <v>1.14</v>
+        <v>1.83</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,80 +4058,80 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="O23">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="P23">
-        <v>4.75</v>
+        <v>4.79</v>
       </c>
       <c r="Q23">
+        <v>2.06</v>
+      </c>
+      <c r="R23">
+        <v>2.21</v>
+      </c>
+      <c r="S23">
+        <v>1.3</v>
+      </c>
+      <c r="T23">
+        <v>3.04</v>
+      </c>
+      <c r="U23">
+        <v>2.4</v>
+      </c>
+      <c r="V23">
+        <v>1.45</v>
+      </c>
+      <c r="W23">
+        <v>1.07</v>
+      </c>
+      <c r="X23">
+        <v>1.03</v>
+      </c>
+      <c r="Y23">
+        <v>1.18</v>
+      </c>
+      <c r="Z23">
+        <v>4.33</v>
+      </c>
+      <c r="AA23">
+        <v>1.62</v>
+      </c>
+      <c r="AB23">
         <v>2.15</v>
       </c>
-      <c r="R23">
-        <v>2.25</v>
-      </c>
-      <c r="S23">
-        <v>1.33</v>
-      </c>
-      <c r="T23">
-        <v>3</v>
-      </c>
-      <c r="U23">
-        <v>2.75</v>
-      </c>
-      <c r="V23">
-        <v>1.4</v>
-      </c>
-      <c r="W23">
-        <v>1.04</v>
-      </c>
-      <c r="X23">
-        <v>1.01</v>
-      </c>
-      <c r="Y23">
+      <c r="AC23">
+        <v>2.68</v>
+      </c>
+      <c r="AD23">
+        <v>1.44</v>
+      </c>
+      <c r="AE23">
+        <v>1.17</v>
+      </c>
+      <c r="AF23">
+        <v>1.67</v>
+      </c>
+      <c r="AG23">
+        <v>2.1</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23">
         <v>1.25</v>
       </c>
-      <c r="Z23">
-        <v>3.5</v>
-      </c>
-      <c r="AA23">
-        <v>1.88</v>
-      </c>
-      <c r="AB23">
-        <v>1.88</v>
-      </c>
-      <c r="AC23">
-        <v>3</v>
-      </c>
-      <c r="AD23">
-        <v>1.3</v>
-      </c>
-      <c r="AE23">
-        <v>1.07</v>
-      </c>
-      <c r="AF23">
-        <v>1.85</v>
-      </c>
-      <c r="AG23">
-        <v>1.85</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ23">
-        <v>1.2</v>
-      </c>
       <c r="AK23">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="O24">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="P24">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="Q24">
-        <v>2.4</v>
+        <v>1.98</v>
       </c>
       <c r="R24">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S24">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T24">
         <v>3.2</v>
       </c>
       <c r="U24">
-        <v>2.47</v>
+        <v>2.75</v>
       </c>
       <c r="V24">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W24">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X24">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y24">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z24">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="AA24">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="AB24">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="AC24">
-        <v>2.7</v>
+        <v>3.13</v>
       </c>
       <c r="AD24">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AE24">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AF24">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AG24">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.19</v>
+        <v>1.07</v>
       </c>
       <c r="AK24">
-        <v>1.8</v>
+        <v>2.17</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.6</v>
+        <v>4.2</v>
       </c>
       <c r="O25">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P25">
-        <v>5.28</v>
+        <v>1.7</v>
       </c>
       <c r="Q25">
+        <v>4.3</v>
+      </c>
+      <c r="R25">
         <v>2.12</v>
       </c>
-      <c r="R25">
-        <v>2.38</v>
-      </c>
       <c r="S25">
+        <v>1.33</v>
+      </c>
+      <c r="T25">
+        <v>3</v>
+      </c>
+      <c r="U25">
+        <v>2.75</v>
+      </c>
+      <c r="V25">
+        <v>1.4</v>
+      </c>
+      <c r="W25">
+        <v>1.04</v>
+      </c>
+      <c r="X25">
+        <v>1.05</v>
+      </c>
+      <c r="Y25">
+        <v>1.25</v>
+      </c>
+      <c r="Z25">
+        <v>3.4</v>
+      </c>
+      <c r="AA25">
+        <v>1.85</v>
+      </c>
+      <c r="AB25">
+        <v>1.85</v>
+      </c>
+      <c r="AC25">
+        <v>3.2</v>
+      </c>
+      <c r="AD25">
         <v>1.3</v>
       </c>
-      <c r="T25">
-        <v>3.04</v>
-      </c>
-      <c r="U25">
-        <v>2.3</v>
-      </c>
-      <c r="V25">
-        <v>1.53</v>
-      </c>
-      <c r="W25">
-        <v>1.12</v>
-      </c>
-      <c r="X25">
-        <v>1.02</v>
-      </c>
-      <c r="Y25">
-        <v>1.18</v>
-      </c>
-      <c r="Z25">
-        <v>4.33</v>
-      </c>
-      <c r="AA25">
-        <v>1.62</v>
-      </c>
-      <c r="AB25">
-        <v>2.08</v>
-      </c>
-      <c r="AC25">
-        <v>2.55</v>
-      </c>
-      <c r="AD25">
-        <v>1.47</v>
-      </c>
       <c r="AE25">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AF25">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AG25">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK25">
-        <v>2.06</v>
+        <v>1.15</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="O26">
         <v>3.8</v>
       </c>
       <c r="P26">
-        <v>5.88</v>
+        <v>4.9</v>
       </c>
       <c r="Q26">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="R26">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="S26">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T26">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="U26">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="V26">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="W26">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X26">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y26">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z26">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AA26">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AB26">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AC26">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="AD26">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE26">
         <v>1.11</v>
       </c>
       <c r="AF26">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AG26">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK26">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="O27">
         <v>4.33</v>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="O28">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="P28">
-        <v>3.33</v>
+        <v>3.2</v>
       </c>
       <c r="Q28">
         <v>2.38</v>
@@ -4894,7 +4894,7 @@
         <v>3.75</v>
       </c>
       <c r="U28">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="V28">
         <v>1.61</v>
@@ -4912,19 +4912,19 @@
         <v>4.95</v>
       </c>
       <c r="AA28">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AB28">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AC28">
-        <v>2.31</v>
+        <v>2.24</v>
       </c>
       <c r="AD28">
         <v>1.53</v>
       </c>
       <c r="AE28">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF28">
         <v>1.46</v>
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="O29">
         <v>2.9</v>
       </c>
       <c r="P29">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="Q29">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="R29">
         <v>1.89</v>
       </c>
       <c r="S29">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="T29">
-        <v>2.36</v>
+        <v>2.67</v>
       </c>
       <c r="U29">
-        <v>3.28</v>
+        <v>3.16</v>
       </c>
       <c r="V29">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W29">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X29">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y29">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="Z29">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="AA29">
-        <v>2.31</v>
+        <v>2.19</v>
       </c>
       <c r="AB29">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AC29">
-        <v>4.15</v>
+        <v>3.95</v>
       </c>
       <c r="AD29">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AE29">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF29">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AG29">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         <v>1.33</v>
       </c>
       <c r="AK29">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,16 +5199,16 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="O30">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P30">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q30">
-        <v>3.12</v>
+        <v>2.98</v>
       </c>
       <c r="R30">
         <v>2.15</v>
@@ -5217,13 +5217,13 @@
         <v>1.33</v>
       </c>
       <c r="T30">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="U30">
         <v>2.62</v>
       </c>
       <c r="V30">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W30">
         <v>1.07</v>
@@ -5232,31 +5232,31 @@
         <v>1.05</v>
       </c>
       <c r="Y30">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z30">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AA30">
         <v>1.77</v>
       </c>
       <c r="AB30">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AC30">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="AD30">
         <v>1.33</v>
       </c>
       <c r="AE30">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF30">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AG30">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK30">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5371,34 +5371,34 @@
         <v>5.5</v>
       </c>
       <c r="Q31">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="R31">
         <v>2.26</v>
       </c>
       <c r="S31">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T31">
         <v>3</v>
       </c>
       <c r="U31">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="V31">
         <v>1.42</v>
       </c>
       <c r="W31">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X31">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y31">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z31">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="AA31">
         <v>1.83</v>
@@ -5413,10 +5413,10 @@
         <v>1.33</v>
       </c>
       <c r="AE31">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF31">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AG31">
         <v>1.75</v>
@@ -5528,61 +5528,61 @@
         <v>3.05</v>
       </c>
       <c r="O32">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="P32">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="Q32">
         <v>3.25</v>
       </c>
       <c r="R32">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S32">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T32">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="U32">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="V32">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="W32">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X32">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z32">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AA32">
         <v>1.61</v>
       </c>
       <c r="AB32">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="AC32">
-        <v>2.7</v>
+        <v>2.43</v>
       </c>
       <c r="AD32">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AE32">
         <v>1.14</v>
       </c>
       <c r="AF32">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG32">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="O33">
-        <v>3.5</v>
+        <v>3.64</v>
       </c>
       <c r="P33">
-        <v>3.2</v>
+        <v>3.56</v>
       </c>
       <c r="Q33">
         <v>2.5</v>
@@ -5709,7 +5709,7 @@
         <v>3.2</v>
       </c>
       <c r="U33">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="V33">
         <v>1.5</v>
@@ -5727,22 +5727,22 @@
         <v>4.1</v>
       </c>
       <c r="AA33">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AB33">
         <v>2.05</v>
       </c>
       <c r="AC33">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AD33">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AE33">
         <v>1.15</v>
       </c>
       <c r="AF33">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AG33">
         <v>2.2</v>
@@ -5851,43 +5851,43 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.63</v>
+        <v>3.45</v>
       </c>
       <c r="O34">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P34">
+        <v>1.9</v>
+      </c>
+      <c r="Q34">
+        <v>4.1</v>
+      </c>
+      <c r="R34">
         <v>2.3</v>
-      </c>
-      <c r="Q34">
-        <v>4.22</v>
-      </c>
-      <c r="R34">
-        <v>2.31</v>
       </c>
       <c r="S34">
         <v>1.25</v>
       </c>
       <c r="T34">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="U34">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="V34">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W34">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X34">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y34">
         <v>1.13</v>
       </c>
       <c r="Z34">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="AA34">
         <v>1.55</v>
@@ -5896,19 +5896,19 @@
         <v>2.27</v>
       </c>
       <c r="AC34">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AD34">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AE34">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF34">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AG34">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK34">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,16 +6014,16 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="O35">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="P35">
-        <v>3.64</v>
+        <v>4.07</v>
       </c>
       <c r="Q35">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="R35">
         <v>2.38</v>
@@ -6032,46 +6032,46 @@
         <v>1.26</v>
       </c>
       <c r="T35">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="U35">
         <v>2.25</v>
       </c>
       <c r="V35">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W35">
         <v>1.12</v>
       </c>
       <c r="X35">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y35">
         <v>1.16</v>
       </c>
       <c r="Z35">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AA35">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="AB35">
         <v>2.21</v>
       </c>
       <c r="AC35">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="AD35">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AE35">
         <v>1.16</v>
       </c>
       <c r="AF35">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AG35">
-        <v>2.23</v>
+        <v>2.16</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK35">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>3.16</v>
+        <v>3.45</v>
       </c>
       <c r="O36">
+        <v>3.85</v>
+      </c>
+      <c r="P36">
+        <v>1.88</v>
+      </c>
+      <c r="Q36">
         <v>3.75</v>
-      </c>
-      <c r="P36">
-        <v>2.12</v>
-      </c>
-      <c r="Q36">
-        <v>3.4</v>
       </c>
       <c r="R36">
         <v>2.22</v>
       </c>
       <c r="S36">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="T36">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="U36">
         <v>2.34</v>
       </c>
       <c r="V36">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="W36">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X36">
         <v>1.03</v>
       </c>
       <c r="Y36">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z36">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AA36">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AB36">
-        <v>2.18</v>
+        <v>2.31</v>
       </c>
       <c r="AC36">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="AD36">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AE36">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AF36">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AG36">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AK36">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,7 +6340,7 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="O37">
         <v>3.2</v>
@@ -6349,7 +6349,7 @@
         <v>3.12</v>
       </c>
       <c r="Q37">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="R37">
         <v>2.05</v>
@@ -6358,7 +6358,7 @@
         <v>1.4</v>
       </c>
       <c r="T37">
-        <v>2.62</v>
+        <v>2.76</v>
       </c>
       <c r="U37">
         <v>3.2</v>
@@ -6367,7 +6367,7 @@
         <v>1.34</v>
       </c>
       <c r="W37">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X37">
         <v>1.07</v>
@@ -6376,28 +6376,28 @@
         <v>1.32</v>
       </c>
       <c r="Z37">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="AA37">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB37">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC37">
-        <v>3.98</v>
+        <v>4.02</v>
       </c>
       <c r="AD37">
         <v>1.22</v>
       </c>
       <c r="AE37">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF37">
         <v>1.85</v>
       </c>
       <c r="AG37">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6503,55 +6503,55 @@
         </is>
       </c>
       <c r="N38">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="O38">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P38">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="Q38">
-        <v>3.6</v>
+        <v>3.56</v>
       </c>
       <c r="R38">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="S38">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T38">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="U38">
-        <v>2.63</v>
+        <v>2.41</v>
       </c>
       <c r="V38">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W38">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X38">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y38">
         <v>1.22</v>
       </c>
       <c r="Z38">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AA38">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AB38">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AC38">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="AD38">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AE38">
         <v>1.14</v>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="AK38">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="O39">
         <v>3.5</v>
       </c>
       <c r="P39">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="Q39">
         <v>2.3</v>
@@ -6681,19 +6681,19 @@
         <v>2.4</v>
       </c>
       <c r="S39">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T39">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="U39">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="V39">
         <v>1.62</v>
       </c>
       <c r="W39">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X39">
         <v>1.03</v>
@@ -6702,10 +6702,10 @@
         <v>1.12</v>
       </c>
       <c r="Z39">
-        <v>4.65</v>
+        <v>4.8</v>
       </c>
       <c r="AA39">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="AB39">
         <v>2.3</v>
@@ -6717,10 +6717,10 @@
         <v>1.53</v>
       </c>
       <c r="AE39">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AF39">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AG39">
         <v>2.45</v>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AK39">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6832,7 +6832,7 @@
         <v>3.2</v>
       </c>
       <c r="O40">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P40">
         <v>1.91</v>
@@ -6847,19 +6847,19 @@
         <v>1.22</v>
       </c>
       <c r="T40">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U40">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="V40">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="W40">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X40">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y40">
         <v>1.09</v>
@@ -6871,22 +6871,22 @@
         <v>1.42</v>
       </c>
       <c r="AB40">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="AC40">
         <v>2.15</v>
       </c>
       <c r="AD40">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AE40">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AF40">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG40">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,7 +6899,7 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AK40">
         <v>1.3</v>
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="O41">
-        <v>4.75</v>
+        <v>4.4</v>
       </c>
       <c r="P41">
-        <v>5.7</v>
+        <v>5.25</v>
       </c>
       <c r="Q41">
         <v>1.83</v>
@@ -7007,10 +7007,10 @@
         <v>2.7</v>
       </c>
       <c r="S41">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="T41">
-        <v>3.82</v>
+        <v>3.84</v>
       </c>
       <c r="U41">
         <v>2.01</v>
@@ -7031,19 +7031,19 @@
         <v>5.65</v>
       </c>
       <c r="AA41">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AB41">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AC41">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AD41">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AE41">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AF41">
         <v>1.5</v>
@@ -7062,7 +7062,7 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AK41">
         <v>2.53</v>
@@ -7155,25 +7155,25 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="O42">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="P42">
-        <v>3.41</v>
+        <v>3.3</v>
       </c>
       <c r="Q42">
-        <v>2.86</v>
+        <v>3.5</v>
       </c>
       <c r="R42">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="S42">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="T42">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="U42">
         <v>3.2</v>
@@ -7194,25 +7194,25 @@
         <v>2.6</v>
       </c>
       <c r="AA42">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="AB42">
         <v>1.53</v>
       </c>
       <c r="AC42">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="AD42">
         <v>1.17</v>
       </c>
       <c r="AE42">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AF42">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AG42">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>1.3</v>
       </c>
       <c r="AK42">
-        <v>1.61</v>
+        <v>1.37</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,19 +7318,19 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="O43">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="P43">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="Q43">
-        <v>3.25</v>
+        <v>3.37</v>
       </c>
       <c r="R43">
-        <v>1.96</v>
+        <v>2.16</v>
       </c>
       <c r="S43">
         <v>1.4</v>
@@ -7348,7 +7348,7 @@
         <v>1.05</v>
       </c>
       <c r="X43">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y43">
         <v>1.33</v>
@@ -7363,19 +7363,19 @@
         <v>1.7</v>
       </c>
       <c r="AC43">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="AD43">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE43">
         <v>1.07</v>
       </c>
       <c r="AF43">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AG43">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AK43">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7484,25 +7484,25 @@
         <v>2.33</v>
       </c>
       <c r="O44">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P44">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q44">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="R44">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="S44">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T44">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="U44">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="V44">
         <v>1.57</v>
@@ -7511,22 +7511,22 @@
         <v>1.11</v>
       </c>
       <c r="X44">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y44">
         <v>1.15</v>
       </c>
       <c r="Z44">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="AA44">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AB44">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="AC44">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="AD44">
         <v>1.47</v>
@@ -7535,10 +7535,10 @@
         <v>1.16</v>
       </c>
       <c r="AF44">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AG44">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7644,31 +7644,31 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="O45">
         <v>3.25</v>
       </c>
       <c r="P45">
-        <v>5.65</v>
+        <v>5.25</v>
       </c>
       <c r="Q45">
         <v>2.2</v>
       </c>
       <c r="R45">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="S45">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="T45">
         <v>2.3</v>
       </c>
       <c r="U45">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="V45">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="W45">
         <v>1.02</v>
@@ -7698,10 +7698,10 @@
         <v>1.05</v>
       </c>
       <c r="AF45">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="AG45">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AK45">
         <v>2.25</v>
@@ -7807,25 +7807,25 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="O46">
-        <v>4.85</v>
+        <v>4.4</v>
       </c>
       <c r="P46">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="Q46">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="R46">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="S46">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="T46">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="U46">
         <v>2.08</v>
@@ -7834,7 +7834,7 @@
         <v>1.77</v>
       </c>
       <c r="W46">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X46">
         <v>1.02</v>
@@ -7843,10 +7843,10 @@
         <v>1.08</v>
       </c>
       <c r="Z46">
-        <v>5.3</v>
+        <v>5.75</v>
       </c>
       <c r="AA46">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AB46">
         <v>2.62</v>
@@ -7880,7 +7880,7 @@
         <v>1.14</v>
       </c>
       <c r="AK46">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7970,10 +7970,10 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="O47">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P47">
         <v>2.2</v>
@@ -7988,7 +7988,7 @@
         <v>1.28</v>
       </c>
       <c r="T47">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="U47">
         <v>2.32</v>
@@ -7997,13 +7997,13 @@
         <v>1.53</v>
       </c>
       <c r="W47">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X47">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y47">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z47">
         <v>4.25</v>
@@ -8012,7 +8012,7 @@
         <v>1.62</v>
       </c>
       <c r="AB47">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AC47">
         <v>2.5</v>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="AK47">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8136,16 +8136,16 @@
         <v>2.2</v>
       </c>
       <c r="O48">
-        <v>3.5</v>
+        <v>3.71</v>
       </c>
       <c r="P48">
         <v>2.65</v>
       </c>
       <c r="Q48">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="R48">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S48">
         <v>1.2</v>
@@ -8157,13 +8157,13 @@
         <v>2.12</v>
       </c>
       <c r="V48">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="W48">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X48">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y48">
         <v>1.09</v>
@@ -8175,19 +8175,19 @@
         <v>1.5</v>
       </c>
       <c r="AB48">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AC48">
-        <v>2.13</v>
+        <v>2.23</v>
       </c>
       <c r="AD48">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AE48">
         <v>1.25</v>
       </c>
       <c r="AF48">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AG48">
         <v>2.62</v>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AK48">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8296,7 +8296,7 @@
         </is>
       </c>
       <c r="N49">
-        <v>4.33</v>
+        <v>4.37</v>
       </c>
       <c r="O49">
         <v>3.8</v>
@@ -8305,13 +8305,13 @@
         <v>1.65</v>
       </c>
       <c r="Q49">
-        <v>4.71</v>
+        <v>4.79</v>
       </c>
       <c r="R49">
         <v>2.45</v>
       </c>
       <c r="S49">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T49">
         <v>3.6</v>
@@ -8323,7 +8323,7 @@
         <v>1.62</v>
       </c>
       <c r="W49">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X49">
         <v>1.03</v>
@@ -8341,7 +8341,7 @@
         <v>2.4</v>
       </c>
       <c r="AC49">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AD49">
         <v>1.55</v>
@@ -8350,7 +8350,7 @@
         <v>1.22</v>
       </c>
       <c r="AF49">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AG49">
         <v>2.35</v>
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AK49">
         <v>1.2</v>
@@ -8459,19 +8459,19 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="O50">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="P50">
-        <v>2.65</v>
+        <v>2.73</v>
       </c>
       <c r="Q50">
         <v>2.61</v>
       </c>
       <c r="R50">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="S50">
         <v>1.25</v>
@@ -8495,7 +8495,7 @@
         <v>1.12</v>
       </c>
       <c r="Z50">
-        <v>4.85</v>
+        <v>4.99</v>
       </c>
       <c r="AA50">
         <v>1.53</v>
@@ -8510,13 +8510,13 @@
         <v>1.53</v>
       </c>
       <c r="AE50">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF50">
         <v>1.44</v>
       </c>
       <c r="AG50">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,31 +8622,31 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.39</v>
+        <v>2.4</v>
       </c>
       <c r="O51">
-        <v>4.75</v>
+        <v>3.5</v>
       </c>
       <c r="P51">
-        <v>5.4</v>
+        <v>2.44</v>
       </c>
       <c r="Q51">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="R51">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="S51">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T51">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="U51">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="V51">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="W51">
         <v>1.13</v>
@@ -8655,31 +8655,31 @@
         <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Z51">
         <v>5.5</v>
       </c>
       <c r="AA51">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AB51">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="AC51">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="AD51">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AE51">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AF51">
-        <v>1.57</v>
+        <v>1.41</v>
       </c>
       <c r="AG51">
-        <v>2.3</v>
+        <v>2.66</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AK51">
-        <v>2.7</v>
+        <v>1.42</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,80 +8785,80 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.44</v>
+        <v>1.43</v>
       </c>
       <c r="O52">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="P52">
-        <v>2.42</v>
+        <v>5.5</v>
       </c>
       <c r="Q52">
-        <v>2.8</v>
+        <v>1.85</v>
       </c>
       <c r="R52">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="S52">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="T52">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="U52">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V52">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="W52">
         <v>1.14</v>
       </c>
       <c r="X52">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y52">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z52">
         <v>5.5</v>
       </c>
       <c r="AA52">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AB52">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="AC52">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="AD52">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AE52">
         <v>1.23</v>
       </c>
       <c r="AF52">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AG52">
+        <v>2.3</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ52">
+        <v>1.18</v>
+      </c>
+      <c r="AK52">
         <v>2.7</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ52">
-        <v>1.2</v>
-      </c>
-      <c r="AK52">
-        <v>1.42</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8948,34 +8948,34 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="O53">
-        <v>4.75</v>
+        <v>4.35</v>
       </c>
       <c r="P53">
         <v>9</v>
       </c>
       <c r="Q53">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="R53">
         <v>2.45</v>
       </c>
       <c r="S53">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T53">
-        <v>2.99</v>
+        <v>2.9</v>
       </c>
       <c r="U53">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="V53">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W53">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X53">
         <v>1</v>
@@ -8984,28 +8984,28 @@
         <v>1.22</v>
       </c>
       <c r="Z53">
-        <v>3.72</v>
+        <v>3.58</v>
       </c>
       <c r="AA53">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AB53">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC53">
-        <v>2.9</v>
+        <v>2.97</v>
       </c>
       <c r="AD53">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AE53">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF53">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AG53">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>1.06</v>
       </c>
       <c r="AK53">
-        <v>3.34</v>
+        <v>3</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9111,16 +9111,16 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="O54">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P54">
-        <v>3</v>
+        <v>3.09</v>
       </c>
       <c r="Q54">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="R54">
         <v>2.2</v>
@@ -9129,28 +9129,28 @@
         <v>1.31</v>
       </c>
       <c r="T54">
-        <v>3.1</v>
+        <v>2.86</v>
       </c>
       <c r="U54">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="V54">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W54">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X54">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y54">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z54">
-        <v>3.82</v>
+        <v>3.84</v>
       </c>
       <c r="AA54">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AB54">
         <v>1.99</v>
@@ -9159,16 +9159,16 @@
         <v>2.88</v>
       </c>
       <c r="AD54">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE54">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF54">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AG54">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9274,22 +9274,22 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="O55">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="P55">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="Q55">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="R55">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="S55">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T55">
         <v>2.8</v>
@@ -9298,7 +9298,7 @@
         <v>2.75</v>
       </c>
       <c r="V55">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W55">
         <v>1.04</v>
@@ -9307,10 +9307,10 @@
         <v>1.02</v>
       </c>
       <c r="Y55">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z55">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AA55">
         <v>2</v>
@@ -9319,19 +9319,19 @@
         <v>1.8</v>
       </c>
       <c r="AC55">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="AD55">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE55">
         <v>1.08</v>
       </c>
       <c r="AF55">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AG55">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,7 +9344,7 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AK55">
         <v>1.46</v>
@@ -9437,10 +9437,10 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="O56">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="P56">
         <v>4.7</v>
@@ -9449,46 +9449,46 @@
         <v>2</v>
       </c>
       <c r="R56">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="S56">
         <v>1.27</v>
       </c>
       <c r="T56">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U56">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="V56">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W56">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X56">
         <v>1.03</v>
       </c>
       <c r="Y56">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z56">
-        <v>4.58</v>
+        <v>4.63</v>
       </c>
       <c r="AA56">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AB56">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AC56">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="AD56">
         <v>1.5</v>
       </c>
       <c r="AE56">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AF56">
         <v>1.62</v>
@@ -9507,7 +9507,7 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AK56">
         <v>2.25</v>
@@ -9603,13 +9603,13 @@
         <v>1.8</v>
       </c>
       <c r="O57">
-        <v>3.36</v>
+        <v>3.25</v>
       </c>
       <c r="P57">
-        <v>4.15</v>
+        <v>4.16</v>
       </c>
       <c r="Q57">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="R57">
         <v>2.28</v>
@@ -9618,34 +9618,34 @@
         <v>1.37</v>
       </c>
       <c r="T57">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="U57">
-        <v>2.65</v>
+        <v>2.73</v>
       </c>
       <c r="V57">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W57">
         <v>1.05</v>
       </c>
       <c r="X57">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y57">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z57">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AA57">
-        <v>1.82</v>
+        <v>1.94</v>
       </c>
       <c r="AB57">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AC57">
-        <v>3.19</v>
+        <v>3.25</v>
       </c>
       <c r="AD57">
         <v>1.33</v>
@@ -9654,10 +9654,10 @@
         <v>1.08</v>
       </c>
       <c r="AF57">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="AG57">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="O58">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="P58">
-        <v>2.98</v>
+        <v>2.75</v>
       </c>
       <c r="Q58">
         <v>2.5</v>
@@ -9784,7 +9784,7 @@
         <v>3.04</v>
       </c>
       <c r="U58">
-        <v>2.28</v>
+        <v>2.54</v>
       </c>
       <c r="V58">
         <v>1.5</v>
@@ -9796,7 +9796,7 @@
         <v>1.04</v>
       </c>
       <c r="Y58">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z58">
         <v>4.1</v>
@@ -9805,22 +9805,22 @@
         <v>1.7</v>
       </c>
       <c r="AB58">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC58">
-        <v>2.57</v>
+        <v>2.63</v>
       </c>
       <c r="AD58">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE58">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF58">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="AG58">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9836,7 +9836,7 @@
         <v>1.23</v>
       </c>
       <c r="AK58">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9926,49 +9926,49 @@
         </is>
       </c>
       <c r="N59">
-        <v>6.85</v>
+        <v>5</v>
       </c>
       <c r="O59">
-        <v>4.35</v>
+        <v>4</v>
       </c>
       <c r="P59">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="Q59">
-        <v>6.3</v>
+        <v>4.94</v>
       </c>
       <c r="R59">
-        <v>2.47</v>
+        <v>2.23</v>
       </c>
       <c r="S59">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T59">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="U59">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="V59">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="W59">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X59">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y59">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z59">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="AA59">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AB59">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="AC59">
         <v>2.62</v>
@@ -9977,10 +9977,10 @@
         <v>1.4</v>
       </c>
       <c r="AE59">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AF59">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG59">
         <v>1.85</v>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.14</v>
+        <v>2.44</v>
       </c>
       <c r="AK59">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10089,16 +10089,16 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="O60">
-        <v>4.4</v>
+        <v>4.05</v>
       </c>
       <c r="P60">
-        <v>4.73</v>
+        <v>4.7</v>
       </c>
       <c r="Q60">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="R60">
         <v>2.64</v>
@@ -10125,7 +10125,7 @@
         <v>1.12</v>
       </c>
       <c r="Z60">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="AA60">
         <v>1.5</v>
@@ -10146,7 +10146,7 @@
         <v>1.57</v>
       </c>
       <c r="AG60">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.4</v>
+        <v>1.98</v>
       </c>
       <c r="O61">
-        <v>4.5</v>
+        <v>3.45</v>
       </c>
       <c r="P61">
-        <v>6.85</v>
+        <v>3.2</v>
       </c>
       <c r="Q61">
-        <v>1.83</v>
+        <v>2.4</v>
       </c>
       <c r="R61">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="S61">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T61">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U61">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="V61">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W61">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X61">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z61">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AA61">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AB61">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AC61">
-        <v>2.8</v>
+        <v>2.68</v>
       </c>
       <c r="AD61">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AE61">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AF61">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AG61">
-        <v>1.73</v>
+        <v>2.15</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="AK61">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.98</v>
+        <v>1.4</v>
       </c>
       <c r="O62">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="P62">
+        <v>6.52</v>
+      </c>
+      <c r="Q62">
+        <v>1.83</v>
+      </c>
+      <c r="R62">
+        <v>2.4</v>
+      </c>
+      <c r="S62">
+        <v>1.29</v>
+      </c>
+      <c r="T62">
         <v>3.3</v>
       </c>
-      <c r="Q62">
-        <v>2.5</v>
-      </c>
-      <c r="R62">
-        <v>2.33</v>
-      </c>
-      <c r="S62">
-        <v>1.33</v>
-      </c>
-      <c r="T62">
-        <v>3.23</v>
-      </c>
       <c r="U62">
-        <v>2.43</v>
+        <v>2.58</v>
       </c>
       <c r="V62">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="W62">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X62">
         <v>1.04</v>
       </c>
       <c r="Y62">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z62">
-        <v>3.85</v>
+        <v>3.84</v>
       </c>
       <c r="AA62">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AB62">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AC62">
-        <v>2.71</v>
+        <v>2.8</v>
       </c>
       <c r="AD62">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE62">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF62">
-        <v>1.58</v>
+        <v>1.92</v>
       </c>
       <c r="AG62">
-        <v>2.12</v>
+        <v>1.83</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="AK62">
-        <v>1.73</v>
+        <v>2.7</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="O63">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P63">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Q63">
         <v>0</v>
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="O64">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P64">
-        <v>4</v>
+        <v>4.47</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -10904,13 +10904,13 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="O65">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="P65">
-        <v>2.87</v>
+        <v>2.91</v>
       </c>
       <c r="Q65">
         <v>0</v>
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="N67">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="O67">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="P67">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="Q67">
         <v>0</v>
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O69">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="P69">
-        <v>3.3</v>
+        <v>3.59</v>
       </c>
       <c r="Q69">
         <v>0</v>
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="O70">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P70">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="Q70">
         <v>0</v>
@@ -12045,19 +12045,19 @@
         </is>
       </c>
       <c r="N72">
-        <v>1.23</v>
+        <v>1.41</v>
       </c>
       <c r="O72">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
       <c r="P72">
-        <v>7.5</v>
+        <v>6.17</v>
       </c>
       <c r="Q72">
         <v>1.67</v>
       </c>
       <c r="R72">
-        <v>2.92</v>
+        <v>2.63</v>
       </c>
       <c r="S72">
         <v>1.2</v>
@@ -12072,7 +12072,7 @@
         <v>1.64</v>
       </c>
       <c r="W72">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X72">
         <v>1.01</v>
@@ -12084,25 +12084,25 @@
         <v>5.25</v>
       </c>
       <c r="AA72">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AB72">
         <v>2.6</v>
       </c>
       <c r="AC72">
-        <v>2.12</v>
+        <v>1.87</v>
       </c>
       <c r="AD72">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AE72">
         <v>1.25</v>
       </c>
       <c r="AF72">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AG72">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AK72">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="O73">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P73">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="Q73">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="R73">
         <v>2.25</v>
       </c>
       <c r="S73">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T73">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="U73">
-        <v>2.32</v>
+        <v>2.59</v>
       </c>
       <c r="V73">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="W73">
         <v>1.05</v>
       </c>
       <c r="X73">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y73">
         <v>1.25</v>
       </c>
       <c r="Z73">
-        <v>3.75</v>
+        <v>3.74</v>
       </c>
       <c r="AA73">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AB73">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AC73">
         <v>3</v>
       </c>
       <c r="AD73">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE73">
         <v>1.13</v>
       </c>
       <c r="AF73">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AG73">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12281,7 +12281,7 @@
         <v>1.29</v>
       </c>
       <c r="AK73">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12374,28 +12374,28 @@
         <v>1.98</v>
       </c>
       <c r="O74">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P74">
-        <v>3.29</v>
+        <v>3.1</v>
       </c>
       <c r="Q74">
-        <v>2.49</v>
+        <v>2.53</v>
       </c>
       <c r="R74">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S74">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T74">
-        <v>3.02</v>
+        <v>2.5</v>
       </c>
       <c r="U74">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="V74">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W74">
         <v>1.07</v>
@@ -12404,31 +12404,31 @@
         <v>1.03</v>
       </c>
       <c r="Y74">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z74">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AA74">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AB74">
-        <v>2.03</v>
+        <v>2.09</v>
       </c>
       <c r="AC74">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="AD74">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="AE74">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF74">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG74">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12534,25 +12534,25 @@
         </is>
       </c>
       <c r="N75">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="O75">
         <v>3.2</v>
       </c>
       <c r="P75">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="Q75">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="R75">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="S75">
         <v>1.37</v>
       </c>
       <c r="T75">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="U75">
         <v>2.7</v>
@@ -12561,7 +12561,7 @@
         <v>1.37</v>
       </c>
       <c r="W75">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X75">
         <v>1.05</v>
@@ -12573,10 +12573,10 @@
         <v>3.45</v>
       </c>
       <c r="AA75">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AB75">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AC75">
         <v>3.35</v>
@@ -12588,7 +12588,7 @@
         <v>1.1</v>
       </c>
       <c r="AF75">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AG75">
         <v>2</v>
@@ -12607,7 +12607,7 @@
         <v>1.33</v>
       </c>
       <c r="AK75">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12697,61 +12697,61 @@
         </is>
       </c>
       <c r="N76">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="O76">
-        <v>4.55</v>
+        <v>4.4</v>
       </c>
       <c r="P76">
-        <v>8.449999999999999</v>
+        <v>6</v>
       </c>
       <c r="Q76">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="R76">
+        <v>2.25</v>
+      </c>
+      <c r="S76">
+        <v>1.31</v>
+      </c>
+      <c r="T76">
+        <v>3.02</v>
+      </c>
+      <c r="U76">
+        <v>2.36</v>
+      </c>
+      <c r="V76">
+        <v>1.49</v>
+      </c>
+      <c r="W76">
+        <v>1.08</v>
+      </c>
+      <c r="X76">
+        <v>1.03</v>
+      </c>
+      <c r="Y76">
+        <v>1.14</v>
+      </c>
+      <c r="Z76">
+        <v>3.2</v>
+      </c>
+      <c r="AA76">
+        <v>1.59</v>
+      </c>
+      <c r="AB76">
+        <v>2.21</v>
+      </c>
+      <c r="AC76">
         <v>2.5</v>
       </c>
-      <c r="S76">
-        <v>1.25</v>
-      </c>
-      <c r="T76">
-        <v>2.96</v>
-      </c>
-      <c r="U76">
-        <v>2.38</v>
-      </c>
-      <c r="V76">
-        <v>1.48</v>
-      </c>
-      <c r="W76">
-        <v>1.12</v>
-      </c>
-      <c r="X76">
-        <v>1.04</v>
-      </c>
-      <c r="Y76">
-        <v>1.2</v>
-      </c>
-      <c r="Z76">
-        <v>4.33</v>
-      </c>
-      <c r="AA76">
-        <v>1.62</v>
-      </c>
-      <c r="AB76">
-        <v>2.15</v>
-      </c>
-      <c r="AC76">
-        <v>2.63</v>
-      </c>
       <c r="AD76">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AE76">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF76">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AG76">
         <v>1.85</v>
@@ -12770,7 +12770,7 @@
         <v>1.2</v>
       </c>
       <c r="AK76">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12860,13 +12860,13 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="O77">
-        <v>6.6</v>
+        <v>6.25</v>
       </c>
       <c r="P77">
-        <v>8.6</v>
+        <v>9.1</v>
       </c>
       <c r="Q77">
         <v>0</v>
@@ -13023,7 +13023,7 @@
         </is>
       </c>
       <c r="N78">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="O78">
         <v>3.92</v>
@@ -13035,7 +13035,7 @@
         <v>2.1</v>
       </c>
       <c r="R78">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="S78">
         <v>1.33</v>
@@ -13053,28 +13053,28 @@
         <v>1.06</v>
       </c>
       <c r="X78">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y78">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z78">
-        <v>4.1</v>
+        <v>3.94</v>
       </c>
       <c r="AA78">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AB78">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AC78">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="AD78">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AE78">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF78">
         <v>1.7</v>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AK78">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>1.88</v>
+        <v>1.72</v>
       </c>
       <c r="O79">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="P79">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="Q79">
-        <v>2.57</v>
+        <v>2.41</v>
       </c>
       <c r="R79">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="S79">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T79">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="U79">
         <v>3.08</v>
       </c>
       <c r="V79">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="W79">
+        <v>1.05</v>
+      </c>
+      <c r="X79">
         <v>1.06</v>
       </c>
-      <c r="X79">
+      <c r="Y79">
+        <v>1.37</v>
+      </c>
+      <c r="Z79">
+        <v>2.92</v>
+      </c>
+      <c r="AA79">
+        <v>2.21</v>
+      </c>
+      <c r="AB79">
+        <v>1.65</v>
+      </c>
+      <c r="AC79">
+        <v>3.78</v>
+      </c>
+      <c r="AD79">
+        <v>1.19</v>
+      </c>
+      <c r="AE79">
         <v>1.07</v>
       </c>
-      <c r="Y79">
-        <v>1.36</v>
-      </c>
-      <c r="Z79">
-        <v>2.7</v>
-      </c>
-      <c r="AA79">
-        <v>2.17</v>
-      </c>
-      <c r="AB79">
-        <v>1.6</v>
-      </c>
-      <c r="AC79">
-        <v>3.82</v>
-      </c>
-      <c r="AD79">
-        <v>1.18</v>
-      </c>
-      <c r="AE79">
-        <v>1.05</v>
-      </c>
       <c r="AF79">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AG79">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AK79">
-        <v>1.72</v>
+        <v>1.91</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13349,28 +13349,28 @@
         </is>
       </c>
       <c r="N80">
-        <v>3</v>
+        <v>3.07</v>
       </c>
       <c r="O80">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="P80">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="Q80">
-        <v>3.76</v>
+        <v>3.79</v>
       </c>
       <c r="R80">
         <v>2.15</v>
       </c>
       <c r="S80">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T80">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="U80">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="V80">
         <v>1.36</v>
@@ -13382,16 +13382,16 @@
         <v>1.06</v>
       </c>
       <c r="Y80">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z80">
         <v>3.3</v>
       </c>
       <c r="AA80">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AB80">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AC80">
         <v>3.3</v>
@@ -13400,13 +13400,13 @@
         <v>1.33</v>
       </c>
       <c r="AE80">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF80">
         <v>1.71</v>
       </c>
       <c r="AG80">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13422,7 +13422,7 @@
         <v>1.33</v>
       </c>
       <c r="AK80">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13518,10 +13518,10 @@
         <v>4</v>
       </c>
       <c r="P81">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="Q81">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="R81">
         <v>2.6</v>
@@ -13533,43 +13533,43 @@
         <v>3.9</v>
       </c>
       <c r="U81">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V81">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="W81">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X81">
         <v>1.01</v>
       </c>
       <c r="Y81">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z81">
-        <v>5.4</v>
+        <v>6.5</v>
       </c>
       <c r="AA81">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AB81">
         <v>3.4</v>
       </c>
       <c r="AC81">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="AD81">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AE81">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AF81">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AG81">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AK81">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13678,61 +13678,61 @@
         <v>2.3</v>
       </c>
       <c r="O82">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P82">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="Q82">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="R82">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="S82">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T82">
-        <v>2.91</v>
+        <v>3.08</v>
       </c>
       <c r="U82">
-        <v>2.53</v>
+        <v>2.42</v>
       </c>
       <c r="V82">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="W82">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X82">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y82">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="Z82">
-        <v>3.76</v>
+        <v>4.05</v>
       </c>
       <c r="AA82">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AB82">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AC82">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="AD82">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AE82">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF82">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG82">
-        <v>2.23</v>
+        <v>2.28</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK82">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13838,52 +13838,52 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="O83">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P83">
-        <v>4.73</v>
+        <v>4.05</v>
       </c>
       <c r="Q83">
         <v>2.6</v>
       </c>
       <c r="R83">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S83">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T83">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="U83">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="V83">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W83">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X83">
         <v>1.07</v>
       </c>
       <c r="Y83">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Z83">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AA83">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB83">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AC83">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="AD83">
         <v>1.25</v>
@@ -13892,10 +13892,10 @@
         <v>1.08</v>
       </c>
       <c r="AF83">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG83">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK83">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14001,19 +14001,19 @@
         </is>
       </c>
       <c r="N84">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="O84">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P84">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="Q84">
         <v>2.5</v>
       </c>
       <c r="R84">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="S84">
         <v>1.5</v>
@@ -14022,7 +14022,7 @@
         <v>2.5</v>
       </c>
       <c r="U84">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="V84">
         <v>1.22</v>
@@ -14040,25 +14040,25 @@
         <v>2.5</v>
       </c>
       <c r="AA84">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="AB84">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AC84">
-        <v>4.8</v>
+        <v>4.85</v>
       </c>
       <c r="AD84">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AE84">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AF84">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AG84">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14167,34 +14167,34 @@
         <v>1.61</v>
       </c>
       <c r="O85">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P85">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="Q85">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="R85">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S85">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T85">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="U85">
         <v>2.45</v>
       </c>
       <c r="V85">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W85">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X85">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y85">
         <v>1.22</v>
@@ -14206,22 +14206,22 @@
         <v>1.8</v>
       </c>
       <c r="AB85">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AC85">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="AD85">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AE85">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF85">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG85">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14327,16 +14327,16 @@
         </is>
       </c>
       <c r="N86">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="O86">
-        <v>3.75</v>
+        <v>3.67</v>
       </c>
       <c r="P86">
-        <v>3.74</v>
+        <v>3.62</v>
       </c>
       <c r="Q86">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="R86">
         <v>2.2</v>
@@ -14357,34 +14357,34 @@
         <v>1.14</v>
       </c>
       <c r="X86">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y86">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z86">
-        <v>4.7</v>
+        <v>3.4</v>
       </c>
       <c r="AA86">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AB86">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AC86">
         <v>1.96</v>
       </c>
       <c r="AD86">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AE86">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AF86">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG86">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14400,7 +14400,7 @@
         <v>1.15</v>
       </c>
       <c r="AK86">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14490,31 +14490,31 @@
         </is>
       </c>
       <c r="N87">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="O87">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="P87">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q87">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="R87">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="S87">
         <v>1.18</v>
       </c>
       <c r="T87">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="U87">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="V87">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="W87">
         <v>1.22</v>
@@ -14523,10 +14523,10 @@
         <v>1.01</v>
       </c>
       <c r="Y87">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z87">
-        <v>6.4</v>
+        <v>6.05</v>
       </c>
       <c r="AA87">
         <v>1.36</v>
@@ -14535,19 +14535,19 @@
         <v>3.1</v>
       </c>
       <c r="AC87">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AD87">
         <v>1.83</v>
       </c>
       <c r="AE87">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AF87">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AG87">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AK87">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14653,61 +14653,61 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="O88">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="P88">
-        <v>7.5</v>
+        <v>10.2</v>
       </c>
       <c r="Q88">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="R88">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="S88">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T88">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U88">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="V88">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="W88">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X88">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y88">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z88">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="AA88">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AB88">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="AC88">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="AD88">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AE88">
         <v>1.08</v>
       </c>
       <c r="AF88">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG88">
         <v>1.63</v>
@@ -14726,7 +14726,7 @@
         <v>1.2</v>
       </c>
       <c r="AK88">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14816,40 +14816,40 @@
         </is>
       </c>
       <c r="N89">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="O89">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P89">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q89">
-        <v>4.57</v>
+        <v>3.75</v>
       </c>
       <c r="R89">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="S89">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="T89">
-        <v>3.32</v>
+        <v>2.63</v>
       </c>
       <c r="U89">
-        <v>2.4</v>
+        <v>2.02</v>
       </c>
       <c r="V89">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="W89">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X89">
         <v>1.04</v>
       </c>
       <c r="Y89">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z89">
         <v>4</v>
@@ -14858,38 +14858,38 @@
         <v>1.7</v>
       </c>
       <c r="AB89">
-        <v>2.1</v>
+        <v>1.86</v>
       </c>
       <c r="AC89">
         <v>2.75</v>
       </c>
       <c r="AD89">
-        <v>1.51</v>
+        <v>1.33</v>
       </c>
       <c r="AE89">
+        <v>1.1</v>
+      </c>
+      <c r="AF89">
+        <v>1.45</v>
+      </c>
+      <c r="AG89">
+        <v>1.95</v>
+      </c>
+      <c r="AH89" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI89" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ89">
+        <v>2</v>
+      </c>
+      <c r="AK89">
         <v>1.16</v>
-      </c>
-      <c r="AF89">
-        <v>1.54</v>
-      </c>
-      <c r="AG89">
-        <v>2.25</v>
-      </c>
-      <c r="AH89" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI89" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ89">
-        <v>1.19</v>
-      </c>
-      <c r="AK89">
-        <v>1.15</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14982,10 +14982,10 @@
         <v>2.66</v>
       </c>
       <c r="O90">
-        <v>3.6</v>
+        <v>3.72</v>
       </c>
       <c r="P90">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="Q90">
         <v>0</v>
@@ -15142,28 +15142,28 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
       <c r="O91">
         <v>3.1</v>
       </c>
       <c r="P91">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="Q91">
-        <v>3.24</v>
+        <v>3.32</v>
       </c>
       <c r="R91">
         <v>2.03</v>
       </c>
       <c r="S91">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T91">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="U91">
-        <v>2.93</v>
+        <v>2.82</v>
       </c>
       <c r="V91">
         <v>1.36</v>
@@ -15172,13 +15172,13 @@
         <v>1.06</v>
       </c>
       <c r="X91">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y91">
         <v>1.27</v>
       </c>
       <c r="Z91">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AA91">
         <v>2</v>
@@ -15193,13 +15193,13 @@
         <v>1.3</v>
       </c>
       <c r="AE91">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF91">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG91">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,7 +15212,7 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AK91">
         <v>1.48</v>
@@ -15332,13 +15332,13 @@
         <v>1.33</v>
       </c>
       <c r="W92">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X92">
         <v>1.06</v>
       </c>
       <c r="Y92">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z92">
         <v>3</v>
@@ -15350,10 +15350,10 @@
         <v>1.68</v>
       </c>
       <c r="AC92">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AD92">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AE92">
         <v>1.06</v>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK92">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15477,16 +15477,16 @@
         <v>2.3</v>
       </c>
       <c r="Q93">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="R93">
         <v>2.11</v>
       </c>
       <c r="S93">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="T93">
-        <v>2.95</v>
+        <v>2.82</v>
       </c>
       <c r="U93">
         <v>2.5</v>
@@ -15501,25 +15501,25 @@
         <v>1</v>
       </c>
       <c r="Y93">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="Z93">
-        <v>3.84</v>
+        <v>3.9</v>
       </c>
       <c r="AA93">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AB93">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="AC93">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="AD93">
         <v>1.33</v>
       </c>
       <c r="AE93">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF93">
         <v>1.57</v>
@@ -15631,43 +15631,43 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="O94">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P94">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q94">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="R94">
         <v>1.98</v>
       </c>
       <c r="S94">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T94">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="U94">
-        <v>3.02</v>
+        <v>2.9</v>
       </c>
       <c r="V94">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="W94">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X94">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y94">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z94">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="AA94">
         <v>2.11</v>
@@ -15676,13 +15676,13 @@
         <v>1.69</v>
       </c>
       <c r="AC94">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="AD94">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AE94">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF94">
         <v>1.8</v>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AK94">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15794,25 +15794,25 @@
         </is>
       </c>
       <c r="N95">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="O95">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="P95">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="Q95">
         <v>1.7</v>
       </c>
       <c r="R95">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="S95">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="T95">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U95">
         <v>2.11</v>
@@ -15827,31 +15827,31 @@
         <v>1.02</v>
       </c>
       <c r="Y95">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="Z95">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="AA95">
         <v>1.44</v>
       </c>
       <c r="AB95">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AC95">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AD95">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AE95">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AF95">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG95">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>

--- a/jogos_2026-08-07.xlsx
+++ b/jogos_2026-08-07.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU95"/>
+  <dimension ref="A1:AU94"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.46</v>
+        <v>2.91</v>
       </c>
       <c r="O5">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="P5">
-        <v>4.4</v>
+        <v>2.2</v>
       </c>
       <c r="Q5">
-        <v>2.18</v>
+        <v>3.4</v>
       </c>
       <c r="R5">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="S5">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T5">
         <v>3.1</v>
       </c>
       <c r="U5">
-        <v>2.56</v>
+        <v>2.44</v>
       </c>
       <c r="V5">
         <v>1.44</v>
       </c>
       <c r="W5">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X5">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y5">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="Z5">
-        <v>3.81</v>
+        <v>3.45</v>
       </c>
       <c r="AA5">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AB5">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="AC5">
-        <v>3.07</v>
+        <v>2.87</v>
       </c>
       <c r="AD5">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AE5">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF5">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AG5">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK5">
-        <v>2.08</v>
+        <v>1.32</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>3.7</v>
+        <v>1.73</v>
       </c>
       <c r="O6">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P6">
-        <v>1.83</v>
+        <v>4.45</v>
       </c>
       <c r="Q6">
-        <v>4.33</v>
+        <v>2.44</v>
       </c>
       <c r="R6">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S6">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="T6">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="U6">
-        <v>2.88</v>
+        <v>3.17</v>
       </c>
       <c r="V6">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="W6">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X6">
         <v>1.04</v>
       </c>
       <c r="Y6">
+        <v>1.37</v>
+      </c>
+      <c r="Z6">
+        <v>3.1</v>
+      </c>
+      <c r="AA6">
+        <v>2.04</v>
+      </c>
+      <c r="AB6">
+        <v>1.65</v>
+      </c>
+      <c r="AC6">
+        <v>3.86</v>
+      </c>
+      <c r="AD6">
         <v>1.26</v>
       </c>
-      <c r="Z6">
-        <v>3.2</v>
-      </c>
-      <c r="AA6">
-        <v>1.87</v>
-      </c>
-      <c r="AB6">
-        <v>1.83</v>
-      </c>
-      <c r="AC6">
-        <v>3.29</v>
-      </c>
-      <c r="AD6">
-        <v>1.3</v>
-      </c>
       <c r="AE6">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF6">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AG6">
-        <v>1.95</v>
+        <v>1.79</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AK6">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.91</v>
+        <v>3.7</v>
       </c>
       <c r="O7">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P7">
+        <v>1.83</v>
+      </c>
+      <c r="Q7">
+        <v>4.33</v>
+      </c>
+      <c r="R7">
         <v>2.2</v>
       </c>
-      <c r="Q7">
-        <v>3.4</v>
-      </c>
-      <c r="R7">
-        <v>2.25</v>
-      </c>
       <c r="S7">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T7">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="U7">
-        <v>2.44</v>
+        <v>2.88</v>
       </c>
       <c r="V7">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W7">
         <v>1.08</v>
       </c>
       <c r="X7">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y7">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="Z7">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="AA7">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AB7">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="AC7">
-        <v>2.87</v>
+        <v>3.29</v>
       </c>
       <c r="AD7">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AE7">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF7">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AG7">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK7">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.73</v>
+        <v>1.46</v>
       </c>
       <c r="O9">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="P9">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="Q9">
-        <v>2.44</v>
+        <v>2.18</v>
       </c>
       <c r="R9">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="S9">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T9">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="U9">
-        <v>3.17</v>
+        <v>2.56</v>
       </c>
       <c r="V9">
+        <v>1.44</v>
+      </c>
+      <c r="W9">
+        <v>1.07</v>
+      </c>
+      <c r="X9">
+        <v>1.02</v>
+      </c>
+      <c r="Y9">
+        <v>1.19</v>
+      </c>
+      <c r="Z9">
+        <v>3.81</v>
+      </c>
+      <c r="AA9">
+        <v>1.81</v>
+      </c>
+      <c r="AB9">
+        <v>2.03</v>
+      </c>
+      <c r="AC9">
+        <v>3.07</v>
+      </c>
+      <c r="AD9">
         <v>1.33</v>
       </c>
-      <c r="W9">
-        <v>1.03</v>
-      </c>
-      <c r="X9">
-        <v>1.04</v>
-      </c>
-      <c r="Y9">
-        <v>1.37</v>
-      </c>
-      <c r="Z9">
-        <v>3.1</v>
-      </c>
-      <c r="AA9">
-        <v>2.04</v>
-      </c>
-      <c r="AB9">
-        <v>1.65</v>
-      </c>
-      <c r="AC9">
-        <v>3.86</v>
-      </c>
-      <c r="AD9">
-        <v>1.26</v>
-      </c>
       <c r="AE9">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AF9">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AG9">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AK9">
-        <v>1.9</v>
+        <v>2.08</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.59</v>
+        <v>4.2</v>
       </c>
       <c r="O23">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="P23">
-        <v>4.79</v>
+        <v>1.7</v>
       </c>
       <c r="Q23">
-        <v>2.06</v>
+        <v>4.3</v>
       </c>
       <c r="R23">
-        <v>2.21</v>
+        <v>2.12</v>
       </c>
       <c r="S23">
+        <v>1.33</v>
+      </c>
+      <c r="T23">
+        <v>3</v>
+      </c>
+      <c r="U23">
+        <v>2.75</v>
+      </c>
+      <c r="V23">
+        <v>1.4</v>
+      </c>
+      <c r="W23">
+        <v>1.04</v>
+      </c>
+      <c r="X23">
+        <v>1.05</v>
+      </c>
+      <c r="Y23">
+        <v>1.25</v>
+      </c>
+      <c r="Z23">
+        <v>3.4</v>
+      </c>
+      <c r="AA23">
+        <v>1.85</v>
+      </c>
+      <c r="AB23">
+        <v>1.85</v>
+      </c>
+      <c r="AC23">
+        <v>3.2</v>
+      </c>
+      <c r="AD23">
         <v>1.3</v>
       </c>
-      <c r="T23">
-        <v>3.04</v>
-      </c>
-      <c r="U23">
-        <v>2.4</v>
-      </c>
-      <c r="V23">
-        <v>1.45</v>
-      </c>
-      <c r="W23">
-        <v>1.07</v>
-      </c>
-      <c r="X23">
-        <v>1.03</v>
-      </c>
-      <c r="Y23">
-        <v>1.18</v>
-      </c>
-      <c r="Z23">
-        <v>4.33</v>
-      </c>
-      <c r="AA23">
-        <v>1.62</v>
-      </c>
-      <c r="AB23">
-        <v>2.15</v>
-      </c>
-      <c r="AC23">
-        <v>2.68</v>
-      </c>
-      <c r="AD23">
-        <v>1.44</v>
-      </c>
       <c r="AE23">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AF23">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AG23">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK23">
-        <v>2.2</v>
+        <v>1.15</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,55 +4221,55 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="O24">
         <v>3.8</v>
       </c>
       <c r="P24">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Q24">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="R24">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="S24">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T24">
-        <v>3.2</v>
+        <v>2.86</v>
       </c>
       <c r="U24">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="V24">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W24">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X24">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y24">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="Z24">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="AA24">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AB24">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AC24">
-        <v>3.13</v>
+        <v>2.95</v>
       </c>
       <c r="AD24">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE24">
         <v>1.11</v>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AK24">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,80 +4384,80 @@
         </is>
       </c>
       <c r="N25">
-        <v>4.2</v>
+        <v>1.59</v>
       </c>
       <c r="O25">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P25">
-        <v>1.7</v>
+        <v>4.79</v>
       </c>
       <c r="Q25">
-        <v>4.3</v>
+        <v>2.06</v>
       </c>
       <c r="R25">
-        <v>2.12</v>
+        <v>2.21</v>
       </c>
       <c r="S25">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T25">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="U25">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="V25">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W25">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X25">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y25">
+        <v>1.18</v>
+      </c>
+      <c r="Z25">
+        <v>4.33</v>
+      </c>
+      <c r="AA25">
+        <v>1.62</v>
+      </c>
+      <c r="AB25">
+        <v>2.15</v>
+      </c>
+      <c r="AC25">
+        <v>2.68</v>
+      </c>
+      <c r="AD25">
+        <v>1.44</v>
+      </c>
+      <c r="AE25">
+        <v>1.17</v>
+      </c>
+      <c r="AF25">
+        <v>1.67</v>
+      </c>
+      <c r="AG25">
+        <v>2.1</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ25">
         <v>1.25</v>
       </c>
-      <c r="Z25">
-        <v>3.4</v>
-      </c>
-      <c r="AA25">
-        <v>1.85</v>
-      </c>
-      <c r="AB25">
-        <v>1.85</v>
-      </c>
-      <c r="AC25">
-        <v>3.2</v>
-      </c>
-      <c r="AD25">
-        <v>1.3</v>
-      </c>
-      <c r="AE25">
-        <v>1.11</v>
-      </c>
-      <c r="AF25">
-        <v>1.78</v>
-      </c>
-      <c r="AG25">
-        <v>1.89</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ25">
-        <v>1.22</v>
-      </c>
       <c r="AK25">
-        <v>1.15</v>
+        <v>2.2</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,55 +4547,55 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="O26">
         <v>3.8</v>
       </c>
       <c r="P26">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Q26">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="R26">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="S26">
+        <v>1.34</v>
+      </c>
+      <c r="T26">
+        <v>3.2</v>
+      </c>
+      <c r="U26">
+        <v>2.75</v>
+      </c>
+      <c r="V26">
+        <v>1.43</v>
+      </c>
+      <c r="W26">
+        <v>1.1</v>
+      </c>
+      <c r="X26">
+        <v>1.05</v>
+      </c>
+      <c r="Y26">
+        <v>1.23</v>
+      </c>
+      <c r="Z26">
+        <v>3.6</v>
+      </c>
+      <c r="AA26">
+        <v>1.74</v>
+      </c>
+      <c r="AB26">
+        <v>1.87</v>
+      </c>
+      <c r="AC26">
+        <v>3.13</v>
+      </c>
+      <c r="AD26">
         <v>1.33</v>
-      </c>
-      <c r="T26">
-        <v>2.86</v>
-      </c>
-      <c r="U26">
-        <v>2.63</v>
-      </c>
-      <c r="V26">
-        <v>1.44</v>
-      </c>
-      <c r="W26">
-        <v>1.05</v>
-      </c>
-      <c r="X26">
-        <v>1</v>
-      </c>
-      <c r="Y26">
-        <v>1.21</v>
-      </c>
-      <c r="Z26">
-        <v>3.58</v>
-      </c>
-      <c r="AA26">
-        <v>1.78</v>
-      </c>
-      <c r="AB26">
-        <v>1.91</v>
-      </c>
-      <c r="AC26">
-        <v>2.95</v>
-      </c>
-      <c r="AD26">
-        <v>1.3</v>
       </c>
       <c r="AE26">
         <v>1.11</v>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.19</v>
+        <v>1.07</v>
       </c>
       <c r="AK26">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,80 +5036,80 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="O29">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="P29">
-        <v>2.77</v>
+        <v>2.6</v>
       </c>
       <c r="Q29">
+        <v>2.98</v>
+      </c>
+      <c r="R29">
+        <v>2.15</v>
+      </c>
+      <c r="S29">
+        <v>1.33</v>
+      </c>
+      <c r="T29">
+        <v>2.95</v>
+      </c>
+      <c r="U29">
+        <v>2.62</v>
+      </c>
+      <c r="V29">
+        <v>1.42</v>
+      </c>
+      <c r="W29">
+        <v>1.07</v>
+      </c>
+      <c r="X29">
+        <v>1.05</v>
+      </c>
+      <c r="Y29">
+        <v>1.28</v>
+      </c>
+      <c r="Z29">
+        <v>3.7</v>
+      </c>
+      <c r="AA29">
+        <v>1.77</v>
+      </c>
+      <c r="AB29">
+        <v>1.96</v>
+      </c>
+      <c r="AC29">
         <v>3.1</v>
       </c>
-      <c r="R29">
-        <v>1.89</v>
-      </c>
-      <c r="S29">
-        <v>1.44</v>
-      </c>
-      <c r="T29">
-        <v>2.67</v>
-      </c>
-      <c r="U29">
-        <v>3.16</v>
-      </c>
-      <c r="V29">
+      <c r="AD29">
+        <v>1.33</v>
+      </c>
+      <c r="AE29">
+        <v>1.08</v>
+      </c>
+      <c r="AF29">
+        <v>1.6</v>
+      </c>
+      <c r="AG29">
+        <v>2.1</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ29">
         <v>1.3</v>
       </c>
-      <c r="W29">
-        <v>1.02</v>
-      </c>
-      <c r="X29">
-        <v>1.03</v>
-      </c>
-      <c r="Y29">
-        <v>1.35</v>
-      </c>
-      <c r="Z29">
-        <v>2.74</v>
-      </c>
-      <c r="AA29">
-        <v>2.19</v>
-      </c>
-      <c r="AB29">
-        <v>1.64</v>
-      </c>
-      <c r="AC29">
-        <v>3.95</v>
-      </c>
-      <c r="AD29">
-        <v>1.18</v>
-      </c>
-      <c r="AE29">
-        <v>1.02</v>
-      </c>
-      <c r="AF29">
-        <v>1.86</v>
-      </c>
-      <c r="AG29">
-        <v>1.84</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ29">
-        <v>1.33</v>
-      </c>
       <c r="AK29">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5157,22 +5157,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.37</v>
+        <v>1.44</v>
       </c>
       <c r="O30">
-        <v>3.2</v>
+        <v>4.25</v>
       </c>
       <c r="P30">
-        <v>2.6</v>
+        <v>5.5</v>
       </c>
       <c r="Q30">
-        <v>2.98</v>
+        <v>2</v>
       </c>
       <c r="R30">
-        <v>2.15</v>
+        <v>2.26</v>
       </c>
       <c r="S30">
         <v>1.33</v>
       </c>
       <c r="T30">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="U30">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="V30">
         <v>1.42</v>
       </c>
       <c r="W30">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X30">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y30">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z30">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="AA30">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AB30">
-        <v>1.96</v>
+        <v>2.01</v>
       </c>
       <c r="AC30">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="AD30">
         <v>1.33</v>
       </c>
       <c r="AE30">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF30">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AG30">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.3</v>
+        <v>1.07</v>
       </c>
       <c r="AK30">
-        <v>1.47</v>
+        <v>2.88</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5320,22 +5320,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,80 +5362,80 @@
         </is>
       </c>
       <c r="N31">
+        <v>3.05</v>
+      </c>
+      <c r="O31">
+        <v>3.42</v>
+      </c>
+      <c r="P31">
+        <v>2.16</v>
+      </c>
+      <c r="Q31">
+        <v>3.25</v>
+      </c>
+      <c r="R31">
+        <v>2.1</v>
+      </c>
+      <c r="S31">
+        <v>1.28</v>
+      </c>
+      <c r="T31">
+        <v>3.15</v>
+      </c>
+      <c r="U31">
+        <v>2.33</v>
+      </c>
+      <c r="V31">
+        <v>1.53</v>
+      </c>
+      <c r="W31">
+        <v>1.1</v>
+      </c>
+      <c r="X31">
+        <v>1.02</v>
+      </c>
+      <c r="Y31">
+        <v>1.2</v>
+      </c>
+      <c r="Z31">
+        <v>4.2</v>
+      </c>
+      <c r="AA31">
+        <v>1.61</v>
+      </c>
+      <c r="AB31">
+        <v>2.1</v>
+      </c>
+      <c r="AC31">
+        <v>2.43</v>
+      </c>
+      <c r="AD31">
         <v>1.44</v>
       </c>
-      <c r="O31">
-        <v>4.25</v>
-      </c>
-      <c r="P31">
-        <v>5.5</v>
-      </c>
-      <c r="Q31">
-        <v>2</v>
-      </c>
-      <c r="R31">
-        <v>2.26</v>
-      </c>
-      <c r="S31">
+      <c r="AE31">
+        <v>1.14</v>
+      </c>
+      <c r="AF31">
+        <v>1.57</v>
+      </c>
+      <c r="AG31">
+        <v>2.25</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ31">
+        <v>1.5</v>
+      </c>
+      <c r="AK31">
         <v>1.33</v>
-      </c>
-      <c r="T31">
-        <v>3</v>
-      </c>
-      <c r="U31">
-        <v>2.6</v>
-      </c>
-      <c r="V31">
-        <v>1.42</v>
-      </c>
-      <c r="W31">
-        <v>1.06</v>
-      </c>
-      <c r="X31">
-        <v>1.04</v>
-      </c>
-      <c r="Y31">
-        <v>1.25</v>
-      </c>
-      <c r="Z31">
-        <v>3.65</v>
-      </c>
-      <c r="AA31">
-        <v>1.83</v>
-      </c>
-      <c r="AB31">
-        <v>2.01</v>
-      </c>
-      <c r="AC31">
-        <v>2.7</v>
-      </c>
-      <c r="AD31">
-        <v>1.33</v>
-      </c>
-      <c r="AE31">
-        <v>1.1</v>
-      </c>
-      <c r="AF31">
-        <v>2</v>
-      </c>
-      <c r="AG31">
-        <v>1.75</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ31">
-        <v>1.07</v>
-      </c>
-      <c r="AK31">
-        <v>2.88</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5483,22 +5483,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>3.05</v>
+        <v>1.95</v>
       </c>
       <c r="O32">
-        <v>3.42</v>
+        <v>3.64</v>
       </c>
       <c r="P32">
-        <v>2.16</v>
+        <v>3.56</v>
       </c>
       <c r="Q32">
-        <v>3.25</v>
+        <v>2.5</v>
       </c>
       <c r="R32">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S32">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="T32">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="U32">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="V32">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W32">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X32">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y32">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z32">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA32">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="AB32">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC32">
-        <v>2.43</v>
+        <v>2.7</v>
       </c>
       <c r="AD32">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AE32">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF32">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG32">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="AK32">
-        <v>1.33</v>
+        <v>1.82</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5646,7 +5646,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.95</v>
+        <v>1.68</v>
       </c>
       <c r="O33">
-        <v>3.64</v>
+        <v>3.8</v>
       </c>
       <c r="P33">
-        <v>3.56</v>
+        <v>4.07</v>
       </c>
       <c r="Q33">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="R33">
+        <v>2.38</v>
+      </c>
+      <c r="S33">
+        <v>1.26</v>
+      </c>
+      <c r="T33">
+        <v>3.6</v>
+      </c>
+      <c r="U33">
         <v>2.25</v>
       </c>
-      <c r="S33">
-        <v>1.32</v>
-      </c>
-      <c r="T33">
-        <v>3.2</v>
-      </c>
-      <c r="U33">
-        <v>2.36</v>
-      </c>
       <c r="V33">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W33">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X33">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y33">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z33">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AA33">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="AB33">
-        <v>2.05</v>
+        <v>2.21</v>
       </c>
       <c r="AC33">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="AD33">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AE33">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF33">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG33">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK33">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5972,22 +5972,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,31 +6014,31 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.68</v>
+        <v>3.31</v>
       </c>
       <c r="O35">
         <v>3.8</v>
       </c>
       <c r="P35">
-        <v>4.07</v>
+        <v>1.88</v>
       </c>
       <c r="Q35">
+        <v>3.6</v>
+      </c>
+      <c r="R35">
         <v>2.22</v>
       </c>
-      <c r="R35">
-        <v>2.38</v>
-      </c>
       <c r="S35">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="T35">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="U35">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="V35">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="W35">
         <v>1.12</v>
@@ -6047,16 +6047,16 @@
         <v>1.03</v>
       </c>
       <c r="Y35">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z35">
-        <v>4.2</v>
+        <v>4.75</v>
       </c>
       <c r="AA35">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AB35">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="AC35">
         <v>2.38</v>
@@ -6065,13 +6065,13 @@
         <v>1.47</v>
       </c>
       <c r="AE35">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AF35">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AG35">
-        <v>2.16</v>
+        <v>2.37</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="AK35">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6130,12 +6130,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>3.45</v>
+        <v>2.1</v>
       </c>
       <c r="O36">
-        <v>3.85</v>
+        <v>3.2</v>
       </c>
       <c r="P36">
-        <v>1.88</v>
+        <v>3.12</v>
       </c>
       <c r="Q36">
-        <v>3.75</v>
+        <v>2.83</v>
       </c>
       <c r="R36">
-        <v>2.22</v>
+        <v>2.05</v>
       </c>
       <c r="S36">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="T36">
-        <v>3.6</v>
+        <v>2.76</v>
       </c>
       <c r="U36">
-        <v>2.34</v>
+        <v>3.2</v>
       </c>
       <c r="V36">
-        <v>1.56</v>
+        <v>1.34</v>
       </c>
       <c r="W36">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X36">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y36">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="Z36">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="AA36">
-        <v>1.59</v>
+        <v>2.15</v>
       </c>
       <c r="AB36">
-        <v>2.31</v>
+        <v>1.66</v>
       </c>
       <c r="AC36">
-        <v>2.38</v>
+        <v>4.02</v>
       </c>
       <c r="AD36">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="AE36">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="AF36">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AG36">
-        <v>2.38</v>
+        <v>1.79</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.8</v>
+        <v>1.26</v>
       </c>
       <c r="AK36">
-        <v>1.29</v>
+        <v>1.74</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6281,7 +6281,7 @@
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>2026-08-07 14:00:00</t>
+          <t>2026-08-07 14:30:00</t>
         </is>
       </c>
     </row>
@@ -6298,22 +6298,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,65 +6340,65 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="O37">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P37">
-        <v>3.12</v>
+        <v>2.15</v>
       </c>
       <c r="Q37">
-        <v>2.83</v>
+        <v>3.56</v>
       </c>
       <c r="R37">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="S37">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="T37">
-        <v>2.76</v>
+        <v>3.02</v>
       </c>
       <c r="U37">
-        <v>3.2</v>
+        <v>2.41</v>
       </c>
       <c r="V37">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="W37">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X37">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y37">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="Z37">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="AA37">
+        <v>1.7</v>
+      </c>
+      <c r="AB37">
+        <v>2</v>
+      </c>
+      <c r="AC37">
+        <v>2.75</v>
+      </c>
+      <c r="AD37">
+        <v>1.37</v>
+      </c>
+      <c r="AE37">
+        <v>1.14</v>
+      </c>
+      <c r="AF37">
+        <v>1.6</v>
+      </c>
+      <c r="AG37">
         <v>2.15</v>
       </c>
-      <c r="AB37">
-        <v>1.66</v>
-      </c>
-      <c r="AC37">
-        <v>4.02</v>
-      </c>
-      <c r="AD37">
-        <v>1.22</v>
-      </c>
-      <c r="AE37">
-        <v>1.07</v>
-      </c>
-      <c r="AF37">
-        <v>1.85</v>
-      </c>
-      <c r="AG37">
-        <v>1.79</v>
-      </c>
       <c r="AH37" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK37">
-        <v>1.74</v>
+        <v>1.36</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6461,22 +6461,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.8</v>
+        <v>1.85</v>
       </c>
       <c r="O38">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P38">
-        <v>2.15</v>
+        <v>3.35</v>
       </c>
       <c r="Q38">
-        <v>3.56</v>
+        <v>2.3</v>
       </c>
       <c r="R38">
-        <v>2.17</v>
+        <v>2.4</v>
       </c>
       <c r="S38">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T38">
-        <v>3.02</v>
+        <v>3.7</v>
       </c>
       <c r="U38">
-        <v>2.41</v>
+        <v>2.2</v>
       </c>
       <c r="V38">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="W38">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="X38">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y38">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="Z38">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="AA38">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AB38">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AC38">
-        <v>2.75</v>
+        <v>2.29</v>
       </c>
       <c r="AD38">
-        <v>1.37</v>
+        <v>1.53</v>
       </c>
       <c r="AE38">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AF38">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="AG38">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK38">
-        <v>1.36</v>
+        <v>1.68</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.85</v>
+        <v>3.2</v>
       </c>
       <c r="O39">
+        <v>3.7</v>
+      </c>
+      <c r="P39">
+        <v>1.91</v>
+      </c>
+      <c r="Q39">
+        <v>3.93</v>
+      </c>
+      <c r="R39">
+        <v>2.5</v>
+      </c>
+      <c r="S39">
+        <v>1.22</v>
+      </c>
+      <c r="T39">
         <v>3.5</v>
       </c>
-      <c r="P39">
-        <v>3.35</v>
-      </c>
-      <c r="Q39">
-        <v>2.3</v>
-      </c>
-      <c r="R39">
-        <v>2.4</v>
-      </c>
-      <c r="S39">
-        <v>1.25</v>
-      </c>
-      <c r="T39">
-        <v>3.7</v>
-      </c>
       <c r="U39">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V39">
         <v>1.62</v>
       </c>
       <c r="W39">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X39">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="Z39">
-        <v>4.8</v>
+        <v>5.35</v>
       </c>
       <c r="AA39">
-        <v>1.6</v>
+        <v>1.42</v>
       </c>
       <c r="AB39">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AC39">
-        <v>2.29</v>
+        <v>2.15</v>
       </c>
       <c r="AD39">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AE39">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AF39">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AG39">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK39">
-        <v>1.68</v>
+        <v>1.3</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>3.2</v>
+        <v>1.41</v>
       </c>
       <c r="O40">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="P40">
-        <v>1.91</v>
+        <v>5.25</v>
       </c>
       <c r="Q40">
-        <v>3.93</v>
+        <v>1.83</v>
       </c>
       <c r="R40">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="S40">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="T40">
-        <v>3.5</v>
+        <v>3.84</v>
       </c>
       <c r="U40">
-        <v>2.18</v>
+        <v>2.01</v>
       </c>
       <c r="V40">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="W40">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X40">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Z40">
-        <v>5.35</v>
+        <v>5.65</v>
       </c>
       <c r="AA40">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="AB40">
-        <v>2.5</v>
+        <v>2.74</v>
       </c>
       <c r="AC40">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AD40">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AE40">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AF40">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AG40">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AK40">
-        <v>1.3</v>
+        <v>2.53</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6945,12 +6945,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>BSK Banja Luka</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,80 +6992,80 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.41</v>
+        <v>2.25</v>
       </c>
       <c r="O41">
-        <v>4.4</v>
+        <v>2.85</v>
       </c>
       <c r="P41">
-        <v>5.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q41">
-        <v>1.83</v>
+        <v>3.5</v>
       </c>
       <c r="R41">
-        <v>2.7</v>
+        <v>1.95</v>
       </c>
       <c r="S41">
-        <v>1.18</v>
+        <v>1.44</v>
       </c>
       <c r="T41">
-        <v>3.84</v>
+        <v>2.36</v>
       </c>
       <c r="U41">
-        <v>2.01</v>
+        <v>3.2</v>
       </c>
       <c r="V41">
-        <v>1.71</v>
+        <v>1.28</v>
       </c>
       <c r="W41">
+        <v>1.02</v>
+      </c>
+      <c r="X41">
+        <v>1.06</v>
+      </c>
+      <c r="Y41">
+        <v>1.45</v>
+      </c>
+      <c r="Z41">
+        <v>2.6</v>
+      </c>
+      <c r="AA41">
+        <v>2.38</v>
+      </c>
+      <c r="AB41">
+        <v>1.53</v>
+      </c>
+      <c r="AC41">
+        <v>4.15</v>
+      </c>
+      <c r="AD41">
         <v>1.17</v>
       </c>
-      <c r="X41">
+      <c r="AE41">
         <v>1.01</v>
       </c>
-      <c r="Y41">
-        <v>1.08</v>
-      </c>
-      <c r="Z41">
-        <v>5.65</v>
-      </c>
-      <c r="AA41">
-        <v>1.35</v>
-      </c>
-      <c r="AB41">
-        <v>2.74</v>
-      </c>
-      <c r="AC41">
-        <v>2</v>
-      </c>
-      <c r="AD41">
-        <v>1.73</v>
-      </c>
-      <c r="AE41">
+      <c r="AF41">
+        <v>1.91</v>
+      </c>
+      <c r="AG41">
+        <v>1.78</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ41">
         <v>1.3</v>
       </c>
-      <c r="AF41">
-        <v>1.5</v>
-      </c>
-      <c r="AG41">
-        <v>2.4</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ41">
-        <v>1.14</v>
-      </c>
       <c r="AK41">
-        <v>2.53</v>
+        <v>1.37</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7096,7 +7096,7 @@
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>2026-08-07 14:30:00</t>
+          <t>2026-08-07 15:00:00</t>
         </is>
       </c>
     </row>
@@ -7113,7 +7113,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>BSK Banja Luka</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.25</v>
+        <v>2.65</v>
       </c>
       <c r="O42">
-        <v>2.85</v>
+        <v>3.15</v>
       </c>
       <c r="P42">
-        <v>3.3</v>
+        <v>2.65</v>
       </c>
       <c r="Q42">
-        <v>3.5</v>
+        <v>3.37</v>
       </c>
       <c r="R42">
-        <v>1.95</v>
+        <v>2.16</v>
       </c>
       <c r="S42">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T42">
-        <v>2.36</v>
+        <v>2.8</v>
       </c>
       <c r="U42">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="V42">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="W42">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X42">
         <v>1.06</v>
       </c>
       <c r="Y42">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="Z42">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="AA42">
-        <v>2.38</v>
+        <v>2.05</v>
       </c>
       <c r="AB42">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AC42">
-        <v>4.15</v>
+        <v>3.7</v>
       </c>
       <c r="AD42">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AE42">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AF42">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AG42">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK42">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7276,7 +7276,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.65</v>
+        <v>2.33</v>
       </c>
       <c r="O43">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="P43">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="Q43">
-        <v>3.37</v>
+        <v>3.03</v>
       </c>
       <c r="R43">
-        <v>2.16</v>
+        <v>2.46</v>
       </c>
       <c r="S43">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="T43">
-        <v>2.8</v>
+        <v>3.34</v>
       </c>
       <c r="U43">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="V43">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="W43">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X43">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="Z43">
-        <v>3.1</v>
+        <v>4.75</v>
       </c>
       <c r="AA43">
-        <v>2.05</v>
+        <v>1.57</v>
       </c>
       <c r="AB43">
-        <v>1.7</v>
+        <v>2.33</v>
       </c>
       <c r="AC43">
-        <v>3.7</v>
+        <v>2.55</v>
       </c>
       <c r="AD43">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="AE43">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="AF43">
-        <v>1.8</v>
+        <v>1.47</v>
       </c>
       <c r="AG43">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK43">
-        <v>1.39</v>
+        <v>1.53</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7439,7 +7439,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.33</v>
+        <v>1.6</v>
       </c>
       <c r="O44">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="P44">
-        <v>2.6</v>
+        <v>5.5</v>
       </c>
       <c r="Q44">
-        <v>3.03</v>
+        <v>2.15</v>
       </c>
       <c r="R44">
-        <v>2.46</v>
+        <v>2</v>
       </c>
       <c r="S44">
-        <v>1.28</v>
+        <v>1.52</v>
       </c>
       <c r="T44">
-        <v>3.34</v>
+        <v>2.3</v>
       </c>
       <c r="U44">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="V44">
-        <v>1.57</v>
+        <v>1.29</v>
       </c>
       <c r="W44">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="X44">
+        <v>1.06</v>
+      </c>
+      <c r="Y44">
+        <v>1.41</v>
+      </c>
+      <c r="Z44">
+        <v>2.52</v>
+      </c>
+      <c r="AA44">
+        <v>2.34</v>
+      </c>
+      <c r="AB44">
+        <v>1.52</v>
+      </c>
+      <c r="AC44">
+        <v>4.33</v>
+      </c>
+      <c r="AD44">
+        <v>1.14</v>
+      </c>
+      <c r="AE44">
         <v>1.01</v>
       </c>
-      <c r="Y44">
-        <v>1.15</v>
-      </c>
-      <c r="Z44">
-        <v>4.75</v>
-      </c>
-      <c r="AA44">
-        <v>1.57</v>
-      </c>
-      <c r="AB44">
-        <v>2.33</v>
-      </c>
-      <c r="AC44">
-        <v>2.55</v>
-      </c>
-      <c r="AD44">
-        <v>1.47</v>
-      </c>
-      <c r="AE44">
-        <v>1.16</v>
-      </c>
       <c r="AF44">
-        <v>1.47</v>
+        <v>2.29</v>
       </c>
       <c r="AG44">
-        <v>2.4</v>
+        <v>1.53</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>1.29</v>
       </c>
       <c r="AK44">
-        <v>1.53</v>
+        <v>2.25</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7602,7 +7602,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,80 +7644,80 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.61</v>
+        <v>1.41</v>
       </c>
       <c r="O45">
-        <v>3.25</v>
+        <v>4.4</v>
       </c>
       <c r="P45">
-        <v>5.25</v>
+        <v>5.1</v>
       </c>
       <c r="Q45">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="R45">
-        <v>1.89</v>
+        <v>2.63</v>
       </c>
       <c r="S45">
-        <v>1.53</v>
+        <v>1.2</v>
       </c>
       <c r="T45">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="U45">
-        <v>3.3</v>
+        <v>2.08</v>
       </c>
       <c r="V45">
-        <v>1.24</v>
+        <v>1.77</v>
       </c>
       <c r="W45">
+        <v>1.15</v>
+      </c>
+      <c r="X45">
         <v>1.02</v>
       </c>
-      <c r="X45">
+      <c r="Y45">
         <v>1.08</v>
       </c>
-      <c r="Y45">
-        <v>1.41</v>
-      </c>
       <c r="Z45">
-        <v>2.52</v>
+        <v>5.75</v>
       </c>
       <c r="AA45">
-        <v>2.35</v>
+        <v>1.4</v>
       </c>
       <c r="AB45">
+        <v>2.62</v>
+      </c>
+      <c r="AC45">
+        <v>2.1</v>
+      </c>
+      <c r="AD45">
+        <v>1.68</v>
+      </c>
+      <c r="AE45">
+        <v>1.29</v>
+      </c>
+      <c r="AF45">
         <v>1.57</v>
       </c>
-      <c r="AC45">
-        <v>4.33</v>
-      </c>
-      <c r="AD45">
+      <c r="AG45">
+        <v>2.28</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ45">
         <v>1.14</v>
       </c>
-      <c r="AE45">
-        <v>1.05</v>
-      </c>
-      <c r="AF45">
-        <v>2.2</v>
-      </c>
-      <c r="AG45">
-        <v>1.57</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ45">
-        <v>1.25</v>
-      </c>
       <c r="AK45">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.41</v>
+        <v>2.75</v>
       </c>
       <c r="O46">
-        <v>4.4</v>
+        <v>3.45</v>
       </c>
       <c r="P46">
-        <v>5.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q46">
-        <v>1.9</v>
+        <v>2.95</v>
       </c>
       <c r="R46">
-        <v>2.63</v>
+        <v>2.24</v>
       </c>
       <c r="S46">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="T46">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="U46">
-        <v>2.08</v>
+        <v>2.32</v>
       </c>
       <c r="V46">
-        <v>1.77</v>
+        <v>1.53</v>
       </c>
       <c r="W46">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X46">
         <v>1.02</v>
       </c>
       <c r="Y46">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="Z46">
-        <v>5.75</v>
+        <v>4.25</v>
       </c>
       <c r="AA46">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AB46">
-        <v>2.62</v>
+        <v>2.19</v>
       </c>
       <c r="AC46">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AD46">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="AE46">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="AF46">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AG46">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AK46">
-        <v>2.63</v>
+        <v>1.36</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="O47">
-        <v>3.45</v>
+        <v>3.71</v>
       </c>
       <c r="P47">
-        <v>2.2</v>
+        <v>2.65</v>
       </c>
       <c r="Q47">
-        <v>2.95</v>
+        <v>2.63</v>
       </c>
       <c r="R47">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="S47">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="T47">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U47">
-        <v>2.32</v>
+        <v>2.12</v>
       </c>
       <c r="V47">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="W47">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X47">
         <v>1.02</v>
       </c>
       <c r="Y47">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="Z47">
-        <v>4.25</v>
+        <v>5.3</v>
       </c>
       <c r="AA47">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AB47">
-        <v>2.19</v>
+        <v>2.5</v>
       </c>
       <c r="AC47">
-        <v>2.5</v>
+        <v>2.23</v>
       </c>
       <c r="AD47">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AE47">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AF47">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AG47">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AK47">
-        <v>1.36</v>
+        <v>1.59</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.2</v>
+        <v>4.37</v>
       </c>
       <c r="O48">
-        <v>3.71</v>
+        <v>3.8</v>
       </c>
       <c r="P48">
-        <v>2.65</v>
+        <v>1.65</v>
       </c>
       <c r="Q48">
-        <v>2.63</v>
+        <v>4.79</v>
       </c>
       <c r="R48">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="S48">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T48">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="U48">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="V48">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="W48">
         <v>1.13</v>
       </c>
       <c r="X48">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y48">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="Z48">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="AA48">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AB48">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AC48">
-        <v>2.23</v>
+        <v>2.33</v>
       </c>
       <c r="AD48">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="AE48">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF48">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="AG48">
-        <v>2.62</v>
+        <v>2.35</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="AK48">
-        <v>1.59</v>
+        <v>1.2</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,19 +8296,19 @@
         </is>
       </c>
       <c r="N49">
-        <v>4.37</v>
+        <v>2.33</v>
       </c>
       <c r="O49">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="P49">
-        <v>1.65</v>
+        <v>2.73</v>
       </c>
       <c r="Q49">
-        <v>4.79</v>
+        <v>2.61</v>
       </c>
       <c r="R49">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="S49">
         <v>1.25</v>
@@ -8317,59 +8317,59 @@
         <v>3.6</v>
       </c>
       <c r="U49">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="V49">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="W49">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X49">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y49">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="Z49">
-        <v>5</v>
+        <v>4.99</v>
       </c>
       <c r="AA49">
+        <v>1.53</v>
+      </c>
+      <c r="AB49">
+        <v>2.35</v>
+      </c>
+      <c r="AC49">
+        <v>2.42</v>
+      </c>
+      <c r="AD49">
+        <v>1.53</v>
+      </c>
+      <c r="AE49">
+        <v>1.2</v>
+      </c>
+      <c r="AF49">
+        <v>1.44</v>
+      </c>
+      <c r="AG49">
+        <v>2.5</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ49">
+        <v>1.23</v>
+      </c>
+      <c r="AK49">
         <v>1.52</v>
-      </c>
-      <c r="AB49">
-        <v>2.4</v>
-      </c>
-      <c r="AC49">
-        <v>2.33</v>
-      </c>
-      <c r="AD49">
-        <v>1.55</v>
-      </c>
-      <c r="AE49">
-        <v>1.22</v>
-      </c>
-      <c r="AF49">
-        <v>1.6</v>
-      </c>
-      <c r="AG49">
-        <v>2.35</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ49">
-        <v>1.18</v>
-      </c>
-      <c r="AK49">
-        <v>1.2</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8412,12 +8412,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,65 +8459,65 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.33</v>
+        <v>1.43</v>
       </c>
       <c r="O50">
-        <v>3.58</v>
+        <v>4.5</v>
       </c>
       <c r="P50">
-        <v>2.73</v>
+        <v>5.5</v>
       </c>
       <c r="Q50">
-        <v>2.61</v>
+        <v>1.85</v>
       </c>
       <c r="R50">
+        <v>2.63</v>
+      </c>
+      <c r="S50">
+        <v>1.2</v>
+      </c>
+      <c r="T50">
+        <v>3.7</v>
+      </c>
+      <c r="U50">
+        <v>2.08</v>
+      </c>
+      <c r="V50">
+        <v>1.64</v>
+      </c>
+      <c r="W50">
+        <v>1.14</v>
+      </c>
+      <c r="X50">
+        <v>1.02</v>
+      </c>
+      <c r="Y50">
+        <v>1.13</v>
+      </c>
+      <c r="Z50">
+        <v>5.5</v>
+      </c>
+      <c r="AA50">
+        <v>1.4</v>
+      </c>
+      <c r="AB50">
+        <v>2.63</v>
+      </c>
+      <c r="AC50">
+        <v>2.05</v>
+      </c>
+      <c r="AD50">
+        <v>1.67</v>
+      </c>
+      <c r="AE50">
+        <v>1.23</v>
+      </c>
+      <c r="AF50">
+        <v>1.57</v>
+      </c>
+      <c r="AG50">
         <v>2.3</v>
       </c>
-      <c r="S50">
-        <v>1.25</v>
-      </c>
-      <c r="T50">
-        <v>3.6</v>
-      </c>
-      <c r="U50">
-        <v>2.25</v>
-      </c>
-      <c r="V50">
-        <v>1.57</v>
-      </c>
-      <c r="W50">
-        <v>1.15</v>
-      </c>
-      <c r="X50">
-        <v>1.01</v>
-      </c>
-      <c r="Y50">
-        <v>1.12</v>
-      </c>
-      <c r="Z50">
-        <v>4.99</v>
-      </c>
-      <c r="AA50">
-        <v>1.53</v>
-      </c>
-      <c r="AB50">
-        <v>2.35</v>
-      </c>
-      <c r="AC50">
-        <v>2.42</v>
-      </c>
-      <c r="AD50">
-        <v>1.53</v>
-      </c>
-      <c r="AE50">
-        <v>1.2</v>
-      </c>
-      <c r="AF50">
-        <v>1.44</v>
-      </c>
-      <c r="AG50">
-        <v>2.5</v>
-      </c>
       <c r="AH50" t="inlineStr">
         <is>
           <t>[]</t>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AK50">
-        <v>1.52</v>
+        <v>2.7</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8563,7 +8563,7 @@
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>2026-08-07 15:00:00</t>
+          <t>2026-08-07 15:15:00</t>
         </is>
       </c>
     </row>
@@ -8743,7 +8743,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="O52">
-        <v>4.5</v>
+        <v>4.35</v>
       </c>
       <c r="P52">
-        <v>5.5</v>
+        <v>9</v>
       </c>
       <c r="Q52">
+        <v>1.8</v>
+      </c>
+      <c r="R52">
+        <v>2.45</v>
+      </c>
+      <c r="S52">
+        <v>1.35</v>
+      </c>
+      <c r="T52">
+        <v>2.9</v>
+      </c>
+      <c r="U52">
+        <v>2.54</v>
+      </c>
+      <c r="V52">
+        <v>1.42</v>
+      </c>
+      <c r="W52">
+        <v>1.05</v>
+      </c>
+      <c r="X52">
+        <v>1</v>
+      </c>
+      <c r="Y52">
+        <v>1.22</v>
+      </c>
+      <c r="Z52">
+        <v>3.58</v>
+      </c>
+      <c r="AA52">
         <v>1.85</v>
       </c>
-      <c r="R52">
-        <v>2.63</v>
-      </c>
-      <c r="S52">
-        <v>1.2</v>
-      </c>
-      <c r="T52">
-        <v>3.7</v>
-      </c>
-      <c r="U52">
-        <v>2.08</v>
-      </c>
-      <c r="V52">
-        <v>1.64</v>
-      </c>
-      <c r="W52">
-        <v>1.14</v>
-      </c>
-      <c r="X52">
-        <v>1.02</v>
-      </c>
-      <c r="Y52">
+      <c r="AB52">
+        <v>1.95</v>
+      </c>
+      <c r="AC52">
+        <v>2.97</v>
+      </c>
+      <c r="AD52">
+        <v>1.35</v>
+      </c>
+      <c r="AE52">
         <v>1.13</v>
       </c>
-      <c r="Z52">
-        <v>5.5</v>
-      </c>
-      <c r="AA52">
-        <v>1.4</v>
-      </c>
-      <c r="AB52">
-        <v>2.63</v>
-      </c>
-      <c r="AC52">
-        <v>2.05</v>
-      </c>
-      <c r="AD52">
-        <v>1.67</v>
-      </c>
-      <c r="AE52">
-        <v>1.23</v>
-      </c>
       <c r="AF52">
-        <v>1.57</v>
+        <v>2.2</v>
       </c>
       <c r="AG52">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="AK52">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8901,12 +8901,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,81 +8948,81 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.33</v>
+        <v>2.1</v>
       </c>
       <c r="O53">
-        <v>4.35</v>
+        <v>3.35</v>
       </c>
       <c r="P53">
-        <v>9</v>
+        <v>3.09</v>
       </c>
       <c r="Q53">
-        <v>1.8</v>
+        <v>2.63</v>
       </c>
       <c r="R53">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="S53">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="T53">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="U53">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="V53">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="W53">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X53">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y53">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z53">
-        <v>3.58</v>
+        <v>3.84</v>
       </c>
       <c r="AA53">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AB53">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="AC53">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="AD53">
         <v>1.35</v>
       </c>
       <c r="AE53">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF53">
+        <v>1.62</v>
+      </c>
+      <c r="AG53">
         <v>2.2</v>
       </c>
-      <c r="AG53">
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ53">
+        <v>1.25</v>
+      </c>
+      <c r="AK53">
         <v>1.62</v>
       </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ53">
-        <v>1.06</v>
-      </c>
-      <c r="AK53">
-        <v>3</v>
-      </c>
       <c r="AL53">
         <v>0</v>
       </c>
@@ -9052,7 +9052,7 @@
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>2026-08-07 15:15:00</t>
+          <t>2026-08-07 15:30:00</t>
         </is>
       </c>
     </row>
@@ -9069,7 +9069,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="O54">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="P54">
-        <v>3.09</v>
+        <v>2.93</v>
       </c>
       <c r="Q54">
-        <v>2.63</v>
+        <v>2.95</v>
       </c>
       <c r="R54">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="S54">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="T54">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="U54">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="V54">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="W54">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X54">
         <v>1.02</v>
       </c>
       <c r="Y54">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="Z54">
-        <v>3.84</v>
+        <v>3.2</v>
       </c>
       <c r="AA54">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AB54">
-        <v>1.99</v>
+        <v>1.8</v>
       </c>
       <c r="AC54">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="AD54">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AE54">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF54">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AG54">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK54">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9232,7 +9232,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Wacker Innsbruck</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,65 +9274,65 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.14</v>
+        <v>1.63</v>
       </c>
       <c r="O55">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="P55">
-        <v>2.8</v>
+        <v>4.7</v>
       </c>
       <c r="Q55">
-        <v>2.75</v>
+        <v>2</v>
       </c>
       <c r="R55">
+        <v>2.55</v>
+      </c>
+      <c r="S55">
+        <v>1.27</v>
+      </c>
+      <c r="T55">
+        <v>3.5</v>
+      </c>
+      <c r="U55">
+        <v>2.38</v>
+      </c>
+      <c r="V55">
+        <v>1.57</v>
+      </c>
+      <c r="W55">
+        <v>1.14</v>
+      </c>
+      <c r="X55">
+        <v>1.03</v>
+      </c>
+      <c r="Y55">
+        <v>1.19</v>
+      </c>
+      <c r="Z55">
+        <v>4.63</v>
+      </c>
+      <c r="AA55">
+        <v>1.6</v>
+      </c>
+      <c r="AB55">
+        <v>2.3</v>
+      </c>
+      <c r="AC55">
+        <v>2.35</v>
+      </c>
+      <c r="AD55">
+        <v>1.5</v>
+      </c>
+      <c r="AE55">
+        <v>1.18</v>
+      </c>
+      <c r="AF55">
+        <v>1.62</v>
+      </c>
+      <c r="AG55">
         <v>2.15</v>
       </c>
-      <c r="S55">
-        <v>1.39</v>
-      </c>
-      <c r="T55">
-        <v>2.8</v>
-      </c>
-      <c r="U55">
-        <v>2.75</v>
-      </c>
-      <c r="V55">
-        <v>1.36</v>
-      </c>
-      <c r="W55">
-        <v>1.04</v>
-      </c>
-      <c r="X55">
-        <v>1.02</v>
-      </c>
-      <c r="Y55">
-        <v>1.3</v>
-      </c>
-      <c r="Z55">
-        <v>3.3</v>
-      </c>
-      <c r="AA55">
-        <v>2</v>
-      </c>
-      <c r="AB55">
-        <v>1.8</v>
-      </c>
-      <c r="AC55">
-        <v>3.4</v>
-      </c>
-      <c r="AD55">
-        <v>1.29</v>
-      </c>
-      <c r="AE55">
-        <v>1.08</v>
-      </c>
-      <c r="AF55">
-        <v>1.71</v>
-      </c>
-      <c r="AG55">
-        <v>2</v>
-      </c>
       <c r="AH55" t="inlineStr">
         <is>
           <t>[]</t>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK55">
-        <v>1.46</v>
+        <v>2.25</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9395,7 +9395,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Wacker Innsbruck</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="O56">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="P56">
-        <v>4.7</v>
+        <v>4.16</v>
       </c>
       <c r="Q56">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="R56">
-        <v>2.55</v>
+        <v>2.28</v>
       </c>
       <c r="S56">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="T56">
-        <v>3.5</v>
+        <v>2.69</v>
       </c>
       <c r="U56">
-        <v>2.38</v>
+        <v>2.73</v>
       </c>
       <c r="V56">
-        <v>1.57</v>
+        <v>1.41</v>
       </c>
       <c r="W56">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="X56">
         <v>1.03</v>
       </c>
       <c r="Y56">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="Z56">
-        <v>4.63</v>
+        <v>3.5</v>
       </c>
       <c r="AA56">
-        <v>1.6</v>
+        <v>1.94</v>
       </c>
       <c r="AB56">
-        <v>2.3</v>
+        <v>1.93</v>
       </c>
       <c r="AC56">
-        <v>2.35</v>
+        <v>3.25</v>
       </c>
       <c r="AD56">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AE56">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AF56">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="AG56">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK56">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="O57">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="P57">
-        <v>4.16</v>
+        <v>2.75</v>
       </c>
       <c r="Q57">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="R57">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="S57">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="T57">
-        <v>2.69</v>
+        <v>3.04</v>
       </c>
       <c r="U57">
-        <v>2.73</v>
+        <v>2.54</v>
       </c>
       <c r="V57">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="W57">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X57">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y57">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z57">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="AA57">
-        <v>1.94</v>
+        <v>1.7</v>
       </c>
       <c r="AB57">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AC57">
-        <v>3.25</v>
+        <v>2.63</v>
       </c>
       <c r="AD57">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AE57">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AF57">
-        <v>1.74</v>
+        <v>1.55</v>
       </c>
       <c r="AG57">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AK57">
-        <v>1.91</v>
+        <v>1.59</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9721,7 +9721,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.2</v>
+        <v>5</v>
       </c>
       <c r="O58">
-        <v>3.42</v>
+        <v>4</v>
       </c>
       <c r="P58">
-        <v>2.75</v>
+        <v>1.5</v>
       </c>
       <c r="Q58">
-        <v>2.5</v>
+        <v>4.94</v>
       </c>
       <c r="R58">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="S58">
         <v>1.29</v>
       </c>
       <c r="T58">
-        <v>3.04</v>
+        <v>3.12</v>
       </c>
       <c r="U58">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="V58">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="W58">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X58">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y58">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z58">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AA58">
         <v>1.7</v>
       </c>
       <c r="AB58">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AC58">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="AD58">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE58">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AF58">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="AG58">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.23</v>
+        <v>2.44</v>
       </c>
       <c r="AK58">
-        <v>1.59</v>
+        <v>1.1</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9879,12 +9879,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>5</v>
+        <v>1.51</v>
       </c>
       <c r="O59">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="P59">
-        <v>1.5</v>
+        <v>4.7</v>
       </c>
       <c r="Q59">
-        <v>4.94</v>
+        <v>1.91</v>
       </c>
       <c r="R59">
-        <v>2.23</v>
+        <v>2.64</v>
       </c>
       <c r="S59">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="T59">
-        <v>3.12</v>
+        <v>3.75</v>
       </c>
       <c r="U59">
-        <v>2.44</v>
+        <v>2.17</v>
       </c>
       <c r="V59">
-        <v>1.46</v>
+        <v>1.61</v>
       </c>
       <c r="W59">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X59">
         <v>1.02</v>
       </c>
       <c r="Y59">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="Z59">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="AA59">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AB59">
-        <v>2.13</v>
+        <v>2.5</v>
       </c>
       <c r="AC59">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="AD59">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AE59">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AF59">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AG59">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>2.44</v>
+        <v>1.12</v>
       </c>
       <c r="AK59">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10030,7 +10030,7 @@
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>2026-08-07 15:30:00</t>
+          <t>2026-08-07 15:45:00</t>
         </is>
       </c>
     </row>
@@ -10047,22 +10047,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.51</v>
+        <v>1.98</v>
       </c>
       <c r="O60">
-        <v>4.05</v>
+        <v>3.45</v>
       </c>
       <c r="P60">
-        <v>4.7</v>
+        <v>3.2</v>
       </c>
       <c r="Q60">
-        <v>1.91</v>
+        <v>2.4</v>
       </c>
       <c r="R60">
-        <v>2.64</v>
+        <v>2.36</v>
       </c>
       <c r="S60">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="T60">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="U60">
-        <v>2.17</v>
+        <v>2.43</v>
       </c>
       <c r="V60">
-        <v>1.61</v>
+        <v>1.45</v>
       </c>
       <c r="W60">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="X60">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y60">
+        <v>1.25</v>
+      </c>
+      <c r="Z60">
+        <v>3.8</v>
+      </c>
+      <c r="AA60">
+        <v>1.8</v>
+      </c>
+      <c r="AB60">
+        <v>2</v>
+      </c>
+      <c r="AC60">
+        <v>2.68</v>
+      </c>
+      <c r="AD60">
+        <v>1.37</v>
+      </c>
+      <c r="AE60">
         <v>1.12</v>
       </c>
-      <c r="Z60">
-        <v>4.8</v>
-      </c>
-      <c r="AA60">
-        <v>1.5</v>
-      </c>
-      <c r="AB60">
-        <v>2.5</v>
-      </c>
-      <c r="AC60">
-        <v>2.3</v>
-      </c>
-      <c r="AD60">
-        <v>1.57</v>
-      </c>
-      <c r="AE60">
-        <v>1.22</v>
-      </c>
       <c r="AF60">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG60">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="AK60">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.98</v>
+        <v>1.4</v>
       </c>
       <c r="O61">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="P61">
-        <v>3.2</v>
+        <v>6.52</v>
       </c>
       <c r="Q61">
+        <v>1.83</v>
+      </c>
+      <c r="R61">
         <v>2.4</v>
       </c>
-      <c r="R61">
-        <v>2.36</v>
-      </c>
       <c r="S61">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T61">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U61">
-        <v>2.43</v>
+        <v>2.58</v>
       </c>
       <c r="V61">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="W61">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X61">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y61">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z61">
-        <v>3.8</v>
+        <v>3.84</v>
       </c>
       <c r="AA61">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AB61">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC61">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="AD61">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AE61">
         <v>1.12</v>
       </c>
       <c r="AF61">
-        <v>1.62</v>
+        <v>1.92</v>
       </c>
       <c r="AG61">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="AK61">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10373,22 +10373,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.4</v>
+        <v>2.05</v>
       </c>
       <c r="O62">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="P62">
-        <v>6.52</v>
+        <v>3.1</v>
       </c>
       <c r="Q62">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="R62">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S62">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T62">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U62">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="V62">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W62">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X62">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y62">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z62">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="AA62">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AB62">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AC62">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD62">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE62">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF62">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG62">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK62">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.05</v>
+        <v>1.72</v>
       </c>
       <c r="O63">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="P63">
-        <v>3.1</v>
+        <v>4.47</v>
       </c>
       <c r="Q63">
         <v>0</v>
@@ -10617,10 +10617,10 @@
         <v>0</v>
       </c>
       <c r="AA63">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB63">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC63">
         <v>0</v>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.72</v>
+        <v>2.33</v>
       </c>
       <c r="O64">
-        <v>3.55</v>
+        <v>3.05</v>
       </c>
       <c r="P64">
-        <v>4.47</v>
+        <v>2.91</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>La Roche VF</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,13 +10904,13 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="O65">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P65">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="Q65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>La Roche VF</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O66">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P66">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="N67">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O67">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="P67">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,13 +11393,13 @@
         </is>
       </c>
       <c r="N68">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O68">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P68">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="Q68">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="O69">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P69">
-        <v>3.59</v>
+        <v>2.48</v>
       </c>
       <c r="Q69">
         <v>0</v>
@@ -11595,10 +11595,10 @@
         <v>0</v>
       </c>
       <c r="AA69">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB69">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC69">
         <v>0</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O70">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P70">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q70">
         <v>0</v>
@@ -11758,10 +11758,10 @@
         <v>0</v>
       </c>
       <c r="AA70">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB70">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC70">
         <v>0</v>
@@ -11840,22 +11840,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O71">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P71">
-        <v>0</v>
+        <v>6.17</v>
       </c>
       <c r="Q71">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R71">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S71">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T71">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="U71">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="V71">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W71">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X71">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y71">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z71">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA71">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB71">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC71">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD71">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE71">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF71">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG71">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK71">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,64 +12045,64 @@
         </is>
       </c>
       <c r="N72">
+        <v>2.05</v>
+      </c>
+      <c r="O72">
+        <v>3.4</v>
+      </c>
+      <c r="P72">
+        <v>3</v>
+      </c>
+      <c r="Q72">
+        <v>2.63</v>
+      </c>
+      <c r="R72">
+        <v>2.25</v>
+      </c>
+      <c r="S72">
+        <v>1.34</v>
+      </c>
+      <c r="T72">
+        <v>3.21</v>
+      </c>
+      <c r="U72">
+        <v>2.59</v>
+      </c>
+      <c r="V72">
         <v>1.41</v>
       </c>
-      <c r="O72">
-        <v>4.5</v>
-      </c>
-      <c r="P72">
-        <v>6.17</v>
-      </c>
-      <c r="Q72">
-        <v>1.67</v>
-      </c>
-      <c r="R72">
-        <v>2.63</v>
-      </c>
-      <c r="S72">
-        <v>1.2</v>
-      </c>
-      <c r="T72">
-        <v>3.72</v>
-      </c>
-      <c r="U72">
-        <v>2.11</v>
-      </c>
-      <c r="V72">
-        <v>1.64</v>
-      </c>
       <c r="W72">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X72">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y72">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="Z72">
-        <v>5.25</v>
+        <v>3.74</v>
       </c>
       <c r="AA72">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="AB72">
-        <v>2.6</v>
+        <v>2.02</v>
       </c>
       <c r="AC72">
-        <v>1.87</v>
+        <v>3</v>
       </c>
       <c r="AD72">
+        <v>1.33</v>
+      </c>
+      <c r="AE72">
+        <v>1.13</v>
+      </c>
+      <c r="AF72">
         <v>1.65</v>
       </c>
-      <c r="AE72">
-        <v>1.25</v>
-      </c>
-      <c r="AF72">
-        <v>1.77</v>
-      </c>
       <c r="AG72">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.13</v>
+        <v>1.29</v>
       </c>
       <c r="AK72">
-        <v>3.5</v>
+        <v>1.57</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="O73">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P73">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Q73">
-        <v>2.63</v>
+        <v>2.53</v>
       </c>
       <c r="R73">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S73">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T73">
-        <v>3.21</v>
+        <v>2.5</v>
       </c>
       <c r="U73">
-        <v>2.59</v>
+        <v>2.45</v>
       </c>
       <c r="V73">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W73">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X73">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y73">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z73">
-        <v>3.74</v>
+        <v>3.9</v>
       </c>
       <c r="AA73">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AB73">
-        <v>2.02</v>
+        <v>2.09</v>
       </c>
       <c r="AC73">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="AD73">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AE73">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF73">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AG73">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK73">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.98</v>
+        <v>1.4</v>
       </c>
       <c r="O74">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="P74">
-        <v>3.1</v>
+        <v>6</v>
       </c>
       <c r="Q74">
-        <v>2.53</v>
+        <v>1.82</v>
       </c>
       <c r="R74">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S74">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T74">
-        <v>2.5</v>
+        <v>3.02</v>
       </c>
       <c r="U74">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="V74">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="W74">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X74">
         <v>1.03</v>
       </c>
       <c r="Y74">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="Z74">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="AA74">
-        <v>1.74</v>
+        <v>1.59</v>
       </c>
       <c r="AB74">
-        <v>2.09</v>
+        <v>2.21</v>
       </c>
       <c r="AC74">
-        <v>2.83</v>
+        <v>2.5</v>
       </c>
       <c r="AD74">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="AE74">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF74">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AG74">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK74">
-        <v>1.73</v>
+        <v>2.8</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12655,22 +12655,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="O76">
-        <v>4.4</v>
+        <v>6.25</v>
       </c>
       <c r="P76">
-        <v>6</v>
+        <v>9.1</v>
       </c>
       <c r="Q76">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="R76">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S76">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T76">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="U76">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="V76">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W76">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X76">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y76">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z76">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA76">
-        <v>1.59</v>
+        <v>1.44</v>
       </c>
       <c r="AB76">
-        <v>2.21</v>
+        <v>2.7</v>
       </c>
       <c r="AC76">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD76">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AE76">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF76">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG76">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK76">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12813,27 +12813,27 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.24</v>
+        <v>1.62</v>
       </c>
       <c r="O77">
-        <v>6.25</v>
+        <v>3.92</v>
       </c>
       <c r="P77">
-        <v>9.1</v>
+        <v>4.2</v>
       </c>
       <c r="Q77">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R77">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S77">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T77">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U77">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="V77">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W77">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X77">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y77">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z77">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AA77">
-        <v>1.44</v>
+        <v>1.72</v>
       </c>
       <c r="AB77">
-        <v>2.7</v>
+        <v>2.07</v>
       </c>
       <c r="AC77">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AD77">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE77">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF77">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG77">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK77">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -12964,7 +12964,7 @@
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>2026-08-07 15:45:00</t>
+          <t>2026-08-07 16:00:00</t>
         </is>
       </c>
     </row>
@@ -12981,22 +12981,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="O78">
-        <v>3.92</v>
+        <v>3.4</v>
       </c>
       <c r="P78">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="Q78">
-        <v>2.1</v>
+        <v>2.41</v>
       </c>
       <c r="R78">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="S78">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="T78">
-        <v>3.04</v>
+        <v>2.41</v>
       </c>
       <c r="U78">
-        <v>2.43</v>
+        <v>3.08</v>
       </c>
       <c r="V78">
-        <v>1.46</v>
+        <v>1.29</v>
       </c>
       <c r="W78">
+        <v>1.05</v>
+      </c>
+      <c r="X78">
         <v>1.06</v>
       </c>
-      <c r="X78">
-        <v>1.02</v>
-      </c>
       <c r="Y78">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="Z78">
-        <v>3.94</v>
+        <v>2.92</v>
       </c>
       <c r="AA78">
-        <v>1.72</v>
+        <v>2.21</v>
       </c>
       <c r="AB78">
-        <v>2.07</v>
+        <v>1.65</v>
       </c>
       <c r="AC78">
-        <v>2.87</v>
+        <v>3.78</v>
       </c>
       <c r="AD78">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AE78">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF78">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AG78">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AK78">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13139,12 +13139,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,65 +13186,65 @@
         </is>
       </c>
       <c r="N79">
-        <v>1.72</v>
+        <v>3</v>
       </c>
       <c r="O79">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P79">
-        <v>4.4</v>
+        <v>2.3</v>
       </c>
       <c r="Q79">
-        <v>2.41</v>
+        <v>3.73</v>
       </c>
       <c r="R79">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="S79">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="T79">
-        <v>2.41</v>
+        <v>2.75</v>
       </c>
       <c r="U79">
-        <v>3.08</v>
+        <v>2.75</v>
       </c>
       <c r="V79">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="W79">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X79">
         <v>1.06</v>
       </c>
       <c r="Y79">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="Z79">
-        <v>2.92</v>
+        <v>3.3</v>
       </c>
       <c r="AA79">
-        <v>2.21</v>
+        <v>1.93</v>
       </c>
       <c r="AB79">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AC79">
-        <v>3.78</v>
+        <v>3.25</v>
       </c>
       <c r="AD79">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="AE79">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF79">
+        <v>1.71</v>
+      </c>
+      <c r="AG79">
         <v>2</v>
       </c>
-      <c r="AG79">
-        <v>1.73</v>
-      </c>
       <c r="AH79" t="inlineStr">
         <is>
           <t>[]</t>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AK79">
-        <v>1.91</v>
+        <v>1.36</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13290,7 +13290,7 @@
       </c>
       <c r="AU79" t="inlineStr">
         <is>
-          <t>2026-08-07 16:00:00</t>
+          <t>2026-08-07 16:15:00</t>
         </is>
       </c>
     </row>
@@ -13302,27 +13302,27 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
-        <v>3.07</v>
+        <v>1.7</v>
       </c>
       <c r="O80">
-        <v>3.08</v>
+        <v>4</v>
       </c>
       <c r="P80">
-        <v>2.3</v>
+        <v>3.9</v>
       </c>
       <c r="Q80">
-        <v>3.79</v>
+        <v>2.08</v>
       </c>
       <c r="R80">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="S80">
-        <v>1.37</v>
+        <v>1.21</v>
       </c>
       <c r="T80">
-        <v>2.65</v>
+        <v>3.9</v>
       </c>
       <c r="U80">
-        <v>2.75</v>
+        <v>2.04</v>
       </c>
       <c r="V80">
+        <v>1.7</v>
+      </c>
+      <c r="W80">
+        <v>1.2</v>
+      </c>
+      <c r="X80">
+        <v>1.01</v>
+      </c>
+      <c r="Y80">
+        <v>1.1</v>
+      </c>
+      <c r="Z80">
+        <v>6.5</v>
+      </c>
+      <c r="AA80">
         <v>1.36</v>
       </c>
-      <c r="W80">
-        <v>1.06</v>
-      </c>
-      <c r="X80">
-        <v>1.06</v>
-      </c>
-      <c r="Y80">
-        <v>1.3</v>
-      </c>
-      <c r="Z80">
-        <v>3.3</v>
-      </c>
-      <c r="AA80">
-        <v>1.93</v>
-      </c>
       <c r="AB80">
-        <v>1.9</v>
+        <v>3.4</v>
       </c>
       <c r="AC80">
-        <v>3.3</v>
+        <v>1.98</v>
       </c>
       <c r="AD80">
-        <v>1.33</v>
+        <v>1.8</v>
       </c>
       <c r="AE80">
-        <v>1.06</v>
+        <v>1.28</v>
       </c>
       <c r="AF80">
-        <v>1.71</v>
+        <v>1.44</v>
       </c>
       <c r="AG80">
-        <v>2.02</v>
+        <v>2.56</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AK80">
-        <v>1.36</v>
+        <v>2.2</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13453,7 +13453,7 @@
       </c>
       <c r="AU80" t="inlineStr">
         <is>
-          <t>2026-08-07 16:15:00</t>
+          <t>2026-08-07 18:15:00</t>
         </is>
       </c>
     </row>
@@ -13465,12 +13465,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="O81">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="P81">
-        <v>3.9</v>
+        <v>2.6</v>
       </c>
       <c r="Q81">
-        <v>2.08</v>
+        <v>2.8</v>
       </c>
       <c r="R81">
+        <v>2.25</v>
+      </c>
+      <c r="S81">
+        <v>1.3</v>
+      </c>
+      <c r="T81">
+        <v>3.08</v>
+      </c>
+      <c r="U81">
+        <v>2.42</v>
+      </c>
+      <c r="V81">
+        <v>1.52</v>
+      </c>
+      <c r="W81">
+        <v>1.11</v>
+      </c>
+      <c r="X81">
+        <v>1.03</v>
+      </c>
+      <c r="Y81">
+        <v>1.16</v>
+      </c>
+      <c r="Z81">
+        <v>4.05</v>
+      </c>
+      <c r="AA81">
+        <v>1.67</v>
+      </c>
+      <c r="AB81">
+        <v>2.15</v>
+      </c>
+      <c r="AC81">
         <v>2.6</v>
       </c>
-      <c r="S81">
-        <v>1.21</v>
-      </c>
-      <c r="T81">
-        <v>3.9</v>
-      </c>
-      <c r="U81">
-        <v>2.04</v>
-      </c>
-      <c r="V81">
-        <v>1.7</v>
-      </c>
-      <c r="W81">
-        <v>1.2</v>
-      </c>
-      <c r="X81">
-        <v>1.01</v>
-      </c>
-      <c r="Y81">
-        <v>1.1</v>
-      </c>
-      <c r="Z81">
-        <v>6.5</v>
-      </c>
-      <c r="AA81">
-        <v>1.36</v>
-      </c>
-      <c r="AB81">
-        <v>3.4</v>
-      </c>
-      <c r="AC81">
-        <v>1.98</v>
-      </c>
       <c r="AD81">
-        <v>1.8</v>
+        <v>1.41</v>
       </c>
       <c r="AE81">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="AF81">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AG81">
-        <v>2.56</v>
+        <v>2.28</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AK81">
-        <v>2.2</v>
+        <v>1.53</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13616,7 +13616,7 @@
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>2026-08-07 18:15:00</t>
+          <t>2026-08-07 19:00:00</t>
         </is>
       </c>
     </row>
@@ -13628,12 +13628,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="O82">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P82">
+        <v>4.05</v>
+      </c>
+      <c r="Q82">
         <v>2.6</v>
       </c>
-      <c r="Q82">
-        <v>2.8</v>
-      </c>
       <c r="R82">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="S82">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="T82">
-        <v>3.08</v>
+        <v>2.75</v>
       </c>
       <c r="U82">
-        <v>2.42</v>
+        <v>2.95</v>
       </c>
       <c r="V82">
-        <v>1.52</v>
+        <v>1.34</v>
       </c>
       <c r="W82">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X82">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y82">
-        <v>1.16</v>
+        <v>1.36</v>
       </c>
       <c r="Z82">
-        <v>4.05</v>
+        <v>3.1</v>
       </c>
       <c r="AA82">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="AB82">
-        <v>2.15</v>
+        <v>1.69</v>
       </c>
       <c r="AC82">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="AD82">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="AE82">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF82">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AG82">
-        <v>2.28</v>
+        <v>1.85</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AK82">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13779,7 +13779,7 @@
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>2026-08-07 19:00:00</t>
+          <t>2026-08-07 19:30:00</t>
         </is>
       </c>
     </row>
@@ -13791,12 +13791,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="O83">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="P83">
-        <v>4.05</v>
+        <v>4.4</v>
       </c>
       <c r="Q83">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="R83">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="S83">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="T83">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="U83">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="V83">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="W83">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X83">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="Y83">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="Z83">
-        <v>3.1</v>
+        <v>2.45</v>
       </c>
       <c r="AA83">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="AB83">
-        <v>1.69</v>
+        <v>1.53</v>
       </c>
       <c r="AC83">
-        <v>3.7</v>
+        <v>4.85</v>
       </c>
       <c r="AD83">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AE83">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AF83">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AG83">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AK83">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13942,7 +13942,7 @@
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>2026-08-07 19:30:00</t>
+          <t>2026-08-07 20:00:00</t>
         </is>
       </c>
     </row>
@@ -13959,7 +13959,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,80 +14001,80 @@
         </is>
       </c>
       <c r="N84">
-        <v>1.87</v>
+        <v>1.61</v>
       </c>
       <c r="O84">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="P84">
-        <v>3.65</v>
+        <v>4.9</v>
       </c>
       <c r="Q84">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="R84">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="S84">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="T84">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="U84">
+        <v>2.45</v>
+      </c>
+      <c r="V84">
+        <v>1.44</v>
+      </c>
+      <c r="W84">
+        <v>1.07</v>
+      </c>
+      <c r="X84">
+        <v>1.04</v>
+      </c>
+      <c r="Y84">
+        <v>1.22</v>
+      </c>
+      <c r="Z84">
         <v>3.5</v>
       </c>
-      <c r="V84">
-        <v>1.22</v>
-      </c>
-      <c r="W84">
-        <v>1.04</v>
-      </c>
-      <c r="X84">
+      <c r="AA84">
+        <v>1.8</v>
+      </c>
+      <c r="AB84">
+        <v>1.95</v>
+      </c>
+      <c r="AC84">
+        <v>2.9</v>
+      </c>
+      <c r="AD84">
+        <v>1.33</v>
+      </c>
+      <c r="AE84">
         <v>1.13</v>
       </c>
-      <c r="Y84">
-        <v>1.47</v>
-      </c>
-      <c r="Z84">
-        <v>2.5</v>
-      </c>
-      <c r="AA84">
-        <v>2.5</v>
-      </c>
-      <c r="AB84">
-        <v>1.44</v>
-      </c>
-      <c r="AC84">
-        <v>4.85</v>
-      </c>
-      <c r="AD84">
-        <v>1.16</v>
-      </c>
-      <c r="AE84">
-        <v>1</v>
-      </c>
       <c r="AF84">
+        <v>1.75</v>
+      </c>
+      <c r="AG84">
+        <v>1.95</v>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI84" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ84">
+        <v>1.25</v>
+      </c>
+      <c r="AK84">
         <v>2.15</v>
-      </c>
-      <c r="AG84">
-        <v>1.66</v>
-      </c>
-      <c r="AH84" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI84" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ84">
-        <v>1.28</v>
-      </c>
-      <c r="AK84">
-        <v>1.79</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14122,7 +14122,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="O85">
+        <v>3.67</v>
+      </c>
+      <c r="P85">
+        <v>3.62</v>
+      </c>
+      <c r="Q85">
+        <v>2.12</v>
+      </c>
+      <c r="R85">
+        <v>2.2</v>
+      </c>
+      <c r="S85">
+        <v>1.25</v>
+      </c>
+      <c r="T85">
+        <v>3.6</v>
+      </c>
+      <c r="U85">
+        <v>2.15</v>
+      </c>
+      <c r="V85">
+        <v>1.6</v>
+      </c>
+      <c r="W85">
+        <v>1.14</v>
+      </c>
+      <c r="X85">
+        <v>1.03</v>
+      </c>
+      <c r="Y85">
+        <v>1.1</v>
+      </c>
+      <c r="Z85">
         <v>3.4</v>
       </c>
-      <c r="P85">
-        <v>4.9</v>
-      </c>
-      <c r="Q85">
-        <v>2.14</v>
-      </c>
-      <c r="R85">
-        <v>2.25</v>
-      </c>
-      <c r="S85">
-        <v>1.3</v>
-      </c>
-      <c r="T85">
-        <v>3.1</v>
-      </c>
-      <c r="U85">
-        <v>2.45</v>
-      </c>
-      <c r="V85">
-        <v>1.44</v>
-      </c>
-      <c r="W85">
-        <v>1.07</v>
-      </c>
-      <c r="X85">
-        <v>1.04</v>
-      </c>
-      <c r="Y85">
+      <c r="AA85">
+        <v>1.49</v>
+      </c>
+      <c r="AB85">
+        <v>2.35</v>
+      </c>
+      <c r="AC85">
+        <v>1.96</v>
+      </c>
+      <c r="AD85">
+        <v>1.53</v>
+      </c>
+      <c r="AE85">
         <v>1.22</v>
       </c>
-      <c r="Z85">
-        <v>3.5</v>
-      </c>
-      <c r="AA85">
-        <v>1.8</v>
-      </c>
-      <c r="AB85">
-        <v>1.95</v>
-      </c>
-      <c r="AC85">
-        <v>2.9</v>
-      </c>
-      <c r="AD85">
-        <v>1.33</v>
-      </c>
-      <c r="AE85">
-        <v>1.13</v>
-      </c>
       <c r="AF85">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AG85">
-        <v>1.95</v>
+        <v>2.38</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AK85">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14280,12 +14280,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,64 +14327,64 @@
         </is>
       </c>
       <c r="N86">
-        <v>1.58</v>
+        <v>1.83</v>
       </c>
       <c r="O86">
-        <v>3.67</v>
+        <v>3.7</v>
       </c>
       <c r="P86">
-        <v>3.62</v>
+        <v>3.3</v>
       </c>
       <c r="Q86">
-        <v>2.12</v>
+        <v>2.36</v>
       </c>
       <c r="R86">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="S86">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="T86">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="U86">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="V86">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="W86">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="X86">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y86">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Z86">
-        <v>3.4</v>
+        <v>6.05</v>
       </c>
       <c r="AA86">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="AB86">
-        <v>2.35</v>
+        <v>3.1</v>
       </c>
       <c r="AC86">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="AD86">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="AE86">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AF86">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="AG86">
-        <v>2.38</v>
+        <v>2.8</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AK86">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14431,7 +14431,7 @@
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>2026-08-07 20:00:00</t>
+          <t>2026-08-07 20:30:00</t>
         </is>
       </c>
     </row>
@@ -14448,7 +14448,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,64 +14490,64 @@
         </is>
       </c>
       <c r="N87">
-        <v>1.83</v>
+        <v>1.27</v>
       </c>
       <c r="O87">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="P87">
-        <v>3.3</v>
+        <v>10.2</v>
       </c>
       <c r="Q87">
-        <v>2.36</v>
+        <v>1.87</v>
       </c>
       <c r="R87">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="S87">
-        <v>1.18</v>
+        <v>1.37</v>
       </c>
       <c r="T87">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="U87">
-        <v>1.98</v>
+        <v>2.66</v>
       </c>
       <c r="V87">
-        <v>1.78</v>
+        <v>1.41</v>
       </c>
       <c r="W87">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="X87">
         <v>1.01</v>
       </c>
       <c r="Y87">
-        <v>1.06</v>
+        <v>1.28</v>
       </c>
       <c r="Z87">
-        <v>6.05</v>
+        <v>3.68</v>
       </c>
       <c r="AA87">
-        <v>1.36</v>
+        <v>1.88</v>
       </c>
       <c r="AB87">
-        <v>3.1</v>
+        <v>1.98</v>
       </c>
       <c r="AC87">
-        <v>1.93</v>
+        <v>2.92</v>
       </c>
       <c r="AD87">
-        <v>1.83</v>
+        <v>1.38</v>
       </c>
       <c r="AE87">
-        <v>1.31</v>
+        <v>1.08</v>
       </c>
       <c r="AF87">
-        <v>1.35</v>
+        <v>2.15</v>
       </c>
       <c r="AG87">
-        <v>2.8</v>
+        <v>1.63</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK87">
-        <v>1.76</v>
+        <v>2.9</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14606,27 +14606,27 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,64 +14653,64 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.27</v>
+        <v>3.87</v>
       </c>
       <c r="O88">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="P88">
-        <v>10.2</v>
+        <v>1.75</v>
       </c>
       <c r="Q88">
-        <v>1.87</v>
+        <v>3.75</v>
       </c>
       <c r="R88">
-        <v>2.48</v>
+        <v>2.1</v>
       </c>
       <c r="S88">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
       <c r="T88">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="U88">
-        <v>2.66</v>
+        <v>2.02</v>
       </c>
       <c r="V88">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W88">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X88">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y88">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="Z88">
-        <v>3.68</v>
+        <v>4</v>
       </c>
       <c r="AA88">
-        <v>1.88</v>
+        <v>1.7</v>
       </c>
       <c r="AB88">
-        <v>1.98</v>
+        <v>1.86</v>
       </c>
       <c r="AC88">
-        <v>2.92</v>
+        <v>2.75</v>
       </c>
       <c r="AD88">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AE88">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF88">
-        <v>2.15</v>
+        <v>1.45</v>
       </c>
       <c r="AG88">
-        <v>1.63</v>
+        <v>1.95</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="AK88">
-        <v>2.9</v>
+        <v>1.16</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14757,7 +14757,7 @@
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>2026-08-07 20:30:00</t>
+          <t>2026-08-07 21:00:00</t>
         </is>
       </c>
     </row>
@@ -14774,7 +14774,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>ETO</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>3.87</v>
+        <v>2.66</v>
       </c>
       <c r="O89">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="P89">
-        <v>1.75</v>
+        <v>2.37</v>
       </c>
       <c r="Q89">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R89">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S89">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T89">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U89">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="V89">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W89">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X89">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y89">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z89">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA89">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB89">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC89">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD89">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE89">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF89">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AG89">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK89">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>ETO</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.66</v>
+        <v>2.45</v>
       </c>
       <c r="O90">
-        <v>3.72</v>
+        <v>3.1</v>
       </c>
       <c r="P90">
-        <v>2.37</v>
+        <v>2.64</v>
       </c>
       <c r="Q90">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R90">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S90">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T90">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U90">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="V90">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W90">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X90">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y90">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z90">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA90">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB90">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC90">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD90">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE90">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF90">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG90">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK90">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15100,7 +15100,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.45</v>
+        <v>2.06</v>
       </c>
       <c r="O91">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P91">
-        <v>2.64</v>
+        <v>3.15</v>
       </c>
       <c r="Q91">
-        <v>3.32</v>
+        <v>2.5</v>
       </c>
       <c r="R91">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="S91">
         <v>1.4</v>
       </c>
       <c r="T91">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="U91">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="V91">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W91">
+        <v>1.05</v>
+      </c>
+      <c r="X91">
         <v>1.06</v>
       </c>
-      <c r="X91">
-        <v>1.02</v>
-      </c>
       <c r="Y91">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="Z91">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AA91">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AB91">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="AC91">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AD91">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AE91">
         <v>1.06</v>
       </c>
       <c r="AF91">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AG91">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AK91">
-        <v>1.48</v>
+        <v>1.59</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15263,22 +15263,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G92">
@@ -15301,68 +15301,68 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N92">
-        <v>2.06</v>
+        <v>2.8</v>
       </c>
       <c r="O92">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P92">
-        <v>3.15</v>
+        <v>2.3</v>
       </c>
       <c r="Q92">
+        <v>3.4</v>
+      </c>
+      <c r="R92">
+        <v>2.11</v>
+      </c>
+      <c r="S92">
+        <v>1.36</v>
+      </c>
+      <c r="T92">
+        <v>2.82</v>
+      </c>
+      <c r="U92">
         <v>2.5</v>
       </c>
-      <c r="R92">
-        <v>2</v>
-      </c>
-      <c r="S92">
-        <v>1.4</v>
-      </c>
-      <c r="T92">
-        <v>2.7</v>
-      </c>
-      <c r="U92">
-        <v>2.88</v>
-      </c>
       <c r="V92">
+        <v>1.44</v>
+      </c>
+      <c r="W92">
+        <v>1.08</v>
+      </c>
+      <c r="X92">
+        <v>1</v>
+      </c>
+      <c r="Y92">
+        <v>1.19</v>
+      </c>
+      <c r="Z92">
+        <v>3.9</v>
+      </c>
+      <c r="AA92">
+        <v>1.74</v>
+      </c>
+      <c r="AB92">
+        <v>1.99</v>
+      </c>
+      <c r="AC92">
+        <v>2.97</v>
+      </c>
+      <c r="AD92">
         <v>1.33</v>
       </c>
-      <c r="W92">
-        <v>1.05</v>
-      </c>
-      <c r="X92">
-        <v>1.06</v>
-      </c>
-      <c r="Y92">
-        <v>1.33</v>
-      </c>
-      <c r="Z92">
-        <v>3</v>
-      </c>
-      <c r="AA92">
-        <v>2.04</v>
-      </c>
-      <c r="AB92">
-        <v>1.68</v>
-      </c>
-      <c r="AC92">
-        <v>3.5</v>
-      </c>
-      <c r="AD92">
-        <v>1.17</v>
-      </c>
       <c r="AE92">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AF92">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AG92">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.26</v>
+        <v>1.57</v>
       </c>
       <c r="AK92">
-        <v>1.59</v>
+        <v>1.36</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15421,27 +15421,27 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G93">
@@ -15464,85 +15464,85 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N93">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="O93">
         <v>3.2</v>
       </c>
       <c r="P93">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="Q93">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="R93">
+        <v>1.98</v>
+      </c>
+      <c r="S93">
+        <v>1.4</v>
+      </c>
+      <c r="T93">
+        <v>2.8</v>
+      </c>
+      <c r="U93">
+        <v>2.9</v>
+      </c>
+      <c r="V93">
+        <v>1.36</v>
+      </c>
+      <c r="W93">
+        <v>1.07</v>
+      </c>
+      <c r="X93">
+        <v>1.06</v>
+      </c>
+      <c r="Y93">
+        <v>1.33</v>
+      </c>
+      <c r="Z93">
+        <v>3.1</v>
+      </c>
+      <c r="AA93">
         <v>2.11</v>
       </c>
-      <c r="S93">
-        <v>1.36</v>
-      </c>
-      <c r="T93">
-        <v>2.82</v>
-      </c>
-      <c r="U93">
-        <v>2.5</v>
-      </c>
-      <c r="V93">
+      <c r="AB93">
+        <v>1.69</v>
+      </c>
+      <c r="AC93">
+        <v>3.9</v>
+      </c>
+      <c r="AD93">
+        <v>1.25</v>
+      </c>
+      <c r="AE93">
+        <v>1.05</v>
+      </c>
+      <c r="AF93">
+        <v>1.8</v>
+      </c>
+      <c r="AG93">
+        <v>1.89</v>
+      </c>
+      <c r="AH93" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI93" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ93">
+        <v>1.33</v>
+      </c>
+      <c r="AK93">
         <v>1.44</v>
       </c>
-      <c r="W93">
-        <v>1.08</v>
-      </c>
-      <c r="X93">
-        <v>1</v>
-      </c>
-      <c r="Y93">
-        <v>1.19</v>
-      </c>
-      <c r="Z93">
-        <v>3.9</v>
-      </c>
-      <c r="AA93">
-        <v>1.74</v>
-      </c>
-      <c r="AB93">
-        <v>1.99</v>
-      </c>
-      <c r="AC93">
-        <v>2.97</v>
-      </c>
-      <c r="AD93">
-        <v>1.33</v>
-      </c>
-      <c r="AE93">
-        <v>1.13</v>
-      </c>
-      <c r="AF93">
-        <v>1.57</v>
-      </c>
-      <c r="AG93">
-        <v>2.2</v>
-      </c>
-      <c r="AH93" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI93" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ93">
-        <v>1.57</v>
-      </c>
-      <c r="AK93">
-        <v>1.36</v>
-      </c>
       <c r="AL93">
         <v>0</v>
       </c>
@@ -15572,7 +15572,7 @@
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>2026-08-07 21:00:00</t>
+          <t>2026-08-07 21:30:00</t>
         </is>
       </c>
     </row>
@@ -15589,7 +15589,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,64 +15631,64 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.45</v>
+        <v>1.3</v>
       </c>
       <c r="O94">
-        <v>3.2</v>
+        <v>5.2</v>
       </c>
       <c r="P94">
-        <v>2.5</v>
+        <v>7.1</v>
       </c>
       <c r="Q94">
-        <v>3.18</v>
+        <v>1.7</v>
       </c>
       <c r="R94">
-        <v>1.98</v>
+        <v>2.7</v>
       </c>
       <c r="S94">
-        <v>1.4</v>
+        <v>1.19</v>
       </c>
       <c r="T94">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="U94">
-        <v>2.9</v>
+        <v>2.11</v>
       </c>
       <c r="V94">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="W94">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="X94">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y94">
-        <v>1.33</v>
+        <v>1.12</v>
       </c>
       <c r="Z94">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="AA94">
-        <v>2.11</v>
+        <v>1.44</v>
       </c>
       <c r="AB94">
-        <v>1.69</v>
+        <v>2.7</v>
       </c>
       <c r="AC94">
-        <v>3.9</v>
+        <v>2.1</v>
       </c>
       <c r="AD94">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="AE94">
-        <v>1.05</v>
+        <v>1.3</v>
       </c>
       <c r="AF94">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AG94">
-        <v>1.89</v>
+        <v>2.05</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AK94">
-        <v>1.44</v>
+        <v>3.3</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15734,169 +15734,6 @@
         <v>0</v>
       </c>
       <c r="AU94" t="inlineStr">
-        <is>
-          <t>2026-08-07 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Chile Primera División</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>Universidad Católica</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Cobresal</t>
-        </is>
-      </c>
-      <c r="G95">
-        <v>0</v>
-      </c>
-      <c r="H95">
-        <v>0</v>
-      </c>
-      <c r="I95">
-        <v>0</v>
-      </c>
-      <c r="J95">
-        <v>0</v>
-      </c>
-      <c r="K95">
-        <v>0</v>
-      </c>
-      <c r="L95">
-        <v>0</v>
-      </c>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N95">
-        <v>1.3</v>
-      </c>
-      <c r="O95">
-        <v>5.2</v>
-      </c>
-      <c r="P95">
-        <v>7.1</v>
-      </c>
-      <c r="Q95">
-        <v>1.7</v>
-      </c>
-      <c r="R95">
-        <v>2.7</v>
-      </c>
-      <c r="S95">
-        <v>1.19</v>
-      </c>
-      <c r="T95">
-        <v>3.8</v>
-      </c>
-      <c r="U95">
-        <v>2.11</v>
-      </c>
-      <c r="V95">
-        <v>1.67</v>
-      </c>
-      <c r="W95">
-        <v>1.18</v>
-      </c>
-      <c r="X95">
-        <v>1.02</v>
-      </c>
-      <c r="Y95">
-        <v>1.12</v>
-      </c>
-      <c r="Z95">
-        <v>5</v>
-      </c>
-      <c r="AA95">
-        <v>1.44</v>
-      </c>
-      <c r="AB95">
-        <v>2.7</v>
-      </c>
-      <c r="AC95">
-        <v>2.1</v>
-      </c>
-      <c r="AD95">
-        <v>1.67</v>
-      </c>
-      <c r="AE95">
-        <v>1.3</v>
-      </c>
-      <c r="AF95">
-        <v>1.7</v>
-      </c>
-      <c r="AG95">
-        <v>2.05</v>
-      </c>
-      <c r="AH95" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI95" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ95">
-        <v>1.15</v>
-      </c>
-      <c r="AK95">
-        <v>3.3</v>
-      </c>
-      <c r="AL95">
-        <v>0</v>
-      </c>
-      <c r="AM95">
-        <v>-1</v>
-      </c>
-      <c r="AN95">
-        <v>-1</v>
-      </c>
-      <c r="AO95">
-        <v>-1</v>
-      </c>
-      <c r="AP95">
-        <v>-1</v>
-      </c>
-      <c r="AQ95">
-        <v>0</v>
-      </c>
-      <c r="AR95">
-        <v>0</v>
-      </c>
-      <c r="AS95">
-        <v>0</v>
-      </c>
-      <c r="AT95">
-        <v>0</v>
-      </c>
-      <c r="AU95" t="inlineStr">
         <is>
           <t>2026-08-07 21:30:00</t>
         </is>

--- a/jogos_2026-08-07.xlsx
+++ b/jogos_2026-08-07.xlsx
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.91</v>
+        <v>1.46</v>
       </c>
       <c r="O5">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="P5">
-        <v>2.2</v>
+        <v>4.4</v>
       </c>
       <c r="Q5">
-        <v>3.4</v>
+        <v>2.18</v>
       </c>
       <c r="R5">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="S5">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T5">
         <v>3.1</v>
       </c>
       <c r="U5">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="V5">
         <v>1.44</v>
       </c>
       <c r="W5">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X5">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="Z5">
-        <v>3.45</v>
+        <v>3.81</v>
       </c>
       <c r="AA5">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AB5">
-        <v>1.93</v>
+        <v>2.03</v>
       </c>
       <c r="AC5">
-        <v>2.87</v>
+        <v>3.07</v>
       </c>
       <c r="AD5">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AE5">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF5">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AG5">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK5">
-        <v>1.32</v>
+        <v>2.08</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.73</v>
+        <v>3.7</v>
       </c>
       <c r="O6">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P6">
-        <v>4.45</v>
+        <v>1.83</v>
       </c>
       <c r="Q6">
-        <v>2.44</v>
+        <v>4.33</v>
       </c>
       <c r="R6">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S6">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T6">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="U6">
-        <v>3.17</v>
+        <v>2.88</v>
       </c>
       <c r="V6">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="W6">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X6">
         <v>1.04</v>
       </c>
       <c r="Y6">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="Z6">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AA6">
-        <v>2.04</v>
+        <v>1.87</v>
       </c>
       <c r="AB6">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="AC6">
-        <v>3.86</v>
+        <v>3.29</v>
       </c>
       <c r="AD6">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AE6">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF6">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AG6">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AK6">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.7</v>
+        <v>2.91</v>
       </c>
       <c r="O7">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P7">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="Q7">
-        <v>4.33</v>
+        <v>3.4</v>
       </c>
       <c r="R7">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S7">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T7">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="U7">
-        <v>2.88</v>
+        <v>2.44</v>
       </c>
       <c r="V7">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W7">
         <v>1.08</v>
       </c>
       <c r="X7">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y7">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="Z7">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="AA7">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AB7">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AC7">
-        <v>3.29</v>
+        <v>2.87</v>
       </c>
       <c r="AD7">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AE7">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF7">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AG7">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK7">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.46</v>
+        <v>1.73</v>
       </c>
       <c r="O9">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="P9">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="Q9">
-        <v>2.18</v>
+        <v>2.44</v>
       </c>
       <c r="R9">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="S9">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="T9">
+        <v>2.75</v>
+      </c>
+      <c r="U9">
+        <v>3.17</v>
+      </c>
+      <c r="V9">
+        <v>1.33</v>
+      </c>
+      <c r="W9">
+        <v>1.03</v>
+      </c>
+      <c r="X9">
+        <v>1.04</v>
+      </c>
+      <c r="Y9">
+        <v>1.37</v>
+      </c>
+      <c r="Z9">
         <v>3.1</v>
       </c>
-      <c r="U9">
-        <v>2.56</v>
-      </c>
-      <c r="V9">
-        <v>1.44</v>
-      </c>
-      <c r="W9">
-        <v>1.07</v>
-      </c>
-      <c r="X9">
-        <v>1.02</v>
-      </c>
-      <c r="Y9">
-        <v>1.19</v>
-      </c>
-      <c r="Z9">
-        <v>3.81</v>
-      </c>
       <c r="AA9">
-        <v>1.81</v>
+        <v>2.04</v>
       </c>
       <c r="AB9">
-        <v>2.03</v>
+        <v>1.65</v>
       </c>
       <c r="AC9">
-        <v>3.07</v>
+        <v>3.86</v>
       </c>
       <c r="AD9">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AE9">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="AF9">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AG9">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AK9">
-        <v>2.08</v>
+        <v>1.9</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,80 +3895,80 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="O22">
-        <v>3.46</v>
+        <v>3.8</v>
       </c>
       <c r="P22">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="Q22">
-        <v>2.41</v>
+        <v>1.98</v>
       </c>
       <c r="R22">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="S22">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T22">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U22">
-        <v>2.47</v>
+        <v>2.75</v>
       </c>
       <c r="V22">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W22">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X22">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y22">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z22">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="AA22">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AB22">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AC22">
-        <v>2.7</v>
+        <v>3.13</v>
       </c>
       <c r="AD22">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AE22">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF22">
-        <v>1.59</v>
+        <v>1.85</v>
       </c>
       <c r="AG22">
+        <v>1.85</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22">
+        <v>1.07</v>
+      </c>
+      <c r="AK22">
         <v>2.17</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ22">
-        <v>1.19</v>
-      </c>
-      <c r="AK22">
-        <v>1.83</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,80 +4058,80 @@
         </is>
       </c>
       <c r="N23">
-        <v>4.2</v>
+        <v>1.59</v>
       </c>
       <c r="O23">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P23">
-        <v>1.7</v>
+        <v>4.79</v>
       </c>
       <c r="Q23">
-        <v>4.3</v>
+        <v>2.06</v>
       </c>
       <c r="R23">
-        <v>2.12</v>
+        <v>2.21</v>
       </c>
       <c r="S23">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T23">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="U23">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="V23">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W23">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X23">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y23">
+        <v>1.18</v>
+      </c>
+      <c r="Z23">
+        <v>4.33</v>
+      </c>
+      <c r="AA23">
+        <v>1.62</v>
+      </c>
+      <c r="AB23">
+        <v>2.15</v>
+      </c>
+      <c r="AC23">
+        <v>2.68</v>
+      </c>
+      <c r="AD23">
+        <v>1.44</v>
+      </c>
+      <c r="AE23">
+        <v>1.17</v>
+      </c>
+      <c r="AF23">
+        <v>1.67</v>
+      </c>
+      <c r="AG23">
+        <v>2.1</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23">
         <v>1.25</v>
       </c>
-      <c r="Z23">
-        <v>3.4</v>
-      </c>
-      <c r="AA23">
-        <v>1.85</v>
-      </c>
-      <c r="AB23">
-        <v>1.85</v>
-      </c>
-      <c r="AC23">
-        <v>3.2</v>
-      </c>
-      <c r="AD23">
-        <v>1.3</v>
-      </c>
-      <c r="AE23">
-        <v>1.11</v>
-      </c>
-      <c r="AF23">
-        <v>1.78</v>
-      </c>
-      <c r="AG23">
-        <v>1.89</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ23">
-        <v>1.22</v>
-      </c>
       <c r="AK23">
-        <v>1.15</v>
+        <v>2.2</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,52 +4221,52 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.57</v>
+        <v>4.2</v>
       </c>
       <c r="O24">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P24">
-        <v>4.9</v>
+        <v>1.7</v>
       </c>
       <c r="Q24">
-        <v>2.1</v>
+        <v>4.3</v>
       </c>
       <c r="R24">
-        <v>2.33</v>
+        <v>2.12</v>
       </c>
       <c r="S24">
         <v>1.33</v>
       </c>
       <c r="T24">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="U24">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="V24">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W24">
+        <v>1.04</v>
+      </c>
+      <c r="X24">
         <v>1.05</v>
       </c>
-      <c r="X24">
-        <v>1</v>
-      </c>
       <c r="Y24">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z24">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="AA24">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AB24">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AC24">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="AD24">
         <v>1.3</v>
@@ -4275,10 +4275,10 @@
         <v>1.11</v>
       </c>
       <c r="AF24">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AG24">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK24">
-        <v>2.2</v>
+        <v>1.15</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="O25">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="P25">
-        <v>4.79</v>
+        <v>4.9</v>
       </c>
       <c r="Q25">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="R25">
-        <v>2.21</v>
+        <v>2.33</v>
       </c>
       <c r="S25">
+        <v>1.33</v>
+      </c>
+      <c r="T25">
+        <v>2.86</v>
+      </c>
+      <c r="U25">
+        <v>2.63</v>
+      </c>
+      <c r="V25">
+        <v>1.44</v>
+      </c>
+      <c r="W25">
+        <v>1.05</v>
+      </c>
+      <c r="X25">
+        <v>1</v>
+      </c>
+      <c r="Y25">
+        <v>1.21</v>
+      </c>
+      <c r="Z25">
+        <v>3.58</v>
+      </c>
+      <c r="AA25">
+        <v>1.78</v>
+      </c>
+      <c r="AB25">
+        <v>1.91</v>
+      </c>
+      <c r="AC25">
+        <v>2.95</v>
+      </c>
+      <c r="AD25">
         <v>1.3</v>
       </c>
-      <c r="T25">
-        <v>3.04</v>
-      </c>
-      <c r="U25">
-        <v>2.4</v>
-      </c>
-      <c r="V25">
-        <v>1.45</v>
-      </c>
-      <c r="W25">
-        <v>1.07</v>
-      </c>
-      <c r="X25">
-        <v>1.03</v>
-      </c>
-      <c r="Y25">
-        <v>1.18</v>
-      </c>
-      <c r="Z25">
-        <v>4.33</v>
-      </c>
-      <c r="AA25">
-        <v>1.62</v>
-      </c>
-      <c r="AB25">
-        <v>2.15</v>
-      </c>
-      <c r="AC25">
-        <v>2.68</v>
-      </c>
-      <c r="AD25">
-        <v>1.44</v>
-      </c>
       <c r="AE25">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AF25">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AG25">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,7 +4454,7 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK25">
         <v>2.2</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="O26">
-        <v>3.8</v>
+        <v>3.46</v>
       </c>
       <c r="P26">
-        <v>5</v>
+        <v>3.75</v>
       </c>
       <c r="Q26">
-        <v>1.98</v>
+        <v>2.41</v>
       </c>
       <c r="R26">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="S26">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T26">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="U26">
-        <v>2.75</v>
+        <v>2.47</v>
       </c>
       <c r="V26">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W26">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X26">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y26">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z26">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="AA26">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AB26">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="AC26">
-        <v>3.13</v>
+        <v>2.7</v>
       </c>
       <c r="AD26">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AE26">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF26">
-        <v>1.85</v>
+        <v>1.59</v>
       </c>
       <c r="AG26">
-        <v>1.85</v>
+        <v>2.17</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AK26">
-        <v>2.17</v>
+        <v>1.83</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.43</v>
+        <v>2.4</v>
       </c>
       <c r="O50">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="P50">
-        <v>5.5</v>
+        <v>2.44</v>
       </c>
       <c r="Q50">
-        <v>1.85</v>
+        <v>2.8</v>
       </c>
       <c r="R50">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="S50">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T50">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="U50">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="V50">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="W50">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X50">
         <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z50">
         <v>5.5</v>
       </c>
       <c r="AA50">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AB50">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="AC50">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="AD50">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AE50">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AF50">
-        <v>1.57</v>
+        <v>1.41</v>
       </c>
       <c r="AG50">
-        <v>2.3</v>
+        <v>2.66</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK50">
-        <v>2.7</v>
+        <v>1.42</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.4</v>
+        <v>1.43</v>
       </c>
       <c r="O51">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="P51">
-        <v>2.44</v>
+        <v>5.5</v>
       </c>
       <c r="Q51">
-        <v>2.8</v>
+        <v>1.85</v>
       </c>
       <c r="R51">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="S51">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T51">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="U51">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="V51">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="W51">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X51">
         <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z51">
         <v>5.5</v>
       </c>
       <c r="AA51">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AB51">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="AC51">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="AD51">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AE51">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AF51">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="AG51">
-        <v>2.66</v>
+        <v>2.3</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK51">
-        <v>1.42</v>
+        <v>2.7</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="O74">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="P74">
-        <v>6</v>
+        <v>2.75</v>
       </c>
       <c r="Q74">
-        <v>1.82</v>
+        <v>2.92</v>
       </c>
       <c r="R74">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="S74">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="T74">
         <v>3.02</v>
       </c>
       <c r="U74">
-        <v>2.36</v>
+        <v>2.7</v>
       </c>
       <c r="V74">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
       <c r="W74">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X74">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y74">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="Z74">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="AA74">
-        <v>1.59</v>
+        <v>1.95</v>
       </c>
       <c r="AB74">
-        <v>2.21</v>
+        <v>1.83</v>
       </c>
       <c r="AC74">
-        <v>2.5</v>
+        <v>3.35</v>
       </c>
       <c r="AD74">
-        <v>1.47</v>
+        <v>1.32</v>
       </c>
       <c r="AE74">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AF74">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AG74">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AK74">
-        <v>2.8</v>
+        <v>1.57</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="O75">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="P75">
-        <v>2.75</v>
+        <v>6</v>
       </c>
       <c r="Q75">
-        <v>2.92</v>
+        <v>1.82</v>
       </c>
       <c r="R75">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="S75">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="T75">
         <v>3.02</v>
       </c>
       <c r="U75">
-        <v>2.7</v>
+        <v>2.36</v>
       </c>
       <c r="V75">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="W75">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X75">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y75">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="Z75">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="AA75">
-        <v>1.95</v>
+        <v>1.59</v>
       </c>
       <c r="AB75">
-        <v>1.83</v>
+        <v>2.21</v>
       </c>
       <c r="AC75">
-        <v>3.35</v>
+        <v>2.5</v>
       </c>
       <c r="AD75">
-        <v>1.32</v>
+        <v>1.47</v>
       </c>
       <c r="AE75">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AF75">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AG75">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AK75">
-        <v>1.57</v>
+        <v>2.8</v>
       </c>
       <c r="AL75">
         <v>0</v>

--- a/jogos_2026-08-07.xlsx
+++ b/jogos_2026-08-07.xlsx
@@ -612,54 +612,54 @@
         </is>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="O2">
-        <v>3.46</v>
+        <v>3.28</v>
       </c>
       <c r="P2">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="Q2">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="R2">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="S2">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="T2">
-        <v>2.82</v>
+        <v>2.53</v>
       </c>
       <c r="U2">
-        <v>2.94</v>
+        <v>3.04</v>
       </c>
       <c r="V2">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W2">
         <v>1.05</v>
@@ -668,74 +668,74 @@
         <v>1.07</v>
       </c>
       <c r="Y2">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z2">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="AA2">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="AB2">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AC2">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="AD2">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AE2">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF2">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AG2">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["7", "18", "58"]</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["11", "81", "90+9", "90+12"]</t>
         </is>
       </c>
       <c r="AJ2">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AK2">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN2">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO2">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP2">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
@@ -775,36 +775,36 @@
         </is>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3">
-        <v>2.26</v>
+        <v>2.35</v>
       </c>
       <c r="O3">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="P3">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="Q3">
         <v>3.02</v>
@@ -813,19 +813,19 @@
         <v>2.01</v>
       </c>
       <c r="S3">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T3">
-        <v>2.89</v>
+        <v>2.79</v>
       </c>
       <c r="U3">
-        <v>3.06</v>
+        <v>2.8</v>
       </c>
       <c r="V3">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W3">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X3">
         <v>1</v>
@@ -837,10 +837,10 @@
         <v>3.4</v>
       </c>
       <c r="AA3">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="AB3">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AC3">
         <v>3.6</v>
@@ -852,19 +852,19 @@
         <v>1.04</v>
       </c>
       <c r="AF3">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AG3">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["36", "45+7", "84", "86"]</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["17", "78", "80"]</t>
         </is>
       </c>
       <c r="AJ3">
@@ -877,28 +877,28 @@
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN3">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO3">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP3">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
@@ -929,22 +929,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -953,115 +953,115 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4">
-        <v>3.22</v>
+        <v>1.55</v>
       </c>
       <c r="O4">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="P4">
-        <v>1.78</v>
+        <v>4.6</v>
       </c>
       <c r="Q4">
-        <v>3.8</v>
+        <v>2.1</v>
       </c>
       <c r="R4">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="S4">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T4">
-        <v>2.87</v>
+        <v>3.1</v>
       </c>
       <c r="U4">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="V4">
         <v>1.44</v>
       </c>
       <c r="W4">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X4">
+        <v>1.02</v>
+      </c>
+      <c r="Y4">
+        <v>1.19</v>
+      </c>
+      <c r="Z4">
+        <v>3.75</v>
+      </c>
+      <c r="AA4">
+        <v>1.75</v>
+      </c>
+      <c r="AB4">
+        <v>2.03</v>
+      </c>
+      <c r="AC4">
+        <v>3.05</v>
+      </c>
+      <c r="AD4">
+        <v>1.33</v>
+      </c>
+      <c r="AE4">
+        <v>1.13</v>
+      </c>
+      <c r="AF4">
+        <v>1.78</v>
+      </c>
+      <c r="AG4">
+        <v>1.91</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>["21"]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>["79"]</t>
+        </is>
+      </c>
+      <c r="AJ4">
+        <v>1.25</v>
+      </c>
+      <c r="AK4">
+        <v>2.14</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
         <v>1</v>
       </c>
-      <c r="Y4">
-        <v>1.25</v>
-      </c>
-      <c r="Z4">
-        <v>4.01</v>
-      </c>
-      <c r="AA4">
-        <v>1.72</v>
-      </c>
-      <c r="AB4">
-        <v>1.97</v>
-      </c>
-      <c r="AC4">
-        <v>2.7</v>
-      </c>
-      <c r="AD4">
-        <v>1.36</v>
-      </c>
-      <c r="AE4">
-        <v>1.15</v>
-      </c>
-      <c r="AF4">
-        <v>1.7</v>
-      </c>
-      <c r="AG4">
-        <v>2.05</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ4">
-        <v>1.9</v>
-      </c>
-      <c r="AK4">
-        <v>1.2</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
-        <v>-1</v>
-      </c>
       <c r="AN4">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO4">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AP4">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
@@ -1092,16 +1092,16 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -1113,79 +1113,79 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5">
         <v>0</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5">
-        <v>1.46</v>
+        <v>1.26</v>
       </c>
       <c r="O5">
-        <v>3.8</v>
+        <v>5.15</v>
       </c>
       <c r="P5">
-        <v>4.4</v>
+        <v>8.19</v>
       </c>
       <c r="Q5">
-        <v>2.18</v>
+        <v>1.75</v>
       </c>
       <c r="R5">
-        <v>2.23</v>
+        <v>2.6</v>
       </c>
       <c r="S5">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="T5">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="U5">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="V5">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="W5">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X5">
         <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="Z5">
-        <v>3.81</v>
+        <v>4.2</v>
       </c>
       <c r="AA5">
-        <v>1.81</v>
+        <v>1.65</v>
       </c>
       <c r="AB5">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="AC5">
-        <v>3.07</v>
+        <v>2.63</v>
       </c>
       <c r="AD5">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AE5">
         <v>1.13</v>
       </c>
       <c r="AF5">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AG5">
-        <v>1.91</v>
+        <v>1.64</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["58"]</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -1194,37 +1194,37 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="AK5">
-        <v>2.08</v>
+        <v>3.35</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN5">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G6">
@@ -1283,35 +1283,35 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6">
-        <v>3.7</v>
+        <v>2.88</v>
       </c>
       <c r="O6">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P6">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="Q6">
-        <v>4.33</v>
+        <v>3.23</v>
       </c>
       <c r="R6">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="S6">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="T6">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="U6">
-        <v>2.88</v>
+        <v>2.42</v>
       </c>
       <c r="V6">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W6">
         <v>1.08</v>
@@ -1320,31 +1320,31 @@
         <v>1.04</v>
       </c>
       <c r="Y6">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z6">
-        <v>3.2</v>
+        <v>4.33</v>
       </c>
       <c r="AA6">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AB6">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AC6">
-        <v>3.29</v>
+        <v>2.84</v>
       </c>
       <c r="AD6">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="AE6">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="AF6">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AG6">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,37 +1357,37 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK6">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN6">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>0.91</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
@@ -1418,16 +1418,16 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -1439,118 +1439,118 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L7">
         <v>0</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7">
-        <v>2.91</v>
+        <v>3.56</v>
       </c>
       <c r="O7">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P7">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="Q7">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="R7">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="S7">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T7">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="U7">
-        <v>2.44</v>
+        <v>3</v>
       </c>
       <c r="V7">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W7">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X7">
+        <v>1.05</v>
+      </c>
+      <c r="Y7">
+        <v>1.26</v>
+      </c>
+      <c r="Z7">
+        <v>3.2</v>
+      </c>
+      <c r="AA7">
+        <v>1.88</v>
+      </c>
+      <c r="AB7">
+        <v>1.82</v>
+      </c>
+      <c r="AC7">
+        <v>3.29</v>
+      </c>
+      <c r="AD7">
+        <v>1.29</v>
+      </c>
+      <c r="AE7">
+        <v>1.1</v>
+      </c>
+      <c r="AF7">
+        <v>1.78</v>
+      </c>
+      <c r="AG7">
+        <v>2.02</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>["68", "90+1"]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7">
+        <v>1.29</v>
+      </c>
+      <c r="AK7">
+        <v>1.19</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>4</v>
+      </c>
+      <c r="AN7">
+        <v>3</v>
+      </c>
+      <c r="AO7">
+        <v>6</v>
+      </c>
+      <c r="AP7">
+        <v>5</v>
+      </c>
+      <c r="AQ7">
         <v>1.03</v>
       </c>
-      <c r="Y7">
-        <v>1.23</v>
-      </c>
-      <c r="Z7">
-        <v>3.45</v>
-      </c>
-      <c r="AA7">
-        <v>1.8</v>
-      </c>
-      <c r="AB7">
-        <v>1.93</v>
-      </c>
-      <c r="AC7">
-        <v>2.87</v>
-      </c>
-      <c r="AD7">
-        <v>1.42</v>
-      </c>
-      <c r="AE7">
+      <c r="AR7">
         <v>1.11</v>
       </c>
-      <c r="AF7">
-        <v>1.57</v>
-      </c>
-      <c r="AG7">
-        <v>2.25</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7">
-        <v>1.24</v>
-      </c>
-      <c r="AK7">
-        <v>1.32</v>
-      </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
-        <v>-1</v>
-      </c>
-      <c r="AN7">
-        <v>-1</v>
-      </c>
-      <c r="AO7">
-        <v>-1</v>
-      </c>
-      <c r="AP7">
-        <v>-1</v>
-      </c>
-      <c r="AQ7">
-        <v>0</v>
-      </c>
-      <c r="AR7">
-        <v>0</v>
-      </c>
       <c r="AS7">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
@@ -1581,100 +1581,100 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J8">
         <v>0</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8">
         <v>0</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8">
+        <v>1.73</v>
+      </c>
+      <c r="O8">
+        <v>3.35</v>
+      </c>
+      <c r="P8">
+        <v>4.9</v>
+      </c>
+      <c r="Q8">
+        <v>2.45</v>
+      </c>
+      <c r="R8">
+        <v>2.1</v>
+      </c>
+      <c r="S8">
+        <v>1.42</v>
+      </c>
+      <c r="T8">
+        <v>2.75</v>
+      </c>
+      <c r="U8">
+        <v>2.84</v>
+      </c>
+      <c r="V8">
+        <v>1.32</v>
+      </c>
+      <c r="W8">
+        <v>1.04</v>
+      </c>
+      <c r="X8">
+        <v>1.02</v>
+      </c>
+      <c r="Y8">
+        <v>1.36</v>
+      </c>
+      <c r="Z8">
+        <v>3.05</v>
+      </c>
+      <c r="AA8">
+        <v>2.04</v>
+      </c>
+      <c r="AB8">
+        <v>1.6</v>
+      </c>
+      <c r="AC8">
+        <v>3.83</v>
+      </c>
+      <c r="AD8">
         <v>1.26</v>
       </c>
-      <c r="O8">
-        <v>5.15</v>
-      </c>
-      <c r="P8">
-        <v>8.19</v>
-      </c>
-      <c r="Q8">
-        <v>1.75</v>
-      </c>
-      <c r="R8">
-        <v>2.6</v>
-      </c>
-      <c r="S8">
-        <v>1.27</v>
-      </c>
-      <c r="T8">
-        <v>3.25</v>
-      </c>
-      <c r="U8">
-        <v>2.55</v>
-      </c>
-      <c r="V8">
-        <v>1.51</v>
-      </c>
-      <c r="W8">
-        <v>1.11</v>
-      </c>
-      <c r="X8">
-        <v>1.03</v>
-      </c>
-      <c r="Y8">
-        <v>1.23</v>
-      </c>
-      <c r="Z8">
-        <v>4.4</v>
-      </c>
-      <c r="AA8">
-        <v>1.57</v>
-      </c>
-      <c r="AB8">
-        <v>2.25</v>
-      </c>
-      <c r="AC8">
-        <v>2.5</v>
-      </c>
-      <c r="AD8">
-        <v>1.39</v>
-      </c>
       <c r="AE8">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AF8">
         <v>1.91</v>
       </c>
       <c r="AG8">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["10", "45+2", "55"]</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
@@ -1683,37 +1683,37 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AK8">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="AL8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN8">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>0.92</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
@@ -1744,19 +1744,19 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -1768,115 +1768,115 @@
         <v>0</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9">
+        <v>3.5</v>
+      </c>
+      <c r="O9">
+        <v>3.7</v>
+      </c>
+      <c r="P9">
+        <v>1.78</v>
+      </c>
+      <c r="Q9">
+        <v>3.8</v>
+      </c>
+      <c r="R9">
+        <v>2.2</v>
+      </c>
+      <c r="S9">
+        <v>1.3</v>
+      </c>
+      <c r="T9">
+        <v>2.86</v>
+      </c>
+      <c r="U9">
+        <v>2.46</v>
+      </c>
+      <c r="V9">
+        <v>1.46</v>
+      </c>
+      <c r="W9">
+        <v>1.07</v>
+      </c>
+      <c r="X9">
+        <v>1.01</v>
+      </c>
+      <c r="Y9">
+        <v>1.25</v>
+      </c>
+      <c r="Z9">
+        <v>3.99</v>
+      </c>
+      <c r="AA9">
         <v>1.73</v>
       </c>
-      <c r="O9">
-        <v>3.35</v>
-      </c>
-      <c r="P9">
-        <v>4.45</v>
-      </c>
-      <c r="Q9">
-        <v>2.44</v>
-      </c>
-      <c r="R9">
-        <v>2.1</v>
-      </c>
-      <c r="S9">
-        <v>1.41</v>
-      </c>
-      <c r="T9">
-        <v>2.75</v>
-      </c>
-      <c r="U9">
-        <v>3.17</v>
-      </c>
-      <c r="V9">
-        <v>1.33</v>
-      </c>
-      <c r="W9">
-        <v>1.03</v>
-      </c>
-      <c r="X9">
-        <v>1.04</v>
-      </c>
-      <c r="Y9">
-        <v>1.37</v>
-      </c>
-      <c r="Z9">
-        <v>3.1</v>
-      </c>
-      <c r="AA9">
-        <v>2.04</v>
-      </c>
       <c r="AB9">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AC9">
-        <v>3.86</v>
+        <v>2.74</v>
       </c>
       <c r="AD9">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="AE9">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="AF9">
+        <v>1.62</v>
+      </c>
+      <c r="AG9">
+        <v>2.05</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>["90+3"]</t>
+        </is>
+      </c>
+      <c r="AJ9">
         <v>1.9</v>
       </c>
-      <c r="AG9">
-        <v>1.79</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9">
-        <v>1.15</v>
-      </c>
       <c r="AK9">
-        <v>1.9</v>
+        <v>1.22</v>
       </c>
       <c r="AL9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN9">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO9">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP9">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
@@ -1916,91 +1916,91 @@
         </is>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J10">
         <v>0</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L10">
         <v>0</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="O10">
-        <v>5.45</v>
+        <v>5.2</v>
       </c>
       <c r="P10">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="Q10">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="R10">
-        <v>3.03</v>
+        <v>2.63</v>
       </c>
       <c r="S10">
+        <v>1.22</v>
+      </c>
+      <c r="T10">
+        <v>4.1</v>
+      </c>
+      <c r="U10">
+        <v>2.05</v>
+      </c>
+      <c r="V10">
+        <v>1.73</v>
+      </c>
+      <c r="W10">
         <v>1.17</v>
       </c>
-      <c r="T10">
-        <v>4.15</v>
-      </c>
-      <c r="U10">
-        <v>1.94</v>
-      </c>
-      <c r="V10">
-        <v>1.8</v>
-      </c>
-      <c r="W10">
-        <v>1.18</v>
-      </c>
       <c r="X10">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z10">
-        <v>6.84</v>
+        <v>5.87</v>
       </c>
       <c r="AA10">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="AB10">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="AC10">
-        <v>1.98</v>
+        <v>2.17</v>
       </c>
       <c r="AD10">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AE10">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AF10">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AG10">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["16", "26", "51", "79"]</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
@@ -2012,34 +2012,34 @@
         <v>1.17</v>
       </c>
       <c r="AK10">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AL10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN10">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO10">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP10">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
@@ -2111,55 +2111,55 @@
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>4.75</v>
+        <v>4.65</v>
       </c>
       <c r="R11">
-        <v>2.05</v>
+        <v>2.24</v>
       </c>
       <c r="S11">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="T11">
-        <v>2.5</v>
+        <v>3.08</v>
       </c>
       <c r="U11">
-        <v>3.04</v>
+        <v>2.63</v>
       </c>
       <c r="V11">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="W11">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X11">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y11">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="Z11">
-        <v>2.87</v>
+        <v>3.94</v>
       </c>
       <c r="AA11">
-        <v>2.05</v>
+        <v>1.69</v>
       </c>
       <c r="AB11">
-        <v>1.6</v>
+        <v>2.13</v>
       </c>
       <c r="AC11">
-        <v>3.72</v>
+        <v>2.69</v>
       </c>
       <c r="AD11">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AE11">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AF11">
-        <v>1.95</v>
+        <v>1.68</v>
       </c>
       <c r="AG11">
-        <v>1.73</v>
+        <v>1.99</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.95</v>
+        <v>1.18</v>
       </c>
       <c r="AK11">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,34 +2265,34 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="O12">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P12">
-        <v>2.87</v>
+        <v>3.4</v>
       </c>
       <c r="Q12">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="R12">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="S12">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T12">
-        <v>2.79</v>
+        <v>2.95</v>
       </c>
       <c r="U12">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="V12">
         <v>1.4</v>
       </c>
       <c r="W12">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X12">
         <v>1.01</v>
@@ -2304,25 +2304,25 @@
         <v>3.8</v>
       </c>
       <c r="AA12">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB12">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC12">
         <v>2.96</v>
       </c>
       <c r="AD12">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AE12">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF12">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AG12">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK12">
-        <v>1.53</v>
+        <v>1.78</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,31 +2428,31 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.62</v>
+        <v>1.81</v>
       </c>
       <c r="O13">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P13">
-        <v>4.35</v>
+        <v>4.1</v>
       </c>
       <c r="Q13">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="R13">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="S13">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T13">
-        <v>2.67</v>
+        <v>2.88</v>
       </c>
       <c r="U13">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="V13">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="W13">
         <v>1.06</v>
@@ -2461,31 +2461,31 @@
         <v>1.02</v>
       </c>
       <c r="Y13">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z13">
-        <v>3.08</v>
+        <v>3.18</v>
       </c>
       <c r="AA13">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AB13">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AC13">
-        <v>3.38</v>
+        <v>3.42</v>
       </c>
       <c r="AD13">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE13">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF13">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AG13">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK13">
         <v>2.1</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,55 +3895,55 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="O22">
         <v>3.8</v>
       </c>
       <c r="P22">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Q22">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="R22">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="S22">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T22">
-        <v>3.2</v>
+        <v>2.86</v>
       </c>
       <c r="U22">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="V22">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W22">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X22">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y22">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="Z22">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="AA22">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AB22">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AC22">
-        <v>3.13</v>
+        <v>2.95</v>
       </c>
       <c r="AD22">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE22">
         <v>1.11</v>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AK22">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.59</v>
+        <v>4.2</v>
       </c>
       <c r="O23">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="P23">
-        <v>4.79</v>
+        <v>1.7</v>
       </c>
       <c r="Q23">
-        <v>2.06</v>
+        <v>4.3</v>
       </c>
       <c r="R23">
-        <v>2.21</v>
+        <v>2.12</v>
       </c>
       <c r="S23">
+        <v>1.33</v>
+      </c>
+      <c r="T23">
+        <v>3</v>
+      </c>
+      <c r="U23">
+        <v>2.75</v>
+      </c>
+      <c r="V23">
+        <v>1.4</v>
+      </c>
+      <c r="W23">
+        <v>1.04</v>
+      </c>
+      <c r="X23">
+        <v>1.05</v>
+      </c>
+      <c r="Y23">
+        <v>1.25</v>
+      </c>
+      <c r="Z23">
+        <v>3.4</v>
+      </c>
+      <c r="AA23">
+        <v>1.85</v>
+      </c>
+      <c r="AB23">
+        <v>1.85</v>
+      </c>
+      <c r="AC23">
+        <v>3.2</v>
+      </c>
+      <c r="AD23">
         <v>1.3</v>
       </c>
-      <c r="T23">
-        <v>3.04</v>
-      </c>
-      <c r="U23">
-        <v>2.4</v>
-      </c>
-      <c r="V23">
-        <v>1.45</v>
-      </c>
-      <c r="W23">
-        <v>1.07</v>
-      </c>
-      <c r="X23">
-        <v>1.03</v>
-      </c>
-      <c r="Y23">
-        <v>1.18</v>
-      </c>
-      <c r="Z23">
-        <v>4.33</v>
-      </c>
-      <c r="AA23">
-        <v>1.62</v>
-      </c>
-      <c r="AB23">
-        <v>2.15</v>
-      </c>
-      <c r="AC23">
-        <v>2.68</v>
-      </c>
-      <c r="AD23">
-        <v>1.44</v>
-      </c>
       <c r="AE23">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AF23">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AG23">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK23">
-        <v>2.2</v>
+        <v>1.15</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>4.2</v>
+        <v>1.83</v>
       </c>
       <c r="O24">
-        <v>3.6</v>
+        <v>3.46</v>
       </c>
       <c r="P24">
+        <v>3.75</v>
+      </c>
+      <c r="Q24">
+        <v>2.41</v>
+      </c>
+      <c r="R24">
+        <v>2.34</v>
+      </c>
+      <c r="S24">
+        <v>1.3</v>
+      </c>
+      <c r="T24">
+        <v>3.1</v>
+      </c>
+      <c r="U24">
+        <v>2.47</v>
+      </c>
+      <c r="V24">
+        <v>1.44</v>
+      </c>
+      <c r="W24">
+        <v>1.06</v>
+      </c>
+      <c r="X24">
+        <v>1.04</v>
+      </c>
+      <c r="Y24">
+        <v>1.2</v>
+      </c>
+      <c r="Z24">
+        <v>4</v>
+      </c>
+      <c r="AA24">
         <v>1.7</v>
       </c>
-      <c r="Q24">
-        <v>4.3</v>
-      </c>
-      <c r="R24">
-        <v>2.12</v>
-      </c>
-      <c r="S24">
-        <v>1.33</v>
-      </c>
-      <c r="T24">
-        <v>3</v>
-      </c>
-      <c r="U24">
-        <v>2.75</v>
-      </c>
-      <c r="V24">
+      <c r="AB24">
+        <v>2.05</v>
+      </c>
+      <c r="AC24">
+        <v>2.7</v>
+      </c>
+      <c r="AD24">
         <v>1.4</v>
       </c>
-      <c r="W24">
-        <v>1.04</v>
-      </c>
-      <c r="X24">
-        <v>1.05</v>
-      </c>
-      <c r="Y24">
-        <v>1.25</v>
-      </c>
-      <c r="Z24">
-        <v>3.4</v>
-      </c>
-      <c r="AA24">
-        <v>1.85</v>
-      </c>
-      <c r="AB24">
-        <v>1.85</v>
-      </c>
-      <c r="AC24">
-        <v>3.2</v>
-      </c>
-      <c r="AD24">
-        <v>1.3</v>
-      </c>
       <c r="AE24">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF24">
-        <v>1.78</v>
+        <v>1.59</v>
       </c>
       <c r="AG24">
-        <v>1.89</v>
+        <v>2.17</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK24">
-        <v>1.15</v>
+        <v>1.83</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,65 +4384,65 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="O25">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="P25">
-        <v>4.9</v>
+        <v>4.79</v>
       </c>
       <c r="Q25">
+        <v>2.06</v>
+      </c>
+      <c r="R25">
+        <v>2.21</v>
+      </c>
+      <c r="S25">
+        <v>1.3</v>
+      </c>
+      <c r="T25">
+        <v>3.04</v>
+      </c>
+      <c r="U25">
+        <v>2.4</v>
+      </c>
+      <c r="V25">
+        <v>1.45</v>
+      </c>
+      <c r="W25">
+        <v>1.07</v>
+      </c>
+      <c r="X25">
+        <v>1.03</v>
+      </c>
+      <c r="Y25">
+        <v>1.18</v>
+      </c>
+      <c r="Z25">
+        <v>4.33</v>
+      </c>
+      <c r="AA25">
+        <v>1.62</v>
+      </c>
+      <c r="AB25">
+        <v>2.15</v>
+      </c>
+      <c r="AC25">
+        <v>2.68</v>
+      </c>
+      <c r="AD25">
+        <v>1.44</v>
+      </c>
+      <c r="AE25">
+        <v>1.17</v>
+      </c>
+      <c r="AF25">
+        <v>1.67</v>
+      </c>
+      <c r="AG25">
         <v>2.1</v>
       </c>
-      <c r="R25">
-        <v>2.33</v>
-      </c>
-      <c r="S25">
-        <v>1.33</v>
-      </c>
-      <c r="T25">
-        <v>2.86</v>
-      </c>
-      <c r="U25">
-        <v>2.63</v>
-      </c>
-      <c r="V25">
-        <v>1.44</v>
-      </c>
-      <c r="W25">
-        <v>1.05</v>
-      </c>
-      <c r="X25">
-        <v>1</v>
-      </c>
-      <c r="Y25">
-        <v>1.21</v>
-      </c>
-      <c r="Z25">
-        <v>3.58</v>
-      </c>
-      <c r="AA25">
-        <v>1.78</v>
-      </c>
-      <c r="AB25">
-        <v>1.91</v>
-      </c>
-      <c r="AC25">
-        <v>2.95</v>
-      </c>
-      <c r="AD25">
-        <v>1.3</v>
-      </c>
-      <c r="AE25">
-        <v>1.11</v>
-      </c>
-      <c r="AF25">
-        <v>1.85</v>
-      </c>
-      <c r="AG25">
-        <v>1.85</v>
-      </c>
       <c r="AH25" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4454,7 +4454,7 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK25">
         <v>2.2</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,80 +4547,80 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="O26">
-        <v>3.46</v>
+        <v>3.8</v>
       </c>
       <c r="P26">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="Q26">
-        <v>2.41</v>
+        <v>1.98</v>
       </c>
       <c r="R26">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="S26">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T26">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U26">
-        <v>2.47</v>
+        <v>2.75</v>
       </c>
       <c r="V26">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W26">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X26">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y26">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z26">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="AA26">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AB26">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AC26">
-        <v>2.7</v>
+        <v>3.13</v>
       </c>
       <c r="AD26">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AE26">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF26">
-        <v>1.59</v>
+        <v>1.85</v>
       </c>
       <c r="AG26">
+        <v>1.85</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ26">
+        <v>1.07</v>
+      </c>
+      <c r="AK26">
         <v>2.17</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ26">
-        <v>1.19</v>
-      </c>
-      <c r="AK26">
-        <v>1.83</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -6503,22 +6503,22 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="O38">
-        <v>3.5</v>
+        <v>4.05</v>
       </c>
       <c r="P38">
         <v>3.35</v>
       </c>
       <c r="Q38">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="R38">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S38">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T38">
         <v>3.7</v>
@@ -6530,34 +6530,34 @@
         <v>1.62</v>
       </c>
       <c r="W38">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X38">
         <v>1.03</v>
       </c>
       <c r="Y38">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="Z38">
-        <v>4.8</v>
+        <v>5.15</v>
       </c>
       <c r="AA38">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AB38">
         <v>2.3</v>
       </c>
       <c r="AC38">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AD38">
         <v>1.53</v>
       </c>
       <c r="AE38">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AF38">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AG38">
         <v>2.45</v>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AK38">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,16 +6666,16 @@
         </is>
       </c>
       <c r="N39">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="O39">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P39">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="Q39">
-        <v>3.93</v>
+        <v>3.25</v>
       </c>
       <c r="R39">
         <v>2.5</v>
@@ -6687,43 +6687,43 @@
         <v>3.5</v>
       </c>
       <c r="U39">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V39">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="W39">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X39">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y39">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="Z39">
-        <v>5.35</v>
+        <v>5</v>
       </c>
       <c r="AA39">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AB39">
         <v>2.5</v>
       </c>
       <c r="AC39">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AD39">
         <v>1.62</v>
       </c>
       <c r="AE39">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF39">
         <v>1.44</v>
       </c>
       <c r="AG39">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AK39">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,10 +6829,10 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="O40">
-        <v>4.4</v>
+        <v>4.55</v>
       </c>
       <c r="P40">
         <v>5.25</v>
@@ -6844,19 +6844,19 @@
         <v>2.7</v>
       </c>
       <c r="S40">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T40">
-        <v>3.84</v>
+        <v>4.5</v>
       </c>
       <c r="U40">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="V40">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="W40">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X40">
         <v>1.01</v>
@@ -6865,22 +6865,22 @@
         <v>1.08</v>
       </c>
       <c r="Z40">
-        <v>5.65</v>
+        <v>5.5</v>
       </c>
       <c r="AA40">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AB40">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AC40">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AD40">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AE40">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AF40">
         <v>1.5</v>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AK40">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7155,19 +7155,19 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="O42">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P42">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="Q42">
-        <v>3.37</v>
+        <v>3.34</v>
       </c>
       <c r="R42">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="S42">
         <v>1.4</v>
@@ -7176,43 +7176,43 @@
         <v>2.8</v>
       </c>
       <c r="U42">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="V42">
         <v>1.33</v>
       </c>
       <c r="W42">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X42">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y42">
         <v>1.33</v>
       </c>
       <c r="Z42">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AA42">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB42">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC42">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AD42">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE42">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF42">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AG42">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AK42">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.4</v>
+        <v>1.36</v>
       </c>
       <c r="O50">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="P50">
-        <v>2.44</v>
+        <v>5.5</v>
       </c>
       <c r="Q50">
-        <v>2.8</v>
+        <v>1.83</v>
       </c>
       <c r="R50">
         <v>2.5</v>
       </c>
       <c r="S50">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T50">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="U50">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="V50">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="W50">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X50">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y50">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z50">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="AA50">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="AB50">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="AC50">
-        <v>2.16</v>
+        <v>2.41</v>
       </c>
       <c r="AD50">
         <v>1.62</v>
       </c>
       <c r="AE50">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AF50">
-        <v>1.41</v>
+        <v>1.75</v>
       </c>
       <c r="AG50">
-        <v>2.66</v>
+        <v>1.95</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AK50">
-        <v>1.42</v>
+        <v>2.9</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.43</v>
+        <v>2.4</v>
       </c>
       <c r="O51">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="P51">
-        <v>5.5</v>
+        <v>2.4</v>
       </c>
       <c r="Q51">
-        <v>1.85</v>
+        <v>2.8</v>
       </c>
       <c r="R51">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="S51">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="T51">
-        <v>3.7</v>
+        <v>3.34</v>
       </c>
       <c r="U51">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V51">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="W51">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X51">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y51">
         <v>1.13</v>
       </c>
       <c r="Z51">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AA51">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AB51">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="AC51">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="AD51">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AE51">
         <v>1.23</v>
       </c>
       <c r="AF51">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AG51">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK51">
-        <v>2.7</v>
+        <v>1.42</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -9763,37 +9763,37 @@
         </is>
       </c>
       <c r="N58">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="O58">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="P58">
         <v>1.5</v>
       </c>
       <c r="Q58">
-        <v>4.94</v>
+        <v>6.04</v>
       </c>
       <c r="R58">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="S58">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T58">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="U58">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="V58">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="W58">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X58">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y58">
         <v>1.18</v>
@@ -9802,25 +9802,25 @@
         <v>4</v>
       </c>
       <c r="AA58">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AB58">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="AC58">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="AD58">
         <v>1.4</v>
       </c>
       <c r="AE58">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AF58">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AG58">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AK58">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="O74">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="P74">
-        <v>2.75</v>
+        <v>6</v>
       </c>
       <c r="Q74">
-        <v>2.92</v>
+        <v>1.82</v>
       </c>
       <c r="R74">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="S74">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="T74">
         <v>3.02</v>
       </c>
       <c r="U74">
-        <v>2.7</v>
+        <v>2.36</v>
       </c>
       <c r="V74">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="W74">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X74">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y74">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="Z74">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="AA74">
-        <v>1.95</v>
+        <v>1.59</v>
       </c>
       <c r="AB74">
-        <v>1.83</v>
+        <v>2.21</v>
       </c>
       <c r="AC74">
-        <v>3.35</v>
+        <v>2.5</v>
       </c>
       <c r="AD74">
-        <v>1.32</v>
+        <v>1.47</v>
       </c>
       <c r="AE74">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AF74">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AG74">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AK74">
-        <v>1.57</v>
+        <v>2.8</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="O75">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="P75">
-        <v>6</v>
+        <v>2.75</v>
       </c>
       <c r="Q75">
-        <v>1.82</v>
+        <v>2.92</v>
       </c>
       <c r="R75">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="S75">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="T75">
         <v>3.02</v>
       </c>
       <c r="U75">
-        <v>2.36</v>
+        <v>2.7</v>
       </c>
       <c r="V75">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
       <c r="W75">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X75">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y75">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="Z75">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="AA75">
-        <v>1.59</v>
+        <v>1.95</v>
       </c>
       <c r="AB75">
-        <v>2.21</v>
+        <v>1.83</v>
       </c>
       <c r="AC75">
-        <v>2.5</v>
+        <v>3.35</v>
       </c>
       <c r="AD75">
-        <v>1.47</v>
+        <v>1.32</v>
       </c>
       <c r="AE75">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AF75">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AG75">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AK75">
-        <v>2.8</v>
+        <v>1.57</v>
       </c>
       <c r="AL75">
         <v>0</v>

--- a/jogos_2026-08-07.xlsx
+++ b/jogos_2026-08-07.xlsx
@@ -2082,13 +2082,13 @@
         <v>0</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11">
         <v>0</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11">
         <v>0</v>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N11">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["5"]</t>
         </is>
       </c>
       <c r="AJ11">
@@ -2181,28 +2181,28 @@
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN11">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO11">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AP11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>0.68</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>0.68</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
@@ -2242,16 +2242,16 @@
         </is>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12">
         <v>0</v>
@@ -2261,7 +2261,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N12">
@@ -2326,12 +2326,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["28", "35"]</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["7"]</t>
         </is>
       </c>
       <c r="AJ12">
@@ -2344,28 +2344,28 @@
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN12">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
@@ -2405,26 +2405,26 @@
         </is>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13">
         <v>0</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13">
         <v>0</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N13">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["33", "62"]</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
@@ -2507,28 +2507,28 @@
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
@@ -2568,13 +2568,13 @@
         </is>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2583,115 +2583,115 @@
         <v>0</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N14">
-        <v>6.83</v>
+        <v>3.65</v>
       </c>
       <c r="O14">
-        <v>5.1</v>
+        <v>3.2</v>
       </c>
       <c r="P14">
-        <v>1.34</v>
+        <v>1.91</v>
       </c>
       <c r="Q14">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="R14">
-        <v>2.49</v>
+        <v>2</v>
       </c>
       <c r="S14">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="T14">
-        <v>3.6</v>
+        <v>2.47</v>
       </c>
       <c r="U14">
-        <v>2.38</v>
+        <v>3.3</v>
       </c>
       <c r="V14">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="W14">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="X14">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y14">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="Z14">
-        <v>4.33</v>
+        <v>2.95</v>
       </c>
       <c r="AA14">
-        <v>1.57</v>
+        <v>2.15</v>
       </c>
       <c r="AB14">
-        <v>2.3</v>
+        <v>1.65</v>
       </c>
       <c r="AC14">
-        <v>2.31</v>
+        <v>3.5</v>
       </c>
       <c r="AD14">
-        <v>1.53</v>
+        <v>1.17</v>
       </c>
       <c r="AE14">
+        <v>1.03</v>
+      </c>
+      <c r="AF14">
+        <v>1.84</v>
+      </c>
+      <c r="AG14">
+        <v>1.73</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>["32"]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>["85"]</t>
+        </is>
+      </c>
+      <c r="AJ14">
+        <v>1.91</v>
+      </c>
+      <c r="AK14">
         <v>1.17</v>
       </c>
-      <c r="AF14">
-        <v>1.67</v>
-      </c>
-      <c r="AG14">
-        <v>2.05</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14">
-        <v>1.13</v>
-      </c>
-      <c r="AK14">
-        <v>1.08</v>
-      </c>
       <c r="AL14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO14">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AP14">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
@@ -2731,16 +2731,16 @@
         </is>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K15">
         <v>0</v>
@@ -2750,111 +2750,111 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N15">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="O15">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="P15">
-        <v>4.5</v>
+        <v>4.88</v>
       </c>
       <c r="Q15">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="R15">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="S15">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="T15">
-        <v>2.97</v>
+        <v>3.45</v>
       </c>
       <c r="U15">
-        <v>2.47</v>
+        <v>2.26</v>
       </c>
       <c r="V15">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="W15">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X15">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z15">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="AA15">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AB15">
-        <v>2</v>
+        <v>2.37</v>
       </c>
       <c r="AC15">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="AD15">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AE15">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AF15">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AG15">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["29", "32", "41"]</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["2", "13"]</t>
         </is>
       </c>
       <c r="AJ15">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AK15">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AL15">
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN15">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO15">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ15">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
@@ -2894,54 +2894,54 @@
         </is>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I16">
         <v>0</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N16">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="O16">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P16">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="Q16">
         <v>3.14</v>
       </c>
       <c r="R16">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S16">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T16">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U16">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="V16">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W16">
         <v>1.08</v>
@@ -2950,40 +2950,40 @@
         <v>1.04</v>
       </c>
       <c r="Y16">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z16">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AA16">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AB16">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AC16">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="AD16">
         <v>1.4</v>
       </c>
       <c r="AE16">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF16">
         <v>1.57</v>
       </c>
       <c r="AG16">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["52", "78"]</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["18", "23", "90+8"]</t>
         </is>
       </c>
       <c r="AJ16">
@@ -2996,28 +2996,28 @@
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO16">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP16">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
@@ -3057,13 +3057,13 @@
         </is>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -3072,115 +3072,115 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N17">
-        <v>1.97</v>
+        <v>1.89</v>
       </c>
       <c r="O17">
         <v>3.25</v>
       </c>
       <c r="P17">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="Q17">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="R17">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="S17">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="T17">
-        <v>2.53</v>
+        <v>2.71</v>
       </c>
       <c r="U17">
-        <v>2.88</v>
+        <v>2.67</v>
       </c>
       <c r="V17">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="W17">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X17">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y17">
+        <v>1.25</v>
+      </c>
+      <c r="Z17">
+        <v>3.6</v>
+      </c>
+      <c r="AA17">
+        <v>1.85</v>
+      </c>
+      <c r="AB17">
+        <v>1.8</v>
+      </c>
+      <c r="AC17">
+        <v>3.25</v>
+      </c>
+      <c r="AD17">
         <v>1.3</v>
       </c>
-      <c r="Z17">
-        <v>2.97</v>
-      </c>
-      <c r="AA17">
-        <v>2</v>
-      </c>
-      <c r="AB17">
-        <v>1.71</v>
-      </c>
-      <c r="AC17">
-        <v>3.34</v>
-      </c>
-      <c r="AD17">
-        <v>1.24</v>
-      </c>
       <c r="AE17">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF17">
+        <v>1.67</v>
+      </c>
+      <c r="AG17">
+        <v>1.95</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>["2"]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>["55", "78"]</t>
+        </is>
+      </c>
+      <c r="AJ17">
+        <v>1.23</v>
+      </c>
+      <c r="AK17">
+        <v>1.73</v>
+      </c>
+      <c r="AL17">
+        <v>0</v>
+      </c>
+      <c r="AM17">
+        <v>5</v>
+      </c>
+      <c r="AN17">
+        <v>4</v>
+      </c>
+      <c r="AO17">
+        <v>15</v>
+      </c>
+      <c r="AP17">
+        <v>6</v>
+      </c>
+      <c r="AQ17">
         <v>1.83</v>
       </c>
-      <c r="AG17">
-        <v>1.87</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17">
-        <v>1.33</v>
-      </c>
-      <c r="AK17">
-        <v>1.66</v>
-      </c>
-      <c r="AL17">
-        <v>0</v>
-      </c>
-      <c r="AM17">
-        <v>-1</v>
-      </c>
-      <c r="AN17">
-        <v>-1</v>
-      </c>
-      <c r="AO17">
-        <v>-1</v>
-      </c>
-      <c r="AP17">
-        <v>-1</v>
-      </c>
-      <c r="AQ17">
-        <v>0</v>
-      </c>
       <c r="AR17">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
@@ -3220,30 +3220,30 @@
         </is>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I18">
         <v>0</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N18">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="O18">
         <v>3.75</v>
@@ -3252,98 +3252,98 @@
         <v>4</v>
       </c>
       <c r="Q18">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="R18">
         <v>2.25</v>
       </c>
       <c r="S18">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T18">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
       <c r="U18">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="V18">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W18">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X18">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z18">
-        <v>3.88</v>
+        <v>3.58</v>
       </c>
       <c r="AA18">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AB18">
-        <v>2.07</v>
+        <v>1.96</v>
       </c>
       <c r="AC18">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AD18">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AE18">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF18">
         <v>1.7</v>
       </c>
       <c r="AG18">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["68", "72"]</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["9", "82"]</t>
         </is>
       </c>
       <c r="AJ18">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK18">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AL18">
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN18">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO18">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP18">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ18">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AR18">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AS18">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="AT18">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
@@ -3406,65 +3406,65 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.87</v>
+        <v>2.4</v>
       </c>
       <c r="O19">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P19">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="Q19">
-        <v>3.82</v>
+        <v>3.18</v>
       </c>
       <c r="R19">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="S19">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="T19">
-        <v>2.56</v>
+        <v>2.79</v>
       </c>
       <c r="U19">
-        <v>2.97</v>
+        <v>2.67</v>
       </c>
       <c r="V19">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="W19">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X19">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y19">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="Z19">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="AA19">
+        <v>1.85</v>
+      </c>
+      <c r="AB19">
+        <v>1.83</v>
+      </c>
+      <c r="AC19">
+        <v>3.08</v>
+      </c>
+      <c r="AD19">
+        <v>1.28</v>
+      </c>
+      <c r="AE19">
+        <v>1.08</v>
+      </c>
+      <c r="AF19">
+        <v>1.65</v>
+      </c>
+      <c r="AG19">
         <v>2.1</v>
       </c>
-      <c r="AB19">
-        <v>1.65</v>
-      </c>
-      <c r="AC19">
-        <v>3.72</v>
-      </c>
-      <c r="AD19">
-        <v>1.2</v>
-      </c>
-      <c r="AE19">
-        <v>1.04</v>
-      </c>
-      <c r="AF19">
-        <v>1.87</v>
-      </c>
-      <c r="AG19">
-        <v>1.87</v>
-      </c>
       <c r="AH19" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK19">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.6</v>
+        <v>1.41</v>
       </c>
       <c r="O20">
-        <v>3.45</v>
+        <v>4.5</v>
       </c>
       <c r="P20">
-        <v>2.25</v>
+        <v>6.17</v>
       </c>
       <c r="Q20">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R20">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="S20">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T20">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U20">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="V20">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W20">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X20">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y20">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z20">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA20">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB20">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC20">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD20">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AE20">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF20">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AG20">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AK20">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,139 +3700,139 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21">
         <v>0</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N21">
-        <v>1.41</v>
+        <v>2.51</v>
       </c>
       <c r="O21">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="P21">
-        <v>6.17</v>
+        <v>2.2</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+2", "90", "90+8"]</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["58", "69"]</t>
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL21">
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO21">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP21">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AQ21">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AR21">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AS21">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AT21">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
@@ -3863,139 +3863,139 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I22">
         <v>0</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22">
         <v>0</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N22">
-        <v>1.57</v>
+        <v>4</v>
       </c>
       <c r="O22">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="P22">
-        <v>4.9</v>
+        <v>1.72</v>
       </c>
       <c r="Q22">
-        <v>2.1</v>
+        <v>4.12</v>
       </c>
       <c r="R22">
-        <v>2.33</v>
+        <v>2.08</v>
       </c>
       <c r="S22">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T22">
-        <v>2.86</v>
+        <v>2.75</v>
       </c>
       <c r="U22">
-        <v>2.63</v>
+        <v>2.71</v>
       </c>
       <c r="V22">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="W22">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X22">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y22">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z22">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="AA22">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AB22">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AC22">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="AD22">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AE22">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF22">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG22">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["63"]</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["29", "37"]</t>
         </is>
       </c>
       <c r="AJ22">
-        <v>1.19</v>
+        <v>2</v>
       </c>
       <c r="AK22">
-        <v>2.2</v>
+        <v>1.12</v>
       </c>
       <c r="AL22">
         <v>0</v>
       </c>
       <c r="AM22">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN22">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO22">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP22">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ22">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AR22">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AS22">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT22">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
@@ -4026,19 +4026,19 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -4047,118 +4047,118 @@
         <v>0</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N23">
-        <v>4.2</v>
+        <v>1.6</v>
       </c>
       <c r="O23">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="P23">
-        <v>1.7</v>
+        <v>4.7</v>
       </c>
       <c r="Q23">
+        <v>2.05</v>
+      </c>
+      <c r="R23">
+        <v>2.38</v>
+      </c>
+      <c r="S23">
+        <v>1.27</v>
+      </c>
+      <c r="T23">
+        <v>3.25</v>
+      </c>
+      <c r="U23">
+        <v>2.38</v>
+      </c>
+      <c r="V23">
+        <v>1.53</v>
+      </c>
+      <c r="W23">
+        <v>1.08</v>
+      </c>
+      <c r="X23">
+        <v>1.03</v>
+      </c>
+      <c r="Y23">
+        <v>1.18</v>
+      </c>
+      <c r="Z23">
         <v>4.3</v>
       </c>
-      <c r="R23">
-        <v>2.12</v>
-      </c>
-      <c r="S23">
-        <v>1.33</v>
-      </c>
-      <c r="T23">
-        <v>3</v>
-      </c>
-      <c r="U23">
-        <v>2.75</v>
-      </c>
-      <c r="V23">
-        <v>1.4</v>
-      </c>
-      <c r="W23">
-        <v>1.04</v>
-      </c>
-      <c r="X23">
-        <v>1.05</v>
-      </c>
-      <c r="Y23">
-        <v>1.25</v>
-      </c>
-      <c r="Z23">
-        <v>3.4</v>
-      </c>
       <c r="AA23">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AB23">
-        <v>1.85</v>
+        <v>2.23</v>
       </c>
       <c r="AC23">
-        <v>3.2</v>
+        <v>2.49</v>
       </c>
       <c r="AD23">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AE23">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF23">
-        <v>1.78</v>
+        <v>1.64</v>
       </c>
       <c r="AG23">
-        <v>1.89</v>
+        <v>2.05</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["89"]</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["86"]</t>
         </is>
       </c>
       <c r="AJ23">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK23">
-        <v>1.15</v>
+        <v>2.11</v>
       </c>
       <c r="AL23">
         <v>0</v>
       </c>
       <c r="AM23">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO23">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ23">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AR23">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AS23">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AT23">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
@@ -4198,72 +4198,72 @@
         </is>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24">
         <v>0</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L24">
         <v>0</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N24">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="O24">
-        <v>3.46</v>
+        <v>3.3</v>
       </c>
       <c r="P24">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="Q24">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="R24">
         <v>2.34</v>
       </c>
       <c r="S24">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T24">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="U24">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="V24">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W24">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X24">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y24">
         <v>1.2</v>
       </c>
       <c r="Z24">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AA24">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AB24">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AC24">
         <v>2.7</v>
@@ -4272,56 +4272,56 @@
         <v>1.4</v>
       </c>
       <c r="AE24">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF24">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AG24">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["51", "57", "67", "76"]</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["38"]</t>
         </is>
       </c>
       <c r="AJ24">
         <v>1.19</v>
       </c>
       <c r="AK24">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AL24">
         <v>0</v>
       </c>
       <c r="AM24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP24">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ24">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AR24">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AS24">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AT24">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
@@ -4361,13 +4361,13 @@
         </is>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -4376,115 +4376,115 @@
         <v>0</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N25">
-        <v>1.59</v>
+        <v>1.73</v>
       </c>
       <c r="O25">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="P25">
-        <v>4.79</v>
+        <v>4.2</v>
       </c>
       <c r="Q25">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="R25">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="S25">
         <v>1.3</v>
       </c>
       <c r="T25">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="U25">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="V25">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W25">
         <v>1.07</v>
       </c>
       <c r="X25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z25">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AA25">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AB25">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AC25">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="AD25">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AE25">
         <v>1.17</v>
       </c>
       <c r="AF25">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG25">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["13", "32", "37"]</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["73", "77", "81"]</t>
         </is>
       </c>
       <c r="AJ25">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK25">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AL25">
         <v>0</v>
       </c>
       <c r="AM25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO25">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP25">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ25">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AR25">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AS25">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AT25">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
@@ -4524,91 +4524,91 @@
         </is>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H26">
         <v>0</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26">
         <v>0</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26">
         <v>0</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N26">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="O26">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="P26">
-        <v>5</v>
+        <v>5.98</v>
       </c>
       <c r="Q26">
         <v>1.98</v>
       </c>
       <c r="R26">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S26">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T26">
         <v>3.2</v>
       </c>
       <c r="U26">
-        <v>2.75</v>
+        <v>2.64</v>
       </c>
       <c r="V26">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W26">
         <v>1.1</v>
       </c>
       <c r="X26">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y26">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z26">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AA26">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="AB26">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="AC26">
-        <v>3.13</v>
+        <v>3</v>
       </c>
       <c r="AD26">
         <v>1.33</v>
       </c>
       <c r="AE26">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF26">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG26">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["34", "78"]</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
@@ -4626,28 +4626,28 @@
         <v>0</v>
       </c>
       <c r="AM26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN26">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO26">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ26">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AR26">
-        <v>0</v>
+        <v>0.92</v>
       </c>
       <c r="AS26">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AT26">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="O27">
-        <v>4.33</v>
+        <v>3.8</v>
       </c>
       <c r="P27">
-        <v>5.25</v>
+        <v>3.9</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA27">
+        <v>1.5</v>
+      </c>
+      <c r="AB27">
+        <v>2.32</v>
+      </c>
+      <c r="AC27">
+        <v>2.23</v>
+      </c>
+      <c r="AD27">
         <v>1.53</v>
       </c>
-      <c r="AB27">
-        <v>2.37</v>
-      </c>
-      <c r="AC27">
-        <v>0</v>
-      </c>
-      <c r="AD27">
-        <v>0</v>
-      </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,80 +4873,80 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.97</v>
+        <v>1.59</v>
       </c>
       <c r="O28">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P28">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="Q28">
+        <v>2.04</v>
+      </c>
+      <c r="R28">
         <v>2.38</v>
       </c>
-      <c r="R28">
-        <v>2.3</v>
-      </c>
       <c r="S28">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T28">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U28">
+        <v>2.34</v>
+      </c>
+      <c r="V28">
+        <v>1.56</v>
+      </c>
+      <c r="W28">
+        <v>1.09</v>
+      </c>
+      <c r="X28">
+        <v>1.04</v>
+      </c>
+      <c r="Y28">
+        <v>1.2</v>
+      </c>
+      <c r="Z28">
+        <v>4.53</v>
+      </c>
+      <c r="AA28">
+        <v>1.66</v>
+      </c>
+      <c r="AB28">
+        <v>2.15</v>
+      </c>
+      <c r="AC28">
+        <v>2.63</v>
+      </c>
+      <c r="AD28">
+        <v>1.48</v>
+      </c>
+      <c r="AE28">
+        <v>1.15</v>
+      </c>
+      <c r="AF28">
+        <v>1.6</v>
+      </c>
+      <c r="AG28">
+        <v>2.11</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ28">
+        <v>1.17</v>
+      </c>
+      <c r="AK28">
         <v>2.29</v>
-      </c>
-      <c r="V28">
-        <v>1.61</v>
-      </c>
-      <c r="W28">
-        <v>1.11</v>
-      </c>
-      <c r="X28">
-        <v>1.03</v>
-      </c>
-      <c r="Y28">
-        <v>1.11</v>
-      </c>
-      <c r="Z28">
-        <v>4.95</v>
-      </c>
-      <c r="AA28">
-        <v>1.53</v>
-      </c>
-      <c r="AB28">
-        <v>2.38</v>
-      </c>
-      <c r="AC28">
-        <v>2.24</v>
-      </c>
-      <c r="AD28">
-        <v>1.53</v>
-      </c>
-      <c r="AE28">
-        <v>1.22</v>
-      </c>
-      <c r="AF28">
-        <v>1.46</v>
-      </c>
-      <c r="AG28">
-        <v>2.53</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ28">
-        <v>1.21</v>
-      </c>
-      <c r="AK28">
-        <v>1.8</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5016,7 +5016,7 @@
         <v>0</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -5028,72 +5028,72 @@
         <v>0</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N29">
-        <v>2.37</v>
+        <v>2.6</v>
       </c>
       <c r="O29">
+        <v>3.1</v>
+      </c>
+      <c r="P29">
+        <v>2.5</v>
+      </c>
+      <c r="Q29">
+        <v>3.14</v>
+      </c>
+      <c r="R29">
+        <v>2.1</v>
+      </c>
+      <c r="S29">
+        <v>1.36</v>
+      </c>
+      <c r="T29">
+        <v>2.81</v>
+      </c>
+      <c r="U29">
+        <v>2.8</v>
+      </c>
+      <c r="V29">
+        <v>1.4</v>
+      </c>
+      <c r="W29">
+        <v>1.06</v>
+      </c>
+      <c r="X29">
+        <v>1.06</v>
+      </c>
+      <c r="Y29">
+        <v>1.3</v>
+      </c>
+      <c r="Z29">
         <v>3.2</v>
       </c>
-      <c r="P29">
-        <v>2.6</v>
-      </c>
-      <c r="Q29">
-        <v>2.98</v>
-      </c>
-      <c r="R29">
-        <v>2.15</v>
-      </c>
-      <c r="S29">
-        <v>1.33</v>
-      </c>
-      <c r="T29">
-        <v>2.95</v>
-      </c>
-      <c r="U29">
-        <v>2.62</v>
-      </c>
-      <c r="V29">
-        <v>1.42</v>
-      </c>
-      <c r="W29">
-        <v>1.07</v>
-      </c>
-      <c r="X29">
-        <v>1.05</v>
-      </c>
-      <c r="Y29">
-        <v>1.28</v>
-      </c>
-      <c r="Z29">
-        <v>3.7</v>
-      </c>
       <c r="AA29">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="AB29">
-        <v>1.96</v>
+        <v>1.88</v>
       </c>
       <c r="AC29">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="AD29">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AE29">
         <v>1.08</v>
       </c>
       <c r="AF29">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AG29">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5102,41 +5102,41 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["61"]</t>
         </is>
       </c>
       <c r="AJ29">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK29">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AL29">
         <v>0</v>
       </c>
       <c r="AM29">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP29">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ29">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="AR29">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AS29">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AT29">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
@@ -5176,13 +5176,13 @@
         </is>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30">
         <v>0</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -5195,47 +5195,47 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N30">
         <v>1.44</v>
       </c>
       <c r="O30">
-        <v>4.25</v>
+        <v>4.1</v>
       </c>
       <c r="P30">
-        <v>5.5</v>
+        <v>6.75</v>
       </c>
       <c r="Q30">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="R30">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="S30">
         <v>1.33</v>
       </c>
       <c r="T30">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="U30">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="V30">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W30">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X30">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z30">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="AA30">
         <v>1.83</v>
@@ -5247,20 +5247,20 @@
         <v>2.7</v>
       </c>
       <c r="AD30">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE30">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF30">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG30">
         <v>1.75</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["23"]</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr">
@@ -5278,28 +5278,28 @@
         <v>0</v>
       </c>
       <c r="AM30">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN30">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO30">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP30">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AQ30">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AR30">
-        <v>0</v>
+        <v>0.46</v>
       </c>
       <c r="AS30">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="AT30">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
@@ -5365,10 +5365,10 @@
         <v>3.05</v>
       </c>
       <c r="O31">
-        <v>3.42</v>
+        <v>3.35</v>
       </c>
       <c r="P31">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="Q31">
         <v>3.25</v>
@@ -5380,46 +5380,46 @@
         <v>1.28</v>
       </c>
       <c r="T31">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="U31">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
       <c r="V31">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W31">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X31">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y31">
         <v>1.2</v>
       </c>
       <c r="Z31">
-        <v>4.2</v>
+        <v>4.76</v>
       </c>
       <c r="AA31">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AB31">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="AC31">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="AD31">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AE31">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF31">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AG31">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>1.5</v>
       </c>
       <c r="AK31">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5505,13 +5505,13 @@
         <v>0</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32">
         <v>0</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32">
         <v>0</v>
@@ -5521,17 +5521,17 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N32">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="O32">
-        <v>3.64</v>
+        <v>3.55</v>
       </c>
       <c r="P32">
-        <v>3.56</v>
+        <v>3.25</v>
       </c>
       <c r="Q32">
         <v>2.5</v>
@@ -5540,13 +5540,13 @@
         <v>2.25</v>
       </c>
       <c r="S32">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="T32">
         <v>3.2</v>
       </c>
       <c r="U32">
-        <v>2.36</v>
+        <v>2.47</v>
       </c>
       <c r="V32">
         <v>1.5</v>
@@ -5561,28 +5561,28 @@
         <v>1.22</v>
       </c>
       <c r="Z32">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AA32">
         <v>1.69</v>
       </c>
       <c r="AB32">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="AC32">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AD32">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AE32">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF32">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG32">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+3"]</t>
         </is>
       </c>
       <c r="AJ32">
@@ -5604,28 +5604,28 @@
         <v>0</v>
       </c>
       <c r="AM32">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO32">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AP32">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AQ32">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AR32">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AS32">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AT32">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
@@ -5656,22 +5656,22 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H33">
         <v>0</v>
       </c>
       <c r="I33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J33">
         <v>0</v>
@@ -5684,111 +5684,111 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N33">
-        <v>1.68</v>
+        <v>3</v>
       </c>
       <c r="O33">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="P33">
-        <v>4.07</v>
+        <v>1.76</v>
       </c>
       <c r="Q33">
-        <v>2.22</v>
+        <v>3.6</v>
       </c>
       <c r="R33">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="S33">
         <v>1.26</v>
       </c>
       <c r="T33">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="U33">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="V33">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="W33">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X33">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y33">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="Z33">
-        <v>4.2</v>
+        <v>4.55</v>
       </c>
       <c r="AA33">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="AB33">
-        <v>2.21</v>
+        <v>2.29</v>
       </c>
       <c r="AC33">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AD33">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AE33">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AF33">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AG33">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
+          <t>["17", "22"]</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ33">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK33">
-        <v>2</v>
+        <v>1.21</v>
       </c>
       <c r="AL33">
         <v>0</v>
       </c>
       <c r="AM33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN33">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO33">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP33">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ33">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AR33">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AS33">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AT33">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
@@ -5819,16 +5819,16 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34">
         <v>0</v>
@@ -5840,30 +5840,30 @@
         <v>0</v>
       </c>
       <c r="K34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34">
         <v>0</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N34">
-        <v>3.45</v>
+        <v>1.71</v>
       </c>
       <c r="O34">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P34">
-        <v>1.9</v>
+        <v>3.8</v>
       </c>
       <c r="Q34">
-        <v>4.1</v>
+        <v>2.15</v>
       </c>
       <c r="R34">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S34">
         <v>1.25</v>
@@ -5872,10 +5872,10 @@
         <v>3.4</v>
       </c>
       <c r="U34">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="V34">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="W34">
         <v>1.14</v>
@@ -5884,74 +5884,74 @@
         <v>1.03</v>
       </c>
       <c r="Y34">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="Z34">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA34">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AB34">
+        <v>2.41</v>
+      </c>
+      <c r="AC34">
+        <v>2.28</v>
+      </c>
+      <c r="AD34">
+        <v>1.47</v>
+      </c>
+      <c r="AE34">
+        <v>1.2</v>
+      </c>
+      <c r="AF34">
+        <v>1.52</v>
+      </c>
+      <c r="AG34">
         <v>2.27</v>
       </c>
-      <c r="AC34">
-        <v>2.35</v>
-      </c>
-      <c r="AD34">
-        <v>1.44</v>
-      </c>
-      <c r="AE34">
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>["54"]</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ34">
         <v>1.17</v>
       </c>
-      <c r="AF34">
-        <v>1.5</v>
-      </c>
-      <c r="AG34">
-        <v>2.3</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ34">
-        <v>1.19</v>
-      </c>
       <c r="AK34">
-        <v>1.24</v>
+        <v>2</v>
       </c>
       <c r="AL34">
         <v>0</v>
       </c>
       <c r="AM34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN34">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO34">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ34">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AR34">
-        <v>0</v>
+        <v>0.98</v>
       </c>
       <c r="AS34">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AT34">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
@@ -5994,7 +5994,7 @@
         <v>0</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -6010,68 +6010,68 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N35">
-        <v>3.31</v>
+        <v>3.68</v>
       </c>
       <c r="O35">
-        <v>3.8</v>
+        <v>4.05</v>
       </c>
       <c r="P35">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="Q35">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="R35">
         <v>2.22</v>
       </c>
       <c r="S35">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="T35">
-        <v>3.34</v>
+        <v>3.58</v>
       </c>
       <c r="U35">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="V35">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="W35">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X35">
         <v>1.03</v>
       </c>
       <c r="Y35">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="Z35">
-        <v>4.75</v>
+        <v>5.25</v>
       </c>
       <c r="AA35">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AB35">
-        <v>2.3</v>
+        <v>2.58</v>
       </c>
       <c r="AC35">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AD35">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="AE35">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AF35">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AG35">
-        <v>2.37</v>
+        <v>2.42</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6080,41 +6080,41 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["-1"]</t>
         </is>
       </c>
       <c r="AJ35">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AK35">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AL35">
         <v>0</v>
       </c>
       <c r="AM35">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN35">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP35">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AQ35">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="AR35">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AS35">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AT35">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="O36">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P36">
-        <v>3.12</v>
+        <v>3.62</v>
       </c>
       <c r="Q36">
-        <v>2.83</v>
+        <v>2.54</v>
       </c>
       <c r="R36">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="S36">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T36">
-        <v>2.76</v>
+        <v>2.85</v>
       </c>
       <c r="U36">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="V36">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W36">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X36">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y36">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="Z36">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AA36">
-        <v>2.15</v>
+        <v>1.92</v>
       </c>
       <c r="AB36">
-        <v>1.66</v>
+        <v>1.83</v>
       </c>
       <c r="AC36">
-        <v>4.02</v>
+        <v>3.45</v>
       </c>
       <c r="AD36">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AE36">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF36">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AG36">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6340,58 +6340,58 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="O37">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P37">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="Q37">
-        <v>3.56</v>
+        <v>2.9</v>
       </c>
       <c r="R37">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="S37">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T37">
-        <v>3.02</v>
+        <v>3.2</v>
       </c>
       <c r="U37">
-        <v>2.41</v>
+        <v>2.48</v>
       </c>
       <c r="V37">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W37">
         <v>1.08</v>
       </c>
       <c r="X37">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y37">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z37">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AA37">
         <v>1.7</v>
       </c>
       <c r="AB37">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AC37">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="AD37">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AE37">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF37">
         <v>1.6</v>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="AK37">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.93</v>
+        <v>2.8</v>
       </c>
       <c r="O38">
-        <v>4.05</v>
+        <v>3.5</v>
       </c>
       <c r="P38">
-        <v>3.35</v>
+        <v>2.05</v>
       </c>
       <c r="Q38">
-        <v>2.38</v>
+        <v>3.25</v>
       </c>
       <c r="R38">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="S38">
         <v>1.22</v>
       </c>
       <c r="T38">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="U38">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="V38">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="W38">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X38">
         <v>1.03</v>
       </c>
       <c r="Y38">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="Z38">
-        <v>5.15</v>
+        <v>5</v>
       </c>
       <c r="AA38">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="AB38">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AC38">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AD38">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AE38">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF38">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG38">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="AK38">
-        <v>1.8</v>
+        <v>1.36</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.8</v>
+        <v>1.44</v>
       </c>
       <c r="O39">
-        <v>3.5</v>
+        <v>4.55</v>
       </c>
       <c r="P39">
-        <v>2.05</v>
+        <v>5.25</v>
       </c>
       <c r="Q39">
-        <v>3.25</v>
+        <v>1.83</v>
       </c>
       <c r="R39">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="S39">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T39">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="U39">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="V39">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="W39">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="X39">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Z39">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AA39">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AB39">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AC39">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="AD39">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AE39">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AF39">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AG39">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AK39">
-        <v>1.36</v>
+        <v>2.44</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.44</v>
+        <v>1.93</v>
       </c>
       <c r="O40">
-        <v>4.55</v>
+        <v>4.05</v>
       </c>
       <c r="P40">
-        <v>5.25</v>
+        <v>3.35</v>
       </c>
       <c r="Q40">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="R40">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="S40">
+        <v>1.22</v>
+      </c>
+      <c r="T40">
+        <v>3.7</v>
+      </c>
+      <c r="U40">
+        <v>2.2</v>
+      </c>
+      <c r="V40">
+        <v>1.62</v>
+      </c>
+      <c r="W40">
+        <v>1.13</v>
+      </c>
+      <c r="X40">
+        <v>1.03</v>
+      </c>
+      <c r="Y40">
+        <v>1.16</v>
+      </c>
+      <c r="Z40">
+        <v>5.15</v>
+      </c>
+      <c r="AA40">
+        <v>1.53</v>
+      </c>
+      <c r="AB40">
+        <v>2.3</v>
+      </c>
+      <c r="AC40">
+        <v>2.33</v>
+      </c>
+      <c r="AD40">
+        <v>1.53</v>
+      </c>
+      <c r="AE40">
         <v>1.2</v>
-      </c>
-      <c r="T40">
-        <v>4.5</v>
-      </c>
-      <c r="U40">
-        <v>2.02</v>
-      </c>
-      <c r="V40">
-        <v>1.7</v>
-      </c>
-      <c r="W40">
-        <v>1.2</v>
-      </c>
-      <c r="X40">
-        <v>1.01</v>
-      </c>
-      <c r="Y40">
-        <v>1.08</v>
-      </c>
-      <c r="Z40">
-        <v>5.5</v>
-      </c>
-      <c r="AA40">
-        <v>1.36</v>
-      </c>
-      <c r="AB40">
-        <v>2.7</v>
-      </c>
-      <c r="AC40">
-        <v>1.98</v>
-      </c>
-      <c r="AD40">
-        <v>1.7</v>
-      </c>
-      <c r="AE40">
-        <v>1.28</v>
       </c>
       <c r="AF40">
         <v>1.5</v>
       </c>
       <c r="AG40">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="AK40">
-        <v>2.44</v>
+        <v>1.8</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6992,25 +6992,25 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O41">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="P41">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="Q41">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="R41">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="S41">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="T41">
-        <v>2.36</v>
+        <v>2.74</v>
       </c>
       <c r="U41">
         <v>3.2</v>
@@ -7019,37 +7019,37 @@
         <v>1.28</v>
       </c>
       <c r="W41">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X41">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y41">
-        <v>1.45</v>
+        <v>1.28</v>
       </c>
       <c r="Z41">
-        <v>2.6</v>
+        <v>3.08</v>
       </c>
       <c r="AA41">
-        <v>2.38</v>
+        <v>2.19</v>
       </c>
       <c r="AB41">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AC41">
-        <v>4.15</v>
+        <v>4.05</v>
       </c>
       <c r="AD41">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AE41">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF41">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AG41">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AK41">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.33</v>
+        <v>2.42</v>
       </c>
       <c r="O43">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="P43">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Q43">
-        <v>3.03</v>
+        <v>3.11</v>
       </c>
       <c r="R43">
-        <v>2.46</v>
+        <v>2.37</v>
       </c>
       <c r="S43">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T43">
-        <v>3.34</v>
+        <v>3.04</v>
       </c>
       <c r="U43">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="V43">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W43">
         <v>1.11</v>
       </c>
       <c r="X43">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y43">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="Z43">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="AA43">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AB43">
-        <v>2.33</v>
+        <v>2.11</v>
       </c>
       <c r="AC43">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="AD43">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AE43">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AF43">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AG43">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK43">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7484,7 +7484,7 @@
         <v>1.6</v>
       </c>
       <c r="O44">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P44">
         <v>5.5</v>
@@ -7499,7 +7499,7 @@
         <v>1.52</v>
       </c>
       <c r="T44">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="U44">
         <v>3.3</v>
@@ -7523,10 +7523,10 @@
         <v>2.34</v>
       </c>
       <c r="AB44">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AC44">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="AD44">
         <v>1.14</v>
@@ -7535,7 +7535,7 @@
         <v>1.01</v>
       </c>
       <c r="AF44">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="AG44">
         <v>1.53</v>
@@ -7554,7 +7554,7 @@
         <v>1.29</v>
       </c>
       <c r="AK44">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7644,61 +7644,61 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="O45">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="P45">
-        <v>5.1</v>
+        <v>4.76</v>
       </c>
       <c r="Q45">
         <v>1.9</v>
       </c>
       <c r="R45">
-        <v>2.63</v>
+        <v>2.54</v>
       </c>
       <c r="S45">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T45">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="U45">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="V45">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="W45">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X45">
         <v>1.02</v>
       </c>
       <c r="Y45">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Z45">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="AA45">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB45">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="AC45">
         <v>2.1</v>
       </c>
       <c r="AD45">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AE45">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AF45">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG45">
         <v>2.28</v>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK45">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7807,65 +7807,65 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="O46">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P46">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="Q46">
         <v>2.95</v>
       </c>
       <c r="R46">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="S46">
         <v>1.28</v>
       </c>
       <c r="T46">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="U46">
-        <v>2.32</v>
+        <v>2.27</v>
       </c>
       <c r="V46">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="W46">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X46">
         <v>1.02</v>
       </c>
       <c r="Y46">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z46">
-        <v>4.25</v>
+        <v>4.4</v>
       </c>
       <c r="AA46">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AB46">
-        <v>2.19</v>
+        <v>2.35</v>
       </c>
       <c r="AC46">
+        <v>2.4</v>
+      </c>
+      <c r="AD46">
+        <v>1.56</v>
+      </c>
+      <c r="AE46">
+        <v>1.17</v>
+      </c>
+      <c r="AF46">
+        <v>1.45</v>
+      </c>
+      <c r="AG46">
         <v>2.5</v>
       </c>
-      <c r="AD46">
-        <v>1.53</v>
-      </c>
-      <c r="AE46">
-        <v>1.16</v>
-      </c>
-      <c r="AF46">
-        <v>1.5</v>
-      </c>
-      <c r="AG46">
-        <v>2.42</v>
-      </c>
       <c r="AH46" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.25</v>
+        <v>1.59</v>
       </c>
       <c r="AK46">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7970,55 +7970,55 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="O47">
-        <v>3.71</v>
+        <v>3.7</v>
       </c>
       <c r="P47">
-        <v>2.65</v>
+        <v>2.42</v>
       </c>
       <c r="Q47">
-        <v>2.63</v>
+        <v>2.99</v>
       </c>
       <c r="R47">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S47">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T47">
-        <v>3.75</v>
+        <v>3.58</v>
       </c>
       <c r="U47">
-        <v>2.12</v>
+        <v>2.29</v>
       </c>
       <c r="V47">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="W47">
         <v>1.13</v>
       </c>
       <c r="X47">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y47">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z47">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="AA47">
         <v>1.5</v>
       </c>
       <c r="AB47">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AC47">
-        <v>2.23</v>
+        <v>2.18</v>
       </c>
       <c r="AD47">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="AE47">
         <v>1.25</v>
@@ -8027,7 +8027,7 @@
         <v>1.42</v>
       </c>
       <c r="AG47">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AK47">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,16 +8133,16 @@
         </is>
       </c>
       <c r="N48">
-        <v>4.37</v>
+        <v>4.2</v>
       </c>
       <c r="O48">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="P48">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="Q48">
-        <v>4.79</v>
+        <v>4.67</v>
       </c>
       <c r="R48">
         <v>2.45</v>
@@ -8151,16 +8151,16 @@
         <v>1.25</v>
       </c>
       <c r="T48">
-        <v>3.6</v>
+        <v>3.52</v>
       </c>
       <c r="U48">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="V48">
         <v>1.62</v>
       </c>
       <c r="W48">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X48">
         <v>1.03</v>
@@ -8169,16 +8169,16 @@
         <v>1.17</v>
       </c>
       <c r="Z48">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AA48">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AB48">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AC48">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="AD48">
         <v>1.55</v>
@@ -8187,10 +8187,10 @@
         <v>1.22</v>
       </c>
       <c r="AF48">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="AG48">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK48">
         <v>1.2</v>
@@ -8296,19 +8296,19 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.33</v>
+        <v>2.39</v>
       </c>
       <c r="O49">
         <v>3.58</v>
       </c>
       <c r="P49">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="Q49">
-        <v>2.61</v>
+        <v>2.88</v>
       </c>
       <c r="R49">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="S49">
         <v>1.25</v>
@@ -8332,28 +8332,28 @@
         <v>1.12</v>
       </c>
       <c r="Z49">
-        <v>4.99</v>
+        <v>5.07</v>
       </c>
       <c r="AA49">
         <v>1.53</v>
       </c>
       <c r="AB49">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AC49">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="AD49">
         <v>1.53</v>
       </c>
       <c r="AE49">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF49">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AG49">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.36</v>
+        <v>2.4</v>
       </c>
       <c r="O50">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="P50">
-        <v>5.5</v>
+        <v>2.4</v>
       </c>
       <c r="Q50">
-        <v>1.83</v>
+        <v>2.8</v>
       </c>
       <c r="R50">
         <v>2.5</v>
       </c>
       <c r="S50">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="T50">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="U50">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="V50">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="W50">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X50">
         <v>1.03</v>
       </c>
       <c r="Y50">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z50">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="AA50">
+        <v>1.5</v>
+      </c>
+      <c r="AB50">
+        <v>2.4</v>
+      </c>
+      <c r="AC50">
+        <v>2.14</v>
+      </c>
+      <c r="AD50">
         <v>1.57</v>
       </c>
-      <c r="AB50">
-        <v>2.35</v>
-      </c>
-      <c r="AC50">
-        <v>2.41</v>
-      </c>
-      <c r="AD50">
-        <v>1.62</v>
-      </c>
       <c r="AE50">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AF50">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AG50">
-        <v>1.95</v>
+        <v>2.6</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AK50">
-        <v>2.9</v>
+        <v>1.42</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.4</v>
+        <v>1.36</v>
       </c>
       <c r="O51">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="P51">
-        <v>2.4</v>
+        <v>5.5</v>
       </c>
       <c r="Q51">
-        <v>2.8</v>
+        <v>1.83</v>
       </c>
       <c r="R51">
         <v>2.5</v>
       </c>
       <c r="S51">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="T51">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="U51">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="V51">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="W51">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X51">
         <v>1.03</v>
       </c>
       <c r="Y51">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z51">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="AA51">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AB51">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AC51">
-        <v>2.14</v>
+        <v>2.41</v>
       </c>
       <c r="AD51">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AE51">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AF51">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="AG51">
-        <v>2.6</v>
+        <v>1.95</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AK51">
-        <v>1.42</v>
+        <v>2.9</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,10 +8785,10 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="O52">
-        <v>4.35</v>
+        <v>4.5</v>
       </c>
       <c r="P52">
         <v>9</v>
@@ -8797,52 +8797,52 @@
         <v>1.8</v>
       </c>
       <c r="R52">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="S52">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T52">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="U52">
-        <v>2.54</v>
+        <v>2.69</v>
       </c>
       <c r="V52">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W52">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X52">
         <v>1</v>
       </c>
       <c r="Y52">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="Z52">
-        <v>3.58</v>
+        <v>3.65</v>
       </c>
       <c r="AA52">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AB52">
         <v>1.95</v>
       </c>
       <c r="AC52">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="AD52">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AE52">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AF52">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AG52">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AK52">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8948,16 +8948,16 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="O53">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P53">
-        <v>3.09</v>
+        <v>3.2</v>
       </c>
       <c r="Q53">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="R53">
         <v>2.2</v>
@@ -8966,13 +8966,13 @@
         <v>1.31</v>
       </c>
       <c r="T53">
-        <v>2.86</v>
+        <v>3.32</v>
       </c>
       <c r="U53">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="V53">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W53">
         <v>1.09</v>
@@ -8984,25 +8984,25 @@
         <v>1.18</v>
       </c>
       <c r="Z53">
-        <v>3.84</v>
+        <v>3.9</v>
       </c>
       <c r="AA53">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AB53">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="AC53">
         <v>2.88</v>
       </c>
       <c r="AD53">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE53">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF53">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG53">
         <v>2.2</v>
@@ -9021,7 +9021,7 @@
         <v>1.25</v>
       </c>
       <c r="AK53">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9111,22 +9111,22 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="O54">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="P54">
-        <v>2.93</v>
+        <v>2.7</v>
       </c>
       <c r="Q54">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="R54">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="S54">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T54">
         <v>2.8</v>
@@ -9135,40 +9135,40 @@
         <v>2.75</v>
       </c>
       <c r="V54">
+        <v>1.4</v>
+      </c>
+      <c r="W54">
+        <v>1.06</v>
+      </c>
+      <c r="X54">
+        <v>1</v>
+      </c>
+      <c r="Y54">
+        <v>1.21</v>
+      </c>
+      <c r="Z54">
+        <v>3.58</v>
+      </c>
+      <c r="AA54">
+        <v>1.75</v>
+      </c>
+      <c r="AB54">
+        <v>1.93</v>
+      </c>
+      <c r="AC54">
+        <v>2.88</v>
+      </c>
+      <c r="AD54">
         <v>1.36</v>
-      </c>
-      <c r="W54">
-        <v>1.04</v>
-      </c>
-      <c r="X54">
-        <v>1.02</v>
-      </c>
-      <c r="Y54">
-        <v>1.29</v>
-      </c>
-      <c r="Z54">
-        <v>3.2</v>
-      </c>
-      <c r="AA54">
-        <v>1.95</v>
-      </c>
-      <c r="AB54">
-        <v>1.8</v>
-      </c>
-      <c r="AC54">
-        <v>3.4</v>
-      </c>
-      <c r="AD54">
-        <v>1.29</v>
       </c>
       <c r="AE54">
         <v>1.08</v>
       </c>
       <c r="AF54">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AG54">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK54">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9274,61 +9274,61 @@
         </is>
       </c>
       <c r="N55">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="O55">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P55">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Q55">
         <v>2</v>
       </c>
       <c r="R55">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="S55">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="T55">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="U55">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="V55">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W55">
         <v>1.14</v>
       </c>
       <c r="X55">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y55">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z55">
-        <v>4.63</v>
+        <v>4.91</v>
       </c>
       <c r="AA55">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AB55">
+        <v>2.44</v>
+      </c>
+      <c r="AC55">
         <v>2.3</v>
       </c>
-      <c r="AC55">
-        <v>2.35</v>
-      </c>
       <c r="AD55">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AE55">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF55">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AG55">
         <v>2.15</v>
@@ -9344,7 +9344,7 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AK55">
         <v>2.25</v>
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="O56">
-        <v>3.25</v>
+        <v>3.56</v>
       </c>
       <c r="P56">
-        <v>4.16</v>
+        <v>4.1</v>
       </c>
       <c r="Q56">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="R56">
         <v>2.28</v>
       </c>
       <c r="S56">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="T56">
-        <v>2.69</v>
+        <v>2.89</v>
       </c>
       <c r="U56">
-        <v>2.73</v>
+        <v>2.43</v>
       </c>
       <c r="V56">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="W56">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X56">
         <v>1.03</v>
       </c>
       <c r="Y56">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z56">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="AA56">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="AB56">
-        <v>1.93</v>
+        <v>2.18</v>
       </c>
       <c r="AC56">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="AD56">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AE56">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF56">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AG56">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK56">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9600,16 +9600,16 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O57">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="P57">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="Q57">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="R57">
         <v>2.3</v>
@@ -9618,10 +9618,10 @@
         <v>1.29</v>
       </c>
       <c r="T57">
-        <v>3.04</v>
+        <v>2.95</v>
       </c>
       <c r="U57">
-        <v>2.54</v>
+        <v>2.47</v>
       </c>
       <c r="V57">
         <v>1.5</v>
@@ -9639,25 +9639,25 @@
         <v>4.1</v>
       </c>
       <c r="AA57">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AB57">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AC57">
-        <v>2.63</v>
+        <v>2.71</v>
       </c>
       <c r="AD57">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AE57">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AF57">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="AG57">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
         <v>1.23</v>
       </c>
       <c r="AK57">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9926,19 +9926,19 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="O59">
-        <v>4.05</v>
+        <v>4.33</v>
       </c>
       <c r="P59">
         <v>4.7</v>
       </c>
       <c r="Q59">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="R59">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="S59">
         <v>1.22</v>
@@ -9956,10 +9956,10 @@
         <v>1.14</v>
       </c>
       <c r="X59">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y59">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="Z59">
         <v>4.8</v>
@@ -9968,16 +9968,16 @@
         <v>1.5</v>
       </c>
       <c r="AB59">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AC59">
         <v>2.3</v>
       </c>
       <c r="AD59">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AE59">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AF59">
         <v>1.57</v>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AK59">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
+        <v>3</v>
+      </c>
+      <c r="O62">
+        <v>2.9</v>
+      </c>
+      <c r="P62">
+        <v>2.25</v>
+      </c>
+      <c r="Q62">
+        <v>4</v>
+      </c>
+      <c r="R62">
+        <v>1.91</v>
+      </c>
+      <c r="S62">
+        <v>1.57</v>
+      </c>
+      <c r="T62">
+        <v>2.5</v>
+      </c>
+      <c r="U62">
+        <v>3.8</v>
+      </c>
+      <c r="V62">
+        <v>1.25</v>
+      </c>
+      <c r="W62">
+        <v>1.04</v>
+      </c>
+      <c r="X62">
+        <v>1.07</v>
+      </c>
+      <c r="Y62">
+        <v>1.44</v>
+      </c>
+      <c r="Z62">
+        <v>2.43</v>
+      </c>
+      <c r="AA62">
+        <v>2.67</v>
+      </c>
+      <c r="AB62">
+        <v>1.45</v>
+      </c>
+      <c r="AC62">
+        <v>5</v>
+      </c>
+      <c r="AD62">
+        <v>1.17</v>
+      </c>
+      <c r="AE62">
+        <v>1.04</v>
+      </c>
+      <c r="AF62">
         <v>2.05</v>
       </c>
-      <c r="O62">
-        <v>3.2</v>
-      </c>
-      <c r="P62">
-        <v>3.1</v>
-      </c>
-      <c r="Q62">
-        <v>0</v>
-      </c>
-      <c r="R62">
-        <v>0</v>
-      </c>
-      <c r="S62">
-        <v>0</v>
-      </c>
-      <c r="T62">
-        <v>0</v>
-      </c>
-      <c r="U62">
-        <v>0</v>
-      </c>
-      <c r="V62">
-        <v>0</v>
-      </c>
-      <c r="W62">
-        <v>0</v>
-      </c>
-      <c r="